--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Warm goat cheese dip &amp; white pimento cheese dip by Chef Gaye Sandoz-Part 2</t>
+          <t>Sandoz bets big on biosimilars and targets $22 billion+ in sales by 2035</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WJHL</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.wjhl.com/video/warm-goat-cheese-dip-white-pimento-cheese-dip-by-chef-gaye-sandoz-part-2/12151812/</t>
+          <t>https://www.indianpharmapost.com/news/sandoz-bets-big-on-biosimilars-and-targets-22-billion-in-sales-by-2035-21812</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11-09-2026 14:30 UTC</t>
+          <t>12-09-2026 16:39 UTC</t>
         </is>
       </c>
     </row>
@@ -512,27 +512,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Servier Becomes Latest Company to License Owkin’s K Pro AI Scientist</t>
+          <t>Pharmacies run out of hormonal treatment for menopausal women and trans people</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Diari ARA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/servier-becomes-latest-company-to-license-owkins-k-pro-ai-scientist/</t>
+          <t>https://en.ara.cat/society/pharmacies-run-out-of-hormonal-treatment-for-menopausal-women-and-trans-people_1_5848398.amp.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11-09-2026 14:48 UTC</t>
+          <t>12-09-2026 18:01 UTC</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>This Week’s Top 5: Philips, NHS, Patchwork, Mars and Nokia</t>
+          <t>Wound Spray Aerosol Livestock Market Forecast to 2035: Intensified Production Animal Systems to Drive 4.5-6.5% CAGR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Healthcare Digital</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://healthcare-digital.com/news/this-weeks-top-5-philips-nhs-patchwork-mars-and-nokia</t>
+          <t>https://www.indexbox.io/blog/wound-spray-aerosol-livestock-market-forecast-to-2035-intensified-production-animal-systems-to-drive-4-5-6-5-cagr/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12-09-2026 08:08 UTC</t>
+          <t>12-09-2026 23:16 UTC</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OpenArt Director Ranks No. 1 in Anime on Physion Labs’ ARC 1.0 AI Video Agent Benchmark</t>
+          <t>Deloitte's Biopharma AI Value Estimates Come With a Timing Catch</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>MarketScale</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/openart-director-ranks-no-1-130000945.html</t>
+          <t>https://www.marketscale.com/industries/sciences/biopharma-ai-deals-now-need-validation-and-roi-timing-written-into-contracts</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12-09-2026 13:00 UTC</t>
+          <t>13-09-2026 01:25 UTC</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rx Rundown: GSK, Novartis, Ionis Pharmaceuticals and more</t>
+          <t>Roche’s collaborator MediLink announces phase III data for Tam-Peli showing significantly improved overall survival in Chinese patient population with relapsed small-cell lung cancer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medical Marketing and Media</t>
+          <t>uk.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.mmm-online.com/news/rx-rundown-gsk-novartis-ionis-pharmaceuticals-and-more/</t>
+          <t>https://uk.finance.yahoo.com/news/roche-collaborator-medilink-announces-phase-000000583.html</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11-09-2026 14:21 UTC</t>
+          <t>13-09-2026 00:00 UTC</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Livestock Embryo Collection Kits Market To 2035: Genetics Programs Drive Growth - News and Statistics</t>
+          <t>This Week’s Top 5: Philips, NHS, Patchwork, Mars and Nokia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>healthcare-digital.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/livestock-embryo-collection-kits-market-forecast-to-2035-demand-accelerates-on-dairy-and-beef-genetics-programs/</t>
+          <t>https://healthcare-digital.com/news/this-weeks-top-5-philips-nhs-patchwork-mars-and-nokia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11-09-2026 16:26 UTC</t>
+          <t>12-09-2026 08:08 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>German Investment in Colombia Gains New Momentum With Business Initiative</t>
+          <t>Receptor Occupancy Fails to Predict Immune Activation in Pembrolizumab Dosing Study</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ColombiaOne.com</t>
+          <t>Bioengineer.org</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://colombiaone.com/2026/09/11/german-investment-colombia/</t>
+          <t>https://bioengineer.org/receptor-occupancy-fails-to-predict-immune-activation-in-pembrolizumab-dosing-study/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11-09-2026 16:31 UTC</t>
+          <t>13-09-2026 02:48 UTC</t>
         </is>
       </c>
     </row>
@@ -679,103 +679,103 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Y Combinator Summer 2026 Batch Company Lumeria Launches Smartphone-Mounted Multispectral Skin Scanner</t>
+          <t>OpenArt Director Ranks No. 1 in Anime on Physion Labs’ ARC 1.0 AI Video Agent Benchmark</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ababnews.com</t>
+          <t>uk.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.ababnews.com/news/528f5545-0782-446f-b4ba-b9d2003dd29b</t>
+          <t>https://uk.finance.yahoo.com/news/openart-director-ranks-no-1-130000945.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12-09-2026 07:47 UTC</t>
+          <t>12-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Blood pressure drug recalled due to failed test</t>
+          <t>Ivonescimab Versus Pembrolizumab in First-Line PD-L1-Positive NSCLC: Positive Overall Survival Results from HARMONi-2 Presented at WCLC 2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cardiovascular Business</t>
+          <t>uk.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://cardiovascularbusiness.com/topics/clinical/hypertension/blood-pressure-drug-recalled-due-failed-test</t>
+          <t>https://uk.finance.yahoo.com/news/ivonescimab-versus-pembrolizumab-first-line-065900064.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11-09-2026 15:33 UTC</t>
+          <t>13-09-2026 06:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amgen Irish Open 2026: How to watch, TV coverage, live streams</t>
+          <t>A Year-Long Trial Finds Tiotropium Fails to Prevent Severe Asthma Attacks in Preschoolers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Golf Channel</t>
+          <t>Bioengineer.org</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.golfchannel.com/dp-world-tour/news/amgen-irish-open-2026-how-to-watch-tv-coverage-live-streams</t>
+          <t>https://bioengineer.org/a-year-long-trial-finds-tiotropium-fails-to-prevent-severe-asthma-attacks-in-preschoolers/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12-09-2026 13:28 UTC</t>
+          <t>12-09-2026 16:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Live Amgen Irish Open round 3 updates: Shane Lowry leads</t>
+          <t>Aster Guardians Global Nursing Award 2026 names Agimol Pradeep from United Kingdom winner of USD 250,000 prize - Global News Network Liberia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RTE.ie</t>
+          <t>Global News Network Liberia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.rte.ie/sport/golf/2026/0912/1591264-amgen-irish-open-round-3-updates-shane-lowry-leads/</t>
+          <t>https://gnnliberia.com/amp/aster-guardians-global-nursing-award-2026-names-agimol-pradeep-from-united-kingdom-winner-of-usd-250000-prize/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12-09-2026 13:15 UTC</t>
+          <t>13-09-2026 05:22 UTC</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amgen Irish Open Tee Times 2026: Round Three</t>
+          <t>Amgen Irish Open 2026: How to watch, TV coverage, live streams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Golf Monthly</t>
+          <t>Golf Channel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.golfmonthly.com/news/amgen-irish-open-tee-times-2026-round-three</t>
+          <t>https://www.golfchannel.com/dp-world-tour/news/amgen-irish-open-2026-how-to-watch-tv-coverage-live-streams</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12-09-2026 08:22 UTC</t>
+          <t>13-09-2026 07:34 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amgen Irish Open | Day two highlights</t>
+          <t>Watch Amgen Irish Open (Third Round)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sky Sports</t>
+          <t>Disney Plus</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/golf/video/33728/13584584/amgen-irish-open-day-two-highlights</t>
+          <t>https://www.disneyplus.com/en-do/browse/entity-4b847354-ff4a-46c9-801c-c8f9eaa7d787</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11-09-2026 19:39 UTC</t>
+          <t>13-09-2026 02:30 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amgen Irish Open Shots of the Day - Round 2</t>
+          <t>Amgen Irish Open: Shane Lowry retains lead of home event as Donald Trump arrives despite protests</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>europeantour.com</t>
+          <t>Sky Sports</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.europeantour.com/dpworld-tour/news/video/amgen-irish-open-shots-of-the-day-round-2</t>
+          <t>https://www.skysports.com/golf/news/12176/13584693/amgen-irish-open-shane-lowry-retains-lead-of-home-event-as-donald-trump-arrives-despite-protests</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11-09-2026 18:17 UTC</t>
+          <t>12-09-2026 19:10 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amgen Irish Open 2026: Best Pictures: Round 2 – Photo 8/22</t>
+          <t>Shane Lowry creates four-shot edge after Round 3 of Amgen Irish Open, Rory McIlroy struggles</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>golfpost.com</t>
+          <t>PGA Tour</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.golfpost.com/galleries/amgen-irish-open-2026-bilder-1789129223-en/8/</t>
+          <t>https://www.pgatour.com/article/news/latest/2026/09/12/shane-lowry-creates-four-shot-edge-after-round-3-of-amgen-irish-open-scores-leaderboard-results-rory-mcilroy</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12-09-2026 06:27 UTC</t>
+          <t>13-09-2026 03:04 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LIV Golf Leaderboard At The Amgen Irish Open: Big Names Well Placed Heading Into The Weekend</t>
+          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Golf Monthly</t>
+          <t>Yahoo Sports</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.golfmonthly.com/news/liv-golf-leaderboard-amgen-irish-open-2026</t>
+          <t>https://sports.yahoo.com/videos/dp-world-tour-highlights-2026-191327477.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12-09-2026 09:22 UTC</t>
+          <t>12-09-2026 19:13 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 2</t>
+          <t>Rory McIlroy enjoys seeing Shane Lowry create buzz at Amgen Irish Open</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Golf Channel</t>
+          <t>europeantour.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.golfchannel.com/watch/golf-central/dp-world-tour-highlights-2026-amgen-irish-open-round-2</t>
+          <t>https://www.europeantour.com/dpworld-tour/news/articles/detail/rory-mcilroy-enjoys-seeing-shane-lowry-create-buzz-at-amgen-irish-open/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11-09-2026 20:58 UTC</t>
+          <t>12-09-2026 17:57 UTC</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shane Lowry seizes Irish Open lead after course-record 62</t>
+          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,228 +959,228 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.golfchannel.com/dp-world-tour/news/shane-lowry-seizes-irish-open-lead-after-course-record-62</t>
+          <t>https://www.golfchannel.com/watch/dp-world-tour/dp-world-tour-highlights-2026-amgen-irish-open-round-3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11-09-2026 20:06 UTC</t>
+          <t>12-09-2026 19:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Endometriosis Market Analysis 2036: Industry Trends, Market Size, and Emerging Therapeutic Developments – DelveInsight | AbbVie, Kissei Pharma, Theramex, Hope Medicine, TiumBio, Viramal, Organon</t>
+          <t>US President Donald Trump Attends Amgen Irish Open</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Barchart.com</t>
+          <t>golfmonthly.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.barchart.com/press-releases/4567845/endometriosis-market-analysis-2036-industry-trends-market-size-and-emerging-therapeutic-developments-delveinsight-abbvie-kissei-pharma-theramex-hope-medicine-tiumbio-viramal-organon</t>
+          <t>https://www.golfmonthly.com/news/us-president-donald-trump-attends-amgen-irish-open</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12-09-2026 03:30 UTC</t>
+          <t>12-09-2026 14:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>€100 million investment plan clears way for bigger Pivot Park</t>
+          <t>Shane Lowry leads Amgen Irish Open by four shots, eyeing second home-event victory</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ioplus.nl</t>
+          <t>Golf Digest Middle East</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://ioplus.nl/en/posts/100-million-investment-plan-clears-way-for-bigger-pivot-park</t>
+          <t>https://golfdigestme.com/shane-lowry-leads-amgen-irish-open-by-four-shots-eyeing-second-home-event-victory/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12-09-2026 08:55 UTC</t>
+          <t>12-09-2026 19:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vitamin D3 may be more effective than D2; here’s why</t>
+          <t>Trump expected to hand over Amgen Irish Open trophy on visit to Ireland</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>lbc.co.uk</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/lifestyle/health/vitamin-d2-vitamin-d3-better-for-raising-vitamin-d-levels-experts-explain-10870161/</t>
+          <t>https://www.lbc.co.uk/article/trump-visit-to-ireland-golf-5HjdhL7_2/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12-09-2026 12:30 UTC</t>
+          <t>13-09-2026 05:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The harvest before the harvest</t>
+          <t>Amgen Irish Open round 3 recap: Lowry goes clear</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Down To Earth</t>
+          <t>RTE.ie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.downtoearth.org.in/agriculture/the-harvest-before-the-harvest</t>
+          <t>https://www.rte.ie/sport/golf/2026/0912/1591264-amgen-irish-open-round-3-updates-shane-lowry-leads/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12-09-2026 04:04 UTC</t>
+          <t>12-09-2026 13:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Labs Receives Two USFDA Observations For Mexico API Facility Records Assessment</t>
+          <t>Amgen Irish Open | Day three highlights</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>Sky Sports</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/dr-reddy-s-labs-receives-two-usfda-observations-for-mexico-api-facility-records-assessment-545961-PE1_C</t>
+          <t>https://www.skysports.com/golf/video/30998/13585175/amgen-irish-open-day-three-highlights</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12-09-2026 05:14 UTC</t>
+          <t>12-09-2026 19:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USFDA issues Form 483 with three observations to Strides Pharma's Alathur facility</t>
+          <t>€100 million investment plan clears way for bigger Pivot Park</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>IO+</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/regulatory/usfda-issues-form-483-with-three-observations-to-strides-pharmas-alathur-facility-21807</t>
+          <t>https://ioplus.nl/en/posts/100-million-investment-plan-clears-way-for-bigger-pivot-park</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12-09-2026 05:36 UTC</t>
+          <t>12-09-2026 08:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What to plant at your country house in autumn to have your own supply of herbs for tea</t>
+          <t>Michael Burry Says SOX 'Will Return To Earth' — And Reveals Fresh $330 Puts On Key Semiconductor ETF</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Українські Національні Новини (УНН)</t>
+          <t>Stocktwits</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://unn.ua/en/news/what-to-plant-at-your-country-house-in-autumn-to-have-your-own-supply-of-herbs-for-tea</t>
+          <t>https://stocktwits.com/news-articles/markets/equity/michael-burry-says-sox-will-return-to-earth-reveals-fresh-puts-on-key-semiconductor-etf/cZBNXiGRe2g</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12-09-2026 07:30 UTC</t>
+          <t>12-09-2026 19:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Strides Pharma gets three USFDA observations after Chennai plant inspection</t>
+          <t>Nellie Berrios Obituary (2026) - Kunkletown, PA - Gower Funeral Home &amp; Crematory, Inc. - Gilbert</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>cnbctv18.com</t>
+          <t>Legacy obituary</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/business/companies/strides-pharma-gets-three-usfda-observations-after-chennai-plant-inspection-19989720.htm/amp</t>
+          <t>https://www.legacy.com/us/obituaries/name/nellie-berrios-obituary?id=62412556</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11-09-2026 18:36 UTC</t>
+          <t>12-09-2026 23:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Far-right AfD says reported Elbit plant in Germany could aid deportation drive</t>
+          <t>Why Jonnagiri gold mine is a game-changer for India</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Haaretz</t>
+          <t>theweek.in</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.haaretz.com/israel-news/2026-09-12/ty-article/israeli-arms-maker-elbits-planned-german-plant-faces-far-right-afd-scrutiny/000001a0-928d-dfa9-ada3-dacf11c20000</t>
+          <t>https://www.theweek.in/theweek/cover/2026/09/12/why-jonnagiri-gold-mine-is-a-game-changer-for-india.html</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11-09-2026 22:40 UTC</t>
+          <t>13-09-2026 04:14 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>How Soybeans Took Over the American Diet — Without Anyone Noticing</t>
+          <t>Vitamin D3 may be more effective than D2; here’s why</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Food Manufacturing</t>
+          <t>indianexpress.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.foodmanufacturing.com/ingredients/news/22974269/how-soybeans-took-over-the-american-diet-without-anyone-noticing</t>
+          <t>https://indianexpress.com/article/lifestyle/health/vitamin-d2-vitamin-d3-better-for-raising-vitamin-d-levels-experts-explain-10870161/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11-09-2026 16:36 UTC</t>
+          <t>12-09-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Getting started with cover crops in the garden</t>
+          <t>16 Cool-Season Crops To Plant After Your Summer Tomatoes Are Done</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>myjournalcourier.com</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.myjournalcourier.com/features/article/cover-crops-keep-garden-alive-plants-not-22415101.php</t>
+          <t>https://shopping.yahoo.com/home-garden/gardening/articles/16-cool-season-crops-plant-175600148.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12-09-2026 05:32 UTC</t>
+          <t>12-09-2026 17:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KR219 can support soil activity under medium nitrogen</t>
+          <t>Tandem duplication fuels terpene diversity in gymnosperms | Newswise</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>agronews.com</t>
+          <t>Newswise</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://agronews.com/us/en/news/agricultural-blog/2026-09-11/103700</t>
+          <t>https://www.newswise.com/articles/tandem-duplication-fuels-terpene-diversity-in-gymnosperms</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12-09-2026 02:22 UTC</t>
+          <t>12-09-2026 15:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Micronutrients shape plant root defense through microbiomes and pathogen evasion</t>
+          <t>How to prepare the landscape for change of seasons</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bioengineer.org</t>
+          <t>Jacksonville Journal-Courier</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://bioengineer.org/micronutrients-shape-plant-root-defense-through-microbiomes-and-pathogen-evasion/</t>
+          <t>https://www.myjournalcourier.com/features/article/season-s-change-means-changes-landscaping-22413402.php</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11-09-2026 20:56 UTC</t>
+          <t>13-09-2026 05:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Volkswagen's Updated Multivan/Caravelle Starts Production at the Hanover Plant</t>
+          <t>13 Best Trees To Plant For Gorgeous Fall Color Every Year</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>autoevolution</t>
+          <t>Southern Living</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.autoevolution.com/news/volkswagen-s-updated-multivan-caravelle-starts-production-at-the-hanover-plant-275463.html</t>
+          <t>https://www.southernliving.com/trees-plant-for-fall-color-12117441</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11-09-2026 14:26 UTC</t>
+          <t>12-09-2026 19:29 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lineas de Nazca and the desert drawings of southern Peru</t>
+          <t>Root anatomy, metabolism and microbes team up to help plants survive nutrient scarcity</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ad-hoc-news.de</t>
+          <t>Bioengineer.org</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/unterhaltung/reisen/lineas-de-nazca-and-the-desert-drawings-of-southern-peru/70093526</t>
+          <t>https://bioengineer.org/root-anatomy-metabolism-and-microbes-team-up-to-help-plants-survive-nutrient-scarcity/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12-09-2026 13:58 UTC</t>
+          <t>12-09-2026 17:42 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,157 +1381,157 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Court blocks Trump from forcing open a dead coal plant that no one wants open</t>
+          <t>foxtail grass (2025) by CaNNNA - For Sale</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Electrek</t>
+          <t>Artsy</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://electrek.co/2026/09/11/court-blocks-trump-from-reopening-broken-coal-plant-that-no-one-wants-open/</t>
+          <t>https://www.artsy.net/artwork/cannna-foxtail-grass</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11-09-2026 17:48 UTC</t>
+          <t>12-09-2026 08:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>Nitrate Feeds Vanilla Best as Ammonium Slows Growth, Study Finds</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>Bioengineer.org</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.medicaleconomics.com/view/pfizer-s-lyme-disease-vaccine-shows-70-efficacy-texas-man-sentenced-to-12-5-years-in-61-5m-medicare-telemarketing-fraud-scheme-novo-nordisk-launches-wegovy-subscription-model-morning-medical-update</t>
+          <t>https://bioengineer.org/nitrate-feeds-vanilla-best-as-ammonium-slows-growth-study-finds/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11-09-2026 21:02 UTC</t>
+          <t>12-09-2026 19:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Long-Term Adverse Effects After COVID-19 Vaccination Vary by Brand</t>
+          <t>Brandon Petersen blunder costs Kaizer Chiefs while in-form AmaZulu march past Marumo Gallants</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Drug Topics</t>
+          <t>Magic 828</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.drugtopics.com/view/long-term-adverse-effects-after-covid-19-vaccination-vary-by-brand</t>
+          <t>https://magic828.co.za/brandon-petersen-blunder-costs-kaizer-chiefs-while-in-form-amazulu-march-past-marumo-gallants/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12-09-2026 14:08 UTC</t>
+          <t>12-09-2026 15:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Inside the deal: How a Montco biotech secured a Pfizer drug candidate</t>
+          <t>The President opened a bean processing plant in the Talas region.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>The Business Journals</t>
+          <t>open.kg</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.bizjournals.com/philadelphia/news/2026/09/11/medicus-pharma-conshohocken-pfizer-melanoma.html</t>
+          <t>https://open.kg/en/news/political-news/121702-prezident-otkryl-zavod-po-pererabotke-fasoli-v-talasskoj-oblasti.html</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11-09-2026 17:36 UTC</t>
+          <t>12-09-2026 08:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pfizer Options Spot-On: On September 11th, 77,125 Contracts Were Traded, With 2.52 Million Open Interest</t>
+          <t>Plant Sterol Bigel Rebuilds Fat Crystals for Healthier Cookies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Moomoo</t>
+          <t>Bioengineer.org</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.moomoo.com/news/post/76163315/pfizer-options-spot-on-on-september-11th-77125-contracts-were</t>
+          <t>https://bioengineer.org/plant-sterol-bigel-rebuilds-fat-crystals-for-healthier-cookies/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11-09-2026 20:30 UTC</t>
+          <t>13-09-2026 01:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AstraZeneca's breast cancer pill fails in late-stage trial</t>
+          <t>Matted fiber leaves the screens at 14 New York sewage plants packed hard enough to hold the shape of the pipe, while the flushable label that takes the blame is on a fraction of it</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>EcoPortal.net</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/astrazenecas-breast-cancer-drug-fails-late-stage-trial-2026-09-11/</t>
+          <t>https://www.ecoportal.net/en/crews-new-york-city-fourteen-sewage/37092/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11-09-2026 22:31 UTC</t>
+          <t>12-09-2026 15:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What to Know About the 2026–2027 COVID-19 Vaccines</t>
+          <t>Medicus Pharma advances SkinJect and Pfizer par...</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Verywell Health</t>
+          <t>pluang.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.verywellhealth.com/updated-covid-vaccines-fall-12075755</t>
+          <t>https://pluang.com/en/news-feed/ceo-medicus-pharma-bahas-kemajuan-skinject-dan-kerjasama-pfizer</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11-09-2026 15:20 UTC</t>
+          <t>12-09-2026 15:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AstraZeneca misses primary goal in breast cancer drug trial</t>
+          <t>AstraZeneca's oral SERD stumbles in Phase III first-line breast cancer trial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UA.NEWS</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://ua.news/en/farmatsevtika/astrazeneca-ne-dosiagla-osnovnoyi-meti-u-viprobuvanni-preparatu-vid-raku-grudei</t>
+          <t>https://firstwordpharma.com/story/7983565</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12-09-2026 06:13 UTC</t>
+          <t>13-09-2026 05:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pfizer (Backpack Securities) Analytics: Price Dynamics, Quarterly Returns, and Annual Price Changes in USD</t>
+          <t>Akeso, Summit’s ivonescimab tops Keytruda in lung cancer survival, with strong data in PD-L1-high patients</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CryptoRank</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://cryptorank.io/price/pfizer-backpack-securities/analytics</t>
+          <t>https://www.fiercepharma.com/pharma/akeso-summit-ivonescimab-tops-keytruda-lung-cancer-survival-strong-data-pd-l1-high-patients</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11-09-2026 14:42 UTC</t>
+          <t>13-09-2026 01:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1624,265 +1624,266 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Here’s Who Is Eligible for the New COVID Vaccines This Fall</t>
+          <t>Midtown Manhattan buildings evacuated after beams found buckling at construction site: Police - ABC News</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>The Healthy @Reader's Digest</t>
+          <t>ABC News - Breaking News, Latest News and Videos</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.thehealthy.com/vaccines/who-is-eligible-for-the-new-2026-covid-vaccines/</t>
+          <t>https://abcnews.com/US/midtown-manhattan-blocks-evacuated-after-beams-found-buckling/story?id=134549272</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11-09-2026 22:34 UTC</t>
+          <t>12-09-2026 21:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Scholar Rock gets first FDA nod for rare muscle-wasting disease</t>
+          <t>Medicus Pharma CEO on SkinJect and Pfizer partnership – ICYMI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KSL.com</t>
+          <t>Proactive financial news</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.ksl.com/article/51623013/us-fda-approves-scholar-rock-drug-for-rare-muscle-wasting-disease</t>
+          <t>https://www.proactiveinvestors.com/companies/news/1098450/medicus-pharma-ceo-on-skinject-and-pfizer-partnership-icymi-1098450.html</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12-09-2026 03:02 UTC</t>
+          <t>12-09-2026 10:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Andy Burnham urged to help Liverpool teen with devastating diagnosis</t>
+          <t>Tesla Futures Margins</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Liverpool Echo</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.liverpoolecho.co.uk/news/liverpool-news/andy-burnham-urged-help-liverpool-34604505</t>
+          <t>https://www.cmegroup.com/markets/equities/single-stock/tesla.margins.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12-09-2026 11:44 UTC</t>
+          <t>12-09-2026 16:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bionovis</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Biocon secures 10-Year supply contract for Pertuzumab in Brazil</t>
+          <t>Long-Term Adverse Effects After COVID-19 Vaccination Vary by Brand</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia</t>
+          <t>Drug Topics</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/25/28365/biocon-secures-10-year-supply-contract-for-pertuzumab-in-brazil.html</t>
+          <t>https://www.drugtopics.com/view/long-term-adverse-effects-after-covid-19-vaccination-vary-by-brand</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>11-09-2026 17:07 UTC</t>
+          <t>12-09-2026 14:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Mexico API facility gets two observations from USFDA</t>
+          <t>AstraZeneca's Breast Cancer Drug Camizestrant Fails Main Goal in Late-Stage Trial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/dr-reddys-mexico-api-facility-gets-two-observations-from-usfda/article71458976.ece</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/astrazenecas-breast-cancer-drug-camizestrant-fails-main-goal-in-late-stage-trial-179121</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12-09-2026 00:16 UTC</t>
+          <t>12-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Labs Receives Two USFDA Observations For Mexico API Facility Records Assessment</t>
+          <t>FINRA Appoints Marguerite Eastwood as Chief Human Resources Officer</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/dr-reddy-s-labs-receives-two-usfda-observations-for-mexico-api-facility-records-assessment-545961-PE1_C</t>
+          <t>https://hrtoday.in/finra-appoints-marguerite-eastwood-as-chief-human-resources-officer/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12-09-2026 05:14 UTC</t>
+          <t>12-09-2026 20:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dr Reddy’s US food and drug administration inspection of Mexico facility ends with two observations</t>
+          <t>AstraZeneca’s Etcamah flunks first-line breast cancer trial, adding to oral SERDs’ failure record</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>telegraphindia.com</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.telegraphindia.com/business/dr-reddys-us-food-and-drug-administration-inspection-of-mexico-api-facility-ends-with-two-observations/cid/2179564</t>
+          <t>https://www.fiercepharma.com/pharma/astrazeneca-etcamah-flunks-first-line-breast-cancer-trial-adding-oral-serds-failure-record</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12-09-2026 04:05 UTC</t>
+          <t>12-09-2026 16:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dr Reddy's Mexico API facility gets 2 observations in US FDA records assessment</t>
+          <t>Biogen Sees Pivotal Pipeline Moment as It Expands Beyond Neurology</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>cnbctv18.com</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/market/stocks/dr-reddys-laboratories-share-price-mexico-api-facility-gets-2-observations-in-us-fda-records-assessment-19989712.htm</t>
+          <t>https://finance.yahoo.com/healthcare/articles/biogen-sees-pivotal-pipeline-moment-210158269.html</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>11-09-2026 18:21 UTC</t>
+          <t>12-09-2026 21:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nifty 50 Today: Closing Bell Market Wrap, 11 September 2026</t>
+          <t>Exclusive | Walmart continues stocking air freshener packed with cancer-causing benzene: lawsuit</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>New York Post</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://univest.in/blogs/nifty-50-today-closing-bell-2026</t>
+          <t>https://nypost.com/2026/09/12/us-news/walmart-air-freshener-packed-with-cancer-causing-benzene-lawsuit/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>11-09-2026 20:16 UTC</t>
+          <t>12-09-2026 14:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Mexico API Plant Receives Two USFDA Observations</t>
+          <t>Andy Burnham urged to intervene to introduce new drug to tackle
+rare disease</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Manchester Evening News</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Mexico-API-Plant-Receives-Two-USFDA-Observations/6aa49cf075fe79b492e4669b</t>
+          <t>https://www.manchestereveningnews.co.uk/news/uk-news/andy-burnham-urged-intervene-introduce-34607984.amp</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>12-09-2026 00:29 UTC</t>
+          <t>12-09-2026 13:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1895,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s: USFDA Completes Assessment at Mexico API Facility</t>
+          <t>UPI has transformed financial inclusion: former RBI Governor</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>InvestyWise</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.investywise.com/dr-reddys-laboratories-usfda-records-assessment-update/</t>
+          <t>https://www.thehindu.com/news/cities/Hyderabad/upi-has-transformed-financial-inclusion-former-rbi-governor/article71460905.ece/amp/</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>11-09-2026 20:58 UTC</t>
+          <t>12-09-2026 17:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1922,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>USFDA completes records assessment at Dr. Reddy's Mexico facility, issues two observations</t>
+          <t>Telangana Vegetable Cultivation Decline Raises Hyderabad Food Risk</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>urbanacres.in</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://businessupturn.com/business/usfda-completes-records-assessment-at-dr-reddys-mexico-facility-issues-two-observations/</t>
+          <t>https://urbanacres.in/telangana-vegetable-cultivation-collapse-exposes-hyderabads-food-risk/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>11-09-2026 22:34 UTC</t>
+          <t>12-09-2026 13:19 UTC</t>
         </is>
       </c>
     </row>
@@ -1948,103 +1949,103 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>USFDA Issues Observations After Reviewing Dr. Reddy’s Mexico API Facility</t>
+          <t>KUDA chief assumes role as TDP election observer for Sri Sathya Sai dist</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>The Hans India</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/usfda-issues-observations-after-reviewing-dr-reddys-mexico-api-facility</t>
+          <t>https://www.thehansindia.com/news/cities/anantapur/kuda-chief-assumes-role-as-tdp-election-observer-for-sri-sathya-sai-dist-1121288</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>11-09-2026 20:27 UTC</t>
+          <t>12-09-2026 22:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Laboratories: ਮੈਕਸੀਕੋ ਪਲਾਂਟ ਨੂੰ ਲੈ ਕੇ USFDA ਦੀ ਨਾਰਾਜ਼ਗੀ, ਮਿਲੀਆਂ **2** ਓਬਜ਼ਰਵੇਸ਼ਨਾਂ</t>
+          <t>Lupin eyes $500 mn biosimilars revenue in medium term, to ramp capacity</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/news/Punjabi/healthcarebiotech/Dr-Reddys-Mexico-API-Plant-Receives-Two-USFDA-Observations/6aa49cf075fe79b492e4669b</t>
+          <t>https://www.business-standard.com/industry/news/companies-news-lupin-eyes-500-mn-biosimilars-revenue-in-medium-term-126091300205_1.html</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>12-09-2026 00:29 UTC</t>
+          <t>13-09-2026 06:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dr. Reddy's: मैक्सिको प्लांट पर USFDA की नजर, मिली **2** ऑब्जर्वेशन</t>
+          <t>15 startups, four student teams win C-CAMP National Bio Entrepreneurship Competition</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/corporate-news/Hindi/healthcarebiotech/Dr-Reddys-Receives-Two-USFDA-Observations-for-Mexico-API-Facility/6aa42ec7f2017017ae692928</t>
+          <t>https://www.newindianexpress.com/states/karnataka/2026/Sep/13/15-startups-four-student-teams-win-c-camp-national-bio-entrepreneurship-competition</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>11-09-2026 16:40 UTC</t>
+          <t>13-09-2026 01:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dr. Reddy's: మెక్సికో ప్లాంట్‌పై USFDA అబ్జర్వేషన్స్.. ఇన్వెస్టర్లు భయపడాలా?</t>
+          <t>Sanjeev Kathuria Appointed Director, Business Unit Head – Oncology Cluster at Cipla</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/corporate-news/Telugu/healthcarebiotech/Dr-Reddys-Receives-Two-USFDA-Observations-for-Mexico-API-Facility/6aa42ec7f2017017ae692928</t>
+          <t>https://hrtoday.in/sanjeev-kathuria-appointed-director-business-unit-head-oncology-cluster-at-cipla/</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11-09-2026 16:40 UTC</t>
+          <t>13-09-2026 06:14 UTC</t>
         </is>
       </c>
     </row>
@@ -2056,238 +2057,238 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Biocon secures 10-Year supply contract for Pertuzumab in Brazil</t>
+          <t>Nagaland: State review meeting highlights growing oral cancer burden</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia</t>
+          <t>Eastern Mirror</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/26/28365/biocon-secures-10-year-supply-contract-for-pertuzumab-in-brazil.html</t>
+          <t>https://www.easternmirrornagaland.com/nagaland-state-review-meeting-highlights-growing-oral-cancer-burden</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>11-09-2026 17:07 UTC</t>
+          <t>12-09-2026 13:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nagaland: State review meeting highlights growing oral cance</t>
+          <t>Aurobindo Pharma Injects $1 Million into New U.S. R&amp;D Arm After A1 Biochem Deal</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eastern Mirror</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.easternmirrornagaland.com/nagaland-state-review-meeting-highlights-growing-oral-cancer-burden</t>
+          <t>https://www.tipranks.com/news/company-announcements/aurobindo-pharma-injects-1-million-into-new-u-s-rd-arm-after-a1-biochem-deal</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>12-09-2026 13:02 UTC</t>
+          <t>12-09-2026 09:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NOHP review, oral cancer orientation at NHAK</t>
+          <t>Making sovereign, open-weight AI the technology frontier</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nagaland Post</t>
+          <t>mistral.ai</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://nagalandpost.com/nohp-review-oral-cancer-orientation-at-nhak/</t>
+          <t>https://mistral.ai/news/mistral-makes-sovereign-open-weight-ai-to-frontier/</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>12-09-2026 05:27 UTC</t>
+          <t>13-09-2026 06:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma acquires 100% stake in A1 Biochem USA for $1 million</t>
+          <t>Best Camera Phones Under Rs. 30,000 in India: Samsung Galaxy F70 Pro 5G, Motorola Edge 70 Fusion, More</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-acquires-100-stake-a1-biochem-usa-1-million/50744648</t>
+          <t>https://www.gadgets360.com/mobiles/features/best-camera-phones-in-india-under-rs-30000-samsung-galaxy-f70-pro-5g-motorola-edge-70-fusion-12028297</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>12-09-2026 07:47 UTC</t>
+          <t>13-09-2026 06:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma adds Emkay Global meeting to September 17 schedule</t>
+          <t>Why Samsung fans are suddenly more excited about the Galaxy Z Fold 9</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>sammobile.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-hold-investor-meetings-kotak-healthcare-forum-2026/50661004</t>
+          <t>https://www.sammobile.com/news/why-samsung-fans-suddenly-more-excited-galaxy-z-fold-9/</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>11-09-2026 16:26 UTC</t>
+          <t>13-09-2026 04:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AUROBINDO PHARMA: Acquires 100% Stake in US Subsidiary</t>
+          <t>Samsung Galaxy S26 FE's India price leaks - GSMArena.com news</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>InvestyWise</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.investywise.com/aurobindo-pharma-limited-acquires-stake-in-a1-biochem-usa-inc/</t>
+          <t>https://www.gsmarena.com/samsung_galaxy_s26_fe_india_price_leaks-news-74595.php</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>12-09-2026 07:23 UTC</t>
+          <t>12-09-2026 16:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma invests USD 1,000,000 in newly subsidiary in the USA</t>
+          <t>Samsung Innovation Campus AI Program (Saudi Arabia)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>fundsforNGOs</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://businessupturn.com/business/aurobindo-pharma-invests-usd-1-000-000-in-newly-subsidiary-in-the-usa/</t>
+          <t>https://www2.fundsforngos.org/innovation/samsung-innovation-campus-ai-program-saudi-arabia/</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>12-09-2026 07:35 UTC</t>
+          <t>12-09-2026 21:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Injects $1 Million into New U.S. R&amp;D Arm After A1 Biochem Deal</t>
+          <t>Samsung’s Galaxy SmartTag3 Leak Shows a New Shape, and No Keyring Hole</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>AndroidPure</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/aurobindo-pharma-injects-1-million-into-new-u-s-rd-arm-after-a1-biochem-deal</t>
+          <t>https://www.androidpure.com/samsung-galaxy-smarttag3-no-keyring-hole/</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>12-09-2026 09:03 UTC</t>
+          <t>12-09-2026 23:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Gets CDSCO Panel Nod for OERIS, World's First Extended-Release Ondansetron Injection</t>
+          <t>Users complain Samsung accounts are being deactivated</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/cdsco/shilpa-medicare-gets-cdsco-panel-nod-for-oeris-worlds-first-extended-release-ondansetron-injection-179085</t>
+          <t>https://mashable.com/tech/samsung-account-randomly-deactivated-issue</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>11-09-2026 14:53 UTC</t>
+          <t>12-09-2026 17:06 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2300,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Making sovereign, open-weight AI the technology frontier</t>
+          <t>Samsung Galaxy S26 FE Price in India Revealed: Exynos 2500 &amp; Slower USB 2.0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>mistral.ai</t>
+          <t>PaidFreeDroid</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://mistral.ai/news/mistral-makes-sovereign-open-weight-ai-to-frontier/</t>
+          <t>https://paidfreedroid.com/2026/09/samsung-galaxy-s26-fe-price-india-exynos-2500-specs.html</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>12-09-2026 08:52 UTC</t>
+          <t>12-09-2026 19:28 UTC</t>
         </is>
       </c>
     </row>
@@ -2326,22 +2327,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The new iPhone is here, but you can buy the Samsung Galaxy S26 FE and get a $200 gift card for free</t>
+          <t>Samsung Galaxy Connect Now Works on More Windows PCs, and We Tested It</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>SammyGuru</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://mashable.com/tech/sept-11-samsung-galaxy-gift-card-deal</t>
+          <t>https://sammyguru.com/galaxy-connect-more-windows-pcs-tested/</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>12-09-2026 12:26 UTC</t>
+          <t>13-09-2026 04:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2353,22 +2354,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 FE price in India revealed: here’s how much it costs</t>
+          <t>Samsung Galaxy Book 6 Pro review: every inch the professional</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>91mobiles.com</t>
+          <t>Creative Bloq</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.91mobiles.com/hub/samsung-galaxy-s26-fe-india-price-revealed/</t>
+          <t>https://www.creativebloq.com/tech/laptops/samsung-galaxy-book-6-pro-review-every-inch-the-professional</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12-09-2026 07:28 UTC</t>
+          <t>13-09-2026 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2380,22 +2381,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Samsung may charge Apple $250 for each foldable iPhone display under reported three-year deal</t>
+          <t>Google has gotten lazy with Android and these Samsung apps prove it</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>MakeUseOf</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/cons-products/electronics/samsung-may-charge-apple-250-for-each-foldable-iphone-display-under-reported-three-year-deal/articleshow/134104415.cms</t>
+          <t>https://www.makeuseof.com/google-has-gotten-lazy-with-android-and-these-samsung-apps-prove-it/</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12-09-2026 02:54 UTC</t>
+          <t>12-09-2026 18:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,22 +2408,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A08 retailer listing gives us specs and official images - GSMArena.com news</t>
+          <t>Dua Lipa’s Samsung Lawsuit Update: Tech Giant Says Singer Can’t Sue Over Her Image on TV Boxes</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>justjared.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.gsmarena.com/samsung_galaxy_a08_retailer_listing_gives_us_specs_and_official_images-news-74590.php</t>
+          <t>https://www.justjared.com/2026/09/13/dua-lipas-samsung-lawsuit-update-tech-giant-says-singer-cant-sue-over-her-image-on-tv-boxes/</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>11-09-2026 20:47 UTC</t>
+          <t>13-09-2026 04:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2434,22 +2435,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Samsung Trolls Apple by Hiring 'Tim Cook' to Endorse Galaxy Z Fold 8</t>
+          <t>Samsung Electronics Opens Fall Semester Enrollment for Galaxy AI Experience Classes Targeting South Korean Elementary and Middle Schoolers</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>pcmag.com</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pcmag.com/news/samsung-trolls-hiring-tim-cook-to-endorse-galaxy-z-fold-8-apple-event</t>
+          <t>https://finance.biggo.com/news/77f6fcfc-c52a-4a4d-bc28-e04ffafbbe62</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>12-09-2026 07:45 UTC</t>
+          <t>13-09-2026 05:05 UTC</t>
         </is>
       </c>
     </row>
@@ -2461,22 +2462,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The hidden Samsung One UI feature that turned me into a Galaxy power user</t>
+          <t>Best Samsung Galaxy phone deals: Save $250 at Amazon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Android Police</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.androidpolice.com/hidden-samsung-one-ui-feature-turned-me-into-galaxy-power-user/</t>
+          <t>https://mashable.com/tech/sept-11-samsung-galaxy-phone-deals</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>12-09-2026 12:15 UTC</t>
+          <t>12-09-2026 15:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2488,967 +2489,373 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 FE India Price Leaks Ahead of September 18 Launch: Here Is What It Might Cost</t>
+          <t>A new software update is rolling out to the Galaxy A57</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>nokiapoweruser.com</t>
+          <t>sammobile.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://nokiapoweruser.com/amsung-galaxy-s26-fe-india-price-leak-launch-date/</t>
+          <t>https://www.sammobile.com/news/galaxy-a57-september-2026-security-patch-released/</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>12-09-2026 11:26 UTC</t>
+          <t>12-09-2026 08:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 FE Specifications: Full Breakdown of Chip, Camera, Display and Battery</t>
+          <t>GSK’s ADC lays down marker for lung cancer scrap with Merck</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Khusoko</t>
+          <t>Fierce Biotech</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://khusoko.com/2026/09/12/samsung-galaxy-s26-fe-specifications/</t>
+          <t>https://www.fiercebiotech.com/biotech/gsks-adc-lays-down-marker-lung-cancer-scrap-merck-co</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>12-09-2026 09:42 UTC</t>
+          <t>12-09-2026 22:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 FE pricing for India leaks</t>
+          <t>Manipal Hospitals scouts for acquisitions in Andhra, Keralam, Delhi-NCR; bets on AI-led healthcare</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>sammobile.com</t>
+          <t>economictimes.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/galaxy-s26-fe-india-price-leaks/</t>
+          <t>https://m.economictimes.com/industry/healthcare/biotech/healthcare/manipal-hospitals-scouts-for-acquisitions-in-andhra-keralam-delhi-ncr-bets-on-ai-led-healthcare/articleshow/134179222.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>12-09-2026 07:20 UTC</t>
+          <t>13-09-2026 05:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Samsung Adds Galaxy S26, S26 Ultra To Renewed Lineup: What Buyers Get</t>
+          <t>Leaders of BRICS countries call for stronger cooperation in health, endorse initiatives on tuberculosis</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>APAC Media</t>
+          <t>economictimes.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://apacnewsnetwork.com/2026/09/samsung-adds-galaxy-s26-s26-ultra-to-renewed-lineup-what-buyers-get/</t>
+          <t>https://m.economictimes.com/industry/healthcare/biotech/healthcare/leaders-of-brics-countries-call-for-stronger-cooperation-in-health-endorse-initiatives-on-tb/articleshow/134139783.cms</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>12-09-2026 05:21 UTC</t>
+          <t>12-09-2026 15:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Samsung is reportedly making Apple’s first foldable phone, iPhone Duo's biggest component and will get $2</t>
+          <t>AstraZeneca breast cancer pill misses mark in pivotal trial, STAT reports</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>streamlinefeed.co.ke</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/technology/mobiles-tabs/samsung-is-reportedly-making-apples-first-foldable-phone-iphone-duos-biggest-component-and-will-get-250-per-device/articleshow/134080969.cms</t>
+          <t>https://streamlinefeed.co.ke/news/astrazeneca-breast-cancer-pill-misses-mark-in-pivotal-trial-stat-reports</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>11-09-2026 17:26 UTC</t>
+          <t>12-09-2026 08:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Samsung E&amp;A lands $3.5 billion Saudi fertilizer project</t>
+          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indian Chemical News</t>
+          <t>Stocktwits</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.indianchemicalnews.com/fertilizer/samsung-ea-lands-35-billion-saudi-fertilizer-project-31859</t>
+          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>12-09-2026 03:42 UTC</t>
+          <t>12-09-2026 17:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Polpharma</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>How Samsung turned Apple’s first foldable into a global competitive-marketing moment</t>
+          <t>Biosimilar race: Sandoz expands pipeline with Henlius, Teva secures ocrelizumab candidate</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Exchange4Media</t>
+          <t>Generics and Biosimilars Initiative</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/marketing-news/how-samsung-turned-apples-first-foldable-into-a-global-competitive-marketing-moment-158175.html</t>
+          <t>https://gabionline.net/es/noticias-farmaceuticas/biosimilar-race-sandoz-expands-pipeline-with-henlius-teva-secures-ocrelizumab-candidate</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>12-09-2026 02:52 UTC</t>
+          <t>12-09-2026 13:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro, iPhone 18 Pro Max Vs Galaxy S26 Ultra: Complete comparison of price, display, camera, perfo</t>
+          <t>Sandu Pharmaceuticals: Board Approves New Chairman and Director Appointments</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>InvestyWise</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/magazines/panache/iphone-18-pro-pro-max-vs-galaxy-s26-ultra-complete-comparison-of-price-display-camera-performance-and-ai-features/articleshow/133981382.cms</t>
+          <t>https://www.investywise.com/sandu-pharmaceuticals-limited-key-management-appointments/</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>12-09-2026 09:26 UTC</t>
+          <t>12-09-2026 12:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IHH Healthcare suffers losses due to MTO approval delay for Fortis acquisition</t>
+          <t>Teva Pharmaceuticals Seeks FDA Greenlight For New Schizophrenia Treatment</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Medical Buyer</t>
+          <t>Stocktwits</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/ihh-healthcare-suffers-losses-due-to-mto-approval-delay-for-fortis-acquisition/</t>
+          <t>https://stocktwits.com/news-articles/markets/equity/teva-pharmaceuticals-seeks-fda-greenlight-for-schizophrenia-treatment/cZRNir1R4xt</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>12-09-2026 06:33 UTC</t>
+          <t>12-09-2026 15:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Imported dialysis solution fails endotoxin test in Himachal; lab flags nine regulatory violations</t>
+          <t>Teva’s $4.9 Billion Bond Sale Pushes Its Debt Wall Into the 2030s</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>TechStock²</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/healthcare/biotech/healthcare/imported-dialysis-solution-fails-endotoxin-test-in-himachal-lab-flags-nine-regulatory-violations/articleshow/134085795.cms</t>
+          <t>https://ts2.tech/en/tevas-4-9-billion-bond-sale-pushes-its-debt-wall-into-the-2030s/</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>11-09-2026 18:47 UTC</t>
+          <t>12-09-2026 10:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SERENA-4 Trial: Etcamah, Palbociclib in ER+ Breast Cancer</t>
+          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mirage News</t>
+          <t>Stocktwits</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.miragenews.com/serena-4-trial-etcamah-palbociclib-in-er-breast-1743006/</t>
+          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>11-09-2026 21:07 UTC</t>
+          <t>12-09-2026 17:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Jamp Pharma</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Coforge Independent Director DK Singh resigns with immediate effect</t>
+          <t>Aurora Cannabis Taps Pharma Veteran to Drive Global Commercial Push</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://businessupturn.com/business/corporates/coforge-independent-director-dk-singh-resigns-with-immediate-effect/</t>
+          <t>https://www.tipranks.com/news/company-announcements/aurora-cannabis-taps-pharma-veteran-to-drive-global-commercial-push</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>11-09-2026 15:50 UTC</t>
+          <t>12-09-2026 15:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JSW Infrastructure gets LoI for Inland Container Depot in Karnataka’s Ballari</t>
+          <t>Samsung Bioepis Named Top Job-Creating Company</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://businessupturn.com/business/corporates/jsw-infrastructure-gets-loi-to-set-up-inland-container-depot-in-karnataka-facility-to-be-operational-within-a-year/</t>
+          <t>https://www.thelec.net/news/articleView.html?idxno=13875</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>11-09-2026 16:18 UTC</t>
+          <t>12-09-2026 23:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Polpharma Biologics</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Coforge independent director DK Singh resigns; board begins global search for additional directors</t>
+          <t>Biosimilar race: Sandoz expands pipeline with Henlius, Teva secures ocrelizumab candidate</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>Generics and Biosimilars Initiative</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.businessupturn.com/business/corporates/coforge-independent-director-dk-singh-resigns-vivek-sharma-to-lead-global-search-for-new-board-members/</t>
+          <t>https://gabionline.net/es/noticias-farmaceuticas/biosimilar-race-sandoz-expands-pipeline-with-henlius-teva-secures-ocrelizumab-candidate</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>11-09-2026 16:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Stocktwits</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>12-09-2026 08:12 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>JCR Pharma</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>MEDIPAL HOLDINGS CORPORATION and JCR Pharmaceuticals Dose First Patient in Global Phase I/II Trial of JR-446 for Mucopolysaccharidosis Type IIIB</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>https://finance.yahoo.com/healthcare/articles/medipal-holdings-corporation-jcr-pharmaceuticals-161100817.html</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>11-09-2026 16:11 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Respiratory Cachexia Nutrition Market</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Future Market Insights</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>https://www.futuremarketinsights.com/reports/respiratory-cachexia-nutrition-market</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>12-09-2026 06:44 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Cancer Patients Needing Ifosfamide Chemotherapy May Receive an Unapproved Imported Version as the U.S. Shortage Persists</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Medical Daily</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>https://www.medicaldaily.com/imported-ifosfamide-shortage-cancer-patients-what-ask-478572</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>12-09-2026 00:45 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Dr. Reddy’s Mexico API Plant Receives Two USFDA Observations</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Whalesbook</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Mexico-API-Plant-Receives-Two-USFDA-Observations/6aa49cf075fe79b492e4669b</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>12-09-2026 00:29 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Dr. Reddy's ਨੂੰ ਮੈਕਸੀਕੋ ਪਲਾਂਟ ਲਈ ਮਿਲਿਆ USFDA ਦਾ ਨੋਟਿਸ, ਜਾਣੋ ਕੀ ਹੈ ਮਾਮਲਾ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Whalesbook</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>https://www.whalesbook.com/corporate-news/Punjabi/healthcarebiotech/Dr-Reddys-Receives-Two-USFDA-Observations-for-Mexico-API-Facility/6aa42ec7f2017017ae692928</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>11-09-2026 16:40 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Diabetic Retinopathy Market Set for Strong Expansion Through 2036 Amid Rising Investment Interest – DelveInsight | Genentech, Ionis Pharma, AstraZeneca, Regenxbio, AbbVie, Palatin Techn, Avirmax Bio</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>barchart.com</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>https://www.barchart.com/press-releases/4567847/diabetic-retinopathy-market-set-for-strong-expansion-through-2036-amid-rising-investment-interest-delveinsight-genentech-ionis-pharma-astrazeneca-regenxbio-abbvie-palatin-techn-avirmax-bio</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>12-09-2026 03:30 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Teva’s $4.9 Billion Bond Sale Pushes Its Debt Wall Into the 2030s</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>TechStock²</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>https://ts2.tech/en/tevas-4-9-billion-bond-sale-pushes-its-debt-wall-into-the-2030s/</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>12-09-2026 10:45 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Teva raises USD 4.9bn to refinance higher-coupon debt</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AllSci</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>https://allsci.com/news/debt-financing/teva-debt-refinancing-refinances-usd-49b-pile-at/</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>11-09-2026 17:17 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Migraine Market: Pharma Pipeline Fuels Rapid Expansion by 2036 – DelveInsight | Eli Lilly, Teva Pharma, Axsome Therapeutics, AEON Biopharma, Charleston Lab, Amgen, Teva Pharma, Anne Lindblad</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>barchart.com</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>https://www.barchart.com/press-releases/4567842/migraine-market-pharma-pipeline-fuels-rapid-expansion-by-2036-delveinsight-eli-lilly-teva-pharma-axsome-therapeutics-aeon-biopharma-charleston-lab-amgen-teva-pharma-anne-lindblad</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>12-09-2026 03:30 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Teva Brings Gore-Tex Protection to Its Revamped Trail Running Shoe</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Gear Patrol</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>https://www.gearpatrol.com/footwear/teva-hurricane-trailsetter-gtx/</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>11-09-2026 19:32 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Teva Announces Successful Pricing of $4.9 billion (Equivalent) Senior Notes</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Indovizka.com</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>https://indovizka.com/news/detail/22713/teva-announces-successful-pricing-of-49-billion-equivalent-senior-notes</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>11-09-2026 23:59 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Slippers Review Moc Slippers Teva Ember Moc Sizing TEVA BLACK EMBER MOC SLEEPING BAG SLIPPER SNEAKER SHOES, WOMEN US</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>fuelcarmagazine</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>https://fuelcarmagazine.com/shop/sold?id=top4034204002270</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>11-09-2026 17:56 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Teva Pharmaceutical Announces Major Senior Notes Financing</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>TipRanks</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>https://www.tipranks.com/news/company-announcements/teva-pharmaceutical-announces-major-senior-notes-financing</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>11-09-2026 20:43 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Lack of biosimilar development could cost billions in lost savings, report warns</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Endpoints News</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>https://endpoints.news/new-report-may-spell-trouble-for-future-cheaper-biologics/</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>11-09-2026 15:22 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Respiratory Cachexia Nutrition Market</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Future Market Insights</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>https://www.futuremarketinsights.com/reports/respiratory-cachexia-nutrition-market</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>12-09-2026 06:44 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Cancer Patients Needing Ifosfamide Chemotherapy May Receive an Unapproved Imported Version as the U.S. Shortage Persists</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Medical Daily</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>https://www.medicaldaily.com/imported-ifosfamide-shortage-cancer-patients-what-ask-478572</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>12-09-2026 00:45 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Dr. Reddy’s Mexico API Plant Receives Two USFDA Observations</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Whalesbook</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Mexico-API-Plant-Receives-Two-USFDA-Observations/6aa49cf075fe79b492e4669b</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>12-09-2026 00:29 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Dr. Reddy's ਨੂੰ ਮੈਕਸੀਕੋ ਪਲਾਂਟ ਲਈ ਮਿਲਿਆ USFDA ਦਾ ਨੋਟਿਸ, ਜਾਣੋ ਕੀ ਹੈ ਮਾਮਲਾ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Whalesbook</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>https://www.whalesbook.com/corporate-news/Punjabi/healthcarebiotech/Dr-Reddys-Receives-Two-USFDA-Observations-for-Mexico-API-Facility/6aa42ec7f2017017ae692928</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>11-09-2026 16:40 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Samsung Biologics Signs $262M Biologics Manufacturing Deal With Undisclosed European Pharma Company</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>BioPharm International</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>https://www.biopharminternational.com/view/samsung-biologics-signs-262m-biologics-manufacturing-deal-with-undisclosed-european-pharma-company</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>11-09-2026 18:51 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Samsung Biologics Signs $262 Million Manufacturing Agreement with European Pharma Firm</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>genengnews.com</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>https://www.genengnews.com/topics/bioprocessing/samsung-biologics-signs-262-million-manufacturing-agreement-with-european-pharma-firm/</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>11-09-2026 14:59 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Transcenta Therapeutics and WuXi Biologics Team Up to Accelerate Commercialization of HiCB Technology</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>genengnews.com</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>https://www.genengnews.com/topics/bioprocessing/transcenta-therapeutics-and-wuxi-biologics-team-up-to-accelerate-commercialization-of-hicb-technology/</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>11-09-2026 15:10 UTC</t>
+          <t>12-09-2026 13:19 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,27 +485,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thailand details 100bn-baht drug research goal and local production talks with global drugmakers on Sept 12</t>
+          <t>STADA appoints Diana Wiedmann as Chief Culture &amp; People Officer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nation Thailand</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.nationthailand.com/news/policy/40070956</t>
+          <t>https://hrtoday.in/stada-appoints-diana-wiedmann-as-chief-culture-people-officer/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12-09-2026 09:21 UTC</t>
+          <t>13-09-2026 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wound Spray Aerosol Livestock Market Forecast to 2035: Intensified Production Animal Systems to Drive 4.5-6.5% CAGR</t>
+          <t>Salmonella Control Vaccines Market Forecast to 2035: Poultry Demand Drives Growth - News and Statistics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/wound-spray-aerosol-livestock-market-forecast-to-2035-intensified-production-animal-systems-to-drive-4-5-6-5-cagr/</t>
+          <t>https://www.indexbox.io/blog/salmonella-control-vaccines-market-to-accelerate-on-poultry-demand-reaching-2035-growth/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12-09-2026 23:16 UTC</t>
+          <t>13-09-2026 10:51 UTC</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uk.finance.yahoo.com</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>This Week’s Top 5: Philips, NHS, Patchwork, Mars and Nokia</t>
+          <t>Wound Spray Aerosol Livestock Market Forecast to 2035: Intensified Production Animal Systems to Drive 4.5-6.5% CAGR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>healthcare-digital.com</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://healthcare-digital.com/news/this-weeks-top-5-philips-nhs-patchwork-mars-and-nokia</t>
+          <t>https://www.indexbox.io/blog/wound-spray-aerosol-livestock-market-forecast-to-2035-intensified-production-animal-systems-to-drive-4-5-6-5-cagr/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12-09-2026 08:08 UTC</t>
+          <t>12-09-2026 23:16 UTC</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bioengineer.org</t>
+          <t>bioengineer.org</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13-09-2026 02:48 UTC</t>
+          <t>13-09-2026 07:41 UTC</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OpenArt Director Ranks No. 1 in Anime on Physion Labs’ ARC 1.0 AI Video Agent Benchmark</t>
+          <t>Ivonescimab Versus Pembrolizumab in First-Line PD-L1-Positive NSCLC: Positive Overall Survival Results from HARMONi-2 Presented at WCLC 2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uk.finance.yahoo.com</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/openart-director-ranks-no-1-130000945.html</t>
+          <t>https://uk.finance.yahoo.com/news/ivonescimab-versus-pembrolizumab-first-line-065900064.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12-09-2026 13:00 UTC</t>
+          <t>13-09-2026 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -706,49 +706,49 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ivonescimab Versus Pembrolizumab in First-Line PD-L1-Positive NSCLC: Positive Overall Survival Results from HARMONi-2 Presented at WCLC 2026</t>
+          <t>A Year-Long Trial Finds Tiotropium Fails to Prevent Severe Asthma Attacks in Preschoolers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uk.finance.yahoo.com</t>
+          <t>bioengineer.org</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/ivonescimab-versus-pembrolizumab-first-line-065900064.html</t>
+          <t>https://bioengineer.org/a-year-long-trial-finds-tiotropium-fails-to-prevent-severe-asthma-attacks-in-preschoolers/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13-09-2026 06:59 UTC</t>
+          <t>12-09-2026 16:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A Year-Long Trial Finds Tiotropium Fails to Prevent Severe Asthma Attacks in Preschoolers</t>
+          <t>Egypt shuts Dar Al-Hikma Hospital after child's death following tonsillectomy - Health - Egypt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bioengineer.org</t>
+          <t>Ahram Online</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://bioengineer.org/a-year-long-trial-finds-tiotropium-fails-to-prevent-severe-asthma-attacks-in-preschoolers/</t>
+          <t>https://english.ahram.org.eg/NewsContent/1/1236/576547/Egypt/Health/Egypt-shuts-Dar-AlHikma-Hospital-after-child;s-dea.aspx</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12-09-2026 16:37 UTC</t>
+          <t>13-09-2026 14:27 UTC</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13-09-2026 07:34 UTC</t>
+          <t>13-09-2026 10:34 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Watch Amgen Irish Open (Third Round)</t>
+          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Disney Plus</t>
+          <t>Golf Channel</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.disneyplus.com/en-do/browse/entity-4b847354-ff4a-46c9-801c-c8f9eaa7d787</t>
+          <t>https://www.golfchannel.com/watch/golf-central/dp-world-tour-highlights-2026-amgen-irish-open-round-2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13-09-2026 02:30 UTC</t>
+          <t>13-09-2026 14:53 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amgen Irish Open: Shane Lowry retains lead of home event as Donald Trump arrives despite protests</t>
+          <t>Live: Amgen Irish Open Day 4 updates: Lowry bidding for glory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sky Sports</t>
+          <t>RTE.ie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/golf/news/12176/13584693/amgen-irish-open-shane-lowry-retains-lead-of-home-event-as-donald-trump-arrives-despite-protests</t>
+          <t>https://www.rte.ie/sport/golf/2026/0913/1591353-amgen-irish-open-day-4-updates-mcilroy-out-early/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12-09-2026 19:10 UTC</t>
+          <t>13-09-2026 09:54 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shane Lowry creates four-shot edge after Round 3 of Amgen Irish Open, Rory McIlroy struggles</t>
+          <t>Sports News, Transfers, Scores | Watch Live Sport</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PGA Tour</t>
+          <t>Sky Sports</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pgatour.com/article/news/latest/2026/09/12/shane-lowry-creates-four-shot-edge-after-round-3-of-amgen-irish-open-scores-leaderboard-results-rory-mcilroy</t>
+          <t>https://www.skysports.com/golf/watch/8647336164003683112/amgen-irish-open-2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13-09-2026 03:04 UTC</t>
+          <t>13-09-2026 12:26 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 3</t>
+          <t>Watch Amgen Irish Open (Third Round)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yahoo Sports</t>
+          <t>Disney Plus</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://sports.yahoo.com/videos/dp-world-tour-highlights-2026-191327477.html</t>
+          <t>https://www.disneyplus.com/en-do/browse/entity-4b847354-ff4a-46c9-801c-c8f9eaa7d787</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12-09-2026 19:13 UTC</t>
+          <t>13-09-2026 02:30 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rory McIlroy enjoys seeing Shane Lowry create buzz at Amgen Irish Open</t>
+          <t>Shane Lowry creates four-shot edge after Round 3 of Amgen Irish Open, Rory McIlroy struggles</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>europeantour.com</t>
+          <t>PGA Tour</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.europeantour.com/dpworld-tour/news/articles/detail/rory-mcilroy-enjoys-seeing-shane-lowry-create-buzz-at-amgen-irish-open/</t>
+          <t>https://www.pgatour.com/article/news/latest/2026/09/12/shane-lowry-creates-four-shot-edge-after-round-3-of-amgen-irish-open-scores-leaderboard-results-rory-mcilroy</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12-09-2026 17:57 UTC</t>
+          <t>13-09-2026 09:04 UTC</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 3</t>
+          <t>2026 Amgen Irish Open money: DP World Tour purse, winner’s share, prize money payout</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Golf Channel</t>
+          <t>Golf News Net</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.golfchannel.com/watch/dp-world-tour/dp-world-tour-highlights-2026-amgen-irish-open-round-3</t>
+          <t>https://thegolfnewsnet.com/golfnewsnetteam/2026/09/13/2026-amgen-irish-open-money-dp-world-tour-purse-winners-share-prize-money-payout-144756/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12-09-2026 19:57 UTC</t>
+          <t>13-09-2026 11:26 UTC</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>US President Donald Trump Attends Amgen Irish Open</t>
+          <t>Irish Open Prize Money Payout 2026: How Much Does The Winner Earn At Doonbeg?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>golfmonthly.com</t>
+          <t>Golf Monthly</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.golfmonthly.com/news/us-president-donald-trump-attends-amgen-irish-open</t>
+          <t>https://www.golfmonthly.com/news/irish-open-prize-money-payout-breakdown-2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12-09-2026 14:46 UTC</t>
+          <t>13-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shane Lowry leads Amgen Irish Open by four shots, eyeing second home-event victory</t>
+          <t>Amgen Irish Open 2026: Best Pictures: Round 2 – Photo 40/43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Golf Digest Middle East</t>
+          <t>golfpost.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://golfdigestme.com/shane-lowry-leads-amgen-irish-open-by-four-shots-eyeing-second-home-event-victory/</t>
+          <t>https://www.golfpost.com/galleries/amgen-irish-open-2026-bilder-1789129223-en/40/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12-09-2026 19:29 UTC</t>
+          <t>13-09-2026 05:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Trump expected to hand over Amgen Irish Open trophy on visit to Ireland</t>
+          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>lbc.co.uk</t>
+          <t>Yahoo Sports</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.lbc.co.uk/article/trump-visit-to-ireland-golf-5HjdhL7_2/</t>
+          <t>https://sports.yahoo.com/videos/dp-world-tour-highlights-2026-191327477.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13-09-2026 05:43 UTC</t>
+          <t>12-09-2026 19:13 UTC</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1057,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amgen Irish Open round 3 recap: Lowry goes clear</t>
+          <t>Amgen Irish Open: Shane Lowry retains lead of home event as Donald Trump arrives despite protests</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RTE.ie</t>
+          <t>Sky Sports</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.rte.ie/sport/golf/2026/0912/1591264-amgen-irish-open-round-3-updates-shane-lowry-leads/</t>
+          <t>https://www.skysports.com/golf/news/12176/13584693/amgen-irish-open-shane-lowry-retains-lead-of-home-event-as-donald-trump-arrives-despite-protests</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12-09-2026 13:15 UTC</t>
+          <t>12-09-2026 19:10 UTC</t>
         </is>
       </c>
     </row>
@@ -1084,49 +1084,49 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amgen Irish Open | Day three highlights</t>
+          <t>Amgen Irish Open Tee Times 2026: Final Round</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sky Sports</t>
+          <t>Golf Monthly</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/golf/video/30998/13585175/amgen-irish-open-day-three-highlights</t>
+          <t>https://www.golfmonthly.com/news/amgen-irish-open-tee-times-final-round-2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12-09-2026 19:49 UTC</t>
+          <t>13-09-2026 08:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>€100 million investment plan clears way for bigger Pivot Park</t>
+          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IO+</t>
+          <t>Golf Channel</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://ioplus.nl/en/posts/100-million-investment-plan-clears-way-for-bigger-pivot-park</t>
+          <t>https://www.golfchannel.com/watch/dp-world-tour/dp-world-tour-highlights-2026-amgen-irish-open-round-3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12-09-2026 08:55 UTC</t>
+          <t>12-09-2026 19:57 UTC</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nellie Berrios Obituary (2026) - Kunkletown, PA - Gower Funeral Home &amp; Crematory, Inc. - Gilbert</t>
+          <t>Cleaning Fresh Walnut Is An Art Form: Watch Hina Khan Peel Douin Like An Expert</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Legacy obituary</t>
+          <t>News18</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.legacy.com/us/obituaries/name/nellie-berrios-obituary?id=62412556</t>
+          <t>https://www.news18.com/amp/lifestyle/food/cleaning-fresh-walnut-is-an-art-form-watch-hina-khan-peel-douin-like-an-expert-10326857.html</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12-09-2026 23:37 UTC</t>
+          <t>13-09-2026 14:36 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Why Jonnagiri gold mine is a game-changer for India</t>
+          <t>How soybeans took over the American diet – without anyone noticing</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>theweek.in</t>
+          <t>Salon.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/theweek/cover/2026/09/12/why-jonnagiri-gold-mine-is-a-game-changer-for-india.html</t>
+          <t>https://www.salon.com/2026/09/13/how-soybeans-took-over-the-american-diet-without-anyone-noticing-partner/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13-09-2026 04:14 UTC</t>
+          <t>13-09-2026 14:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vitamin D3 may be more effective than D2; here’s why</t>
+          <t>Why Jonnagiri gold mine is a game-changer for India</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>indianexpress.com</t>
+          <t>theweek.in</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/lifestyle/health/vitamin-d2-vitamin-d3-better-for-raising-vitamin-d-levels-experts-explain-10870161/</t>
+          <t>https://www.theweek.in/theweek/cover/2026/09/12/why-jonnagiri-gold-mine-is-a-game-changer-for-india.html</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12-09-2026 12:30 UTC</t>
+          <t>13-09-2026 04:14 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16 Cool-Season Crops To Plant After Your Summer Tomatoes Are Done</t>
+          <t>Powdery mildew disease can be controlled</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>Chicago Tribune</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://shopping.yahoo.com/home-garden/gardening/articles/16-cool-season-crops-plant-175600148.html</t>
+          <t>https://www.chicagotribune.com/2026/09/13/overgrown-lilacs-pruning-powdery-mildew/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12-09-2026 17:56 UTC</t>
+          <t>13-09-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tandem duplication fuels terpene diversity in gymnosperms | Newswise</t>
+          <t>16 Cool-Season Crops To Plant After Your Summer Tomatoes Are Done</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Newswise</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.newswise.com/articles/tandem-duplication-fuels-terpene-diversity-in-gymnosperms</t>
+          <t>https://shopping.yahoo.com/home-garden/gardening/articles/16-cool-season-crops-plant-175600148.html</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12-09-2026 15:50 UTC</t>
+          <t>12-09-2026 17:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>How to prepare the landscape for change of seasons</t>
+          <t>Tandem duplication fuels terpene diversity in gymnosperms | Newswise</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jacksonville Journal-Courier</t>
+          <t>Newswise</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.myjournalcourier.com/features/article/season-s-change-means-changes-landscaping-22413402.php</t>
+          <t>https://www.newswise.com/articles/tandem-duplication-fuels-terpene-diversity-in-gymnosperms</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>13-09-2026 05:49 UTC</t>
+          <t>12-09-2026 15:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Root anatomy, metabolism and microbes team up to help plants survive nutrient scarcity</t>
+          <t>Far-right AfD Says Reported Elbit Plant in Germany Could Aid Deportation Drive</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bioengineer.org</t>
+          <t>israeldefense.co.il</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://bioengineer.org/root-anatomy-metabolism-and-microbes-team-up-to-help-plants-survive-nutrient-scarcity/</t>
+          <t>https://www.israeldefense.co.il/en/node/70730</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12-09-2026 17:42 UTC</t>
+          <t>13-09-2026 08:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>foxtail grass (2025) by CaNNNA - For Sale</t>
+          <t>How to prepare the landscape for change of seasons</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Artsy</t>
+          <t>Jacksonville Journal-Courier</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.artsy.net/artwork/cannna-foxtail-grass</t>
+          <t>https://www.myjournalcourier.com/features/article/season-s-change-means-changes-landscaping-22413402.php</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12-09-2026 08:48 UTC</t>
+          <t>13-09-2026 05:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nitrate Feeds Vanilla Best as Ammonium Slows Growth, Study Finds</t>
+          <t>Root anatomy, metabolism and microbes team up to help plants survive nutrient scarcity</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://bioengineer.org/nitrate-feeds-vanilla-best-as-ammonium-slows-growth-study-finds/</t>
+          <t>https://bioengineer.org/root-anatomy-metabolism-and-microbes-team-up-to-help-plants-survive-nutrient-scarcity/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12-09-2026 19:03 UTC</t>
+          <t>12-09-2026 17:42 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brandon Petersen blunder costs Kaizer Chiefs while in-form AmaZulu march past Marumo Gallants</t>
+          <t>Nitrate Feeds Vanilla Best as Ammonium Slows Growth, Study Finds</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Magic 828</t>
+          <t>Bioengineer.org</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://magic828.co.za/brandon-petersen-blunder-costs-kaizer-chiefs-while-in-form-amazulu-march-past-marumo-gallants/</t>
+          <t>https://bioengineer.org/nitrate-feeds-vanilla-best-as-ammonium-slows-growth-study-finds/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12-09-2026 15:52 UTC</t>
+          <t>12-09-2026 19:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The President opened a bean processing plant in the Talas region.</t>
+          <t>Brandon Petersen blunder costs Kaizer Chiefs while in-form AmaZulu march past Marumo Gallants</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>open.kg</t>
+          <t>Magic 828</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://open.kg/en/news/political-news/121702-prezident-otkryl-zavod-po-pererabotke-fasoli-v-talasskoj-oblasti.html</t>
+          <t>https://magic828.co.za/brandon-petersen-blunder-costs-kaizer-chiefs-while-in-form-amazulu-march-past-marumo-gallants/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12-09-2026 08:26 UTC</t>
+          <t>12-09-2026 15:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Plant Sterol Bigel Rebuilds Fat Crystals for Healthier Cookies</t>
+          <t>Moyes plants the seed for Jarrad Branthwaite after Tottenham 0-0 Everton</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bioengineer.org</t>
+          <t>everton.news</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://bioengineer.org/plant-sterol-bigel-rebuilds-fat-crystals-for-healthier-cookies/</t>
+          <t>https://www.everton.news/moyes-plants-the-seed-for-jarrad-branthwaite-after-tottenham-0-0-everton/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13-09-2026 01:39 UTC</t>
+          <t>13-09-2026 08:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Medicus Pharma advances SkinJect and Pfizer par...</t>
+          <t>Pfizer Makes an Unusual Enemy in $2 Billion Fight Over Unwanted Covid-19 Vaccines</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>pluang.com</t>
+          <t>WSJ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/ceo-medicus-pharma-bahas-kemajuan-skinject-dan-kerjasama-pfizer</t>
+          <t>https://www.wsj.com/business/pfizer-makes-an-unusual-enemy-in-2-billion-fight-over-unwanted-covid-19-vaccines-a5ad7c8d</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12-09-2026 15:09 UTC</t>
+          <t>13-09-2026 14:39 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AstraZeneca's oral SERD stumbles in Phase III first-line breast cancer trial</t>
+          <t>Medicus Pharma advances SkinJect and Pfizer par...</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7983565</t>
+          <t>https://pluang.com/en/news-feed/ceo-medicus-pharma-bahas-kemajuan-skinject-dan-kerjasama-pfizer</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13-09-2026 05:52 UTC</t>
+          <t>12-09-2026 15:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Akeso, Summit’s ivonescimab tops Keytruda in lung cancer survival, with strong data in PD-L1-high patients</t>
+          <t>AstraZeneca's oral SERD stumbles in Phase III first-line breast cancer trial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>firstwordpharma.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/akeso-summit-ivonescimab-tops-keytruda-lung-cancer-survival-strong-data-pd-l1-high-patients</t>
+          <t>https://firstwordpharma.com/story/7983565</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13-09-2026 01:44 UTC</t>
+          <t>13-09-2026 06:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Midtown Manhattan buildings evacuated after beams found buckling at construction site: Police - ABC News</t>
+          <t>Japan: Syphilis surge and Penicillin shortage is not a good combination</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ABC News - Breaking News, Latest News and Videos</t>
+          <t>Outbreak News Today</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://abcnews.com/US/midtown-manhattan-blocks-evacuated-after-beams-found-buckling/story?id=134549272</t>
+          <t>https://outbreaknewstoday.substack.com/p/japan-syphilis-surge-and-penicillin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12-09-2026 21:46 UTC</t>
+          <t>13-09-2026 12:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Medicus Pharma CEO on SkinJect and Pfizer partnership – ICYMI</t>
+          <t>Akeso, Summit’s ivonescimab tops Keytruda in lung cancer survival, with strong data in PD-L1-high patients</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Proactive financial news</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.proactiveinvestors.com/companies/news/1098450/medicus-pharma-ceo-on-skinject-and-pfizer-partnership-icymi-1098450.html</t>
+          <t>https://www.fiercepharma.com/pharma/akeso-summit-ivonescimab-tops-keytruda-lung-cancer-survival-strong-data-pd-l1-high-patients</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12-09-2026 10:32 UTC</t>
+          <t>13-09-2026 01:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1705,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Long-Term Adverse Effects After COVID-19 Vaccination Vary by Brand</t>
+          <t>FINRA Appoints Marguerite Eastwood as Chief Human Resources Officer</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Drug Topics</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.drugtopics.com/view/long-term-adverse-effects-after-covid-19-vaccination-vary-by-brand</t>
+          <t>https://hrtoday.in/finra-appoints-marguerite-eastwood-as-chief-human-resources-officer/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12-09-2026 14:08 UTC</t>
+          <t>12-09-2026 20:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1732,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AstraZeneca's Breast Cancer Drug Camizestrant Fails Main Goal in Late-Stage Trial</t>
+          <t>AstraZeneca’s Etcamah flunks first-line breast cancer trial, adding to oral SERDs’ failure record</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/astrazenecas-breast-cancer-drug-camizestrant-fails-main-goal-in-late-stage-trial-179121</t>
+          <t>https://www.fiercepharma.com/pharma/astrazeneca-etcamah-flunks-first-line-breast-cancer-trial-adding-oral-serds-failure-record</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12-09-2026 13:00 UTC</t>
+          <t>12-09-2026 16:43 UTC</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1759,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FINRA Appoints Marguerite Eastwood as Chief Human Resources Officer</t>
+          <t>Mizzou volleyball handles Wichita State in three sets</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>Newsbug.info</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/finra-appoints-marguerite-eastwood-as-chief-human-resources-officer/</t>
+          <t>https://www.newsbug.info/sports/national/mizzou-volleyball-handles-wichita-state-in-three-sets/article_b0ba7099-fcfa-5b77-ba73-fc8ad151844e.html</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12-09-2026 20:52 UTC</t>
+          <t>12-09-2026 23:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1786,49 +1786,49 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AstraZeneca’s Etcamah flunks first-line breast cancer trial, adding to oral SERDs’ failure record</t>
+          <t>Where was Disclosure Day filmed?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>The Worldwide Guide To Movie Locations</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/astrazeneca-etcamah-flunks-first-line-breast-cancer-trial-adding-oral-serds-failure-record</t>
+          <t>https://movie-locations.com/movies/d/Disclosure-Day.php</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12-09-2026 16:43 UTC</t>
+          <t>13-09-2026 08:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Biogen Sees Pivotal Pipeline Moment as It Expands Beyond Neurology</t>
+          <t>AstraZeneca’s breast cancer pill falls short</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/biogen-sees-pivotal-pipeline-moment-210158269.html</t>
+          <t>https://www.manilatimes.net/2026/09/13/world/astrazenecas-breast-cancer-pill-falls-short/2423833</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12-09-2026 21:01 UTC</t>
+          <t>12-09-2026 16:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,50 +1840,49 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Exclusive | Walmart continues stocking air freshener packed with cancer-causing benzene: lawsuit</t>
+          <t>Biogen Sees Pivotal Pipeline Moment as It Expands Beyond Neurology</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nypost.com/2026/09/12/us-news/walmart-air-freshener-packed-with-cancer-causing-benzene-lawsuit/</t>
+          <t>https://finance.yahoo.com/healthcare/articles/biogen-sees-pivotal-pipeline-moment-210158269.html</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12-09-2026 14:51 UTC</t>
+          <t>12-09-2026 21:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Andy Burnham urged to intervene to introduce new drug to tackle
-rare disease</t>
+          <t>Dr Reddy’s Mexico API Facility Gets Two Observations From USFDA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Manchester Evening News</t>
+          <t>Daily Pioneer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.manchestereveningnews.co.uk/news/uk-news/andy-burnham-urged-intervene-introduce-34607984.amp</t>
+          <t>https://dailypioneer.com/news/slug-lite/usfda-conducts-assessment-of-dr-reddys-mexico-facility?year=2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>12-09-2026 13:06 UTC</t>
+          <t>13-09-2026 08:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1895,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UPI has transformed financial inclusion: former RBI Governor</t>
+          <t>Apollo Hospitals seeks ₹7,500 million NCDs, Reddy reappointment at AGM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/Hyderabad/upi-has-transformed-financial-inclusion-former-rbi-governor/article71460905.ece/amp/</t>
+          <t>https://scanx.trade/stock-market-news/companies/apollo-hospitals-latest-results-consolidated-revenue-up-16-to-252-285-million-in-fy26/47115579</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>12-09-2026 17:08 UTC</t>
+          <t>13-09-2026 05:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1922,22 +1921,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Telangana Vegetable Cultivation Decline Raises Hyderabad Food Risk</t>
+          <t>UPI has transformed financial inclusion: former RBI Governor</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>urbanacres.in</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://urbanacres.in/telangana-vegetable-cultivation-collapse-exposes-hyderabads-food-risk/</t>
+          <t>https://www.thehindu.com/news/cities/Hyderabad/upi-has-transformed-financial-inclusion-former-rbi-governor/article71460905.ece/amp/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>12-09-2026 13:19 UTC</t>
+          <t>12-09-2026 17:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1949,49 +1948,49 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KUDA chief assumes role as TDP election observer for Sri Sathya Sai dist</t>
+          <t>TV Today Network Approves Sale Of FM Radio Business To Creative Channel</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>ascendants.in</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/cities/anantapur/kuda-chief-assumes-role-as-tdp-election-observer-for-sri-sathya-sai-dist-1121288</t>
+          <t>https://ascendants.in/industry_events/tv-today-network-fm-radio-sale-creative-channel/attachment/web-image-2-copy-2-13/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12-09-2026 22:51 UTC</t>
+          <t>13-09-2026 05:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lupin eyes $500 mn biosimilars revenue in medium term, to ramp capacity</t>
+          <t>KUDA chief assumes role as TDP election observer for Sri Sathya Sai dist</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>The Hans India</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/news/companies-news-lupin-eyes-500-mn-biosimilars-revenue-in-medium-term-126091300205_1.html</t>
+          <t>https://www.thehansindia.com/news/cities/anantapur/kuda-chief-assumes-role-as-tdp-election-observer-for-sri-sathya-sai-dist-1121288</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>13-09-2026 06:57 UTC</t>
+          <t>12-09-2026 22:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2003,22 +2002,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15 startups, four student teams win C-CAMP National Bio Entrepreneurship Competition</t>
+          <t>Lupin eyes $500 mn biosimilars revenue in medium term, to ramp capacity</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/states/karnataka/2026/Sep/13/15-startups-four-student-teams-win-c-camp-national-bio-entrepreneurship-competition</t>
+          <t>https://www.business-standard.com/industry/news/companies-news-lupin-eyes-500-mn-biosimilars-revenue-in-medium-term-126091300205_1.html</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>13-09-2026 01:17 UTC</t>
+          <t>13-09-2026 06:57 UTC</t>
         </is>
       </c>
     </row>
@@ -2030,22 +2029,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sanjeev Kathuria Appointed Director, Business Unit Head – Oncology Cluster at Cipla</t>
+          <t>15 startups, four student teams win C-CAMP National Bio Entrepreneurship Competition</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/sanjeev-kathuria-appointed-director-business-unit-head-oncology-cluster-at-cipla/</t>
+          <t>https://www.newindianexpress.com/states/karnataka/2026/Sep/13/15-startups-four-student-teams-win-c-camp-national-bio-entrepreneurship-competition</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>13-09-2026 06:14 UTC</t>
+          <t>13-09-2026 01:17 UTC</t>
         </is>
       </c>
     </row>
@@ -2057,49 +2056,49 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nagaland: State review meeting highlights growing oral cancer burden</t>
+          <t>Sanjeev Kathuria Appointed Director, Business Unit Head – Oncology Cluster at Cipla</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eastern Mirror</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.easternmirrornagaland.com/nagaland-state-review-meeting-highlights-growing-oral-cancer-burden</t>
+          <t>https://hrtoday.in/sanjeev-kathuria-appointed-director-business-unit-head-oncology-cluster-at-cipla/</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>12-09-2026 13:02 UTC</t>
+          <t>13-09-2026 06:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Injects $1 Million into New U.S. R&amp;D Arm After A1 Biochem Deal</t>
+          <t>Russians attack Ukraine's second-largest pharmaceutical warehouse twice</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/aurobindo-pharma-injects-1-million-into-new-u-s-rd-arm-after-a1-biochem-deal</t>
+          <t>https://www.yahoo.com/news/world/articles/russians-attack-ukraines-second-largest-081300256.html</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>12-09-2026 09:03 UTC</t>
+          <t>13-09-2026 08:13 UTC</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2125,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>13-09-2026 06:51 UTC</t>
+          <t>13-09-2026 12:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2138,22 +2137,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Best Camera Phones Under Rs. 30,000 in India: Samsung Galaxy F70 Pro 5G, Motorola Edge 70 Fusion, More</t>
+          <t>I Used The Samsung Galaxy Watch Ultra2 And It Changed My Perspective About What Smartwatches Can Actually Do</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>BW Businessworld</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/features/best-camera-phones-in-india-under-rs-30000-samsung-galaxy-f70-pro-5g-motorola-edge-70-fusion-12028297</t>
+          <t>https://www.businessworld.in/article/i-used-the-samsung-galaxy-watch-ultra2-and-it-changed-my-perspective-about-what-smartwatches-can-actually-do-622455</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>13-09-2026 06:30 UTC</t>
+          <t>13-09-2026 09:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2169,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sammobile.com</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2192,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 FE's India price leaks - GSMArena.com news</t>
+          <t>From Samsung to Salesforce to Google: How an IITian turned his ‘will to prove it’ into a dream career | Success story</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.gsmarena.com/samsung_galaxy_s26_fe_india_price_leaks-news-74595.php</t>
+          <t>https://www.livemint.com/news/trends/from-samsung-to-salesforce-then-cracking-job-at-google-inside-iitians-journey-of-his-will-to-prove-it-to-himse-11789302161025.html</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>12-09-2026 16:01 UTC</t>
+          <t>13-09-2026 13:42 UTC</t>
         </is>
       </c>
     </row>
@@ -2219,22 +2218,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Samsung Innovation Campus AI Program (Saudi Arabia)</t>
+          <t>Semiconductor patent rankings; China IP Forum; Samsung SDI strategy; Via Licensing DRAM pool launch; ETSI director-general keynote; plus much more</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>fundsforNGOs</t>
+          <t>IAM Patent</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/innovation/samsung-innovation-campus-ai-program-saudi-arabia/</t>
+          <t>https://www.iam-media.com/article/semiconductor-patent-rankings-china-ip-forum-samsung-sdi-strategy-licensing-dram-pool-launch-etsi-director-general-keynote-plus-much-more</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>12-09-2026 21:55 UTC</t>
+          <t>13-09-2026 10:43 UTC</t>
         </is>
       </c>
     </row>
@@ -2246,22 +2245,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Samsung’s Galaxy SmartTag3 Leak Shows a New Shape, and No Keyring Hole</t>
+          <t>iPhone Duo alternatives for less at T-Mobile: Samsung Galaxy Z Fold 8, Motorola Razr Fold</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AndroidPure</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.androidpure.com/samsung-galaxy-smarttag3-no-keyring-hole/</t>
+          <t>https://mashable.com/tech/sept-10-iphone-duo-alternatives-t-mobile-deals</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>12-09-2026 23:07 UTC</t>
+          <t>13-09-2026 09:29 UTC</t>
         </is>
       </c>
     </row>
@@ -2273,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Users complain Samsung accounts are being deactivated</t>
+          <t>Samsung Galaxy S26 FE's India price leaks - GSMArena.com news</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://mashable.com/tech/samsung-account-randomly-deactivated-issue</t>
+          <t>https://www.gsmarena.com/samsung_galaxy_s26_fe_india_price_leaks-news-74595.php</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12-09-2026 17:06 UTC</t>
+          <t>12-09-2026 16:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2300,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 FE Price in India Revealed: Exynos 2500 &amp; Slower USB 2.0</t>
+          <t>Samsung Biologics signs $262M manufacturing deal through 2033, pushing longer CDMO bookings</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PaidFreeDroid</t>
+          <t>MarketScale</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://paidfreedroid.com/2026/09/samsung-galaxy-s26-fe-price-india-exynos-2500-specs.html</t>
+          <t>https://www.marketscale.com/industries/sciences/samsung-biologics-signs-262m-manufacturing-deal-through-2033-pushing-longer-cdmo-bookings</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>12-09-2026 19:28 UTC</t>
+          <t>13-09-2026 11:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2327,22 +2326,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Connect Now Works on More Windows PCs, and We Tested It</t>
+          <t>Best Camera Phones Under Rs. 30,000 in India: Samsung Galaxy F70 Pro 5G, Motorola Edge 70 Fusion, More</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SammyGuru</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://sammyguru.com/galaxy-connect-more-windows-pcs-tested/</t>
+          <t>https://www.gadgets360.com/mobiles/features/best-camera-phones-in-india-under-rs-30000-samsung-galaxy-f70-pro-5g-motorola-edge-70-fusion-12028297</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>13-09-2026 04:52 UTC</t>
+          <t>13-09-2026 06:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2354,22 +2353,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Book 6 Pro review: every inch the professional</t>
+          <t>The chip boom and a currency paradox: How a stronger won may soften Samsung, SK hynix earnings</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Creative Bloq</t>
+          <t>Korea JoongAng Daily</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.creativebloq.com/tech/laptops/samsung-galaxy-book-6-pro-review-every-inch-the-professional</t>
+          <t>https://www.koreajoongangdaily.com/business/the-chip-boom-and-a-currency-paradox-how-a-stronger-won-may-soften-samsung-sk-hynix-earnings/12872948</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13-09-2026 07:00 UTC</t>
+          <t>13-09-2026 10:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2380,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Google has gotten lazy with Android and these Samsung apps prove it</t>
+          <t>Rapido driver demands Rs 18k to return stolen Samsung S24 Ultra</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MakeUseOf</t>
+          <t>The Siasat Daily</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.makeuseof.com/google-has-gotten-lazy-with-android-and-these-samsung-apps-prove-it/</t>
+          <t>https://www.siasat.com/rapido-driver-demands-rs-18k-to-return-stolen-samsung-s24-ultra-3541438/</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12-09-2026 18:00 UTC</t>
+          <t>13-09-2026 11:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2408,22 +2407,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dua Lipa’s Samsung Lawsuit Update: Tech Giant Says Singer Can’t Sue Over Her Image on TV Boxes</t>
+          <t>More than 610 Singaporeans Unite to Take Steps for Better Heart Health at Samsung Singapore’s First Galaxy Walkathon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>justjared.com</t>
+          <t>news.samsung.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.justjared.com/2026/09/13/dua-lipas-samsung-lawsuit-update-tech-giant-says-singer-cant-sue-over-her-image-on-tv-boxes/</t>
+          <t>https://news.samsung.com/sg/more-than-610-singaporeans-unite-to-take-steps-for-better-heart-health-at-samsung-singapores-first-galaxy-walkathon</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>13-09-2026 04:07 UTC</t>
+          <t>13-09-2026 08:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2435,22 +2434,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Samsung Electronics Opens Fall Semester Enrollment for Galaxy AI Experience Classes Targeting South Korean Elementary and Middle Schoolers</t>
+          <t>Ultra-lightweight smartphone powerhouse with a 6.9-inch OLED screen—Samsung Galaxy Z Flip 8 review</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Notebookcheck</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/77f6fcfc-c52a-4a4d-bc28-e04ffafbbe62</t>
+          <t>https://www.notebookcheck.net/Ultra-lightweight-smartphone-powerhouse-with-a-6-9-inch-OLED-screen-Samsung-Galaxy-Z-Flip-8-review.1398173.0.html</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>13-09-2026 05:05 UTC</t>
+          <t>13-09-2026 13:10 UTC</t>
         </is>
       </c>
     </row>
@@ -2462,22 +2461,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Best Samsung Galaxy phone deals: Save $250 at Amazon</t>
+          <t>Rosé Spotted With iPhone 18 — Samsung Fires Back: "Should've Asked Us for a Real Phone"</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://mashable.com/tech/sept-11-samsung-galaxy-phone-deals</t>
+          <t>https://finance.biggo.com/news/d38bc930-519c-48ba-b897-b3f5ffc531c1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>12-09-2026 15:27 UTC</t>
+          <t>13-09-2026 11:25 UTC</t>
         </is>
       </c>
     </row>
@@ -2489,22 +2488,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A new software update is rolling out to the Galaxy A57</t>
+          <t>How To Set Up HDMI-CEC On Your Samsung TV</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sammobile.com</t>
+          <t>Engadget</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/galaxy-a57-september-2026-security-patch-released/</t>
+          <t>https://www.engadget.com/2252825/how-to-set-up-hdmi-cec-samsung-tv/</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>12-09-2026 08:34 UTC</t>
+          <t>13-09-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2516,22 +2515,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GSK’s ADC lays down marker for lung cancer scrap with Merck</t>
+          <t>Tokyo court dismisses NTK's claims against Daiichi Sankyo; costs on NTK</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fierce Biotech</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.fiercebiotech.com/biotech/gsks-adc-lays-down-marker-lung-cancer-scrap-merck-co</t>
+          <t>https://scanx.trade/stock-market-news/companies/tokyo-district-court-dismisses-ntk-s-claim-against-daiichi-sankyo/50658388</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>12-09-2026 22:57 UTC</t>
+          <t>13-09-2026 06:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2543,22 +2542,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Manipal Hospitals scouts for acquisitions in Andhra, Keralam, Delhi-NCR; bets on AI-led healthcare</t>
+          <t>Swarup Datta Appointed Vice President – Head R&amp;D, CDMO at Glochem Industries</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>economictimes.com</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/healthcare/biotech/healthcare/manipal-hospitals-scouts-for-acquisitions-in-andhra-keralam-delhi-ncr-bets-on-ai-led-healthcare/articleshow/134179222.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
+          <t>https://hrtoday.in/swarup-datta-appointed-vice-president-head-rd-cdmo-at-glochem-industries/</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>13-09-2026 05:14 UTC</t>
+          <t>13-09-2026 11:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2570,22 +2569,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Leaders of BRICS countries call for stronger cooperation in health, endorse initiatives on tuberculosis</t>
+          <t>GSK’s ADC lays down marker for lung cancer scrap with Merck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>economictimes.com</t>
+          <t>Fierce Biotech</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/healthcare/biotech/healthcare/leaders-of-brics-countries-call-for-stronger-cooperation-in-health-endorse-initiatives-on-tb/articleshow/134139783.cms</t>
+          <t>https://www.fiercebiotech.com/biotech/gsks-adc-lays-down-marker-lung-cancer-scrap-merck-co</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>12-09-2026 15:08 UTC</t>
+          <t>12-09-2026 22:57 UTC</t>
         </is>
       </c>
     </row>
@@ -2597,103 +2596,103 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AstraZeneca breast cancer pill misses mark in pivotal trial, STAT reports</t>
+          <t>Manipal Hospitals scouts for acquisitions in Andhra, Keralam, Delhi-NCR; bets on AI-led healthcare</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>streamlinefeed.co.ke</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://streamlinefeed.co.ke/news/astrazeneca-breast-cancer-pill-misses-mark-in-pivotal-trial-stat-reports</t>
+          <t>https://m.economictimes.com/industry/healthcare/biotech/healthcare/manipal-hospitals-scouts-for-acquisitions-in-andhra-keralam-delhi-ncr-bets-on-ai-led-healthcare/articleshow/134179222.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>12-09-2026 08:19 UTC</t>
+          <t>13-09-2026 05:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+          <t>Leaders of BRICS countries call for stronger cooperation in health, endorse initiatives on tuberculosis</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+          <t>https://m.economictimes.com/industry/healthcare/biotech/healthcare/leaders-of-brics-countries-call-for-stronger-cooperation-in-health-endorse-initiatives-on-tb/articleshow/134139783.cms</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>12-09-2026 17:29 UTC</t>
+          <t>12-09-2026 15:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Polpharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Biosimilar race: Sandoz expands pipeline with Henlius, Teva secures ocrelizumab candidate</t>
+          <t>JSW Infrastructure achieves 'Low Risk' ESG rating from Morningstar Sustainalytics</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Generics and Biosimilars Initiative</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://gabionline.net/es/noticias-farmaceuticas/biosimilar-race-sandoz-expands-pipeline-with-henlius-teva-secures-ocrelizumab-candidate</t>
+          <t>https://businessupturn.com/business/corporates/jsw-infrastructure-achieves-low-risk-esg-rating-from-morningstar-sustainalytics/</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>12-09-2026 13:19 UTC</t>
+          <t>12-09-2026 23:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sandu Pharmaceuticals: Board Approves New Chairman and Director Appointments</t>
+          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>InvestyWise</t>
+          <t>Stocktwits</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.investywise.com/sandu-pharmaceuticals-limited-key-management-appointments/</t>
+          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>12-09-2026 12:04 UTC</t>
+          <t>12-09-2026 17:29 UTC</t>
         </is>
       </c>
     </row>
@@ -2732,130 +2731,157 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Teva’s $4.9 Billion Bond Sale Pushes Its Debt Wall Into the 2030s</t>
+          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TechStock²</t>
+          <t>Stocktwits</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://ts2.tech/en/tevas-4-9-billion-bond-sale-pushes-its-debt-wall-into-the-2030s/</t>
+          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>12-09-2026 10:45 UTC</t>
+          <t>12-09-2026 17:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Jamp Pharma</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+          <t>Aurora Cannabis Taps Pharma Veteran to Drive Global Commercial Push</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+          <t>https://www.tipranks.com/news/company-announcements/aurora-cannabis-taps-pharma-veteran-to-drive-global-commercial-push</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>12-09-2026 17:29 UTC</t>
+          <t>12-09-2026 15:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Jamp Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Aurora Cannabis Taps Pharma Veteran to Drive Global Commercial Push</t>
+          <t>Samsung Bioepis Named Top Job-Creating Company</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/aurora-cannabis-taps-pharma-veteran-to-drive-global-commercial-push</t>
+          <t>https://www.thelec.net/news/articleView.html?idxno=13875</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>12-09-2026 15:04 UTC</t>
+          <t>12-09-2026 23:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Samsung Bioepis Named Top Job-Creating Company</t>
+          <t>Samsung Biologics signs $262M manufacturing deal through 2033, pushing longer CDMO bookings</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>thelec.net</t>
+          <t>MarketScale</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.thelec.net/news/articleView.html?idxno=13875</t>
+          <t>https://www.marketscale.com/industries/sciences/samsung-biologics-signs-262m-manufacturing-deal-through-2033-pushing-longer-cdmo-bookings</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>12-09-2026 23:26 UTC</t>
+          <t>13-09-2026 11:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Polpharma Biologics</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Biosimilar race: Sandoz expands pipeline with Henlius, Teva secures ocrelizumab candidate</t>
+          <t>APAC Healthcare Weekly (Sept 13) – Hansoh, InSilico, Shionogi, Kyowa Kirin, Samsung Bio, SK Biopharm</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Generics and Biosimilars Initiative</t>
+          <t>smartkarma.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://gabionline.net/es/noticias-farmaceuticas/biosimilar-race-sandoz-expands-pipeline-with-henlius-teva-secures-ocrelizumab-candidate</t>
+          <t>https://www.smartkarma.com/insights/apac-healthcare-weekly-sept-13-hansoh-insilico-shionogi-kyowa-kirin-samsung-bio-sk-biopharm</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>12-09-2026 13:19 UTC</t>
+          <t>13-09-2026 01:46 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Samsung Biologics (KRX: 207940) Secures $262M Manufacturing Deal With European Pharma As Peptide Push Advances</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>londoninsider.co.uk</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://londoninsider.co.uk/samsung-biologics-krx-207940-secures-262m-manufacturing-deal-with-european-pharma-as-peptide-push-advances/</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>13-09-2026 10:49 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,76 +463,76 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz bets big on biosimilars and targets $22 billion+ in sales by 2035</t>
+          <t>Thailand moves from buying medicines to building them</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Pattaya Mail</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/sandoz-bets-big-on-biosimilars-and-targets-22-billion-in-sales-by-2035-21812</t>
+          <t>https://www.pattayamail.com/latestnews/news/thailand-moves-from-buying-medicines-to-building-them-564872</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12-09-2026 16:39 UTC</t>
+          <t>13-09-2026 19:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stada</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>STADA appoints Diana Wiedmann as Chief Culture &amp; People Officer</t>
+          <t>Thailand seeks 100 billion baht in pharmaceutical research investment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>Pattaya Mail</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/stada-appoints-diana-wiedmann-as-chief-culture-people-officer/</t>
+          <t>https://www.pattayamail.com/thailandnews/thailand-seeks-100-billion-baht-in-pharmaceutical-research-investment-564941</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13-09-2026 07:53 UTC</t>
+          <t>13-09-2026 18:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pharmacies run out of hormonal treatment for menopausal women and trans people</t>
+          <t>Salmonella Control Vaccines Market Forecast to 2035: Poultry Demand Drives Growth - News and Statistics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Diari ARA</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://en.ara.cat/society/pharmacies-run-out-of-hormonal-treatment-for-menopausal-women-and-trans-people_1_5848398.amp.html</t>
+          <t>https://www.indexbox.io/blog/salmonella-control-vaccines-market-to-accelerate-on-poultry-demand-reaching-2035-growth/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12-09-2026 18:01 UTC</t>
+          <t>13-09-2026 10:51 UTC</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Salmonella Control Vaccines Market Forecast to 2035: Poultry Demand Drives Growth - News and Statistics</t>
+          <t>Increased deaths shadow AstraZeneca, Daiichi’s Enhertu first-line lung cancer data</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/salmonella-control-vaccines-market-to-accelerate-on-poultry-demand-reaching-2035-growth/</t>
+          <t>https://www.fiercepharma.com/pharma/higher-death-risk-shadows-astrazeneca-daiichi-enhertu-first-line-lung-cancer-data</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13-09-2026 10:51 UTC</t>
+          <t>13-09-2026 23:00 UTC</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte's Biopharma AI Value Estimates Come With a Timing Catch</t>
+          <t>Phase III MAVERICK Trial Supports Brain MRI Surveillance Alone as Standard of Care for Small-Cell Lung Cancer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MarketScale</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.marketscale.com/industries/sciences/biopharma-ai-deals-now-need-validation-and-roi-timing-written-into-contracts</t>
+          <t>https://uk.finance.yahoo.com/news/phase-iii-maverick-trial-supports-125400219.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13-09-2026 01:25 UTC</t>
+          <t>13-09-2026 12:54 UTC</t>
         </is>
       </c>
     </row>
@@ -598,184 +598,184 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Roche’s collaborator MediLink announces phase III data for Tam-Peli showing significantly improved overall survival in Chinese patient population with relapsed small-cell lung cancer</t>
+          <t>Avian Newcastle Disease Tests Market Forecast to 2035: Growth Driven by Expanding Poultry Biosecurity Mandates</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/roche-collaborator-medilink-announces-phase-000000583.html</t>
+          <t>https://www.indexbox.io/blog/avian-newcastle-disease-tests-market-forecast-to-2035-growth-driven-by-expanding-poultry-biosecurity-mandates/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13-09-2026 00:00 UTC</t>
+          <t>13-09-2026 17:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wound Spray Aerosol Livestock Market Forecast to 2035: Intensified Production Animal Systems to Drive 4.5-6.5% CAGR</t>
+          <t>Egypt shuts Dar Al-Hikma Hospital after child's death following tonsillectomy - Health - Egypt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>Ahram Online</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/wound-spray-aerosol-livestock-market-forecast-to-2035-intensified-production-animal-systems-to-drive-4-5-6-5-cagr/</t>
+          <t>https://english.ahram.org.eg/NewsContentP/1/576547/Egypt/Egypt-shuts-Dar-AlHikma-Hospital-after-child;s-dea.aspx</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12-09-2026 23:16 UTC</t>
+          <t>13-09-2026 14:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Receptor Occupancy Fails to Predict Immune Activation in Pembrolizumab Dosing Study</t>
+          <t>Al-Ahly Tripoli advances to CAF Confederation Cup second round</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bioengineer.org</t>
+          <t>The Libya Observer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://bioengineer.org/receptor-occupancy-fails-to-predict-immune-activation-in-pembrolizumab-dosing-study/</t>
+          <t>https://libyaobserver.ly/sports/al-ahly-tripoli-advances-caf-confederation-cup-second-round</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13-09-2026 07:41 UTC</t>
+          <t>13-09-2026 16:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ivonescimab Versus Pembrolizumab in First-Line PD-L1-Positive NSCLC: Positive Overall Survival Results from HARMONi-2 Presented at WCLC 2026</t>
+          <t>Fatat takes bronze at Arab Women’s Basketball Championship</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>Arab Times Kuwait News</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/ivonescimab-versus-pembrolizumab-first-line-065900064.html</t>
+          <t>https://www.arabtimesonline.com/news/fatat-takes-bronze-at-arab-womens-basketball-championship/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13-09-2026 06:59 UTC</t>
+          <t>13-09-2026 17:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A Year-Long Trial Finds Tiotropium Fails to Prevent Severe Asthma Attacks in Preschoolers</t>
+          <t>Amgen Irish Open 2026: Shane Lowry Chases $1.02 Million Winner’s Prize</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bioengineer.org</t>
+          <t>NDTV Sports</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://bioengineer.org/a-year-long-trial-finds-tiotropium-fails-to-prevent-severe-asthma-attacks-in-preschoolers/</t>
+          <t>https://sports.ndtv.com/us/golf/amgen-irish-open-2026-shane-lowry-chases-1-02-million-winner-s-prize-12042352</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12-09-2026 16:37 UTC</t>
+          <t>13-09-2026 18:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Egypt shuts Dar Al-Hikma Hospital after child's death following tonsillectomy - Health - Egypt</t>
+          <t>Advancing Innovation in Small Cell Lung Cancer at WCLC 2026 – Amgen</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ahram Online</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://english.ahram.org.eg/NewsContent/1/1236/576547/Egypt/Health/Egypt-shuts-Dar-AlHikma-Hospital-after-child;s-dea.aspx</t>
+          <t>https://oncodaily.com/industry/amgen-585539</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13-09-2026 14:27 UTC</t>
+          <t>13-09-2026 19:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aster Guardians Global Nursing Award 2026 names Agimol Pradeep from United Kingdom winner of USD 250,000 prize - Global News Network Liberia</t>
+          <t>Amgen Irish Open | Day four highlights</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Global News Network Liberia</t>
+          <t>Sky Sports</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://gnnliberia.com/amp/aster-guardians-global-nursing-award-2026-names-agimol-pradeep-from-united-kingdom-winner-of-usd-250000-prize/</t>
+          <t>https://www.skysports.com/golf/video/30998/13585561/amgen-irish-open-day-four-highlights</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13-09-2026 05:22 UTC</t>
+          <t>13-09-2026 18:20 UTC</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amgen Irish Open 2026: How to watch, TV coverage, live streams</t>
+          <t>Shane Lowry surges to stunning Amgen Irish Open victory</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Golf Channel</t>
+          <t>DP World Tour</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.golfchannel.com/dp-world-tour/news/amgen-irish-open-2026-how-to-watch-tv-coverage-live-streams</t>
+          <t>https://www.europeantour.com/dpworld-tour/news/articles/detail/shane-lowry-surges-to-stunning-amgen-irish-open-victory/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13-09-2026 10:34 UTC</t>
+          <t>13-09-2026 17:24 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 2</t>
+          <t>Shane Lowry Claims Dominant Home Soil Victory at Amgen Irish Open</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Golf Channel</t>
+          <t>ACCESS Newswire</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.golfchannel.com/watch/golf-central/dp-world-tour-highlights-2026-amgen-irish-open-round-2</t>
+          <t>https://www.accessnewswire.com/newsroom/en/sports-leisure-and-entertainment/shane-lowry-claims-dominant-home-soil-victory-at-amgen-irish-open-1220343</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13-09-2026 14:53 UTC</t>
+          <t>13-09-2026 19:59 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Live: Amgen Irish Open Day 4 updates: Lowry bidding for glory</t>
+          <t>Final LIV Golf Leaderboard At The Amgen Irish Open</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RTE.ie</t>
+          <t>golfmonthly.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.rte.ie/sport/golf/2026/0913/1591353-amgen-irish-open-day-4-updates-mcilroy-out-early/</t>
+          <t>https://www.golfmonthly.com/news/liv-golf-leaderboard-amgen-irish-open-2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13-09-2026 09:54 UTC</t>
+          <t>13-09-2026 20:14 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sports News, Transfers, Scores | Watch Live Sport</t>
+          <t>Trump’s in Ireland to meet leaders and attend Amgen Irish Open</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sky Sports</t>
+          <t>eciks.org</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/golf/watch/8647336164003683112/amgen-irish-open-2026</t>
+          <t>https://eciks.org/26569-trump-arrives-ireland-doonbeg</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13-09-2026 12:26 UTC</t>
+          <t>13-09-2026 22:24 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Watch Amgen Irish Open (Third Round)</t>
+          <t>Shane Lowry wins Amgen Irish Open by a whopping 11 shots over Patrick Reed, Joaquin Niemann</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Disney Plus</t>
+          <t>Golfweek</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.disneyplus.com/en-do/browse/entity-4b847354-ff4a-46c9-801c-c8f9eaa7d787</t>
+          <t>https://golfweek.usatoday.com/story/sports/golf/dpworldtour/2026/09/13/shane-lowry-wins-amgen-irish-open-2026-10-shots/91746369007/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13-09-2026 02:30 UTC</t>
+          <t>13-09-2026 18:16 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shane Lowry creates four-shot edge after Round 3 of Amgen Irish Open, Rory McIlroy struggles</t>
+          <t>GALLERY: Trump attends Amgen Irish Open in Doonbeg, Ireland</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PGA Tour</t>
+          <t>WXLV</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pgatour.com/article/news/latest/2026/09/12/shane-lowry-creates-four-shot-edge-after-round-3-of-amgen-irish-open-scores-leaderboard-results-rory-mcilroy</t>
+          <t>https://abc45.com/news/nation-world/gallery-us-president-donald-trump-attends-amgen-irish-open-in-doonbeg-ireland-trump-international-golf-links-and-hotel-tournament-shane-lowry-eric-trump-guy-kinnings-joaquin-niemann-jacob-skov-olesen-andy-sullivan-tom-mckibbin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13-09-2026 09:04 UTC</t>
+          <t>13-09-2026 14:24 UTC</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026 Amgen Irish Open money: DP World Tour purse, winner’s share, prize money payout</t>
+          <t>Shane Lowry runs away with record 11-stroke victory at Amgen Irish Open, Rory McIlroy closes on positive note</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Golf News Net</t>
+          <t>PGA Tour</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://thegolfnewsnet.com/golfnewsnetteam/2026/09/13/2026-amgen-irish-open-money-dp-world-tour-purse-winners-share-prize-money-payout-144756/</t>
+          <t>https://www.pgatour.com/article/news/latest/2026/09/13/shane-lowry-runs-away-with-record-11-shot-victory-at-2026-amgen-irish-open-scores-leaderboard-results-rory-mcilroy-patrick-reed</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13-09-2026 11:26 UTC</t>
+          <t>13-09-2026 19:14 UTC</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Irish Open Prize Money Payout 2026: How Much Does The Winner Earn At Doonbeg?</t>
+          <t>GALLERY: Trump attends Amgen Irish Open in Doonbeg, Ireland</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Golf Monthly</t>
+          <t>National News Desk</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.golfmonthly.com/news/irish-open-prize-money-payout-breakdown-2026</t>
+          <t>https://thenationaldesk.com/news/americas-news-now/gallery-us-president-donald-trump-attends-amgen-irish-open-in-doonbeg-ireland-trump-international-golf-links-and-hotel-tournament-shane-lowry-eric-trump-guy-kinnings-joaquin-niemann-jacob-skov-olesen-andy-sullivan-tom-mckibbin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13-09-2026 13:00 UTC</t>
+          <t>13-09-2026 14:14 UTC</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amgen Irish Open 2026: Best Pictures: Round 2 – Photo 40/43</t>
+          <t>Amgen Irish Open Day 4 recap: Lowry wins in style</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>golfpost.com</t>
+          <t>RTE.ie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.golfpost.com/galleries/amgen-irish-open-2026-bilder-1789129223-en/40/</t>
+          <t>https://www.rte.ie/sport/golf/2026/0913/1591353-amgen-irish-open-day-4-updates-mcilroy-out-early/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13-09-2026 05:50 UTC</t>
+          <t>13-09-2026 09:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1030,130 +1030,130 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 3</t>
+          <t>Amgen Irish Open: Shane Lowry secures record 11-stroke victory at Trump International Links in Doonbeg</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yahoo Sports</t>
+          <t>Sky Sports</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://sports.yahoo.com/videos/dp-world-tour-highlights-2026-191327477.html</t>
+          <t>https://www.skysports.com/golf/news/12176/13585479/amgen-irish-open-shane-lowry-secures-record-11-stroke-victory-at-trump-international-links-in-doonbeg</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12-09-2026 19:13 UTC</t>
+          <t>13-09-2026 18:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amgen Irish Open: Shane Lowry retains lead of home event as Donald Trump arrives despite protests</t>
+          <t>Urban Jungle: Adopting Nature in London's Barbican Conservatory</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sky Sports</t>
+          <t>Devdiscourse</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/golf/news/12176/13584693/amgen-irish-open-shane-lowry-retains-lead-of-home-event-as-donald-trump-arrives-despite-protests</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3976751-urban-jungle-adopting-nature-in-londons-barbican-conservatory</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12-09-2026 19:10 UTC</t>
+          <t>14-09-2026 06:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amgen Irish Open Tee Times 2026: Final Round</t>
+          <t>London 'plant parents' adopt a piece of historic Barbican urban jungle</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Golf Monthly</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.golfmonthly.com/news/amgen-irish-open-tee-times-final-round-2026</t>
+          <t>https://www.reuters.com/lifestyle/london-plant-parents-adopt-piece-historic-barbican-urban-jungle-2026-09-14/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13-09-2026 08:58 UTC</t>
+          <t>14-09-2026 06:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 3</t>
+          <t>BRICS Backs Expert Group on Traditional Medicine, Calls for Evidence-Based Global Cooperation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Golf Channel</t>
+          <t>PIB</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.golfchannel.com/watch/dp-world-tour/dp-world-tour-highlights-2026-amgen-irish-open-round-3</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2309695&amp;reg=3&amp;lang=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12-09-2026 19:57 UTC</t>
+          <t>13-09-2026 08:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Michael Burry Says SOX 'Will Return To Earth' — And Reveals Fresh $330 Puts On Key Semiconductor ETF</t>
+          <t>Windsor Ventra Assembly auto parts workers vote by 99 percent to authorize strike</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>World Socialist Web Site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/michael-burry-says-sox-will-return-to-earth-reveals-fresh-puts-on-key-semiconductor-etf/cZBNXiGRe2g</t>
+          <t>https://www.wsws.org/en/articles/2026/09/14/ivvi-s14.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12-09-2026 19:43 UTC</t>
+          <t>14-09-2026 02:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cleaning Fresh Walnut Is An Art Form: Watch Hina Khan Peel Douin Like An Expert</t>
+          <t>18% of booths have got 5 or fewer forms for new voters in electoral roll</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>News18</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.news18.com/amp/lifestyle/food/cleaning-fresh-walnut-is-an-art-form-watch-hina-khan-peel-douin-like-an-expert-10326857.html</t>
+          <t>https://timesofindia.indiatimes.com/city/ranchi/18-of-booths-have-got-5-or-fewer-forms-for-new-voters-in-electoral-roll/amp_articleshow/134216422.cms</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13-09-2026 14:36 UTC</t>
+          <t>13-09-2026 17:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>How soybeans took over the American diet – without anyone noticing</t>
+          <t>Cleaning Fresh Walnut Is An Art Form: Watch Hina Khan Peel Douin Like An Expert</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Salon.com</t>
+          <t>News18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.salon.com/2026/09/13/how-soybeans-took-over-the-american-diet-without-anyone-noticing-partner/</t>
+          <t>https://www.news18.com/amp/lifestyle/food/cleaning-fresh-walnut-is-an-art-form-watch-hina-khan-peel-douin-like-an-expert-10326857.html</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13-09-2026 14:30 UTC</t>
+          <t>13-09-2026 14:36 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Why Jonnagiri gold mine is a game-changer for India</t>
+          <t>Essex data centre could 'threaten bumblebee and one of Britain's rarest plants'</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>theweek.in</t>
+          <t>BBC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/theweek/cover/2026/09/12/why-jonnagiri-gold-mine-is-a-game-changer-for-india.html</t>
+          <t>https://www.bbc.co.uk/news/articles/c24jrm0v8j4o</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13-09-2026 04:14 UTC</t>
+          <t>14-09-2026 05:43 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Powdery mildew disease can be controlled</t>
+          <t>How ammonium sulphate delivers plant available sulphur</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago Tribune</t>
+          <t>RealAgriculture</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.chicagotribune.com/2026/09/13/overgrown-lilacs-pruning-powdery-mildew/</t>
+          <t>https://www.realagriculture.com/2026/09/how-ammonium-sulphate-delivers-plant-available-sulphur/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13-09-2026 11:00 UTC</t>
+          <t>13-09-2026 10:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16 Cool-Season Crops To Plant After Your Summer Tomatoes Are Done</t>
+          <t>How soybeans took over the American diet – without anyone noticing</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>salon.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://shopping.yahoo.com/home-garden/gardening/articles/16-cool-season-crops-plant-175600148.html</t>
+          <t>https://www.salon.com/2026/09/13/how-soybeans-took-over-the-american-diet-without-anyone-noticing-partner/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12-09-2026 17:56 UTC</t>
+          <t>13-09-2026 14:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tandem duplication fuels terpene diversity in gymnosperms | Newswise</t>
+          <t>Bill Ferree Obituary Sep 10, 2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Newswise</t>
+          <t>Pugh Funeral Home</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.newswise.com/articles/tandem-duplication-fuels-terpene-diversity-in-gymnosperms</t>
+          <t>https://www.pughfuneralhome.com/obituaries/bill-ferree</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12-09-2026 15:50 UTC</t>
+          <t>14-09-2026 07:25 UTC</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13 Best Trees To Plant For Gorgeous Fall Color Every Year</t>
+          <t>Nanomaterials trigger stage specific plant responses</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Southern Living</t>
+          <t>agronews.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.southernliving.com/trees-plant-for-fall-color-12117441</t>
+          <t>https://agronews.com/us/en/news/agricultural-blog/2026-09-13/103751</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12-09-2026 19:29 UTC</t>
+          <t>13-09-2026 23:39 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Far-right AfD Says Reported Elbit Plant in Germany Could Aid Deportation Drive</t>
+          <t>Cut Back These 5 Flowering Vines This Fall for Even More Growth Next Spring, Gardening Pros Say</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>israeldefense.co.il</t>
+          <t>The Spruce</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.israeldefense.co.il/en/node/70730</t>
+          <t>https://www.thespruce.com/flowering-vines-to-cut-in-fall-12083508</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13-09-2026 08:44 UTC</t>
+          <t>13-09-2026 23:36 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>How to prepare the landscape for change of seasons</t>
+          <t>Where can the LEGO Botanicals personality plants go next?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jacksonville Journal-Courier</t>
+          <t>Brick Fanatics</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.myjournalcourier.com/features/article/season-s-change-means-changes-landscaping-22413402.php</t>
+          <t>https://www.brickfanatics.com/where-can-lego-botanicals-personality-plants-go</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13-09-2026 05:49 UTC</t>
+          <t>13-09-2026 18:14 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Root anatomy, metabolism and microbes team up to help plants survive nutrient scarcity</t>
+          <t>Powdery mildew disease can be controlled</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bioengineer.org</t>
+          <t>chicagotribune.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://bioengineer.org/root-anatomy-metabolism-and-microbes-team-up-to-help-plants-survive-nutrient-scarcity/</t>
+          <t>https://www.chicagotribune.com/2026/09/13/overgrown-lilacs-pruning-powdery-mildew/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12-09-2026 17:42 UTC</t>
+          <t>13-09-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,103 +1435,103 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nitrate Feeds Vanilla Best as Ammonium Slows Growth, Study Finds</t>
+          <t>Rural crime survey 'will shape priorities', says Durham police commissioner</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bioengineer.org</t>
+          <t>BBC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://bioengineer.org/nitrate-feeds-vanilla-best-as-ammonium-slows-growth-study-finds/</t>
+          <t>https://www.bbc.co.uk/news/articles/c86x78e9yd4o</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12-09-2026 19:03 UTC</t>
+          <t>13-09-2026 16:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Brandon Petersen blunder costs Kaizer Chiefs while in-form AmaZulu march past Marumo Gallants</t>
+          <t>Pfizer Quality Improvement Grant for System-Level Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Magic 828</t>
+          <t>fundsforNGOs</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://magic828.co.za/brandon-petersen-blunder-costs-kaizer-chiefs-while-in-form-amazulu-march-past-marumo-gallants/</t>
+          <t>https://www2.fundsforngos.org/research-2/pfizer-quality-improvement-grant-for-system-level-solutions/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12-09-2026 15:52 UTC</t>
+          <t>14-09-2026 05:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Moyes plants the seed for Jarrad Branthwaite after Tottenham 0-0 Everton</t>
+          <t>Pfizer Makes an Unusual Enemy in $2 Billion Fight Over Unwanted Covid-19 Vaccines</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>everton.news</t>
+          <t>WSJ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.everton.news/moyes-plants-the-seed-for-jarrad-branthwaite-after-tottenham-0-0-everton/</t>
+          <t>https://www.wsj.com/business/pfizer-makes-an-unusual-enemy-in-2-billion-fight-over-unwanted-covid-19-vaccines-a5ad7c8d</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13-09-2026 08:00 UTC</t>
+          <t>13-09-2026 14:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Matted fiber leaves the screens at 14 New York sewage plants packed hard enough to hold the shape of the pipe, while the flushable label that takes the blame is on a fraction of it</t>
+          <t>Pfizer Independent Medical Education Grant Program</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EcoPortal.net</t>
+          <t>fundsforNGOs</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.ecoportal.net/en/crews-new-york-city-fourteen-sewage/37092/</t>
+          <t>https://www2.fundsforngos.org/research-2/pfizer-independent-medical-education-grant-program/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12-09-2026 15:50 UTC</t>
+          <t>14-09-2026 05:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pfizer Makes an Unusual Enemy in $2 Billion Fight Over Unwanted Covid-19 Vaccines</t>
+          <t>Viatris names Kim Sun-A head of Japan-Korea cluster</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/business/pfizer-makes-an-unusual-enemy-in-2-billion-fight-over-unwanted-covid-19-vaccines-a5ad7c8d</t>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33156</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13-09-2026 14:39 UTC</t>
+          <t>14-09-2026 04:17 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Medicus Pharma advances SkinJect and Pfizer par...</t>
+          <t>Pfizer seizes air traffic fees to recover $2.2b from Poland, Romania - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/ceo-medicus-pharma-bahas-kemajuan-skinject-dan-kerjasama-pfizer</t>
+          <t>https://biz.chosun.com/en/en-international/2026/09/14/GB5CCJRCGRGZ3BAWLCUXEBW6JU/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12-09-2026 15:09 UTC</t>
+          <t>14-09-2026 05:43 UTC</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AstraZeneca's oral SERD stumbles in Phase III first-line breast cancer trial</t>
+          <t>Etcamah misses main goal after recent FDA approval</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>firstwordpharma.com</t>
+          <t>lifesciencenordic.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7983565</t>
+          <t>https://www.lifesciencenordic.com/article/view/1245758/etcamah_misses_main_goal_after_recent_fda_approval</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13-09-2026 06:11 UTC</t>
+          <t>14-09-2026 08:17 UTC</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Japan: Syphilis surge and Penicillin shortage is not a good combination</t>
+          <t>After a brief storm of political headwinds, mRNA is back with strong momentum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Outbreak News Today</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://outbreaknewstoday.substack.com/p/japan-syphilis-surge-and-penicillin</t>
+          <t>https://www.biospace.com/drug-development/after-a-brief-storm-of-political-headwinds-mrna-is-back-with-strong-momentum</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13-09-2026 12:56 UTC</t>
+          <t>14-09-2026 04:10 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Akeso, Summit’s ivonescimab tops Keytruda in lung cancer survival, with strong data in PD-L1-high patients</t>
+          <t>Japan: Syphilis surge and Penicillin shortage is not a good combination</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>outbreaknewstoday.substack.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/akeso-summit-ivonescimab-tops-keytruda-lung-cancer-survival-strong-data-pd-l1-high-patients</t>
+          <t>https://outbreaknewstoday.substack.com/p/japan-syphilis-surge-and-penicillin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13-09-2026 01:44 UTC</t>
+          <t>13-09-2026 12:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1678,22 +1678,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tesla Futures Margins</t>
+          <t>Where was Disclosure Day filmed?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>movie-locations.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.cmegroup.com/markets/equities/single-stock/tesla.margins.html</t>
+          <t>https://movie-locations.com/movies/d/Disclosure-Day.php</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12-09-2026 16:47 UTC</t>
+          <t>14-09-2026 01:14 UTC</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1705,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FINRA Appoints Marguerite Eastwood as Chief Human Resources Officer</t>
+          <t>Call for Applications: Cultural Entrepreneurship Programme</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>fundsforNGOs</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/finra-appoints-marguerite-eastwood-as-chief-human-resources-officer/</t>
+          <t>https://www2.fundsforngos.org/events/call-for-applications-cultural-entrepreneurship-programme/?noamp=mobile</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12-09-2026 20:52 UTC</t>
+          <t>14-09-2026 06:13 UTC</t>
         </is>
       </c>
     </row>
@@ -1732,130 +1732,130 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AstraZeneca’s Etcamah flunks first-line breast cancer trial, adding to oral SERDs’ failure record</t>
+          <t>Pfizer aims at air-traffic controllers for Covid-19 vaccine money, WSJ says</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/astrazeneca-etcamah-flunks-first-line-breast-cancer-trial-adding-oral-serds-failure-record</t>
+          <t>https://www.tipranks.com/news/the-fly/pfizer-aims-at-air-traffic-controllers-for-covid-19-vaccine-money-wsj-says-thefly-news?mod=mw_quote_news</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12-09-2026 16:43 UTC</t>
+          <t>14-09-2026 02:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mizzou volleyball handles Wichita State in three sets</t>
+          <t>Nanaga Mtb Race 2019 - LIVE Part 1 2019 UCI MTB Marathon World Championships Grachen SUI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Newsbug.info</t>
+          <t>defensorianna.gob.ar</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.newsbug.info/sports/national/mizzou-volleyball-handles-wichita-state-in-three-sets/article_b0ba7099-fcfa-5b77-ba73-fc8ad151844e.html</t>
+          <t>https://www.defensorianna.gob.ar/?d=332801414</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12-09-2026 23:37 UTC</t>
+          <t>13-09-2026 08:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Where was Disclosure Day filmed?</t>
+          <t>USFDA Issues Two Observations After Records Assessment of Dr. Reddy's Mexico API Facility</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>The Worldwide Guide To Movie Locations</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://movie-locations.com/movies/d/Disclosure-Day.php</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/usfda-issues-two-observations-after-records-assessment-of-dr-reddys-mexico-api-facility-179163</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13-09-2026 08:08 UTC</t>
+          <t>13-09-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AstraZeneca’s breast cancer pill falls short</t>
+          <t>Dr Reddy’s Mexico API Facility Gets Two Observations From USFDA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>Daily Pioneer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.manilatimes.net/2026/09/13/world/astrazenecas-breast-cancer-pill-falls-short/2423833</t>
+          <t>https://dailypioneer.com/news/slug-lite/usfda-conducts-assessment-of-dr-reddys-mexico-facility?year=2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12-09-2026 16:04 UTC</t>
+          <t>13-09-2026 08:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Biogen Sees Pivotal Pipeline Moment as It Expands Beyond Neurology</t>
+          <t>Dry skin? 8 skincare products recommended by cosmetologists | Fashion Trends</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Hindustan Times</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/biogen-sees-pivotal-pipeline-moment-210158269.html</t>
+          <t>https://www.hindustantimes.com/lifestyle/fashion/dry-skin-8-skincare-products-recommended-by-cosmetologists-101789019112080-amp.html</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12-09-2026 21:01 UTC</t>
+          <t>14-09-2026 04:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Mexico API Facility Gets Two Observations From USFDA</t>
+          <t>Morgan Stanley drops blunt verdict on Ozempic maker</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Daily Pioneer</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://dailypioneer.com/news/slug-lite/usfda-conducts-assessment-of-dr-reddys-mexico-facility?year=2026</t>
+          <t>https://sg.finance.yahoo.com/news/morgan-stanley-drops-blunt-verdict-014700805.html</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>13-09-2026 08:55 UTC</t>
+          <t>14-09-2026 01:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Apollo Hospitals seeks ₹7,500 million NCDs, Reddy reappointment at AGM</t>
+          <t>Strides Pharma Gets Three USFDA Observations Following Alathur Facility Inspection</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/apollo-hospitals-latest-results-consolidated-revenue-up-16-to-252-285-million-in-fy26/47115579</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/strides-pharma-gets-three-usfda-observations-following-alathur-facility-inspection-179165</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>13-09-2026 05:56 UTC</t>
+          <t>13-09-2026 13:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1921,184 +1921,184 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UPI has transformed financial inclusion: former RBI Governor</t>
+          <t>Sun Pharma Gets CDSCO Panel Recommendation for Phase IV Sovateltide Trial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/Hyderabad/upi-has-transformed-financial-inclusion-former-rbi-governor/article71460905.ece/amp/</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/sun-pharma-gets-cdsco-panel-recommendation-for-phase-iv-sovateltide-trial-179164</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>12-09-2026 17:08 UTC</t>
+          <t>13-09-2026 14:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TV Today Network Approves Sale Of FM Radio Business To Creative Channel</t>
+          <t>C-CAMP National Bio Entrepreneurship competition 2026 recognises 15 startups and four student teams</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ascendants.in</t>
+          <t>indianpharmapost.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://ascendants.in/industry_events/tv-today-network-fm-radio-sale-creative-channel/attachment/web-image-2-copy-2-13/</t>
+          <t>https://www.indianpharmapost.com/startup/c-camp-national-bio-entrepreneurship-competition-2026-recognises-15-startups-and-four-student-teams-21825</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>13-09-2026 05:40 UTC</t>
+          <t>14-09-2026 02:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KUDA chief assumes role as TDP election observer for Sri Sathya Sai dist</t>
+          <t>SKUAST-K scholar wins national bio-entrepreneurship award</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>thekashmirimages.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/cities/anantapur/kuda-chief-assumes-role-as-tdp-election-observer-for-sri-sathya-sai-dist-1121288</t>
+          <t>https://thekashmirimages.com/2026/09/14/skuast-k-scholar-wins-national-bio-entrepreneurship-award/</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>12-09-2026 22:51 UTC</t>
+          <t>13-09-2026 18:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lupin eyes $500 mn biosimilars revenue in medium term, to ramp capacity</t>
+          <t>Aurobindo Pharma’s API facility clears FDA inspection</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/industry/news/companies-news-lupin-eyes-500-mn-biosimilars-revenue-in-medium-term-126091300205_1.html</t>
+          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/aurobindo-pharmas-api-facility-clears-fda-inspection/134230645</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>13-09-2026 06:57 UTC</t>
+          <t>14-09-2026 02:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15 startups, four student teams win C-CAMP National Bio Entrepreneurship Competition</t>
+          <t>Aurobindo Pharma's Apitoria clears US FDA inspection with zero observations</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>indianpharmapost.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/states/karnataka/2026/Sep/13/15-startups-four-student-teams-win-c-camp-national-bio-entrepreneurship-competition</t>
+          <t>https://www.indianpharmapost.com/news/aurobindo-pharmas-apitoria-clears-us-fda-inspection-with-zero-observations-21829</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>13-09-2026 01:17 UTC</t>
+          <t>14-09-2026 04:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sanjeev Kathuria Appointed Director, Business Unit Head – Oncology Cluster at Cipla</t>
+          <t>Gland Pharma to acquire 100% stake in US subsidiary for US$ 501,208</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>indianpharmapost.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/sanjeev-kathuria-appointed-director-business-unit-head-oncology-cluster-at-cipla/</t>
+          <t>https://www.indianpharmapost.com/news/lite/gland-pharma-to-acquire-100-stake-in-us-subsidiary-for-us-501208-21827</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>13-09-2026 06:14 UTC</t>
+          <t>13-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Russians attack Ukraine's second-largest pharmaceutical warehouse twice</t>
+          <t>Marking Eight Generations of Foldable Innovation: The Incredible Evolution of Samsung’s Galaxy Z Series</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.yahoo.com/news/world/articles/russians-attack-ukraines-second-largest-081300256.html</t>
+          <t>https://news.samsung.com/ph/marking-eight-generations-of-foldable-innovation-the-incredible-evolution-of-samsungs-galaxy-z-series</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>13-09-2026 08:13 UTC</t>
+          <t>14-09-2026 04:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>13-09-2026 12:52 UTC</t>
+          <t>14-09-2026 05:20 UTC</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2137,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>I Used The Samsung Galaxy Watch Ultra2 And It Changed My Perspective About What Smartwatches Can Actually Do</t>
+          <t>Samsung launches Galaxy S26 FE in India, says it brings flagship features to more people</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BW Businessworld</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/i-used-the-samsung-galaxy-watch-ultra2-and-it-changed-my-perspective-about-what-smartwatches-can-actually-do-622455</t>
+          <t>https://www.indiatoday.in/amp/technology/news/story/samsung-launches-galaxy-s26-fe-in-india-says-it-brings-flagship-features-to-more-people-2994173-2026-09-14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>13-09-2026 09:27 UTC</t>
+          <t>14-09-2026 08:22 UTC</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2164,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Why Samsung fans are suddenly more excited about the Galaxy Z Fold 9</t>
+          <t>Samsung Galaxy S26 FE Launched in India With Exynos 2500 Chip, 4,900mAh Battery: Price, Specifications</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/why-samsung-fans-suddenly-more-excited-galaxy-z-fold-9/</t>
+          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s26-fe-price-in-india-launch-sale-date-features-specifications-12044001</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13-09-2026 04:12 UTC</t>
+          <t>14-09-2026 08:08 UTC</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>From Samsung to Salesforce to Google: How an IITian turned his ‘will to prove it’ into a dream career | Success story</t>
+          <t>Samsung And ASML Expand High-NA EUV Partnership</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>electronicsforyou.biz</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/trends/from-samsung-to-salesforce-then-cracking-job-at-google-inside-iitians-journey-of-his-will-to-prove-it-to-himse-11789302161025.html</t>
+          <t>https://www.electronicsforyou.biz/industry-buzz/samsung-and-asml-expand-high-na-euv-partnership/</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13-09-2026 13:42 UTC</t>
+          <t>14-09-2026 08:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2218,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Semiconductor patent rankings; China IP Forum; Samsung SDI strategy; Via Licensing DRAM pool launch; ETSI director-general keynote; plus much more</t>
+          <t>Samsung unveils a 10,000-nit OLED screen, the brightest yet for smartphones</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IAM Patent</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.iam-media.com/article/semiconductor-patent-rankings-china-ip-forum-samsung-sdi-strategy-licensing-dram-pool-launch-etsi-director-general-keynote-plus-much-more</t>
+          <t>https://www.sammobile.com/news/samsung-display-unveils-10000-nits-oled-screen-brightest-smartphones/</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>13-09-2026 10:43 UTC</t>
+          <t>14-09-2026 05:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2245,22 +2245,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>iPhone Duo alternatives for less at T-Mobile: Samsung Galaxy Z Fold 8, Motorola Razr Fold</t>
+          <t>Samsung's Galaxy S27 could get a display upgrade the Pixel 11 apparently missed</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>Android Authority</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://mashable.com/tech/sept-10-iphone-duo-alternatives-t-mobile-deals</t>
+          <t>https://www.androidauthority.com/samsung-galaxy-s27-m16-oled-display-3710724/</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>13-09-2026 09:29 UTC</t>
+          <t>14-09-2026 04:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 FE's India price leaks - GSMArena.com news</t>
+          <t>iQOO 16 confirmed to feature a 2K 165Hz display with Samsung M16 OLED material</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>91mobiles.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.gsmarena.com/samsung_galaxy_s26_fe_india_price_leaks-news-74595.php</t>
+          <t>https://www.91mobiles.com/hub/iqoo-16-samsung-m16-oled-display-confirmed/amp/</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12-09-2026 16:01 UTC</t>
+          <t>14-09-2026 05:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Samsung Biologics signs $262M manufacturing deal through 2033, pushing longer CDMO bookings</t>
+          <t>Samsung, SK Hynix reject KEPCO’s $17 billion power-bill prepayment plan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MarketScale</t>
+          <t>KED Global</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.marketscale.com/industries/sciences/samsung-biologics-signs-262m-manufacturing-deal-through-2033-pushing-longer-cdmo-bookings</t>
+          <t>https://www.kedglobal.com/korean-chipmakers/newsView/ked202609140001</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>13-09-2026 11:54 UTC</t>
+          <t>14-09-2026 07:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2326,22 +2326,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Best Camera Phones Under Rs. 30,000 in India: Samsung Galaxy F70 Pro 5G, Motorola Edge 70 Fusion, More</t>
+          <t>Galaxy S27 Ultra Camera Leaks: Samsung to Keep 5x Zoom, Drop 3x Lens?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>Nokiamob</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/features/best-camera-phones-in-india-under-rs-30000-samsung-galaxy-f70-pro-5g-motorola-edge-70-fusion-12028297</t>
+          <t>https://nokiamob.net/2026/09/14/samsung-galaxy-s27-ultra-rumors-the-truth-about-the-50mp-4x-sensor/</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>13-09-2026 06:30 UTC</t>
+          <t>14-09-2026 07:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2353,22 +2353,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The chip boom and a currency paradox: How a stronger won may soften Samsung, SK hynix earnings</t>
+          <t>Train Run Recover: Why Galaxy Wellness Goes Beyond Working Out</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Korea JoongAng Daily</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.koreajoongangdaily.com/business/the-chip-boom-and-a-currency-paradox-how-a-stronger-won-may-soften-samsung-sk-hynix-earnings/12872948</t>
+          <t>https://news.samsung.com/ph/train-run-recover-why-galaxy-wellness-goes-beyond-working-out</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13-09-2026 10:01 UTC</t>
+          <t>14-09-2026 04:07 UTC</t>
         </is>
       </c>
     </row>
@@ -2380,22 +2380,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Rapido driver demands Rs 18k to return stolen Samsung S24 Ultra</t>
+          <t>Samsung Galaxy S26 FE Price in India, Storage Variants Leaked Ahead of Launch</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>The Siasat Daily</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/rapido-driver-demands-rs-18k-to-return-stolen-samsung-s24-ultra-3541438/</t>
+          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s26-fe-price-in-india-storage-variants-leak-launch-date-12043187</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>13-09-2026 11:53 UTC</t>
+          <t>14-09-2026 04:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,103 +2407,103 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>More than 610 Singaporeans Unite to Take Steps for Better Heart Health at Samsung Singapore’s First Galaxy Walkathon</t>
+          <t>Samsung digs deep into its pockets as US companies poach top chip talent</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>news.samsung.com</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/sg/more-than-610-singaporeans-unite-to-take-steps-for-better-heart-health-at-samsung-singapores-first-galaxy-walkathon</t>
+          <t>https://www.sammobile.com/news/samsung-digs-deep-into-its-pockets-as-us-companies-poach-top-chip-talent/</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>13-09-2026 08:56 UTC</t>
+          <t>14-09-2026 07:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ultra-lightweight smartphone powerhouse with a 6.9-inch OLED screen—Samsung Galaxy Z Flip 8 review</t>
+          <t>Samsung Heavy Wins $1B Order for Four LNG Carriers</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Notebookcheck</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.notebookcheck.net/Ultra-lightweight-smartphone-powerhouse-with-a-6-9-inch-OLED-screen-Samsung-Galaxy-Z-Flip-8-review.1398173.0.html</t>
+          <t>https://en.sedaily.com/finance/2026/09/14/samsung-heavy-wins-1b-order-for-four-lng-carriers</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>13-09-2026 13:10 UTC</t>
+          <t>14-09-2026 06:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Rosé Spotted With iPhone 18 — Samsung Fires Back: "Should've Asked Us for a Real Phone"</t>
+          <t>Tokyo court dismisses Malaysia’s IHH unit’s claims against Daiichi Sankyo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Medical Buyer</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/d38bc930-519c-48ba-b897-b3f5ffc531c1</t>
+          <t>https://medicalbuyer.co.in/tokyo-court-dismisses-malaysias-ihh-units-claims-against-daiichi-sankyo/</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>13-09-2026 11:25 UTC</t>
+          <t>14-09-2026 08:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>How To Set Up HDMI-CEC On Your Samsung TV</t>
+          <t>Increased deaths shadow AstraZeneca, Daiichi’s Enhertu first-line lung cancer data</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Engadget</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2252825/how-to-set-up-hdmi-cec-samsung-tv/</t>
+          <t>https://www.fiercepharma.com/pharma/higher-death-risk-shadows-astrazeneca-daiichi-enhertu-first-line-lung-cancer-data</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>13-09-2026 14:00 UTC</t>
+          <t>13-09-2026 23:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2515,22 +2515,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tokyo court dismisses NTK's claims against Daiichi Sankyo; costs on NTK</t>
+          <t>Tokyo Court rejects IHH unit's claims against Daiichi Sankyo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>sbr.com.sg</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/tokyo-district-court-dismisses-ntk-s-claim-against-daiichi-sankyo/50658388</t>
+          <t>https://sbr.com.sg/healthcare/news/tokyo-court-rejects-ihh-units-claims-against-daiichi-sankyo</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>13-09-2026 06:37 UTC</t>
+          <t>14-09-2026 02:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2542,22 +2542,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Swarup Datta Appointed Vice President – Head R&amp;D, CDMO at Glochem Industries</t>
+          <t>Enhertu® Demonstrated a Median Progression-Free Survival of 14.3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>natlawreview.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/swarup-datta-appointed-vice-president-head-rd-cdmo-at-glochem-industries/</t>
+          <t>https://natlawreview.com/press-releases/enhertur-demonstrated-median-progression-free-survival-143-months-first-line</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>13-09-2026 11:04 UTC</t>
+          <t>14-09-2026 03:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2569,22 +2569,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GSK’s ADC lays down marker for lung cancer scrap with Merck</t>
+          <t>AstraZeneca, Daiichi report Enhertu benefit in advanced lung cancer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fierce Biotech</t>
+          <t>London South East</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.fiercebiotech.com/biotech/gsks-adc-lays-down-marker-lung-cancer-scrap-merck-co</t>
+          <t>https://www.lse.co.uk/news/astrazeneca-daiichi-report-enhertu-benefit-in-advanced-lung-cancer-o6o75ns4dmqn0hr.html</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>12-09-2026 22:57 UTC</t>
+          <t>14-09-2026 02:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,290 +2596,695 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Manipal Hospitals scouts for acquisitions in Andhra, Keralam, Delhi-NCR; bets on AI-led healthcare</t>
+          <t>ENHERTU® (fam-trastuzumab deruxtecan-nxki) demonstrated a median progression-free survival of 14.3 months as 1st-line therapy in patients with HER2-mutant advanced non-small cell lung cancer in DESTINY-Lung04 Phase III trial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>FinancialContent</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/healthcare/biotech/healthcare/manipal-hospitals-scouts-for-acquisitions-in-andhra-keralam-delhi-ncr-bets-on-ai-led-healthcare/articleshow/134179222.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
+          <t>https://www.financialcontent.com/article/bizwire-2026-9-14-enhertu-fam-trastuzumab-deruxtecan-nxki-demonstrated-a-median-progression-free-survival-of-143-months-as-1st-line-therapy-in-patients-with-her2-mutant-advanced-non-small-cell-lung-cancer-in-destiny-lung04-phase-iii-trial</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>13-09-2026 05:14 UTC</t>
+          <t>14-09-2026 01:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Leaders of BRICS countries call for stronger cooperation in health, endorse initiatives on tuberculosis</t>
+          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Stocktwits</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/healthcare/biotech/healthcare/leaders-of-brics-countries-call-for-stronger-cooperation-in-health-endorse-initiatives-on-tb/articleshow/134139783.cms</t>
+          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>12-09-2026 15:08 UTC</t>
+          <t>13-09-2026 21:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JSW Infrastructure achieves 'Low Risk' ESG rating from Morningstar Sustainalytics</t>
+          <t>MEDIPAL HOLDINGS CORPORATION and JCR Pharmaceuticals Dose First Patient in Global Phase I/II Trial of JR-446 for Mucopolysaccharidosis Type IIIB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://businessupturn.com/business/corporates/jsw-infrastructure-achieves-low-risk-esg-rating-from-morningstar-sustainalytics/</t>
+          <t>https://www.biospace.com/press-releases/medipal-holdings-corporation-and-jcr-pharmaceuticals-dose-first-patient-in-global-phase-i-ii-trial-of-jr-446-for-mucopolysaccharidosis-type-iiib</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>12-09-2026 23:27 UTC</t>
+          <t>14-09-2026 02:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+          <t>MEDIPAL, JCR Dose First Patient in Global Phase I/II Trial of JR-446 for Sanfilippo Syndrome</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>BioPharma APAC</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+          <t>https://biopharmaapac.com/news/86/8425/medipal-jcr-dose-first-patient-in-global-phase-i-ii-trial-of-jr-446-for-sanfilippo-syndrome.html</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>12-09-2026 17:29 UTC</t>
+          <t>13-09-2026 18:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Teva Pharmaceuticals Seeks FDA Greenlight For New Schizophrenia Treatment</t>
+          <t>EMPLOYMENT (14-09-2026)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>dailyexcelsior.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/teva-pharmaceuticals-seeks-fda-greenlight-for-schizophrenia-treatment/cZRNir1R4xt</t>
+          <t>https://www.dailyexcelsior.com/employment-14-09-2026/amp</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>12-09-2026 15:28 UTC</t>
+          <t>14-09-2026 05:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+          <t>Irish pharmacists warn against replacing prescription medicines with social media health trends</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>Galway Advertiser</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+          <t>http://www.advertiser.ie/galway/article/151819/irish-pharmacists-warn-against-replacing-prescription-medicines-with-social-media-health-trends</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>12-09-2026 17:29 UTC</t>
+          <t>13-09-2026 10:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Jamp Pharma</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Aurora Cannabis Taps Pharma Veteran to Drive Global Commercial Push</t>
+          <t>Certain Ordinary Shares of Alvotech are subject to a Lock-Up Agreement Ending on 14-SEP-2026.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/aurora-cannabis-taps-pharma-veteran-to-drive-global-commercial-push</t>
+          <t>https://www.marketscreener.com/news/certain-ordinary-shares-of-alvotech-are-subject-to-a-lock-up-agreement-ending-on-14-sep-2026-ce785bdcd889f520</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>12-09-2026 15:04 UTC</t>
+          <t>14-09-2026 00:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Samsung Bioepis Named Top Job-Creating Company</t>
+          <t>eQ Plc Members of the Shareholders’ Nomination Committee</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>thelec.net</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.thelec.net/news/articleView.html?idxno=13875</t>
+          <t>https://uk.finance.yahoo.com/news/avacta-appoints-mats-blom-board-060000062.html</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>12-09-2026 23:26 UTC</t>
+          <t>14-09-2026 06:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Samsung Biologics signs $262M manufacturing deal through 2033, pushing longer CDMO bookings</t>
+          <t>Results for Teva Bouchgua at REMA Saquarema Surf Festival 2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MarketScale</t>
+          <t>World Surf League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.marketscale.com/industries/sciences/samsung-biologics-signs-262m-manufacturing-deal-through-2033-pushing-longer-cdmo-bookings</t>
+          <t>https://www.worldsurfleague.com/athletes/9259/teva-bouchgua/eventresults?eventId=5182</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>13-09-2026 11:54 UTC</t>
+          <t>13-09-2026 20:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>APAC Healthcare Weekly (Sept 13) – Hansoh, InSilico, Shionogi, Kyowa Kirin, Samsung Bio, SK Biopharm</t>
+          <t>Teva Women's Teva Ember Moc Sizing Teva Ember Moc Teva Slip On Shoes Teva Ember Moc Slip On Blue</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>smartkarma.com</t>
+          <t>fuelcarmagazine</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.smartkarma.com/insights/apac-healthcare-weekly-sept-13-hansoh-insilico-shionogi-kyowa-kirin-samsung-bio-sk-biopharm</t>
+          <t>https://fuelcarmagazine.com/?x=4032494051270</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>13-09-2026 01:46 UTC</t>
+          <t>13-09-2026 19:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>How to Trade This $2 Billion Biotech Name Moving Quickly Toward Profit</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>pro.thestreet.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://pro.thestreet.com/trade-ideas/how-to-trade-this-2-billion-biotech-name-moving-quickly-toward-profit</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>13-09-2026 15:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>13-09-2026 21:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Samsung, LG to Pay Suppliers ₩1.9 Trillion (approximately $1.4 Billion) Early Ahead of Chuseok</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>finance.biggo.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://finance.biggo.com/news/8b2649e0-23cf-481b-b34d-61f9cf822d8a</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>14-09-2026 06:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>“Samsung Group to release KRW 1.3 trillion before Chuseok,” paying suppliers seven days early</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>매일경제</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/en/business/12151952</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Samsung advances 1.3 trillion-won supplier payments to boost Korea’s economy - CHOSUNBIZ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://biz.chosun.com/en/en-it/2026/09/14/233PHRZEDBEHTOHAB26HDNIAA4/</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Samsung and LG Advance 1.9 Trillion Won in Payments Ahead of Chuseok, All-Out Effort for Mutual Growth and Domestic Demand</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>아시아경제</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.asiae.co.kr/en/article/enterprise-CEO/2026091410510214218</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Samsung Biologics signs $262M manufacturing deal through 2033, pushing longer CDMO bookings</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>MarketScale</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.marketscale.com/industries/sciences/samsung-biologics-signs-262m-manufacturing-deal-through-2033-pushing-longer-cdmo-bookings</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>13-09-2026 11:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>“Samsung Group to release KRW 1.3 trillion before Chuseok,” paying suppliers seven days early</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>매일경제</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/en/business/12151952</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Songdo Opens Bio Training Center to Ease Talent Shortage</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Seoul Economic Daily</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://en.sedaily.com/society/2026/09/14/songdo-opens-bio-training-center-to-ease-talent-shortage</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>14-09-2026 00:29 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>The CDMO Revolution: How Contract Drug Manufacturers Are Reshaping Global Pharma- Expert View by Spherical Insights</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>sphericalinsights.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.sphericalinsights.com/blogs/the-cdmo-revolution-how-contract-drug-manufacturers-are-reshaping-global-pharma</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>13-09-2026 17:51 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Samsung advances 1.3 trillion-won supplier payments to boost Korea’s economy - CHOSUNBIZ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://biz.chosun.com/en/en-it/2026/09/14/233PHRZEDBEHTOHAB26HDNIAA4/</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Samsung and LG Advance 1.9 Trillion Won in Payments Ahead of Chuseok, All-Out Effort for Mutual Growth and Domestic Demand</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>아시아경제</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.asiae.co.kr/en/article/enterprise-CEO/2026091410510214218</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Samsung, LG to Pay Suppliers ₩1.9 Trillion (approximately $1.4 Billion) Early Ahead of Chuseok</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>finance.biggo.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://finance.biggo.com/news/8b2649e0-23cf-481b-b34d-61f9cf822d8a</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>14-09-2026 06:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Samsung to pay 1.3 trillion won early to suppliers</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>디지털투데이</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.digitaltoday.co.kr/en/view/103165/samsung-to-pay-1-3-trillion-won-early-to-suppliers</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>U.S., Japan Rate Decisions Converge in Super Week</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Seoul Economic Daily</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://en.sedaily.com/finance/2026/09/14/us-japan-rate-decisions-converge-in-super-week</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>14-09-2026 01:51 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
         <is>
           <t>Samsung Biologics (KRX: 207940) Secures $262M Manufacturing Deal With European Pharma As Peptide Push Advances</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>londoninsider.co.uk</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>https://londoninsider.co.uk/samsung-biologics-krx-207940-secures-262m-manufacturing-deal-with-european-pharma-as-peptide-push-advances/</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>13-09-2026 10:49 UTC</t>
         </is>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thailand moves from buying medicines to building them</t>
+          <t>Sandoz issues EUR 500 million bond</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pattaya Mail</t>
+          <t>boerse.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pattayamail.com/latestnews/news/thailand-moves-from-buying-medicines-to-building-them-564872</t>
+          <t>https://www.boerse.de/nachrichten-amp/Sandoz-issues-EUR-500-million-bond/38598140</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13-09-2026 19:19 UTC</t>
+          <t>14-09-2026 15:40 UTC</t>
         </is>
       </c>
     </row>
@@ -490,346 +490,346 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thailand seeks 100 billion baht in pharmaceutical research investment</t>
+          <t>Lupin targets $500 million biosimilar revenue in five years</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pattaya Mail</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pattayamail.com/thailandnews/thailand-seeks-100-billion-baht-in-pharmaceutical-research-investment-564941</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/lupin-targets-500-million-biosimilar-revenue-in-five-years</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13-09-2026 18:45 UTC</t>
+          <t>14-09-2026 15:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Salmonella Control Vaccines Market Forecast to 2035: Poultry Demand Drives Growth - News and Statistics</t>
+          <t>Avecho Biotechnology (ASX:AVE): Phase III Insomnia Trial and Commercial Pathway in Focus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>Kalkine</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/salmonella-control-vaccines-market-to-accelerate-on-poultry-demand-reaching-2035-growth/</t>
+          <t>https://kalkine.com.au/news/healthcare/avecho-biotechnology-asxave-phase-iii-insomnia-trial-and-commercial-pathway-in-focus</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13-09-2026 10:51 UTC</t>
+          <t>14-09-2026 08:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Increased deaths shadow AstraZeneca, Daiichi’s Enhertu first-line lung cancer data</t>
+          <t>Meche Cancels Jury Selection</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>St. Landry Now Online Newspaper</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/higher-death-risk-shadows-astrazeneca-daiichi-enhertu-first-line-lung-cancer-data</t>
+          <t>https://www.stlandrynow.com/community/local-news/meche-cancels-jury-selection/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13-09-2026 23:00 UTC</t>
+          <t>14-09-2026 16:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Phase III MAVERICK Trial Supports Brain MRI Surveillance Alone as Standard of Care for Small-Cell Lung Cancer</t>
+          <t>Thailand moves from buying medicines to building them</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>Pattaya Mail</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/phase-iii-maverick-trial-supports-125400219.html</t>
+          <t>https://www.pattayamail.com/latestnews/news/thailand-moves-from-buying-medicines-to-building-them-564872</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13-09-2026 12:54 UTC</t>
+          <t>13-09-2026 19:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Avian Newcastle Disease Tests Market Forecast to 2035: Growth Driven by Expanding Poultry Biosecurity Mandates</t>
+          <t>Thailand seeks 100 billion baht in pharmaceutical research investment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>Pattaya Mail</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/avian-newcastle-disease-tests-market-forecast-to-2035-growth-driven-by-expanding-poultry-biosecurity-mandates/</t>
+          <t>https://www.pattayamail.com/thailandnews/thailand-seeks-100-billion-baht-in-pharmaceutical-research-investment-564941</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13-09-2026 17:16 UTC</t>
+          <t>13-09-2026 18:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Egypt shuts Dar Al-Hikma Hospital after child's death following tonsillectomy - Health - Egypt</t>
+          <t>BUILDING HEALTHIER COMMUNITIES: VIETNAM’S HEALTHCARE OUTLOOK &amp; OPPORTUNITIES</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ahram Online</t>
+          <t>CarePlus VietNam</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://english.ahram.org.eg/NewsContentP/1/576547/Egypt/Egypt-shuts-Dar-AlHikma-Hospital-after-child;s-dea.aspx</t>
+          <t>https://www.careplusvn.com/en/building-healthier-communities-vietnams-healthcare-outlook-opportunities</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13-09-2026 14:27 UTC</t>
+          <t>14-09-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Al-Ahly Tripoli advances to CAF Confederation Cup second round</t>
+          <t>When Words Stay Silent: How Sign Language Avatars Are Transforming Access to Medicine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The Libya Observer</t>
+          <t>CSRwire</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://libyaobserver.ly/sports/al-ahly-tripoli-advances-caf-confederation-cup-second-round</t>
+          <t>https://csrwire.com/press-release/when-words-stay-silent-how-sign-language-avatars-transforming-access-medicine/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13-09-2026 16:29 UTC</t>
+          <t>14-09-2026 14:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fatat takes bronze at Arab Women’s Basketball Championship</t>
+          <t>Takeda R&amp;D President Andy Plump to Retire in 2027</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Arab Times Kuwait News</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.arabtimesonline.com/news/fatat-takes-bronze-at-arab-womens-basketball-championship/</t>
+          <t>https://www.contractpharma.com/breaking-news/takeda-rd-president-andy-plump-to-retire-in-2027/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13-09-2026 17:14 UTC</t>
+          <t>14-09-2026 14:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amgen Irish Open 2026: Shane Lowry Chases $1.02 Million Winner’s Prize</t>
+          <t>DLG's animal nutrition unit beats expectations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NDTV Sports</t>
+          <t>Feed Strategy</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://sports.ndtv.com/us/golf/amgen-irish-open-2026-shane-lowry-chases-1-02-million-winner-s-prize-12042352</t>
+          <t>https://www.feedstrategy.com/business-markets/company-news/news/15834794/dlgs-animal-nutrition-unit-beats-expectations</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13-09-2026 18:30 UTC</t>
+          <t>14-09-2026 16:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Advancing Innovation in Small Cell Lung Cancer at WCLC 2026 – Amgen</t>
+          <t>Vyome Welcomes Jerry Leonard as New Chief Financial Officer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oncodaily</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://oncodaily.com/industry/amgen-585539</t>
+          <t>https://www.contractpharma.com/breaking-news/vyome-welcomes-jerry-leonard-as-new-chief-financial-officer/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13-09-2026 19:00 UTC</t>
+          <t>14-09-2026 16:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amgen Irish Open | Day four highlights</t>
+          <t>CAR-T therapies, bispecific antibodies, and antifibrotics in development open a new avenue against scleroderma</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sky Sports</t>
+          <t>Demócrata</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/golf/video/30998/13585561/amgen-irish-open-day-four-highlights</t>
+          <t>https://www.democrata.es/en/health/car-t-therapies-bispecific-antibodies-and-antifibrotics-in-development-open-a-new-avenue-against-scleroderma/amp/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13-09-2026 18:20 UTC</t>
+          <t>14-09-2026 14:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shane Lowry surges to stunning Amgen Irish Open victory</t>
+          <t>Hikma MP says crossings were closed to stop suspects fleeing to Iran</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DP World Tour</t>
+          <t>964media</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.europeantour.com/dpworld-tour/news/articles/detail/shane-lowry-surges-to-stunning-amgen-irish-open-victory/</t>
+          <t>https://en.964media.com/52521/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13-09-2026 17:24 UTC</t>
+          <t>14-09-2026 09:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shane Lowry Claims Dominant Home Soil Victory at Amgen Irish Open</t>
+          <t>Fatat takes bronze at Arab Women’s Basketball Championship</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ACCESS Newswire</t>
+          <t>Arab Times Kuwait News</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.accessnewswire.com/newsroom/en/sports-leisure-and-entertainment/shane-lowry-claims-dominant-home-soil-victory-at-amgen-irish-open-1220343</t>
+          <t>https://www.arabtimesonline.com/news/fatat-takes-bronze-at-arab-womens-basketball-championship/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13-09-2026 19:59 UTC</t>
+          <t>13-09-2026 17:14 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Final LIV Golf Leaderboard At The Amgen Irish Open</t>
+          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>golfmonthly.com</t>
+          <t>Golf Channel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.golfmonthly.com/news/liv-golf-leaderboard-amgen-irish-open-2026</t>
+          <t>https://www.golfchannel.com/watch/dp-world-tour/dp-world-tour-highlights-2026-amgen-irish-open-round-3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13-09-2026 20:14 UTC</t>
+          <t>14-09-2026 08:47 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trump’s in Ireland to meet leaders and attend Amgen Irish Open</t>
+          <t>Amgen Leads The Pack With First Filing For US Opdivo Biosimilar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>eciks.org</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://eciks.org/26569-trump-arrives-ireland-doonbeg</t>
+          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/amgen-leads-the-pack-with-first-filing-for-us-opdivo-biosimilar-PD6ZNDEA2VA4XKUQ44XCXQCZHI/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13-09-2026 22:24 UTC</t>
+          <t>14-09-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shane Lowry wins Amgen Irish Open by a whopping 11 shots over Patrick Reed, Joaquin Niemann</t>
+          <t>Points and prize money: See what every player won at the Amgen Irish Open</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Golfweek</t>
+          <t>DP World Tour</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://golfweek.usatoday.com/story/sports/golf/dpworldtour/2026/09/13/shane-lowry-wins-amgen-irish-open-2026-10-shots/91746369007/</t>
+          <t>https://www.europeantour.com/dpworld-tour/news/articles/detail/points-and-prize-money-see-what-every-player-won-at-the-2026-amgen-irish-open/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13-09-2026 18:16 UTC</t>
+          <t>14-09-2026 09:21 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GALLERY: Trump attends Amgen Irish Open in Doonbeg, Ireland</t>
+          <t>Amgen Irish Open 2026: Shane Lowry Chases $1.02 Million Winner’s Prize</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WXLV</t>
+          <t>NDTV Sports</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://abc45.com/news/nation-world/gallery-us-president-donald-trump-attends-amgen-irish-open-in-doonbeg-ireland-trump-international-golf-links-and-hotel-tournament-shane-lowry-eric-trump-guy-kinnings-joaquin-niemann-jacob-skov-olesen-andy-sullivan-tom-mckibbin</t>
+          <t>https://sports.ndtv.com/us/golf/amgen-irish-open-2026-shane-lowry-chases-1-02-million-winner-s-prize-12042352</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13-09-2026 14:24 UTC</t>
+          <t>13-09-2026 18:30 UTC</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shane Lowry runs away with record 11-stroke victory at Amgen Irish Open, Rory McIlroy closes on positive note</t>
+          <t>Amgen Gets FDA Approval to Reduce Monitoring Time for First Two Imdelltra Doses</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PGA Tour</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pgatour.com/article/news/latest/2026/09/13/shane-lowry-runs-away-with-record-11-shot-victory-at-2026-amgen-irish-open-scores-leaderboard-results-rory-mcilroy-patrick-reed</t>
+          <t>https://www.marketscreener.com/news/amgen-gets-fda-approval-to-reduce-monitoring-time-for-first-two-imdelltra-doses-ce785bdcdc81f62d</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13-09-2026 19:14 UTC</t>
+          <t>14-09-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GALLERY: Trump attends Amgen Irish Open in Doonbeg, Ireland</t>
+          <t>Shane Lowry runs away with record 11-stroke victory at Amgen Irish Open, Rory McIlroy closes on positive note</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>National News Desk</t>
+          <t>pgatour.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://thenationaldesk.com/news/americas-news-now/gallery-us-president-donald-trump-attends-amgen-irish-open-in-doonbeg-ireland-trump-international-golf-links-and-hotel-tournament-shane-lowry-eric-trump-guy-kinnings-joaquin-niemann-jacob-skov-olesen-andy-sullivan-tom-mckibbin</t>
+          <t>https://www.pgatour.com/article/news/latest/2026/09/13/shane-lowry-runs-away-with-record-11-shot-victory-at-2026-amgen-irish-open-scores-leaderboard-results-rory-mcilroy-patrick-reed</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13-09-2026 14:14 UTC</t>
+          <t>14-09-2026 09:16 UTC</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amgen Irish Open Day 4 recap: Lowry wins in style</t>
+          <t>Amgen Irish Open | Day four highlights</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RTE.ie</t>
+          <t>Sky Sports</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.rte.ie/sport/golf/2026/0913/1591353-amgen-irish-open-day-4-updates-mcilroy-out-early/</t>
+          <t>https://www.skysports.com/golf/video/30998/13585561/amgen-irish-open-day-four-highlights</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13-09-2026 09:54 UTC</t>
+          <t>13-09-2026 18:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1030,49 +1030,49 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amgen Irish Open: Shane Lowry secures record 11-stroke victory at Trump International Links in Doonbeg</t>
+          <t>FDA shortens monitoring time for first IMDELLTR...</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sky Sports</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/golf/news/12176/13585479/amgen-irish-open-shane-lowry-secures-record-11-stroke-victory-at-trump-international-links-in-doonbeg</t>
+          <t>https://pluang.com/en/news-feed/fda-setujui-pengurangan-waktu-pemantauan-imdelltra</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13-09-2026 18:59 UTC</t>
+          <t>14-09-2026 13:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Urban Jungle: Adopting Nature in London's Barbican Conservatory</t>
+          <t>FDA accepts extended duration sNDA for MIUDELLA IUD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Devdiscourse</t>
+          <t>contemporaryobgyn.net</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3976751-urban-jungle-adopting-nature-in-londons-barbican-conservatory</t>
+          <t>http://www.contemporaryobgyn.net/view/fda-accepts-extended-duration-snda-miudella-iud</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14-09-2026 06:00 UTC</t>
+          <t>14-09-2026 15:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>London 'plant parents' adopt a piece of historic Barbican urban jungle</t>
+          <t>In the early 1800s, Giant Hogweed was introduced by British explorers for ornamental gardens, but it spre</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/lifestyle/london-plant-parents-adopt-piece-historic-barbican-urban-jungle-2026-09-14/</t>
+          <t>https://timesofindia.indiatimes.com/world/uk/in-the-early-1800s-giant-hogweed-was-introduced-by-british-explorers-for-ornamental-gardens-but-it-spread-beyond-control-and-is-now-a-feared-invasive-plant/articleshow/134127954.cms</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14-09-2026 06:07 UTC</t>
+          <t>14-09-2026 09:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BRICS Backs Expert Group on Traditional Medicine, Calls for Evidence-Based Global Cooperation</t>
+          <t>BeautifulChinaING: Walking through Changbai Mountain for 40 years, a Chinese botanist captures 520,000 plant images and China’s changing landscape</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PIB</t>
+          <t>Global Times</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2309695&amp;reg=3&amp;lang=1</t>
+          <t>https://www.globaltimes.cn/page/202609/1370511.shtml</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13-09-2026 08:37 UTC</t>
+          <t>14-09-2026 13:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Windsor Ventra Assembly auto parts workers vote by 99 percent to authorize strike</t>
+          <t>What Your Jade Plant Needs in September to Stay Bright and Healthy Through Fall</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>World Socialist Web Site</t>
+          <t>Homes and Gardens</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.wsws.org/en/articles/2026/09/14/ivvi-s14.html</t>
+          <t>https://www.homesandgardens.com/gardens/what-a-jade-plant-needs-in-september</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14-09-2026 02:15 UTC</t>
+          <t>14-09-2026 16:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18% of booths have got 5 or fewer forms for new voters in electoral roll</t>
+          <t>Almonty and the Government of Rwanda Form Strategic Tungsten Partnership</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/ranchi/18-of-booths-have-got-5-or-fewer-forms-for-new-voters-in-electoral-roll/amp_articleshow/134216422.cms</t>
+          <t>https://www.businesswire.com/news/home/20260914171760/en/Almonty-and-the-Government-of-Rwanda-Form-Strategic-Tungsten-Partnership</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13-09-2026 17:45 UTC</t>
+          <t>14-09-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cleaning Fresh Walnut Is An Art Form: Watch Hina Khan Peel Douin Like An Expert</t>
+          <t>PPPL and UKAEA Experts Make a Plan to Connect Research on Two Fusion Supercomputers Across the Atlantic | Newswise</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>News18</t>
+          <t>Newswise</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.news18.com/amp/lifestyle/food/cleaning-fresh-walnut-is-an-art-form-watch-hina-khan-peel-douin-like-an-expert-10326857.html</t>
+          <t>https://www.newswise.com/articles/pppl-and-ukaea-experts-make-a-plan-to-connect-research-on-two-fusion-supercomputers-across-the-atlantic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13-09-2026 14:36 UTC</t>
+          <t>14-09-2026 14:40 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Essex data centre could 'threaten bumblebee and one of Britain's rarest plants'</t>
+          <t>The Thematic Showcase: Material Form &amp; Tactile Surface</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BBC</t>
+          <t>Mutual Art</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.bbc.co.uk/news/articles/c24jrm0v8j4o</t>
+          <t>https://www.mutualart.com/Article/The-Thematic-Showcase--Material-Form---T/1ED2A4F0F98FE1F7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14-09-2026 05:43 UTC</t>
+          <t>14-09-2026 14:29 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>How ammonium sulphate delivers plant available sulphur</t>
+          <t>How soybeans took over the American diet – without anyone noticing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RealAgriculture</t>
+          <t>Cobb Courier</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.realagriculture.com/2026/09/how-ammonium-sulphate-delivers-plant-available-sulphur/</t>
+          <t>https://cobbcountycourier.com/2026/09/how-soybeans-took-over-the-american-diet-without-anyone-noticing/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13-09-2026 10:08 UTC</t>
+          <t>14-09-2026 14:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>How soybeans took over the American diet – without anyone noticing</t>
+          <t>Florist Special With Bri Lovie</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>salon.com</t>
+          <t>Thursd</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.salon.com/2026/09/13/how-soybeans-took-over-the-american-diet-without-anyone-noticing-partner/</t>
+          <t>https://thursd.com/articles/florist-special-with-bri-lovie</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13-09-2026 14:30 UTC</t>
+          <t>14-09-2026 09:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bill Ferree Obituary Sep 10, 2026</t>
+          <t>Urban Jungle: Adopting Nature in London's Barbican Conservatory</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pugh Funeral Home</t>
+          <t>Devdiscourse</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pughfuneralhome.com/obituaries/bill-ferree</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3976751-urban-jungle-adopting-nature-in-londons-barbican-conservatory</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14-09-2026 07:25 UTC</t>
+          <t>14-09-2026 06:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nanomaterials trigger stage specific plant responses</t>
+          <t>Rytas Vilgalys Explores a Hidden World Under Our Feet</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>agronews.com</t>
+          <t>Duke Today</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://agronews.com/us/en/news/agricultural-blog/2026-09-13/103751</t>
+          <t>https://today.duke.edu/2026/09/rytas-vilgalys-explores-hidden-world-under-our-feet</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13-09-2026 23:39 UTC</t>
+          <t>14-09-2026 16:05 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cut Back These 5 Flowering Vines This Fall for Even More Growth Next Spring, Gardening Pros Say</t>
+          <t>Lonza deepens US bet with commercial plant in Oregon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The Spruce</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.thespruce.com/flowering-vines-to-cut-in-fall-12083508</t>
+          <t>https://www.thepharmaletter.com/pharma-news/lonza-deepens-us-bet-with-commercial-spray-drying-plant-in-oregon</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13-09-2026 23:36 UTC</t>
+          <t>14-09-2026 10:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Where can the LEGO Botanicals personality plants go next?</t>
+          <t>Harnessing sunlight to fight bacteria</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brick Fanatics</t>
+          <t>Sciworthy</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.brickfanatics.com/where-can-lego-botanicals-personality-plants-go</t>
+          <t>https://sciworthy.com/harnessing-sunlight-to-fight-bacteria/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13-09-2026 18:14 UTC</t>
+          <t>14-09-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,49 +1408,49 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Powdery mildew disease can be controlled</t>
+          <t>London 'plant parents' adopt a piece of historic Barbican urban jungle</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>chicagotribune.com</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.chicagotribune.com/2026/09/13/overgrown-lilacs-pruning-powdery-mildew/</t>
+          <t>https://www.reuters.com/lifestyle/london-plant-parents-adopt-piece-historic-barbican-urban-jungle-2026-09-14/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13-09-2026 11:00 UTC</t>
+          <t>14-09-2026 06:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rural crime survey 'will shape priorities', says Durham police commissioner</t>
+          <t>Pfizer Independent Medical Education Grant Program</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BBC</t>
+          <t>fundsforngos.org</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.bbc.co.uk/news/articles/c86x78e9yd4o</t>
+          <t>https://www2.fundsforngos.org/research-2/pfizer-independent-medical-education-grant-program/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13-09-2026 16:44 UTC</t>
+          <t>14-09-2026 05:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pfizer Quality Improvement Grant for System-Level Solutions</t>
+          <t>Can Pfizer Overcome Its COVID and Patent Cliff Headwinds?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>fundsforNGOs</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research-2/pfizer-quality-improvement-grant-for-system-level-solutions/</t>
+          <t>https://finance.yahoo.com/healthcare/articles/pfizer-overcome-covid-patent-cliff-133700992.html</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14-09-2026 05:44 UTC</t>
+          <t>14-09-2026 13:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pfizer Makes an Unusual Enemy in $2 Billion Fight Over Unwanted Covid-19 Vaccines</t>
+          <t>Transcript : Pfizer Inc. Presents at Morgan Stanley 24th Annual Global Healthcare Conference, Sep-14-2026 10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/business/pfizer-makes-an-unusual-enemy-in-2-billion-fight-over-unwanted-covid-19-vaccines-a5ad7c8d</t>
+          <t>https://www.marketscreener.com/news/transcript-pfizer-inc-presents-at-morgan-stanley-24th-annual-global-healthcare-conference-sep-14-ce785bdcdf81f720</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13-09-2026 14:39 UTC</t>
+          <t>14-09-2026 15:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pfizer Independent Medical Education Grant Program</t>
+          <t>Cluster Headache Treatment Tips and Nuances</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>fundsforNGOs</t>
+          <t>Medscape</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research-2/pfizer-independent-medical-education-grant-program/</t>
+          <t>https://www.medscape.com/viewarticle/cluster-headache-treatment-tips-and-nuances-2026a1000v1k?src=</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14-09-2026 05:49 UTC</t>
+          <t>14-09-2026 13:05 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Viatris names Kim Sun-A head of Japan-Korea cluster</t>
+          <t>Pfizer Sets Novel Path in Fee Fight | The Wall Street Journal - newspaper</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Magzter</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33156</t>
+          <t>https://www.magzter.com/stories/newspaper/The-Wall-Street-Journal/PFIZER-SETS-NOVEL-PATH-IN-FEE-FIGHT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>14-09-2026 04:17 UTC</t>
+          <t>14-09-2026 15:41 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pfizer seizes air traffic fees to recover $2.2b from Poland, Romania - CHOSUNBIZ</t>
+          <t>Pfizer Quality Improvement Grant for System-Level Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>fundsforngos.org</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-international/2026/09/14/GB5CCJRCGRGZ3BAWLCUXEBW6JU/</t>
+          <t>https://www2.fundsforngos.org/research-2/pfizer-quality-improvement-grant-for-system-level-solutions/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14-09-2026 05:43 UTC</t>
+          <t>14-09-2026 05:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Etcamah misses main goal after recent FDA approval</t>
+          <t>Association Between COVID-19 Vaccine Doses and Neurosensory Symptoms Among COVID-19-Positive Patients: A Retrospective Cross-Sectional Study</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>lifesciencenordic.com</t>
+          <t>Cureus</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.lifesciencenordic.com/article/view/1245758/etcamah_misses_main_goal_after_recent_fda_approval</t>
+          <t>https://www.cureus.com/articles/531853-association-between-covid-19-vaccine-doses-and-neurosensory-symptoms-among-covid-19-positive-patients-a-retrospective-cross-sectional-study?score_article=true</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>14-09-2026 08:17 UTC</t>
+          <t>14-09-2026 16:24 UTC</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>After a brief storm of political headwinds, mRNA is back with strong momentum</t>
+          <t>Pfizer Says Major Headwinds Are Easing as Pipeline, Obesity Plans Take Center Stage</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/drug-development/after-a-brief-storm-of-political-headwinds-mrna-is-back-with-strong-momentum</t>
+          <t>https://finance.yahoo.com/healthcare/articles/pfizer-says-major-headwinds-easing-160235029.html</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>14-09-2026 04:10 UTC</t>
+          <t>14-09-2026 16:02 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Japan: Syphilis surge and Penicillin shortage is not a good combination</t>
+          <t>Viatris names Kim Sun-A head of Japan-Korea cluster</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>outbreaknewstoday.substack.com</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://outbreaknewstoday.substack.com/p/japan-syphilis-surge-and-penicillin</t>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33156</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13-09-2026 12:56 UTC</t>
+          <t>14-09-2026 04:17 UTC</t>
         </is>
       </c>
     </row>
@@ -1678,103 +1678,103 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Where was Disclosure Day filmed?</t>
+          <t>Pfizer seizes air traffic fees to recover $2.2b from Poland, Romania - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>movie-locations.com</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://movie-locations.com/movies/d/Disclosure-Day.php</t>
+          <t>https://biz.chosun.com/en/en-international/2026/09/14/GB5CCJRCGRGZ3BAWLCUXEBW6JU/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>14-09-2026 01:14 UTC</t>
+          <t>14-09-2026 05:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Call for Applications: Cultural Entrepreneurship Programme</t>
+          <t>Cape Pioneer 2026 promises fierce racing as route changes and rider numbers rise</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>fundsforNGOs</t>
+          <t>George Herald</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/events/call-for-applications-cultural-entrepreneurship-programme/?noamp=mobile</t>
+          <t>https://www.georgeherald.com/Sport/Article/Other/cape-pioneer-2026-promises-fierce-racing-as-route-changes-and-rider-numbers-rise-202609141025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14-09-2026 06:13 UTC</t>
+          <t>14-09-2026 08:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pfizer aims at air-traffic controllers for Covid-19 vaccine money, WSJ says</t>
+          <t>Dr Reddy’s launches educational initiative to strengthen obesity care workforce</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/the-fly/pfizer-aims-at-air-traffic-controllers-for-covid-19-vaccine-money-wsj-says-thefly-news?mod=mw_quote_news</t>
+          <t>https://www.thehindubusinessline.com/companies/dr-reddys-launches-educational-initiative-to-strengthen-obesity-care-workforce/article71465962.ece</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14-09-2026 02:34 UTC</t>
+          <t>14-09-2026 11:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nanaga Mtb Race 2019 - LIVE Part 1 2019 UCI MTB Marathon World Championships Grachen SUI</t>
+          <t>Dr. Reddy’s launches nationwide programme to train 5,000+ certified obesity educators</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>defensorianna.gob.ar</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.defensorianna.gob.ar/?d=332801414</t>
+          <t>https://www.indianpharmapost.com/healthcare/dr-reddys-launches-nationwide-programme-to-train-5000-certified-obesity-educators-21836</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>13-09-2026 08:41 UTC</t>
+          <t>14-09-2026 11:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USFDA Issues Two Observations After Records Assessment of Dr. Reddy's Mexico API Facility</t>
+          <t>Dr Reddy's halts semaglutide supplies on impurity issue</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/usfda-issues-two-observations-after-records-assessment-of-dr-reddys-mexico-api-facility-179163</t>
+          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-laboratories-delays-semaglutide-supplies-due-to-api-issue/45115417</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13-09-2026 12:30 UTC</t>
+          <t>13-09-2026 19:05 UTC</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Mexico API Facility Gets Two Observations From USFDA</t>
+          <t>Income Tax Notice Issued to Non-Existent Entity After Merger Unsustainable: Telangana HC [Read Order]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Daily Pioneer</t>
+          <t>Taxscan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://dailypioneer.com/news/slug-lite/usfda-conducts-assessment-of-dr-reddys-mexico-facility?year=2026</t>
+          <t>https://www.taxscan.in/top-stories/income-tax-notice-issued-to-non-existent-entity-after-merger-unsustainable-telangana-hc-1451423</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13-09-2026 08:55 UTC</t>
+          <t>14-09-2026 06:17 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dry skin? 8 skincare products recommended by cosmetologists | Fashion Trends</t>
+          <t>OT security cannot follow an IT playbook when cyber risk can stop production and endanger safety</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hindustan Times</t>
+          <t>ET CISO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/lifestyle/fashion/dry-skin-8-skincare-products-recommended-by-cosmetologists-101789019112080-amp.html</t>
+          <t>https://ciso.economictimes.indiatimes.com/news/ot-security/ot-security-cannot-follow-an-it-playbook-when-cyber-risk-can-stop-production-and-endanger-safety/134235383</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>14-09-2026 04:30 UTC</t>
+          <t>14-09-2026 09:33 UTC</t>
         </is>
       </c>
     </row>
@@ -1867,76 +1867,76 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Morgan Stanley drops blunt verdict on Ozempic maker</t>
+          <t>Dr. Reddy’s Reports FDA Records Assessment at Mexican API Plant Concluding with Two Observations</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/morgan-stanley-drops-blunt-verdict-014700805.html</t>
+          <t>https://www.tipranks.com/news/company-announcements/dr-reddys-reports-fda-records-assessment-at-mexican-api-plant-concluding-with-two-observations</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>14-09-2026 01:47 UTC</t>
+          <t>14-09-2026 11:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Strides Pharma Gets Three USFDA Observations Following Alathur Facility Inspection</t>
+          <t>AI is changing cyberattacks from automated to adaptive; SOCs must respond at the same speed</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>ET CISO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/strides-pharma-gets-three-usfda-observations-following-alathur-facility-inspection-179165</t>
+          <t>https://ciso.economictimes.indiatimes.com/news/corporate/ai-is-changing-cyberattacks-from-automated-to-adaptive-socs-must-respond-at-the-same-speed/134235124</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>13-09-2026 13:45 UTC</t>
+          <t>14-09-2026 09:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sun Pharma Gets CDSCO Panel Recommendation for Phase IV Sovateltide Trial</t>
+          <t>C-CAMP National Bio Entrepreneurship competition 2026 recognises 15 startups and four student teams</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/sun-pharma-gets-cdsco-panel-recommendation-for-phase-iv-sovateltide-trial-179164</t>
+          <t>https://www.indianpharmapost.com/news/c-camp-national-bio-entrepreneurship-competition-2026-recognises-15-startups-and-four-student-teams-21825</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>13-09-2026 14:30 UTC</t>
+          <t>14-09-2026 03:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1948,22 +1948,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>C-CAMP National Bio Entrepreneurship competition 2026 recognises 15 startups and four student teams</t>
+          <t>275 register for free health camp in Phesama</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>indianpharmapost.com</t>
+          <t>Eastern Mirror</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/startup/c-camp-national-bio-entrepreneurship-competition-2026-recognises-15-startups-and-four-student-teams-21825</t>
+          <t>https://www.easternmirrornagaland.com/275-register-for-free-health-camp-in-phesama</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14-09-2026 02:44 UTC</t>
+          <t>14-09-2026 16:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1975,76 +1975,76 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SKUAST-K scholar wins national bio-entrepreneurship award</t>
+          <t>275 register for free cancer screening, health camp at Phesama</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>thekashmirimages.com</t>
+          <t>MorungExpress</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://thekashmirimages.com/2026/09/14/skuast-k-scholar-wins-national-bio-entrepreneurship-award/</t>
+          <t>https://morungexpress.com/275-register-for-free-cancer-screening-health-camp-at-phesama</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>13-09-2026 18:41 UTC</t>
+          <t>14-09-2026 15:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma’s API facility clears FDA inspection</t>
+          <t>Russian forces strike BaDM warehouse in fourth attack on pharma distributor in two weeks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>The New Voice of Ukraine</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/aurobindo-pharmas-api-facility-clears-fda-inspection/134230645</t>
+          <t>https://english.nv.ua/business/russian-attack-hits-badm-warehouse-marking-fourth-hit-on-top-pharma-company-in-two-weeks-50641173.html</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14-09-2026 02:00 UTC</t>
+          <t>14-09-2026 09:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma's Apitoria clears US FDA inspection with zero observations</t>
+          <t>SKUAST-K scholar wins national bio-entrepreneurship award</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>indianpharmapost.com</t>
+          <t>thekashmirimages.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/aurobindo-pharmas-apitoria-clears-us-fda-inspection-with-zero-observations-21829</t>
+          <t>https://thekashmirimages.com/2026/09/14/skuast-k-scholar-wins-national-bio-entrepreneurship-award/</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>14-09-2026 04:19 UTC</t>
+          <t>13-09-2026 18:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2056,103 +2056,103 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gland Pharma to acquire 100% stake in US subsidiary for US$ 501,208</t>
+          <t>Aurobindo Pharma’s API facility clears FDA inspection</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>indianpharmapost.com</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/lite/gland-pharma-to-acquire-100-stake-in-us-subsidiary-for-us-501208-21827</t>
+          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/aurobindo-pharmas-api-facility-clears-fda-inspection/134230645</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>13-09-2026 13:00 UTC</t>
+          <t>14-09-2026 02:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Marking Eight Generations of Foldable Innovation: The Incredible Evolution of Samsung’s Galaxy Z Series</t>
+          <t>Aurobindo Pharma's Apitoria clears US FDA inspection with zero observations</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/ph/marking-eight-generations-of-foldable-innovation-the-incredible-evolution-of-samsungs-galaxy-z-series</t>
+          <t>https://www.indianpharmapost.com/news/aurobindo-pharmas-apitoria-clears-us-fda-inspection-with-zero-observations-21829</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14-09-2026 04:07 UTC</t>
+          <t>14-09-2026 04:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Making sovereign, open-weight AI the technology frontier</t>
+          <t>The CDMO Revolution: How Contract Drug Manufacturers Are Reshaping Global Pharma- Expert View by Spherical Insights</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>mistral.ai</t>
+          <t>Spherical Insights</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://mistral.ai/news/mistral-makes-sovereign-open-weight-ai-to-frontier/</t>
+          <t>https://www.sphericalinsights.com/blogs/the-cdmo-revolution-how-contract-drug-manufacturers-are-reshaping-global-pharma</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14-09-2026 05:20 UTC</t>
+          <t>13-09-2026 17:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Samsung launches Galaxy S26 FE in India, says it brings flagship features to more people</t>
+          <t>Zydus Spine Surgeons Push the Boundaries of Complex Spine Care, Delivering Excellent Outcomes Across All Ages</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/amp/technology/news/story/samsung-launches-galaxy-s26-fe-in-india-says-it-brings-flagship-features-to-more-people-2994173-2026-09-14</t>
+          <t>https://finance.yahoo.com/healthcare/articles/zydus-spine-surgeons-push-boundaries-043000290.html</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>14-09-2026 08:22 UTC</t>
+          <t>14-09-2026 04:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2164,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 FE Launched in India With Exynos 2500 Chip, 4,900mAh Battery: Price, Specifications</t>
+          <t>Samsung Launches Galaxy S26 FE in India, Bringing Flagship Camera, Galaxy AI and Powerful Performance</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s26-fe-price-in-india-launch-sale-date-features-specifications-12044001</t>
+          <t>https://news.samsung.com/in/samsung-launches-galaxy-s26-fe-in-india-bringing-flagship-camera-galaxy-ai-and-powerful-performance</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>14-09-2026 08:08 UTC</t>
+          <t>14-09-2026 11:16 UTC</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Samsung And ASML Expand High-NA EUV Partnership</t>
+          <t>Samsung Galaxy S27 Pro and S27 Ultra to feature next-generation M16 OLED panel - GSMArena.com news</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>electronicsforyou.biz</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.electronicsforyou.biz/industry-buzz/samsung-and-asml-expand-high-na-euv-partnership/</t>
+          <t>https://www.gsmarena.com/samsung_galaxy_s27_pro_and_s27_ultra_to_feature_nextgeneration_m16_oled_panel-news-74603.php</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14-09-2026 08:04 UTC</t>
+          <t>14-09-2026 15:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2218,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Samsung unveils a 10,000-nit OLED screen, the brightest yet for smartphones</t>
+          <t>Samsung Galaxy S27 Ultra Said to Retain 5x Telephoto Camera; May Ditch Dedicated 3x Camera</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/samsung-display-unveils-10000-nits-oled-screen-brightest-smartphones/</t>
+          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s27-ultra-5x-telephoto-camera-rear-features-specifications-leak-12045072</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>14-09-2026 05:47 UTC</t>
+          <t>14-09-2026 12:10 UTC</t>
         </is>
       </c>
     </row>
@@ -2245,22 +2245,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Samsung's Galaxy S27 could get a display upgrade the Pixel 11 apparently missed</t>
+          <t>Making sovereign, open-weight AI the technology frontier</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Android Authority</t>
+          <t>mistral.ai</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.androidauthority.com/samsung-galaxy-s27-m16-oled-display-3710724/</t>
+          <t>https://mistral.ai/news/mistral-makes-sovereign-open-weight-ai-to-frontier/</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14-09-2026 04:23 UTC</t>
+          <t>14-09-2026 15:02 UTC</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>iQOO 16 confirmed to feature a 2K 165Hz display with Samsung M16 OLED material</t>
+          <t>Samsung unveils a 10,000-nit OLED screen, the brightest yet for smartphones</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>91mobiles.com</t>
+          <t>sammobile.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.91mobiles.com/hub/iqoo-16-samsung-m16-oled-display-confirmed/amp/</t>
+          <t>https://www.sammobile.com/news/samsung-display-unveils-10000-nits-oled-screen-brightest-smartphones/</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14-09-2026 05:53 UTC</t>
+          <t>14-09-2026 05:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Samsung, SK Hynix reject KEPCO’s $17 billion power-bill prepayment plan</t>
+          <t>Galaxy S26 FE Is Now Official In India, Price Confirmed</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KED Global</t>
+          <t>SammyGuru</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kedglobal.com/korean-chipmakers/newsView/ked202609140001</t>
+          <t>https://sammyguru.com/galaxy-s26-fe-launches-in-india-price-confirmed/</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>14-09-2026 07:11 UTC</t>
+          <t>14-09-2026 16:42 UTC</t>
         </is>
       </c>
     </row>
@@ -2326,22 +2326,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Galaxy S27 Ultra Camera Leaks: Samsung to Keep 5x Zoom, Drop 3x Lens?</t>
+          <t>Samsung Galaxy S26 FE launched in India: Price in India, specifications and all you need to know</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nokiamob</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://nokiamob.net/2026/09/14/samsung-galaxy-s27-ultra-rumors-the-truth-about-the-50mp-4x-sensor/</t>
+          <t>https://timesofindia.indiatimes.com/technology/tech-news/samsung-galaxy-s26-fe-launched-in-india-price-in-india-specifications-and-all-you-need-to-know/articleshow/134244501.cms</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14-09-2026 07:11 UTC</t>
+          <t>14-09-2026 16:25 UTC</t>
         </is>
       </c>
     </row>
@@ -2353,22 +2353,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Train Run Recover: Why Galaxy Wellness Goes Beyond Working Out</t>
+          <t>I tried Samsung's Auto Blocker; it does way more than I expected</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Android Police</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/ph/train-run-recover-why-galaxy-wellness-goes-beyond-working-out</t>
+          <t>https://www.androidpolice.com/samsungs-auto-blocker-does-way-more-than-i-expected/</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14-09-2026 04:07 UTC</t>
+          <t>14-09-2026 12:15 UTC</t>
         </is>
       </c>
     </row>
@@ -2380,22 +2380,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 FE Price in India, Storage Variants Leaked Ahead of Launch</t>
+          <t>Samsung launches Galaxy S26 FE for the premium segment buyers in India</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s26-fe-price-in-india-storage-variants-leak-launch-date-12043187</t>
+          <t>https://www.thehindu.com/sci-tech/technology/gadgets/samsung-launches-galaxy-s26-fe-for-the-premium-segment-buyers-in-india/article71465729.ece</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>14-09-2026 04:11 UTC</t>
+          <t>14-09-2026 08:46 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,827 +2407,827 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Samsung digs deep into its pockets as US companies poach top chip talent</t>
+          <t>Samsung Galaxy S26 FE With Exynos 2500 Chipset, IP68 Rating Launched In India At Rs 79,999</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>ETV Bharat</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/samsung-digs-deep-into-its-pockets-as-us-companies-poach-top-chip-talent/</t>
+          <t>https://www.etvbharat.com/en/technology/samsung-galaxy-s26-fe-launched-in-india-price-specifications-availability-enn26091404544</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>14-09-2026 07:09 UTC</t>
+          <t>14-09-2026 12:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Samsung Heavy Wins $1B Order for Four LNG Carriers</t>
+          <t>Samsung Galaxy S26 Plus is available at a lower price: Details here</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/14/samsung-heavy-wins-1b-order-for-four-lng-carriers</t>
+          <t>https://www.indiatoday.in/visualstories/technology/samsung-galaxy-s26-plus-is-available-at-a-lower-price-details-here-285702-14-09-2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>14-09-2026 06:39 UTC</t>
+          <t>14-09-2026 13:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tokyo court dismisses Malaysia’s IHH unit’s claims against Daiichi Sankyo</t>
+          <t>Samsung and Verizon Complete Successful ISAC Trial Over Virtualized Network at Global Sports Event</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Medical Buyer</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/tokyo-court-dismisses-malaysias-ihh-units-claims-against-daiichi-sankyo/</t>
+          <t>https://news.samsung.com/global/samsung-and-verizon-complete-successful-isac-trial-over-virtualized-network-at-global-sports-event</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>14-09-2026 08:17 UTC</t>
+          <t>14-09-2026 13:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Increased deaths shadow AstraZeneca, Daiichi’s Enhertu first-line lung cancer data</t>
+          <t>Compare Samsung Galaxy A08</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/higher-death-risk-shadows-astrazeneca-daiichi-enhertu-first-line-lung-cancer-data</t>
+          <t>https://www.gsmarena.com/compare.php3?idPhone1=14938</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>13-09-2026 23:00 UTC</t>
+          <t>14-09-2026 12:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tokyo Court rejects IHH unit's claims against Daiichi Sankyo</t>
+          <t>Samsung may launch the Galaxy Tab S12+ and Ultra on October 7</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>sbr.com.sg</t>
+          <t>sammobile.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://sbr.com.sg/healthcare/news/tokyo-court-rejects-ihh-units-claims-against-daiichi-sankyo</t>
+          <t>https://www.sammobile.com/news/samsung-may-launch-the-galaxy-tab-s12-and-ultra-on-october-7/</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>14-09-2026 02:37 UTC</t>
+          <t>14-09-2026 08:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Enhertu® Demonstrated a Median Progression-Free Survival of 14.3</t>
+          <t>Marking Eight Generations of Foldable Innovation: The Incredible Evolution of Samsung’s Galaxy Z Series</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>natlawreview.com</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://natlawreview.com/press-releases/enhertur-demonstrated-median-progression-free-survival-143-months-first-line</t>
+          <t>https://news.samsung.com/sg/marking-eight-generations-of-foldable-innovation-the-incredible-evolution-of-samsungs-galaxy-z-series</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>14-09-2026 03:37 UTC</t>
+          <t>14-09-2026 12:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi report Enhertu benefit in advanced lung cancer</t>
+          <t>Samsung Heavy Wins $1B Order for Four LNG Carriers</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>London South East</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.lse.co.uk/news/astrazeneca-daiichi-report-enhertu-benefit-in-advanced-lung-cancer-o6o75ns4dmqn0hr.html</t>
+          <t>https://en.sedaily.com/finance/2026/09/14/samsung-heavy-wins-1b-order-for-four-lng-carriers</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>14-09-2026 02:47 UTC</t>
+          <t>14-09-2026 06:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ENHERTU® (fam-trastuzumab deruxtecan-nxki) demonstrated a median progression-free survival of 14.3 months as 1st-line therapy in patients with HER2-mutant advanced non-small cell lung cancer in DESTINY-Lung04 Phase III trial</t>
+          <t>Prestige BioPharma Calls Shareholder Meeting to Refresh Board and Expand Capital-Raising Powers</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FinancialContent</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.financialcontent.com/article/bizwire-2026-9-14-enhertu-fam-trastuzumab-deruxtecan-nxki-demonstrated-a-median-progression-free-survival-of-143-months-as-1st-line-therapy-in-patients-with-her2-mutant-advanced-non-small-cell-lung-cancer-in-destiny-lung04-phase-iii-trial</t>
+          <t>https://www.tipranks.com/news/company-announcements/prestige-biopharma-calls-shareholder-meeting-to-refresh-board-and-expand-capital-raising-powers</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>14-09-2026 01:55 UTC</t>
+          <t>14-09-2026 09:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+          <t>Tokyo court dismisses Malaysia’s IHH unit’s claims against Daiichi Sankyo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>Medical Buyer</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+          <t>https://medicalbuyer.co.in/tokyo-court-dismisses-malaysias-ihh-units-claims-against-daiichi-sankyo/</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>13-09-2026 21:54 UTC</t>
+          <t>14-09-2026 08:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MEDIPAL HOLDINGS CORPORATION and JCR Pharmaceuticals Dose First Patient in Global Phase I/II Trial of JR-446 for Mucopolysaccharidosis Type IIIB</t>
+          <t>Increased deaths shadow AstraZeneca, Daiichi’s Enhertu first-line lung cancer data</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/medipal-holdings-corporation-and-jcr-pharmaceuticals-dose-first-patient-in-global-phase-i-ii-trial-of-jr-446-for-mucopolysaccharidosis-type-iiib</t>
+          <t>https://www.fiercepharma.com/pharma/higher-death-risk-shadows-astrazeneca-daiichi-enhertu-first-line-lung-cancer-data</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>14-09-2026 02:46 UTC</t>
+          <t>13-09-2026 23:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MEDIPAL, JCR Dose First Patient in Global Phase I/II Trial of JR-446 for Sanfilippo Syndrome</t>
+          <t>Tokyo Court rejects IHH unit's claims against Daiichi Sankyo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>Singapore Business Review</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/86/8425/medipal-jcr-dose-first-patient-in-global-phase-i-ii-trial-of-jr-446-for-sanfilippo-syndrome.html</t>
+          <t>https://sbr.com.sg/healthcare/news/tokyo-court-rejects-ihh-units-claims-against-daiichi-sankyo</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>13-09-2026 18:36 UTC</t>
+          <t>14-09-2026 02:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EMPLOYMENT (14-09-2026)</t>
+          <t>ENHERTU® (fam-trastuzumab deruxtecan-nxki) demonstrated a median progression-free survival of 14.3 months as 1st-line therapy in patients with HER2-mutant advanced non-small cell lung cancer in DESTINY-Lung04 Phase III trial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>dailyexcelsior.com</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/employment-14-09-2026/amp</t>
+          <t>https://www.biospace.com/press-releases/enhertu-fam-trastuzumab-deruxtecan-nxki-demonstrated-a-median-progression-free-survival-of-14-3-months-as-1st-line-therapy-in-patients-with-her2-mutant-advanced-non-small-cell-lung-cancer-in-destiny-lung04-phase-iii-trial</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>14-09-2026 05:19 UTC</t>
+          <t>14-09-2026 04:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Irish pharmacists warn against replacing prescription medicines with social media health trends</t>
+          <t>Enhertu® Demonstrated a Median Progression-Free Survival of 14.3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Galway Advertiser</t>
+          <t>natlawreview.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>http://www.advertiser.ie/galway/article/151819/irish-pharmacists-warn-against-replacing-prescription-medicines-with-social-media-health-trends</t>
+          <t>https://natlawreview.com/press-releases/enhertur-demonstrated-median-progression-free-survival-143-months-first-line</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>13-09-2026 10:33 UTC</t>
+          <t>14-09-2026 03:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Certain Ordinary Shares of Alvotech are subject to a Lock-Up Agreement Ending on 14-SEP-2026.</t>
+          <t>AstraZeneca, Daiichi report Enhertu benefit in advanced lung cancer</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>London South East</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/certain-ordinary-shares-of-alvotech-are-subject-to-a-lock-up-agreement-ending-on-14-sep-2026-ce785bdcd889f520</t>
+          <t>https://www.lse.co.uk/news/astrazeneca-daiichi-report-enhertu-benefit-in-advanced-lung-cancer-o6o75ns4dmqn0hr.html</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>14-09-2026 00:37 UTC</t>
+          <t>14-09-2026 02:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>eQ Plc Members of the Shareholders’ Nomination Committee</t>
+          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>Stocktwits</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/avacta-appoints-mats-blom-board-060000062.html</t>
+          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>14-09-2026 06:26 UTC</t>
+          <t>13-09-2026 21:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Results for Teva Bouchgua at REMA Saquarema Surf Festival 2026</t>
+          <t>MEDIPAL, JCR Dose First Patient in Global Phase I/II Trial of JR-446 for Sanfilippo Syndrome</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>World Surf League</t>
+          <t>BioPharma APAC</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.worldsurfleague.com/athletes/9259/teva-bouchgua/eventresults?eventId=5182</t>
+          <t>https://biopharmaapac.com/news/86/8425/medipal-jcr-dose-first-patient-in-global-phase-i-ii-trial-of-jr-446-for-sanfilippo-syndrome.html</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>13-09-2026 20:31 UTC</t>
+          <t>13-09-2026 18:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Teva Women's Teva Ember Moc Sizing Teva Ember Moc Teva Slip On Shoes Teva Ember Moc Slip On Blue</t>
+          <t>Perfect Pitch: Inside the scheme that gets junior lawyers selling to clients</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>fuelcarmagazine</t>
+          <t>lifesciencesipreview.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://fuelcarmagazine.com/?x=4032494051270</t>
+          <t>https://www.lifesciencesipreview.com/regulation-and-industry/perfect-pitch-inside-the-scheme-that-gets-junior-lawyers-selling-to-clients</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>13-09-2026 19:42 UTC</t>
+          <t>14-09-2026 15:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>How to Trade This $2 Billion Biotech Name Moving Quickly Toward Profit</t>
+          <t>AbelZeta Receives FDA IND Clearance for Phase 1b/2 Clinical Trial of C-CAR168 in Progressive Multiple Sclerosis</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>pro.thestreet.com</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://pro.thestreet.com/trade-ideas/how-to-trade-this-2-billion-biotech-name-moving-quickly-toward-profit</t>
+          <t>https://www.prnewswire.com/news-releases/abelzeta-receives-fda-ind-clearance-for-phase-1b2-clinical-trial-of-c-car168-in-progressive-multiple-sclerosis-302877555.html</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>13-09-2026 15:00 UTC</t>
+          <t>14-09-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+          <t>EMPLOYMENT (14-09-2026)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>Daily Excelsior</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+          <t>https://www.dailyexcelsior.com/employment-14-09-2026/amp</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>13-09-2026 21:54 UTC</t>
+          <t>14-09-2026 05:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Samsung, LG to Pay Suppliers ₩1.9 Trillion (approximately $1.4 Billion) Early Ahead of Chuseok</t>
+          <t>Total Energy Services Inc. Announces Changes to Board of Directors</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/8b2649e0-23cf-481b-b34d-61f9cf822d8a</t>
+          <t>https://www.manilatimes.net/2026/09/14/tmt-newswire/globenewswire/total-energy-services-inc-announces-changes-to-board-of-directors/2424520/amp</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14-09-2026 06:05 UTC</t>
+          <t>14-09-2026 12:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>“Samsung Group to release KRW 1.3 trillion before Chuseok,” paying suppliers seven days early</t>
+          <t>Certain Ordinary Shares of Alvotech are subject to a Lock-Up Agreement Ending on 14-SEP-2026.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/en/business/12151952</t>
+          <t>https://www.marketscreener.com/news/certain-ordinary-shares-of-alvotech-are-subject-to-a-lock-up-agreement-ending-on-14-sep-2026-ce785bdcd889f520</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>14-09-2026 00:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Samsung advances 1.3 trillion-won supplier payments to boost Korea’s economy - CHOSUNBIZ</t>
+          <t>eQ Plc Members of the Shareholders’ Nomination Committee</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-it/2026/09/14/233PHRZEDBEHTOHAB26HDNIAA4/</t>
+          <t>https://uk.finance.yahoo.com/news/avacta-appoints-mats-blom-board-060000062.html</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>14-09-2026 06:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Samsung and LG Advance 1.9 Trillion Won in Payments Ahead of Chuseok, All-Out Effort for Mutual Growth and Domestic Demand</t>
+          <t>Teva Pharmaceuticals Sees Pivot to Growth Accelerating on Branded Drugs, Biosimilars</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/enterprise-CEO/2026091410510214218</t>
+          <t>https://finance.yahoo.com/healthcare/articles/teva-pharmaceuticals-sees-pivot-growth-140227795.html</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>14-09-2026 14:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Samsung Biologics signs $262M manufacturing deal through 2033, pushing longer CDMO bookings</t>
+          <t>Results for Teva Bouchgua at REMA Saquarema Surf Festival 2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MarketScale</t>
+          <t>World Surf League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.marketscale.com/industries/sciences/samsung-biologics-signs-262m-manufacturing-deal-through-2033-pushing-longer-cdmo-bookings</t>
+          <t>https://www.worldsurfleague.com/athletes/9259/teva-bouchgua/eventresults?eventId=5182</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>13-09-2026 11:54 UTC</t>
+          <t>13-09-2026 20:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>“Samsung Group to release KRW 1.3 trillion before Chuseok,” paying suppliers seven days early</t>
+          <t>Teva Women's Teva Ember Moc Sizing Teva Ember Moc Teva Slip On Shoes Teva Ember Moc Slip On Blue</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>fuelcarmagazine</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/en/business/12151952</t>
+          <t>https://fuelcarmagazine.com/?x=4032494051270</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>13-09-2026 19:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Songdo Opens Bio Training Center to Ease Talent Shortage</t>
+          <t>Lupin targets $500 million biosimilar revenue in five years</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/society/2026/09/14/songdo-opens-bio-training-center-to-ease-talent-shortage</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/lupin-targets-500-million-biosimilar-revenue-in-five-years</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>14-09-2026 00:29 UTC</t>
+          <t>14-09-2026 15:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The CDMO Revolution: How Contract Drug Manufacturers Are Reshaping Global Pharma- Expert View by Spherical Insights</t>
+          <t>Samsung, LG to Pay Suppliers ₩1.9 Trillion (approximately $1.4 Billion) Early Ahead of Chuseok</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>sphericalinsights.com</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.sphericalinsights.com/blogs/the-cdmo-revolution-how-contract-drug-manufacturers-are-reshaping-global-pharma</t>
+          <t>https://finance.biggo.com/news/8b2649e0-23cf-481b-b34d-61f9cf822d8a</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>13-09-2026 17:51 UTC</t>
+          <t>14-09-2026 06:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Samsung advances 1.3 trillion-won supplier payments to boost Korea’s economy - CHOSUNBIZ</t>
+          <t>Samsung, Hyundai, LG Advance Payments to Suppliers Ahead of Chuseok</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-it/2026/09/14/233PHRZEDBEHTOHAB26HDNIAA4/</t>
+          <t>https://www.chosun.com/english/industry-en/2026/09/14/GWXBHH6C7VAIHLLINZIJCGKADU/</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>14-09-2026 09:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Samsung and LG Advance 1.9 Trillion Won in Payments Ahead of Chuseok, All-Out Effort for Mutual Growth and Domestic Demand</t>
+          <t>KRTL Biotech Appoints Federal Controlled-Substance Compliance Specialist Justin Abril as President-Designate</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/enterprise-CEO/2026091410510214218</t>
+          <t>https://sg.finance.yahoo.com/news/krtl-biotech-appoints-federal-controlled-130000493.html</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>14-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Samsung, LG to Pay Suppliers ₩1.9 Trillion (approximately $1.4 Billion) Early Ahead of Chuseok</t>
+          <t>“Samsung Group to release KRW 1.3 trillion before Chuseok,” paying suppliers seven days early</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/8b2649e0-23cf-481b-b34d-61f9cf822d8a</t>
+          <t>https://www.mk.co.kr/en/business/12151952</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>14-09-2026 06:05 UTC</t>
+          <t>14-09-2026 05:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Samsung to pay 1.3 trillion won early to suppliers</t>
+          <t>Samsung and LG Advance 1.9 Trillion Won in Payments Ahead of Chuseok, All-Out Effort for Mutual Growth and Domestic Demand</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>디지털투데이</t>
+          <t>asiae.co.kr</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.digitaltoday.co.kr/en/view/103165/samsung-to-pay-1-3-trillion-won-early-to-suppliers</t>
+          <t>https://www.asiae.co.kr/en/article/enterprise-CEO/2026091410510214218</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3239,54 +3239,378 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>U.S., Japan Rate Decisions Converge in Super Week</t>
+          <t>SleepRes Receives Frost &amp; Sullivan's 2026 North America New Product Innovation Recognition for Excellence in Positive Airway Pressure Device Innovation</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/14/us-japan-rate-decisions-converge-in-super-week</t>
+          <t>https://sg.finance.yahoo.com/news/sleepres-receives-frost-sullivans-2026-130000178.html</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>14-09-2026 01:51 UTC</t>
+          <t>14-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Samsung advances 1.3 trillion-won supplier payments to boost Korea’s economy - CHOSUNBIZ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://biz.chosun.com/en/en-it/2026/09/14/233PHRZEDBEHTOHAB26HDNIAA4/</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Perfect Pitch: Inside the scheme that gets junior lawyers selling to clients</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>lifesciencesipreview.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.lifesciencesipreview.com/regulation-and-industry/perfect-pitch-inside-the-scheme-that-gets-junior-lawyers-selling-to-clients</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>14-09-2026 15:11 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Samsung Biologics (KRX: 207940) Secures $262M Manufacturing Deal With European Pharma As Peptide Push Advances</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>londoninsider.co.uk</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>https://londoninsider.co.uk/samsung-biologics-krx-207940-secures-262m-manufacturing-deal-with-european-pharma-as-peptide-push-advances/</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>13-09-2026 10:49 UTC</t>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>The CDMO Revolution: How Contract Drug Manufacturers Are Reshaping Global Pharma- Expert View by Spherical Insights</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Spherical Insights</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.sphericalinsights.com/blogs/the-cdmo-revolution-how-contract-drug-manufacturers-are-reshaping-global-pharma</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>13-09-2026 17:51 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Samsung, Hyundai, LG Advance Payments to Suppliers Ahead of Chuseok</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.chosun.com/english/industry-en/2026/09/14/GWXBHH6C7VAIHLLINZIJCGKADU/</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>14-09-2026 09:32 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Songdo Opens Bio Training Center to Ease Talent Shortage</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Seoul Economic Daily</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://en.sedaily.com/society/2026/09/14/songdo-opens-bio-training-center-to-ease-talent-shortage</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>14-09-2026 00:29 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Samsung advances 1.3 trillion-won supplier payments to boost Korea’s economy - CHOSUNBIZ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://biz.chosun.com/en/en-it/2026/09/14/233PHRZEDBEHTOHAB26HDNIAA4/</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>“Samsung Group to release KRW 1.3 trillion before Chuseok,” paying suppliers seven days early</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>매일경제</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/en/business/12151952</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Samsung, LG to pay suppliers 1.9 trillion won early ahead of Chuseok</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Aju Press</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://m.ajupress.com/amp/20260914171524025</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>14-09-2026 08:25 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Samsung and LG Advance 1.9 Trillion Won in Payments Ahead of Chuseok, All-Out Effort for Mutual Growth and Domestic Demand</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>asiae.co.kr</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.asiae.co.kr/en/article/enterprise-CEO/2026091410510214218</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Samsung, LG to Pay Suppliers ₩1.9 Trillion (approximately $1.4 Billion) Early Ahead of Chuseok</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>finance.biggo.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://finance.biggo.com/news/8b2649e0-23cf-481b-b34d-61f9cf822d8a</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>14-09-2026 06:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Samsung to pay 1.3 trillion won early to suppliers</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>디지털투데이</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.digitaltoday.co.kr/en/view/103165/samsung-to-pay-1-3-trillion-won-early-to-suppliers</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>U.S., Japan Rate Decisions Converge in Super Week</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Seoul Economic Daily</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://en.sedaily.com/finance/2026/09/14/us-japan-rate-decisions-converge-in-super-week</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>14-09-2026 01:51 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Samsung, LG to Pay Suppliers Early Ahead of Chuseok</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Seoul Economic Daily</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://en.sedaily.com/finance/2026/09/14/samsung-lg-to-pay-suppliers-19-trillion-won-early-before</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>14-09-2026 05:00 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>boerse.de</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.boerse.de/nachrichten-amp/Sandoz-issues-EUR-500-million-bond/38598140</t>
+          <t>https://www.sandoz.com/sandoz-issues-eur-500-million-bond/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14-09-2026 15:40 UTC</t>
+          <t>14-09-2026 16:16 UTC</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lupin targets $500 million biosimilar revenue in five years</t>
+          <t>Sandoz Group Launches EUR500 Million Bond</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/lupin-targets-500-million-biosimilar-revenue-in-five-years</t>
+          <t>https://www.marketscreener.com/news/sandoz-group-launches-eur500-million-bond-ce785bddd98df626</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14-09-2026 15:22 UTC</t>
+          <t>15-09-2026 03:29 UTC</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Avecho Biotechnology (ASX:AVE): Phase III Insomnia Trial and Commercial Pathway in Focus</t>
+          <t>Lupin targets $500 million biosimilar revenue in five years</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kalkine</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://kalkine.com.au/news/healthcare/avecho-biotechnology-asxave-phase-iii-insomnia-trial-and-commercial-pathway-in-focus</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/lupin-targets-500-million-biosimilar-revenue-in-five-years</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14-09-2026 08:08 UTC</t>
+          <t>14-09-2026 15:29 UTC</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Meche Cancels Jury Selection</t>
+          <t>ONYX Hospitality Group Strengthens Sustainable Hotel Operations Through Strategic Partnership with SP Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Landry Now Online Newspaper</t>
+          <t>finanzen.ch</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.stlandrynow.com/community/local-news/meche-cancels-jury-selection/</t>
+          <t>https://www.finanzen.ch/nachrichten/aktien/onyx-hospitality-group-strengthens-sustainable-hotel-operations-through-strategic-partnership-with-sp-group-1036545062</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14-09-2026 16:11 UTC</t>
+          <t>15-09-2026 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -571,76 +571,76 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thailand moves from buying medicines to building them</t>
+          <t>Meche Cancels Jury Selection</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pattaya Mail</t>
+          <t>St. Landry Now Online Newspaper</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pattayamail.com/latestnews/news/thailand-moves-from-buying-medicines-to-building-them-564872</t>
+          <t>https://www.stlandrynow.com/community/local-news/meche-cancels-jury-selection/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13-09-2026 19:19 UTC</t>
+          <t>14-09-2026 16:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thailand seeks 100 billion baht in pharmaceutical research investment</t>
+          <t>When Words Stay Silent: How Sign Language Avatars Are Transforming Access to Medicine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pattaya Mail</t>
+          <t>CSRwire</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pattayamail.com/thailandnews/thailand-seeks-100-billion-baht-in-pharmaceutical-research-investment-564941</t>
+          <t>https://csrwire.com/press-release/when-words-stay-silent-how-sign-language-avatars-transforming-access-medicine/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13-09-2026 18:45 UTC</t>
+          <t>14-09-2026 14:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BUILDING HEALTHIER COMMUNITIES: VIETNAM’S HEALTHCARE OUTLOOK &amp; OPPORTUNITIES</t>
+          <t>Takeda R&amp;D President Andy Plump to Retire in 2027</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CarePlus VietNam</t>
+          <t>contractpharma.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.careplusvn.com/en/building-healthier-communities-vietnams-healthcare-outlook-opportunities</t>
+          <t>https://www.contractpharma.com/breaking-news/takeda-rd-president-andy-plump-to-retire-in-2027/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14-09-2026 12:00 UTC</t>
+          <t>14-09-2026 14:45 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When Words Stay Silent: How Sign Language Avatars Are Transforming Access to Medicine</t>
+          <t>When breathlessness isn’t just ageing: Campaign urges early action on pulmonary fibrosis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CSRwire</t>
+          <t>gulfnews.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://csrwire.com/press-release/when-words-stay-silent-how-sign-language-avatars-transforming-access-medicine/</t>
+          <t>https://gulfnews.com/uae/health/when-breathlessness-isnt-just-ageing-campaign-urges-early-action-on-pulmonary-fibrosis-1.500673910</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14-09-2026 14:02 UTC</t>
+          <t>15-09-2026 06:12 UTC</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Takeda R&amp;D President Andy Plump to Retire in 2027</t>
+          <t>DLG's animal nutrition unit beats expectations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Feed Strategy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/takeda-rd-president-andy-plump-to-retire-in-2027/</t>
+          <t>https://www.feedstrategy.com/business-markets/company-news/news/15834794/dlgs-animal-nutrition-unit-beats-expectations</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14-09-2026 14:45 UTC</t>
+          <t>14-09-2026 16:03 UTC</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DLG's animal nutrition unit beats expectations</t>
+          <t>Paper + Spark adds seven new clients as it’s named agency of the year at 2026 AMI Awards</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Feed Strategy</t>
+          <t>Campaign Brief</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.feedstrategy.com/business-markets/company-news/news/15834794/dlgs-animal-nutrition-unit-beats-expectations</t>
+          <t>https://campaignbrief.com/paper-spark-adds-seven-new-clients-as-its-named-agency-of-the-year-at-2026-ami-awards/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14-09-2026 16:04 UTC</t>
+          <t>15-09-2026 04:08 UTC</t>
         </is>
       </c>
     </row>
@@ -733,103 +733,103 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vyome Welcomes Jerry Leonard as New Chief Financial Officer</t>
+          <t>How changes in prefrontal brain activity can impair the ability to change behavior</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Medical Xpress</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/vyome-welcomes-jerry-leonard-as-new-chief-financial-officer/</t>
+          <t>https://medicalxpress.com/news/2026-09-prefrontal-brain-impair-ability-behavior.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14-09-2026 16:29 UTC</t>
+          <t>14-09-2026 18:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CAR-T therapies, bispecific antibodies, and antifibrotics in development open a new avenue against scleroderma</t>
+          <t>Hikma MP says crossings were closed to stop suspects fleeing to Iran</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Demócrata</t>
+          <t>964media</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.democrata.es/en/health/car-t-therapies-bispecific-antibodies-and-antifibrotics-in-development-open-a-new-avenue-against-scleroderma/amp/</t>
+          <t>https://en.964media.com/52521/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14-09-2026 14:44 UTC</t>
+          <t>14-09-2026 09:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hikma MP says crossings were closed to stop suspects fleeing to Iran</t>
+          <t>Shane Lowry Secures Record Home Victory at the 2026 Amgen Irish Open</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>964media</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://en.964media.com/52521/</t>
+          <t>https://www.amgen.com/stories/2026/09/shane-lowry-secures-record-home-victory-at-the-2026-amgen-irish-open</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14-09-2026 09:35 UTC</t>
+          <t>14-09-2026 21:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fatat takes bronze at Arab Women’s Basketball Championship</t>
+          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arab Times Kuwait News</t>
+          <t>Golf Channel</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.arabtimesonline.com/news/fatat-takes-bronze-at-arab-womens-basketball-championship/</t>
+          <t>https://www.golfchannel.com/watch/dp-world-tour/dp-world-tour-highlights-2026-amgen-irish-open-round-3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13-09-2026 17:14 UTC</t>
+          <t>14-09-2026 08:47 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 3</t>
+          <t>Amgen Leads The Pack With First Filing For US Opdivo Biosimilar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Golf Channel</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.golfchannel.com/watch/dp-world-tour/dp-world-tour-highlights-2026-amgen-irish-open-round-3</t>
+          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/amgen-leads-the-pack-with-first-filing-for-us-opdivo-biosimilar-PD6ZNDEA2VA4XKUQ44XCXQCZHI/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14-09-2026 08:47 UTC</t>
+          <t>14-09-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amgen Leads The Pack With First Filing For US Opdivo Biosimilar</t>
+          <t>Points and prize money: See what every player won at the Amgen Irish Open</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>europeantour.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/amgen-leads-the-pack-with-first-filing-for-us-opdivo-biosimilar-PD6ZNDEA2VA4XKUQ44XCXQCZHI/</t>
+          <t>https://www.europeantour.com/dpworld-tour/news/articles/detail/points-and-prize-money-see-what-every-player-won-at-the-2026-amgen-irish-open/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14-09-2026 10:30 UTC</t>
+          <t>14-09-2026 09:21 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Points and prize money: See what every player won at the Amgen Irish Open</t>
+          <t>Amgen vs. Vertex Pharmaceuticals: Value Stability vs. High-Growth Biotech Investment Plays</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DP World Tour</t>
+          <t>NAI500</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.europeantour.com/dpworld-tour/news/articles/detail/points-and-prize-money-see-what-every-player-won-at-the-2026-amgen-irish-open/</t>
+          <t>https://nai500.com/blog/2026/09/amgen-vs-vertex-pharmaceuticals-value-stability-vs-high-growth-biotech-investment-plays/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14-09-2026 09:21 UTC</t>
+          <t>15-09-2026 02:47 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amgen Irish Open 2026: Shane Lowry Chases $1.02 Million Winner’s Prize</t>
+          <t>Amgen Gets FDA Approval to Reduce Monitoring Time for First Two Imdelltra Doses</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NDTV Sports</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://sports.ndtv.com/us/golf/amgen-irish-open-2026-shane-lowry-chases-1-02-million-winner-s-prize-12042352</t>
+          <t>https://www.marketscreener.com/news/amgen-gets-fda-approval-to-reduce-monitoring-time-for-first-two-imdelltra-doses-ce785bdcdc81f62d</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13-09-2026 18:30 UTC</t>
+          <t>14-09-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -949,103 +949,103 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amgen Gets FDA Approval to Reduce Monitoring Time for First Two Imdelltra Doses</t>
+          <t>FDA shortens monitoring time for first IMDELLTR...</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/amgen-gets-fda-approval-to-reduce-monitoring-time-for-first-two-imdelltra-doses-ce785bdcdc81f62d</t>
+          <t>https://pluang.com/en/news-feed/fda-setujui-pengurangan-waktu-pemantauan-imdelltra</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14-09-2026 14:00 UTC</t>
+          <t>14-09-2026 13:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shane Lowry runs away with record 11-stroke victory at Amgen Irish Open, Rory McIlroy closes on positive note</t>
+          <t>Organon Announces US FDA Has Accepted for Review a Supplemental New Drug Application for MIUDELLA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pgatour.com</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pgatour.com/article/news/latest/2026/09/13/shane-lowry-runs-away-with-record-11-shot-victory-at-2026-amgen-irish-open-scores-leaderboard-results-rory-mcilroy-patrick-reed</t>
+          <t>https://www.businesswire.com/news/home/20260914839018/en/Organon-Announces-US-FDA-Has-Accepted-for-Review-a-Supplemental-New-Drug-Application-for-MIUDELLA-a-Hormone-Free-Intrauterine-Device</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14-09-2026 09:16 UTC</t>
+          <t>14-09-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amgen Irish Open | Day four highlights</t>
+          <t>FDA Accepts Extended Duration sNDA for Miudella Hormone-Free IUD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sky Sports</t>
+          <t>Patient Care Online</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/golf/video/30998/13585561/amgen-irish-open-day-four-highlights</t>
+          <t>https://www.patientcareonline.com/view/fda-accepts-extended-duration-snda-for-miudella-hormone-free-iud</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13-09-2026 18:20 UTC</t>
+          <t>14-09-2026 17:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FDA shortens monitoring time for first IMDELLTR...</t>
+          <t>Sun Pharma Subsidiaries Settle US Generic Drug Pricing Antitrust Litigation For Confidential Amount</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>Sahi</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/fda-setujui-pengurangan-waktu-pemantauan-imdelltra</t>
+          <t>https://www.sahi.com/news/sun-pharma-subsidiaries-settle-us-generic-drug-pricing-antitrust-litigation-for-confidential-amount</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14-09-2026 13:19 UTC</t>
+          <t>15-09-2026 00:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>contemporaryobgyn.net</t>
+          <t>Contemporary OB/GYN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1079,27 +1079,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>In the early 1800s, Giant Hogweed was introduced by British explorers for ornamental gardens, but it spre</t>
+          <t>Organon announces U.S. FDA accepted for review Sebela’s sNDA for Miudella</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/world/uk/in-the-early-1800s-giant-hogweed-was-introduced-by-british-explorers-for-ornamental-gardens-but-it-spread-beyond-control-and-is-now-a-feared-invasive-plant/articleshow/134127954.cms</t>
+          <t>https://www.tipranks.com/news/the-fly/organon-announces-u-s-fda-accepted-for-review-sebelas-snda-for-miudella-thefly-news</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14-09-2026 09:20 UTC</t>
+          <t>14-09-2026 14:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BeautifulChinaING: Walking through Changbai Mountain for 40 years, a Chinese botanist captures 520,000 plant images and China’s changing landscape</t>
+          <t>No need to buy lavender again: this cutting trick multiplies your plants</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Global Times</t>
+          <t>Futura, le média qui explore le monde</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.globaltimes.cn/page/202609/1370511.shtml</t>
+          <t>https://www.futura-sciences.com/en/no-need-to-buy-lavender-again-this-cutting-trick-multiplies-your-plants_39379/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14-09-2026 13:20 UTC</t>
+          <t>14-09-2026 12:28 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What Your Jade Plant Needs in September to Stay Bright and Healthy Through Fall</t>
+          <t>BeautifulChinaING: Walking through Changbai Mountain for 40 years, a Chinese botanist captures 520,000 plant images and China’s changing landscape</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Homes and Gardens</t>
+          <t>globaltimes.cn</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.homesandgardens.com/gardens/what-a-jade-plant-needs-in-september</t>
+          <t>https://www.globaltimes.cn/page/202609/1370511.shtml</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14-09-2026 16:00 UTC</t>
+          <t>14-09-2026 13:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Almonty and the Government of Rwanda Form Strategic Tungsten Partnership</t>
+          <t>Florist Special With Bri Lovie</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>thursd.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260914171760/en/Almonty-and-the-Government-of-Rwanda-Form-Strategic-Tungsten-Partnership</t>
+          <t>https://thursd.com/articles/florist-special-with-bri-lovie</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>14-09-2026 11:30 UTC</t>
+          <t>14-09-2026 18:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PPPL and UKAEA Experts Make a Plan to Connect Research on Two Fusion Supercomputers Across the Atlantic | Newswise</t>
+          <t>What Your Jade Plant Needs in September to Stay Bright and Healthy Through Fall</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Newswise</t>
+          <t>homesandgardens.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.newswise.com/articles/pppl-and-ukaea-experts-make-a-plan-to-connect-research-on-two-fusion-supercomputers-across-the-atlantic</t>
+          <t>https://www.homesandgardens.com/gardens/what-a-jade-plant-needs-in-september</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14-09-2026 14:40 UTC</t>
+          <t>14-09-2026 16:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Thematic Showcase: Material Form &amp; Tactile Surface</t>
+          <t>London ‘plant parents’ adopt a piece of historic Barbican urban jungle</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mutual Art</t>
+          <t>dawn.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.mutualart.com/Article/The-Thematic-Showcase--Material-Form---T/1ED2A4F0F98FE1F7</t>
+          <t>https://www.dawn.com/news/2030024</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14-09-2026 14:29 UTC</t>
+          <t>15-09-2026 02:33 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>How soybeans took over the American diet – without anyone noticing</t>
+          <t>Plant This Low-Maintenance Evergreen Now for a Beautiful Yard All Winter Long</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cobb Courier</t>
+          <t>House Beautiful</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://cobbcountycourier.com/2026/09/how-soybeans-took-over-the-american-diet-without-anyone-noticing/</t>
+          <t>https://www.housebeautiful.com/lifestyle/gardening/a73643733/arborvitae-care-winter-landscape/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14-09-2026 14:37 UTC</t>
+          <t>14-09-2026 19:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Florist Special With Bri Lovie</t>
+          <t>Almonty and the Government of Rwanda Form Strategic Tungsten Partnership</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thursd</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://thursd.com/articles/florist-special-with-bri-lovie</t>
+          <t>https://www.businesswire.com/news/home/20260914171760/en/Almonty-and-the-Government-of-Rwanda-Form-Strategic-Tungsten-Partnership</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14-09-2026 09:26 UTC</t>
+          <t>14-09-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Urban Jungle: Adopting Nature in London's Barbican Conservatory</t>
+          <t>Witness: There’s no space in SALN form for business acquisition costs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Devdiscourse</t>
+          <t>Inquirer.net</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3976751-urban-jungle-adopting-nature-in-londons-barbican-conservatory</t>
+          <t>https://newsinfo.inquirer.net/2305382/witness-theres-no-space-in-saln-form-for-business-acquisition-costs</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14-09-2026 06:00 UTC</t>
+          <t>15-09-2026 04:19 UTC</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rytas Vilgalys Explores a Hidden World Under Our Feet</t>
+          <t>The Thematic Showcase: Material Form &amp; Tactile Surface</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Duke Today</t>
+          <t>Mutual Art</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://today.duke.edu/2026/09/rytas-vilgalys-explores-hidden-world-under-our-feet</t>
+          <t>https://www.mutualart.com/Article/The-Thematic-Showcase--Material-Form---T/1ED2A4F0F98FE1F7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>14-09-2026 16:05 UTC</t>
+          <t>14-09-2026 14:33 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lonza deepens US bet with commercial plant in Oregon</t>
+          <t>How soybeans took over the American diet – without anyone noticing</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Cobb Courier</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/lonza-deepens-us-bet-with-commercial-spray-drying-plant-in-oregon</t>
+          <t>https://cobbcountycourier.com/2026/09/how-soybeans-took-over-the-american-diet-without-anyone-noticing/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14-09-2026 10:48 UTC</t>
+          <t>14-09-2026 14:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Harnessing sunlight to fight bacteria</t>
+          <t>Bill Ferree Obituary Sep 10, 2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sciworthy</t>
+          <t>Pugh Funeral Home</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://sciworthy.com/harnessing-sunlight-to-fight-bacteria/</t>
+          <t>https://www.pughfuneralhome.com/obituaries/bill-ferree</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14-09-2026 11:00 UTC</t>
+          <t>14-09-2026 17:43 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>London 'plant parents' adopt a piece of historic Barbican urban jungle</t>
+          <t>Hardy Mums for Minnesota Gardens: Color That Returns Every Fall</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Fillmore County Journal</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/lifestyle/london-plant-parents-adopt-piece-historic-barbican-urban-jungle-2026-09-14/</t>
+          <t>https://fillmorecountyjournal.com/hardy-mums-for-minnesota-gardens-color-that-returns-every-fall/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14-09-2026 06:07 UTC</t>
+          <t>14-09-2026 17:29 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pfizer Independent Medical Education Grant Program</t>
+          <t>Why the EU Biotech Act must deliver practical improvements for clinical trials in Europe</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>fundsforngos.org</t>
+          <t>The Parliament Magazine</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research-2/pfizer-independent-medical-education-grant-program/</t>
+          <t>https://www.theparliamentmagazine.eu/partner/article/why-the-eu-biotech-act-must-deliver-practical-improvements-for-clinical-trials-in-europe</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>14-09-2026 05:49 UTC</t>
+          <t>15-09-2026 06:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Can Pfizer Overcome Its COVID and Patent Cliff Headwinds?</t>
+          <t>Pfizer 52 Week Low Streak: Four-Day Breakdown Deepens</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>univest.in</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/pfizer-overcome-covid-patent-cliff-133700992.html</t>
+          <t>https://univest.in/blogs/why-pfizer-ltd-share-52-week-consecutive-low-2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14-09-2026 13:37 UTC</t>
+          <t>15-09-2026 04:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Transcript : Pfizer Inc. Presents at Morgan Stanley 24th Annual Global Healthcare Conference, Sep-14-2026 10</t>
+          <t>IP Group H1 NAV Rises 3.2% as Pfizer Obesity Royalty Asset Reaches £152 Million</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/transcript-pfizer-inc-presents-at-morgan-stanley-24th-annual-global-healthcare-conference-sep-14-ce785bdcdf81f720</t>
+          <t>https://uk.finance.yahoo.com/news/ip-group-h1-nav-rises-070831998.html</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>14-09-2026 15:50 UTC</t>
+          <t>15-09-2026 07:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cluster Headache Treatment Tips and Nuances</t>
+          <t>News | Lender doubles down on New York office conversions after Pfizer setback</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>costar.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.medscape.com/viewarticle/cluster-headache-treatment-tips-and-nuances-2026a1000v1k?src=</t>
+          <t>https://www.costar.com/article/1364458074/lender-doubles-down-on-new-york-office-conversions-after-pfizer-setback</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14-09-2026 13:05 UTC</t>
+          <t>14-09-2026 23:14 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pfizer Sets Novel Path in Fee Fight | The Wall Street Journal - newspaper</t>
+          <t>Transcript : Pfizer Inc. Presents at Morgan Stanley 24th Annual Global Healthcare Conference, Sep-14-2026 10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Magzter</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.magzter.com/stories/newspaper/The-Wall-Street-Journal/PFIZER-SETS-NOVEL-PATH-IN-FEE-FIGHT</t>
+          <t>https://www.marketscreener.com/news/transcript-pfizer-inc-presents-at-morgan-stanley-24th-annual-global-healthcare-conference-sep-14-ce785bdcdf81f720</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>14-09-2026 15:41 UTC</t>
+          <t>14-09-2026 15:50 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pfizer Quality Improvement Grant for System-Level Solutions</t>
+          <t>Pfizer loses patent case over Enbrel generic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>fundsforngos.org</t>
+          <t>Lawyerly</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research-2/pfizer-quality-improvement-grant-for-system-level-solutions/</t>
+          <t>https://www.lawyerly.com.au/pfizer-loses-patent-case-over-enbrel-generic/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14-09-2026 05:44 UTC</t>
+          <t>15-09-2026 07:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Association Between COVID-19 Vaccine Doses and Neurosensory Symptoms Among COVID-19-Positive Patients: A Retrospective Cross-Sectional Study</t>
+          <t>NCCN awards grants for metastatic prostate cancer quality initiatives</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cureus</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.cureus.com/articles/531853-association-between-covid-19-vaccine-doses-and-neurosensory-symptoms-among-covid-19-positive-patients-a-retrospective-cross-sectional-study?score_article=true</t>
+          <t>https://scanx.trade/stock-market-news/companies/nccn-awards-grants-metastatic-prostate-cancer-quality-initiatives/50936962</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>14-09-2026 16:24 UTC</t>
+          <t>14-09-2026 17:31 UTC</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pfizer Says Major Headwinds Are Easing as Pipeline, Obesity Plans Take Center Stage</t>
+          <t>Pfizer Sets Novel Path in Fee Fight | The Wall Street Journal - newspaper</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Magzter</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/pfizer-says-major-headwinds-easing-160235029.html</t>
+          <t>https://www.magzter.com/stories/newspaper/The-Wall-Street-Journal/PFIZER-SETS-NOVEL-PATH-IN-FEE-FIGHT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>14-09-2026 16:02 UTC</t>
+          <t>14-09-2026 15:41 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,49 +1651,49 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Viatris names Kim Sun-A head of Japan-Korea cluster</t>
+          <t>Association Between COVID-19 Vaccine Doses and Neurosensory Symptoms Among COVID-19-Positive Patients: A Retrospective Cross-Sectional Study</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Cureus</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33156</t>
+          <t>https://www.cureus.com/articles/531853-association-between-covid-19-vaccine-doses-and-neurosensory-symptoms-among-covid-19-positive-patients-a-retrospective-cross-sectional-study?score_article=true</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>14-09-2026 04:17 UTC</t>
+          <t>14-09-2026 16:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pfizer seizes air traffic fees to recover $2.2b from Poland, Romania - CHOSUNBIZ</t>
+          <t>Biogen Eyes Wave of Phase III Readouts as It Expands Beyond Neuroscience</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-international/2026/09/14/GB5CCJRCGRGZ3BAWLCUXEBW6JU/</t>
+          <t>https://finance.yahoo.com/healthcare/articles/biogen-eyes-wave-phase-iii-040205385.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>14-09-2026 05:43 UTC</t>
+          <t>15-09-2026 04:02 UTC</t>
         </is>
       </c>
     </row>
@@ -1705,130 +1705,130 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cape Pioneer 2026 promises fierce racing as route changes and rider numbers rise</t>
+          <t>Trump's Drug Pricing Policy Could Drive Up Prices in South Korea and Other Overseas Markets</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>George Herald</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.georgeherald.com/Sport/Article/Other/cape-pioneer-2026-promises-fierce-racing-as-route-changes-and-rider-numbers-rise-202609141025</t>
+          <t>https://finance.biggo.com/news/65eb6133-9aae-4a67-ac88-0eff477771bb</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14-09-2026 08:40 UTC</t>
+          <t>14-09-2026 10:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dr Reddy’s launches educational initiative to strengthen obesity care workforce</t>
+          <t>Scholar Rock Drug Wins First-in-Class Approval in Rare Neuromuscular Disease</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>MedCity News</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/dr-reddys-launches-educational-initiative-to-strengthen-obesity-care-workforce/article71465962.ece</t>
+          <t>https://medcitynews.com/2026/09/scholar-rock-drug-wins-first-in-class-approval-in-rare-neuromuscular-disease/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14-09-2026 11:36 UTC</t>
+          <t>14-09-2026 19:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s launches nationwide programme to train 5,000+ certified obesity educators</t>
+          <t>Scholar Rock secures first FDA approval for muscle-targeting rare disease drug</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/healthcare/dr-reddys-launches-nationwide-programme-to-train-5000-certified-obesity-educators-21836</t>
+          <t>https://www.biospace.com/fda/scholar-rock-secures-first-fda-approval-for-muscle-targeting-rare-disease-drug</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>14-09-2026 11:04 UTC</t>
+          <t>14-09-2026 12:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dr Reddy's halts semaglutide supplies on impurity issue</t>
+          <t>Cape Pioneer 2026 promises fierce racing as route changes and rider numbers rise</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>George Herald</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-laboratories-delays-semaglutide-supplies-due-to-api-issue/45115417</t>
+          <t>https://www.georgeherald.com/Sport/Article/Other/cape-pioneer-2026-promises-fierce-racing-as-route-changes-and-rider-numbers-rise-202609141025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13-09-2026 19:05 UTC</t>
+          <t>14-09-2026 08:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Income Tax Notice Issued to Non-Existent Entity After Merger Unsustainable: Telangana HC [Read Order]</t>
+          <t>2026 Race With Soul promises fierce racing, heartfelt hospitality, and a route twist</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Taxscan</t>
+          <t>mosselbayadvertiser.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.taxscan.in/top-stories/income-tax-notice-issued-to-non-existent-entity-after-merger-unsustainable-telangana-hc-1451423</t>
+          <t>https://www.mosselbayadvertiser.com/Galleries/Gallery/Sport/2026-race-with-soul-promises-fierce-racing-heartfelt-hospitality-and-a-route-twist-202609141024</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>14-09-2026 06:17 UTC</t>
+          <t>14-09-2026 08:22 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OT security cannot follow an IT playbook when cyber risk can stop production and endanger safety</t>
+          <t>Dr. Reddy’s To Train 5,000 Professionals In Obesity Care</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ET CISO</t>
+          <t>BW Healthcare World</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://ciso.economictimes.indiatimes.com/news/ot-security/ot-security-cannot-follow-an-it-playbook-when-cyber-risk-can-stop-production-and-endanger-safety/134235383</t>
+          <t>https://www.bwhealthcareworld.com/article/dr-reddy-s-to-train-5-000-professionals-in-obesity-care-623671</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>14-09-2026 09:33 UTC</t>
+          <t>15-09-2026 04:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1867,61 +1867,61 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Reports FDA Records Assessment at Mexican API Plant Concluding with Two Observations</t>
+          <t>How Dr. Reddy’s is helping build India’s obesity workforce</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>HR Katha</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/dr-reddys-reports-fda-records-assessment-at-mexican-api-plant-concluding-with-two-observations</t>
+          <t>https://www.hrkatha.com/news/learning-development/how-dr-reddys-is-helping-build-indias-obesity-workforce/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>14-09-2026 11:12 UTC</t>
+          <t>15-09-2026 04:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AI is changing cyberattacks from automated to adaptive; SOCs must respond at the same speed</t>
+          <t>Dr Reddy’s launches educational initiative to strengthen obesity care workforce</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ET CISO</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://ciso.economictimes.indiatimes.com/news/corporate/ai-is-changing-cyberattacks-from-automated-to-adaptive-socs-must-respond-at-the-same-speed/134235124</t>
+          <t>https://www.thehindubusinessline.com/companies/dr-reddys-launches-educational-initiative-to-strengthen-obesity-care-workforce/article71465962.ece</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14-09-2026 09:30 UTC</t>
+          <t>14-09-2026 11:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C-CAMP National Bio Entrepreneurship competition 2026 recognises 15 startups and four student teams</t>
+          <t>Dr. Reddy’s launches nationwide programme to train 5,000+ certified obesity educators</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1931,498 +1931,498 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/c-camp-national-bio-entrepreneurship-competition-2026-recognises-15-startups-and-four-student-teams-21825</t>
+          <t>https://www.indianpharmapost.com/healthcare/dr-reddys-launches-nationwide-programme-to-train-5000-certified-obesity-educators-21836</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14-09-2026 03:18 UTC</t>
+          <t>14-09-2026 11:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>275 register for free health camp in Phesama</t>
+          <t>Dr. Reddy’s Launches Obesity Care Training Initiative</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Eastern Mirror</t>
+          <t>Voice of Healthcare</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.easternmirrornagaland.com/275-register-for-free-health-camp-in-phesama</t>
+          <t>https://vohnetwork.com/news/policy/dr-reddy-s-laboratories-launches-nationwide-educational-initiative-to-strengthen-india-s-obesity-care-workforce</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14-09-2026 16:03 UTC</t>
+          <t>14-09-2026 12:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>275 register for free cancer screening, health camp at Phesama</t>
+          <t>OT security cannot follow an IT playbook when cyber risk can stop production and endanger safety</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MorungExpress</t>
+          <t>ET CISO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/275-register-for-free-cancer-screening-health-camp-at-phesama</t>
+          <t>https://ciso.economictimes.indiatimes.com/amp/news/ot-security/ot-security-cannot-follow-an-it-playbook-when-cyber-risk-can-stop-production-and-endanger-safety/134235383</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14-09-2026 15:55 UTC</t>
+          <t>14-09-2026 09:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Russian forces strike BaDM warehouse in fourth attack on pharma distributor in two weeks</t>
+          <t>Frymaster tour</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>The New Voice of Ukraine</t>
+          <t>The Shreveport-Bossier City Advocate</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://english.nv.ua/business/russian-attack-hits-badm-warehouse-marking-fourth-hit-on-top-pharma-company-in-two-weeks-50641173.html</t>
+          <t>https://www.shreveportbossieradvocate.com/frymaster-tour/image_aa372f6f-387d-4d0e-a194-58000e9a9a05.html</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14-09-2026 09:04 UTC</t>
+          <t>14-09-2026 22:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SKUAST-K scholar wins national bio-entrepreneurship award</t>
+          <t>Glendiay Brown, Frymaster2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>thekashmirimages.com</t>
+          <t>The Shreveport-Bossier City Advocate</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://thekashmirimages.com/2026/09/14/skuast-k-scholar-wins-national-bio-entrepreneurship-award/</t>
+          <t>https://www.shreveportbossieradvocate.com/glendiay-brown-frymaster2/image_b8ef3f4a-6b3c-49ed-bfc7-05bf6a12971e.html</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>13-09-2026 18:41 UTC</t>
+          <t>14-09-2026 19:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma’s API facility clears FDA inspection</t>
+          <t>Glen Brown Frymaster</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>The Shreveport-Bossier City Advocate</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/aurobindo-pharmas-api-facility-clears-fda-inspection/134230645</t>
+          <t>https://www.shreveportbossieradvocate.com/glen-brown-frymaster/image_f5009e63-6ef9-490e-a1ae-9e7c370ec0a5.html</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>14-09-2026 02:00 UTC</t>
+          <t>14-09-2026 19:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma's Apitoria clears US FDA inspection with zero observations</t>
+          <t>Dr. Reddy’s Reports FDA Records Assessment at Mexican API Plant Concluding with Two Observations</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/aurobindo-pharmas-apitoria-clears-us-fda-inspection-with-zero-observations-21829</t>
+          <t>https://www.tipranks.com/news/company-announcements/dr-reddys-reports-fda-records-assessment-at-mexican-api-plant-concluding-with-two-observations</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14-09-2026 04:32 UTC</t>
+          <t>14-09-2026 11:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The CDMO Revolution: How Contract Drug Manufacturers Are Reshaping Global Pharma- Expert View by Spherical Insights</t>
+          <t>Shobiz CEO Sameer Tobaccowala on How Audience Expectations Are Changing</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spherical Insights</t>
+          <t>Storyboard18</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.sphericalinsights.com/blogs/the-cdmo-revolution-how-contract-drug-manufacturers-are-reshaping-global-pharma</t>
+          <t>https://www.storyboard18.com/videos/brand-marketing/shobiz-ceo-sameer-tobaccowala-on-how-audience-expectations-are-changing-110689.htm</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>13-09-2026 17:51 UTC</t>
+          <t>15-09-2026 06:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Zydus Spine Surgeons Push the Boundaries of Complex Spine Care, Delivering Excellent Outcomes Across All Ages</t>
+          <t>AI is changing cyberattacks from automated to adaptive; SOCs must respond at the same speed</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>ET CISO</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/zydus-spine-surgeons-push-boundaries-043000290.html</t>
+          <t>https://ciso.economictimes.indiatimes.com/news/corporate/ai-is-changing-cyberattacks-from-automated-to-adaptive-socs-must-respond-at-the-same-speed/134235124</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>14-09-2026 04:30 UTC</t>
+          <t>14-09-2026 09:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Samsung Launches Galaxy S26 FE in India, Bringing Flagship Camera, Galaxy AI and Powerful Performance</t>
+          <t>Russian forces strike BaDM warehouse in fourth attack on pharma distributor in two weeks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>english.nv.ua</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/in/samsung-launches-galaxy-s26-fe-in-india-bringing-flagship-camera-galaxy-ai-and-powerful-performance</t>
+          <t>https://english.nv.ua/business/russian-attack-hits-badm-warehouse-marking-fourth-hit-on-top-pharma-company-in-two-weeks-50641173.html</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>14-09-2026 11:16 UTC</t>
+          <t>14-09-2026 09:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S27 Pro and S27 Ultra to feature next-generation M16 OLED panel - GSMArena.com news</t>
+          <t>Free Cancer Screening cum Health Camp held at Phesama</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>Nagaland Post</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.gsmarena.com/samsung_galaxy_s27_pro_and_s27_ultra_to_feature_nextgeneration_m16_oled_panel-news-74603.php</t>
+          <t>https://nagalandpost.com/free-cancer-screening-cum-health-camp-held-at-phesama/</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14-09-2026 15:11 UTC</t>
+          <t>15-09-2026 05:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S27 Ultra Said to Retain 5x Telephoto Camera; May Ditch Dedicated 3x Camera</t>
+          <t>275 register for free cancer screening, health camp at Phesama</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>MorungExpress</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s27-ultra-5x-telephoto-camera-rear-features-specifications-leak-12045072</t>
+          <t>https://morungexpress.com/275-register-for-free-cancer-screening-health-camp-at-phesama</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>14-09-2026 12:10 UTC</t>
+          <t>14-09-2026 15:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Making sovereign, open-weight AI the technology frontier</t>
+          <t>275 register for free health camp in Phesama</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>mistral.ai</t>
+          <t>Eastern Mirror</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://mistral.ai/news/mistral-makes-sovereign-open-weight-ai-to-frontier/</t>
+          <t>https://www.easternmirrornagaland.com/275-register-for-free-health-camp-in-phesama</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14-09-2026 15:02 UTC</t>
+          <t>14-09-2026 17:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Samsung unveils a 10,000-nit OLED screen, the brightest yet for smartphones</t>
+          <t>Korea Exchange: வர்த்தக நேரத்தை நீட்டித்த கொரியா! இந்தியா எடுக்கப்போகும் முடிவு என்ன?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sammobile.com</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/samsung-display-unveils-10000-nits-oled-screen-brightest-smartphones/</t>
+          <t>https://www.whalesbook.com/news/Tamil/sebiexchange/Korea-Exchange-Extends-Trading-Hours-India-Sticks-to-Current-Clock/6aa80c9075fe79b492e69e89</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14-09-2026 05:47 UTC</t>
+          <t>14-09-2026 15:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Galaxy S26 FE Is Now Official In India, Price Confirmed</t>
+          <t>Aurobindo Pharma Unit-IV API Facility Concludes US FDA Inspection With Zero Observations</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SammyGuru</t>
+          <t>Sahi</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://sammyguru.com/galaxy-s26-fe-launches-in-india-price-confirmed/</t>
+          <t>https://www.sahi.com/news/aurobindo-pharma-unit-iv-api-facility-concludes-us-fda-inspection-with-zero-observations</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>14-09-2026 16:42 UTC</t>
+          <t>15-09-2026 00:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 FE launched in India: Price in India, specifications and all you need to know</t>
+          <t>Piramal Pharma UK Facility Gets 7 US FDA Observations</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/technology/tech-news/samsung-galaxy-s26-fe-launched-in-india-price-in-india-specifications-and-all-you-need-to-know/articleshow/134244501.cms</t>
+          <t>https://money.rediff.com/amp/news/market/piramal-pharma-uk-facility-gets-7-us-fda-observations/54335420260914</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14-09-2026 16:25 UTC</t>
+          <t>14-09-2026 16:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>I tried Samsung's Auto Blocker; it does way more than I expected</t>
+          <t>Aurobindo Pharma secures USFDA approval for Beclomethasone Dipropionate HFA Inhalation Aerosol</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Android Police</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.androidpolice.com/samsungs-auto-blocker-does-way-more-than-i-expected/</t>
+          <t>https://businessupturn.com/business/aurobindo-pharma-secures-usfda-approval-for-beclomethasone-dipropionate-hfa-inhalation-aerosol/</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14-09-2026 12:15 UTC</t>
+          <t>15-09-2026 07:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Samsung launches Galaxy S26 FE for the premium segment buyers in India</t>
+          <t>Aurobindo Pharma Wins USFDA Nod for First Inhaler, Targeting $301 Million Asthma Market</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/sci-tech/technology/gadgets/samsung-launches-galaxy-s26-fe-for-the-premium-segment-buyers-in-india/article71465729.ece</t>
+          <t>https://www.tipranks.com/news/company-announcements/aurobindo-pharma-wins-usfda-nod-for-first-inhaler-targeting-301-million-asthma-market</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>14-09-2026 08:46 UTC</t>
+          <t>15-09-2026 08:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 FE With Exynos 2500 Chipset, IP68 Rating Launched In India At Rs 79,999</t>
+          <t>High-Concentration, Low-Volume Subcutaneous Formulation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>PharmTech.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/technology/samsung-galaxy-s26-fe-launched-in-india-price-specifications-availability-enn26091404544</t>
+          <t>https://www.pharmtech.com/view/high-concentration-low-volume-subcutaneous-formulation</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>14-09-2026 12:09 UTC</t>
+          <t>14-09-2026 19:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2434,22 +2434,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 Plus is available at a lower price: Details here</t>
+          <t>Samsung Launches Galaxy S26 FE in India, Bringing Flagship Camera, Galaxy AI and Powerful Performance</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/visualstories/technology/samsung-galaxy-s26-plus-is-available-at-a-lower-price-details-here-285702-14-09-2026</t>
+          <t>https://news.samsung.com/in/samsung-launches-galaxy-s26-fe-in-india-bringing-flagship-camera-galaxy-ai-and-powerful-performance</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>14-09-2026 13:23 UTC</t>
+          <t>14-09-2026 11:16 UTC</t>
         </is>
       </c>
     </row>
@@ -2461,22 +2461,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Samsung and Verizon Complete Successful ISAC Trial Over Virtualized Network at Global Sports Event</t>
+          <t>Samsung's India public policy chief resigns, sources say</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>cfo.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-and-verizon-complete-successful-isac-trial-over-virtualized-network-at-global-sports-event</t>
+          <t>https://cfo.economictimes.indiatimes.com/news/leadership/samsungs-india-public-policy-chief-resigns-sources-say/134255191</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>14-09-2026 13:10 UTC</t>
+          <t>15-09-2026 07:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Compare Samsung Galaxy A08</t>
+          <t>Samsung SDS Becomes Korea’s First Select Tier Partner in Anthropic’s Claude Partner Network</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>Samsung SDS America</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.gsmarena.com/compare.php3?idPhone1=14938</t>
+          <t>https://www.samsungsds.com/en/news/1295381_5252.html</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>14-09-2026 12:46 UTC</t>
+          <t>15-09-2026 06:10 UTC</t>
         </is>
       </c>
     </row>
@@ -2515,22 +2515,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Samsung may launch the Galaxy Tab S12+ and Ultra on October 7</t>
+          <t>iPhone 18 Pro Max vs. Samsung Galaxy S26 Ultra: Battle of the flagships</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>sammobile.com</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/samsung-may-launch-the-galaxy-tab-s12-and-ultra-on-october-7/</t>
+          <t>https://mashable.com/tech/iphone-18-pro-max-vs-galaxy-s26-ultra-price-specs</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>14-09-2026 08:36 UTC</t>
+          <t>14-09-2026 17:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2542,751 +2542,751 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Marking Eight Generations of Foldable Innovation: The Incredible Evolution of Samsung’s Galaxy Z Series</t>
+          <t>Samsung Galaxy Tab S12 Series Will Reportedly Launch Early Next Month: Expected Specifications</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/sg/marking-eight-generations-of-foldable-innovation-the-incredible-evolution-of-samsungs-galaxy-z-series</t>
+          <t>https://www.gadgets360.com/tablets/news/samsung-galaxy-tab-s12-series-launch-date-tipped-specifications-features-12047802</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>14-09-2026 12:25 UTC</t>
+          <t>15-09-2026 05:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Samsung Heavy Wins $1B Order for Four LNG Carriers</t>
+          <t>Samsung faces local hedge fund's push to cancel preferred shares</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/14/samsung-heavy-wins-1b-order-for-four-lng-carriers</t>
+          <t>https://www.moneycontrol.com/news/business/samsung-faces-local-hedge-fund-s-push-to-cancel-preferred-shares-14029825.html</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>14-09-2026 06:39 UTC</t>
+          <t>15-09-2026 02:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Prestige BioPharma Calls Shareholder Meeting to Refresh Board and Expand Capital-Raising Powers</t>
+          <t>Samsung's India public policy chief Rajiv ‌Aggarwal resigns, sources say</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/prestige-biopharma-calls-shareholder-meeting-to-refresh-board-and-expand-capital-raising-powers</t>
+          <t>https://www.thehindubusinessline.com/info-tech/samsungs-india-public-policy-chief-rajiv-aggarwal-resigns-sources-say/article71466989.ece</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>14-09-2026 09:16 UTC</t>
+          <t>15-09-2026 07:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tokyo court dismisses Malaysia’s IHH unit’s claims against Daiichi Sankyo</t>
+          <t>Samsung India public policy chief Rajiv ​Aggarwal steps down: Reports</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Medical Buyer</t>
+          <t>Exchange4Media</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/tokyo-court-dismisses-malaysias-ihh-units-claims-against-daiichi-sankyo/</t>
+          <t>https://www.exchange4media.com/people-movement-news/samsung-india-public-policy-chief-rajiv-aggarwal-steps-down-reports-158245.html</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>14-09-2026 08:17 UTC</t>
+          <t>15-09-2026 07:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Increased deaths shadow AstraZeneca, Daiichi’s Enhertu first-line lung cancer data</t>
+          <t>Samsung quietly makes the Galaxy A08 official with a bigger battery - GSMArena.com news</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/higher-death-risk-shadows-astrazeneca-daiichi-enhertu-first-line-lung-cancer-data</t>
+          <t>https://www.gsmarena.com/samsung_quietly_makes_the_galaxy_a08_official_with_a_bigger_battery-news-74614.php</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>13-09-2026 23:00 UTC</t>
+          <t>15-09-2026 07:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tokyo Court rejects IHH unit's claims against Daiichi Sankyo</t>
+          <t>Samsung India public affairs head Rajiv Aggarwal resigns after nearly four years</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Singapore Business Review</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://sbr.com.sg/healthcare/news/tokyo-court-rejects-ihh-units-claims-against-daiichi-sankyo</t>
+          <t>https://www.cnbctv18.com/business/companies/samsung-india-public-affairs-head-rajiv-aggarwal-resigns-19990859.htm</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>14-09-2026 02:37 UTC</t>
+          <t>15-09-2026 08:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ENHERTU® (fam-trastuzumab deruxtecan-nxki) demonstrated a median progression-free survival of 14.3 months as 1st-line therapy in patients with HER2-mutant advanced non-small cell lung cancer in DESTINY-Lung04 Phase III trial</t>
+          <t>Samsung brings Galaxy S26 FE to India</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Telecompaper</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/enhertu-fam-trastuzumab-deruxtecan-nxki-demonstrated-a-median-progression-free-survival-of-14-3-months-as-1st-line-therapy-in-patients-with-her2-mutant-advanced-non-small-cell-lung-cancer-in-destiny-lung04-phase-iii-trial</t>
+          <t>https://www.telecompaper.com/news/samsung-brings-galaxy-s26-fe-to-india--1582648</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>14-09-2026 04:21 UTC</t>
+          <t>15-09-2026 02:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Enhertu® Demonstrated a Median Progression-Free Survival of 14.3</t>
+          <t>Samsung invests in Nvidia rival: Dutch AI chip startup gets $230 million funding as quest for alternatives grow</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>natlawreview.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://natlawreview.com/press-releases/enhertur-demonstrated-median-progression-free-survival-143-months-first-line</t>
+          <t>https://www.livemint.com/companies/news/samsung-invests-in-nvidia-rival-dutch-ai-chip-startup-euclyd-gets-230-million-funding-as-quest-for-alternatives-grow-11789444181041.html</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>14-09-2026 03:37 UTC</t>
+          <t>15-09-2026 05:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi report Enhertu benefit in advanced lung cancer</t>
+          <t>Samsung is about to make everyone's phones more expensive</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>London South East</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.lse.co.uk/news/astrazeneca-daiichi-report-enhertu-benefit-in-advanced-lung-cancer-o6o75ns4dmqn0hr.html</t>
+          <t>https://www.sammobile.com/news/samsung-is-about-to-make-everyones-phones-more-expensive/</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>14-09-2026 02:47 UTC</t>
+          <t>15-09-2026 07:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>$19.6B Infusion In US Plants With Lower Drug Prices: White House’s Deal With Mid-size Drugmakers</t>
+          <t>Samsung Galaxy S27 Ultra Tipped to Feature M16 OLED Panels; May Prioritise Privacy Over Brightness</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://stocktwits.com/news-articles/markets/equity/19-6-b-infusion-in-us-plants-with-lower-drug-prices-white-house-s-deal-with-mid-size-drugmakers/cZYz7nNRJtG</t>
+          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s27-ultra-pro-m16-oled-panels-privacy-display-feature-leak-12047803</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>13-09-2026 21:54 UTC</t>
+          <t>15-09-2026 05:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MEDIPAL, JCR Dose First Patient in Global Phase I/II Trial of JR-446 for Sanfilippo Syndrome</t>
+          <t>Celltrion files for US phase 4 trial of 240 mg Zymfentra dose</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/86/8425/medipal-jcr-dose-first-patient-in-global-phase-i-ii-trial-of-jr-446-for-sanfilippo-syndrome.html</t>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33176</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>13-09-2026 18:36 UTC</t>
+          <t>15-09-2026 04:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Perfect Pitch: Inside the scheme that gets junior lawyers selling to clients</t>
+          <t>Celltrion Launches US Zymfentra High-Dose Trial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>lifesciencesipreview.com</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.lifesciencesipreview.com/regulation-and-industry/perfect-pitch-inside-the-scheme-that-gets-junior-lawyers-selling-to-clients</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=276960</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>14-09-2026 15:11 UTC</t>
+          <t>15-09-2026 03:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AbelZeta Receives FDA IND Clearance for Phase 1b/2 Clinical Trial of C-CAR168 in Progressive Multiple Sclerosis</t>
+          <t>Celltrion is launching phase 4 clinical trials in the U.S. to secure the basis for the high dose of</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/abelzeta-receives-fda-ind-clearance-for-phase-1b2-clinical-trial-of-c-car168-in-progressive-multiple-sclerosis-302877555.html</t>
+          <t>https://www.mk.co.kr/en/it/12152917</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>14-09-2026 11:30 UTC</t>
+          <t>15-09-2026 01:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EMPLOYMENT (14-09-2026)</t>
+          <t>Celltrion Moves to Expand Zymfentra Use in the U.S. With New Phase 4 Trial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Daily Excelsior</t>
+          <t>koreaittimes.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.dailyexcelsior.com/employment-14-09-2026/amp</t>
+          <t>https://www.koreaittimes.com/news/articleView.html?idxno=157163</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>14-09-2026 05:19 UTC</t>
+          <t>15-09-2026 01:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc. Announces Changes to Board of Directors</t>
+          <t>Celltrion Advances High-Dose Clinical Trial for "Zymfentra" to Broaden U.S. Prescription Base</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.manilatimes.net/2026/09/14/tmt-newswire/globenewswire/total-energy-services-inc-announces-changes-to-board-of-directors/2424520/amp</t>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026091509285390683</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14-09-2026 12:17 UTC</t>
+          <t>15-09-2026 00:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Certain Ordinary Shares of Alvotech are subject to a Lock-Up Agreement Ending on 14-SEP-2026.</t>
+          <t>Chong Kun Dang Joins the SC Conversion Race... IP Competition Heats Up</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/certain-ordinary-shares-of-alvotech-are-subject-to-a-lock-up-agreement-ending-on-14-sep-2026-ce785bdcd889f520</t>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026091507340241619</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>14-09-2026 00:37 UTC</t>
+          <t>15-09-2026 01:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>eQ Plc Members of the Shareholders’ Nomination Committee</t>
+          <t>Prestige BioPharma Calls Shareholder Meeting to Refresh Board and Expand Capital-Raising Powers</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/avacta-appoints-mats-blom-board-060000062.html</t>
+          <t>https://www.tipranks.com/news/company-announcements/prestige-biopharma-calls-shareholder-meeting-to-refresh-board-and-expand-capital-raising-powers</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14-09-2026 06:26 UTC</t>
+          <t>14-09-2026 09:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Teva Pharmaceuticals Sees Pivot to Growth Accelerating on Branded Drugs, Biosimilars</t>
+          <t>Enhertu Shows Six-Month PFS Gain In HER2-Mutant Lung Cancer</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>BW Healthcare World</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/teva-pharmaceuticals-sees-pivot-growth-140227795.html</t>
+          <t>https://www.bwhealthcareworld.com/article/enhertu-shows-six-month-pfs-gain-in-her2-mutant-lung-cancer-623644</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>14-09-2026 14:02 UTC</t>
+          <t>15-09-2026 04:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Results for Teva Bouchgua at REMA Saquarema Surf Festival 2026</t>
+          <t>Enhertu EU Milestone And Legal Win Might Change The Case For Investing In Daiichi Sankyo (TSE:4568)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>World Surf League</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.worldsurfleague.com/athletes/9259/teva-bouchgua/eventresults?eventId=5182</t>
+          <t>https://uk.finance.yahoo.com/news/enhertu-eu-milestone-legal-win-151207313.html</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>13-09-2026 20:31 UTC</t>
+          <t>14-09-2026 15:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Teva Women's Teva Ember Moc Sizing Teva Ember Moc Teva Slip On Shoes Teva Ember Moc Slip On Blue</t>
+          <t>WCLC26: Enhertu's PFS lung cancer win comes with an OS question mark</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>fuelcarmagazine</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://fuelcarmagazine.com/?x=4032494051270</t>
+          <t>https://firstwordpharma.com/story/7990485</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>13-09-2026 19:42 UTC</t>
+          <t>14-09-2026 22:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lupin targets $500 million biosimilar revenue in five years</t>
+          <t>Enhertu Phase III win supports first-line expansion in HER2-mutant NSCLC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>AllSci</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/lupin-targets-500-million-biosimilar-revenue-in-five-years</t>
+          <t>https://allsci.com/news/clinical-trials/her2-mutant-lung-cancer-enhertu-cuts-progression/</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>14-09-2026 15:22 UTC</t>
+          <t>14-09-2026 11:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Samsung, LG to Pay Suppliers ₩1.9 Trillion (approximately $1.4 Billion) Early Ahead of Chuseok</t>
+          <t>Roche, MediLink notch phase 3 lung cancer win but trail GSK on cross-trial survival</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Fierce Biotech</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/8b2649e0-23cf-481b-b34d-61f9cf822d8a</t>
+          <t>https://www.fiercebiotech.com/biotech/roche-and-medilink-notch-phase-3-lung-cancer-win-trail-gsk-cross-trial-survival</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>14-09-2026 06:05 UTC</t>
+          <t>14-09-2026 09:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Samsung, Hyundai, LG Advance Payments to Suppliers Ahead of Chuseok</t>
+          <t>Trastuzumab Deruxtecan Improves PFS in First-Line HER2-Mutant NSCLC in DESTINY-Lung04</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/english/industry-en/2026/09/14/GWXBHH6C7VAIHLLINZIJCGKADU/</t>
+          <t>https://oncodaily.com/trial-updates/trastuzumab-deruxtecan-585631</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>14-09-2026 09:32 UTC</t>
+          <t>14-09-2026 09:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>KRTL Biotech Appoints Federal Controlled-Substance Compliance Specialist Justin Abril as President-Designate</t>
+          <t>Enhertu keeps first-line HER2-mutant lung cancer in check for six months longer — but early deaths run higher</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>Dealroom</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/krtl-biotech-appoints-federal-controlled-130000493.html</t>
+          <t>https://app.dealroom.co/news/note/enhertu-keeps-first-line-her2-mutant-lung-cancer-in-check-for-six-months-longer-but-early-deaths-run-higher</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>14-09-2026 13:00 UTC</t>
+          <t>14-09-2026 13:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>“Samsung Group to release KRW 1.3 trillion before Chuseok,” paying suppliers seven days early</t>
+          <t>China phase III trials make case for B7-H3 ADCs in relapsed SCLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>BioWorld News</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/en/business/12151952</t>
+          <t>https://www.bioworld.com/articles/734038-china-phase-iii-trials-make-case-for-b7-h3-adcs-in-relapsed-sclc</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>14-09-2026 16:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Samsung and LG Advance 1.9 Trillion Won in Payments Ahead of Chuseok, All-Out Effort for Mutual Growth and Domestic Demand</t>
+          <t>AstraZeneca's Etcamah misses primary goal in breast cancer trial</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>asiae.co.kr</t>
+          <t>NewsBytes</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/enterprise-CEO/2026091410510214218</t>
+          <t>https://www.newsbytesapp.com/news/business/astrazenecas-etcamah-misses-primary-goal-in-breast-cancer-trial/tldr</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>14-09-2026 15:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SleepRes Receives Frost &amp; Sullivan's 2026 North America New Product Innovation Recognition for Excellence in Positive Airway Pressure Device Innovation</t>
+          <t>[No. 243] Kenji Hagiwara</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>keio.ac.jp</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/sleepres-receives-frost-sullivans-2026-130000178.html</t>
+          <t>https://www.keio.ac.jp/en/st/campus-life/alumni_relay/2609/</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>14-09-2026 13:00 UTC</t>
+          <t>15-09-2026 03:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Samsung advances 1.3 trillion-won supplier payments to boost Korea’s economy - CHOSUNBIZ</t>
+          <t>Amgen vs. Vertex Pharmaceuticals: Value Stability vs. High-Growth Biotech Investment Plays</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>NAI500</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-it/2026/09/14/233PHRZEDBEHTOHAB26HDNIAA4/</t>
+          <t>https://nai500.com/blog/2026/09/amgen-vs-vertex-pharmaceuticals-value-stability-vs-high-growth-biotech-investment-plays/</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>15-09-2026 02:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>lifesciencesipreview.com</t>
+          <t>Life Sciences IP Review</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3320,297 +3320,648 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>The CDMO Revolution: How Contract Drug Manufacturers Are Reshaping Global Pharma- Expert View by Spherical Insights</t>
+          <t>AbelZeta Receives FDA IND Clearance for Phase 1b/2 Clinical Trial of C-CAR168 in Progressive Multiple Sclerosis</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spherical Insights</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.sphericalinsights.com/blogs/the-cdmo-revolution-how-contract-drug-manufacturers-are-reshaping-global-pharma</t>
+          <t>https://www.prnewswire.com/news-releases/abelzeta-receives-fda-ind-clearance-for-phase-1b2-clinical-trial-of-c-car168-in-progressive-multiple-sclerosis-302877555.html</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>13-09-2026 17:51 UTC</t>
+          <t>14-09-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Samsung, Hyundai, LG Advance Payments to Suppliers Ahead of Chuseok</t>
+          <t>Total Energy Services Inc. Announces Changes to Board of Directors</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/english/industry-en/2026/09/14/GWXBHH6C7VAIHLLINZIJCGKADU/</t>
+          <t>https://www.manilatimes.net/2026/09/14/tmt-newswire/globenewswire/total-energy-services-inc-announces-changes-to-board-of-directors/2424520/amp</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>14-09-2026 09:32 UTC</t>
+          <t>14-09-2026 12:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Songdo Opens Bio Training Center to Ease Talent Shortage</t>
+          <t>FACT CHECK: Mike Rogers Repeatedly Voted for Higher Prescription Drug Costs and Healthcare Premiums for Michiganders</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Michigan Democratic Party</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/society/2026/09/14/songdo-opens-bio-training-center-to-ease-talent-shortage</t>
+          <t>https://michigandems.com/fact-check-mike-rogers-repeatedly-voted-for-higher-prescription-drug-costs-and-healthcare-premiums-for-michiganders/</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>14-09-2026 00:29 UTC</t>
+          <t>14-09-2026 21:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Samsung advances 1.3 trillion-won supplier payments to boost Korea’s economy - CHOSUNBIZ</t>
+          <t>GSK Pharma Shareholders Approve Board and Managing Director Appointments via Postal Ballot</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-it/2026/09/14/233PHRZEDBEHTOHAB26HDNIAA4/</t>
+          <t>https://www.tipranks.com/news/company-announcements/gsk-pharma-shareholders-approve-board-and-managing-director-appointments-via-postal-ballot</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>15-09-2026 08:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>“Samsung Group to release KRW 1.3 trillion before Chuseok,” paying suppliers seven days early</t>
+          <t>Alto Ingredients, Inc. to Participate in the H.C. Wainwright 28th Annual Global Investment Conference</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/en/business/12151952</t>
+          <t>https://uk.finance.yahoo.com/news/alto-ingredients-inc-participate-h-123000655.html</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>14-09-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Samsung, LG to pay suppliers 1.9 trillion won early ahead of Chuseok</t>
+          <t>We're turning into a more innovative company: Teva Pharmaceuticals CEO Richard Francis</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Aju Press</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://m.ajupress.com/amp/20260914171524025</t>
+          <t>https://www.cnbc.com/video/2026/09/14/were-turning-into-a-more-innovative-company-teva-pharmaceuticals-ceo-richard-francis.html</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>14-09-2026 08:25 UTC</t>
+          <t>14-09-2026 18:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Samsung and LG Advance 1.9 Trillion Won in Payments Ahead of Chuseok, All-Out Effort for Mutual Growth and Domestic Demand</t>
+          <t>Teva Pharmaceuticals Sees Pivot to Growth Accelerating on Branded Drugs, Biosimilars</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>asiae.co.kr</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/enterprise-CEO/2026091410510214218</t>
+          <t>https://finance.yahoo.com/healthcare/articles/teva-pharmaceuticals-sees-pivot-growth-140227795.html</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>14-09-2026 14:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Samsung, LG to Pay Suppliers ₩1.9 Trillion (approximately $1.4 Billion) Early Ahead of Chuseok</t>
+          <t>Pearce IP BioBlast® for the fortnight ending 11 September 2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Pearce IP</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/8b2649e0-23cf-481b-b34d-61f9cf822d8a</t>
+          <t>https://www.pearceip.law/2026/09/15/pearce-ip-bioblast-for-the-fortnight-ending-11-september-2026/</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>14-09-2026 06:05 UTC</t>
+          <t>15-09-2026 05:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Samsung to pay 1.3 trillion won early to suppliers</t>
+          <t>Lupin targets $500 million biosimilar revenue in five years</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>디지털투데이</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.digitaltoday.co.kr/en/view/103165/samsung-to-pay-1-3-trillion-won-early-to-suppliers</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/lupin-targets-500-million-biosimilar-revenue-in-five-years</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>14-09-2026 05:00 UTC</t>
+          <t>14-09-2026 15:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>U.S., Japan Rate Decisions Converge in Super Week</t>
+          <t>Coultreon Biopharma Appoints Nate Massari as Chief Business Officer</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/14/us-japan-rate-decisions-converge-in-super-week</t>
+          <t>https://sg.finance.yahoo.com/news/coultreon-biopharma-appoints-nate-massari-130000693.html</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>14-09-2026 01:51 UTC</t>
+          <t>14-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Samsung, Hyundai, LG Advance Payments to Suppliers Ahead of Chuseok</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>chosun.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.chosun.com/english/industry-en/2026/09/14/GWXBHH6C7VAIHLLINZIJCGKADU/</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>14-09-2026 09:32 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Chong Kun Dang Joins the SC Conversion Race... IP Competition Heats Up</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>아시아경제</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026091507340241619</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>15-09-2026 01:35 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pfizer loses patent case over Enbrel generic</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Lawyerly</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://www.lawyerly.com.au/pfizer-loses-patent-case-over-enbrel-generic/</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>15-09-2026 07:27 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>KRTL Biotech Appoints Federal Controlled-Substance Compliance Specialist Justin Abril as President-Designate</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Singapore</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://sg.finance.yahoo.com/news/krtl-biotech-appoints-federal-controlled-130000493.html</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>14-09-2026 13:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SleepRes Receives Frost &amp; Sullivan's 2026 North America New Product Innovation Recognition for Excellence in Positive Airway Pressure Device Innovation</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Singapore</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://sg.finance.yahoo.com/news/sleepres-receives-frost-sullivans-2026-130000178.html</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>14-09-2026 13:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Perfect Pitch: Inside the scheme that gets junior lawyers selling to clients</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Life Sciences IP Review</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://www.lifesciencesipreview.com/regulation-and-industry/perfect-pitch-inside-the-scheme-that-gets-junior-lawyers-selling-to-clients</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>14-09-2026 15:11 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Samsung, LG to Pay Suppliers Early Ahead of Chuseok</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Seoul Economic Daily</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>https://en.sedaily.com/finance/2026/09/14/samsung-lg-to-pay-suppliers-19-trillion-won-early-before</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>14-09-2026 05:00 UTC</t>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Samsung Biologics signs USD 262 million manufacturing agreement with European pharmaceutical company</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Drug Discovery News</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.drugdiscoverynews.com/samsung-biologics-signs-usd-262-million-manufacturing-agreement-with-european-pharmaceutical-company-17527</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>14-09-2026 19:48 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>An Integrated Analytical Approach To Lipase Risk Management In Biologics Development</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Bioprocess Online</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.bioprocessonline.com/doc/an-integrated-analytical-approach-to-lipase-risk-management-in-biologics-development-0001</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>15-09-2026 00:39 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Samsung, Hyundai, LG Advance Payments to Suppliers Ahead of Chuseok</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>chosun.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://www.chosun.com/english/industry-en/2026/09/14/GWXBHH6C7VAIHLLINZIJCGKADU/</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>14-09-2026 09:32 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Samsung, SK Hynix Limit Pre-Market Losses Despite 5.86% Plunge in Philadelphia Semiconductor Index</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>finance.biggo.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://finance.biggo.com/news/ccfd0caa-c0c1-43f1-80a4-b1aaf6a773d4</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>15-09-2026 00:35 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Samsung, LG to pay suppliers 1.9 trillion won early ahead of Chuseok</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Aju Press</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://m.ajupress.com/amp/20260914171524025</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>14-09-2026 08:25 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>KOSPI falls for fourth session on foreign and institutional selling</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>디지털투데이</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://www.digitaltoday.co.kr/en/view/103708/kospi-falls-for-fourth-session-on-foreign-and-institutional-selling</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>15-09-2026 07:04 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Controlling Complexity In ADC Formulation Development</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Bioprocess Online</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://www.bioprocessonline.com/doc/controlling-complexity-in-adc-formulation-development-0001</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>15-09-2026 00:38 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Government Launches Korea Premium Weeks: Integrated Capital Market Event</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>chosun.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.chosun.com/english/market-money-en/2026/09/15/DSYD3II34FBQPMWS4EYZOCNMXI/</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>15-09-2026 05:46 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lupin targets $500 million biosimilar revenue in five years</t>
+          <t>Child anaemia falls to 8%, stunting to 4% in Egypt - Health - Egypt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>english.ahram.org.eg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/lupin-targets-500-million-biosimilar-revenue-in-five-years</t>
+          <t>https://english.ahram.org.eg/NewsContent/1/1236/576675/Egypt/Health/Child-anaemia-falls-to-,-stunting-to--in-Egypt.aspx</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14-09-2026 15:29 UTC</t>
+          <t>15-09-2026 09:00 UTC</t>
         </is>
       </c>
     </row>
@@ -544,49 +544,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ONYX Hospitality Group Strengthens Sustainable Hotel Operations Through Strategic Partnership with SP Group</t>
+          <t>Meche Cancels Jury Selection</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>finanzen.ch</t>
+          <t>St. Landry Now Online Newspaper</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.finanzen.ch/nachrichten/aktien/onyx-hospitality-group-strengthens-sustainable-hotel-operations-through-strategic-partnership-with-sp-group-1036545062</t>
+          <t>https://www.stlandrynow.com/community/local-news/meche-cancels-jury-selection/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15-09-2026 03:21 UTC</t>
+          <t>14-09-2026 16:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meche Cancels Jury Selection</t>
+          <t>Boehringer provides update on EASi-KIDNEY trial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Landry Now Online Newspaper</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.stlandrynow.com/community/local-news/meche-cancels-jury-selection/</t>
+          <t>https://www.boehringer-ingelheim.com/human-health/boehringer-provides-update-easi-kidney-trial</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14-09-2026 16:11 UTC</t>
+          <t>15-09-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>When Words Stay Silent: How Sign Language Avatars Are Transforming Access to Medicine</t>
+          <t>When breathlessness isn’t just ageing: Campaign urges early action on pulmonary fibrosis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CSRwire</t>
+          <t>Gulf News</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://csrwire.com/press-release/when-words-stay-silent-how-sign-language-avatars-transforming-access-medicine/</t>
+          <t>https://gulfnews.com/amp/story/uae%2Fhealth%2Fwhen-breathlessness-isnt-just-ageing-campaign-urges-early-action-on-pulmonary-fibrosis-1.500673910</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14-09-2026 14:18 UTC</t>
+          <t>15-09-2026 06:12 UTC</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Takeda R&amp;D President Andy Plump to Retire in 2027</t>
+          <t>Sugar Clinics: A One-Stop Shop for Improved Diabetes Care in Mexico</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>contractpharma.com</t>
+          <t>ACCESS Newswire</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/takeda-rd-president-andy-plump-to-retire-in-2027/</t>
+          <t>https://www.accessnewswire.com/newsroom/en/healthcare-and-pharmaceutical/sugar-clinics-a-one-stop-shop-for-improved-diabetes-care-in-mexico-1221166</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14-09-2026 14:45 UTC</t>
+          <t>15-09-2026 14:36 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When breathlessness isn’t just ageing: Campaign urges early action on pulmonary fibrosis</t>
+          <t>Genexine’s GX-BP1 (SOX2 bioPROTAC) Suppresses Tumor Regrowth despite Osimertinib and Dato-DXd Combination and Achieves 6/6 Complete Responses in Triple Combination</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gulfnews.com</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://gulfnews.com/uae/health/when-breathlessness-isnt-just-ageing-campaign-urges-early-action-on-pulmonary-fibrosis-1.500673910</t>
+          <t>https://uk.finance.yahoo.com/news/genexine-gx-bp1-sox2-bioprotac-091600149.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15-09-2026 06:12 UTC</t>
+          <t>15-09-2026 09:16 UTC</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DLG's animal nutrition unit beats expectations</t>
+          <t>Study shows how changes in prefontal brain activity can impair the ability to change behaviour</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Feed Strategy</t>
+          <t>University of Nottingham</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.feedstrategy.com/business-markets/company-news/news/15834794/dlgs-animal-nutrition-unit-beats-expectations</t>
+          <t>https://www.nottingham.ac.uk/news/study-shows-how-changes-in-prefontal-brain-activity-can-impair-the-ability-to-change-behaviour</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14-09-2026 16:03 UTC</t>
+          <t>15-09-2026 09:09 UTC</t>
         </is>
       </c>
     </row>
@@ -728,54 +728,54 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>How changes in prefrontal brain activity can impair the ability to change behavior</t>
+          <t>Khalid Yassin Top Healthcare Leaders 2026 Founders &amp; Shareholders</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Medical Xpress</t>
+          <t>Forbes Middle East</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://medicalxpress.com/news/2026-09-prefrontal-brain-impair-ability-behavior.html</t>
+          <t>https://www.forbesmiddleeast.com/lists/top-healthcare-leaders-2026-founders-shareholders/khalid-yassin/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14-09-2026 18:00 UTC</t>
+          <t>15-09-2026 02:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hikma MP says crossings were closed to stop suspects fleeing to Iran</t>
+          <t>Amgen to deploy Veeva Vault CRM globally to spe...</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>964media</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://en.964media.com/52521/</t>
+          <t>https://pluang.com/en/news-feed/biotek-terkemuka-pilih-veeva-vault-crm-global</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14-09-2026 09:35 UTC</t>
+          <t>15-09-2026 11:29 UTC</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shane Lowry Secures Record Home Victory at the 2026 Amgen Irish Open</t>
+          <t>FDA reduces monitoring time for Amgen’s Imdelltra infusions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>pharmaceutical-technology.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.amgen.com/stories/2026/09/shane-lowry-secures-record-home-victory-at-the-2026-amgen-irish-open</t>
+          <t>https://www.pharmaceutical-technology.com/news/fda-reduces-monitoring-time-amgens-imdelltra/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14-09-2026 21:47 UTC</t>
+          <t>15-09-2026 10:49 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DP World Tour highlights 2026: Amgen Irish Open, Round 3</t>
+          <t>Shane Lowry Secures Record Home Victory at the 2026 Amgen Irish Open</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Golf Channel</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.golfchannel.com/watch/dp-world-tour/dp-world-tour-highlights-2026-amgen-irish-open-round-3</t>
+          <t>https://www.amgen.com/stories/2026/09/shane-lowry-secures-record-home-victory-at-the-2026-amgen-irish-open</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14-09-2026 08:47 UTC</t>
+          <t>14-09-2026 21:47 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amgen Leads The Pack With First Filing For US Opdivo Biosimilar</t>
+          <t>Amgen to Deploy Veeva Vault CRM Globally</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/amgen-leads-the-pack-with-first-filing-for-us-opdivo-biosimilar-PD6ZNDEA2VA4XKUQ44XCXQCZHI/</t>
+          <t>https://www.marketscreener.com/news/amgen-to-deploy-veeva-vault-crm-globally-ce785bdddd89f622</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14-09-2026 10:30 UTC</t>
+          <t>15-09-2026 11:49 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Points and prize money: See what every player won at the Amgen Irish Open</t>
+          <t>Leading Biotech Selects Veeva Vault CRM Globally</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>europeantour.com</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.europeantour.com/dpworld-tour/news/articles/detail/points-and-prize-money-see-what-every-player-won-at-the-2026-amgen-irish-open/</t>
+          <t>https://www.prnewswire.com/news-releases/leading-biotech-selects-veeva-vault-crm-globally-302878548.html</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14-09-2026 09:21 UTC</t>
+          <t>15-09-2026 11:03 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amgen vs. Vertex Pharmaceuticals: Value Stability vs. High-Growth Biotech Investment Plays</t>
+          <t>Shane Lowry sinks final putt to claim historic 11-shot victory at Irish Open</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NAI500</t>
+          <t>Golf Channel</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nai500.com/blog/2026/09/amgen-vs-vertex-pharmaceuticals-value-stability-vs-high-growth-biotech-investment-plays/</t>
+          <t>https://www.golfchannel.com/watch/dp-world-tour/shane-lowry-sinks-final-putt-to-claim-historic-11-shot-victory-at-irish-open</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15-09-2026 02:47 UTC</t>
+          <t>15-09-2026 11:50 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amgen Gets FDA Approval to Reduce Monitoring Time for First Two Imdelltra Doses</t>
+          <t>AMGN Looks 4.2% Overvalued on GF Value™</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/amgen-gets-fda-approval-to-reduce-monitoring-time-for-first-two-imdelltra-doses-ce785bdcdc81f62d</t>
+          <t>https://www.gurufocus.com/news/9081551/amgn-looks-42-overvalued-on-gf-value</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14-09-2026 14:00 UTC</t>
+          <t>15-09-2026 11:47 UTC</t>
         </is>
       </c>
     </row>
@@ -949,103 +949,103 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FDA shortens monitoring time for first IMDELLTR...</t>
+          <t>Amgen vs. Vertex Pharmaceuticals: Value Stability vs. High-Growth Biotech Investment Plays</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>NAI500</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/fda-setujui-pengurangan-waktu-pemantauan-imdelltra</t>
+          <t>https://nai500.com/blog/2026/09/amgen-vs-vertex-pharmaceuticals-value-stability-vs-high-growth-biotech-investment-plays/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14-09-2026 13:19 UTC</t>
+          <t>15-09-2026 02:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Organon Announces US FDA Has Accepted for Review a Supplemental New Drug Application for MIUDELLA</t>
+          <t>BK’s Breakdowns: Shane Lowry’s winning WITB, 2026 Amgen Irish Open</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>GolfWRX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260914839018/en/Organon-Announces-US-FDA-Has-Accepted-for-Review-a-Supplemental-New-Drug-Application-for-MIUDELLA-a-Hormone-Free-Intrauterine-Device</t>
+          <t>https://golfwrx.com/786218/bks-breakdowns-shane-lowrys-winning-witb-2026-amgen-irish-open/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14-09-2026 11:30 UTC</t>
+          <t>15-09-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FDA Accepts Extended Duration sNDA for Miudella Hormone-Free IUD</t>
+          <t>FDA cuts IMDELLTRA monitoring time for first two doses</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Patient Care Online</t>
+          <t>Voice of Healthcare</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.patientcareonline.com/view/fda-accepts-extended-duration-snda-for-miudella-hormone-free-iud</t>
+          <t>https://vohnetwork.com/news/pharma/fda-reduces-monitoring-time-for-first-two-imdelltra-doses</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14-09-2026 17:57 UTC</t>
+          <t>15-09-2026 04:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sun Pharma Subsidiaries Settle US Generic Drug Pricing Antitrust Litigation For Confidential Amount</t>
+          <t>WATCH | Shane Lowry moves TEN ahead</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>europeantour.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/sun-pharma-subsidiaries-settle-us-generic-drug-pricing-antitrust-litigation-for-confidential-amount</t>
+          <t>https://www.europeantour.com/dpworld-tour/news/video/watch-shane-lowry-moves-ten-ahead/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15-09-2026 00:55 UTC</t>
+          <t>14-09-2026 17:32 UTC</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1057,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FDA accepts extended duration sNDA for MIUDELLA IUD</t>
+          <t>FDA Accepts Extended Duration sNDA for Miudella Hormone-Free IUD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Contemporary OB/GYN</t>
+          <t>Patient Care Online</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>http://www.contemporaryobgyn.net/view/fda-accepts-extended-duration-snda-miudella-iud</t>
+          <t>https://www.patientcareonline.com/view/fda-accepts-extended-duration-snda-for-miudella-hormone-free-iud</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14-09-2026 15:51 UTC</t>
+          <t>14-09-2026 17:57 UTC</t>
         </is>
       </c>
     </row>
@@ -1084,49 +1084,49 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Organon announces U.S. FDA accepted for review Sebela’s sNDA for Miudella</t>
+          <t>Sun Pharma Subsidiaries Settle US Generic Drug Pricing Antitrust Litigation For Confidential Amount</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Sahi</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/the-fly/organon-announces-u-s-fda-accepted-for-review-sebelas-snda-for-miudella-thefly-news</t>
+          <t>https://www.sahi.com/news/sun-pharma-subsidiaries-settle-us-generic-drug-pricing-antitrust-litigation-for-confidential-amount</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14-09-2026 14:59 UTC</t>
+          <t>15-09-2026 00:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>No need to buy lavender again: this cutting trick multiplies your plants</t>
+          <t>FDA accepts extended duration sNDA for MIUDELLA IUD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Futura, le média qui explore le monde</t>
+          <t>Contemporary OB/GYN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.futura-sciences.com/en/no-need-to-buy-lavender-again-this-cutting-trick-multiplies-your-plants_39379/</t>
+          <t>http://www.contemporaryobgyn.net/view/fda-accepts-extended-duration-snda-miudella-iud</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14-09-2026 12:28 UTC</t>
+          <t>14-09-2026 15:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BeautifulChinaING: Walking through Changbai Mountain for 40 years, a Chinese botanist captures 520,000 plant images and China’s changing landscape</t>
+          <t>NSF Study Aims to Reveal How Plants Sense, Respond to Heat</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>globaltimes.cn</t>
+          <t>University of Mississippi | Ole Miss</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.globaltimes.cn/page/202609/1370511.shtml</t>
+          <t>https://olemiss.edu/news/2026/09/nsf-study-aims-to-reveal-how-plants-sense-respond-to-heat/index.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14-09-2026 13:20 UTC</t>
+          <t>15-09-2026 15:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Florist Special With Bri Lovie</t>
+          <t>Automated Snack Formers Market Size, Share &amp; Forecast 2036</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>thursd.com</t>
+          <t>Fact.MR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://thursd.com/articles/florist-special-with-bri-lovie</t>
+          <t>https://www.factmr.com/report/automated-snack-formers-market</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>14-09-2026 18:48 UTC</t>
+          <t>15-09-2026 12:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What Your Jade Plant Needs in September to Stay Bright and Healthy Through Fall</t>
+          <t>Gas Turbine Report H2 2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>homesandgardens.com</t>
+          <t>Rystad Energy</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.homesandgardens.com/gardens/what-a-jade-plant-needs-in-september</t>
+          <t>https://www.rystadenergy.com/insights/gas-turbine-report-H2-2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14-09-2026 16:00 UTC</t>
+          <t>15-09-2026 08:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>London ‘plant parents’ adopt a piece of historic Barbican urban jungle</t>
+          <t>This Australian cave hid 25,000 years of ritual secrets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dawn.com</t>
+          <t>Science Daily</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.dawn.com/news/2030024</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260914102443.htm</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15-09-2026 02:33 UTC</t>
+          <t>15-09-2026 14:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Plant This Low-Maintenance Evergreen Now for a Beautiful Yard All Winter Long</t>
+          <t>How soybeans took over the American diet without anyone noticing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>House Beautiful</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.housebeautiful.com/lifestyle/gardening/a73643733/arborvitae-care-winter-landscape/</t>
+          <t>https://www.washingtonpost.com/ripple/2026/09/11/how-soybeans-took-over-the-american-diet-without-anyone-noticing/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14-09-2026 19:30 UTC</t>
+          <t>15-09-2026 13:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Almonty and the Government of Rwanda Form Strategic Tungsten Partnership</t>
+          <t>Tungsten West advances Hemerdon restart with TOMRA Mining sorting tech a key component of redesigned plant</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>International Mining</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260914171760/en/Almonty-and-the-Government-of-Rwanda-Form-Strategic-Tungsten-Partnership</t>
+          <t>https://im-mining.com/2026/09/15/tungsten-west-advances-hemerdon-restart-with-tomra-mining-sorting-tech-a-key-component-of-redesigned-plant/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14-09-2026 11:30 UTC</t>
+          <t>15-09-2026 13:16 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Witness: There’s no space in SALN form for business acquisition costs</t>
+          <t>'Plant parents' cut a piece of London's historic Barbican urban jungle</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inquirer.net</t>
+          <t>newseu.cgtn.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://newsinfo.inquirer.net/2305382/witness-theres-no-space-in-saln-form-for-business-acquisition-costs</t>
+          <t>https://newseu.cgtn.com/news/2026-09-15/-Plant-parents-cut-a-piece-of-London-s-historic-Barbican-urban-jungle-1QrqxKtw9MI/share_amp.html</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15-09-2026 04:19 UTC</t>
+          <t>15-09-2026 12:24 UTC</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Thematic Showcase: Material Form &amp; Tactile Surface</t>
+          <t>Industrial farming poses threat to fungi, small organisms vital to healthy soil – UN Decade</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mutual Art</t>
+          <t>Farmers Review Africa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.mutualart.com/Article/The-Thematic-Showcase--Material-Form---T/1ED2A4F0F98FE1F7</t>
+          <t>https://farmersreviewafrica.com/industrial-farming-poses-threat-to-fungi-small-organisms-vital-to-healthy-soil-un-decade/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>14-09-2026 14:33 UTC</t>
+          <t>15-09-2026 10:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>How soybeans took over the American diet – without anyone noticing</t>
+          <t>Beyond Meat® Announces Availability of Beyond Steak® Filet at Erewhon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cobb Courier</t>
+          <t>Beyond Meat</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://cobbcountycourier.com/2026/09/how-soybeans-took-over-the-american-diet-without-anyone-noticing/</t>
+          <t>https://investors.beyondmeat.com/news-releases/news-release-details/beyond-meatr-announces-availability-beyond-steakr-filet-erewhon</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14-09-2026 14:37 UTC</t>
+          <t>15-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bill Ferree Obituary Sep 10, 2026</t>
+          <t>Florist Special With Bri Lovie</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pugh Funeral Home</t>
+          <t>Thursd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pughfuneralhome.com/obituaries/bill-ferree</t>
+          <t>https://thursd.com/articles/florist-special-with-bri-lovie</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14-09-2026 17:43 UTC</t>
+          <t>14-09-2026 18:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hardy Mums for Minnesota Gardens: Color That Returns Every Fall</t>
+          <t>Plant This Low-Maintenance Evergreen Now for a Beautiful Yard All Winter Long</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fillmore County Journal</t>
+          <t>housebeautiful.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://fillmorecountyjournal.com/hardy-mums-for-minnesota-gardens-color-that-returns-every-fall/</t>
+          <t>https://www.housebeautiful.com/lifestyle/gardening/a73643733/arborvitae-care-winter-landscape/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14-09-2026 17:29 UTC</t>
+          <t>14-09-2026 19:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Why the EU Biotech Act must deliver practical improvements for clinical trials in Europe</t>
+          <t>Pfizer Invites Public to Listen to Webcast of Pfizer Discussion at Healthcare Conference</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>The Parliament Magazine</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.theparliamentmagazine.eu/partner/article/why-the-eu-biotech-act-must-deliver-practical-improvements-for-clinical-trials-in-europe</t>
+          <t>https://www.businesswire.com/news/home/20260915286706/en/Pfizer-Invites-Public-to-Listen-to-Webcast-of-Pfizer-Discussion-at-Healthcare-Conference</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>15-09-2026 06:55 UTC</t>
+          <t>15-09-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pfizer 52 Week Low Streak: Four-Day Breakdown Deepens</t>
+          <t>Why the EU Biotech Act must deliver practical improvements for clinical trials in Europe</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>univest.in</t>
+          <t>The Parliament Magazine</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://univest.in/blogs/why-pfizer-ltd-share-52-week-consecutive-low-2026</t>
+          <t>https://www.theparliamentmagazine.eu/partner/article/why-the-eu-biotech-act-must-deliver-practical-improvements-for-clinical-trials-in-europe</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>15-09-2026 04:51 UTC</t>
+          <t>15-09-2026 06:55 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IP Group H1 NAV Rises 3.2% as Pfizer Obesity Royalty Asset Reaches £152 Million</t>
+          <t>Pfizer 52 Week Low Streak: Four-Day Breakdown Deepens</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>univest.in</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/ip-group-h1-nav-rises-070831998.html</t>
+          <t>https://univest.in/blogs/why-pfizer-ltd-share-52-week-consecutive-low-2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>15-09-2026 07:08 UTC</t>
+          <t>15-09-2026 04:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>News | Lender doubles down on New York office conversions after Pfizer setback</t>
+          <t>IP Group eyes busy second half as Pfizer obesity investment catches the eye</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>costar.com</t>
+          <t>Proactive financial news</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.costar.com/article/1364458074/lender-doubles-down-on-new-york-office-conversions-after-pfizer-setback</t>
+          <t>https://www.proactiveinvestors.com/companies/news/1098540/ip-group-eyes-busy-second-half-as-pfizer-obesity-investment-catches-the-eye-1098540.html</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14-09-2026 23:14 UTC</t>
+          <t>15-09-2026 07:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Transcript : Pfizer Inc. Presents at Morgan Stanley 24th Annual Global Healthcare Conference, Sep-14-2026 10</t>
+          <t>News | Lender doubles down on New York office conversions after Pfizer setback</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/transcript-pfizer-inc-presents-at-morgan-stanley-24th-annual-global-healthcare-conference-sep-14-ce785bdcdf81f720</t>
+          <t>https://www.costar.com/article/1364458074/lender-doubles-down-on-new-york-office-conversions-after-pfizer-setback</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>14-09-2026 15:50 UTC</t>
+          <t>14-09-2026 23:14 UTC</t>
         </is>
       </c>
     </row>
@@ -1597,76 +1597,76 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NCCN awards grants for metastatic prostate cancer quality initiatives</t>
+          <t>IP Group H1 NAV Rises 3.2% as Pfizer Obesity Royalty Asset Reaches £152 Million</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/nccn-awards-grants-metastatic-prostate-cancer-quality-initiatives/50936962</t>
+          <t>https://uk.finance.yahoo.com/news/ip-group-h1-nav-rises-070831998.html</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>14-09-2026 17:31 UTC</t>
+          <t>15-09-2026 07:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pfizer Sets Novel Path in Fee Fight | The Wall Street Journal - newspaper</t>
+          <t>Biogen Eyes Wave of Phase III Readouts as It Expands Beyond Neuroscience</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Magzter</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.magzter.com/stories/newspaper/The-Wall-Street-Journal/PFIZER-SETS-NOVEL-PATH-IN-FEE-FIGHT</t>
+          <t>https://finance.yahoo.com/healthcare/articles/biogen-eyes-wave-phase-iii-040205385.html</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>14-09-2026 15:41 UTC</t>
+          <t>15-09-2026 04:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Association Between COVID-19 Vaccine Doses and Neurosensory Symptoms Among COVID-19-Positive Patients: A Retrospective Cross-Sectional Study</t>
+          <t>Hummingbird Bioscience Appoints Dr. James Garner as President</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cureus</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.cureus.com/articles/531853-association-between-covid-19-vaccine-doses-and-neurosensory-symptoms-among-covid-19-positive-patients-a-retrospective-cross-sectional-study?score_article=true</t>
+          <t>https://www.manilatimes.net/2026/09/15/tmt-newswire/globenewswire/hummingbird-bioscience-appoints-dr-james-garner-as-president/2425252</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>14-09-2026 16:24 UTC</t>
+          <t>15-09-2026 09:14 UTC</t>
         </is>
       </c>
     </row>
@@ -1678,157 +1678,157 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Biogen Eyes Wave of Phase III Readouts as It Expands Beyond Neuroscience</t>
+          <t>Scholar Rock Drug Wins First-in-Class Approval in Rare Neuromuscular Disease</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>MedCity News</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/biogen-eyes-wave-phase-iii-040205385.html</t>
+          <t>https://medcitynews.com/2026/09/scholar-rock-drug-wins-first-in-class-approval-in-rare-neuromuscular-disease/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>15-09-2026 04:02 UTC</t>
+          <t>14-09-2026 19:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Trump's Drug Pricing Policy Could Drive Up Prices in South Korea and Other Overseas Markets</t>
+          <t>Dr. Reddy’s Laboratories launches Nivorz in India</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/65eb6133-9aae-4a67-ac88-0eff477771bb</t>
+          <t>https://www.thehindubusinessline.com/news/dr-reddys-laboratories-launches-nivorz-in-india/article71467764.ece</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14-09-2026 10:35 UTC</t>
+          <t>15-09-2026 11:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Scholar Rock Drug Wins First-in-Class Approval in Rare Neuromuscular Disease</t>
+          <t>Dr. Reddy’s launches initiative to train India’s obesity care workforce</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MedCity News</t>
+          <t>Express Pharma</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://medcitynews.com/2026/09/scholar-rock-drug-wins-first-in-class-approval-in-rare-neuromuscular-disease/</t>
+          <t>https://www.expresspharma.in/dr-reddys-launches-initiative-to-train-indias-obesity-care-workforce/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14-09-2026 19:33 UTC</t>
+          <t>15-09-2026 05:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Scholar Rock secures first FDA approval for muscle-targeting rare disease drug</t>
+          <t>Dr Reddy’s launches Opdivo biosimilar Nivorz in India, enters immuno-oncology segment</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/fda/scholar-rock-secures-first-fda-approval-for-muscle-targeting-rare-disease-drug</t>
+          <t>https://www.moneycontrol.com/news/business/dr-reddy-s-launches-opdivo-biosimilar-nivorz-in-india-enters-immuno-oncology-segment-14030366.html/amp</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>14-09-2026 12:25 UTC</t>
+          <t>15-09-2026 12:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cape Pioneer 2026 promises fierce racing as route changes and rider numbers rise</t>
+          <t>Dr. Reddy’s launches nivolumab biosimilar NIVORZ in India</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>George Herald</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.georgeherald.com/Sport/Article/Other/cape-pioneer-2026-promises-fierce-racing-as-route-changes-and-rider-numbers-rise-202609141025</t>
+          <t>https://www.indianpharmapost.com/news/dr-reddys-launches-nivolumab-biosimilar-nivorz-in-india-21853</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>14-09-2026 08:40 UTC</t>
+          <t>15-09-2026 11:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026 Race With Soul promises fierce racing, heartfelt hospitality, and a route twist</t>
+          <t>Dr. Reddy's launches nivolumab biosimilar in India</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mosselbayadvertiser.com</t>
+          <t>economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.mosselbayadvertiser.com/Galleries/Gallery/Sport/2026-race-with-soul-promises-fierce-racing-heartfelt-hospitality-and-a-route-twist-202609141024</t>
+          <t>https://economictimes.indiatimes.com/industry/healthcare/biotech/pharmaceuticals/dr-reddys-launches-nivolumab-biosimilar-in-india/articleshow/134266368.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>14-09-2026 08:22 UTC</t>
+          <t>15-09-2026 14:05 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s To Train 5,000 Professionals In Obesity Care</t>
+          <t>Dr Reddy’s launches cancer drug biosimilar in India, targets 12 indications</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BW Healthcare World</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.bwhealthcareworld.com/article/dr-reddy-s-to-train-5-000-professionals-in-obesity-care-623671</t>
+          <t>https://www.cnbctv18.com/market/stocks/dr-reddys-launches-cancer-drug-biosimilar-in-india-targets-12-indications-19991078.htm/amp</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15-09-2026 04:27 UTC</t>
+          <t>15-09-2026 11:16 UTC</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>How Dr. Reddy’s is helping build India’s obesity workforce</t>
+          <t>Dr. Reddy’s To Train 5,000 Professionals In Obesity Care</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HR Katha</t>
+          <t>BW Healthcare World</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.hrkatha.com/news/learning-development/how-dr-reddys-is-helping-build-indias-obesity-workforce/</t>
+          <t>https://www.bwhealthcareworld.com/article/dr-reddy-s-to-train-5-000-professionals-in-obesity-care-623671</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>15-09-2026 04:28 UTC</t>
+          <t>15-09-2026 04:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dr Reddy’s launches educational initiative to strengthen obesity care workforce</t>
+          <t>Dr Reddy's Labs Q2 FY27: Results Preview</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>univest.in</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/dr-reddys-launches-educational-initiative-to-strengthen-obesity-care-workforce/article71465962.ece</t>
+          <t>https://univest.in/blogs/dr-reddys-laboratories-q2-results-fy27-preview-date-expectations</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14-09-2026 11:36 UTC</t>
+          <t>15-09-2026 05:41 UTC</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s launches nationwide programme to train 5,000+ certified obesity educators</t>
+          <t>How Dr. Reddy’s is helping build India’s obesity workforce</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>HR Katha</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/healthcare/dr-reddys-launches-nationwide-programme-to-train-5000-certified-obesity-educators-21836</t>
+          <t>https://www.hrkatha.com/news/learning-development/how-dr-reddys-is-helping-build-indias-obesity-workforce/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14-09-2026 11:04 UTC</t>
+          <t>15-09-2026 04:28 UTC</t>
         </is>
       </c>
     </row>
@@ -1948,22 +1948,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Launches Obesity Care Training Initiative</t>
+          <t>Dr. Reddy's Launches Program to Strengthen Obesity Care in India</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Voice of Healthcare</t>
+          <t>Siliconindia</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://vohnetwork.com/news/policy/dr-reddy-s-laboratories-launches-nationwide-educational-initiative-to-strengthen-india-s-obesity-care-workforce</t>
+          <t>https://www.siliconindia.com/news/dr-reddy-s-launches-program-to-strengthen-obesity-care-in-india-nwid-55454.html</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14-09-2026 12:50 UTC</t>
+          <t>15-09-2026 11:29 UTC</t>
         </is>
       </c>
     </row>
@@ -1975,130 +1975,130 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OT security cannot follow an IT playbook when cyber risk can stop production and endanger safety</t>
+          <t>Shreveport Frymaster celebrates purchase, expansion</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ET CISO</t>
+          <t>The Shreveport-Bossier City Advocate</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://ciso.economictimes.indiatimes.com/amp/news/ot-security/ot-security-cannot-follow-an-it-playbook-when-cyber-risk-can-stop-production-and-endanger-safety/134235383</t>
+          <t>https://www.shreveportbossieradvocate.com/business/more-space-lines-and-employees-at-shreveport-frymaster/article_0ca48873-0dd0-40b0-8320-c265ad5bbc8f.html</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14-09-2026 09:33 UTC</t>
+          <t>15-09-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Frymaster tour</t>
+          <t>C-CAMP National Bio Entrepreneurship Competition 2026 sees 15 startups, 4 student teams bag top honours</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>The Shreveport-Bossier City Advocate</t>
+          <t>Pharmabiz.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.shreveportbossieradvocate.com/frymaster-tour/image_aa372f6f-387d-4d0e-a194-58000e9a9a05.html</t>
+          <t>https://www.pharmabiz.com/NewsDetails.aspx?aid=190587&amp;sid=2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14-09-2026 22:31 UTC</t>
+          <t>15-09-2026 10:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Glendiay Brown, Frymaster2</t>
+          <t>15 startups, 4 student teams win C-CAMP National Bio Entrepreneurship Competition 2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>The Shreveport-Bossier City Advocate</t>
+          <t>Express Pharma</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.shreveportbossieradvocate.com/glendiay-brown-frymaster2/image_b8ef3f4a-6b3c-49ed-bfc7-05bf6a12971e.html</t>
+          <t>https://www.expresspharma.in/amp/15-startups-4-student-teams-win-c-camp-national-bio-entrepreneurship-competition-2026/</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>14-09-2026 19:53 UTC</t>
+          <t>15-09-2026 07:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Glen Brown Frymaster</t>
+          <t>Shobiz CEO Sameer Tobaccowala on How Audience Expectations Are Changing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>The Shreveport-Bossier City Advocate</t>
+          <t>storyboard18.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.shreveportbossieradvocate.com/glen-brown-frymaster/image_f5009e63-6ef9-490e-a1ae-9e7c370ec0a5.html</t>
+          <t>https://www.storyboard18.com/videos/brand-marketing/shobiz-ceo-sameer-tobaccowala-on-how-audience-expectations-are-changing-110689.htm</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>14-09-2026 19:37 UTC</t>
+          <t>15-09-2026 06:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Reports FDA Records Assessment at Mexican API Plant Concluding with Two Observations</t>
+          <t>Free Cancer Screening cum Health Camp held at Phesama</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Nagaland Post</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/dr-reddys-reports-fda-records-assessment-at-mexican-api-plant-concluding-with-two-observations</t>
+          <t>https://nagalandpost.com/free-cancer-screening-cum-health-camp-held-at-phesama/</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14-09-2026 11:12 UTC</t>
+          <t>15-09-2026 05:18 UTC</t>
         </is>
       </c>
     </row>
@@ -2110,184 +2110,184 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shobiz CEO Sameer Tobaccowala on How Audience Expectations Are Changing</t>
+          <t>275 register for free health camp in Phesama</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Storyboard18</t>
+          <t>Eastern Mirror</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.storyboard18.com/videos/brand-marketing/shobiz-ceo-sameer-tobaccowala-on-how-audience-expectations-are-changing-110689.htm</t>
+          <t>https://www.easternmirrornagaland.com/275-register-for-free-health-camp-in-phesama</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>15-09-2026 06:00 UTC</t>
+          <t>14-09-2026 17:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AI is changing cyberattacks from automated to adaptive; SOCs must respond at the same speed</t>
+          <t>Aurobindo Pharma wins U.S. FDA approval for generic asthma inhaler</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ET CISO</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://ciso.economictimes.indiatimes.com/news/corporate/ai-is-changing-cyberattacks-from-automated-to-adaptive-socs-must-respond-at-the-same-speed/134235124</t>
+          <t>https://www.thehindu.com/business/Industry/aurobindo-pharma-wins-us-fda-approval-for-generic-asthma-inhaler/article71469168.ece</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>14-09-2026 09:30 UTC</t>
+          <t>15-09-2026 15:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Russian forces strike BaDM warehouse in fourth attack on pharma distributor in two weeks</t>
+          <t>Aurobindo Pharma Gains USFDA Approval for Inhalation Aerosol in $301 Million Market</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>english.nv.ua</t>
+          <t>Sahi</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://english.nv.ua/business/russian-attack-hits-badm-warehouse-marking-fourth-hit-on-top-pharma-company-in-two-weeks-50641173.html</t>
+          <t>https://www.sahi.com/news/aurobindo-pharma-unit-iv-api-facility-concludes-us-fda-inspection-with-zero-observations</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>14-09-2026 09:04 UTC</t>
+          <t>15-09-2026 14:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Free Cancer Screening cum Health Camp held at Phesama</t>
+          <t>Aurobindo Pharma US FDA inspection at Telangana API facility concludes with 1 procedural observation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nagaland Post</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://nagalandpost.com/free-cancer-screening-cum-health-camp-held-at-phesama/</t>
+          <t>https://www.cnbctv18.com/business/companies/aurobindo-pharma-us-fda-inspection-at-telangana-api-facility-concludes-with-1-procedural-observation-19991204.htm</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>15-09-2026 05:18 UTC</t>
+          <t>15-09-2026 14:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>275 register for free cancer screening, health camp at Phesama</t>
+          <t>Aurobindo Pharma Gets First USFDA Nod For First Metered-Dose Inhaler</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MorungExpress</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://morungexpress.com/275-register-for-free-cancer-screening-health-camp-at-phesama</t>
+          <t>https://www.ndtvprofit.com/business/aurobindo-pharma-gets-first-usfda-nod-for-first-metered-dose-inhaler-12049337</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>14-09-2026 15:55 UTC</t>
+          <t>15-09-2026 12:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>275 register for free health camp in Phesama</t>
+          <t>Aurobindo Pharma receives US FDA nod for metered Beclomethasone Dipropionate aerosol</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eastern Mirror</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.easternmirrornagaland.com/275-register-for-free-health-camp-in-phesama</t>
+          <t>https://www.business-standard.com/markets/capital-market-news/aurobindo-pharma-receives-us-fda-nod-for-metered-beclomethasone-dipropionate-aerosol-126091500592_1.html</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14-09-2026 17:13 UTC</t>
+          <t>15-09-2026 09:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Korea Exchange: வர்த்தக நேரத்தை நீட்டித்த கொரியா! இந்தியா எடுக்கப்போகும் முடிவு என்ன?</t>
+          <t>Aurobindo Pharma’s Unit IV Clears USFDA Inspection: Shares Down</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>equitypandit.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/news/Tamil/sebiexchange/Korea-Exchange-Extends-Trading-Hours-India-Sticks-to-Current-Clock/6aa80c9075fe79b492e69e89</t>
+          <t>https://www.equitypandit.com/aurobindo-pharmas-unit-iv-clears-usfda-inspection-shares-down/</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14-09-2026 15:02 UTC</t>
+          <t>15-09-2026 07:32 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Unit-IV API Facility Concludes US FDA Inspection With Zero Observations</t>
+          <t>Aurobindo Pharma gets USFDA approval for Beclomethasone HFA aerosol</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/aurobindo-pharma-unit-iv-api-facility-concludes-us-fda-inspection-with-zero-observations</t>
+          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-gets-usfda-nod-beclomethasone-hfa-aerosol/51004109</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15-09-2026 00:55 UTC</t>
+          <t>15-09-2026 08:08 UTC</t>
         </is>
       </c>
     </row>
@@ -2326,22 +2326,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Piramal Pharma UK Facility Gets 7 US FDA Observations</t>
+          <t>U.S. FDA issues observation to Aurobindo Pharma arm’s API unit</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/amp/news/market/piramal-pharma-uk-facility-gets-7-us-fda-observations/54335420260914</t>
+          <t>https://www.thehindu.com/business/Industry/us-fda-issues-observation-to-aurobindo-pharma-arms-api-unit/article71469185.ece</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14-09-2026 16:46 UTC</t>
+          <t>15-09-2026 15:14 UTC</t>
         </is>
       </c>
     </row>
@@ -2353,22 +2353,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma secures USFDA approval for Beclomethasone Dipropionate HFA Inhalation Aerosol</t>
+          <t>Aurobindo Pharma gets USFDA approval for generic inhalation aerosol for asthma patients</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://businessupturn.com/business/aurobindo-pharma-secures-usfda-approval-for-beclomethasone-dipropionate-hfa-inhalation-aerosol/</t>
+          <t>https://www.thehindubusinessline.com/companies/aurobindo-pharma-gets-usfda-approval-for-generic-inhalation-aerosol-for-asthma-patients/article71467611.ece/amp/</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>15-09-2026 07:45 UTC</t>
+          <t>15-09-2026 10:36 UTC</t>
         </is>
       </c>
     </row>
@@ -2380,22 +2380,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Wins USFDA Nod for First Inhaler, Targeting $301 Million Asthma Market</t>
+          <t>Aurobindo Pharma receives USFDA approval for Beclomethasone Dipropionate HFA Inhalation Aerosol</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/aurobindo-pharma-wins-usfda-nod-for-first-inhaler-targeting-301-million-asthma-market</t>
+          <t>https://www.business-standard.com/markets/capital-market-news/aurobindo-pharma-receives-usfda-approval-for-beclomethasone-dipropionate-hfa-inhalation-aerosol-126091500646_1.html</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>15-09-2026 08:02 UTC</t>
+          <t>15-09-2026 09:46 UTC</t>
         </is>
       </c>
     </row>
@@ -2429,27 +2429,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Samsung Launches Galaxy S26 FE in India, Bringing Flagship Camera, Galaxy AI and Powerful Performance</t>
+          <t>Functional labels with integrated gas barrier reduce oxygen ingress into COC syringes</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Manufacturing Chemist</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/in/samsung-launches-galaxy-s26-fe-in-india-bringing-flagship-camera-galaxy-ai-and-powerful-performance</t>
+          <t>https://manufacturingchemist.com/functional-labels-with-integrated-gas-barrier-reduce-oxygen</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>14-09-2026 11:16 UTC</t>
+          <t>15-09-2026 12:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2461,22 +2461,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Samsung's India public policy chief resigns, sources say</t>
+          <t>The Samsung Galaxy A18 4G launches with a new chipset, IP64 rating and a notch - GSMArena.com news</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>cfo.economictimes.indiatimes.com</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://cfo.economictimes.indiatimes.com/news/leadership/samsungs-india-public-policy-chief-resigns-sources-say/134255191</t>
+          <t>https://www.gsmarena.com/the_samsung_galaxy_a18_4g_launches_with_a_new_chipset_ip64_rating_and_a_notch-news-74622.php</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>15-09-2026 07:30 UTC</t>
+          <t>15-09-2026 11:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Samsung SDS Becomes Korea’s First Select Tier Partner in Anthropic’s Claude Partner Network</t>
+          <t>Samsung's India public policy chief Rajiv Aggarwal resigns</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Samsung SDS America</t>
+          <t>electronics.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.samsungsds.com/en/news/1295381_5252.html</t>
+          <t>http://electronics.economictimes.indiatimes.com/news/consumer-electronics/samsungs-india-public-policy-chief-rajiv-aggarwal-resigns/134254973</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>15-09-2026 06:10 UTC</t>
+          <t>15-09-2026 13:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2515,22 +2515,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max vs. Samsung Galaxy S26 Ultra: Battle of the flagships</t>
+          <t>Samsung Galaxy S25 gets cheaper: Know the deal</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://mashable.com/tech/iphone-18-pro-max-vs-galaxy-s26-ultra-price-specs</t>
+          <t>https://www.indiatoday.in/visualstories/technology/samsung-galaxy-s25-gets-cheaper-know-the-deal-285748-15-09-2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>14-09-2026 17:30 UTC</t>
+          <t>15-09-2026 13:39 UTC</t>
         </is>
       </c>
     </row>
@@ -2542,22 +2542,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Tab S12 Series Will Reportedly Launch Early Next Month: Expected Specifications</t>
+          <t>Samsung opens Galaxy A25 One UI 9.0 beta program</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/tablets/news/samsung-galaxy-tab-s12-series-launch-date-tipped-specifications-features-12047802</t>
+          <t>https://www.sammobile.com/news/samsung-opens-galaxy-a25-one-ui-9-0-beta-program/</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>15-09-2026 05:43 UTC</t>
+          <t>15-09-2026 12:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2569,22 +2569,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Samsung faces local hedge fund's push to cancel preferred shares</t>
+          <t>6 Samsung phone apps you've probably never heard of, but should download today</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>MakeUseOf</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/samsung-faces-local-hedge-fund-s-push-to-cancel-preferred-shares-14029825.html</t>
+          <t>https://www.makeuseof.com/samsung-phone-apps-you-should-download/</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>15-09-2026 02:24 UTC</t>
+          <t>15-09-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,22 +2596,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Samsung's India public policy chief Rajiv ‌Aggarwal resigns, sources say</t>
+          <t>Samsung Leads $230 Mn Funding for European Chip Co EUCLYD Amid Memory Shortage</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>analyticsindiamag.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/info-tech/samsungs-india-public-policy-chief-rajiv-aggarwal-resigns-sources-say/article71466989.ece</t>
+          <t>https://analyticsindiamag.com/ai-news/samsung-leads-230-mn-funding-for-european-chip-co-euclyd-amid-memory-shortage</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>15-09-2026 07:33 UTC</t>
+          <t>15-09-2026 08:38 UTC</t>
         </is>
       </c>
     </row>
@@ -2623,22 +2623,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Samsung India public policy chief Rajiv ​Aggarwal steps down: Reports</t>
+          <t>Samsung Galaxy Z Fold 8 versus iPhone Duo: Nvidia chief Jensen Huang and Apple's John Ternus flaunt foldables</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Exchange4Media</t>
+          <t>t2online.in</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/people-movement-news/samsung-india-public-policy-chief-rajiv-aggarwal-steps-down-reports-158245.html</t>
+          <t>https://t2online.in/tech/tech-news/samsung-galaxy-z-fold-8-versus-iphone-duo--nvidia-chief-jensen-huang-and-apple-s-john-ternus-flaunt-foldables/2008020</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>15-09-2026 07:03 UTC</t>
+          <t>15-09-2026 09:17 UTC</t>
         </is>
       </c>
     </row>
@@ -2650,22 +2650,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Samsung quietly makes the Galaxy A08 official with a bigger battery - GSMArena.com news</t>
+          <t>Samsung's India public policy chief resigns, sources say</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.gsmarena.com/samsung_quietly_makes_the_galaxy_a08_official_with_a_bigger_battery-news-74614.php</t>
+          <t>https://www.reuters.com/world/asia-pacific/samsungs-india-public-policy-chief-resigns-sources-say-2026-09-15/</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>15-09-2026 07:31 UTC</t>
+          <t>15-09-2026 06:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2677,22 +2677,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Samsung India public affairs head Rajiv Aggarwal resigns after nearly four years</t>
+          <t>What Samsung's investment in Euclyd says about Europe's dominance</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>IO+</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/business/companies/samsung-india-public-affairs-head-rajiv-aggarwal-resigns-19990859.htm</t>
+          <t>https://ioplus.nl/en/posts/what-samsungs-investment-in-euclyd-says-about-europes-dominance</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>15-09-2026 08:01 UTC</t>
+          <t>15-09-2026 12:33 UTC</t>
         </is>
       </c>
     </row>
@@ -2704,22 +2704,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Samsung brings Galaxy S26 FE to India</t>
+          <t>Samsung Galaxy A08 with 6000mAh battery announced</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Telecompaper</t>
+          <t>FoneArena.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.telecompaper.com/news/samsung-brings-galaxy-s26-fe-to-india--1582648</t>
+          <t>https://www.fonearena.com/blog/492318/samsung-galaxy-a08-price-specifications.html</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>15-09-2026 02:44 UTC</t>
+          <t>15-09-2026 11:13 UTC</t>
         </is>
       </c>
     </row>
@@ -2731,22 +2731,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Samsung invests in Nvidia rival: Dutch AI chip startup gets $230 million funding as quest for alternatives grow</t>
+          <t>Verizon and Samsung trial AI-native ISAC sensing on vRAN</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>Telecoms Tech News</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/companies/news/samsung-invests-in-nvidia-rival-dutch-ai-chip-startup-euclyd-gets-230-million-funding-as-quest-for-alternatives-grow-11789444181041.html</t>
+          <t>https://www.telecomstechnews.com/news/verizon-samsung-trial-ai-native-isac-sensing-on-vran/</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>15-09-2026 05:20 UTC</t>
+          <t>15-09-2026 14:42 UTC</t>
         </is>
       </c>
     </row>
@@ -2758,22 +2758,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Samsung is about to make everyone's phones more expensive</t>
+          <t>Galaxy A18 Launches in Europe With Six Years of Updates</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>AndroidPure</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/samsung-is-about-to-make-everyones-phones-more-expensive/</t>
+          <t>https://www.androidpure.com/galaxy-a18-europe-launch-six-years-updates/</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>15-09-2026 07:30 UTC</t>
+          <t>15-09-2026 15:10 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S27 Ultra Tipped to Feature M16 OLED Panels; May Prioritise Privacy Over Brightness</t>
+          <t>Samsung Galaxy A18 Price and Specifications Reportedly Leaked Again Ahead of Expected Launch</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2795,66 +2795,66 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s27-ultra-pro-m16-oled-panels-privacy-display-feature-leak-12047803</t>
+          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-a18-4g-price-expected-specifications-leak-12048574</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15-09-2026 05:42 UTC</t>
+          <t>15-09-2026 09:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Celltrion files for US phase 4 trial of 240 mg Zymfentra dose</t>
+          <t>I spent hours digging through obscure Samsung Galaxy features, and these 4 deserve more attention</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>How-To Geek</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33176</t>
+          <t>https://www.howtogeek.com/i-spent-hours-digging-through-obscure-samsung-galaxy-features-these-4-deserve-more-attention/</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>15-09-2026 04:58 UTC</t>
+          <t>15-09-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Celltrion Launches US Zymfentra High-Dose Trial</t>
+          <t>Samsung opens registrations for 6th edition of Solve for Tomorrow: high school students invited to turn ideas into solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>Business Review</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=276960</t>
+          <t>https://business-review.eu/education/samsung-opens-registrations-for-6th-edition-of-solve-for-tomorrow-high-school-students-invited-to-turn-ideas-into-solutions-300479</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>15-09-2026 03:11 UTC</t>
+          <t>15-09-2026 14:37 UTC</t>
         </is>
       </c>
     </row>
@@ -2866,22 +2866,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Celltrion is launching phase 4 clinical trials in the U.S. to secure the basis for the high dose of</t>
+          <t>Celltrion files for US phase 4 trial of 240 mg Zymfentra dose</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/en/it/12152917</t>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33176</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>15-09-2026 01:43 UTC</t>
+          <t>15-09-2026 05:33 UTC</t>
         </is>
       </c>
     </row>
@@ -2893,22 +2893,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Celltrion Moves to Expand Zymfentra Use in the U.S. With New Phase 4 Trial</t>
+          <t>South Korea's Celltrion Initiates U.S. Phase 4 Trial for High-Dose 240mg Zymfentra, Expanding Prescribing Options</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>koreaittimes.com</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.koreaittimes.com/news/articleView.html?idxno=157163</t>
+          <t>https://finance.biggo.com/news/5d004363-4793-483d-96a1-283277b01391</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>15-09-2026 01:25 UTC</t>
+          <t>15-09-2026 02:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Celltrion Advances High-Dose Clinical Trial for "Zymfentra" to Broaden U.S. Prescription Base</t>
+          <t>Celltrion Launches US Zymfentra High-Dose Trial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026091509285390683</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=276960</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>15-09-2026 00:28 UTC</t>
+          <t>15-09-2026 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2947,103 +2947,103 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Chong Kun Dang Joins the SC Conversion Race... IP Competition Heats Up</t>
+          <t>Celltrion is launching phase 4 clinical trials in the U.S. to secure the basis for the high dose of</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026091507340241619</t>
+          <t>https://www.mk.co.kr/en/it/12152917</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>15-09-2026 01:35 UTC</t>
+          <t>15-09-2026 01:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Prestige BioPharma Calls Shareholder Meeting to Refresh Board and Expand Capital-Raising Powers</t>
+          <t>Celltrion Moves to Expand Zymfentra Use in the U.S. With New Phase 4 Trial</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>koreaittimes.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/prestige-biopharma-calls-shareholder-meeting-to-refresh-board-and-expand-capital-raising-powers</t>
+          <t>https://www.koreaittimes.com/news/articleView.html?idxno=157163</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14-09-2026 09:16 UTC</t>
+          <t>15-09-2026 01:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Enhertu Shows Six-Month PFS Gain In HER2-Mutant Lung Cancer</t>
+          <t>Celltrion Advances High-Dose Clinical Trial for "Zymfentra" to Broaden U.S. Prescription Base</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BW Healthcare World</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.bwhealthcareworld.com/article/enhertu-shows-six-month-pfs-gain-in-her2-mutant-lung-cancer-623644</t>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026091509285390683</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>15-09-2026 04:27 UTC</t>
+          <t>15-09-2026 00:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Enhertu EU Milestone And Legal Win Might Change The Case For Investing In Daiichi Sankyo (TSE:4568)</t>
+          <t>Chong Kun Dang Joins the SC Conversion Race... IP Competition Heats Up</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/enhertu-eu-milestone-legal-win-151207313.html</t>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026091507340241619</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>14-09-2026 15:12 UTC</t>
+          <t>15-09-2026 01:35 UTC</t>
         </is>
       </c>
     </row>
@@ -3055,22 +3055,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WCLC26: Enhertu's PFS lung cancer win comes with an OS question mark</t>
+          <t>Daiichi Sankyo Company (TSE:4568) Could Be 31% Below Fair Value As Legal Risk Clears</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7990485</t>
+          <t>https://sg.finance.yahoo.com/news/daiichi-sankyo-company-tse-4568-181153944.html</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14-09-2026 22:36 UTC</t>
+          <t>14-09-2026 18:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3082,22 +3082,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Enhertu Phase III win supports first-line expansion in HER2-mutant NSCLC</t>
+          <t>Enhertu Shows Six-Month PFS Gain In HER2-Mutant Lung Cancer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AllSci</t>
+          <t>BW Healthcare World</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://allsci.com/news/clinical-trials/her2-mutant-lung-cancer-enhertu-cuts-progression/</t>
+          <t>https://www.bwhealthcareworld.com/article/enhertu-shows-six-month-pfs-gain-in-her2-mutant-lung-cancer-623644</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>14-09-2026 11:44 UTC</t>
+          <t>15-09-2026 04:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3109,22 +3109,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Roche, MediLink notch phase 3 lung cancer win but trail GSK on cross-trial survival</t>
+          <t>WCLC26: Enhertu's PFS lung cancer win comes with an OS question mark</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fierce Biotech</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.fiercebiotech.com/biotech/roche-and-medilink-notch-phase-3-lung-cancer-win-trail-gsk-cross-trial-survival</t>
+          <t>https://firstwordpharma.com/story/7990485</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>14-09-2026 09:50 UTC</t>
+          <t>14-09-2026 22:36 UTC</t>
         </is>
       </c>
     </row>
@@ -3136,22 +3136,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Trastuzumab Deruxtecan Improves PFS in First-Line HER2-Mutant NSCLC in DESTINY-Lung04</t>
+          <t>China approves third medical device standard for brain-computer interfaces</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Oncodaily</t>
+          <t>Medical Buyer</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://oncodaily.com/trial-updates/trastuzumab-deruxtecan-585631</t>
+          <t>https://medicalbuyer.co.in/china-approves-third-medical-device-standard-for-brain-computer-interfaces/</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>14-09-2026 09:36 UTC</t>
+          <t>15-09-2026 02:23 UTC</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>14-09-2026 13:24 UTC</t>
+          <t>14-09-2026 19:17 UTC</t>
         </is>
       </c>
     </row>
@@ -3190,22 +3190,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>China phase III trials make case for B7-H3 ADCs in relapsed SCLC</t>
+          <t>BioNTech's Gotistobart Nearly Doubles Survival in Tough-to-Treat Lung Cancer</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BioWorld News</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.bioworld.com/articles/734038-china-phase-iii-trials-make-case-for-b7-h3-adcs-in-relapsed-sclc</t>
+          <t>https://finance.biggo.com/news/58aacd1d-d012-4a4c-ada4-4c419a170566</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>14-09-2026 16:00 UTC</t>
+          <t>14-09-2026 18:38 UTC</t>
         </is>
       </c>
     </row>
@@ -3217,184 +3217,184 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AstraZeneca's Etcamah misses primary goal in breast cancer trial</t>
+          <t>Evoke-03’s miss raises bar for TROP2 ADCs in front-line NSCLC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NewsBytes</t>
+          <t>bioworld.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.newsbytesapp.com/news/business/astrazenecas-etcamah-misses-primary-goal-in-breast-cancer-trial/tldr</t>
+          <t>https://www.bioworld.com/articles/734037-evoke-03s-miss-raises-bar-for-trop2-adcs-in-front-line-nsclc</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>14-09-2026 15:39 UTC</t>
+          <t>14-09-2026 16:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>[No. 243] Kenji Hagiwara</t>
+          <t>Remedy Plan Therapeutics Announces Multiple Development and Corporate Milestones as First-In-Class Hyperbolic NAMPT Inhibitor, RPT1G, Advances in Phase 1 Dose Escalation Trial in AML/MDS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>keio.ac.jp</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.keio.ac.jp/en/st/campus-life/alumni_relay/2609/</t>
+          <t>https://www.manilatimes.net/2026/09/15/tmt-newswire/globenewswire/remedy-plan-therapeutics-announces-multiple-development-and-corporate-milestones-as-first-in-class-hyperbolic-nampt-inhibitor-rpt1g-advances-in-phase-1-dose-escalation-trial-in-amlmds/2425375</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15-09-2026 03:41 UTC</t>
+          <t>15-09-2026 11:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Amgen vs. Vertex Pharmaceuticals: Value Stability vs. High-Growth Biotech Investment Plays</t>
+          <t>China phase III trials make case for B7-H3 ADCs in relapsed SCLC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NAI500</t>
+          <t>bioworld.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://nai500.com/blog/2026/09/amgen-vs-vertex-pharmaceuticals-value-stability-vs-high-growth-biotech-investment-plays/</t>
+          <t>https://www.bioworld.com/articles/734038-china-phase-iii-trials-make-case-for-b7-h3-adcs-in-relapsed-sclc</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>15-09-2026 02:47 UTC</t>
+          <t>14-09-2026 16:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Perfect Pitch: Inside the scheme that gets junior lawyers selling to clients</t>
+          <t>Exploring Daiichi Sankyo UK’s Impact on Cardiovascular and Oncology Care</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Life Sciences IP Review</t>
+          <t>NewsHub.co.uk</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.lifesciencesipreview.com/regulation-and-industry/perfect-pitch-inside-the-scheme-that-gets-junior-lawyers-selling-to-clients</t>
+          <t>https://www.newshub.co.uk/automotive/2026/09/15/exploring-daiichi-sankyo-uks-impact-on-cardiovascular-and-oncology-care/</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>14-09-2026 15:11 UTC</t>
+          <t>15-09-2026 08:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AbelZeta Receives FDA IND Clearance for Phase 1b/2 Clinical Trial of C-CAR168 in Progressive Multiple Sclerosis</t>
+          <t>Crystalline Amino Acids Market To 2035: Feed Demand and High-Purity Grades Drive Growth - News and Statistics</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/abelzeta-receives-fda-ind-clearance-for-phase-1b2-clinical-trial-of-c-car168-in-progressive-multiple-sclerosis-302877555.html</t>
+          <t>https://www.indexbox.io/blog/crystalline-amino-acids-market-forecast-to-2035-demand-accelerates-on-animal-protein-expansion-and-specialty-grade-uptake/</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>14-09-2026 11:30 UTC</t>
+          <t>15-09-2026 11:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc. Announces Changes to Board of Directors</t>
+          <t>[No. 243] Kenji Hagiwara</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>keio.ac.jp</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.manilatimes.net/2026/09/14/tmt-newswire/globenewswire/total-energy-services-inc-announces-changes-to-board-of-directors/2424520/amp</t>
+          <t>https://www.keio.ac.jp/en/st/campus-life/alumni_relay/2609/</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>14-09-2026 12:17 UTC</t>
+          <t>15-09-2026 03:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FACT CHECK: Mike Rogers Repeatedly Voted for Higher Prescription Drug Costs and Healthcare Premiums for Michiganders</t>
+          <t>Amgen vs. Vertex Pharmaceuticals: Value Stability vs. High-Growth Biotech Investment Plays</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Michigan Democratic Party</t>
+          <t>NAI500</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://michigandems.com/fact-check-mike-rogers-repeatedly-voted-for-higher-prescription-drug-costs-and-healthcare-premiums-for-michiganders/</t>
+          <t>https://nai500.com/blog/2026/09/amgen-vs-vertex-pharmaceuticals-value-stability-vs-high-growth-biotech-investment-plays/</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>14-09-2026 21:05 UTC</t>
+          <t>15-09-2026 02:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3406,238 +3406,238 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GSK Pharma Shareholders Approve Board and Managing Director Appointments via Postal Ballot</t>
+          <t>NIRF Pharmacy Ranking 2026; Check Top Pharmacy Colleges List</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Shiksha.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/gsk-pharma-shareholders-approve-board-and-managing-director-appointments-via-postal-ballot</t>
+          <t>https://www.shiksha.com/medicine-health-sciences/articles/nirf-pharmacy-ranking-2026-check-top-pharmacy-colleges-list-blogId-241927</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>15-09-2026 08:02 UTC</t>
+          <t>15-09-2026 11:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Alto Ingredients, Inc. to Participate in the H.C. Wainwright 28th Annual Global Investment Conference</t>
+          <t>GSK Pharma shareholders approve Karine Natland appointment as non-executive director</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/alto-ingredients-inc-participate-h-123000655.html</t>
+          <t>https://scanx.trade/stock-market-news/companies/gsk-pharma-shareholders-approve-karine-natland-appointment-non/51003377</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>14-09-2026 12:30 UTC</t>
+          <t>15-09-2026 07:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>We're turning into a more innovative company: Teva Pharmaceuticals CEO Richard Francis</t>
+          <t>Contineum Thera down after depression drug miss</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/video/2026/09/14/were-turning-into-a-more-innovative-company-teva-pharmaceuticals-ceo-richard-francis.html</t>
+          <t>https://www.thepharmaletter.com/biotech-news/contineum-thera-down-after-depression-drug-miss</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>14-09-2026 18:58 UTC</t>
+          <t>15-09-2026 08:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Teva Pharmaceuticals Sees Pivot to Growth Accelerating on Branded Drugs, Biosimilars</t>
+          <t>FACT CHECK: Mike Rogers Repeatedly Voted for Higher Prescription Drug Costs and Healthcare Premiums for Michiganders</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Michigan Democratic Party</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/teva-pharmaceuticals-sees-pivot-growth-140227795.html</t>
+          <t>https://michigandems.com/fact-check-mike-rogers-repeatedly-voted-for-higher-prescription-drug-costs-and-healthcare-premiums-for-michiganders/</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>14-09-2026 14:02 UTC</t>
+          <t>14-09-2026 21:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Pearce IP BioBlast® for the fortnight ending 11 September 2026</t>
+          <t>GSK Pharma Shareholders Approve Board and Managing Director Appointments via Postal Ballot</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Pearce IP</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://www.pearceip.law/2026/09/15/pearce-ip-bioblast-for-the-fortnight-ending-11-september-2026/</t>
+          <t>https://www.tipranks.com/news/company-announcements/gsk-pharma-shareholders-approve-board-and-managing-director-appointments-via-postal-ballot</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>15-09-2026 05:30 UTC</t>
+          <t>15-09-2026 08:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lupin targets $500 million biosimilar revenue in five years</t>
+          <t>Leading Biotech Selects Veeva Vault CRM Globally</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/lupin-targets-500-million-biosimilar-revenue-in-five-years</t>
+          <t>https://uk.finance.yahoo.com/news/leading-biotech-selects-veeva-vault-110300562.html</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>14-09-2026 15:29 UTC</t>
+          <t>15-09-2026 11:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Coultreon Biopharma Appoints Nate Massari as Chief Business Officer</t>
+          <t>Delhi HC orders tax dept to refund ₹783 cr to Teva Israel over Ranbaxy payment</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/coultreon-biopharma-appoints-nate-massari-130000693.html</t>
+          <t>https://www.livemint.com/companies/delhi-hc-tax-refund-to-teva-israel-ranbaxy-sun-pharma-income-tax-india-11789467986662.html</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>14-09-2026 13:00 UTC</t>
+          <t>15-09-2026 11:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Samsung, Hyundai, LG Advance Payments to Suppliers Ahead of Chuseok</t>
+          <t>We're turning into a more innovative company: Teva Pharmaceuticals CEO Richard Francis</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>chosun.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/english/industry-en/2026/09/14/GWXBHH6C7VAIHLLINZIJCGKADU/</t>
+          <t>https://www.cnbc.com/video/2026/09/14/were-turning-into-a-more-innovative-company-teva-pharmaceuticals-ceo-richard-francis.html</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>14-09-2026 09:32 UTC</t>
+          <t>14-09-2026 18:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Chong Kun Dang Joins the SC Conversion Race... IP Competition Heats Up</t>
+          <t>Tue: Enlight leads TASE lower - Globes</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Globes - Israel Business News</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026091507340241619</t>
+          <t>https://en.globes.co.il/en/article-tue-enlight-leads-tase-lower-1001555561</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>15-09-2026 01:35 UTC</t>
+          <t>15-09-2026 15:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3649,22 +3649,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Pfizer loses patent case over Enbrel generic</t>
+          <t>Pearce IP BioBlast® for the fortnight ending 11 September 2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lawyerly</t>
+          <t>Pearce IP</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://www.lawyerly.com.au/pfizer-loses-patent-case-over-enbrel-generic/</t>
+          <t>https://www.pearceip.law/2026/09/15/pearce-ip-bioblast-for-the-fortnight-ending-11-september-2026/</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>15-09-2026 07:27 UTC</t>
+          <t>15-09-2026 05:30 UTC</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>KRTL Biotech Appoints Federal Controlled-Substance Compliance Specialist Justin Abril as President-Designate</t>
+          <t>Avaí Bio and Austrianova Complete Adventitious Agent Testing of Master Cell Bank, Establish Working Cell Bank for α-Klotho Anti-Aging Therapy</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/krtl-biotech-appoints-federal-controlled-130000493.html</t>
+          <t>https://sg.finance.yahoo.com/news/ava-bio-austrianova-complete-adventitious-124500596.html</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>14-09-2026 13:00 UTC</t>
+          <t>15-09-2026 12:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3703,76 +3703,76 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SleepRes Receives Frost &amp; Sullivan's 2026 North America New Product Innovation Recognition for Excellence in Positive Airway Pressure Device Innovation</t>
+          <t>Chong Kun Dang Joins the SC Conversion Race... IP Competition Heats Up</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/sleepres-receives-frost-sullivans-2026-130000178.html</t>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026091507340241619</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>14-09-2026 13:00 UTC</t>
+          <t>15-09-2026 01:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Perfect Pitch: Inside the scheme that gets junior lawyers selling to clients</t>
+          <t>Pfizer loses patent case over Enbrel generic</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Life Sciences IP Review</t>
+          <t>Lawyerly</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://www.lifesciencesipreview.com/regulation-and-industry/perfect-pitch-inside-the-scheme-that-gets-junior-lawyers-selling-to-clients</t>
+          <t>https://www.lawyerly.com.au/pfizer-loses-patent-case-over-enbrel-generic/</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>14-09-2026 15:11 UTC</t>
+          <t>15-09-2026 07:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Samsung Biologics signs USD 262 million manufacturing agreement with European pharmaceutical company</t>
+          <t>Local Dispensary Named "Best in Central Illinois" for Third Straight Year</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Drug Discovery News</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://www.drugdiscoverynews.com/samsung-biologics-signs-usd-262-million-manufacturing-agreement-with-european-pharmaceutical-company-17527</t>
+          <t>https://sg.finance.yahoo.com/news/local-dispensary-named-best-central-100000166.html</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>14-09-2026 19:48 UTC</t>
+          <t>15-09-2026 10:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3784,22 +3784,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>An Integrated Analytical Approach To Lipase Risk Management In Biologics Development</t>
+          <t>Samsung Biologics signs USD 262 million manufacturing agreement with European pharmaceutical company</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bioprocess Online</t>
+          <t>Drug Discovery News</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://www.bioprocessonline.com/doc/an-integrated-analytical-approach-to-lipase-risk-management-in-biologics-development-0001</t>
+          <t>https://www.drugdiscoverynews.com/samsung-biologics-signs-usd-262-million-manufacturing-agreement-with-european-pharmaceutical-company-17527</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>15-09-2026 00:39 UTC</t>
+          <t>14-09-2026 19:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3811,22 +3811,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Samsung, Hyundai, LG Advance Payments to Suppliers Ahead of Chuseok</t>
+          <t>An Integrated Analytical Approach To Lipase Risk Management In Biologics Development</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>chosun.com</t>
+          <t>Bioprocess Online</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/english/industry-en/2026/09/14/GWXBHH6C7VAIHLLINZIJCGKADU/</t>
+          <t>https://www.bioprocessonline.com/doc/an-integrated-analytical-approach-to-lipase-risk-management-in-biologics-development-0001</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>14-09-2026 09:32 UTC</t>
+          <t>15-09-2026 00:39 UTC</t>
         </is>
       </c>
     </row>
@@ -3838,22 +3838,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Samsung, SK Hynix Limit Pre-Market Losses Despite 5.86% Plunge in Philadelphia Semiconductor Index</t>
+          <t>Samsung Biologics union's show of force backfires at the bargaining table</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/ccfd0caa-c0c1-43f1-80a4-b1aaf6a773d4</t>
+          <t>https://mbiz.heraldcorp.com/article/10874287</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>15-09-2026 00:35 UTC</t>
+          <t>15-09-2026 06:25 UTC</t>
         </is>
       </c>
     </row>
@@ -3865,22 +3865,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Samsung, LG to pay suppliers 1.9 trillion won early ahead of Chuseok</t>
+          <t>KOSPI falls for fourth session on foreign and institutional selling</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Aju Press</t>
+          <t>디지털투데이</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://m.ajupress.com/amp/20260914171524025</t>
+          <t>https://www.digitaltoday.co.kr/en/view/103708/kospi-falls-for-fourth-session-on-foreign-and-institutional-selling</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>14-09-2026 08:25 UTC</t>
+          <t>15-09-2026 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3892,22 +3892,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>KOSPI falls for fourth session on foreign and institutional selling</t>
+          <t>[Closing Market] KOSPI Retreats to 6,620 Mark Amid Stronger Dollar</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>디지털투데이</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://www.digitaltoday.co.kr/en/view/103708/kospi-falls-for-fourth-session-on-foreign-and-institutional-selling</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277008</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>15-09-2026 07:04 UTC</t>
+          <t>15-09-2026 08:42 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,22 +3919,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Controlling Complexity In ADC Formulation Development</t>
+          <t>Samsung, SK Hynix Limit Pre-Market Losses Despite 5.86% Plunge in Philadelphia Semiconductor Index</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bioprocess Online</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.bioprocessonline.com/doc/controlling-complexity-in-adc-formulation-development-0001</t>
+          <t>https://finance.biggo.com/news/ccfd0caa-c0c1-43f1-80a4-b1aaf6a773d4</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>15-09-2026 00:38 UTC</t>
+          <t>15-09-2026 00:35 UTC</t>
         </is>
       </c>
     </row>
@@ -3946,22 +3946,76 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
+          <t>South Korean shares recoup early losses as chipmakers rebound</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Business Recorder</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.brecorder.com/news/amp/40439558</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>15-09-2026 05:50 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
           <t>Government Launches Korea Premium Weeks: Integrated Capital Market Event</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>chosun.com</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
         <is>
           <t>https://www.chosun.com/english/market-money-en/2026/09/15/DSYD3II34FBQPMWS4EYZOCNMXI/</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>15-09-2026 05:46 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Controlling Complexity In ADC Formulation Development</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Bioprocess Online</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://www.bioprocessonline.com/doc/controlling-complexity-in-adc-formulation-development-0001</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>15-09-2026 00:38 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz issues EUR 500 million bond</t>
+          <t>Sandoz issues 500 million euros bond to extend debt maturity profile</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.sandoz.com/sandoz-issues-eur-500-million-bond/</t>
+          <t>https://www.thepharmaletter.com/generics-news/sandoz-issues-500-million-euros-bond-to-extend-debt-maturity-profile</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14-09-2026 16:16 UTC</t>
+          <t>15-09-2026 22:14 UTC</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sandoz Group Launches EUR500 Million Bond</t>
+          <t>Sandoz pays up for duration in €500m trade</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Global Capital</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/sandoz-group-launches-eur500-million-bond-ce785bddd98df626</t>
+          <t>https://www.globalcapital.com/article/2gw8sima1juifixzkivi8/corporate-bonds/high-grade-and-crossover-bonds/sandoz-pays-up-for-duration-in-500m-trade</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15-09-2026 03:29 UTC</t>
+          <t>15-09-2026 15:48 UTC</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Child anaemia falls to 8%, stunting to 4% in Egypt - Health - Egypt</t>
+          <t>Norma Stoeger Obituary (1938 - 2026) - Valentine, NE - North Platte Telegraph</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>english.ahram.org.eg</t>
+          <t>Legacy obituary</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://english.ahram.org.eg/NewsContent/1/1236/576675/Egypt/Health/Child-anaemia-falls-to-,-stunting-to--in-Egypt.aspx</t>
+          <t>https://www.legacy.com/us/obituaries/nptelegraph/name/norma-stoeger-obituary?id=62435196</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15-09-2026 09:00 UTC</t>
+          <t>16-09-2026 05:41 UTC</t>
         </is>
       </c>
     </row>
@@ -544,76 +544,76 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Meche Cancels Jury Selection</t>
+          <t>Egypt reports sharp decline in child anaemia, stunting rates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Landry Now Online Newspaper</t>
+          <t>Dailynewsegypt</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.stlandrynow.com/community/local-news/meche-cancels-jury-selection/</t>
+          <t>https://www.dailynewsegypt.com/2026/09/15/egypt-reports-sharp-decline-in-child-anaemia-stunting-rates/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14-09-2026 16:11 UTC</t>
+          <t>15-09-2026 18:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boehringer provides update on EASi-KIDNEY trial</t>
+          <t>Child anaemia falls to 8%, stunting to 4% in Egypt - Health - Egypt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Ahram Online</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.boehringer-ingelheim.com/human-health/boehringer-provides-update-easi-kidney-trial</t>
+          <t>https://english.ahram.org.eg/NewsContent/1/1236/576675/Egypt/Health/Child-anaemia-falls-to-,-stunting-to--in-Egypt.aspx</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15-09-2026 10:30 UTC</t>
+          <t>15-09-2026 09:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>When breathlessness isn’t just ageing: Campaign urges early action on pulmonary fibrosis</t>
+          <t>Robert Gerald Engstrom Obituary (2026) - Hendersonville, NC - Church Street Funeral &amp; Cremation - Hendersonville</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gulf News</t>
+          <t>Legacy obituary</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://gulfnews.com/amp/story/uae%2Fhealth%2Fwhen-breathlessness-isnt-just-ageing-campaign-urges-early-action-on-pulmonary-fibrosis-1.500673910</t>
+          <t>https://www.legacy.com/us/obituaries/name/robert-engstrom-obituary?id=62434785</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15-09-2026 06:12 UTC</t>
+          <t>16-09-2026 02:57 UTC</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sugar Clinics: A One-Stop Shop for Improved Diabetes Care in Mexico</t>
+          <t>Boehringer provides update on EASi-KIDNEY trial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ACCESS Newswire</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.accessnewswire.com/newsroom/en/healthcare-and-pharmaceutical/sugar-clinics-a-one-stop-shop-for-improved-diabetes-care-in-mexico-1221166</t>
+          <t>https://www.boehringer-ingelheim.com/human-health/boehringer-provides-update-easi-kidney-trial</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15-09-2026 14:36 UTC</t>
+          <t>15-09-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Genexine’s GX-BP1 (SOX2 bioPROTAC) Suppresses Tumor Regrowth despite Osimertinib and Dato-DXd Combination and Achieves 6/6 Complete Responses in Triple Combination</t>
+          <t>Webinar: Immunosuppression: Consequences for the bird and farmer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>WATTPoultry.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/genexine-gx-bp1-sox2-bioprotac-091600149.html</t>
+          <t>https://www.wattagnet.com/webinars/webinar/15834930/boehringer-ingelheim-webinar-immunosuppression-consequences-for-the-bird-and-farmer</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15-09-2026 09:16 UTC</t>
+          <t>15-09-2026 20:59 UTC</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Study shows how changes in prefontal brain activity can impair the ability to change behaviour</t>
+          <t>Sugar Clinics: A One-Stop Shop for Improved Diabetes Care in Mexico</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>University of Nottingham</t>
+          <t>StreetInsider</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.nottingham.ac.uk/news/study-shows-how-changes-in-prefontal-brain-activity-can-impair-the-ability-to-change-behaviour</t>
+          <t>https://www.streetinsider.com/ACCESS+Newswire/Sugar+Clinics%3A+A+One-Stop+Shop+for+Improved+Diabetes+Care+in+Mexico/27063162.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15-09-2026 09:09 UTC</t>
+          <t>15-09-2026 14:37 UTC</t>
         </is>
       </c>
     </row>
@@ -706,130 +706,130 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Paper + Spark adds seven new clients as it’s named agency of the year at 2026 AMI Awards</t>
+          <t>Vicadrostat EASi-KIDNEY Trial Discontinued for Lack of Benefit in CKD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Campaign Brief</t>
+          <t>HCPLive</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://campaignbrief.com/paper-spark-adds-seven-new-clients-as-its-named-agency-of-the-year-at-2026-ami-awards/</t>
+          <t>https://www.hcplive.com/view/vicadrostat-easi-kidney-trial-discontinued-for-lack-of-benefit-in-ckd</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15-09-2026 04:08 UTC</t>
+          <t>15-09-2026 22:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Khalid Yassin Top Healthcare Leaders 2026 Founders &amp; Shareholders</t>
+          <t>When the Scan Knows Before the Spirometer Does</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Forbes Middle East</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.forbesmiddleeast.com/lists/top-healthcare-leaders-2026-founders-shareholders/khalid-yassin/</t>
+          <t>https://www.clinicaltrialvanguard.com/executiveinterviews/when-the-scan-knows-before-the-spirometer-does/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15-09-2026 02:40 UTC</t>
+          <t>15-09-2026 16:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amgen to deploy Veeva Vault CRM globally to spe...</t>
+          <t>Adisseo names Li Bo as its new chairman and CEO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>Feed Strategy</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/biotek-terkemuka-pilih-veeva-vault-crm-global</t>
+          <t>https://www.feedstrategy.com/business-markets/company-news/news/15834953/adisseo-names-li-bo-as-its-new-chairman-and-ceo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15-09-2026 11:29 UTC</t>
+          <t>15-09-2026 20:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FDA reduces monitoring time for Amgen’s Imdelltra infusions</t>
+          <t>Genexine’s GX-BP1 (SOX2 bioPROTAC) Suppresses Tumor Regrowth despite Osimertinib and Dato-DXd Combination and Achieves 6/6 Complete Responses in Triple Combination</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>pharmaceutical-technology.com</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pharmaceutical-technology.com/news/fda-reduces-monitoring-time-amgens-imdelltra/</t>
+          <t>https://uk.finance.yahoo.com/news/genexine-gx-bp1-sox2-bioprotac-091600149.html</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15-09-2026 10:49 UTC</t>
+          <t>15-09-2026 09:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shane Lowry Secures Record Home Victory at the 2026 Amgen Irish Open</t>
+          <t>Study shows how changes in prefontal brain activity can impair the ability to change behaviour</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>University of Nottingham</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.amgen.com/stories/2026/09/shane-lowry-secures-record-home-victory-at-the-2026-amgen-irish-open</t>
+          <t>https://www.nottingham.ac.uk/news/study-shows-how-changes-in-prefontal-brain-activity-can-impair-the-ability-to-change-behaviour</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14-09-2026 21:47 UTC</t>
+          <t>15-09-2026 09:09 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amgen to Deploy Veeva Vault CRM Globally</t>
+          <t>Bristol Myers sues Amgen over proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/amgen-to-deploy-veeva-vault-crm-globally-ce785bdddd89f622</t>
+          <t>https://www.reuters.com/legal/litigation/bristol-myers-sues-amgen-over-proposed-opdivo-biosimilar-2026-09-15/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15-09-2026 11:49 UTC</t>
+          <t>15-09-2026 20:25 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Leading Biotech Selects Veeva Vault CRM Globally</t>
+          <t>FDA reduces initial monitoring time for Amgen’s Imdelltra</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/leading-biotech-selects-veeva-vault-crm-globally-302878548.html</t>
+          <t>https://www.indianpharmapost.com/regulatory/fda-reduces-initial-monitoring-time-for-amgens-imdelltra-21863</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15-09-2026 11:03 UTC</t>
+          <t>16-09-2026 02:37 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shane Lowry sinks final putt to claim historic 11-shot victory at Irish Open</t>
+          <t>Amgen to deploy Veeva Vault CRM globally to spe...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Golf Channel</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.golfchannel.com/watch/dp-world-tour/shane-lowry-sinks-final-putt-to-claim-historic-11-shot-victory-at-irish-open</t>
+          <t>https://pluang.com/en/news-feed/biotek-terkemuka-pilih-veeva-vault-crm-global</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15-09-2026 11:50 UTC</t>
+          <t>15-09-2026 11:29 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMGN Looks 4.2% Overvalued on GF Value™</t>
+          <t>Amgen Highlights MariTide, IMDELLTRA Pipeline Progress and Growth Priorities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>finance.yahoo.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/9081551/amgn-looks-42-overvalued-on-gf-value</t>
+          <t>https://finance.yahoo.com/healthcare/articles/amgen-highlights-maritide-imdelltra-pipeline-050213898.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15-09-2026 11:47 UTC</t>
+          <t>16-09-2026 05:02 UTC</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amgen vs. Vertex Pharmaceuticals: Value Stability vs. High-Growth Biotech Investment Plays</t>
+          <t>FDA reduces monitoring time for Amgen’s Imdelltra infusions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NAI500</t>
+          <t>Pharmaceutical Technology</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nai500.com/blog/2026/09/amgen-vs-vertex-pharmaceuticals-value-stability-vs-high-growth-biotech-investment-plays/</t>
+          <t>https://www.pharmaceutical-technology.com/news/fda-reduces-monitoring-time-amgens-imdelltra/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15-09-2026 02:47 UTC</t>
+          <t>15-09-2026 10:49 UTC</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BK’s Breakdowns: Shane Lowry’s winning WITB, 2026 Amgen Irish Open</t>
+          <t>Bristol-Myers Targets Amgen’s Opdivo Biosimilar in Patent Suit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GolfWRX</t>
+          <t>Bloomberg Law News</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://golfwrx.com/786218/bks-breakdowns-shane-lowrys-winning-witb-2026-amgen-irish-open/</t>
+          <t>https://news.bloomberglaw.com/ip-law/bristol-myers-targets-amgens-opdivo-biosimilar-in-patent-suit</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15-09-2026 10:30 UTC</t>
+          <t>15-09-2026 17:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FDA cuts IMDELLTRA monitoring time for first two doses</t>
+          <t>Skorney: Novartis's Lp(a) Miss Exposes a Modeling Flaw That Now Threatens Amgen and Lilly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Voice of Healthcare</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://vohnetwork.com/news/pharma/fda-reduces-monitoring-time-for-first-two-imdelltra-doses</t>
+          <t>https://finance.biggo.com/news/1c49c250a2209ff1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15-09-2026 04:50 UTC</t>
+          <t>15-09-2026 17:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1030,49 +1030,49 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WATCH | Shane Lowry moves TEN ahead</t>
+          <t>Leading Biotech Selects Veeva Vault CRM Globally</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>europeantour.com</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.europeantour.com/dpworld-tour/news/video/watch-shane-lowry-moves-ten-ahead/</t>
+          <t>https://www.prnewswire.com/news-releases/leading-biotech-selects-veeva-vault-crm-globally-302878548.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14-09-2026 17:32 UTC</t>
+          <t>15-09-2026 11:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FDA Accepts Extended Duration sNDA for Miudella Hormone-Free IUD</t>
+          <t>FDA Approves Shorter Monitoring for First Two Tarlatamab Doses in ES-SCLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Patient Care Online</t>
+          <t>CancerNetwork</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.patientcareonline.com/view/fda-accepts-extended-duration-snda-for-miudella-hormone-free-iud</t>
+          <t>https://www.cancernetwork.com/view/fda-approves-shorter-monitoring-for-first-two-tarlatamab-doses-in-es-sclc</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14-09-2026 17:57 UTC</t>
+          <t>15-09-2026 16:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sun Pharma Subsidiaries Settle US Generic Drug Pricing Antitrust Litigation For Confidential Amount</t>
+          <t>Boryung, Organon Korea Team Up on Cholesterol Drug Atozet</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>en.sedaily.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/sun-pharma-subsidiaries-settle-us-generic-drug-pricing-antitrust-litigation-for-confidential-amount</t>
+          <t>https://en.sedaily.com/culture/2026/09/16/boryung-organon-korea-team-up-on-cholesterol-drug-atozet</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15-09-2026 00:55 UTC</t>
+          <t>16-09-2026 01:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FDA accepts extended duration sNDA for MIUDELLA IUD</t>
+          <t>Boryung to Take Charge of Domestic Sales and Marketing for 'Atojet'... Expanding Presence in the Dyslipidemia Market</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contemporary OB/GYN</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>http://www.contemporaryobgyn.net/view/fda-accepts-extended-duration-snda-miudella-iud</t>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026091615093005618</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14-09-2026 15:51 UTC</t>
+          <t>16-09-2026 06:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NSF Study Aims to Reveal How Plants Sense, Respond to Heat</t>
+          <t>HNLU Labour Law Students Visit Bhilai Steel Plant To Gain Practical Exposure To Industrial Operations And ...</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>University of Mississippi | Ole Miss</t>
+          <t>Live Law</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://olemiss.edu/news/2026/09/nsf-study-aims-to-reveal-how-plants-sense-respond-to-heat/index.html</t>
+          <t>https://www.livelaw.in/amp/lawschool/news/hnlu-labour-law-students-visit-bhilai-steel-plant-550211</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>15-09-2026 15:03 UTC</t>
+          <t>16-09-2026 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Automated Snack Formers Market Size, Share &amp; Forecast 2036</t>
+          <t>Attackers Exploit WooCommerce Wholesale Lead Capture Flaw to Plant PHP Web Shells</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fact.MR</t>
+          <t>thehackernews.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.factmr.com/report/automated-snack-formers-market</t>
+          <t>https://thehackernews.com/2026/09/attackers-exploit-woocommerce-wholesale.html</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15-09-2026 12:37 UTC</t>
+          <t>16-09-2026 05:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gas Turbine Report H2 2026</t>
+          <t>In 2017, a fully automated facility for plant bioscience research was launched to the International Space</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rystad Energy</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.rystadenergy.com/insights/gas-turbine-report-H2-2026</t>
+          <t>https://m.economictimes.com/news/international/us/science-in-2017-a-fully-automated-facility-for-plant-bioscience-research-was-launched-to-the-international-space-station-what-nasa-studied-in-space/articleshow/134275632.cms</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15-09-2026 08:20 UTC</t>
+          <t>16-09-2026 00:13 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>This Australian cave hid 25,000 years of ritual secrets</t>
+          <t>NSF Study Aims to Reveal How Plants Sense, Respond to Heat</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Science Daily</t>
+          <t>University of Mississippi | Ole Miss</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260914102443.htm</t>
+          <t>https://olemiss.edu/news/2026/09/nsf-study-aims-to-reveal-how-plants-sense-respond-to-heat/index.html</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15-09-2026 14:52 UTC</t>
+          <t>15-09-2026 15:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>How soybeans took over the American diet without anyone noticing</t>
+          <t>Automated Snack Formers Market Size, Share &amp; Forecast 2036</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>Fact.MR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.washingtonpost.com/ripple/2026/09/11/how-soybeans-took-over-the-american-diet-without-anyone-noticing/</t>
+          <t>https://www.factmr.com/report/automated-snack-formers-market</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15-09-2026 13:06 UTC</t>
+          <t>15-09-2026 12:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tungsten West advances Hemerdon restart with TOMRA Mining sorting tech a key component of redesigned plant</t>
+          <t>Barhale completes Anglian Water’s first plant tackling emerging contaminant Cypermethrin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>International Mining</t>
+          <t>Water Magazine</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://im-mining.com/2026/09/15/tungsten-west-advances-hemerdon-restart-with-tomra-mining-sorting-tech-a-key-component-of-redesigned-plant/</t>
+          <t>https://www.watermagazine.co.uk/2026/09/16/barhale-completes-anglian-waters-first-plant-tackling-emerging-contaminant-cypermethrin/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15-09-2026 13:16 UTC</t>
+          <t>16-09-2026 04:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>'Plant parents' cut a piece of London's historic Barbican urban jungle</t>
+          <t>This Australian cave hid 25,000 years of ritual secrets</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>newseu.cgtn.com</t>
+          <t>ScienceDaily</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://newseu.cgtn.com/news/2026-09-15/-Plant-parents-cut-a-piece-of-London-s-historic-Barbican-urban-jungle-1QrqxKtw9MI/share_amp.html</t>
+          <t>https://www.sciencedaily.com/releases/2026/09/260914102443.htm</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15-09-2026 12:24 UTC</t>
+          <t>15-09-2026 14:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Industrial farming poses threat to fungi, small organisms vital to healthy soil – UN Decade</t>
+          <t>These Plants Have a Protein-Packed Diet, Too</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Farmers Review Africa</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://farmersreviewafrica.com/industrial-farming-poses-threat-to-fungi-small-organisms-vital-to-healthy-soil-un-decade/</t>
+          <t>https://www.nytimes.com/2026/09/07/style/carnivorous-houseplants-venus-flytrap-pitcher-plant.html</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>15-09-2026 10:00 UTC</t>
+          <t>15-09-2026 23:29 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Beyond Meat® Announces Availability of Beyond Steak® Filet at Erewhon</t>
+          <t>How soybeans took over the American diet without anyone noticing</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Beyond Meat</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://investors.beyondmeat.com/news-releases/news-release-details/beyond-meatr-announces-availability-beyond-steakr-filet-erewhon</t>
+          <t>https://www.washingtonpost.com/ripple/2026/09/11/how-soybeans-took-over-the-american-diet-without-anyone-noticing/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>15-09-2026 13:00 UTC</t>
+          <t>15-09-2026 19:02 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Florist Special With Bri Lovie</t>
+          <t>Tungsten West advances Hemerdon restart with TOMRA Mining sorting tech a key component of redesigned plant</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thursd</t>
+          <t>International Mining</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://thursd.com/articles/florist-special-with-bri-lovie</t>
+          <t>https://im-mining.com/2026/09/15/tungsten-west-advances-hemerdon-restart-with-tomra-mining-sorting-tech-a-key-component-of-redesigned-plant/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14-09-2026 18:48 UTC</t>
+          <t>15-09-2026 13:16 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,76 +1408,76 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Plant This Low-Maintenance Evergreen Now for a Beautiful Yard All Winter Long</t>
+          <t>Iron overload: how tea, coffee, red meat and alcohol can affect absorption</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>housebeautiful.com</t>
+          <t>The Conversation</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.housebeautiful.com/lifestyle/gardening/a73643733/arborvitae-care-winter-landscape/</t>
+          <t>https://theconversation.com/iron-overload-how-tea-coffee-red-meat-and-alcohol-can-affect-absorption-289770</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14-09-2026 19:30 UTC</t>
+          <t>15-09-2026 13:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pfizer Invites Public to Listen to Webcast of Pfizer Discussion at Healthcare Conference</t>
+          <t>True Form Ss Keto Gummies Reviews: A Realistic, Hands On Assessment [oOYQPSvW76t]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>santeestrie.qc.ca</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260915286706/en/Pfizer-Invites-Public-to-Listen-to-Webcast-of-Pfizer-Discussion-at-Healthcare-Conference</t>
+          <t>https://www.santeestrie.qc.ca/typo3conf/ext/wrs_pannellum/Resources/Public/Vendor/pannellum/pannellum.htm?config=/%5C/video.unkk.top/panketo2/oOYQPSvW76t</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>15-09-2026 14:00 UTC</t>
+          <t>16-09-2026 06:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Why the EU Biotech Act must deliver practical improvements for clinical trials in Europe</t>
+          <t>Native Plant Communities: Salt Marshes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>The Parliament Magazine</t>
+          <t>Maine Audubon</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.theparliamentmagazine.eu/partner/article/why-the-eu-biotech-act-must-deliver-practical-improvements-for-clinical-trials-in-europe</t>
+          <t>https://maineaudubon.org/news/native-plant-communities-salt-marshes/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>15-09-2026 06:55 UTC</t>
+          <t>15-09-2026 19:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pfizer 52 Week Low Streak: Four-Day Breakdown Deepens</t>
+          <t>Pfizer – Every Insight Matters – HCP (Information from Industry)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>univest.in</t>
+          <t>DocWireNews</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://univest.in/blogs/why-pfizer-ltd-share-52-week-consecutive-low-2026</t>
+          <t>https://www.docwirenews.com/videos/pfizer-every-insight-matters-hcp-information-from-industry-breast-summit</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>15-09-2026 04:51 UTC</t>
+          <t>15-09-2026 19:22 UTC</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IP Group eyes busy second half as Pfizer obesity investment catches the eye</t>
+          <t>Two structural columns buckled on the 21st floor of the former Pfizer headquarters during its conversion into about 1,600 apartments. The failure prompted New York City to widen inspections, and work was subsequently halted at other Manhattan office-to-resi</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Proactive financial news</t>
+          <t>ScienceBlog.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.proactiveinvestors.com/companies/news/1098540/ip-group-eyes-busy-second-half-as-pfizer-obesity-investment-catches-the-eye-1098540.html</t>
+          <t>https://scienceblog.com/m-two-structural-columns-buckled-on-the-21st-floor-of-the-former-pfizer-headquarters-during-its-conversion-into-about-1-600-apartments-the-failure-prompted-new-york-city-to-widen-ins/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15-09-2026 07:49 UTC</t>
+          <t>15-09-2026 22:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>News | Lender doubles down on New York office conversions after Pfizer setback</t>
+          <t>Pfizer Invites Public to Listen to Webcast of Pfizer Discussion at Healthcare Conference</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>finance.yahoo.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.costar.com/article/1364458074/lender-doubles-down-on-new-york-office-conversions-after-pfizer-setback</t>
+          <t>https://finance.yahoo.com/healthcare/articles/pfizer-invites-public-listen-webcast-140000774.html</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>14-09-2026 23:14 UTC</t>
+          <t>15-09-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pfizer loses patent case over Enbrel generic</t>
+          <t>John Dorfman: CEOs buy shares at Pfizer, Uber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lawyerly</t>
+          <t>TribLIVE.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.lawyerly.com.au/pfizer-loses-patent-case-over-enbrel-generic/</t>
+          <t>https://community.triblive.com/news/4140336</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15-09-2026 07:27 UTC</t>
+          <t>16-09-2026 01:57 UTC</t>
         </is>
       </c>
     </row>
@@ -1597,49 +1597,49 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IP Group H1 NAV Rises 3.2% as Pfizer Obesity Royalty Asset Reaches £152 Million</t>
+          <t>Before Karnataka police busted counterfeit medicine racket, CDSCO had sought regulation of pharma packaging suppliers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>The South First</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/ip-group-h1-nav-rises-070831998.html</t>
+          <t>https://thesouthfirst.com/health/before-karnataka-police-busted-counterfeit-medicine-racket-cdsco-had-sought-regulation-of-pharma-packaging-suppliers/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>15-09-2026 07:08 UTC</t>
+          <t>16-09-2026 01:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Biogen Eyes Wave of Phase III Readouts as It Expands Beyond Neuroscience</t>
+          <t>Pfizer (Backpack Securities) to British Pound Sterling Price Today | Live PFE to GBP Converter &amp; Exchange Rate</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>CryptoRank</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/biogen-eyes-wave-phase-iii-040205385.html</t>
+          <t>https://cryptorank.io/price/pfizer-backpack-securities/gbp</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>15-09-2026 04:02 UTC</t>
+          <t>15-09-2026 18:22 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hummingbird Bioscience Appoints Dr. James Garner as President</t>
+          <t>Eisai and Biogen Announce Japan Approval of LEQEMBI Pen, a Once-Weekly Subcutaneous Alzheimer’s Treatment</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>Quiver Quantitative</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.manilatimes.net/2026/09/15/tmt-newswire/globenewswire/hummingbird-bioscience-appoints-dr-james-garner-as-president/2425252</t>
+          <t>https://www.quiverquant.com/news/Eisai+and+Biogen+Announce+Japan+Approval+of+LEQEMBI+Pen%2C+a+Once-Weekly+Subcutaneous+Alzheimer%E2%80%99s+Treatment</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>15-09-2026 09:14 UTC</t>
+          <t>16-09-2026 06:10 UTC</t>
         </is>
       </c>
     </row>
@@ -1678,76 +1678,76 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Scholar Rock Drug Wins First-in-Class Approval in Rare Neuromuscular Disease</t>
+          <t>LEQEMBI® Pen (Subcutaneous Formulation of LEQEMBI®)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MedCity News</t>
+          <t>GlobeNewswire</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://medcitynews.com/2026/09/scholar-rock-drug-wins-first-in-class-approval-in-rare-neuromuscular-disease/</t>
+          <t>https://www.globenewswire.com/news-release/2026/09/16/3362836/0/en/leqembi-pen-subcutaneous-formulation-of-leqembi-approved-in-japan-for-the-treatment-of-early-alzheimer-s-disease.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>14-09-2026 19:33 UTC</t>
+          <t>16-09-2026 06:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Laboratories launches Nivorz in India</t>
+          <t>Canada agrees to help pay for Alzheimer’s drug LEQEMBI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>Longevity.Technology</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/news/dr-reddys-laboratories-launches-nivorz-in-india/article71467764.ece</t>
+          <t>https://longevity.technology/news/canada-agrees-to-help-pay-for-alzheimers-drug-leqembi/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>15-09-2026 11:08 UTC</t>
+          <t>15-09-2026 23:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s launches initiative to train India’s obesity care workforce</t>
+          <t>Fianna Fáil says reimbursement for Friedreich's ataxia drug to be in place from 1 October</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>The Journal</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.expresspharma.in/dr-reddys-launches-initiative-to-train-indias-obesity-care-workforce/</t>
+          <t>https://www.thejournal.ie/skyclarys-reimbursement-ireland-7163736-Sep2026/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15-09-2026 05:23 UTC</t>
+          <t>15-09-2026 20:31 UTC</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1759,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dr Reddy’s launches Opdivo biosimilar Nivorz in India, enters immuno-oncology segment</t>
+          <t>Dr. Reddy’s forays into India’s biosimilar immuno-oncology market, launches Nivorz</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/dr-reddy-s-launches-opdivo-biosimilar-nivorz-in-india-enters-immuno-oncology-segment-14030366.html/amp</t>
+          <t>https://www.thehindu.com/business/Industry/dr-reddys-forays-into-indias-biosimilar-immuno-oncology-market-launches-nivorz/article71469381.ece</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>15-09-2026 12:06 UTC</t>
+          <t>15-09-2026 16:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s launches nivolumab biosimilar NIVORZ in India</t>
+          <t>Dr. Reddy’s Laboratories launches NIVORZ in India</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Express Pharma</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/dr-reddys-launches-nivolumab-biosimilar-nivorz-in-india-21853</t>
+          <t>https://www.expresspharma.in/dr-reddys-laboratories-launches-nivorz-in-india/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>15-09-2026 11:56 UTC</t>
+          <t>15-09-2026 11:42 UTC</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dr. Reddy's launches nivolumab biosimilar in India</t>
+          <t>Dr. Reddy’s Laboratories launches Nivorz in India</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>economictimes.indiatimes.com</t>
+          <t>thehindubusinessline.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://economictimes.indiatimes.com/industry/healthcare/biotech/pharmaceuticals/dr-reddys-launches-nivolumab-biosimilar-in-india/articleshow/134266368.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
+          <t>https://www.thehindubusinessline.com/companies/dr-reddys-laboratories-launches-nivorz-in-india/article71467764.ece</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>15-09-2026 14:05 UTC</t>
+          <t>15-09-2026 11:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dr Reddy’s launches cancer drug biosimilar in India, targets 12 indications</t>
+          <t>Buy, Sell Or Hold: Dr Reddy's Labs, BEL, L&amp;T, HDFC Bank, Welspun Corp And Canara Bank — Ask Profit</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/market/stocks/dr-reddys-launches-cancer-drug-biosimilar-in-india-targets-12-indications-19991078.htm/amp</t>
+          <t>https://www.ndtvprofit.com/markets/buy-sell-or-hold-dr-reddys-labs-bel-l-t-hdfc-bank-welspun-corp-and-canara-bank-ask-profit-12051254</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15-09-2026 11:16 UTC</t>
+          <t>15-09-2026 17:07 UTC</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s To Train 5,000 Professionals In Obesity Care</t>
+          <t>Dr Reddy’s launches cancer blockbuster nivolumab biosimilar in India</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BW Healthcare World</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.bwhealthcareworld.com/article/dr-reddy-s-to-train-5-000-professionals-in-obesity-care-623671</t>
+          <t>https://pharma.economictimes.indiatimes.com/news/drug-approvals-and-launches/dr-reddys-launches-cancer-blockbuster-nivolumab-biosimilar-in-india/134262279</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>15-09-2026 04:27 UTC</t>
+          <t>15-09-2026 12:38 UTC</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dr Reddy's Labs Q2 FY27: Results Preview</t>
+          <t>Dr Reddy’s launches Opdivo biosimilar Nivorz in India, enters immuno-oncology segment</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>univest.in</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://univest.in/blogs/dr-reddys-laboratories-q2-results-fy27-preview-date-expectations</t>
+          <t>https://www.moneycontrol.com/news/business/dr-reddy-s-launches-opdivo-biosimilar-nivorz-in-india-enters-immuno-oncology-segment-14030366.html</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>15-09-2026 05:41 UTC</t>
+          <t>15-09-2026 12:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>How Dr. Reddy’s is helping build India’s obesity workforce</t>
+          <t>Dr. Reddy’s launches nivolumab biosimilar NIVORZ in India</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HR Katha</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.hrkatha.com/news/learning-development/how-dr-reddys-is-helping-build-indias-obesity-workforce/</t>
+          <t>https://www.indianpharmapost.com/news/dr-reddys-launches-nivolumab-biosimilar-nivorz-in-india-21853</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>15-09-2026 04:28 UTC</t>
+          <t>15-09-2026 11:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1948,22 +1948,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Launches Program to Strengthen Obesity Care in India</t>
+          <t>Dr Reddy’s forays into Indian biosimilar immuno-oncology market</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Siliconindia</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.siliconindia.com/news/dr-reddy-s-launches-program-to-strengthen-obesity-care-in-india-nwid-55454.html</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/dr-reddys-forays-into-indian-biosimilar-immuno-oncology-market/articleshow/134268510.cms</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>15-09-2026 11:29 UTC</t>
+          <t>15-09-2026 16:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1975,292 +1975,292 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Shreveport Frymaster celebrates purchase, expansion</t>
+          <t>Dr. Reddy's launches nivolumab biosimilar in India</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>The Shreveport-Bossier City Advocate</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.shreveportbossieradvocate.com/business/more-space-lines-and-employees-at-shreveport-frymaster/article_0ca48873-0dd0-40b0-8320-c265ad5bbc8f.html</t>
+          <t>https://m.economictimes.com/industry/healthcare/biotech/pharmaceuticals/dr-reddys-launches-nivolumab-biosimilar-in-india/articleshow/134266368.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>15-09-2026 11:30 UTC</t>
+          <t>15-09-2026 14:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>C-CAMP National Bio Entrepreneurship Competition 2026 sees 15 startups, 4 student teams bag top honours</t>
+          <t>Domestic pharma market sustains growth momentum, but margins remain key</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pharmabiz.com</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pharmabiz.com/NewsDetails.aspx?aid=190587&amp;sid=2</t>
+          <t>https://www.livemint.com/market/mark-to-market/indian-pharma-market-ipm-pharma-stocks-domestic-pharma-dr-reddy-s-laboratories-sun-pharma-ajanta-pharma-glenmark/amp-11789538290089.html</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>15-09-2026 10:59 UTC</t>
+          <t>16-09-2026 07:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15 startups, 4 student teams win C-CAMP National Bio Entrepreneurship Competition 2026</t>
+          <t>Shreveport Frymaster celebrates purchase, expansion</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>The Shreveport-Bossier City Advocate</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.expresspharma.in/amp/15-startups-4-student-teams-win-c-camp-national-bio-entrepreneurship-competition-2026/</t>
+          <t>https://www.shreveportbossieradvocate.com/business/more-space-lines-and-employees-at-shreveport-frymaster/article_0ca48873-0dd0-40b0-8320-c265ad5bbc8f.html</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>15-09-2026 07:07 UTC</t>
+          <t>15-09-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shobiz CEO Sameer Tobaccowala on How Audience Expectations Are Changing</t>
+          <t>Nestlé Health Science and Dr. Reddy's 2024 India Joint Venture</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>storyboard18.com</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.storyboard18.com/videos/brand-marketing/shobiz-ceo-sameer-tobaccowala-on-how-audience-expectations-are-changing-110689.htm</t>
+          <t>https://www.openpr.com/news/4632173/nestle-health-science-and-dr-reddy-s-2024-india-joint-venture</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>15-09-2026 06:00 UTC</t>
+          <t>15-09-2026 16:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Free Cancer Screening cum Health Camp held at Phesama</t>
+          <t>BioTecNika Times-15-09-2026: Freshers Job at Accenture, Paid Internship at IISER &amp; Intas, Parexel WFH Jobs &amp; More</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nagaland Post</t>
+          <t>biotecnika.org</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nagalandpost.com/free-cancer-screening-cum-health-camp-held-at-phesama/</t>
+          <t>https://www.biotecnika.org/2026/09/biotecnika-times-15-09-2026/</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15-09-2026 05:18 UTC</t>
+          <t>15-09-2026 13:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>275 register for free health camp in Phesama</t>
+          <t>Cipla Formalizes Leadership Transition with Board Meeting Outcome and Regulatory Disclosures</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eastern Mirror</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.easternmirrornagaland.com/275-register-for-free-health-camp-in-phesama</t>
+          <t>https://scanx.trade/stock-market-news/companies/cipla-shareholders-approve-leadership-appointments-through-postal-ballot-with-strong-majority/36103377</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14-09-2026 17:13 UTC</t>
+          <t>15-09-2026 20:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma wins U.S. FDA approval for generic asthma inhaler</t>
+          <t>C-CAMP National Bio Entrepreneurship Competition 2026 sees 15 startups, 4 student teams bag top honours</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Pharmabiz.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/aurobindo-pharma-wins-us-fda-approval-for-generic-asthma-inhaler/article71469168.ece</t>
+          <t>https://www.pharmabiz.com/NewsDetails.aspx?aid=190587&amp;sid=2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>15-09-2026 15:07 UTC</t>
+          <t>15-09-2026 10:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Gains USFDA Approval for Inhalation Aerosol in $301 Million Market</t>
+          <t>ET Under 40 2026: How technology is creating younger leaders</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/aurobindo-pharma-unit-iv-api-facility-concludes-us-fda-inspection-with-zero-observations</t>
+          <t>https://m.economictimes.com/news/company/corporate-trends/et-under-40-2026-how-technology-is-creating-younger-leaders/amp_articleshow/134271381.cms</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>15-09-2026 14:48 UTC</t>
+          <t>15-09-2026 18:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma US FDA inspection at Telangana API facility concludes with 1 procedural observation</t>
+          <t>Kiran Mazumdar-Shaw Calls Out Fendi’s Rs 8.3 Lakh ‘Navratri’ Bag: ‘Undermines Our Authentic Talent’</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>Pragativadi</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/business/companies/aurobindo-pharma-us-fda-inspection-at-telangana-api-facility-concludes-with-1-procedural-observation-19991204.htm</t>
+          <t>https://pragativadi.com/kiran-mazumdar-shaw-calls-out-fendis-rs-8-3-lakh-navratri-bag-undermines-our-authentic-talent/</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>15-09-2026 14:14 UTC</t>
+          <t>16-09-2026 06:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Gets First USFDA Nod For First Metered-Dose Inhaler</t>
+          <t>Kiran Mazumdar-Shaw Slams Fendi’s Rs 8.3 Lakh Navratri-Style Bag, Says It Undermines Indian Talent</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>newsable.asianetnews.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.ndtvprofit.com/business/aurobindo-pharma-gets-first-usfda-nod-for-first-metered-dose-inhaler-12049337</t>
+          <t>https://newsable.asianetnews.com/entertainment/kiran-mazumdar-shaw-slams-fendis-rs-83-lakh-navratri-style-bag-says-it-undermines-indian-talent-articleshow-eo73h7b</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>15-09-2026 12:07 UTC</t>
+          <t>16-09-2026 07:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma receives US FDA nod for metered Beclomethasone Dipropionate aerosol</t>
+          <t>Harsh Goenka, Kiran Mazumdar-Shaw Call Out Fendi’s ₹8.3 Lakh ‘Navratri Bag’, Question Indian Craft</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>freepressjournal.in</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/markets/capital-market-news/aurobindo-pharma-receives-us-fda-nod-for-metered-beclomethasone-dipropionate-aerosol-126091500592_1.html</t>
+          <t>https://www.freepressjournal.in/lifestyle/harsh-goenka-kiran-mazumdar-shaw-call-out-fendis-83-lakh-navratri-bag-question-indian-craft-credit-netizens-react</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>15-09-2026 09:21 UTC</t>
+          <t>16-09-2026 07:20 UTC</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma’s Unit IV Clears USFDA Inspection: Shares Down</t>
+          <t>Aurobindo Pharma gets FDA nod for asthma inhaler</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>equitypandit.com</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.equitypandit.com/aurobindo-pharmas-unit-iv-clears-usfda-inspection-shares-down/</t>
+          <t>https://pharma.economictimes.indiatimes.com/amp/news/drug-approvals-and-launches/aurobindo-pharma-gets-fda-nod-for-asthma-inhaler/134276350</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>15-09-2026 07:32 UTC</t>
+          <t>16-09-2026 02:15 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma gets USFDA approval for Beclomethasone HFA aerosol</t>
+          <t>U.S. FDA issues observation to Aurobindo Pharma arm’s API unit</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-gets-usfda-nod-beclomethasone-hfa-aerosol/51004109</t>
+          <t>https://www.thehindu.com/business/Industry/us-fda-issues-observation-to-aurobindo-pharma-arms-api-unit/article71469185.ece</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15-09-2026 08:08 UTC</t>
+          <t>15-09-2026 15:14 UTC</t>
         </is>
       </c>
     </row>
@@ -2326,22 +2326,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U.S. FDA issues observation to Aurobindo Pharma arm’s API unit</t>
+          <t>Aurobindo Pharma shares in focus after USFDA issues one observation for Telangana facility</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/us-fda-issues-observation-to-aurobindo-pharma-arms-api-unit/article71469185.ece</t>
+          <t>https://www.moneycontrol.com/news/business/markets/aurobindo-pharma-shares-in-focus-after-usfda-issues-one-observation-for-telangana-facility-14030516.html/amp</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>15-09-2026 15:14 UTC</t>
+          <t>16-09-2026 01:35 UTC</t>
         </is>
       </c>
     </row>
@@ -2353,22 +2353,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma gets USFDA approval for generic inhalation aerosol for asthma patients</t>
+          <t>Aurobindo Pharma Gains USFDA Approval for Inhalation Aerosol in $301 Million Market</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>Sahi</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/aurobindo-pharma-gets-usfda-approval-for-generic-inhalation-aerosol-for-asthma-patients/article71467611.ece/amp/</t>
+          <t>https://www.sahi.com/news/aurobindo-pharma-unit-iv-api-facility-concludes-us-fda-inspection-with-zero-observations</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>15-09-2026 10:36 UTC</t>
+          <t>15-09-2026 14:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2380,400 +2380,400 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma receives USFDA approval for Beclomethasone Dipropionate HFA Inhalation Aerosol</t>
+          <t>Aurobindo Pharma Gets USFDA Nod for First Metered-Dose Inhaler, Beclomethasone Aerosol</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/markets/capital-market-news/aurobindo-pharma-receives-usfda-approval-for-beclomethasone-dipropionate-hfa-inhalation-aerosol-126091500646_1.html</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/aurobindo-pharma-gets-usfda-nod-for-first-metered-dose-inhaler-beclomethasone-aerosol-179322</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>15-09-2026 09:46 UTC</t>
+          <t>15-09-2026 16:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>High-Concentration, Low-Volume Subcutaneous Formulation</t>
+          <t>Aurobindo Pharma US FDA inspection at Telangana API facility concludes with 1 procedural observation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PharmTech.com</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pharmtech.com/view/high-concentration-low-volume-subcutaneous-formulation</t>
+          <t>https://www.cnbctv18.com/business/companies/aurobindo-pharma-us-fda-inspection-at-telangana-api-facility-concludes-with-1-procedural-observation-19991204.htm</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>14-09-2026 19:11 UTC</t>
+          <t>15-09-2026 14:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Functional labels with integrated gas barrier reduce oxygen ingress into COC syringes</t>
+          <t>Aurobindo Pharma gets USFDA approval for generic inhalation aerosol for asthma patients</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Manufacturing Chemist</t>
+          <t>thehindubusinessline.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://manufacturingchemist.com/functional-labels-with-integrated-gas-barrier-reduce-oxygen</t>
+          <t>https://www.thehindubusinessline.com/companies/aurobindo-pharma-gets-usfda-approval-for-generic-inhalation-aerosol-for-asthma-patients/article71467611.ece</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>15-09-2026 12:56 UTC</t>
+          <t>15-09-2026 10:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Samsung Galaxy A18 4G launches with a new chipset, IP64 rating and a notch - GSMArena.com news</t>
+          <t>Aurobindo Pharma Gets First USFDA Nod For First Metered-Dose Inhaler</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.gsmarena.com/the_samsung_galaxy_a18_4g_launches_with_a_new_chipset_ip64_rating_and_a_notch-news-74622.php</t>
+          <t>https://www.ndtvprofit.com/business/aurobindo-pharma-gets-first-usfda-nod-for-first-metered-dose-inhaler-12049337</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>15-09-2026 11:53 UTC</t>
+          <t>15-09-2026 12:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Samsung's India public policy chief Rajiv Aggarwal resigns</t>
+          <t>Aurobindo Pharma receives US FDA nod for metered Beclomethasone Dipropionate aerosol</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>electronics.economictimes.indiatimes.com</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>http://electronics.economictimes.indiatimes.com/news/consumer-electronics/samsungs-india-public-policy-chief-rajiv-aggarwal-resigns/134254973</t>
+          <t>https://www.business-standard.com/markets/capital-market-news/aurobindo-pharma-receives-us-fda-nod-for-metered-beclomethasone-dipropionate-aerosol-126091500592_1.html</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>15-09-2026 13:09 UTC</t>
+          <t>15-09-2026 09:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S25 gets cheaper: Know the deal</t>
+          <t>Price Action: Saatvik Green Energy rises 5% on Rs 1,041cr order win; Aurobindo Pharma down 2% on USFDA...</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/visualstories/technology/samsung-galaxy-s25-gets-cheaper-know-the-deal-285748-15-09-2026</t>
+          <t>https://www.moneycontrol.com/news/business/stocks/price-action-saatvik-green-energy-rises-5-on-order-win-worth-rs-1-041cr-aurobindo-pharma-down-2-on-usfda-observation-14030713.html</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>15-09-2026 13:39 UTC</t>
+          <t>16-09-2026 06:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Samsung opens Galaxy A25 One UI 9.0 beta program</t>
+          <t>Aurobindo Pharma wins U.S. FDA approval for generic asthma inhaler</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/samsung-opens-galaxy-a25-one-ui-9-0-beta-program/</t>
+          <t>https://www.thehindu.com/business/Industry/aurobindo-pharma-wins-us-fda-approval-for-generic-asthma-inhaler/article71469168.ece</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>15-09-2026 12:41 UTC</t>
+          <t>15-09-2026 15:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6 Samsung phone apps you've probably never heard of, but should download today</t>
+          <t>Aurobindo Pharma receives USFDA approval for Beclomethasone Dipropionate HFA Inhalation Aerosol</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MakeUseOf</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.makeuseof.com/samsung-phone-apps-you-should-download/</t>
+          <t>https://www.business-standard.com/markets/capital-market-news/aurobindo-pharma-receives-usfda-approval-for-beclomethasone-dipropionate-hfa-inhalation-aerosol-126091500646_1.html</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>15-09-2026 14:00 UTC</t>
+          <t>15-09-2026 09:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Samsung Leads $230 Mn Funding for European Chip Co EUCLYD Amid Memory Shortage</t>
+          <t>Aurobindo Pharma gets US FDA nod to sell first metered-dose asthma inhaler in US</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>analyticsindiamag.com</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://analyticsindiamag.com/ai-news/samsung-leads-230-mn-funding-for-european-chip-co-euclyd-amid-memory-shortage</t>
+          <t>https://www.cnbctv18.com/market/aurobindo-pharma-gets-us-fda-nod-to-sell-first-metered-dose-asthma-inhaler-in-us-19990888.htm/amp</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>15-09-2026 08:38 UTC</t>
+          <t>15-09-2026 08:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Hetero Biopharma</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Z Fold 8 versus iPhone Duo: Nvidia chief Jensen Huang and Apple's John Ternus flaunt foldables</t>
+          <t>Freshers Job at Hetero | Microbiology Graduates Eligible | Apply Online</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>t2online.in</t>
+          <t>biotecnika.org</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://t2online.in/tech/tech-news/samsung-galaxy-z-fold-8-versus-iphone-duo--nvidia-chief-jensen-huang-and-apple-s-john-ternus-flaunt-foldables/2008020</t>
+          <t>https://www.biotecnika.org/2026/09/hetero-microbiology-job-freshers/</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>15-09-2026 09:17 UTC</t>
+          <t>15-09-2026 09:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Samsung's India public policy chief resigns, sources say</t>
+          <t>Shilpa Biologicals and SPIMACO Bio sign strategic license agreement for PD-1 Biosimilar for MENA market</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>BioSpectrum Asia</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/samsungs-india-public-policy-chief-resigns-sources-say-2026-09-15/</t>
+          <t>https://www.biospectrumasia.com/news/25/28379/shilpa-biologicals-and-spimaco-bio-sign-strategic-license-agreement-for-pd-1-biosimilar-for-mena-market.html</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>15-09-2026 06:23 UTC</t>
+          <t>16-09-2026 03:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>What Samsung's investment in Euclyd says about Europe's dominance</t>
+          <t>Shilpa Biologicals and SPIMACO Collaborate on PD-1 Biosimilar for MENA Market</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IO+</t>
+          <t>chemindigest.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://ioplus.nl/en/posts/what-samsungs-investment-in-euclyd-says-about-europes-dominance</t>
+          <t>https://chemindigest.com/shilpa-biologicals-and-spimaco-collaborate-on-pd-1-biosimilar-for-mena-market/</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>15-09-2026 12:33 UTC</t>
+          <t>16-09-2026 06:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A08 with 6000mAh battery announced</t>
+          <t>Complex-Molecule Specialist Shilpa CDMO Launches at CPHI Milan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FoneArena.com</t>
+          <t>contractpharma.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.fonearena.com/blog/492318/samsung-galaxy-a08-price-specifications.html</t>
+          <t>https://www.contractpharma.com/live_from_shows/complex-molecule-specialist-shilpa-cdmo-launches-at-cphi-milan/</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>15-09-2026 11:13 UTC</t>
+          <t>15-09-2026 19:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Verizon and Samsung trial AI-native ISAC sensing on vRAN</t>
+          <t>Shilpa Biologicals, SPIMACO sign MENA licensing deal for PD-1 biosimilars</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Telecoms Tech News</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.telecomstechnews.com/news/verizon-samsung-trial-ai-native-isac-sensing-on-vran/</t>
+          <t>https://www.indianpharmapost.com/biopharma/lite/shilpa-biologicals-spimaco-sign-mena-licensing-deal-for-pd-1-biosimilars-21860</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>15-09-2026 14:42 UTC</t>
+          <t>15-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Galaxy A18 Launches in Europe With Six Years of Updates</t>
+          <t>PI Industries Introduces CARVINT Insecticide in India</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AndroidPure</t>
+          <t>chemindigest.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.androidpure.com/galaxy-a18-europe-launch-six-years-updates/</t>
+          <t>https://chemindigest.com/pi-industries-introduces-carvint-insecticide-in-india/</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>15-09-2026 15:10 UTC</t>
+          <t>16-09-2026 06:29 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,22 +2785,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A18 Price and Specifications Reportedly Leaked Again Ahead of Expected Launch</t>
+          <t>More details about the Samsung Galaxy S27 Ultra's cameras emerge - GSMArena.com news</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-a18-4g-price-expected-specifications-leak-12048574</t>
+          <t>https://www.gsmarena.com/more_details_about_the_samsung_galaxy_s27_ultras_cameras_emerge-news-74633.php</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15-09-2026 09:18 UTC</t>
+          <t>15-09-2026 23:31 UTC</t>
         </is>
       </c>
     </row>
@@ -2812,22 +2812,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>I spent hours digging through obscure Samsung Galaxy features, and these 4 deserve more attention</t>
+          <t>From 253 Grams to 201 Grams: the World’s Lightest Fold</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>How-To Geek</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.howtogeek.com/i-spent-hours-digging-through-obscure-samsung-galaxy-features-these-4-deserve-more-attention/</t>
+          <t>https://news.samsung.com/au/from-253-grams-to-201-grams-the-worlds-lightest-fold</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>15-09-2026 14:00 UTC</t>
+          <t>16-09-2026 07:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2839,1183 +2839,1588 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Samsung opens registrations for 6th edition of Solve for Tomorrow: high school students invited to turn ideas into solutions</t>
+          <t>Samsung releases stable One UI 9.0 update for Galaxy S26 series</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Business Review</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://business-review.eu/education/samsung-opens-registrations-for-6th-edition-of-solve-for-tomorrow-high-school-students-invited-to-turn-ideas-into-solutions-300479</t>
+          <t>https://www.sammobile.com/news/galaxy-s26-stable-one-ui-9-0-update-released/</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>15-09-2026 14:37 UTC</t>
+          <t>16-09-2026 07:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Celltrion files for US phase 4 trial of 240 mg Zymfentra dose</t>
+          <t>Best Samsung foldable deal: Galaxy Z Fold 8 Ultra drops to $1,799.99</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33176</t>
+          <t>https://mashable.com/tech/sept-9-samsung-galaxy-z-fold-8-ultra-deal</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>15-09-2026 05:33 UTC</t>
+          <t>16-09-2026 03:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>South Korea's Celltrion Initiates U.S. Phase 4 Trial for High-Dose 240mg Zymfentra, Expanding Prescribing Options</t>
+          <t>Samsung Galaxy A18 4G is Official: Specs, Features, and Price</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Nokiamob</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/5d004363-4793-483d-96a1-283277b01391</t>
+          <t>https://nokiamob.net/2026/09/15/samsung-galaxy-a18-4g-price-and-specs-is-it-worth-the-upgrade/</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>15-09-2026 02:55 UTC</t>
+          <t>15-09-2026 17:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Celltrion Launches US Zymfentra High-Dose Trial</t>
+          <t>Samsung’s foldable lead faces the Apple test</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>theinvestor.co.kr</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=276960</t>
+          <t>https://www.theinvestor.co.kr/article/10875737</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>15-09-2026 03:11 UTC</t>
+          <t>16-09-2026 06:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Celltrion is launching phase 4 clinical trials in the U.S. to secure the basis for the high dose of</t>
+          <t>Samsung Galaxy A18 4G Is Now Official — Here Are Its Specs and Price</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>Android Headlines</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/en/it/12152917</t>
+          <t>https://www.androidheadlines.com/samsung-galaxy-a18-4g</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>15-09-2026 01:43 UTC</t>
+          <t>16-09-2026 03:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Celltrion Moves to Expand Zymfentra Use in the U.S. With New Phase 4 Trial</t>
+          <t>Galaxy S27 Ultra: Samsung To Change Screen After Three Years</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>koreaittimes.com</t>
+          <t>Forbes</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.koreaittimes.com/news/articleView.html?idxno=157163</t>
+          <t>https://www.forbes.com/sites/jaymcgregor/2026/09/15/samsung-galaxy-s27-ultra-leak-display-upgrade-galaxy-s27-pro-specs/</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>15-09-2026 01:25 UTC</t>
+          <t>15-09-2026 21:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Celltrion Advances High-Dose Clinical Trial for "Zymfentra" to Broaden U.S. Prescription Base</t>
+          <t>Samsung Galaxy A18 4G Launched With 50-Megapixel Main Camera, Exynos 1610 SoC: Price, Specifications</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026091509285390683</t>
+          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-a18-4g-price-launch-availability-specifications-features-12052999</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>15-09-2026 00:28 UTC</t>
+          <t>16-09-2026 06:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Chong Kun Dang Joins the SC Conversion Race... IP Competition Heats Up</t>
+          <t>Samsung Is Fast-Tracking Galaxy Z TriFold 2 After iPhone Duo Reveal, According to Leaks</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>CNET</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026091507340241619</t>
+          <t>https://www.cnet.com/tech/mobile/samsung-is-fast-tracking-galaxy-z-trifold-2-after-iphone-duo-reveal-according-to-leaks/</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>15-09-2026 01:35 UTC</t>
+          <t>15-09-2026 22:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Company (TSE:4568) Could Be 31% Below Fair Value As Legal Risk Clears</t>
+          <t>Aditya Babbar completes 15 years at Samsung Mobile</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>Exchange4Media</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/daiichi-sankyo-company-tse-4568-181153944.html</t>
+          <t>https://www.exchange4media.com/industry-briefing-news/aditya-babbar-completes-15-years-at-samsung-mobile-158286.html</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14-09-2026 18:11 UTC</t>
+          <t>16-09-2026 08:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Enhertu Shows Six-Month PFS Gain In HER2-Mutant Lung Cancer</t>
+          <t>Samsung Electronics chairman, Japanese lawmakers discuss AI, chip partnership</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BW Healthcare World</t>
+          <t>KED Global</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.bwhealthcareworld.com/article/enhertu-shows-six-month-pfs-gain-in-her2-mutant-lung-cancer-623644</t>
+          <t>https://www.kedglobal.com/korean-chipmakers/newsView/ked202609160008</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>15-09-2026 04:53 UTC</t>
+          <t>16-09-2026 06:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WCLC26: Enhertu's PFS lung cancer win comes with an OS question mark</t>
+          <t>How Samsung is Building a More Seamless AI Experience</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7990485</t>
+          <t>https://news.samsung.com/au/how-samsung-is-building-a-more-seamless-ai-experience</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>14-09-2026 22:36 UTC</t>
+          <t>16-09-2026 07:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>China approves third medical device standard for brain-computer interfaces</t>
+          <t>Android's solution to reduce motion sickness is rolling out to Galaxy phones</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Medical Buyer</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/china-approves-third-medical-device-standard-for-brain-computer-interfaces/</t>
+          <t>https://www.sammobile.com/news/galaxy-phones-reduce-motion-sickness-feature-released/</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>15-09-2026 02:23 UTC</t>
+          <t>15-09-2026 18:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Enhertu keeps first-line HER2-mutant lung cancer in check for six months longer — but early deaths run higher</t>
+          <t>Celltrion Repurchases KRW100 Billion in Shares</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dealroom</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://app.dealroom.co/news/note/enhertu-keeps-first-line-her2-mutant-lung-cancer-in-check-for-six-months-longer-but-early-deaths-run-higher</t>
+          <t>https://www.marketscreener.com/news/celltrion-repurchases-krw100-billion-in-shares-ce785bd2db8ef021</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>14-09-2026 19:17 UTC</t>
+          <t>16-09-2026 07:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BioNTech's Gotistobart Nearly Doubles Survival in Tough-to-Treat Lung Cancer</t>
+          <t>Zymfentra, Xcopri projected to become Korea’s 1st $1 billion blockbuster drugs in 2027</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/58aacd1d-d012-4a4c-ada4-4c419a170566</t>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33200</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>14-09-2026 18:38 UTC</t>
+          <t>16-09-2026 06:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Evoke-03’s miss raises bar for TROP2 ADCs in front-line NSCLC</t>
+          <t>Celltrion, SK Biopharmaceuticals Drugs Poised to Top ₩1 Trillion Each Next Year — South Korea's First Blockbusters in Sight</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>bioworld.com</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.bioworld.com/articles/734037-evoke-03s-miss-raises-bar-for-trop2-adcs-in-front-line-nsclc</t>
+          <t>https://finance.biggo.com/news/3a921a30-a622-4e22-bc3e-17f7934234eb</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>14-09-2026 16:00 UTC</t>
+          <t>16-09-2026 01:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Remedy Plan Therapeutics Announces Multiple Development and Corporate Milestones as First-In-Class Hyperbolic NAMPT Inhibitor, RPT1G, Advances in Phase 1 Dose Escalation Trial in AML/MDS</t>
+          <t>Celltrion Submits Phase 4 Trial Plan for Zymfentra</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.manilatimes.net/2026/09/15/tmt-newswire/globenewswire/remedy-plan-therapeutics-announces-multiple-development-and-corporate-milestones-as-first-in-class-hyperbolic-nampt-inhibitor-rpt1g-advances-in-phase-1-dose-escalation-trial-in-amlmds/2425375</t>
+          <t>https://www.thelec.net/news/articleView.html?idxno=13949</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15-09-2026 11:15 UTC</t>
+          <t>15-09-2026 22:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>China phase III trials make case for B7-H3 ADCs in relapsed SCLC</t>
+          <t>Celltrion to Cancel 100 Billion Won in Treasury Shares</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>bioworld.com</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.bioworld.com/articles/734038-china-phase-iii-trials-make-case-for-b7-h3-adcs-in-relapsed-sclc</t>
+          <t>https://en.sedaily.com/finance/2026/09/16/celltrion-to-cancel-100-billion-won-in-treasury-shares</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>14-09-2026 16:00 UTC</t>
+          <t>15-09-2026 23:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Exploring Daiichi Sankyo UK’s Impact on Cardiovascular and Oncology Care</t>
+          <t>Celltrion retires W100b in shares, pledges third of net profit to shareholders</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NewsHub.co.uk</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.newshub.co.uk/automotive/2026/09/15/exploring-daiichi-sankyo-uks-impact-on-cardiovascular-and-oncology-care/</t>
+          <t>https://mbiz.heraldcorp.com/article/10874870</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>15-09-2026 08:59 UTC</t>
+          <t>15-09-2026 23:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Crystalline Amino Acids Market To 2035: Feed Demand and High-Purity Grades Drive Growth - News and Statistics</t>
+          <t>South Korea's Celltrion Resolves to Retire ₩100 Billion in Treasury Shares; Full-Year Return Tops ₩200 Billion</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/crystalline-amino-acids-market-forecast-to-2035-demand-accelerates-on-animal-protein-expansion-and-specialty-grade-uptake/</t>
+          <t>https://finance.biggo.com/news/93eb049d-6238-433b-ab92-151e68e9dfa8</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>15-09-2026 11:41 UTC</t>
+          <t>16-09-2026 00:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[No. 243] Kenji Hagiwara</t>
+          <t>Celltrion cancels 540,000 shares, expands Korea buybacks to 200 billion won - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>keio.ac.jp</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.keio.ac.jp/en/st/campus-life/alumni_relay/2609/</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/16/7BIJI2VO4ZCB5PU5P3LGJWECKE/?outputType=amp</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>15-09-2026 03:41 UTC</t>
+          <t>15-09-2026 23:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Amgen vs. Vertex Pharmaceuticals: Value Stability vs. High-Growth Biotech Investment Plays</t>
+          <t>Celltrion to cancel $73 million in treasury shares</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NAI500</t>
+          <t>The Korea News Plus</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://nai500.com/blog/2026/09/amgen-vs-vertex-pharmaceuticals-value-stability-vs-high-growth-biotech-investment-plays/</t>
+          <t>https://www.newsarticleinsiders.com/news/articleView.html?idxno=4557</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15-09-2026 02:47 UTC</t>
+          <t>15-09-2026 23:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NIRF Pharmacy Ranking 2026; Check Top Pharmacy Colleges List</t>
+          <t>Zymfentra, Xcopri Set to Join Korea's First 1 Trillion Won Drug Club</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Shiksha.com</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.shiksha.com/medicine-health-sciences/articles/nirf-pharmacy-ranking-2026-check-top-pharmacy-colleges-list-blogId-241927</t>
+          <t>https://en.sedaily.com/finance/2026/09/16/zymfentra-xcopri-set-to-join-koreas-first-1-trillion-won</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>15-09-2026 11:58 UTC</t>
+          <t>16-09-2026 00:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GSK Pharma shareholders approve Karine Natland appointment as non-executive director</t>
+          <t>Zymfentra, Xcopri near Korea’s first blockbuster as sales surge past 1 trillion won - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/gsk-pharma-shareholders-approve-karine-natland-appointment-non/51003377</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/16/5DC4LLVP4FDENMPU7SIK7UBU3Q/?outputType=amp</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>15-09-2026 07:39 UTC</t>
+          <t>16-09-2026 00:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Contineum Thera down after depression drug miss</t>
+          <t>Korean Blockbuster Drugs 'On the Horizon': Zymfentra and Xcopri Race Towards Trillion-Won Sales</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>재경일보</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biotech-news/contineum-thera-down-after-depression-drug-miss</t>
+          <t>https://news.jkn.co.kr/post/987178</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>15-09-2026 08:25 UTC</t>
+          <t>15-09-2026 23:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FACT CHECK: Mike Rogers Repeatedly Voted for Higher Prescription Drug Costs and Healthcare Premiums for Michiganders</t>
+          <t>Celltrion Nears KRW 100 Billion Target in Treasury Share Buyback</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Michigan Democratic Party</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://michigandems.com/fact-check-mike-rogers-repeatedly-voted-for-higher-prescription-drug-costs-and-healthcare-premiums-for-michiganders/</t>
+          <t>https://www.tipranks.com/news/company-announcements/celltrion-nears-krw-100-billion-target-in-treasury-share-buyback</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>14-09-2026 21:05 UTC</t>
+          <t>15-09-2026 23:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GSK Pharma Shareholders Approve Board and Managing Director Appointments via Postal Ballot</t>
+          <t>AstraZeneca, Daiichi Sankyo’s ENHERTU Cuts Disease Progression Risk by 37% in HER2-Mutant Lung Cancer</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>BioPharma APAC</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/gsk-pharma-shareholders-approve-board-and-managing-director-appointments-via-postal-ballot</t>
+          <t>https://biopharmaapac.com/news/31/8438/astrazeneca-daiichi-sankyos-enhertu-cuts-disease-progression-risk-by-37-in-her2-mutant-lung-cancer.html</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>15-09-2026 08:02 UTC</t>
+          <t>16-09-2026 00:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Leading Biotech Selects Veeva Vault CRM Globally</t>
+          <t>Fortis Healthcare files Supreme Court petition against Delhi HC order</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/leading-biotech-selects-veeva-vault-110300562.html</t>
+          <t>https://scanx.trade/stock-market-news/companies/fortis-healthcare-files-supreme-court-petition-against-delhi-hc-order/51082591</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>15-09-2026 11:03 UTC</t>
+          <t>16-09-2026 05:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Delhi HC orders tax dept to refund ₹783 cr to Teva Israel over Ranbaxy payment</t>
+          <t>Fortis Healthcare Files Special Leave Petition Before Supreme Court Against Delhi HC Judgment</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>Sahi</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/companies/delhi-hc-tax-refund-to-teva-israel-ranbaxy-sun-pharma-income-tax-india-11789467986662.html</t>
+          <t>https://www.sahi.com/news/fortis-healthcare-files-special-leave-petition-before-supreme-court-against-delhi-hc-judgment</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>15-09-2026 11:06 UTC</t>
+          <t>16-09-2026 05:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>We're turning into a more innovative company: Teva Pharmaceuticals CEO Richard Francis</t>
+          <t>YES Bank challenges Delhi HC order on forensic audit in Fortis case in SC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>Medical Buyer</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/video/2026/09/14/were-turning-into-a-more-innovative-company-teva-pharmaceuticals-ceo-richard-francis.html</t>
+          <t>https://medicalbuyer.co.in/yes-bank-challenges-delhi-hc-order-on-forensic-audit-in-fortis-case-in-sc/</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>14-09-2026 18:58 UTC</t>
+          <t>16-09-2026 02:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tue: Enlight leads TASE lower - Globes</t>
+          <t>Fortis Healthcare moves Supreme Court against Delhi HC forensic audit order; Axis Bank may follow</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Globes - Israel Business News</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://en.globes.co.il/en/article-tue-enlight-leads-tase-lower-1001555561</t>
+          <t>https://m.economictimes.com/news/india/fortis-healthcare-moves-supreme-court-against-delhi-hc-forensic-audit-order-axis-bank-may-follow/amp_articleshow/134279742.cms</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>15-09-2026 15:26 UTC</t>
+          <t>16-09-2026 06:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Pearce IP BioBlast® for the fortnight ending 11 September 2026</t>
+          <t>Exploring Daiichi Sankyo UK’s Impact on Cardiovascular and Oncology Care</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pearce IP</t>
+          <t>NewsHub.co.uk</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://www.pearceip.law/2026/09/15/pearce-ip-bioblast-for-the-fortnight-ending-11-september-2026/</t>
+          <t>https://www.newshub.co.uk/automotive/2026/09/15/exploring-daiichi-sankyo-uks-impact-on-cardiovascular-and-oncology-care/</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>15-09-2026 05:30 UTC</t>
+          <t>15-09-2026 08:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Avaí Bio and Austrianova Complete Adventitious Agent Testing of Master Cell Bank, Establish Working Cell Bank for α-Klotho Anti-Aging Therapy</t>
+          <t>How Daiichi-Fortis ruling could hurt FDI</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>financialexpress.com</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/ava-bio-austrianova-complete-adventitious-124500596.html</t>
+          <t>https://www.financialexpress.com/opinion/how-daiichi-fortis-ruling-could-hurt-fdi/4339903/</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>15-09-2026 12:45 UTC</t>
+          <t>15-09-2026 16:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Chong Kun Dang Joins the SC Conversion Race... IP Competition Heats Up</t>
+          <t>Fortis Healthcare: Files Special Leave Petition in Supreme Court</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>investywise.com</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026091507340241619</t>
+          <t>https://www.investywise.com/fortis-healthcare-files-special-leave-petition/</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>15-09-2026 01:35 UTC</t>
+          <t>16-09-2026 05:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pfizer loses patent case over Enbrel generic</t>
+          <t>Fortis Forensic Audit Dispute Reaches Supreme Court as Yes Bank Challenges HC Order</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Lawyerly</t>
+          <t>urbanacres.in</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://www.lawyerly.com.au/pfizer-loses-patent-case-over-enbrel-generic/</t>
+          <t>https://urbanacres.in/fortis-forensic-audit-dispute-reaches-supreme-court-as-yes-bank-challenges-hc-order/</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>15-09-2026 07:27 UTC</t>
+          <t>15-09-2026 16:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Local Dispensary Named "Best in Central Illinois" for Third Straight Year</t>
+          <t>Yes Bank Challenges Supreme Court On Fortis Forensic Audit Order</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/local-dispensary-named-best-central-100000166.html</t>
+          <t>https://www.whalesbook.com/news/English/bankingfinance/Yes-Bank-Challenges-Supreme-Court-On-Fortis-Forensic-Audit-Order/6aa9aa040416c068539db4ff</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>15-09-2026 10:00 UTC</t>
+          <t>15-09-2026 21:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Samsung Biologics signs USD 262 million manufacturing agreement with European pharmaceutical company</t>
+          <t>Crystalline Amino Acids Market To 2035: Feed Demand and High-Purity Grades Drive Growth - News and Statistics</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Drug Discovery News</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://www.drugdiscoverynews.com/samsung-biologics-signs-usd-262-million-manufacturing-agreement-with-european-pharmaceutical-company-17527</t>
+          <t>https://www.indexbox.io/blog/crystalline-amino-acids-market-forecast-to-2035-demand-accelerates-on-animal-protein-expansion-and-specialty-grade-uptake/</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>14-09-2026 19:48 UTC</t>
+          <t>15-09-2026 11:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>An Integrated Analytical Approach To Lipase Risk Management In Biologics Development</t>
+          <t>Dr. Reddy’s Launches Cancer Drug Nivorz In India</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bioprocess Online</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://www.bioprocessonline.com/doc/an-integrated-analytical-approach-to-lipase-risk-management-in-biologics-development-0001</t>
+          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Launches-Cancer-Drug-Nivorz-In-India/6aa990790416c068539d68fc</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>15-09-2026 00:39 UTC</t>
+          <t>15-09-2026 21:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Samsung Biologics union's show of force backfires at the bargaining table</t>
+          <t>Successful Internal Audit Planning and Execution</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>PharmTech.com</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://mbiz.heraldcorp.com/article/10874287</t>
+          <t>http://www.pharmtech.com/view/successful-internal-audit-planning-and-execution</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>15-09-2026 06:25 UTC</t>
+          <t>15-09-2026 18:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>KOSPI falls for fourth session on foreign and institutional selling</t>
+          <t>NIRF Pharmacy Ranking 2026; Check Top Pharmacy Colleges List</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>디지털투데이</t>
+          <t>Shiksha.com</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://www.digitaltoday.co.kr/en/view/103708/kospi-falls-for-fourth-session-on-foreign-and-institutional-selling</t>
+          <t>https://www.shiksha.com/medicine-health-sciences/articles/nirf-pharmacy-ranking-2026-check-top-pharmacy-colleges-list-blogId-241927</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>15-09-2026 07:04 UTC</t>
+          <t>15-09-2026 11:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[Closing Market] KOSPI Retreats to 6,620 Mark Amid Stronger Dollar</t>
+          <t>Contineum Thera down after depression drug miss</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277008</t>
+          <t>https://www.thepharmaletter.com/biotech-news/contineum-thera-down-after-depression-drug-miss</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>15-09-2026 08:42 UTC</t>
+          <t>15-09-2026 08:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Samsung, SK Hynix Limit Pre-Market Losses Despite 5.86% Plunge in Philadelphia Semiconductor Index</t>
+          <t>J&amp;J’s Contineum-partnered depression drug flunks another phase 2 test</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Fierce Biotech</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/ccfd0caa-c0c1-43f1-80a4-b1aaf6a773d4</t>
+          <t>https://www.fiercebiotech.com/biotech/jjs-contineum-partnered-asset-flunks-another-phase-2-test</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>15-09-2026 00:35 UTC</t>
+          <t>15-09-2026 08:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>South Korean shares recoup early losses as chipmakers rebound</t>
+          <t>Leading Biotech Selects Veeva Vault CRM Globally</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Business Recorder</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://www.brecorder.com/news/amp/40439558</t>
+          <t>https://uk.finance.yahoo.com/news/leading-biotech-selects-veeva-vault-110300562.html</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>15-09-2026 05:50 UTC</t>
+          <t>15-09-2026 11:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Government Launches Korea Premium Weeks: Integrated Capital Market Event</t>
+          <t>Delhi HC orders tax dept to refund ₹783 cr to Teva Israel over Ranbaxy payment</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.chosun.com/english/market-money-en/2026/09/15/DSYD3II34FBQPMWS4EYZOCNMXI/</t>
+          <t>https://www.livemint.com/companies/delhi-hc-tax-refund-to-teva-israel-ranbaxy-sun-pharma-income-tax-india-11789467986662.html</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>15-09-2026 05:46 UTC</t>
+          <t>15-09-2026 11:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Tue: Enlight leads TASE lower - Globes</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Globes - Israel Business News</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://en.globes.co.il/en/article-tue-enlight-leads-tase-lower-1001555561</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>15-09-2026 15:26 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Laughter Really Is The Best Medicine</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Medscape</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://www.medscape.com/viewarticle/laughter-really-best-medicine-2026a1000xdh?src=</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>15-09-2026 19:46 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma receives US FDA nod for metered Beclomethasone Dipropionate aerosol</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/amp/markets/capital-market-news/aurobindo-pharma-receives-us-fda-nod-for-metered-beclomethasone-dipropionate-aerosol-126091500592_1.html</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>15-09-2026 09:21 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ukrainians warned of possible medicine shortages</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Новини аграрного бізнесу</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://agronews.ua/en/news/ukrainians-warned-of-possible-medicine-shortages/</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>15-09-2026 16:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>American Council of Learned Societies Announces Winners of 2026 ACLS Open Access Book Prizes and Arcadia Open Access Publishing Awards</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Singapore</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://sg.finance.yahoo.com/news/american-council-learned-societies-announces-231500703.html</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>15-09-2026 23:15 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Avaí Bio and Austrianova Complete Adventitious Agent Testing of Master Cell Bank, Establish Working Cell Bank for α-Klotho Anti-Aging Therapy</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Singapore</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://sg.finance.yahoo.com/news/ava-bio-austrianova-complete-adventitious-124500596.html</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>15-09-2026 12:45 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>BIX 2026 Names Canada as Country of Honor, Showcasing Bioindustry Trends from BCI to Biotech Foods</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>더바이오</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28154</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>15-09-2026 23:49 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Local Dispensary Named "Best in Central Illinois" for Third Straight Year</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Singapore</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://sg.finance.yahoo.com/news/local-dispensary-named-best-central-100000166.html</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>15-09-2026 10:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Europe Biosimilar Market Size and Outlook Report 2034 Halaman 1</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Kompasiana.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://www.kompasiana.com/yadwenderkumar9745/6aaa2ecec925c4173e22ced9/europe-biosimilar-market-size-and-outlook-report-2034</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>16-09-2026 05:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Dr. Reddy’s Launches Cancer Drug Nivorz In India</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Whalesbook</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Launches-Cancer-Drug-Nivorz-In-India/6aa990790416c068539d68fc</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>15-09-2026 21:56 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Controlling Complexity In ADC Formulation Development</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Bioprocess Online</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>https://www.bioprocessonline.com/doc/controlling-complexity-in-adc-formulation-development-0001</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>15-09-2026 00:38 UTC</t>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Semiconductor rebound lifts KOSPI 1.37 percent, back above 6,700</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>디지털투데이</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://www.digitaltoday.co.kr/en/view/104340/semiconductor-rebound-lifts-kospi-1-37-percent-back-above-6700</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>16-09-2026 07:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>The KOSPI, which has been on a downward trend in recent days, started falling on the 16th, but close..</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>매일경제</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/en/stock/12154354</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>16-09-2026 07:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Axiom, GeneFab Partner to Advance Therapeutic Pipeline</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>contractpharma.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://www.contractpharma.com/breaking-news/axiom-genefab-partner-to-advance-therapeutic-pipeline/</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>15-09-2026 16:46 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>South Korean shares rise as chipmakers gain ahead of Fed outcome</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Business Recorder</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://www.brecorder.com/news/amp/40439737</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>16-09-2026 05:33 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>55 Listed Companies Join Korea Premium Weeks 2026 Starting Sept. 28</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Businesskorea</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277063</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>16-09-2026 01:55 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>[Closing Market] KOSPI Retreats to 6,620 Mark Amid Stronger Dollar</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Businesskorea</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277008</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>15-09-2026 08:42 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz issues 500 million euros bond to extend debt maturity profile</t>
+          <t>Sandoz Appoints Ha Vo as General Manager, Vietnam</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/generics-news/sandoz-issues-500-million-euros-bond-to-extend-debt-maturity-profile</t>
+          <t>https://hrtoday.in/sandoz-appoints-ha-vo-as-general-manager-vietnam/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15-09-2026 22:14 UTC</t>
+          <t>16-09-2026 12:54 UTC</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sandoz pays up for duration in €500m trade</t>
+          <t>Sandoz issues 500 million euros bond to extend debt maturity profile</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Global Capital</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.globalcapital.com/article/2gw8sima1juifixzkivi8/corporate-bonds/high-grade-and-crossover-bonds/sandoz-pays-up-for-duration-in-500m-trade</t>
+          <t>https://www.thepharmaletter.com/generics-news/sandoz-issues-500-million-euros-bond-to-extend-debt-maturity-profile</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15-09-2026 15:48 UTC</t>
+          <t>15-09-2026 22:14 UTC</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Norma Stoeger Obituary (1938 - 2026) - Valentine, NE - North Platte Telegraph</t>
+          <t>Sandoz pays up for duration in €500m trade</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Legacy obituary</t>
+          <t>Global Capital |</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.legacy.com/us/obituaries/nptelegraph/name/norma-stoeger-obituary?id=62435196</t>
+          <t>https://www.globalcapital.com/article/2gw8sima1juifixzkivi8/corporate-bonds/high-grade-and-crossover-bonds/sandoz-pays-up-for-duration-in-500m-trade</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16-09-2026 05:41 UTC</t>
+          <t>15-09-2026 15:48 UTC</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Egypt reports sharp decline in child anaemia, stunting rates</t>
+          <t>Norma Stoeger Obituary (1938 - 2026) - Valentine, NE - North Platte Telegraph</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dailynewsegypt</t>
+          <t>Legacy obituary</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.dailynewsegypt.com/2026/09/15/egypt-reports-sharp-decline-in-child-anaemia-stunting-rates/</t>
+          <t>https://www.legacy.com/us/obituaries/nptelegraph/name/norma-stoeger-obituary?id=62435196</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15-09-2026 18:48 UTC</t>
+          <t>16-09-2026 05:41 UTC</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Child anaemia falls to 8%, stunting to 4% in Egypt - Health - Egypt</t>
+          <t>Egypt reports sharp decline in child anaemia, stunting rates</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ahram Online</t>
+          <t>Dailynewsegypt</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://english.ahram.org.eg/NewsContent/1/1236/576675/Egypt/Health/Child-anaemia-falls-to-,-stunting-to--in-Egypt.aspx</t>
+          <t>https://www.dailynewsegypt.com/2026/09/15/egypt-reports-sharp-decline-in-child-anaemia-stunting-rates/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15-09-2026 09:00 UTC</t>
+          <t>15-09-2026 18:48 UTC</t>
         </is>
       </c>
     </row>
@@ -598,76 +598,76 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Robert Gerald Engstrom Obituary (2026) - Hendersonville, NC - Church Street Funeral &amp; Cremation - Hendersonville</t>
+          <t>Parmigiani Fleurier commemorates thirty years of horological mastery with the Mechanical Wonders exhibition in Tokyo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Legacy obituary</t>
+          <t>senatus.net</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.legacy.com/us/obituaries/name/robert-engstrom-obituary?id=62434785</t>
+          <t>https://senatus.net/album/view/17714/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16-09-2026 02:57 UTC</t>
+          <t>16-09-2026 14:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boehringer provides update on EASi-KIDNEY trial</t>
+          <t>Robert Gerald Engstrom Obituary (2026) - Hendersonville, NC - Church Street Funeral &amp; Cremation - Hendersonville</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Legacy obituary</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.boehringer-ingelheim.com/human-health/boehringer-provides-update-easi-kidney-trial</t>
+          <t>https://www.legacy.com/us/obituaries/name/robert-engstrom-obituary?id=62434785</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15-09-2026 10:30 UTC</t>
+          <t>16-09-2026 02:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Webinar: Immunosuppression: Consequences for the bird and farmer</t>
+          <t>OneSource Specialty Pharma Q1FY27 revenue up 37%, EBITDA surges 39%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WATTPoultry.com</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.wattagnet.com/webinars/webinar/15834930/boehringer-ingelheim-webinar-immunosuppression-consequences-for-the-bird-and-farmer</t>
+          <t>https://scanx.trade/stock-market-news/companies/onesource-specialty-pharma-to-discuss-q1fy27-results-on-jul-25/46162875</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15-09-2026 20:59 UTC</t>
+          <t>15-09-2026 18:46 UTC</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sugar Clinics: A One-Stop Shop for Improved Diabetes Care in Mexico</t>
+          <t>Vicadrostat EASi-KIDNEY Trial Discontinued for Lack of Benefit in CKD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>StreetInsider</t>
+          <t>HCPLive</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.streetinsider.com/ACCESS+Newswire/Sugar+Clinics%3A+A+One-Stop+Shop+for+Improved+Diabetes+Care+in+Mexico/27063162.html</t>
+          <t>https://www.hcplive.com/view/vicadrostat-easi-kidney-trial-discontinued-for-lack-of-benefit-in-ckd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15-09-2026 14:37 UTC</t>
+          <t>15-09-2026 22:42 UTC</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vicadrostat EASi-KIDNEY Trial Discontinued for Lack of Benefit in CKD</t>
+          <t>Webinar: Immunosuppression: Consequences for the bird and farmer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HCPLive</t>
+          <t>WATTPoultry.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.hcplive.com/view/vicadrostat-easi-kidney-trial-discontinued-for-lack-of-benefit-in-ckd</t>
+          <t>https://www.wattagnet.com/webinars/webinar/15834930/boehringer-ingelheim-webinar-immunosuppression-consequences-for-the-bird-and-farmer</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15-09-2026 22:42 UTC</t>
+          <t>15-09-2026 20:59 UTC</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The Clinical Trial Vanguard</t>
+          <t>clinicaltrialvanguard.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Genexine’s GX-BP1 (SOX2 bioPROTAC) Suppresses Tumor Regrowth despite Osimertinib and Dato-DXd Combination and Achieves 6/6 Complete Responses in Triple Combination</t>
+          <t>Lilly backs Circle's latest fundraising as second cancer drug progresses towards clinic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/genexine-gx-bp1-sox2-bioprotac-091600149.html</t>
+          <t>https://firstwordpharma.com/story/7996747</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15-09-2026 09:16 UTC</t>
+          <t>16-09-2026 12:29 UTC</t>
         </is>
       </c>
     </row>
@@ -814,103 +814,103 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Study shows how changes in prefontal brain activity can impair the ability to change behaviour</t>
+          <t>Zealand Pharma out-licenses GLP-1/gastrin peptide platform to Elvinix for regenerative type 1 diabetes therapy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>University of Nottingham</t>
+          <t>app.dealroom.co</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.nottingham.ac.uk/news/study-shows-how-changes-in-prefontal-brain-activity-can-impair-the-ability-to-change-behaviour</t>
+          <t>https://app.dealroom.co/news/note/zealand-pharma-out-licenses-glp-1-gastrin-peptide-platform-to-elvinix-for-regenerative-type-1-diabetes-therapy</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15-09-2026 09:09 UTC</t>
+          <t>15-09-2026 15:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bristol Myers sues Amgen over proposed Opdivo biosimilar</t>
+          <t>Interstitial Lung Disease Market to Grow from USD 6 Billion at a CAGR of 8.7% Through 2036</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/litigation/bristol-myers-sues-amgen-over-proposed-opdivo-biosimilar-2026-09-15/</t>
+          <t>https://www.openpr.com/news/4632856/interstitial-lung-disease-market-to-grow-from-usd-6-billion-at</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15-09-2026 20:25 UTC</t>
+          <t>16-09-2026 07:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FDA reduces initial monitoring time for Amgen’s Imdelltra</t>
+          <t>Europe Biosimilar Market Size and Outlook Report 2034 Halaman 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Kompasiana.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/regulatory/fda-reduces-initial-monitoring-time-for-amgens-imdelltra-21863</t>
+          <t>https://www.kompasiana.com/yadwenderkumar9745/6aaa2ecec925c4173e22ced9/europe-biosimilar-market-size-and-outlook-report-2034</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16-09-2026 02:37 UTC</t>
+          <t>16-09-2026 05:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amgen to deploy Veeva Vault CRM globally to spe...</t>
+          <t>Iron Sucrose Market Set to Surpass USD 796.4 Million by 2033,</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/biotek-terkemuka-pilih-veeva-vault-crm-global</t>
+          <t>https://www.openpr.com/news/4632934/iron-sucrose-market-set-to-surpass-usd-796-4-million-by-2033</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15-09-2026 11:29 UTC</t>
+          <t>16-09-2026 08:14 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amgen Highlights MariTide, IMDELLTRA Pipeline Progress and Growth Priorities</t>
+          <t>BMS, Ono take Amgen to task as FDA's Opdivo biosimilar decision looms</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>finance.yahoo.com</t>
+          <t>fiercepharma.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/amgen-highlights-maritide-imdelltra-pipeline-050213898.html</t>
+          <t>https://www.fiercepharma.com/pharma/bms-ono-take-amgen-task-fdas-opdivo-biosimilar-decision-looms</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16-09-2026 05:02 UTC</t>
+          <t>16-09-2026 15:08 UTC</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FDA reduces monitoring time for Amgen’s Imdelltra infusions</t>
+          <t>Bristol Myers sues Amgen over proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pharmaceutical Technology</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pharmaceutical-technology.com/news/fda-reduces-monitoring-time-amgens-imdelltra/</t>
+          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/bristol-myers-sues-amgen-over-proposed-opdivo-biosimilar/134282973</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15-09-2026 10:49 UTC</t>
+          <t>16-09-2026 08:46 UTC</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bristol-Myers Targets Amgen’s Opdivo Biosimilar in Patent Suit</t>
+          <t>FDA cuts monitoring time for first two doses of Amgen’s IMDELLTRA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bloomberg Law News</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.bloomberglaw.com/ip-law/bristol-myers-targets-amgens-opdivo-biosimilar-in-patent-suit</t>
+          <t>https://www.indianpharmapost.com/regulatory/fda-cuts-monitoring-time-for-first-two-doses-of-amgens-imdelltra-21872</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15-09-2026 17:06 UTC</t>
+          <t>16-09-2026 12:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Skorney: Novartis's Lp(a) Miss Exposes a Modeling Flaw That Now Threatens Amgen and Lilly</t>
+          <t>Bristol Myers sues Amgen over proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/1c49c250a2209ff1</t>
+          <t>https://www.reuters.com/legal/litigation/bristol-myers-sues-amgen-over-proposed-opdivo-biosimilar-2026-09-15/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15-09-2026 17:08 UTC</t>
+          <t>15-09-2026 20:25 UTC</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Leading Biotech Selects Veeva Vault CRM Globally</t>
+          <t>Amgen Highlights MariTide, IMDELLTRA Pipeline Progress and Growth Priorities</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>finance.yahoo.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/leading-biotech-selects-veeva-vault-crm-globally-302878548.html</t>
+          <t>https://finance.yahoo.com/healthcare/articles/amgen-highlights-maritide-imdelltra-pipeline-050213898.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15-09-2026 11:03 UTC</t>
+          <t>16-09-2026 05:02 UTC</t>
         </is>
       </c>
     </row>
@@ -1057,292 +1057,292 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FDA Approves Shorter Monitoring for First Two Tarlatamab Doses in ES-SCLC</t>
+          <t>FDA reduces monitoring time for Amgen’s Imdelltra infusions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CancerNetwork</t>
+          <t>Pharmaceutical Business review -</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.cancernetwork.com/view/fda-approves-shorter-monitoring-for-first-two-tarlatamab-doses-in-es-sclc</t>
+          <t>https://www.pharmaceutical-business-review.com/news/fda-reduces-monitoring-time-amgens-imdelltra/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15-09-2026 16:09 UTC</t>
+          <t>15-09-2026 16:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Boryung, Organon Korea Team Up on Cholesterol Drug Atozet</t>
+          <t>FDA reduces initial monitoring time for Amgen’s Imdelltra</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>en.sedaily.com</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/culture/2026/09/16/boryung-organon-korea-team-up-on-cholesterol-drug-atozet</t>
+          <t>https://www.indianpharmapost.com/news/fda-reduces-initial-monitoring-time-for-amgens-imdelltra-21863</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16-09-2026 01:48 UTC</t>
+          <t>16-09-2026 03:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Boryung to Take Charge of Domestic Sales and Marketing for 'Atojet'... Expanding Presence in the Dyslipidemia Market</t>
+          <t>DP World Tour unveils 2027 schedule</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Golf Business News</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026091615093005618</t>
+          <t>https://golfbusinessnews.com/news/sponsorship-and-events/dp-world-tour-unveils-2027-schedule/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16-09-2026 06:09 UTC</t>
+          <t>16-09-2026 11:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HNLU Labour Law Students Visit Bhilai Steel Plant To Gain Practical Exposure To Industrial Operations And ...</t>
+          <t>Bristol-Myers Targets Amgen’s Opdivo Biosimilar in Patent Suit</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Live Law</t>
+          <t>Bloomberg Law News</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.livelaw.in/amp/lawschool/news/hnlu-labour-law-students-visit-bhilai-steel-plant-550211</t>
+          <t>https://news.bloomberglaw.com/ip-law/bristol-myers-targets-amgens-opdivo-biosimilar-in-patent-suit</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16-09-2026 04:45 UTC</t>
+          <t>15-09-2026 17:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Attackers Exploit WooCommerce Wholesale Lead Capture Flaw to Plant PHP Web Shells</t>
+          <t>DoP Secretary Manoj Joshi visits Amneal Pharmaceuticals</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>thehackernews.com</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://thehackernews.com/2026/09/attackers-exploit-woocommerce-wholesale.html</t>
+          <t>https://www.indianpharmapost.com/news/dop-secretary-manoj-joshi-visits-amneal-pharmaceuticals-21865</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16-09-2026 05:48 UTC</t>
+          <t>16-09-2026 10:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>In 2017, a fully automated facility for plant bioscience research was launched to the International Space</t>
+          <t>Boryung and Korea Organon join to market Atozet for dyslipidemia in Korea - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/international/us/science-in-2017-a-fully-automated-facility-for-plant-bioscience-research-was-launched-to-the-international-space-station-what-nasa-studied-in-space/articleshow/134275632.cms</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/16/XIBOSIHBPRGKPAZEWREFTCCMLQ/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16-09-2026 00:13 UTC</t>
+          <t>16-09-2026 08:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NSF Study Aims to Reveal How Plants Sense, Respond to Heat</t>
+          <t>Boryung, Organon Korea Team Up on Cholesterol Drug Atozet</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>University of Mississippi | Ole Miss</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://olemiss.edu/news/2026/09/nsf-study-aims-to-reveal-how-plants-sense-respond-to-heat/index.html</t>
+          <t>https://en.sedaily.com/culture/2026/09/16/boryung-organon-korea-team-up-on-cholesterol-drug-atozet</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15-09-2026 15:03 UTC</t>
+          <t>16-09-2026 01:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Automated Snack Formers Market Size, Share &amp; Forecast 2036</t>
+          <t>PhaseV Appoints Biopharma Leaders Klaus Beck and Avi Kulkarni to Scientific Advisory Board to Guide Expansion of AI Conductor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fact.MR</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.factmr.com/report/automated-snack-formers-market</t>
+          <t>https://www.prnewswire.com/il/news-releases/phasev-appoints-biopharma-leaders-klaus-beck-and-avi-kulkarni-to-scientific-advisory-board-to-guide-expansion-of-ai-conductor-302880241.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15-09-2026 12:37 UTC</t>
+          <t>16-09-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Barhale completes Anglian Water’s first plant tackling emerging contaminant Cypermethrin</t>
+          <t>Sandoz Appoints Ha Vo as General Manager, Vietnam</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Water Magazine</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.watermagazine.co.uk/2026/09/16/barhale-completes-anglian-waters-first-plant-tackling-emerging-contaminant-cypermethrin/</t>
+          <t>https://hrtoday.in/sandoz-appoints-ha-vo-as-general-manager-vietnam/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16-09-2026 04:00 UTC</t>
+          <t>16-09-2026 12:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>This Australian cave hid 25,000 years of ritual secrets</t>
+          <t>Boryung to Take Charge of Domestic Sales and Marketing for 'Atojet'... Expanding Presence in the Dyslipidemia Market</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ScienceDaily</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.sciencedaily.com/releases/2026/09/260914102443.htm</t>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026091615093005618</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15-09-2026 14:52 UTC</t>
+          <t>16-09-2026 06:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>These Plants Have a Protein-Packed Diet, Too</t>
+          <t>Apotex Joins National "Hope Alliance" Campaign to Support Uninsured Patients</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/09/07/style/carnivorous-houseplants-venus-flytrap-pitcher-plant.html</t>
+          <t>https://www.prnewswire.com/news-releases/apotex-joins-national-hope-alliance-campaign-to-support-uninsured-patients-302879290.html</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>15-09-2026 23:29 UTC</t>
+          <t>16-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>How soybeans took over the American diet without anyone noticing</t>
+          <t>Pharmaceutical Manufacturing Plant Setup in India</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>IMARC Group</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.washingtonpost.com/ripple/2026/09/11/how-soybeans-took-over-the-american-diet-without-anyone-noticing/</t>
+          <t>https://www.imarcgroup.com/insight/pharmaceutical-manufacturing-plant-setup-cost-india</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>15-09-2026 19:02 UTC</t>
+          <t>16-09-2026 12:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tungsten West advances Hemerdon restart with TOMRA Mining sorting tech a key component of redesigned plant</t>
+          <t>The East African Community Seed and Plant Varieties Bill, 2025 must protect the Farmers and Seed Systems that feed the region</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>International Mining</t>
+          <t>greenpeace.org</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://im-mining.com/2026/09/15/tungsten-west-advances-hemerdon-restart-with-tomra-mining-sorting-tech-a-key-component-of-redesigned-plant/</t>
+          <t>https://www.greenpeace.org/africa/en/op-ed/61603/the-east-african-community-seed-and-plant-varieties-bill-2025-must-protect-the-farmers-and-seed-systems-that-feed-the-region/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>15-09-2026 13:16 UTC</t>
+          <t>16-09-2026 13:17 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Iron overload: how tea, coffee, red meat and alcohol can affect absorption</t>
+          <t>HNLU Labour Law Students Visit Bhilai Steel Plant To Gain Practical Exposure To Industrial Operations And ...</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>The Conversation</t>
+          <t>Live Law</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://theconversation.com/iron-overload-how-tea-coffee-red-meat-and-alcohol-can-affect-absorption-289770</t>
+          <t>https://www.livelaw.in/amp/lawschool/news/hnlu-labour-law-students-visit-bhilai-steel-plant-550211</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15-09-2026 13:16 UTC</t>
+          <t>16-09-2026 04:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>True Form Ss Keto Gummies Reviews: A Realistic, Hands On Assessment [oOYQPSvW76t]</t>
+          <t>Can plant-based omega-3s really protect your heart?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>santeestrie.qc.ca</t>
+          <t>futura-sciences.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.santeestrie.qc.ca/typo3conf/ext/wrs_pannellum/Resources/Public/Vendor/pannellum/pannellum.htm?config=/%5C/video.unkk.top/panketo2/oOYQPSvW76t</t>
+          <t>https://www.futura-sciences.com/en/doctors-stunned-these-2-omega-3-foods-could-dramatically-protect-your-arteries_900009/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16-09-2026 06:57 UTC</t>
+          <t>16-09-2026 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,562 +1462,562 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Native Plant Communities: Salt Marshes</t>
+          <t>Trees Can Tell When They’re Crooked and Grow Special Wood to Straighten Themselves</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Maine Audubon</t>
+          <t>ZME Science</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://maineaudubon.org/news/native-plant-communities-salt-marshes/</t>
+          <t>https://www.zmescience.com/science/biology/trees-correct-posture</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>15-09-2026 19:08 UTC</t>
+          <t>16-09-2026 13:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pfizer – Every Insight Matters – HCP (Information from Industry)</t>
+          <t>Skanska starts work on Nowy Format office complex in Poland</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DocWireNews</t>
+          <t>World Construction Network</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.docwirenews.com/videos/pfizer-every-insight-matters-hcp-information-from-industry-breast-summit</t>
+          <t>https://www.worldconstructionnetwork.com/news/skanska-starts-work-nowy-format/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>15-09-2026 19:22 UTC</t>
+          <t>16-09-2026 10:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Two structural columns buckled on the 21st floor of the former Pfizer headquarters during its conversion into about 1,600 apartments. The failure prompted New York City to widen inspections, and work was subsequently halted at other Manhattan office-to-resi</t>
+          <t>Attackers Exploit WooCommerce Wholesale Lead Capture Flaw to Plant PHP Web Shells</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ScienceBlog.com</t>
+          <t>The Hacker News</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://scienceblog.com/m-two-structural-columns-buckled-on-the-21st-floor-of-the-former-pfizer-headquarters-during-its-conversion-into-about-1-600-apartments-the-failure-prompted-new-york-city-to-widen-ins/</t>
+          <t>https://thehackernews.com/2026/09/attackers-exploit-woocommerce-wholesale.html</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15-09-2026 22:03 UTC</t>
+          <t>16-09-2026 05:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pfizer Invites Public to Listen to Webcast of Pfizer Discussion at Healthcare Conference</t>
+          <t>Plant Defies Inheritance: Sex Without Shuffle</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>finance.yahoo.com</t>
+          <t>miragenews.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/pfizer-invites-public-listen-webcast-140000774.html</t>
+          <t>https://www.miragenews.com/plant-defies-inheritance-sex-without-shuffle-1745432/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>15-09-2026 14:00 UTC</t>
+          <t>16-09-2026 15:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>John Dorfman: CEOs buy shares at Pfizer, Uber</t>
+          <t>In 2017, a fully automated facility for plant bioscience research was launched to the International Space</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TribLIVE.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://community.triblive.com/news/4140336</t>
+          <t>https://m.economictimes.com/news/international/us/science-in-2017-a-fully-automated-facility-for-plant-bioscience-research-was-launched-to-the-international-space-station-what-nasa-studied-in-space/articleshow/134275632.cms</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>16-09-2026 01:57 UTC</t>
+          <t>16-09-2026 00:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Before Karnataka police busted counterfeit medicine racket, CDSCO had sought regulation of pharma packaging suppliers</t>
+          <t>Barhale completes Anglian Water’s first plant tackling emerging contaminant Cypermethrin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>The South First</t>
+          <t>watermagazine.co.uk</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://thesouthfirst.com/health/before-karnataka-police-busted-counterfeit-medicine-racket-cdsco-had-sought-regulation-of-pharma-packaging-suppliers/</t>
+          <t>https://www.watermagazine.co.uk/2026/09/16/barhale-completes-anglian-waters-first-plant-tackling-emerging-contaminant-cypermethrin/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>16-09-2026 01:32 UTC</t>
+          <t>16-09-2026 04:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pfizer (Backpack Securities) to British Pound Sterling Price Today | Live PFE to GBP Converter &amp; Exchange Rate</t>
+          <t>These Plants Have a Protein-Packed Diet, Too</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CryptoRank</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://cryptorank.io/price/pfizer-backpack-securities/gbp</t>
+          <t>https://www.nytimes.com/2026/09/07/style/carnivorous-houseplants-venus-flytrap-pitcher-plant.html</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>15-09-2026 18:22 UTC</t>
+          <t>15-09-2026 20:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Eisai and Biogen Announce Japan Approval of LEQEMBI Pen, a Once-Weekly Subcutaneous Alzheimer’s Treatment</t>
+          <t>Hastings apartment building reopens after ricin exposure</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Quiver Quantitative</t>
+          <t>Lansing State Journal</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.quiverquant.com/news/Eisai+and+Biogen+Announce+Japan+Approval+of+LEQEMBI+Pen%2C+a+Once-Weekly+Subcutaneous+Alzheimer%E2%80%99s+Treatment</t>
+          <t>https://www.lansingstatejournal.com/story/news/local/michigan/2026/09/16/ricin-hastings-apartment-complex-mdhhs/91789647007/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16-09-2026 06:10 UTC</t>
+          <t>16-09-2026 14:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Viatris-Mylan</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LEQEMBI® Pen (Subcutaneous Formulation of LEQEMBI®)</t>
+          <t>Gilead expands lenacapavir licensing to cover once-yearly HIV prevention</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>StreetInsider</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/09/16/3362836/0/en/leqembi-pen-subcutaneous-formulation-of-leqembi-approved-in-japan-for-the-treatment-of-early-alzheimer-s-disease.html</t>
+          <t>https://www.streetinsider.com/Corporate+News/Gilead+expands+lenacapavir+licensing+to+cover+once-yearly+HIV+prevention/27067898.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16-09-2026 06:00 UTC</t>
+          <t>16-09-2026 12:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Canada agrees to help pay for Alzheimer’s drug LEQEMBI</t>
+          <t>Pfizer follows AstraZeneca in pulling EU bladder cancer filing after CHMP concerns</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Longevity.Technology</t>
+          <t>allsci.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://longevity.technology/news/canada-agrees-to-help-pay-for-alzheimers-drug-leqembi/</t>
+          <t>https://allsci.com/news/regulatory/zumrad-eu-application-pfizer-withdraws-zumrads/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>15-09-2026 23:10 UTC</t>
+          <t>16-09-2026 11:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fianna Fáil says reimbursement for Friedreich's ataxia drug to be in place from 1 October</t>
+          <t>Pfizer – Every Insight Matters – HCP (Information from Industry)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>The Journal</t>
+          <t>DocWireNews</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.thejournal.ie/skyclarys-reimbursement-ireland-7163736-Sep2026/</t>
+          <t>https://www.docwirenews.com/videos/pfizer-every-insight-matters-hcp-information-from-industry-breast-summit</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15-09-2026 20:31 UTC</t>
+          <t>15-09-2026 19:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s forays into India’s biosimilar immuno-oncology market, launches Nivorz</t>
+          <t>IP Group: NAV Reaches £1 Billion As Pfizer Obesity Royalty Value Rises To £152 Million</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Pulse 2.0</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/dr-reddys-forays-into-indias-biosimilar-immuno-oncology-market-launches-nivorz/article71469381.ece</t>
+          <t>https://pulse2.com/ip-group-nav-reaches-1-billion-as-pfizer-obesity-royalty-value-rises-to-152-million/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>15-09-2026 16:03 UTC</t>
+          <t>16-09-2026 13:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Laboratories launches NIVORZ in India</t>
+          <t>Pfizer Invites Public to Listen to Webcast of Pfizer Discussion at Healthcare Conference - September 15, 2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.expresspharma.in/dr-reddys-laboratories-launches-nivorz-in-india/</t>
+          <t>https://www.biospace.com/press-releases/pfizer-invites-public-to-listen-to-webcast-of-pfizer-discussion-at-healthcare-conference-september-15-2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>15-09-2026 11:42 UTC</t>
+          <t>16-09-2026 02:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Laboratories launches Nivorz in India</t>
+          <t>Sourabh Pandey Appointed Senior Director, Commercial AI at Pfizer</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>thehindubusinessline.com</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/dr-reddys-laboratories-launches-nivorz-in-india/article71467764.ece</t>
+          <t>https://hrtoday.in/sourabh-pandey-appointed-senior-director-commercial-ai-at-pfizer/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>15-09-2026 11:08 UTC</t>
+          <t>16-09-2026 09:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Buy, Sell Or Hold: Dr Reddy's Labs, BEL, L&amp;T, HDFC Bank, Welspun Corp And Canara Bank — Ask Profit</t>
+          <t>What is Pfizer rStock | How RPFE Works, Use Cases and Values | MEXC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>MEXC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.ndtvprofit.com/markets/buy-sell-or-hold-dr-reddys-labs-bel-l-t-hdfc-bank-welspun-corp-and-canara-bank-ask-profit-12051254</t>
+          <t>https://www.mexc.co/en-PH/price/pfizer-rstock/info</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15-09-2026 17:07 UTC</t>
+          <t>16-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dr Reddy’s launches cancer blockbuster nivolumab biosimilar in India</t>
+          <t>Fake-drug racket suspect holed up in Azerbaijan, Karnataka mulls CBI probe</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>The Indian Express</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/news/drug-approvals-and-launches/dr-reddys-launches-cancer-blockbuster-nivolumab-biosimilar-in-india/134262279</t>
+          <t>https://indianexpress.com/article/cities/bangalore/bidadi-fake-drug-racket-karnataka-cbi-probe-azerbaijan-link-10880597/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>15-09-2026 12:38 UTC</t>
+          <t>16-09-2026 10:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dr Reddy’s launches Opdivo biosimilar Nivorz in India, enters immuno-oncology segment</t>
+          <t>Two structural columns buckled on the 21st floor of the former Pfizer headquarters during its conversion into about 1,600 apartments. The failure prompted New York City to widen inspections, and work was subsequently halted at other Manhattan office-to-resi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>ScienceBlog.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/dr-reddy-s-launches-opdivo-biosimilar-nivorz-in-india-enters-immuno-oncology-segment-14030366.html</t>
+          <t>https://scienceblog.com/m-two-structural-columns-buckled-on-the-21st-floor-of-the-former-pfizer-headquarters-during-its-conversion-into-about-1-600-apartments-the-failure-prompted-new-york-city-to-widen-ins/</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>15-09-2026 12:06 UTC</t>
+          <t>15-09-2026 22:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s launches nivolumab biosimilar NIVORZ in India</t>
+          <t>Before Karnataka police busted counterfeit medicine racket, CDSCO had sought regulation of pharma packaging suppliers</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>The South First</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/dr-reddys-launches-nivolumab-biosimilar-nivorz-in-india-21853</t>
+          <t>https://thesouthfirst.com/health/before-karnataka-police-busted-counterfeit-medicine-racket-cdsco-had-sought-regulation-of-pharma-packaging-suppliers/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>15-09-2026 11:56 UTC</t>
+          <t>16-09-2026 01:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dr Reddy’s forays into Indian biosimilar immuno-oncology market</t>
+          <t>Eisai and Biogen Announce Japan Approval of LEQEMBI Pen, a Once-Weekly Subcutaneous Alzheimer’s Treatment</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Quiver Quantitative</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/dr-reddys-forays-into-indian-biosimilar-immuno-oncology-market/articleshow/134268510.cms</t>
+          <t>https://www.quiverquant.com/news/Eisai+and+Biogen+Announce+Japan+Approval+of+LEQEMBI+Pen%2C+a+Once-Weekly+Subcutaneous+Alzheimer%E2%80%99s+Treatment</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>15-09-2026 16:04 UTC</t>
+          <t>16-09-2026 06:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dr. Reddy's launches nivolumab biosimilar in India</t>
+          <t>LEQEMBI® Pen (Subcutaneous Formulation of LEQEMBI®)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>GlobeNewswire</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/healthcare/biotech/pharmaceuticals/dr-reddys-launches-nivolumab-biosimilar-in-india/articleshow/134266368.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
+          <t>https://www.globenewswire.com/news-release/2026/09/16/3362836/0/en/leqembi-pen-subcutaneous-formulation-of-leqembi-approved-in-japan-for-the-treatment-of-early-alzheimer-s-disease.html</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>15-09-2026 14:05 UTC</t>
+          <t>16-09-2026 06:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Domestic pharma market sustains growth momentum, but margins remain key</t>
+          <t>Canada agrees to help pay for Alzheimer’s drug LEQEMBI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Longevity.Technology</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/market/mark-to-market/indian-pharma-market-ipm-pharma-stocks-domestic-pharma-dr-reddy-s-laboratories-sun-pharma-ajanta-pharma-glenmark/amp-11789538290089.html</t>
+          <t>https://longevity.technology/news/canada-agrees-to-help-pay-for-alzheimers-drug-leqembi/</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>16-09-2026 07:26 UTC</t>
+          <t>15-09-2026 23:10 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,22 +2029,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shreveport Frymaster celebrates purchase, expansion</t>
+          <t>Dr. Reddy’s forays into India’s biosimilar immuno-oncology market, launches Nivorz</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>The Shreveport-Bossier City Advocate</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.shreveportbossieradvocate.com/business/more-space-lines-and-employees-at-shreveport-frymaster/article_0ca48873-0dd0-40b0-8320-c265ad5bbc8f.html</t>
+          <t>https://www.thehindu.com/business/Industry/dr-reddys-forays-into-indias-biosimilar-immuno-oncology-market-launches-nivorz/article71469381.ece</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>15-09-2026 11:30 UTC</t>
+          <t>15-09-2026 16:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2056,481 +2056,481 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nestlé Health Science and Dr. Reddy's 2024 India Joint Venture</t>
+          <t>Buy, Sell Or Hold: Dr Reddy's Labs, BEL, L&amp;T, HDFC Bank, Welspun Corp And Canara Bank — Ask Profit</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4632173/nestle-health-science-and-dr-reddy-s-2024-india-joint-venture</t>
+          <t>https://www.ndtvprofit.com/markets/buy-sell-or-hold-dr-reddys-labs-bel-l-t-hdfc-bank-welspun-corp-and-canara-bank-ask-profit-12051254</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>15-09-2026 16:29 UTC</t>
+          <t>15-09-2026 17:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BioTecNika Times-15-09-2026: Freshers Job at Accenture, Paid Internship at IISER &amp; Intas, Parexel WFH Jobs &amp; More</t>
+          <t>Militant nurses accused of targeting billionaire health boss and daughter in disturbing campaign: ‘He can’t hide’</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>biotecnika.org</t>
+          <t>New York Post</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.biotecnika.org/2026/09/biotecnika-times-15-09-2026/</t>
+          <t>https://nypost.com/2026/09/16/us-news/prime-healthcare-ceo-prem-reddy-accuses-california-nurses-association-of-targeting-family-homes/</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15-09-2026 13:10 UTC</t>
+          <t>16-09-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cipla Formalizes Leadership Transition with Board Meeting Outcome and Regulatory Disclosures</t>
+          <t>Domestic pharma market sustains growth momentum, but margins remain key</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/cipla-shareholders-approve-leadership-appointments-through-postal-ballot-with-strong-majority/36103377</t>
+          <t>https://www.livemint.com/market/mark-to-market/indian-pharma-market-ipm-pharma-stocks-domestic-pharma-dr-reddy-s-laboratories-sun-pharma-ajanta-pharma-glenmark/amp-11789538290089.html</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>15-09-2026 20:06 UTC</t>
+          <t>16-09-2026 07:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C-CAMP National Bio Entrepreneurship Competition 2026 sees 15 startups, 4 student teams bag top honours</t>
+          <t>Dr Reddy’s forays into Indian biosimilar immuno-oncology market</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pharmabiz.com</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pharmabiz.com/NewsDetails.aspx?aid=190587&amp;sid=2</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/dr-reddys-forays-into-indian-biosimilar-immuno-oncology-market/articleshow/134268510.cms</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>15-09-2026 10:59 UTC</t>
+          <t>15-09-2026 16:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ET Under 40 2026: How technology is creating younger leaders</t>
+          <t>What Happens To Indian IT If AI Development Actually Slows</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/company/corporate-trends/et-under-40-2026-how-technology-is-creating-younger-leaders/amp_articleshow/134271381.cms</t>
+          <t>https://upstox.com/news/market-news/latest-updates/what-happens-to-indian-it-if-ai-development-actually-slows/video-200348/</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>15-09-2026 18:19 UTC</t>
+          <t>16-09-2026 07:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw Calls Out Fendi’s Rs 8.3 Lakh ‘Navratri’ Bag: ‘Undermines Our Authentic Talent’</t>
+          <t>NSE Indices announces rejig across multiple Nifty indices, changes effective September 30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pragativadi</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/kiran-mazumdar-shaw-calls-out-fendis-rs-8-3-lakh-navratri-bag-undermines-our-authentic-talent/</t>
+          <t>https://www.business-standard.com/amp/markets/capital-market-news/nse-indices-announces-rejig-across-multiple-nifty-indices-changes-effective-september-30-126091600365_1.html</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>16-09-2026 06:53 UTC</t>
+          <t>16-09-2026 06:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw Slams Fendi’s Rs 8.3 Lakh Navratri-Style Bag, Says It Undermines Indian Talent</t>
+          <t>US billionaire healthcare boss Prem Reddy sues nurses over 'track them down' campaign targeting him, daug</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>newsable.asianetnews.com</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://newsable.asianetnews.com/entertainment/kiran-mazumdar-shaw-slams-fendis-rs-83-lakh-navratri-style-bag-says-it-undermines-indian-talent-articleshow-eo73h7b</t>
+          <t>https://timesofindia.indiatimes.com/world/us/us-billionaire-healthcare-boss-prem-reddy-sues-nurses-over-track-them-down-campaign-targeting-him-daughter/articleshow/134289250.cms</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>16-09-2026 07:10 UTC</t>
+          <t>16-09-2026 14:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Harsh Goenka, Kiran Mazumdar-Shaw Call Out Fendi’s ₹8.3 Lakh ‘Navratri Bag’, Question Indian Craft</t>
+          <t>Gilead expands lenacapavir licensing to cover once-yearly HIV prevention</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>freepressjournal.in</t>
+          <t>StreetInsider</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/lifestyle/harsh-goenka-kiran-mazumdar-shaw-call-out-fendis-83-lakh-navratri-bag-question-indian-craft-credit-netizens-react</t>
+          <t>https://www.streetinsider.com/Corporate+News/Gilead+expands+lenacapavir+licensing+to+cover+once-yearly+HIV+prevention/27067898.html</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>16-09-2026 07:20 UTC</t>
+          <t>16-09-2026 12:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma gets FDA nod for asthma inhaler</t>
+          <t>Dr. Reddy’s Laboratories: कैंसर की नई दवा 'Nivorz' के साथ भारतीय बाजार में एंट्री</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/amp/news/drug-approvals-and-launches/aurobindo-pharma-gets-fda-nod-for-asthma-inhaler/134276350</t>
+          <t>https://www.whalesbook.com/news/Hindi/healthcarebiotech/Dr-Reddys-Launches-Cancer-Drug-Nivorz-In-India/6aa990790416c068539d68fc</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>16-09-2026 02:15 UTC</t>
+          <t>15-09-2026 22:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U.S. FDA issues observation to Aurobindo Pharma arm’s API unit</t>
+          <t>Nestlé Health Science and Dr. Reddy's 2024 India Joint Venture</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/us-fda-issues-observation-to-aurobindo-pharma-arms-api-unit/article71469185.ece</t>
+          <t>https://www.openpr.com/news/4632173/nestle-health-science-and-dr-reddy-s-2024-india-joint-venture</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15-09-2026 15:14 UTC</t>
+          <t>15-09-2026 16:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma shares in focus after USFDA issues one observation for Telangana facility</t>
+          <t>Dr. Reddy’s Launches Cancer Drug Nivorz In India</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/markets/aurobindo-pharma-shares-in-focus-after-usfda-issues-one-observation-for-telangana-facility-14030516.html/amp</t>
+          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Launches-Cancer-Drug-Nivorz-In-India/6aa990790416c068539d68fc</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16-09-2026 01:35 UTC</t>
+          <t>15-09-2026 21:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Gains USFDA Approval for Inhalation Aerosol in $301 Million Market</t>
+          <t>BioTecNika Times-15-09-2026: Freshers Job at Accenture, Paid Internship at IISER &amp; Intas, Parexel WFH Jobs &amp; More</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>BioTecNika</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/aurobindo-pharma-unit-iv-api-facility-concludes-us-fda-inspection-with-zero-observations</t>
+          <t>https://www.biotecnika.org/2026/09/biotecnika-times-15-09-2026/</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>15-09-2026 14:52 UTC</t>
+          <t>15-09-2026 16:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Gets USFDA Nod for First Metered-Dose Inhaler, Beclomethasone Aerosol</t>
+          <t>Cipla Formalizes Leadership Transition with Board Meeting Outcome and Regulatory Disclosures</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/aurobindo-pharma-gets-usfda-nod-for-first-metered-dose-inhaler-beclomethasone-aerosol-179322</t>
+          <t>https://scanx.trade/stock-market-news/companies/cipla-shareholders-approve-leadership-appointments-through-postal-ballot-with-strong-majority/36103377</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>15-09-2026 16:49 UTC</t>
+          <t>15-09-2026 20:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma US FDA inspection at Telangana API facility concludes with 1 procedural observation</t>
+          <t>Biocon Ltd. Downgraded to Sell Amid Technical and Financial Concerns</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>MarketsMojo</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/business/companies/aurobindo-pharma-us-fda-inspection-at-telangana-api-facility-concludes-with-1-procedural-observation-19991204.htm</t>
+          <t>https://www.marketsmojo.com/news/stock-recommendation/biocon-ltd-downgraded-to-sell-amid-technical-and-financial-concerns-4194441</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>15-09-2026 14:14 UTC</t>
+          <t>16-09-2026 04:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma gets USFDA approval for generic inhalation aerosol for asthma patients</t>
+          <t>ET Under 40 2026: How technology is creating younger leaders</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>thehindubusinessline.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/aurobindo-pharma-gets-usfda-approval-for-generic-inhalation-aerosol-for-asthma-patients/article71467611.ece</t>
+          <t>https://m.economictimes.com/news/company/corporate-trends/et-under-40-2026-how-technology-is-creating-younger-leaders/amp_articleshow/134271381.cms</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>15-09-2026 10:36 UTC</t>
+          <t>15-09-2026 18:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Gets First USFDA Nod For First Metered-Dose Inhaler</t>
+          <t>Kiran Mazumdar-Shaw Calls Out Fendi’s Rs 8.3 Lakh ‘Navratri’ Bag: ‘Undermines Our Authentic Talent’</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Pragativadi</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.ndtvprofit.com/business/aurobindo-pharma-gets-first-usfda-nod-for-first-metered-dose-inhaler-12049337</t>
+          <t>https://pragativadi.com/kiran-mazumdar-shaw-calls-out-fendis-rs-8-3-lakh-navratri-bag-undermines-our-authentic-talent/</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>15-09-2026 12:07 UTC</t>
+          <t>16-09-2026 06:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma receives US FDA nod for metered Beclomethasone Dipropionate aerosol</t>
+          <t>Kiran Mazumdar-Shaw Slams Fendi’s Rs 8.3 Lakh Navratri-Style Bag, Says It Undermines Indian Talent</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Asianet Newsable</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/markets/capital-market-news/aurobindo-pharma-receives-us-fda-nod-for-metered-beclomethasone-dipropionate-aerosol-126091500592_1.html</t>
+          <t>https://newsable.asianetnews.com/entertainment/kiran-mazumdar-shaw-slams-fendis-rs-83-lakh-navratri-style-bag-says-it-undermines-indian-talent-articleshow-eo73h7b</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>15-09-2026 09:21 UTC</t>
+          <t>16-09-2026 07:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Price Action: Saatvik Green Energy rises 5% on Rs 1,041cr order win; Aurobindo Pharma down 2% on USFDA...</t>
+          <t>Harsh Goenka, Kiran Mazumdar-Shaw Call Out Fendi’s ₹8.3 Lakh ‘Navratri Bag’, Question Indian Craft</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Free Press Journal</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/stocks/price-action-saatvik-green-energy-rises-5-on-order-win-worth-rs-1-041cr-aurobindo-pharma-down-2-on-usfda-observation-14030713.html</t>
+          <t>https://www.freepressjournal.in/amp/viral/harsh-goenka-kiran-mazumdar-shaw-call-out-fendis-83-lakh-navratri-bag-question-indian-craft-credit-netizens-react</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16-09-2026 06:22 UTC</t>
+          <t>16-09-2026 07:20 UTC</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>15-09-2026 15:07 UTC</t>
+          <t>16-09-2026 04:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2569,22 +2569,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma receives USFDA approval for Beclomethasone Dipropionate HFA Inhalation Aerosol</t>
+          <t>Aurobindo Pharma receives final USFDA approval for generic Beclomethasone inhalation Aerosol</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/markets/capital-market-news/aurobindo-pharma-receives-usfda-approval-for-beclomethasone-dipropionate-hfa-inhalation-aerosol-126091500646_1.html</t>
+          <t>https://www.indianpharmapost.com/regulatory/aurobindo-pharma-receives-final-usfda-approval-for-generic-beclomethasone-inhalation-aerosol-21875</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>15-09-2026 09:46 UTC</t>
+          <t>16-09-2026 12:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,400 +2596,400 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma gets US FDA nod to sell first metered-dose asthma inhaler in US</t>
+          <t>Aurobindo Pharma gets FDA nod for asthma inhaler</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/market/aurobindo-pharma-gets-us-fda-nod-to-sell-first-metered-dose-asthma-inhaler-in-us-19990888.htm/amp</t>
+          <t>https://pharma.economictimes.indiatimes.com/amp/news/drug-approvals-and-launches/aurobindo-pharma-gets-fda-nod-for-asthma-inhaler/134276350</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>15-09-2026 08:16 UTC</t>
+          <t>16-09-2026 02:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Hetero Biopharma</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Freshers Job at Hetero | Microbiology Graduates Eligible | Apply Online</t>
+          <t>Aurobindo Pharma Gets USFDA Nod for First Metered-Dose Inhaler, Beclomethasone Aerosol</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>biotecnika.org</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.biotecnika.org/2026/09/hetero-microbiology-job-freshers/</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/aurobindo-pharma-gets-usfda-nod-for-first-metered-dose-inhaler-beclomethasone-aerosol-179322</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>15-09-2026 09:01 UTC</t>
+          <t>15-09-2026 16:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals and SPIMACO Bio sign strategic license agreement for PD-1 Biosimilar for MENA market</t>
+          <t>Aurobindo Pharma Gets First USFDA Inhaler Nod</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia</t>
+          <t>Voice of Healthcare</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/25/28379/shilpa-biologicals-and-spimaco-bio-sign-strategic-license-agreement-for-pd-1-biosimilar-for-mena-market.html</t>
+          <t>https://vohnetwork.com/news/pharma/aurobindo-pharma-receives-first-usfda-approval-for-metered-dose-inhaler</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>16-09-2026 03:54 UTC</t>
+          <t>16-09-2026 06:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals and SPIMACO Collaborate on PD-1 Biosimilar for MENA Market</t>
+          <t>Aurobindo Pharma shares in focus after USFDA issues one observation for Telangana facility</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>chemindigest.com</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://chemindigest.com/shilpa-biologicals-and-spimaco-collaborate-on-pd-1-biosimilar-for-mena-market/</t>
+          <t>https://www.moneycontrol.com/news/business/markets/aurobindo-pharma-shares-in-focus-after-usfda-issues-one-observation-for-telangana-facility-14030516.html/amp</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>16-09-2026 06:27 UTC</t>
+          <t>16-09-2026 01:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Complex-Molecule Specialist Shilpa CDMO Launches at CPHI Milan</t>
+          <t>Aurobindo obtains FDA OK for generic QVAR</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>contractpharma.com</t>
+          <t>Drug Store News</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/live_from_shows/complex-molecule-specialist-shilpa-cdmo-launches-at-cphi-milan/</t>
+          <t>https://drugstorenews.com/aurobindo-obtains-fda-ok-generic-qvar</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>15-09-2026 19:33 UTC</t>
+          <t>15-09-2026 15:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals, SPIMACO sign MENA licensing deal for PD-1 biosimilars</t>
+          <t>Aurobindo arm Apitoria gets USFDA observation for Telangana API unit</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/biopharma/lite/shilpa-biologicals-spimaco-sign-mena-licensing-deal-for-pd-1-biosimilars-21860</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/aurobindo-arm-apitoria-gets-usfda-observation-for-telangana-api-unit/articleshow/134268517.cms</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>15-09-2026 13:00 UTC</t>
+          <t>15-09-2026 16:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PI Industries Introduces CARVINT Insecticide in India</t>
+          <t>Aurobindo Pharma: अमेरिकी FDA जांच में कंपनी को मिली बड़ी राहत, सिर्फ **1** ऑब्जर्वेशन</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>chemindigest.com</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://chemindigest.com/pi-industries-introduces-carvint-insecticide-in-india/</t>
+          <t>https://www.whalesbook.com/corporate-news/Hindi/healthcarebiotech/Aurobindo-Pharma-Subsidiary-Unit-II-Clears-US-FDA-Inspection-With-One-Observation/6aa93dd0f2017017ae6a7fab</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>16-09-2026 06:29 UTC</t>
+          <t>16-09-2026 06:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>More details about the Samsung Galaxy S27 Ultra's cameras emerge - GSMArena.com news</t>
+          <t>Aurobindo Pharma Wins First Inhaler Approval, Faces Unit Audit</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.gsmarena.com/more_details_about_the_samsung_galaxy_s27_ultras_cameras_emerge-news-74633.php</t>
+          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Aurobindo-Pharma-Wins-First-Inhaler-Approval-Faces-Unit-Audit/6aa9fa570416c068539e1373</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15-09-2026 23:31 UTC</t>
+          <t>16-09-2026 02:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>From 253 Grams to 201 Grams: the World’s Lightest Fold</t>
+          <t>Aurobindo Pharma: అమెరికా FDA తనిఖీల్లో క్లీన్ చిట్.. ఒక్క అబ్జర్వేషన్‌తో ముగిసిన ఆడిట్</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/au/from-253-grams-to-201-grams-the-worlds-lightest-fold</t>
+          <t>https://www.whalesbook.com/corporate-news/Telugu/healthcarebiotech/Aurobindo-Pharma-Subsidiary-Unit-II-Clears-US-FDA-Inspection-With-One-Observation/6aa93dd0f2017017ae6a7fab</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16-09-2026 07:56 UTC</t>
+          <t>16-09-2026 03:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Samsung releases stable One UI 9.0 update for Galaxy S26 series</t>
+          <t>Shilpa Biologicals, SPIMACO Bio Ink MENA Biosimilars Deal</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/galaxy-s26-stable-one-ui-9-0-update-released/</t>
+          <t>https://www.contractpharma.com/breaking-news/shilpa-biologicals-spimaco-bio-ink-mena-biosimilars-deal/</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>16-09-2026 07:43 UTC</t>
+          <t>16-09-2026 13:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Best Samsung foldable deal: Galaxy Z Fold 8 Ultra drops to $1,799.99</t>
+          <t>Shilpa Biologicals and SPIMACO Bio sign strategic license agreement for PD-1 Biosimilar for MENA market</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>Express Pharma</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://mashable.com/tech/sept-9-samsung-galaxy-z-fold-8-ultra-deal</t>
+          <t>https://www.expresspharma.in/shilpa-biologicals-and-spimaco-bio-sign-strategic-license-agreement-for-pd-1-biosimilar-for-mena-market/</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>16-09-2026 03:20 UTC</t>
+          <t>16-09-2026 07:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A18 4G is Official: Specs, Features, and Price</t>
+          <t>Shilpa Biologicals and SPIMACO Bio sign strategic license agreement for PD-1 Biosimilar for MENA market</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Nokiamob</t>
+          <t>biospectrumasia.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://nokiamob.net/2026/09/15/samsung-galaxy-a18-4g-price-and-specs-is-it-worth-the-upgrade/</t>
+          <t>https://www.biospectrumasia.com/news/25/28379/shilpa-biologicals-and-spimaco-bio-sign-strategic-license-agreement-for-pd-1-biosimilar-for-mena-market.html</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>15-09-2026 17:51 UTC</t>
+          <t>16-09-2026 03:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Samsung’s foldable lead faces the Apple test</t>
+          <t>Shilpa Biologicals and SPIMACO Collaborate on PD-1 Biosimilar for MENA Market</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>theinvestor.co.kr</t>
+          <t>Chemical Industry Digest</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.theinvestor.co.kr/article/10875737</t>
+          <t>https://chemindigest.com/shilpa-biologicals-and-spimaco-collaborate-on-pd-1-biosimilar-for-mena-market/</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16-09-2026 06:02 UTC</t>
+          <t>16-09-2026 06:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A18 4G Is Now Official — Here Are Its Specs and Price</t>
+          <t>Complex-Molecule Specialist Shilpa CDMO Launches at CPHI Milan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Android Headlines</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.androidheadlines.com/samsung-galaxy-a18-4g</t>
+          <t>https://www.contractpharma.com/live_from_shows/complex-molecule-specialist-shilpa-cdmo-launches-at-cphi-milan/</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>16-09-2026 03:40 UTC</t>
+          <t>15-09-2026 19:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Galaxy S27 Ultra: Samsung To Change Screen After Three Years</t>
+          <t>Unclogging India’s innovation pipeline</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Forbes</t>
+          <t>Express Pharma</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.forbes.com/sites/jaymcgregor/2026/09/15/samsung-galaxy-s27-ultra-leak-display-upgrade-galaxy-s27-pro-specs/</t>
+          <t>https://www.expresspharma.in/unclogging-indias-innovation-pipeline/</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>15-09-2026 21:07 UTC</t>
+          <t>16-09-2026 08:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3001,22 +3001,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A18 4G Launched With 50-Megapixel Main Camera, Exynos 1610 SoC: Price, Specifications</t>
+          <t>Samsung Begins Official Rollout of One UI 9, Bringing the Latest Galaxy Experiences to More Devices</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-a18-4g-price-launch-availability-specifications-features-12052999</t>
+          <t>https://news.samsung.com/global/samsung-begins-official-rollout-of-one-ui-9-bringing-the-latest-galaxy-experiences-to-more-devices</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>16-09-2026 06:30 UTC</t>
+          <t>16-09-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Samsung Is Fast-Tracking Galaxy Z TriFold 2 After iPhone Duo Reveal, According to Leaks</t>
+          <t>Samsung Begins Official Rollout of One UI 9, Bringing the Latest Galaxy Experiences to More Devices</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CNET</t>
+          <t>samsungmobilepress.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.cnet.com/tech/mobile/samsung-is-fast-tracking-galaxy-z-trifold-2-after-iphone-duo-reveal-according-to-leaks/</t>
+          <t>https://www.samsungmobilepress.com/articles/one-ui-9-official-rollout-latest-galaxy-experiences</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>15-09-2026 22:00 UTC</t>
+          <t>16-09-2026 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3055,22 +3055,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Aditya Babbar completes 15 years at Samsung Mobile</t>
+          <t>Samsung announces official One UI 9 rollout</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Exchange4Media</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/industry-briefing-news/aditya-babbar-completes-15-years-at-samsung-mobile-158286.html</t>
+          <t>https://www.sammobile.com/news/samsung-announces-official-one-ui-9-rollout/</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>16-09-2026 08:06 UTC</t>
+          <t>16-09-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3082,22 +3082,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Samsung Electronics chairman, Japanese lawmakers discuss AI, chip partnership</t>
+          <t>Samsung India expects double-digit growth in H2 fuelled by festive demand, premiumisation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KED Global</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kedglobal.com/korean-chipmakers/newsView/ked202609160008</t>
+          <t>https://www.thehindubusinessline.com/companies/samsung-india-expects-double-digit-growth-in-h2-fuelled-by-festive-demand-premiumisation/article71473172.ece</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>16-09-2026 06:49 UTC</t>
+          <t>16-09-2026 14:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3109,22 +3109,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>How Samsung is Building a More Seamless AI Experience</t>
+          <t>Samsung India launches 2026 Bespoke AI appliances</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>t2online.in</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/au/how-samsung-is-building-a-more-seamless-ai-experience</t>
+          <t>https://t2online.in/tech/tech-news/samsung-india-launches-2026-bespoke-ai-appliances/2008052</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>16-09-2026 07:36 UTC</t>
+          <t>16-09-2026 11:14 UTC</t>
         </is>
       </c>
     </row>
@@ -3136,265 +3136,265 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Android's solution to reduce motion sickness is rolling out to Galaxy phones</t>
+          <t>This is the Android phone I wish Google and Samsung would copy</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>How-To Geek</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/galaxy-phones-reduce-motion-sickness-feature-released/</t>
+          <t>https://www.howtogeek.com/this-is-the-android-phone-i-wish-google-and-samsung-would-copy/</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>15-09-2026 18:20 UTC</t>
+          <t>16-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Celltrion Repurchases KRW100 Billion in Shares</t>
+          <t>Samsung Galaxy S26 One UI 9 Stable Update: What's Confirmed</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Gadget Hacks</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/celltrion-repurchases-krw100-billion-in-shares-ce785bd2db8ef021</t>
+          <t>https://samsung.gadgethacks.com/news/samsung-galaxy-s26-one-ui-9-stable-update-whats-confirmed/</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>16-09-2026 07:33 UTC</t>
+          <t>16-09-2026 13:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Zymfentra, Xcopri projected to become Korea’s 1st $1 billion blockbuster drugs in 2027</t>
+          <t>One UI 9 stable update starts rolling out for Samsung Galaxy S26 users</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>91mobiles.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33200</t>
+          <t>https://www.91mobiles.com/hub/one-ui-9-stable-update-rollout-galaxy-s26-series/</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>16-09-2026 06:19 UTC</t>
+          <t>16-09-2026 11:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Celltrion, SK Biopharmaceuticals Drugs Poised to Top ₩1 Trillion Each Next Year — South Korea's First Blockbusters in Sight</t>
+          <t>Samsung expects double-digit H2 growth in appliances on festive demand, premiumisation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/3a921a30-a622-4e22-bc3e-17f7934234eb</t>
+          <t>https://www.moneycontrol.com/news/business/companies/samsung-expects-double-digit-h2-growth-in-appliances-on-festive-demand-premiumisation-14031241.html</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>16-09-2026 01:35 UTC</t>
+          <t>16-09-2026 10:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Celltrion Submits Phase 4 Trial Plan for Zymfentra</t>
+          <t>Samsung officially releases One UI 9 for the Galaxy S26, S26+, and S26 Ultra - GSMArena.com news</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>thelec.net</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.thelec.net/news/articleView.html?idxno=13949</t>
+          <t>https://www.gsmarena.com/samsung_officially_releases_one_ui_9_based_on_android_17_for_the_galaxy_s26_s26_and_s26_ultra-news-74642.php</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15-09-2026 22:49 UTC</t>
+          <t>16-09-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Celltrion to Cancel 100 Billion Won in Treasury Shares</t>
+          <t>Samsung India Launches 2026 Range of Bespoke AI Appliances Designed to be Your True Home Companion</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/16/celltrion-to-cancel-100-billion-won-in-treasury-shares</t>
+          <t>https://news.samsung.com/in/samsung-india-launches-2026-range-of-bespoke-ai-appliances-designed-to-be-your-true-home-companion</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>15-09-2026 23:53 UTC</t>
+          <t>16-09-2026 12:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Celltrion retires W100b in shares, pledges third of net profit to shareholders</t>
+          <t>Samsung releases stable One UI 9.0 update for Galaxy S26 series</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://mbiz.heraldcorp.com/article/10874870</t>
+          <t>https://www.sammobile.com/news/galaxy-s26-stable-one-ui-9-0-update-released/</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>15-09-2026 23:21 UTC</t>
+          <t>16-09-2026 08:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>South Korea's Celltrion Resolves to Retire ₩100 Billion in Treasury Shares; Full-Year Return Tops ₩200 Billion</t>
+          <t>Samsung India expects double-digit growth in H2 appliances biz on festive demand</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/93eb049d-6238-433b-ab92-151e68e9dfa8</t>
+          <t>https://www.thehindubusinessline.com/companies/samsung-india-expects-double-digit-growth-in-h2-appliances-biz-on-festive-demand/article71472514.ece</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>16-09-2026 00:55 UTC</t>
+          <t>16-09-2026 12:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Celltrion cancels 540,000 shares, expands Korea buybacks to 200 billion won - CHOSUNBIZ</t>
+          <t>More details about the Samsung Galaxy S27 Ultra's cameras emerge - GSMArena.com news</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/16/7BIJI2VO4ZCB5PU5P3LGJWECKE/?outputType=amp</t>
+          <t>https://www.gsmarena.com/more_details_about_the_samsung_galaxy_s27_ultras_cameras_emerge-news-74633.php</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>15-09-2026 23:51 UTC</t>
+          <t>15-09-2026 23:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Celltrion to cancel $73 million in treasury shares</t>
+          <t>Samsung Begins Official Rollout of One UI 9, Bringing the Latest Galaxy Experiences to More Devices</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>The Korea News Plus</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.newsarticleinsiders.com/news/articleView.html?idxno=4557</t>
+          <t>https://news.samsung.com/us/samsung-begins-official-rollout-one-ui-9-latest-galaxy-experiences-devices</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15-09-2026 23:52 UTC</t>
+          <t>16-09-2026 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3406,22 +3406,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Zymfentra, Xcopri Set to Join Korea's First 1 Trillion Won Drug Club</t>
+          <t>Zymfentra, Xcopri projected to become Korea’s 1st $1 billion blockbuster drugs in 2027</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/16/zymfentra-xcopri-set-to-join-koreas-first-1-trillion-won</t>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33200</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>16-09-2026 00:17 UTC</t>
+          <t>16-09-2026 06:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3433,22 +3433,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Zymfentra, Xcopri near Korea’s first blockbuster as sales surge past 1 trillion won - CHOSUNBIZ</t>
+          <t>Celltrion, SK Biopharmaceuticals Drugs Poised to Top ₩1 Trillion Each Next Year — South Korea's First Blockbusters in Sight</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/16/5DC4LLVP4FDENMPU7SIK7UBU3Q/?outputType=amp</t>
+          <t>https://finance.biggo.com/news/3a921a30-a622-4e22-bc3e-17f7934234eb</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>16-09-2026 00:45 UTC</t>
+          <t>16-09-2026 01:35 UTC</t>
         </is>
       </c>
     </row>
@@ -3460,22 +3460,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Korean Blockbuster Drugs 'On the Horizon': Zymfentra and Xcopri Race Towards Trillion-Won Sales</t>
+          <t>Celltrion Submits Phase 4 Trial Plan for Zymfentra</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>재경일보</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.jkn.co.kr/post/987178</t>
+          <t>https://www.thelec.net/news/articleView.html?idxno=13949</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>15-09-2026 23:35 UTC</t>
+          <t>15-09-2026 22:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3487,238 +3487,238 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Celltrion Nears KRW 100 Billion Target in Treasury Share Buyback</t>
+          <t>Celltrion Repurchases KRW100 Billion in Shares</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/celltrion-nears-krw-100-billion-target-in-treasury-share-buyback</t>
+          <t>https://www.marketscreener.com/news/celltrion-repurchases-krw100-billion-in-shares-ce785bd2db8ef021</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>15-09-2026 23:15 UTC</t>
+          <t>16-09-2026 07:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi Sankyo’s ENHERTU Cuts Disease Progression Risk by 37% in HER2-Mutant Lung Cancer</t>
+          <t>Celltrion retires W100b in shares, pledges third of net profit to shareholders</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/31/8438/astrazeneca-daiichi-sankyos-enhertu-cuts-disease-progression-risk-by-37-in-her2-mutant-lung-cancer.html</t>
+          <t>https://mbiz.heraldcorp.com/article/10874870</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>16-09-2026 00:32 UTC</t>
+          <t>15-09-2026 23:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Fortis Healthcare files Supreme Court petition against Delhi HC order</t>
+          <t>Celltrion to Cancel 100 Billion Won in Treasury Shares</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/fortis-healthcare-files-supreme-court-petition-against-delhi-hc-order/51082591</t>
+          <t>https://en.sedaily.com/finance/2026/09/16/celltrion-to-cancel-100-billion-won-in-treasury-shares</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>16-09-2026 05:39 UTC</t>
+          <t>15-09-2026 23:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Files Special Leave Petition Before Supreme Court Against Delhi HC Judgment</t>
+          <t>South Korea's Celltrion Resolves to Retire ₩100 Billion in Treasury Shares; Full-Year Return Tops ₩200 Billion</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/fortis-healthcare-files-special-leave-petition-before-supreme-court-against-delhi-hc-judgment</t>
+          <t>https://finance.biggo.com/news/93eb049d-6238-433b-ab92-151e68e9dfa8</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>16-09-2026 05:52 UTC</t>
+          <t>16-09-2026 00:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>YES Bank challenges Delhi HC order on forensic audit in Fortis case in SC</t>
+          <t>Celltrion to cancel $73 million in treasury shares</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Medical Buyer</t>
+          <t>The Korea News Plus</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/yes-bank-challenges-delhi-hc-order-on-forensic-audit-in-fortis-case-in-sc/</t>
+          <t>https://www.newsarticleinsiders.com/news/articleView.html?idxno=4557</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>16-09-2026 02:29 UTC</t>
+          <t>15-09-2026 23:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Fortis Healthcare moves Supreme Court against Delhi HC forensic audit order; Axis Bank may follow</t>
+          <t>Celltrion cancels 540,000 shares, expands Korea buybacks to 200 billion won - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/fortis-healthcare-moves-supreme-court-against-delhi-hc-forensic-audit-order-axis-bank-may-follow/amp_articleshow/134279742.cms</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/16/7BIJI2VO4ZCB5PU5P3LGJWECKE/?outputType=amp</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>16-09-2026 06:10 UTC</t>
+          <t>15-09-2026 23:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Exploring Daiichi Sankyo UK’s Impact on Cardiovascular and Oncology Care</t>
+          <t>Zymfentra, Xcopri Set to Join Korea's First 1 Trillion Won Drug Club</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NewsHub.co.uk</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://www.newshub.co.uk/automotive/2026/09/15/exploring-daiichi-sankyo-uks-impact-on-cardiovascular-and-oncology-care/</t>
+          <t>https://en.sedaily.com/finance/2026/09/16/zymfentra-xcopri-set-to-join-koreas-first-1-trillion-won</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>15-09-2026 08:59 UTC</t>
+          <t>16-09-2026 00:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>How Daiichi-Fortis ruling could hurt FDI</t>
+          <t>Zymfentra, Xcopri near Korea’s first blockbuster as sales surge past 1 trillion won - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>financialexpress.com</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/opinion/how-daiichi-fortis-ruling-could-hurt-fdi/4339903/</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/16/5DC4LLVP4FDENMPU7SIK7UBU3Q/?outputType=amp</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>15-09-2026 16:27 UTC</t>
+          <t>16-09-2026 00:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fortis Healthcare: Files Special Leave Petition in Supreme Court</t>
+          <t>Korean Blockbuster Drugs 'On the Horizon': Zymfentra and Xcopri Race Towards Trillion-Won Sales</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>investywise.com</t>
+          <t>재경일보</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.investywise.com/fortis-healthcare-files-special-leave-petition/</t>
+          <t>https://news.jkn.co.kr/post/987178</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>16-09-2026 05:34 UTC</t>
+          <t>15-09-2026 23:35 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,22 +3730,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fortis Forensic Audit Dispute Reaches Supreme Court as Yes Bank Challenges HC Order</t>
+          <t>Fortis Healthcare Challenges Forensic Audit in Daiichi Case</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>urbanacres.in</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://urbanacres.in/fortis-forensic-audit-dispute-reaches-supreme-court-as-yes-bank-challenges-hc-order/</t>
+          <t>https://money.rediff.com/news/market/fortis-healthcare-challenges-forensic-audit-in-daiichi-case/54450820260916</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>15-09-2026 16:57 UTC</t>
+          <t>16-09-2026 14:57 UTC</t>
         </is>
       </c>
     </row>
@@ -3757,670 +3757,1210 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Yes Bank Challenges Supreme Court On Fortis Forensic Audit Order</t>
+          <t>Fortis Healthcare moves SC against Delhi HC order directing forensic audit in Daiichi Sankyo case</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>ETLegalWorld.com</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/news/English/bankingfinance/Yes-Bank-Challenges-Supreme-Court-On-Fortis-Forensic-Audit-Order/6aa9aa040416c068539db4ff</t>
+          <t>https://legal.economictimes.indiatimes.com/news/litigation/fortis-healthcare-moves-sc-against-delhi-hc-order-directing-forensic-audit-in-daiichi-sankyo-case/134280337</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>15-09-2026 21:56 UTC</t>
+          <t>16-09-2026 07:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Crystalline Amino Acids Market To 2035: Feed Demand and High-Purity Grades Drive Growth - News and Statistics</t>
+          <t>Fortis moves SC against HC forensic audit order in company transactions</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/crystalline-amino-acids-market-forecast-to-2035-demand-accelerates-on-animal-protein-expansion-and-specialty-grade-uptake/</t>
+          <t>https://www.business-standard.com/amp/companies/news/fortis-moves-sc-against-hc-forensic-audit-order-in-company-transactions-126091600888_1.html</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>15-09-2026 11:41 UTC</t>
+          <t>16-09-2026 11:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Launches Cancer Drug Nivorz In India</t>
+          <t>AstraZeneca, Daiichi Sankyo’s ENHERTU Cuts Disease Progression Risk by 37% in HER2-Mutant Lung Cancer</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>BioPharma APAC</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Launches-Cancer-Drug-Nivorz-In-India/6aa990790416c068539d68fc</t>
+          <t>https://biopharmaapac.com/news/31/8438/astrazeneca-daiichi-sankyos-enhertu-cuts-disease-progression-risk-by-37-in-her2-mutant-lung-cancer.html</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>15-09-2026 21:56 UTC</t>
+          <t>16-09-2026 00:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Successful Internal Audit Planning and Execution</t>
+          <t>Daiichi and AstraZeneca cancer drugs secure further approvals in Japan</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PharmTech.com</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>http://www.pharmtech.com/view/successful-internal-audit-planning-and-execution</t>
+          <t>https://www.marketscreener.com/news/daiichi-and-astrazeneca-cancer-drugs-secure-further-approvals-in-japan-ce785bd2da8bff24</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>15-09-2026 18:42 UTC</t>
+          <t>16-09-2026 08:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NIRF Pharmacy Ranking 2026; Check Top Pharmacy Colleges List</t>
+          <t>Fortis Healthcare files Supreme Court petition against Delhi HC order</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Shiksha.com</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://www.shiksha.com/medicine-health-sciences/articles/nirf-pharmacy-ranking-2026-check-top-pharmacy-colleges-list-blogId-241927</t>
+          <t>https://scanx.trade/stock-market-news/companies/fortis-healthcare-files-supreme-court-petition-against-delhi-hc-order/51082591</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>15-09-2026 11:58 UTC</t>
+          <t>16-09-2026 05:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Contineum Thera down after depression drug miss</t>
+          <t>Fortis moves SC against Delhi HC order in Daiichi Sankyo award case</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Asianet Newsable</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biotech-news/contineum-thera-down-after-depression-drug-miss</t>
+          <t>https://newsable.asianetnews.com/india/fortis-moves-sc-against-delhi-hc-order-in-daiichi-sankyo-award-case-articleshow-v6wnlq7</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>15-09-2026 08:25 UTC</t>
+          <t>16-09-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>J&amp;J’s Contineum-partnered depression drug flunks another phase 2 test</t>
+          <t>Fortis Healthcare: సుప్రీంకోర్టుకు చేరిన Daiichi Sankyo వివాదం.. కంపెనీ కీలక అప్డేట్</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fierce Biotech</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.fiercebiotech.com/biotech/jjs-contineum-partnered-asset-flunks-another-phase-2-test</t>
+          <t>https://www.whalesbook.com/corporate-news/Telugu/healthcarebiotech/Fortis-Healthcare-Files-Supreme-Court-Plea-In-Daiichi-Sankyo-Case/6aaa2a35f2017017ae6aefa5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>15-09-2026 08:40 UTC</t>
+          <t>16-09-2026 05:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Leading Biotech Selects Veeva Vault CRM Globally</t>
+          <t>Former Infosys chief’s AI startup nabs another $53M</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>TechCrunch</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/leading-biotech-selects-veeva-vault-110300562.html</t>
+          <t>https://techcrunch.com/2026/09/16/former-infosys-chiefs-ai-startup-adds-50m-to-seed-weeks-after-initial-raise/</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>15-09-2026 11:03 UTC</t>
+          <t>16-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Delhi HC orders tax dept to refund ₹783 cr to Teva Israel over Ranbaxy payment</t>
+          <t>Fresenius SE &amp; Co. KGaA : Barclays reaffirms its Buy rating</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/companies/delhi-hc-tax-refund-to-teva-israel-ranbaxy-sun-pharma-income-tax-india-11789467986662.html</t>
+          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-barclays-reaffirms-its-buy-rating-ce785bd2dc88f726</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>15-09-2026 11:06 UTC</t>
+          <t>16-09-2026 12:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tue: Enlight leads TASE lower - Globes</t>
+          <t>SK Hynix reportedly in talks with Intel to build memory chips in US</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Globes - Israel Business News</t>
+          <t>TechCrunch</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://en.globes.co.il/en/article-tue-enlight-leads-tase-lower-1001555561</t>
+          <t>https://techcrunch.com/2026/09/16/sk-hynix-reportedly-in-talks-with-intel-to-build-memory-chips-in-us/</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>15-09-2026 15:26 UTC</t>
+          <t>16-09-2026 13:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Laughter Really Is The Best Medicine</t>
+          <t>Iron Sucrose Market Set to Surpass USD 796.4 Million by 2033,</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://www.medscape.com/viewarticle/laughter-really-best-medicine-2026a1000xdh?src=</t>
+          <t>https://www.openpr.com/news/4632934/iron-sucrose-market-set-to-surpass-usd-796-4-million-by-2033</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>15-09-2026 19:46 UTC</t>
+          <t>16-09-2026 08:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma receives US FDA nod for metered Beclomethasone Dipropionate aerosol</t>
+          <t>Dr. Reddy’s Launches Cancer Drug Nivorz In India</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/markets/capital-market-news/aurobindo-pharma-receives-us-fda-nod-for-metered-beclomethasone-dipropionate-aerosol-126091500592_1.html</t>
+          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Launches-Cancer-Drug-Nivorz-In-India/6aa990790416c068539d68fc</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>15-09-2026 09:21 UTC</t>
+          <t>15-09-2026 21:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ukrainians warned of possible medicine shortages</t>
+          <t>Successful Internal Audit Planning and Execution</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Новини аграрного бізнесу</t>
+          <t>PharmTech.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://agronews.ua/en/news/ukrainians-warned-of-possible-medicine-shortages/</t>
+          <t>http://www.pharmtech.com/view/successful-internal-audit-planning-and-execution</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>15-09-2026 16:00 UTC</t>
+          <t>15-09-2026 18:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>American Council of Learned Societies Announces Winners of 2026 ACLS Open Access Book Prizes and Arcadia Open Access Publishing Awards</t>
+          <t>Alkermes Announces Appointment of Anne C. Whitaker to Board of Directors</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/american-council-learned-societies-announces-231500703.html</t>
+          <t>https://www.biospace.com/press-releases/alkermes-announces-appointment-of-anne-c-whitaker-to-board-of-directors</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>15-09-2026 23:15 UTC</t>
+          <t>16-09-2026 14:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Avaí Bio and Austrianova Complete Adventitious Agent Testing of Master Cell Bank, Establish Working Cell Bank for α-Klotho Anti-Aging Therapy</t>
+          <t>Alvotech upgraded to Overweight from Underweight at Barclays</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/ava-bio-austrianova-complete-adventitious-124500596.html</t>
+          <t>https://www.tipranks.com/news/the-fly/alvotech-upgraded-to-overweight-from-underweight-at-barclays-thefly-news?mod=mw_quote_news</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>15-09-2026 12:45 UTC</t>
+          <t>16-09-2026 12:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BIX 2026 Names Canada as Country of Honor, Showcasing Bioindustry Trends from BCI to Biotech Foods</t>
+          <t>Delhi HC orders tax dept to refund ₹783 cr to Teva Israel over Ranbaxy payment</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>더바이오</t>
+          <t>A2Z Taxcorp LLP</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28154</t>
+          <t>https://a2ztaxcorp.net/delhi-hc-orders-tax-dept-to-refund-%E2%82%B9783-cr-to-teva-israel-over-ranbaxy-payment/</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>15-09-2026 23:49 UTC</t>
+          <t>16-09-2026 12:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Local Dispensary Named "Best in Central Illinois" for Third Straight Year</t>
+          <t>Teva Launches LongActingImpact.com to Advance Understanding of Earlier, Effective and Uninterrupted Schizophrenia Care</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/local-dispensary-named-best-central-100000166.html</t>
+          <t>https://ca.finance.yahoo.com/news/teva-launches-longactingimpact-com-advance-120000554.html</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>15-09-2026 10:00 UTC</t>
+          <t>16-09-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Europe Biosimilar Market Size and Outlook Report 2034 Halaman 1</t>
+          <t>Teva launches educational website for HCPs to advance understanding of LAIs in schizophrenia care</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Kompasiana.com</t>
+          <t>PharmaLive</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://www.kompasiana.com/yadwenderkumar9745/6aaa2ecec925c4173e22ced9/europe-biosimilar-market-size-and-outlook-report-2034</t>
+          <t>https://www.pharmalive.com/teva-launches-educational-website-for-hcps-to-advance-understanding-of-lais-in-schizophrenia-care/</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>16-09-2026 05:53 UTC</t>
+          <t>16-09-2026 13:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Launches Cancer Drug Nivorz In India</t>
+          <t>Is the Teva Trailpeak as adventurous as its name suggests?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Believe in the Run</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Launches-Cancer-Drug-Nivorz-In-India/6aa990790416c068539d68fc</t>
+          <t>https://believeintherun.com/shoe-reviews/teva-trailpeak-review/</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>15-09-2026 21:56 UTC</t>
+          <t>16-09-2026 13:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Semiconductor rebound lifts KOSPI 1.37 percent, back above 6,700</t>
+          <t>Teva Trailpeak Review; 3 Comparisons</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>디지털투데이</t>
+          <t>roadtrailrun.com</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://www.digitaltoday.co.kr/en/view/104340/semiconductor-rebound-lifts-kospi-1-37-percent-back-above-6700</t>
+          <t>https://www.roadtrailrun.com/2026/09/teva-trailpeak-review-3-comparisons.html</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>16-09-2026 07:05 UTC</t>
+          <t>16-09-2026 11:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>The KOSPI, which has been on a downward trend in recent days, started falling on the 16th, but close..</t>
+          <t>Increasing unusual option volume: MAT FDXF FPS BN JBHT GPRE CSWC TEVA GPCR DEO AADX ECO GFL MBOT</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>StreetInsider</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/en/stock/12154354</t>
+          <t>https://www.streetinsider.com/Options/Increasing+unusual+option+volume%3A+MAT+FDXF+FPS+BN+JBHT+GPRE+CSWC+TEVA+GPCR+DEO+AADX+ECO+GFL+MBOT/27068725.html</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>16-09-2026 07:05 UTC</t>
+          <t>16-09-2026 14:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Axiom, GeneFab Partner to Advance Therapeutic Pipeline</t>
+          <t>Mere Payment By Indian Resident To Non-Resident Not Income Accruing In India: Delhi High Court</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>contractpharma.com</t>
+          <t>LiveLawBiz</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/axiom-genefab-partner-to-advance-therapeutic-pipeline/</t>
+          <t>https://www.livelawbiz.com/income-tax/high-court/mere-payment-by-indian-resident-to-non-resident-not-income-accruing-in-india-delhi-high-court-550360</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>15-09-2026 16:46 UTC</t>
+          <t>16-09-2026 14:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>South Korean shares rise as chipmakers gain ahead of Fed outcome</t>
+          <t>Remepy appoints Eran Harary as Chief Medical Officer</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Business Recorder</t>
+          <t>calcalistech.com</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://www.brecorder.com/news/amp/40439737</t>
+          <t>https://www.calcalistech.com/ctechnews/article/h1n6jzdtgx</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>16-09-2026 05:33 UTC</t>
+          <t>16-09-2026 11:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>55 Listed Companies Join Korea Premium Weeks 2026 Starting Sept. 28</t>
+          <t>Shilpa Bio inks deal for PD-1 biosimilar for MENA market</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277063</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/shilpa-bio-inks-deal-for--1-biosimilar-for-mena-market</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>16-09-2026 01:55 UTC</t>
+          <t>16-09-2026 11:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>VivoSim Labs Unveils New NAMkind™ Drug Toxicity Data at EUROTOX 2026, Demonstrating Predictive Superiority in Liver and Gastrointestinal Safety Across Small Molecules and ADCs</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Singapore</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://sg.finance.yahoo.com/news/vivosim-labs-unveils-namkind-drug-120500630.html</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>16-09-2026 12:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>American Council of Learned Societies Announces Winners of 2026 ACLS Open Access Book Prizes and Arcadia Open Access Publishing Awards</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Singapore</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://sg.finance.yahoo.com/news/american-council-learned-societies-announces-231500703.html</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>15-09-2026 23:15 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>BIX 2026 Names Canada as Country of Honor, Showcasing Bioindustry Trends from BCI to Biotech Foods</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>더바이오</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28154</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>15-09-2026 23:49 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Europe Biosimilar Market Size and Outlook Report 2034 Halaman 1</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Kompasiana.com</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://www.kompasiana.com/yadwenderkumar9745/6aaa2ecec925c4173e22ced9/europe-biosimilar-market-size-and-outlook-report-2034</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>16-09-2026 05:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Former Infosys chief’s AI startup nabs another $53M</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/16/former-infosys-chiefs-ai-startup-adds-50m-to-seed-weeks-after-initial-raise/</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>16-09-2026 13:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA : Barclays reaffirms its Buy rating</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>marketscreener.com</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-barclays-reaffirms-its-buy-rating-ce785bd2dc88f726</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>16-09-2026 12:09 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SK Hynix reportedly in talks with Intel to build memory chips in US</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/16/sk-hynix-reportedly-in-talks-with-intel-to-build-memory-chips-in-us/</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>16-09-2026 13:23 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Iron Sucrose Market Set to Surpass USD 796.4 Million by 2033,</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>https://www.openpr.com/news/4632934/iron-sucrose-market-set-to-surpass-usd-796-4-million-by-2033</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>16-09-2026 08:14 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Dr. Reddy’s Launches Cancer Drug Nivorz In India</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Whalesbook</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Launches-Cancer-Drug-Nivorz-In-India/6aa990790416c068539d68fc</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>15-09-2026 21:56 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
           <t>Samsung Biologics</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>[Closing Market] KOSPI Retreats to 6,620 Mark Amid Stronger Dollar</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Semiconductor rebound lifts KOSPI 1.37 percent, back above 6,700</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>디지털투데이</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://www.digitaltoday.co.kr/en/view/104340/semiconductor-rebound-lifts-kospi-1-37-percent-back-above-6700</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>16-09-2026 07:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>55 Listed Companies Join Korea Premium Weeks 2026 Starting Sept. 28</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
         <is>
           <t>Businesskorea</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277008</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>15-09-2026 08:42 UTC</t>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277063</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>16-09-2026 01:55 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>The KOSPI, which has been on a downward trend in recent days, started falling on the 16th, but close..</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>매일경제</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/en/stock/12154354</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>16-09-2026 07:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Shilpa Biologicals, SPIMACO Bio Ink MENA Biosimilars Deal</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Contract Pharma</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://www.contractpharma.com/breaking-news/shilpa-biologicals-spimaco-bio-ink-mena-biosimilars-deal/</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>16-09-2026 13:24 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Corrugated Vial Shipping Trays Market Forecast to 2035: Biologics Demand Drives Expansion - News and Statistics</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>IndexBox</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://www.indexbox.io/blog/corrugated-vial-shipping-trays-market-to-accelerate-on-biologics-demand-reaching-2035-growth/</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>16-09-2026 13:31 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Sanofi, UCB, Opella Join Clean Heat Program</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Contract Pharma</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://www.contractpharma.com/breaking-news/sanofi-ucb-opella-join-clean-heat-program/</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>16-09-2026 12:55 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>South Korean shares rise as chipmakers gain ahead of Fed outcome</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Business Recorder</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://www.brecorder.com/news/amp/40439737</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>16-09-2026 05:33 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Graves’ Orbitopathy Market to Grow from USD 2.06 Billion at a CAGR of 19.8% Through 2034</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Barchart.com</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://www.barchart.com/press-releases/4625289/graves-orbitopathy-market-to-grow-from-usd-2-06-billion-at-a-cagr-of-19-8-through-2034</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>16-09-2026 02:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>CDMO Capacity: Stainless by Volume, Single-Use by Number</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Contract Pharma</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://www.contractpharma.com/exclusives/cdmo-capacity-stainless-by-volume-single-use-by-number/</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>15-09-2026 18:03 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Axiom, GeneFab Partner to Advance Therapeutic Pipeline</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Contract Pharma</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://www.contractpharma.com/breaking-news/axiom-genefab-partner-to-advance-therapeutic-pipeline/</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>15-09-2026 16:46 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Biologics Contract Manufacturing Market to Reach US$ 83.47</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://www.openpr.com/news/4633375/biologics-contract-manufacturing-market-to-reach-us-83-47</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>16-09-2026 13:24 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Ori Biotech Lands 10-Year, $120M Commercial Cell Therapy Manufacturing Deal</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Contract Pharma</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://www.contractpharma.com/breaking-news/ori-biotech-lands-10-year-120m-commercial-cell-therapy-manufacturing-deal/</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>15-09-2026 18:58 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E168"/>
+  <dimension ref="A1:E162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sandoz issues 500 million euros bond to extend debt maturity profile</t>
+          <t>‘It’s Incredibly Rare In A Career To Be In This Position’ – Sandoz CFO On Bio100 And The Path Ahead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/generics-news/sandoz-issues-500-million-euros-bond-to-extend-debt-maturity-profile</t>
+          <t>https://insights.citeline.com/generics-bulletin/leadership/interviews/its-incredibly-rare-in-a-career-to-be-in-this-position-sandoz-cfo-on-bio100-and-the-path-ahead-XYNMGOM3BNEXXBNG4RDWBV3U3Y/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15-09-2026 22:14 UTC</t>
+          <t>16-09-2026 12:23 UTC</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sandoz pays up for duration in €500m trade</t>
+          <t>Shilpa Bio inks deal for PD-1 biosimilar for MENA market</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Global Capital |</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.globalcapital.com/article/2gw8sima1juifixzkivi8/corporate-bonds/high-grade-and-crossover-bonds/sandoz-pays-up-for-duration-in-500m-trade</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/shilpa-bio-inks-deal-for--1-biosimilar-for-mena-market</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15-09-2026 15:48 UTC</t>
+          <t>16-09-2026 11:08 UTC</t>
         </is>
       </c>
     </row>
@@ -544,130 +544,130 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Norma Stoeger Obituary (1938 - 2026) - Valentine, NE - North Platte Telegraph</t>
+          <t>Parmigiani Fleurier commemorates thirty years of horological mastery with the Mechanical Wonders exhibition in Tokyo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Legacy obituary</t>
+          <t>senatus.net</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.legacy.com/us/obituaries/nptelegraph/name/norma-stoeger-obituary?id=62435196</t>
+          <t>https://senatus.net/album/view/17714/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16-09-2026 05:41 UTC</t>
+          <t>16-09-2026 14:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Egypt reports sharp decline in child anaemia, stunting rates</t>
+          <t>Städa med Grumme såpa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dailynewsegypt</t>
+          <t>metromode.se</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.dailynewsegypt.com/2026/09/15/egypt-reports-sharp-decline-in-child-anaemia-stunting-rates/</t>
+          <t>https://metromode.se/en/tag/stada-med-grumme-sapa/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15-09-2026 18:48 UTC</t>
+          <t>16-09-2026 13:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Parmigiani Fleurier commemorates thirty years of horological mastery with the Mechanical Wonders exhibition in Tokyo</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>senatus.net</t>
+          <t>via.ritzau.dk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://senatus.net/album/view/17714/</t>
+          <t>https://via.ritzau.dk/pressemeddelelse/15166947/boehringer-ingelheim?publisherId=90446&amp;lang=en</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16-09-2026 14:48 UTC</t>
+          <t>17-09-2026 05:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Robert Gerald Engstrom Obituary (2026) - Hendersonville, NC - Church Street Funeral &amp; Cremation - Hendersonville</t>
+          <t>Boehringer ends late-stage kidney disease study of Jardiance combo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Legacy obituary</t>
+          <t>FirstWord PHARMA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.legacy.com/us/obituaries/name/robert-engstrom-obituary?id=62434785</t>
+          <t>https://firstwordpharma.com/story/7998608</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16-09-2026 02:57 UTC</t>
+          <t>16-09-2026 22:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OneSource Specialty Pharma Q1FY27 revenue up 37%, EBITDA surges 39%</t>
+          <t>Lilly backs Circle's latest fundraise as second cancer drug nears clinic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>FirstWord PHARMA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/onesource-specialty-pharma-to-discuss-q1fy27-results-on-jul-25/46162875</t>
+          <t>https://firstwordpharma.com/story/7996747</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15-09-2026 18:46 UTC</t>
+          <t>16-09-2026 18:23 UTC</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vicadrostat EASi-KIDNEY Trial Discontinued for Lack of Benefit in CKD</t>
+          <t>Inside FIND-CKD: Can Finerenone Pair With Immunosuppression in GN?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.hcplive.com/view/vicadrostat-easi-kidney-trial-discontinued-for-lack-of-benefit-in-ckd</t>
+          <t>https://www.hcplive.com/view/inside-find-ckd-can-finerenone-pair-with-immunosuppression-in-gn-</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15-09-2026 22:42 UTC</t>
+          <t>16-09-2026 19:06 UTC</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Webinar: Immunosuppression: Consequences for the bird and farmer</t>
+          <t>Livestock Temperature Monitoring Tags Market To 2035: Disease Surveillance Drives Expansion - News and Statistics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WATTPoultry.com</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.wattagnet.com/webinars/webinar/15834930/boehringer-ingelheim-webinar-immunosuppression-consequences-for-the-bird-and-farmer</t>
+          <t>https://www.indexbox.io/blog/livestock-temperature-monitoring-tags-market-forecast-to-2035-growth-accelerates-on-disease-surveillance-demand/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15-09-2026 20:59 UTC</t>
+          <t>16-09-2026 20:51 UTC</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>When the Scan Knows Before the Spirometer Does</t>
+          <t>Vaccine Contract Manufacturing Market Poised for Steady Growth Through 2032 Amid Rising Immunization Demand – DelveInsight</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>clinicaltrialvanguard.com</t>
+          <t>Barchart.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.clinicaltrialvanguard.com/executiveinterviews/when-the-scan-knows-before-the-spirometer-does/</t>
+          <t>https://www.barchart.com/press-releases/4646007/vaccine-contract-manufacturing-market-poised-for-steady-growth-through-2032-amid-rising-immunization-demand-delveinsight</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15-09-2026 16:04 UTC</t>
+          <t>16-09-2026 23:30 UTC</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adisseo names Li Bo as its new chairman and CEO</t>
+          <t>CMU, Pitt, UPMC and Highmark showcase AI-powered convergence in life sciences</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Feed Strategy</t>
+          <t>The Business Journals</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.feedstrategy.com/business-markets/company-news/news/15834953/adisseo-names-li-bo-as-its-new-chairman-and-ceo</t>
+          <t>https://www.bizjournals.com/pittsburgh/news/2026/09/16/pittsburgh-life-sciences-alliance-bio-health.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15-09-2026 20:11 UTC</t>
+          <t>16-09-2026 18:47 UTC</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lilly backs Circle's latest fundraising as second cancer drug progresses towards clinic</t>
+          <t>Oligomerix puts tau drug in new hands as trials begin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>Longevity.Technology</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7996747</t>
+          <t>https://longevity.technology/news/oligomerix-puts-tau-drug-in-new-hands-as-trials-begin/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16-09-2026 12:29 UTC</t>
+          <t>16-09-2026 17:26 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zealand Pharma out-licenses GLP-1/gastrin peptide platform to Elvinix for regenerative type 1 diabetes therapy</t>
+          <t>3 Steps to Support Mental Health for Rural Youth</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>app.dealroom.co</t>
+          <t>The Miner Online</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://app.dealroom.co/news/note/zealand-pharma-out-licenses-glp-1-gastrin-peptide-platform-to-elvinix-for-regenerative-type-1-diabetes-therapy</t>
+          <t>https://www.pendoreillerivervalley.com/article/6059,3-steps-to-support-mental-health-for-rural-youth</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15-09-2026 15:50 UTC</t>
+          <t>16-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Interstitial Lung Disease Market to Grow from USD 6 Billion at a CAGR of 8.7% Through 2036</t>
+          <t>Interstitial Lung Disease Market Poised for Strong Growth Through 2036 with Breakthrough ILD Treatments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,39 +851,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4632856/interstitial-lung-disease-market-to-grow-from-usd-6-billion-at</t>
+          <t>https://www.openpr.com/news/4633962/interstitial-lung-disease-market-poised-for-strong-growth</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16-09-2026 07:17 UTC</t>
+          <t>17-09-2026 05:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Europe Biosimilar Market Size and Outlook Report 2034 Halaman 1</t>
+          <t>Weapons plan principles to be announced in early October, Hikma spox says</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kompasiana.com</t>
+          <t>964media</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kompasiana.com/yadwenderkumar9745/6aaa2ecec925c4173e22ced9/europe-biosimilar-market-size-and-outlook-report-2034</t>
+          <t>https://en.964media.com/52693/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16-09-2026 05:53 UTC</t>
+          <t>17-09-2026 07:07 UTC</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>fiercepharma.com</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bristol Myers sues Amgen over proposed Opdivo biosimilar</t>
+          <t>BMS, Ono sue to protect Opdivo from Amgen biosimilar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>FirstWord PHARMA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/bristol-myers-sues-amgen-over-proposed-opdivo-biosimilar/134282973</t>
+          <t>https://firstwordpharma.com/story/7998630</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16-09-2026 08:46 UTC</t>
+          <t>16-09-2026 22:04 UTC</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FDA cuts monitoring time for first two doses of Amgen’s IMDELLTRA</t>
+          <t>Amgen hit with lawsuit over its proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Life Sciences IP Review</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/regulatory/fda-cuts-monitoring-time-for-first-two-doses-of-amgens-imdelltra-21872</t>
+          <t>https://www.lifesciencesipreview.com/biotech/amgen-hit-with-lawsuit-over-its-proposed-opdivo-biosimilar</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16-09-2026 12:26 UTC</t>
+          <t>16-09-2026 21:23 UTC</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bristol Myers sues Amgen over proposed Opdivo biosimilar</t>
+          <t>From the Financial Crisis to the 2022 Bear Market, How Does Amgen Demonstrate Resilience?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>NAI500</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/litigation/bristol-myers-sues-amgen-over-proposed-opdivo-biosimilar-2026-09-15/</t>
+          <t>https://nai500.com/blog/2026/09/from-the-financial-crisis-to-the-2022-bear-market-how-does-amgen-demonstrate-resilience/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15-09-2026 20:25 UTC</t>
+          <t>17-09-2026 07:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amgen Highlights MariTide, IMDELLTRA Pipeline Progress and Growth Priorities</t>
+          <t>Amgen Confident In Cardiometabolic Pipeline After Novartis’s Negative Lp(a) Readout</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>finance.yahoo.com</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/amgen-highlights-maritide-imdelltra-pipeline-050213898.html</t>
+          <t>https://insights.citeline.com/scrip/therapeutic-category/cardiovascular/amgen-confident-in-cardiometabolic-pipeline-after-novartiss-negative-lpa-readout-44IU5KUHR5GCVH5BZWKTKT6WXU/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16-09-2026 05:02 UTC</t>
+          <t>16-09-2026 22:14 UTC</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1057,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FDA reduces monitoring time for Amgen’s Imdelltra infusions</t>
+          <t>FDA cuts monitoring time for first two doses of Amgen’s IMDELLTRA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pharmaceutical Business review -</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pharmaceutical-business-review.com/news/fda-reduces-monitoring-time-amgens-imdelltra/</t>
+          <t>https://www.indianpharmapost.com/regulatory/fda-cuts-monitoring-time-for-first-two-doses-of-amgens-imdelltra-21872</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15-09-2026 16:55 UTC</t>
+          <t>16-09-2026 12:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FDA reduces initial monitoring time for Amgen’s Imdelltra</t>
+          <t>Bristol Myers sues Amgen over proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/fda-reduces-initial-monitoring-time-for-amgens-imdelltra-21863</t>
+          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/bristol-myers-sues-amgen-over-proposed-opdivo-biosimilar/134282973</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16-09-2026 03:09 UTC</t>
+          <t>16-09-2026 08:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DP World Tour unveils 2027 schedule</t>
+          <t>Bristol-Myers Looks To Block Amgen's Cancer Biosimilar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Golf Business News</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://golfbusinessnews.com/news/sponsorship-and-events/dp-world-tour-unveils-2027-schedule/</t>
+          <t>https://www.law360.com/ip/articles/2525837/bristol-myers-looks-to-block-amgen-s-cancer-biosimilar-</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16-09-2026 11:10 UTC</t>
+          <t>16-09-2026 19:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,76 +1138,76 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bristol-Myers Targets Amgen’s Opdivo Biosimilar in Patent Suit</t>
+          <t>DP World Tour: BMW PGA Championship gets new date for 2027 due to Ryder Cup as significant schedule changes announced</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bloomberg Law News</t>
+          <t>Sky Sports</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.bloomberglaw.com/ip-law/bristol-myers-targets-amgens-opdivo-biosimilar-in-patent-suit</t>
+          <t>https://www.skysports.com/golf/news/12176/13588539/dp-world-tour-bmw-pga-championship-gets-new-date-for-2027-due-to-ryder-cup-as-significant-schedule-changes-announced</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>15-09-2026 17:06 UTC</t>
+          <t>16-09-2026 16:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DoP Secretary Manoj Joshi visits Amneal Pharmaceuticals</t>
+          <t>2027 Irish Open moved to July date at K Club</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>RTE.ie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/dop-secretary-manoj-joshi-visits-amneal-pharmaceuticals-21865</t>
+          <t>https://www.rte.ie/sport/golf/2026/0916/1591745-2027-irish-open-moved-to-july-date/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16-09-2026 10:23 UTC</t>
+          <t>16-09-2026 09:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Boryung and Korea Organon join to market Atozet for dyslipidemia in Korea - CHOSUNBIZ</t>
+          <t>DoP Secretary Manoj Joshi visits Amneal Pharmaceuticals</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/16/XIBOSIHBPRGKPAZEWREFTCCMLQ/</t>
+          <t>https://www.indianpharmapost.com/news/dop-secretary-manoj-joshi-visits-amneal-pharmaceuticals-21865</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16-09-2026 08:27 UTC</t>
+          <t>16-09-2026 10:23 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Boryung, Organon Korea Team Up on Cholesterol Drug Atozet</t>
+          <t>Boryung and Korea Organon join to market Atozet for dyslipidemia in Korea - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/culture/2026/09/16/boryung-organon-korea-team-up-on-cholesterol-drug-atozet</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/16/XIBOSIHBPRGKPAZEWREFTCCMLQ/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16-09-2026 01:48 UTC</t>
+          <t>16-09-2026 08:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PhaseV Appoints Biopharma Leaders Klaus Beck and Avi Kulkarni to Scientific Advisory Board to Guide Expansion of AI Conductor</t>
+          <t>Sandoz Appoints Ha Vo as General Manager, Vietnam</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/il/news-releases/phasev-appoints-biopharma-leaders-klaus-beck-and-avi-kulkarni-to-scientific-advisory-board-to-guide-expansion-of-ai-conductor-302880241.html</t>
+          <t>https://hrtoday.in/sandoz-appoints-ha-vo-as-general-manager-vietnam/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16-09-2026 12:30 UTC</t>
+          <t>16-09-2026 12:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sandoz Appoints Ha Vo as General Manager, Vietnam</t>
+          <t>PhaseV Appoints Biopharma Leaders Klaus Beck and Avi Kulkarni to Scientific Advisory Board to Guide Expansion of AI Conductor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/sandoz-appoints-ha-vo-as-general-manager-vietnam/</t>
+          <t>https://www.prnewswire.com/il/news-releases/phasev-appoints-biopharma-leaders-klaus-beck-and-avi-kulkarni-to-scientific-advisory-board-to-guide-expansion-of-ai-conductor-302880241.html</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16-09-2026 12:54 UTC</t>
+          <t>16-09-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Boryung to Take Charge of Domestic Sales and Marketing for 'Atojet'... Expanding Presence in the Dyslipidemia Market</t>
+          <t>PhaseV Adds Klaus Beck and Avi Kulkarni to Scientific Advisory Board</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>citybiz</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026091615093005618</t>
+          <t>https://www.citybiz.co/article/904492/phasev-adds-klaus-beck-and-avi-kulkarni-to-scientific-advisory-board/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16-09-2026 06:09 UTC</t>
+          <t>16-09-2026 20:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pharmaceutical Manufacturing Plant Setup in India</t>
+          <t>Xanthate Flotation Collectors Market</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IMARC Group</t>
+          <t>futuremarketinsights.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.imarcgroup.com/insight/pharmaceutical-manufacturing-plant-setup-cost-india</t>
+          <t>https://www.futuremarketinsights.com/reports/xanthate-flotation-collectors-market</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16-09-2026 12:54 UTC</t>
+          <t>17-09-2026 06:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The East African Community Seed and Plant Varieties Bill, 2025 must protect the Farmers and Seed Systems that feed the region</t>
+          <t>Dry Fungi Mycoproteins Market Size, Share &amp; Forecast 2036</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>greenpeace.org</t>
+          <t>Fact.MR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.greenpeace.org/africa/en/op-ed/61603/the-east-african-community-seed-and-plant-varieties-bill-2025-must-protect-the-farmers-and-seed-systems-that-feed-the-region/</t>
+          <t>https://www.factmr.com/report/dry-fungi-mycoproteins-market</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16-09-2026 13:17 UTC</t>
+          <t>17-09-2026 07:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HNLU Labour Law Students Visit Bhilai Steel Plant To Gain Practical Exposure To Industrial Operations And ...</t>
+          <t>Premier Energies to Form JV for 12 GWh BESS Facility</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Live Law</t>
+          <t>Construction World</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.livelaw.in/amp/lawschool/news/hnlu-labour-law-students-visit-bhilai-steel-plant-550211</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/premier-energies-to-form-jv-for-12-gwh-bess-facility/97510</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16-09-2026 04:45 UTC</t>
+          <t>17-09-2026 07:33 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Can plant-based omega-3s really protect your heart?</t>
+          <t>Pharmaceutical Manufacturing Plant Setup in India</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>futura-sciences.com</t>
+          <t>imarcgroup.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.futura-sciences.com/en/doctors-stunned-these-2-omega-3-foods-could-dramatically-protect-your-arteries_900009/</t>
+          <t>https://www.imarcgroup.com/insight/pharmaceutical-manufacturing-plant-setup-cost-india</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16-09-2026 12:12 UTC</t>
+          <t>16-09-2026 15:19 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Trees Can Tell When They’re Crooked and Grow Special Wood to Straighten Themselves</t>
+          <t>21,000 living plants shape Ganesh idol with a green message in Andhra Pradesh</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ZME Science</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.zmescience.com/science/biology/trees-correct-posture</t>
+          <t>https://www.indiatoday.in/india/story/21000-living-plants-turn-ganesh-idol-into-a-green-message-in-anakapalli-2996395-2026-09-17</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16-09-2026 13:08 UTC</t>
+          <t>16-09-2026 20:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Skanska starts work on Nowy Format office complex in Poland</t>
+          <t>Without bacteria or chemicals: How methanol and formaldehyde form abiotically in nature</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>World Construction Network</t>
+          <t>Phys.org</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.worldconstructionnetwork.com/news/skanska-starts-work-nowy-format/</t>
+          <t>https://phys.org/news/2026-09-bacteria-chemicals-methanol-formaldehyde-abiotically.html</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>16-09-2026 10:58 UTC</t>
+          <t>16-09-2026 19:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Attackers Exploit WooCommerce Wholesale Lead Capture Flaw to Plant PHP Web Shells</t>
+          <t>In 2020, NASA put seeds from 11 crops aboard an experimental spaceplane; after months in orbit, scientists</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>The Hacker News</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://thehackernews.com/2026/09/attackers-exploit-woocommerce-wholesale.html</t>
+          <t>https://m.economictimes.com/news/international/us/in-2020-nasa-put-seeds-from-11-crops-aboard-an-experimental-spaceplane-after-months-in-orbit-scientists-brought-them-back-to-test-whether-they-could-still-grow/amp_articleshow/134296275.cms</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16-09-2026 05:48 UTC</t>
+          <t>16-09-2026 20:18 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Plant Defies Inheritance: Sex Without Shuffle</t>
+          <t>What the Strait of Hormuz exposed about fertilizer security</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>miragenews.com</t>
+          <t>World Fertilizer</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.miragenews.com/plant-defies-inheritance-sex-without-shuffle-1745432/</t>
+          <t>https://www.worldfertilizer.com/environment/16092026/what-the-strait-of-hormuz-exposed-about-fertilizer-security/amp/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16-09-2026 15:11 UTC</t>
+          <t>16-09-2026 15:36 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>In 2017, a fully automated facility for plant bioscience research was launched to the International Space</t>
+          <t>Nevada’s First Wastewater-to-Drinking-Water Plant Takes Shape in Reno</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Governing</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/international/us/science-in-2017-a-fully-automated-facility-for-plant-bioscience-research-was-launched-to-the-international-space-station-what-nasa-studied-in-space/articleshow/134275632.cms</t>
+          <t>https://www.governing.com/infrastructure/nevadas-first-wastewater-to-drinking-water-plant-takes-shape-in-reno</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>16-09-2026 00:13 UTC</t>
+          <t>16-09-2026 21:21 UTC</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Barhale completes Anglian Water’s first plant tackling emerging contaminant Cypermethrin</t>
+          <t>The East African Community Seed and Plant Varieties Bill, 2025 must protect the Farmers and Seed Systems that feed the region</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>watermagazine.co.uk</t>
+          <t>greenpeace.org</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.watermagazine.co.uk/2026/09/16/barhale-completes-anglian-waters-first-plant-tackling-emerging-contaminant-cypermethrin/</t>
+          <t>https://www.greenpeace.org/africa/en/op-ed/61603/the-east-african-community-seed-and-plant-varieties-bill-2025-must-protect-the-farmers-and-seed-systems-that-feed-the-region/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>16-09-2026 04:00 UTC</t>
+          <t>16-09-2026 13:17 UTC</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>These Plants Have a Protein-Packed Diet, Too</t>
+          <t>Can plant-based omega-3s really protect your heart?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>Futura, le média qui explore le monde</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/09/07/style/carnivorous-houseplants-venus-flytrap-pitcher-plant.html</t>
+          <t>https://www.futura-sciences.com/en/doctors-stunned-these-2-omega-3-foods-could-dramatically-protect-your-arteries_900009/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>15-09-2026 20:08 UTC</t>
+          <t>16-09-2026 12:12 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,130 +1651,130 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hastings apartment building reopens after ricin exposure</t>
+          <t>Fertilizer Production Plant Feasibility Study Report 2026: Setup Cost, ROI &amp; Business Plan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lansing State Journal</t>
+          <t>industrytoday.co.uk</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.lansingstatejournal.com/story/news/local/michigan/2026/09/16/ricin-hastings-apartment-complex-mdhhs/91789647007/</t>
+          <t>https://industrytoday.co.uk/manufacturing/fertilizer-production-plant-feasibility-study-report-2026-setup-cost-roi-business-plan</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16-09-2026 14:41 UTC</t>
+          <t>16-09-2026 13:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Viatris-Mylan</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gilead expands lenacapavir licensing to cover once-yearly HIV prevention</t>
+          <t>Trees Can Tell When They’re Crooked and Grow Special Wood to Straighten Themselves</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>StreetInsider</t>
+          <t>ZME Science</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.streetinsider.com/Corporate+News/Gilead+expands+lenacapavir+licensing+to+cover+once-yearly+HIV+prevention/27067898.html</t>
+          <t>https://www.zmescience.com/science/biology/trees-correct-posture</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16-09-2026 12:33 UTC</t>
+          <t>16-09-2026 13:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pfizer follows AstraZeneca in pulling EU bladder cancer filing after CHMP concerns</t>
+          <t>Bringing the art of Bonsai to Utah</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>allsci.com</t>
+          <t>BYU Daily Universe</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://allsci.com/news/regulatory/zumrad-eu-application-pfizer-withdraws-zumrads/</t>
+          <t>https://universe.byu.edu/metro/bringing-the-art-of-bonsai-to-utah</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16-09-2026 11:12 UTC</t>
+          <t>16-09-2026 18:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pfizer – Every Insight Matters – HCP (Information from Industry)</t>
+          <t>Head and Neck Cancer Pipeline Gains Momentum: 80+ Companies Lead the Charge in Pioneering New Treatments | DelveInsight</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DocWireNews</t>
+          <t>Barchart.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.docwirenews.com/videos/pfizer-every-insight-matters-hcp-information-from-industry-breast-summit</t>
+          <t>https://www.barchart.com/press-releases/4646128/head-and-neck-cancer-pipeline-gains-momentum-80-companies-lead-the-charge-in-pioneering-new-treatments-delveinsight</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15-09-2026 19:22 UTC</t>
+          <t>16-09-2026 23:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Viatris-Mylan</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IP Group: NAV Reaches £1 Billion As Pfizer Obesity Royalty Value Rises To £152 Million</t>
+          <t>Gilead expands lenacapavir licensing to cover once-yearly HIV prevention</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pulse 2.0</t>
+          <t>StreetInsider</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://pulse2.com/ip-group-nav-reaches-1-billion-as-pfizer-obesity-royalty-value-rises-to-152-million/</t>
+          <t>https://www.streetinsider.com/Corporate+News/Gilead+expands+lenacapavir+licensing+to+cover+once-yearly+HIV+prevention/27067898.html</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16-09-2026 13:10 UTC</t>
+          <t>16-09-2026 12:31 UTC</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pfizer Invites Public to Listen to Webcast of Pfizer Discussion at Healthcare Conference - September 15, 2026</t>
+          <t>Is Pfizer’s New Business Big Enough To Carry The Old One?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Trefis</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/pfizer-invites-public-to-listen-to-webcast-of-pfizer-discussion-at-healthcare-conference-september-15-2026</t>
+          <t>https://www.trefis.com/stock/pfe/articles/615508/is-pfizers-new-business-big-enough-to-carry-the-old-one/2026-09-16</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>16-09-2026 02:28 UTC</t>
+          <t>16-09-2026 20:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sourabh Pandey Appointed Senior Director, Commercial AI at Pfizer</t>
+          <t>Pharma sector doubles down on AI to slash costs, timelines</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/sourabh-pandey-appointed-senior-director-commercial-ai-at-pfizer/</t>
+          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/pharma-sector-doubles-down-ai-amid-hopes-slashing-costs-timelines-2026-09-16/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>16-09-2026 09:40 UTC</t>
+          <t>16-09-2026 20:42 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>What is Pfizer rStock | How RPFE Works, Use Cases and Values | MEXC</t>
+          <t>Pfizer Raises 2026 Revenue Guidance to $62 Billion. Here’s What’s Behind the Beat</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MEXC</t>
+          <t>TIKR.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.mexc.co/en-PH/price/pfizer-rstock/info</t>
+          <t>https://www.tikr.com/blog/pfizer-raises-2026-revenue-guidance-to-62-billion-heres-whats-behind-the-beat</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>16-09-2026 13:00 UTC</t>
+          <t>16-09-2026 22:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fake-drug racket suspect holed up in Azerbaijan, Karnataka mulls CBI probe</t>
+          <t>Sourabh Pandey Appointed Senior Director, Commercial AI at Pfizer</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/bangalore/bidadi-fake-drug-racket-karnataka-cbi-probe-azerbaijan-link-10880597/</t>
+          <t>https://hrtoday.in/sourabh-pandey-appointed-senior-director-commercial-ai-at-pfizer/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>16-09-2026 10:36 UTC</t>
+          <t>16-09-2026 09:40 UTC</t>
         </is>
       </c>
     </row>
@@ -1894,22 +1894,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Two structural columns buckled on the 21st floor of the former Pfizer headquarters during its conversion into about 1,600 apartments. The failure prompted New York City to widen inspections, and work was subsequently halted at other Manhattan office-to-resi</t>
+          <t>The Zacks Analyst Blog Highlights Pfizer, Novartis, Candel and Janux</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ScienceBlog.com</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://scienceblog.com/m-two-structural-columns-buckled-on-the-21st-floor-of-the-former-pfizer-headquarters-during-its-conversion-into-about-1-600-apartments-the-failure-prompted-new-york-city-to-widen-ins/</t>
+          <t>https://finance.yahoo.com/healthcare/articles/zacks-analyst-blog-highlights-pfizer-094700942.html</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>15-09-2026 22:03 UTC</t>
+          <t>16-09-2026 09:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1921,265 +1921,265 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Before Karnataka police busted counterfeit medicine racket, CDSCO had sought regulation of pharma packaging suppliers</t>
+          <t>Pfizer follows AstraZeneca in pulling EU bladder cancer filing after CHMP concerns</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>The South First</t>
+          <t>AllSci</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://thesouthfirst.com/health/before-karnataka-police-busted-counterfeit-medicine-racket-cdsco-had-sought-regulation-of-pharma-packaging-suppliers/</t>
+          <t>https://allsci.com/news/regulatory/zumrad-eu-application-pfizer-withdraws-zumrads/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>16-09-2026 01:32 UTC</t>
+          <t>16-09-2026 11:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Eisai and Biogen Announce Japan Approval of LEQEMBI Pen, a Once-Weekly Subcutaneous Alzheimer’s Treatment</t>
+          <t>IP Group: NAV Reaches £1 Billion As Pfizer Obesity Royalty Value Rises To £152 Million</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Quiver Quantitative</t>
+          <t>Pulse 2.0</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.quiverquant.com/news/Eisai+and+Biogen+Announce+Japan+Approval+of+LEQEMBI+Pen%2C+a+Once-Weekly+Subcutaneous+Alzheimer%E2%80%99s+Treatment</t>
+          <t>https://pulse2.com/ip-group-nav-reaches-1-billion-as-pfizer-obesity-royalty-value-rises-to-152-million/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>16-09-2026 06:10 UTC</t>
+          <t>16-09-2026 13:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LEQEMBI® Pen (Subcutaneous Formulation of LEQEMBI®)</t>
+          <t>What is Pfizer rStock | How RPFE Works, Use Cases and Values | MEXC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>MEXC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/09/16/3362836/0/en/leqembi-pen-subcutaneous-formulation-of-leqembi-approved-in-japan-for-the-treatment-of-early-alzheimer-s-disease.html</t>
+          <t>https://www.mexc.co/en-PH/price/pfizer-rstock/info</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>16-09-2026 06:00 UTC</t>
+          <t>17-09-2026 00:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Canada agrees to help pay for Alzheimer’s drug LEQEMBI</t>
+          <t>Alteogen Files Patent for Once-Monthly Obesity Drug Technology; Preclinical Results Due in November</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Longevity.Technology</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://longevity.technology/news/canada-agrees-to-help-pay-for-alzheimers-drug-leqembi/</t>
+          <t>https://finance.biggo.com/news/6b592b49-bff8-4b09-bd35-a65185b3eb83</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>15-09-2026 23:10 UTC</t>
+          <t>17-09-2026 01:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s forays into India’s biosimilar immuno-oncology market, launches Nivorz</t>
+          <t>Fake-drug racket suspect holed up in Azerbaijan, Karnataka mulls CBI probe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>The Indian Express</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/dr-reddys-forays-into-indias-biosimilar-immuno-oncology-market-launches-nivorz/article71469381.ece</t>
+          <t>https://indianexpress.com/article/cities/bangalore/bidadi-fake-drug-racket-karnataka-cbi-probe-azerbaijan-link-10880597/</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>15-09-2026 16:03 UTC</t>
+          <t>16-09-2026 10:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Buy, Sell Or Hold: Dr Reddy's Labs, BEL, L&amp;T, HDFC Bank, Welspun Corp And Canara Bank — Ask Profit</t>
+          <t>Japan approves subcutaneous formulation of LEQEMBI® for treatment of early Alzheimer’s Disease</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>BioSpectrum Asia</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.ndtvprofit.com/markets/buy-sell-or-hold-dr-reddys-labs-bel-l-t-hdfc-bank-welspun-corp-and-canara-bank-ask-profit-12051254</t>
+          <t>https://www.biospectrumasia.com/news/30/28386/japan-approves-subcutaneous-formulation-of-leqembi-for-treatment-of-early-alzheimers-disease-.html</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>15-09-2026 17:07 UTC</t>
+          <t>17-09-2026 07:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Militant nurses accused of targeting billionaire health boss and daughter in disturbing campaign: ‘He can’t hide’</t>
+          <t>Revealed: The largest corporate charitable contributors in the Bay State</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>The Business Journals</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nypost.com/2026/09/16/us-news/prime-healthcare-ceo-prem-reddy-accuses-california-nurses-association-of-targeting-family-homes/</t>
+          <t>https://www.bizjournals.com/boston/research/lists/2026/largest-corporate-charitable-contributors-2026.html</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>16-09-2026 12:00 UTC</t>
+          <t>16-09-2026 23:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Domestic pharma market sustains growth momentum, but margins remain key</t>
+          <t>Midlands TD Insists Skyclarys Must Be Made Available As Soon As Possible</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>midlands103.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/market/mark-to-market/indian-pharma-market-ipm-pharma-stocks-domestic-pharma-dr-reddy-s-laboratories-sun-pharma-ajanta-pharma-glenmark/amp-11789538290089.html</t>
+          <t>https://www.midlands103.com/news/midlands-news/midlands-td-insists-skyclarys-must-be-made-available-as-soon-as-possible/</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>16-09-2026 07:26 UTC</t>
+          <t>17-09-2026 07:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Dr Reddy’s forays into Indian biosimilar immuno-oncology market</t>
+          <t>BREAKING – Petition which could help FA sisters reaches 100,000 signatures</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>The Redditch Standard</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/dr-reddys-forays-into-indian-biosimilar-immuno-oncology-market/articleshow/134268510.cms</t>
+          <t>https://redditchstandard.co.uk/news/breaking-petition-which-could-help-fa-sisters-reaches-100000-signatures/</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>15-09-2026 16:04 UTC</t>
+          <t>16-09-2026 23:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What Happens To Indian IT If AI Development Actually Slows</t>
+          <t>Eisai, Biogen announce Leqembi Pen has been approved in Japan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://upstox.com/news/market-news/latest-updates/what-happens-to-indian-it-if-ai-development-actually-slows/video-200348/</t>
+          <t>https://www.tipranks.com/news/the-fly/eisai-biogen-announce-leqembi-pen-has-been-approved-in-japan-thefly-news</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>16-09-2026 07:48 UTC</t>
+          <t>16-09-2026 12:57 UTC</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NSE Indices announces rejig across multiple Nifty indices, changes effective September 30</t>
+          <t>Dr. Reddy’s expands Gilead pact for HIV prevention drug</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/markets/capital-market-news/nse-indices-announces-rejig-across-multiple-nifty-indices-changes-effective-september-30-126091600365_1.html</t>
+          <t>https://www.thehindubusinessline.com/companies/dr-reddys-expands-pact-with-gilead-for-investigational-hiv-prevention-drug/article71475705.ece</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>16-09-2026 06:20 UTC</t>
+          <t>17-09-2026 07:35 UTC</t>
         </is>
       </c>
     </row>
@@ -2245,22 +2245,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gilead expands lenacapavir licensing to cover once-yearly HIV prevention</t>
+          <t>Militant nurses accused of targeting billionaire health boss and daughter in disturbing campaign: ‘He can’t hide’</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>StreetInsider</t>
+          <t>New York Post</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.streetinsider.com/Corporate+News/Gilead+expands+lenacapavir+licensing+to+cover+once-yearly+HIV+prevention/27067898.html</t>
+          <t>https://nypost.com/2026/09/16/us-news/prime-healthcare-ceo-prem-reddy-accuses-california-nurses-association-of-targeting-family-homes/</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>16-09-2026 12:33 UTC</t>
+          <t>16-09-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Laboratories: कैंसर की नई दवा 'Nivorz' के साथ भारतीय बाजार में एंट्री</t>
+          <t>Gilead expands lenacapavir licensing to cover once-yearly HIV prevention</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>StreetInsider</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/news/Hindi/healthcarebiotech/Dr-Reddys-Launches-Cancer-Drug-Nivorz-In-India/6aa990790416c068539d68fc</t>
+          <t>https://www.streetinsider.com/Corporate+News/Gilead+expands+lenacapavir+licensing+to+cover+once-yearly+HIV+prevention/27067898.html</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>15-09-2026 22:55 UTC</t>
+          <t>16-09-2026 12:31 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nestlé Health Science and Dr. Reddy's 2024 India Joint Venture</t>
+          <t>MFs turn selective, pick Coal India, LIC among large-caps</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4632173/nestle-health-science-and-dr-reddy-s-2024-india-joint-venture</t>
+          <t>https://m.economictimes.com/mf/analysis/mfs-turn-selective-pick-coal-india-lic-among-large-caps/amp_articleshow/134298752.cms</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15-09-2026 16:29 UTC</t>
+          <t>17-09-2026 02:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2326,76 +2326,76 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Launches Cancer Drug Nivorz In India</t>
+          <t>Remepy Welcomes Pharma R&amp;D Leader, Eran Harary, MD, as Chief Medical Officer, to Advance Hybrid Drug™ Pipeline</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>sg.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Launches-Cancer-Drug-Nivorz-In-India/6aa990790416c068539d68fc</t>
+          <t>https://sg.finance.yahoo.com/news/remepy-welcomes-pharma-r-d-113000258.html</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>15-09-2026 21:56 UTC</t>
+          <t>16-09-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BioTecNika Times-15-09-2026: Freshers Job at Accenture, Paid Internship at IISER &amp; Intas, Parexel WFH Jobs &amp; More</t>
+          <t>India clears 642-car import quota from UK under India-UK trade agreement</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BioTecNika</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.biotecnika.org/2026/09/biotecnika-times-15-09-2026/</t>
+          <t>https://m.economictimes.com/industry/auto/auto-news/india-clears-642-car-import-quota-from-uk-under-india-uk-trade-agreement/amp_articleshow/134283859.cms</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>15-09-2026 16:18 UTC</t>
+          <t>16-09-2026 09:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cipla Formalizes Leadership Transition with Board Meeting Outcome and Regulatory Disclosures</t>
+          <t>Kiran Mazumdar-Shaw Calls Out Fendi’s Rs 8.3 Lakh ‘Navratri’ Bag: ‘Undermines Our Authentic Talent’</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Pragativadi</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/cipla-shareholders-approve-leadership-appointments-through-postal-ballot-with-strong-majority/36103377</t>
+          <t>https://pragativadi.com/kiran-mazumdar-shaw-calls-out-fendis-rs-8-3-lakh-navratri-bag-undermines-our-authentic-talent/</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>15-09-2026 20:06 UTC</t>
+          <t>16-09-2026 19:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2407,22 +2407,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Biocon Ltd. Downgraded to Sell Amid Technical and Financial Concerns</t>
+          <t>Cultural Appropriation or Collaboration? Fendi’s 'Navratri' Bag With Indian Roots Sparks Debate</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MarketsMojo</t>
+          <t>herzindagi.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.marketsmojo.com/news/stock-recommendation/biocon-ltd-downgraded-to-sell-amid-technical-and-financial-concerns-4194441</t>
+          <t>https://www.herzindagi.com/fashion/cultural-appropriation-or-collaboration-fendi-navratri-bag-with-indian-roots-sparks-debate-article-1069221</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16-09-2026 04:19 UTC</t>
+          <t>17-09-2026 07:39 UTC</t>
         </is>
       </c>
     </row>
@@ -2434,103 +2434,103 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ET Under 40 2026: How technology is creating younger leaders</t>
+          <t>Fendi’s Rs 8 lakh ‘Gujarati mirror work bag’ sparks outrage - The Sentinel</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>The Sentinel - of this Land, for its People</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/company/corporate-trends/et-under-40-2026-how-technology-is-creating-younger-leaders/amp_articleshow/134271381.cms</t>
+          <t>https://www.sentinelassam.com/amp/story/more-news/entertainment/fendis-rs-8-lakh-gujarati-mirror-work-bag-sparks-outrage</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>15-09-2026 18:19 UTC</t>
+          <t>17-09-2026 03:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw Calls Out Fendi’s Rs 8.3 Lakh ‘Navratri’ Bag: ‘Undermines Our Authentic Talent’</t>
+          <t>Aurobindo Pharma receives final USFDA approval for generic Beclomethasone inhalation Aerosol</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pragativadi</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/kiran-mazumdar-shaw-calls-out-fendis-rs-8-3-lakh-navratri-bag-undermines-our-authentic-talent/</t>
+          <t>https://www.indianpharmapost.com/regulatory/aurobindo-pharma-receives-final-usfda-approval-for-generic-beclomethasone-inhalation-aerosol-21875</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>16-09-2026 06:53 UTC</t>
+          <t>16-09-2026 14:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw Slams Fendi’s Rs 8.3 Lakh Navratri-Style Bag, Says It Undermines Indian Talent</t>
+          <t>Remepy Welcomes Pharma R&amp;D Leader, Eran Harary, MD, as Chief Medical Officer, to Advance Hybrid Drug™ Pipeline</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Asianet Newsable</t>
+          <t>sg.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://newsable.asianetnews.com/entertainment/kiran-mazumdar-shaw-slams-fendis-rs-83-lakh-navratri-style-bag-says-it-undermines-indian-talent-articleshow-eo73h7b</t>
+          <t>https://sg.finance.yahoo.com/news/remepy-welcomes-pharma-r-d-113000258.html</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>16-09-2026 07:10 UTC</t>
+          <t>16-09-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Harsh Goenka, Kiran Mazumdar-Shaw Call Out Fendi’s ₹8.3 Lakh ‘Navratri Bag’, Question Indian Craft</t>
+          <t>Closing Bell: Market snaps 2-day fall; Sensex up 332 pts, Nifty above 23,200</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Free Press Journal</t>
+          <t>IndiaIPO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/amp/viral/harsh-goenka-kiran-mazumdar-shaw-call-out-fendis-83-lakh-navratri-bag-question-indian-craft-credit-netizens-react</t>
+          <t>https://www.indiaipo.in/news/detail/closing-bell-market-snaps-2-day-fall-sensex-up-332-pts-nifty-above-23200</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16-09-2026 07:20 UTC</t>
+          <t>16-09-2026 11:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2542,22 +2542,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma wins U.S. FDA approval for generic asthma inhaler</t>
+          <t>Former Novartis Executive Ingrid Zhang Named Legend Biotech CEO, Succeeds Ying Huang</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>medicaldialogues.in</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/aurobindo-pharma-wins-us-fda-approval-for-generic-asthma-inhaler/article71469168.ece</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/former-novartis-executive-ingrid-zhang-named-legend-biotech-ceo-succeeds-ying-huang-179378</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>16-09-2026 04:51 UTC</t>
+          <t>16-09-2026 13:12 UTC</t>
         </is>
       </c>
     </row>
@@ -2569,22 +2569,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma receives final USFDA approval for generic Beclomethasone inhalation Aerosol</t>
+          <t>Bristol Myers, Ono Sue Amgen to Block Proposed Opdivo Biosimilar in US</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>medicaldialogues.in</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/regulatory/aurobindo-pharma-receives-final-usfda-approval-for-generic-beclomethasone-inhalation-aerosol-21875</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/bristol-myers-ono-sue-amgen-to-block-proposed-opdivo-biosimilar-in-us-179377</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>16-09-2026 12:52 UTC</t>
+          <t>16-09-2026 13:05 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,22 +2596,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma gets FDA nod for asthma inhaler</t>
+          <t>Sjögren's Syndrome Market to Witness Sustained Growth During the Forecast Period (2026-2036) Due to the Development of Targeted Immunotherapies, FcRn Inhibitors, TYK2 Inhibitors, and Cell Therapies | DelveInsight</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>prnewswire.co.uk</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/amp/news/drug-approvals-and-launches/aurobindo-pharma-gets-fda-nod-for-asthma-inhaler/134276350</t>
+          <t>https://www.prnewswire.co.uk/news-releases/sjogrens-syndrome-market-to-witness-sustained-growth-during-the-forecast-period-20262036-due-to-the-development-of-targeted-immunotherapies-fcrn-inhibitors-tyk2-inhibitors-and-cell-therapies--delveinsight-302880061.html</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>16-09-2026 02:15 UTC</t>
+          <t>16-09-2026 14:31 UTC</t>
         </is>
       </c>
     </row>
@@ -2623,22 +2623,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Gets USFDA Nod for First Metered-Dose Inhaler, Beclomethasone Aerosol</t>
+          <t>Gilead Expands Lenacapavir Access With New PAHO Deal in Latin America</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>sg.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/aurobindo-pharma-gets-usfda-nod-for-first-metered-dose-inhaler-beclomethasone-aerosol-179322</t>
+          <t>https://sg.finance.yahoo.com/news/gilead-expands-lenacapavir-access-paho-142600311.html</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>15-09-2026 16:49 UTC</t>
+          <t>16-09-2026 14:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2650,22 +2650,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Gets First USFDA Inhaler Nod</t>
+          <t>Market wrap: SBI, HDFC Life, TCS, Infosys top gainers and losers on Nifty and Sensex on Thursday</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Voice of Healthcare</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://vohnetwork.com/news/pharma/aurobindo-pharma-receives-first-usfda-approval-for-metered-dose-inhaler</t>
+          <t>https://m.economictimes.com/markets/stocks/news/market-wrap-sbi-hdfc-life-tcs-infosys-top-gainers-and-losers-on-nifty-and-sensex-on-thursday/articleshow/134286572.cms</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>16-09-2026 06:20 UTC</t>
+          <t>16-09-2026 11:33 UTC</t>
         </is>
       </c>
     </row>
@@ -2677,22 +2677,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma shares in focus after USFDA issues one observation for Telangana facility</t>
+          <t>AI, algorithms and human judgement: The future of portfolio management</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/markets/aurobindo-pharma-shares-in-focus-after-usfda-issues-one-observation-for-telangana-facility-14030516.html/amp</t>
+          <t>https://m.economictimes.com/markets/stocks/news/ai-algorithms-and-human-judgement-the-future-of-portfolio-management/articleshow/134285324.cms</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>16-09-2026 01:35 UTC</t>
+          <t>16-09-2026 10:42 UTC</t>
         </is>
       </c>
     </row>
@@ -2704,22 +2704,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Aurobindo obtains FDA OK for generic QVAR</t>
+          <t>Sebi bars two entities over alleged cross-derivatives manipulation</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Drug Store News</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://drugstorenews.com/aurobindo-obtains-fda-ok-generic-qvar</t>
+          <t>https://m.economictimes.com/markets/stocks/news/indian-regulator-bars-two-entities-over-alleged-cross-derivatives-manipulation/articleshow/134291762.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>15-09-2026 15:37 UTC</t>
+          <t>16-09-2026 15:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2731,22 +2731,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Aurobindo arm Apitoria gets USFDA observation for Telangana API unit</t>
+          <t>India clears 642-car import quota from UK under India-UK trade agreement</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/aurobindo-arm-apitoria-gets-usfda-observation-for-telangana-api-unit/articleshow/134268517.cms</t>
+          <t>https://m.economictimes.com/industry/auto/auto-news/india-clears-642-car-import-quota-from-uk-under-india-uk-trade-agreement/amp_articleshow/134283859.cms</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>15-09-2026 16:04 UTC</t>
+          <t>16-09-2026 09:49 UTC</t>
         </is>
       </c>
     </row>
@@ -2758,76 +2758,76 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma: अमेरिकी FDA जांच में कंपनी को मिली बड़ी राहत, सिर्फ **1** ऑब्जर्वेशन</t>
+          <t>Cabinet raises PF wage ceiling to Rs 25,000 from Rs 15,000</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/corporate-news/Hindi/healthcarebiotech/Aurobindo-Pharma-Subsidiary-Unit-II-Clears-US-FDA-Inspection-With-One-Observation/6aa93dd0f2017017ae6a7fab</t>
+          <t>https://m.economictimes.com/industry/banking/finance/cabinet-raises-pf-wage-ceiling-to-rs-25000-ashwini-vaishnaw/amp_articleshow/134284053.cms</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>16-09-2026 06:24 UTC</t>
+          <t>16-09-2026 09:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Wins First Inhaler Approval, Faces Unit Audit</t>
+          <t>Shilpa Biologicals, SPIMACO Bio Ink MENA Biosimilars Deal</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Aurobindo-Pharma-Wins-First-Inhaler-Approval-Faces-Unit-Audit/6aa9fa570416c068539e1373</t>
+          <t>https://www.contractpharma.com/breaking-news/shilpa-biologicals-spimaco-bio-ink-mena-biosimilars-deal/</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16-09-2026 02:09 UTC</t>
+          <t>16-09-2026 13:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma: అమెరికా FDA తనిఖీల్లో క్లీన్ చిట్.. ఒక్క అబ్జర్వేషన్‌తో ముగిసిన ఆడిట్</t>
+          <t>Shilpa Bio inks deal for PD-1 biosimilar for MENA market</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/corporate-news/Telugu/healthcarebiotech/Aurobindo-Pharma-Subsidiary-Unit-II-Clears-US-FDA-Inspection-With-One-Observation/6aa93dd0f2017017ae6a7fab</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/shilpa-bio-inks-deal-for--1-biosimilar-for-mena-market</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16-09-2026 03:36 UTC</t>
+          <t>16-09-2026 11:08 UTC</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals, SPIMACO Bio Ink MENA Biosimilars Deal</t>
+          <t>Piramal Pharma Plans Solar Power Plant in UK</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/shilpa-biologicals-spimaco-bio-ink-mena-biosimilars-deal/</t>
+          <t>https://www.contractpharma.com/breaking-news/piramal-pharma-plans-solar-power-plant-in-uk/</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>16-09-2026 13:24 UTC</t>
+          <t>16-09-2026 14:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2866,22 +2866,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals and SPIMACO Bio sign strategic license agreement for PD-1 Biosimilar for MENA market</t>
+          <t>Thermo Fisher Launches SuperScript V Reverse Transcriptase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.expresspharma.in/shilpa-biologicals-and-spimaco-bio-sign-strategic-license-agreement-for-pd-1-biosimilar-for-mena-market/</t>
+          <t>https://www.contractpharma.com/breaking-news/thermo-fisher-launches-superscript-v-reverse-transcriptase/</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>16-09-2026 07:32 UTC</t>
+          <t>16-09-2026 19:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2893,22 +2893,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals and SPIMACO Bio sign strategic license agreement for PD-1 Biosimilar for MENA market</t>
+          <t>Gilead Partners With Pan American Health Organization on Lenacapavir Access for Latin America, Caribbean</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>biospectrumasia.com</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/25/28379/shilpa-biologicals-and-spimaco-bio-sign-strategic-license-agreement-for-pd-1-biosimilar-for-mena-market.html</t>
+          <t>https://www.contractpharma.com/breaking-news/gilead-partners-with-pan-american-health-organization-on-lenacapavir-access-for-latin-america-caribbean/</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>16-09-2026 03:57 UTC</t>
+          <t>16-09-2026 19:36 UTC</t>
         </is>
       </c>
     </row>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals and SPIMACO Collaborate on PD-1 Biosimilar for MENA Market</t>
+          <t>Lilly TuneLab, Twist Bioscience Partner on Antibody Drug Discovery</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chemical Industry Digest</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://chemindigest.com/shilpa-biologicals-and-spimaco-collaborate-on-pd-1-biosimilar-for-mena-market/</t>
+          <t>https://www.contractpharma.com/breaking-news/lilly-tunelab-twist-bioscience-partner-on-antibody-drug-discovery/</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16-09-2026 06:27 UTC</t>
+          <t>16-09-2026 16:02 UTC</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Complex-Molecule Specialist Shilpa CDMO Launches at CPHI Milan</t>
+          <t>Hovione Doubles US Spray-Drying Capacity With Opening of New NJ Facility</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2957,39 +2957,39 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/live_from_shows/complex-molecule-specialist-shilpa-cdmo-launches-at-cphi-milan/</t>
+          <t>https://www.contractpharma.com/breaking-news/hovione-doubles-us-spray-drying-capacity-with-opening-of-new-nj-facility/</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>15-09-2026 19:33 UTC</t>
+          <t>16-09-2026 14:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Unclogging India’s innovation pipeline</t>
+          <t>Samsung Begins Official Rollout of One UI 9, Bringing the Latest Galaxy Experiences to More Devices</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.expresspharma.in/unclogging-indias-innovation-pipeline/</t>
+          <t>https://news.samsung.com/global/samsung-begins-official-rollout-of-one-ui-9-bringing-the-latest-galaxy-experiences-to-more-devices</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>16-09-2026 08:03 UTC</t>
+          <t>16-09-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3001,22 +3001,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Samsung Begins Official Rollout of One UI 9, Bringing the Latest Galaxy Experiences to More Devices</t>
+          <t>Samsung Galaxy S26 Price To Hike By Rs 12,000 in India: Check New Prices</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>My Mobile India</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-begins-official-rollout-of-one-ui-9-bringing-the-latest-galaxy-experiences-to-more-devices</t>
+          <t>https://www.mymobileindia.com/samsung-galaxy-s26-price-to-hike-by-rs-12000-in-india-check-new-prices/</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>16-09-2026 12:00 UTC</t>
+          <t>17-09-2026 04:08 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Samsung Begins Official Rollout of One UI 9, Bringing the Latest Galaxy Experiences to More Devices</t>
+          <t>Samsung Galaxy S26 gets first price hike in India, will start at Rs 99,999 from September 20th</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>samsungmobilepress.com</t>
+          <t>91mobiles.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.samsungmobilepress.com/articles/one-ui-9-official-rollout-latest-galaxy-experiences</t>
+          <t>https://www.91mobiles.com/hub/samsung-galaxy-s26-first-price-hike-india-september-20th/</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>16-09-2026 12:04 UTC</t>
+          <t>17-09-2026 04:38 UTC</t>
         </is>
       </c>
     </row>
@@ -3055,22 +3055,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Samsung announces official One UI 9 rollout</t>
+          <t>Samsung Begins Official Rollout of One UI 9, Bringing the Latest Galaxy Experiences to More Devices</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Samsung Mobile Press</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/samsung-announces-official-one-ui-9-rollout/</t>
+          <t>https://www.samsungmobilepress.com/articles/one-ui-9-official-rollout-latest-galaxy-experiences</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>16-09-2026 12:00 UTC</t>
+          <t>16-09-2026 12:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3082,22 +3082,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Samsung India expects double-digit growth in H2 fuelled by festive demand, premiumisation</t>
+          <t>Samsung One UI 9 Rollout Starts for Galaxy S26 Series: Check Eligible Galaxy Devices, New Features</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/samsung-india-expects-double-digit-growth-in-h2-fuelled-by-festive-demand-premiumisation/article71473172.ece</t>
+          <t>https://www.gadgets360.com/mobiles/news/samsung-one-ui-9-rollout-galaxy-s26-series-eligible-devices-features-12057853</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>16-09-2026 14:49 UTC</t>
+          <t>17-09-2026 06:17 UTC</t>
         </is>
       </c>
     </row>
@@ -3109,22 +3109,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Samsung India launches 2026 Bespoke AI appliances</t>
+          <t>Samsung India Sees Strong Festive Season Demand, Projects Double-Digit Growth</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>t2online.in</t>
+          <t>Indian Retailer</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://t2online.in/tech/tech-news/samsung-india-launches-2026-bespoke-ai-appliances/2008052</t>
+          <t>https://www.indianretailer.com/news/samsung-india-sees-strong-festive-season-demand-projects-double-digit-growth</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>16-09-2026 11:14 UTC</t>
+          <t>17-09-2026 06:22 UTC</t>
         </is>
       </c>
     </row>
@@ -3136,22 +3136,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>This is the Android phone I wish Google and Samsung would copy</t>
+          <t>Samsung launches new AI fridge in India that recommends recipes; check Bespoke AI lineup and prices</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>How-To Geek</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.howtogeek.com/this-is-the-android-phone-i-wish-google-and-samsung-would-copy/</t>
+          <t>https://www.livemint.com/technology/samsung-launches-new-ai-fridge-in-india-that-recommends-recipes-check-bespoke-ai-lineup-and-prices-11789621850749.html</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>16-09-2026 13:00 UTC</t>
+          <t>17-09-2026 05:56 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,22 +3163,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 One UI 9 Stable Update: What's Confirmed</t>
+          <t>Samsung India expects double-digit growth in H2 appliances on festive demand</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gadget Hacks</t>
+          <t>The Shillong Times</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://samsung.gadgethacks.com/news/samsung-galaxy-s26-one-ui-9-stable-update-whats-confirmed/</t>
+          <t>https://theshillongtimes.com/2026/09/17/samsung-india-expects-double-digit-growth-in-h2-appliances-on-festive-demand/</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>16-09-2026 13:50 UTC</t>
+          <t>17-09-2026 00:44 UTC</t>
         </is>
       </c>
     </row>
@@ -3190,22 +3190,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>One UI 9 stable update starts rolling out for Samsung Galaxy S26 users</t>
+          <t>Samsung just made its refrigerator smarter with Gemini; new AI appliances launched in India | Technology News
+(HT Tech)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>91mobiles.com</t>
+          <t>Hindustan Times</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.91mobiles.com/hub/one-ui-9-stable-update-rollout-galaxy-s26-series/</t>
+          <t>https://www.hindustantimes.com/technology/samsung-just-made-its-refrigerator-smarter-with-gemini-new-ai-appliances-launched-in-india-101789624645164.html</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>16-09-2026 11:22 UTC</t>
+          <t>17-09-2026 06:14 UTC</t>
         </is>
       </c>
     </row>
@@ -3217,22 +3218,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Samsung expects double-digit H2 growth in appliances on festive demand, premiumisation</t>
+          <t>Samsung Launches Stable One UI 9.0 for Galaxy S26 Series</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>India News Network</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/companies/samsung-expects-double-digit-h2-growth-in-appliances-on-festive-demand-premiumisation-14031241.html</t>
+          <t>https://www.indianewsnetwork.com/en/samsung-launches-stable-one-ui-9-0-galaxy-s26-series-20260917</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>16-09-2026 10:44 UTC</t>
+          <t>17-09-2026 04:40 UTC</t>
         </is>
       </c>
     </row>
@@ -3244,22 +3245,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Samsung officially releases One UI 9 for the Galaxy S26, S26+, and S26 Ultra - GSMArena.com news</t>
+          <t>Samsung One UI 9 stable update rolls out starting with Galaxy S26 series</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>FoneArena.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.gsmarena.com/samsung_officially_releases_one_ui_9_based_on_android_17_for_the_galaxy_s26_s26_and_s26_ultra-news-74642.php</t>
+          <t>https://www.fonearena.com/blog/492571/samsung-one-ui-9-stable-roll-out-galaxy-s26-series.html</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>16-09-2026 12:00 UTC</t>
+          <t>17-09-2026 05:14 UTC</t>
         </is>
       </c>
     </row>
@@ -3271,22 +3272,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Samsung India Launches 2026 Range of Bespoke AI Appliances Designed to be Your True Home Companion</t>
+          <t>Samsung One UI 9.0 Stable Update Based on Android 17 Rolls Out for Galaxy S26 Series: Check New Features</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Gizbot</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/in/samsung-india-launches-2026-range-of-bespoke-ai-appliances-designed-to-be-your-true-home-companion</t>
+          <t>https://www.gizbot.com/mobile/news/samsung-one-ui-9-0-stable-update-android-17-rolls-out-galaxy-s26-series-new-features-128585.html</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>16-09-2026 12:17 UTC</t>
+          <t>17-09-2026 06:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3298,22 +3299,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Samsung releases stable One UI 9.0 update for Galaxy S26 series</t>
+          <t>Samsung begins rolling out One UI 9 with Android 17: Galaxy phones getting update and new features</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/galaxy-s26-stable-one-ui-9-0-update-released/</t>
+          <t>https://www.businesstoday.in/technology/news/story/samsung-begins-rolling-out-one-ui-9-with-android-17-galaxy-phones-getting-update-and-new-features-556067-2026-09-17</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>16-09-2026 08:28 UTC</t>
+          <t>17-09-2026 06:02 UTC</t>
         </is>
       </c>
     </row>
@@ -3325,76 +3326,76 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Samsung India expects double-digit growth in H2 appliances biz on festive demand</t>
+          <t>Samsung launches Samsung Innovation Campus 2026 in Karnataka to Build an AI-ready Future, to Train 2000 Students</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/samsung-india-expects-double-digit-growth-in-h2-appliances-biz-on-festive-demand/article71472514.ece</t>
+          <t>https://news.samsung.com/in/samsung-launches-samsung-innovation-campus-2026-in-karnataka-to-build-an-ai-ready-future-to-train-2000-students</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>16-09-2026 12:48 UTC</t>
+          <t>17-09-2026 05:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>More details about the Samsung Galaxy S27 Ultra's cameras emerge - GSMArena.com news</t>
+          <t>Celltrion’s Remsima Takes No. 1 in Japan After 11 Years</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.gsmarena.com/more_details_about_the_samsung_galaxy_s27_ultras_cameras_emerge-news-74633.php</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277185</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>15-09-2026 23:31 UTC</t>
+          <t>17-09-2026 03:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Samsung Begins Official Rollout of One UI 9, Bringing the Latest Galaxy Experiences to More Devices</t>
+          <t>Celltrion's Remsima Tops Japan's Infliximab Market, Surpassing Originator Drug</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/us/samsung-begins-official-rollout-one-ui-9-latest-galaxy-experiences-devices</t>
+          <t>https://finance.biggo.com/news/2ce8c00d-beb2-47a2-af48-bd21e57cd128</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>16-09-2026 12:04 UTC</t>
+          <t>17-09-2026 02:25 UTC</t>
         </is>
       </c>
     </row>
@@ -3406,22 +3407,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Zymfentra, Xcopri projected to become Korea’s 1st $1 billion blockbuster drugs in 2027</t>
+          <t>Celltrion’s Remsima Takes No. 1 Spot in Japan’s Infliximab Market After 11 Years</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Korea IT Times</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33200</t>
+          <t>https://www.koreaittimes.com/news/articleView.html?idxno=157265</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>16-09-2026 06:19 UTC</t>
+          <t>17-09-2026 01:37 UTC</t>
         </is>
       </c>
     </row>
@@ -3433,22 +3434,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Celltrion, SK Biopharmaceuticals Drugs Poised to Top ₩1 Trillion Each Next Year — South Korea's First Blockbusters in Sight</t>
+          <t>Celltrion's autoimmune disease treatment "Ramsima" overtook the original drug 11 years after its lau..</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/3a921a30-a622-4e22-bc3e-17f7934234eb</t>
+          <t>https://www.mk.co.kr/en/it/12155321</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>16-09-2026 01:35 UTC</t>
+          <t>17-09-2026 05:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3460,22 +3461,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Celltrion Submits Phase 4 Trial Plan for Zymfentra</t>
+          <t>Celltrion's Remsima Tops Japan Infliximab Market After 11 Years</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>thelec.net</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.thelec.net/news/articleView.html?idxno=13949</t>
+          <t>https://en.sedaily.com/finance/2026/09/17/celltrions-remsima-tops-japan-infliximab-market-after-11</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>15-09-2026 22:49 UTC</t>
+          <t>17-09-2026 00:20 UTC</t>
         </is>
       </c>
     </row>
@@ -3487,22 +3488,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Celltrion Repurchases KRW100 Billion in Shares</t>
+          <t>Celltrion's Ramcima tops Japan's infliximab market for first time, overtaking originator</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/celltrion-repurchases-krw100-billion-in-shares-ce785bd2db8ef021</t>
+          <t>https://mbiz.heraldcorp.com/article/10876273</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>16-09-2026 07:33 UTC</t>
+          <t>16-09-2026 23:04 UTC</t>
         </is>
       </c>
     </row>
@@ -3514,22 +3515,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Celltrion retires W100b in shares, pledges third of net profit to shareholders</t>
+          <t>Celltrion captures Japan lead with Remsima biosimilar, eyes SC launch - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://mbiz.heraldcorp.com/article/10874870</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/17/EBUUYC3ILVC6THC2NCM5WFOSQU/</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>15-09-2026 23:21 UTC</t>
+          <t>16-09-2026 23:56 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,22 +3542,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Celltrion to Cancel 100 Billion Won in Treasury Shares</t>
+          <t>Celltrion's Remsima Tops Japanese Infliximab Prescriptions After 11 Years Since Launch</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/16/celltrion-to-cancel-100-billion-won-in-treasury-shares</t>
+          <t>https://www.asiae.co.kr/en/article/2026091707490713431</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>15-09-2026 23:53 UTC</t>
+          <t>16-09-2026 22:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3568,157 +3569,157 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>South Korea's Celltrion Resolves to Retire ₩100 Billion in Treasury Shares; Full-Year Return Tops ₩200 Billion</t>
+          <t>Zymfentra, Xcopri Near $1 Billion Sales Mark</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/93eb049d-6238-433b-ab92-151e68e9dfa8</t>
+          <t>https://en.sedaily.com/finance/2026/09/17/zymfentra-xcopri-near-1-billion-sales-mark</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>16-09-2026 00:55 UTC</t>
+          <t>16-09-2026 22:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Celltrion to cancel $73 million in treasury shares</t>
+          <t>Prestige Biopharma IDC Obtains International Certification for Environmental and Occupational Health and Safety Standards</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>The Korea News Plus</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.newsarticleinsiders.com/news/articleView.html?idxno=4557</t>
+          <t>https://www.asiae.co.kr/en/article/stock-etc/2026091709115812850</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>15-09-2026 23:52 UTC</t>
+          <t>17-09-2026 00:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Celltrion cancels 540,000 shares, expands Korea buybacks to 200 billion won - CHOSUNBIZ</t>
+          <t>About 20 Pusan National University Students Visit Bio and Logistics Sites... BJFEZ Holds 'Insight Trip'</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/16/7BIJI2VO4ZCB5PU5P3LGJWECKE/?outputType=amp</t>
+          <t>https://www.asiae.co.kr/en/article/yeongnam/2026091715044359776</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>15-09-2026 23:51 UTC</t>
+          <t>17-09-2026 06:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Zymfentra, Xcopri Set to Join Korea's First 1 Trillion Won Drug Club</t>
+          <t>Fortis Healthcare moves Supreme Court against forensic audit order</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/16/zymfentra-xcopri-set-to-join-koreas-first-1-trillion-won</t>
+          <t>https://www.thehindubusinessline.com/companies/fortis-healthcare-files-slp-against-forensic-audit-order-in-daiichi-sankyo-case/article71473603.ece</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>16-09-2026 00:17 UTC</t>
+          <t>16-09-2026 15:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Zymfentra, Xcopri near Korea’s first blockbuster as sales surge past 1 trillion won - CHOSUNBIZ</t>
+          <t>AZ, Daiichi's Enhertu scores long-awaited NICE blessing in HER2-low breast cancer</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/16/5DC4LLVP4FDENMPU7SIK7UBU3Q/?outputType=amp</t>
+          <t>https://www.fiercepharma.com/pharma/az-daiichis-enhertu-wins-long-awaited-nice-blessing</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>16-09-2026 00:45 UTC</t>
+          <t>16-09-2026 23:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Korean Blockbuster Drugs 'On the Horizon': Zymfentra and Xcopri Race Towards Trillion-Won Sales</t>
+          <t>Fortis moves SC against HC forensic audit order in company transactions</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>재경일보</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.jkn.co.kr/post/987178</t>
+          <t>https://www.business-standard.com/amp/companies/news/fortis-moves-sc-against-hc-forensic-audit-order-in-company-transactions-126091600888_1.html</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>15-09-2026 23:35 UTC</t>
+          <t>16-09-2026 11:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,22 +3731,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Challenges Forensic Audit in Daiichi Case</t>
+          <t>Daiichi and AstraZeneca cancer drugs secure further approvals in Japan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/fortis-healthcare-challenges-forensic-audit-in-daiichi-case/54450820260916</t>
+          <t>https://www.marketscreener.com/news/daiichi-and-astrazeneca-cancer-drugs-secure-further-approvals-in-japan-ce785bd2da8bff24</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>16-09-2026 14:57 UTC</t>
+          <t>16-09-2026 08:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3757,22 +3758,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Fortis Healthcare moves SC against Delhi HC order directing forensic audit in Daiichi Sankyo case</t>
+          <t>Fortis Healthcare moves Supreme Court against Delhi HC forensic audit order</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ETLegalWorld.com</t>
+          <t>Rediff</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://legal.economictimes.indiatimes.com/news/litigation/fortis-healthcare-moves-sc-against-delhi-hc-order-directing-forensic-audit-in-daiichi-sankyo-case/134280337</t>
+          <t>https://www.rediff.com/business/report/fortis-healthcare-challenges-delhi-hc-forensic-audit-into-alleged-asset-erosion-by-former-promoters/20260917.htm</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>16-09-2026 07:43 UTC</t>
+          <t>17-09-2026 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3784,373 +3785,373 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Fortis moves SC against HC forensic audit order in company transactions</t>
+          <t>Fortis moves SC against Delhi HC order in Daiichi Sankyo award case</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Asianet Newsable</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/companies/news/fortis-moves-sc-against-hc-forensic-audit-order-in-company-transactions-126091600888_1.html</t>
+          <t>https://newsable.asianetnews.com/india/fortis-moves-sc-against-delhi-hc-order-in-daiichi-sankyo-award-case-articleshow-v6wnlq7</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>16-09-2026 11:51 UTC</t>
+          <t>16-09-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi Sankyo’s ENHERTU Cuts Disease Progression Risk by 37% in HER2-Mutant Lung Cancer</t>
+          <t>Vishal Sikka's Hang Ten Systems Raises $53M Just Five Weeks After Seed Round</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>BBN Times</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/31/8438/astrazeneca-daiichi-sankyos-enhertu-cuts-disease-progression-risk-by-37-in-her2-mutant-lung-cancer.html</t>
+          <t>https://www.bbntimes.com/technology/vishal-sikka-s-hang-ten-systems-raises-53m-just-five-weeks-after-seed-round</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>16-09-2026 00:32 UTC</t>
+          <t>16-09-2026 18:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Daiichi and AstraZeneca cancer drugs secure further approvals in Japan</t>
+          <t>Former Infosys chief’s AI startup nabs another $53M</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>TechCrunch</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/daiichi-and-astrazeneca-cancer-drugs-secure-further-approvals-in-japan-ce785bd2da8bff24</t>
+          <t>https://techcrunch.com/2026/09/16/former-infosys-chiefs-ai-startup-adds-50m-to-seed-weeks-after-initial-raise/</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>16-09-2026 08:47 UTC</t>
+          <t>16-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Fortis Healthcare files Supreme Court petition against Delhi HC order</t>
+          <t>Fresenius SE &amp; Co. KGaA : Barclays reaffirms its Buy rating</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/fortis-healthcare-files-supreme-court-petition-against-delhi-hc-order/51082591</t>
+          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-barclays-reaffirms-its-buy-rating-ce785bd2dc88f726</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>16-09-2026 05:39 UTC</t>
+          <t>16-09-2026 12:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Fortis moves SC against Delhi HC order in Daiichi Sankyo award case</t>
+          <t>SK Hynix reportedly in talks with Intel to build memory chips in US</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Asianet Newsable</t>
+          <t>TechCrunch</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://newsable.asianetnews.com/india/fortis-moves-sc-against-delhi-hc-order-in-daiichi-sankyo-award-case-articleshow-v6wnlq7</t>
+          <t>https://techcrunch.com/2026/09/16/sk-hynix-reportedly-in-talks-with-intel-to-build-memory-chips-in-us/</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>16-09-2026 11:00 UTC</t>
+          <t>16-09-2026 13:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Fortis Healthcare: సుప్రీంకోర్టుకు చేరిన Daiichi Sankyo వివాదం.. కంపెనీ కీలక అప్డేట్</t>
+          <t>Trialynx Wins DPHARM Idol Disrupt 2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/corporate-news/Telugu/healthcarebiotech/Fortis-Healthcare-Files-Supreme-Court-Plea-In-Daiichi-Sankyo-Case/6aaa2a35f2017017ae6aefa5</t>
+          <t>https://www.fiercepharma.com/partner-content/trialynx-wins-dpharm-idol-disrupt-2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>16-09-2026 05:40 UTC</t>
+          <t>16-09-2026 16:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Former Infosys chief’s AI startup nabs another $53M</t>
+          <t>Alkermes Announces Appointment of Anne C. Whitaker to Board of Directors</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TechCrunch</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/former-infosys-chiefs-ai-startup-adds-50m-to-seed-weeks-after-initial-raise/</t>
+          <t>https://www.biospace.com/press-releases/alkermes-announces-appointment-of-anne-c-whitaker-to-board-of-directors</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>16-09-2026 13:00 UTC</t>
+          <t>16-09-2026 14:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA : Barclays reaffirms its Buy rating</t>
+          <t>GSK Pharma Shareholders Approve Board and Managing Director Appointments via Postal Ballot</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-barclays-reaffirms-its-buy-rating-ce785bd2dc88f726</t>
+          <t>https://www.tipranks.com/news/company-announcements/gsk-pharma-shareholders-approve-board-and-managing-director-appointments-via-postal-ballot</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>16-09-2026 12:09 UTC</t>
+          <t>16-09-2026 16:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SK Hynix reportedly in talks with Intel to build memory chips in US</t>
+          <t>Alvotech Shares Rise After Double Upgrade From Barclays</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TechCrunch</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/sk-hynix-reportedly-in-talks-with-intel-to-build-memory-chips-in-us/</t>
+          <t>https://www.marketscreener.com/news/alvotech-shares-rise-after-double-upgrade-from-barclays-ce785bd2de81f42d</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>16-09-2026 13:23 UTC</t>
+          <t>16-09-2026 18:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Iron Sucrose Market Set to Surpass USD 796.4 Million by 2033,</t>
+          <t>Alvotech upgraded to Overweight from Underweight at Barclays</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4632934/iron-sucrose-market-set-to-surpass-usd-796-4-million-by-2033</t>
+          <t>https://www.tipranks.com/news/the-fly/alvotech-upgraded-to-overweight-from-underweight-at-barclays-thefly-news?mod=mw_quote_news</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>16-09-2026 08:14 UTC</t>
+          <t>16-09-2026 12:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Launches Cancer Drug Nivorz In India</t>
+          <t>About Teva Pharmaceutical Industries Ltd. rStock</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Launches-Cancer-Drug-Nivorz-In-India/6aa990790416c068539d68fc</t>
+          <t>https://www.coinbase.com/en-pt/price/teva-pharmaceutical-industries-ltd-rstock</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>15-09-2026 21:56 UTC</t>
+          <t>17-09-2026 00:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Successful Internal Audit Planning and Execution</t>
+          <t>Delhi HC orders tax dept to refund ₹783 cr to Teva Israel over Ranbaxy payment</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PharmTech.com</t>
+          <t>A2Z Taxcorp LLP</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>http://www.pharmtech.com/view/successful-internal-audit-planning-and-execution</t>
+          <t>https://a2ztaxcorp.net/delhi-hc-orders-tax-dept-to-refund-%E2%82%B9783-cr-to-teva-israel-over-ranbaxy-payment/</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>15-09-2026 18:42 UTC</t>
+          <t>16-09-2026 12:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Alkermes Announces Appointment of Anne C. Whitaker to Board of Directors</t>
+          <t>Teva’s Lab-Made Antibody Shot for Celiac Shows Hopeful Results</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>allergicliving.com</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/alkermes-announces-appointment-of-anne-c-whitaker-to-board-of-directors</t>
+          <t>https://www.allergicliving.com/2026/09/16/tevas-lab-made-antibody-shot-for-celiac-shows-hopeful-results/</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>16-09-2026 14:12 UTC</t>
+          <t>16-09-2026 22:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Alvotech upgraded to Overweight from Underweight at Barclays</t>
+          <t>Mere Payment By Indian Resident To Non-Resident Not Income Accruing In India: Delhi High Court</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>livelawbiz.com</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/the-fly/alvotech-upgraded-to-overweight-from-underweight-at-barclays-thefly-news?mod=mw_quote_news</t>
+          <t>https://www.livelawbiz.com/amp/income-tax/high-court/mere-payment-by-indian-resident-to-non-resident-not-income-accruing-in-india-delhi-high-court-550360</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>16-09-2026 12:43 UTC</t>
+          <t>16-09-2026 14:11 UTC</t>
         </is>
       </c>
     </row>
@@ -4162,22 +4163,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Delhi HC orders tax dept to refund ₹783 cr to Teva Israel over Ranbaxy payment</t>
+          <t>Teva launches educational website for HCPs to advance understanding of LAIs in schizophrenia care</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>A2Z Taxcorp LLP</t>
+          <t>PharmaLive</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/delhi-hc-orders-tax-dept-to-refund-%E2%82%B9783-cr-to-teva-israel-over-ranbaxy-payment/</t>
+          <t>https://www.pharmalive.com/teva-launches-educational-website-for-hcps-to-advance-understanding-of-lais-in-schizophrenia-care/</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>16-09-2026 12:34 UTC</t>
+          <t>16-09-2026 13:44 UTC</t>
         </is>
       </c>
     </row>
@@ -4189,22 +4190,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Teva Launches LongActingImpact.com to Advance Understanding of Earlier, Effective and Uninterrupted Schizophrenia Care</t>
+          <t>Is the Teva Trailpeak as adventurous as its name suggests?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Yahoo! Finance Canada</t>
+          <t>believeintherun.com</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://ca.finance.yahoo.com/news/teva-launches-longactingimpact-com-advance-120000554.html</t>
+          <t>https://believeintherun.com/shoe-reviews/teva-trailpeak-review/</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>16-09-2026 12:00 UTC</t>
+          <t>16-09-2026 13:39 UTC</t>
         </is>
       </c>
     </row>
@@ -4216,427 +4217,427 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Teva launches educational website for HCPs to advance understanding of LAIs in schizophrenia care</t>
+          <t>Most Active Options Report: FPS, TEVA, AFL</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PharmaLive</t>
+          <t>Schaeffer's Investment Research</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://www.pharmalive.com/teva-launches-educational-website-for-hcps-to-advance-understanding-of-lais-in-schizophrenia-care/</t>
+          <t>https://www.schaeffersresearch.com/content/options/2026/09/16/most-active-options-report-fps-teva-afl</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>16-09-2026 13:43 UTC</t>
+          <t>16-09-2026 15:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Is the Teva Trailpeak as adventurous as its name suggests?</t>
+          <t>Shilpa Bio inks deal for PD-1 biosimilar for MENA market</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Believe in the Run</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://believeintherun.com/shoe-reviews/teva-trailpeak-review/</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/shilpa-bio-inks-deal-for--1-biosimilar-for-mena-market</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>16-09-2026 13:34 UTC</t>
+          <t>16-09-2026 11:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Teva Trailpeak Review; 3 Comparisons</t>
+          <t>Clarivate Reveals Citation Laureates 2026 Recognizing Transformative Scientific Breakthroughs</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>roadtrailrun.com</t>
+          <t>sg.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://www.roadtrailrun.com/2026/09/teva-trailpeak-review-3-comparisons.html</t>
+          <t>https://sg.finance.yahoo.com/news/clarivate-reveals-citation-laureates-2026-070500489.html</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>16-09-2026 11:22 UTC</t>
+          <t>17-09-2026 07:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Increasing unusual option volume: MAT FDXF FPS BN JBHT GPRE CSWC TEVA GPCR DEO AADX ECO GFL MBOT</t>
+          <t>Thirty Inspiring Middle School Scientists and Engineers Named Finalists in the 2026 Thermo Fisher Scientific Junior Innovators Challenge</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>StreetInsider</t>
+          <t>sg.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://www.streetinsider.com/Options/Increasing+unusual+option+volume%3A+MAT+FDXF+FPS+BN+JBHT+GPRE+CSWC+TEVA+GPCR+DEO+AADX+ECO+GFL+MBOT/27068725.html</t>
+          <t>https://sg.finance.yahoo.com/news/thirty-inspiring-middle-school-scientists-160300649.html</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>16-09-2026 14:06 UTC</t>
+          <t>16-09-2026 16:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Mere Payment By Indian Resident To Non-Resident Not Income Accruing In India: Delhi High Court</t>
+          <t>VivoSim Labs Unveils New NAMkind™ Drug Toxicity Data at EUROTOX 2026, Demonstrating Predictive Superiority in Liver and Gastrointestinal Safety Across Small Molecules and ADCs</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>LiveLawBiz</t>
+          <t>sg.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://www.livelawbiz.com/income-tax/high-court/mere-payment-by-indian-resident-to-non-resident-not-income-accruing-in-india-delhi-high-court-550360</t>
+          <t>https://sg.finance.yahoo.com/news/vivosim-labs-unveils-namkind-drug-120500630.html</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>16-09-2026 14:11 UTC</t>
+          <t>16-09-2026 12:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Remepy appoints Eran Harary as Chief Medical Officer</t>
+          <t>Government of Canada invests up to $1.98 million to develop sustainable fertilizer technology to reduce emissions and microplastics</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>calcalistech.com</t>
+          <t>sg.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://www.calcalistech.com/ctechnews/article/h1n6jzdtgx</t>
+          <t>https://sg.finance.yahoo.com/news/government-canada-invests-1-98-163400092.html</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>16-09-2026 11:43 UTC</t>
+          <t>16-09-2026 16:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Shilpa Bio inks deal for PD-1 biosimilar for MENA market</t>
+          <t>Vishal Sikka's Hang Ten Systems Raises $53M Just Five Weeks After Seed Round</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>BBN Times</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/shilpa-bio-inks-deal-for--1-biosimilar-for-mena-market</t>
+          <t>https://www.bbntimes.com/technology/vishal-sikka-s-hang-ten-systems-raises-53m-just-five-weeks-after-seed-round</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>16-09-2026 11:03 UTC</t>
+          <t>16-09-2026 18:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>VivoSim Labs Unveils New NAMkind™ Drug Toxicity Data at EUROTOX 2026, Demonstrating Predictive Superiority in Liver and Gastrointestinal Safety Across Small Molecules and ADCs</t>
+          <t>Former Infosys chief’s AI startup nabs another $53M</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>TechCrunch</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/vivosim-labs-unveils-namkind-drug-120500630.html</t>
+          <t>https://techcrunch.com/2026/09/16/former-infosys-chiefs-ai-startup-adds-50m-to-seed-weeks-after-initial-raise/</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>16-09-2026 12:05 UTC</t>
+          <t>16-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>American Council of Learned Societies Announces Winners of 2026 ACLS Open Access Book Prizes and Arcadia Open Access Publishing Awards</t>
+          <t>Fresenius SE &amp; Co. KGaA : Barclays reaffirms its Buy rating</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/american-council-learned-societies-announces-231500703.html</t>
+          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-barclays-reaffirms-its-buy-rating-ce785bd2dc88f726</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>15-09-2026 23:15 UTC</t>
+          <t>16-09-2026 12:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BIX 2026 Names Canada as Country of Honor, Showcasing Bioindustry Trends from BCI to Biotech Foods</t>
+          <t>SK Hynix reportedly in talks with Intel to build memory chips in US</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>더바이오</t>
+          <t>TechCrunch</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://www.thebionews.net/news/articleViewAmp.html?idxno=28154</t>
+          <t>https://techcrunch.com/2026/09/16/sk-hynix-reportedly-in-talks-with-intel-to-build-memory-chips-in-us/</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>15-09-2026 23:49 UTC</t>
+          <t>16-09-2026 13:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Europe Biosimilar Market Size and Outlook Report 2034 Halaman 1</t>
+          <t>KOSPI Opens Higher, Shaking Off Hawkish FOMC Shock; AI and Falling Oil Prices Provide Lift</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Kompasiana.com</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://www.kompasiana.com/yadwenderkumar9745/6aaa2ecec925c4173e22ced9/europe-biosimilar-market-size-and-outlook-report-2034</t>
+          <t>https://finance.biggo.com/news/e6307ee5-9f5d-4361-aff0-d05874e91306</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>16-09-2026 05:53 UTC</t>
+          <t>17-09-2026 02:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Former Infosys chief’s AI startup nabs another $53M</t>
+          <t>Shilpa Biologicals, SPIMACO Bio Ink MENA Biosimilars Deal</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TechCrunch</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/former-infosys-chiefs-ai-startup-adds-50m-to-seed-weeks-after-initial-raise/</t>
+          <t>https://www.contractpharma.com/breaking-news/shilpa-biologicals-spimaco-bio-ink-mena-biosimilars-deal/</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>16-09-2026 13:00 UTC</t>
+          <t>16-09-2026 13:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA : Barclays reaffirms its Buy rating</t>
+          <t>KOSPI ends near flat despite hawkish FOMC as foreigners net sell 2.3 trillion won</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>디지털투데이</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-barclays-reaffirms-its-buy-rating-ce785bd2dc88f726</t>
+          <t>https://www.digitaltoday.co.kr/en/view/104900/kospi-ends-flat-despite-hawkish-fomc-as-foreigners-net-sell-2-3-trillion-won</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>16-09-2026 12:09 UTC</t>
+          <t>17-09-2026 07:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SK Hynix reportedly in talks with Intel to build memory chips in US</t>
+          <t>KOSPI, KOSDAQ Open Higher Despite Hawkish Fed Signals</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TechCrunch</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/sk-hynix-reportedly-in-talks-with-intel-to-build-memory-chips-in-us/</t>
+          <t>https://en.sedaily.com/finance/2026/09/17/kospi-kosdaq-open-higher-despite-hawkish-fed-signals</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>16-09-2026 13:23 UTC</t>
+          <t>17-09-2026 00:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Iron Sucrose Market Set to Surpass USD 796.4 Million by 2033,</t>
+          <t>KOSPI Posts Early Gains Despite Fed Rate Hike...Individuals Lead Net Buying</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4632934/iron-sucrose-market-set-to-surpass-usd-796-4-million-by-2033</t>
+          <t>https://www.asiae.co.kr/en/article/2026091710074710967</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>16-09-2026 08:14 UTC</t>
+          <t>17-09-2026 01:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Launches Cancer Drug Nivorz In India</t>
+          <t>Despite the U.S. Federal Reserve's (Fed) rate hike last night, the KOSPI started higher on the 17th.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Dr-Reddys-Launches-Cancer-Drug-Nivorz-In-India/6aa990790416c068539d68fc</t>
+          <t>https://www.mk.co.kr/en/stock/12155032</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>15-09-2026 21:56 UTC</t>
+          <t>17-09-2026 00:20 UTC</t>
         </is>
       </c>
     </row>
@@ -4648,22 +4649,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Semiconductor rebound lifts KOSPI 1.37 percent, back above 6,700</t>
+          <t>Sanofi, UCB, Opella Join Clean Heat Program</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>디지털투데이</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://www.digitaltoday.co.kr/en/view/104340/semiconductor-rebound-lifts-kospi-1-37-percent-back-above-6700</t>
+          <t>https://www.contractpharma.com/breaking-news/sanofi-ucb-opella-join-clean-heat-program/</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>16-09-2026 07:05 UTC</t>
+          <t>16-09-2026 12:55 UTC</t>
         </is>
       </c>
     </row>
@@ -4675,22 +4676,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>55 Listed Companies Join Korea Premium Weeks 2026 Starting Sept. 28</t>
+          <t>Corrugated Vial Shipping Trays Market Forecast to 2035: Biologics Demand Drives Expansion - News and Statistics</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277063</t>
+          <t>https://www.indexbox.io/blog/corrugated-vial-shipping-trays-market-to-accelerate-on-biologics-demand-reaching-2035-growth/</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>16-09-2026 01:55 UTC</t>
+          <t>16-09-2026 13:31 UTC</t>
         </is>
       </c>
     </row>
@@ -4702,22 +4703,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>The KOSPI, which has been on a downward trend in recent days, started falling on the 16th, but close..</t>
+          <t>[Opening Market] KOSPI Opens 0.9% Higher As Fed Uncertainty Eases</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/en/stock/12154354</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277168</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>16-09-2026 07:05 UTC</t>
+          <t>17-09-2026 02:19 UTC</t>
         </is>
       </c>
     </row>
@@ -4729,22 +4730,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals, SPIMACO Bio Ink MENA Biosimilars Deal</t>
+          <t>Won-dollar exchange rate fluctuates in upper 1,370s</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/shilpa-biologicals-spimaco-bio-ink-mena-biosimilars-deal/</t>
+          <t>https://mbiz.heraldcorp.com/article/10877041</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>16-09-2026 13:24 UTC</t>
+          <t>17-09-2026 04:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4756,22 +4757,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Corrugated Vial Shipping Trays Market Forecast to 2035: Biologics Demand Drives Expansion - News and Statistics</t>
+          <t>Samsung Electronics, SK Hynix Rally Alongside U.S. Semiconductor Rebound</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/corrugated-vial-shipping-trays-market-to-accelerate-on-biologics-demand-reaching-2035-growth/</t>
+          <t>https://finance.biggo.com/news/3813f228-d1ad-486f-b0ad-7dd522d8db96</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>16-09-2026 13:31 UTC</t>
+          <t>17-09-2026 01:26 UTC</t>
         </is>
       </c>
     </row>
@@ -4783,184 +4784,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Sanofi, UCB, Opella Join Clean Heat Program</t>
+          <t>Special prosecutor raids National Election Commission headquarters, 8 other sites</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/sanofi-ucb-opella-join-clean-heat-program/</t>
+          <t>https://mbiz.heraldcorp.com/article/10876510</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>16-09-2026 12:55 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>South Korean shares rise as chipmakers gain ahead of Fed outcome</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Business Recorder</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>https://www.brecorder.com/news/amp/40439737</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>16-09-2026 05:33 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Graves’ Orbitopathy Market to Grow from USD 2.06 Billion at a CAGR of 19.8% Through 2034</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Barchart.com</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>https://www.barchart.com/press-releases/4625289/graves-orbitopathy-market-to-grow-from-usd-2-06-billion-at-a-cagr-of-19-8-through-2034</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>16-09-2026 02:58 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>CDMO Capacity: Stainless by Volume, Single-Use by Number</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Contract Pharma</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>https://www.contractpharma.com/exclusives/cdmo-capacity-stainless-by-volume-single-use-by-number/</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>15-09-2026 18:03 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Axiom, GeneFab Partner to Advance Therapeutic Pipeline</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Contract Pharma</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>https://www.contractpharma.com/breaking-news/axiom-genefab-partner-to-advance-therapeutic-pipeline/</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>15-09-2026 16:46 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Biologics Contract Manufacturing Market to Reach US$ 83.47</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>https://www.openpr.com/news/4633375/biologics-contract-manufacturing-market-to-reach-us-83-47</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>16-09-2026 13:24 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Ori Biotech Lands 10-Year, $120M Commercial Cell Therapy Manufacturing Deal</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Contract Pharma</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>https://www.contractpharma.com/breaking-news/ori-biotech-lands-10-year-120m-commercial-cell-therapy-manufacturing-deal/</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>15-09-2026 18:58 UTC</t>
+          <t>17-09-2026 00:33 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -463,130 +463,130 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz Appoints Ha Vo as General Manager, Vietnam</t>
+          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>thepharmaletter.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/sandoz-appoints-ha-vo-as-general-manager-vietnam/</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16-09-2026 12:54 UTC</t>
+          <t>17-09-2026 12:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>‘It’s Incredibly Rare In A Career To Be In This Position’ – Sandoz CFO On Bio100 And The Path Ahead</t>
+          <t>Boehringer Ingelheim launches PED Essentials, an online learning resource that gives patients a stronger voice</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>biospace.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/leadership/interviews/its-incredibly-rare-in-a-career-to-be-in-this-position-sandoz-cfo-on-bio100-and-the-path-ahead-XYNMGOM3BNEXXBNG4RDWBV3U3Y/</t>
+          <t>https://www.biospace.com/press-releases/boehringer-ingelheim-launches-ped-essentials-an-online-learning-resource-that-gives-patients-a-stronger-voice</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16-09-2026 12:23 UTC</t>
+          <t>17-09-2026 09:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shilpa Bio inks deal for PD-1 biosimilar for MENA market</t>
+          <t>Boehringer launches hub for patient experience data</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>pharmaphorum.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/shilpa-bio-inks-deal-for--1-biosimilar-for-mena-market</t>
+          <t>https://pharmaphorum.com/news/boehringer-launches-hub-patient-experience-data</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16-09-2026 11:08 UTC</t>
+          <t>17-09-2026 09:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Parmigiani Fleurier commemorates thirty years of horological mastery with the Mechanical Wonders exhibition in Tokyo</t>
+          <t>Boehringer ends late-stage kidney disease study of Jardiance combo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>senatus.net</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://senatus.net/album/view/17714/</t>
+          <t>https://firstwordpharma.com/story/7998608</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16-09-2026 14:56 UTC</t>
+          <t>16-09-2026 22:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Stada</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Städa med Grumme såpa</t>
+          <t>Boehringer halts Phase III kidney trial of vicadrostat/Jardiance combination</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>metromode.se</t>
+          <t>thepharmaletter.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://metromode.se/en/tag/stada-med-grumme-sapa/</t>
+          <t>https://www.thepharmaletter.com/pharma-news/boehringer-halts-phase-iii-kidney-trial-of-vicadrostat-jardiance-combination</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16-09-2026 13:06 UTC</t>
+          <t>17-09-2026 08:57 UTC</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Paper + Spark adds seven new clients as it’s named agency of the year at 2026 AMI Awards</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>via.ritzau.dk</t>
+          <t>Campaign Brief</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://via.ritzau.dk/pressemeddelelse/15166947/boehringer-ingelheim?publisherId=90446&amp;lang=en</t>
+          <t>https://campaignbrief.com/paper-spark-adds-seven-new-clients-as-its-named-agency-of-the-year-at-2026-ami-awards/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17-09-2026 05:33 UTC</t>
+          <t>17-09-2026 10:02 UTC</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boehringer ends late-stage kidney disease study of Jardiance combo</t>
+          <t>Lilly backs Circle's latest fundraise as second cancer drug nears clinic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FirstWord PHARMA</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7998608</t>
+          <t>https://firstwordpharma.com/story/7996747</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16-09-2026 22:04 UTC</t>
+          <t>16-09-2026 18:23 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lilly backs Circle's latest fundraise as second cancer drug nears clinic</t>
+          <t>Mayor Nancy expands employment opportunities in Makati</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FirstWord PHARMA</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7996747</t>
+          <t>https://www.manilatimes.net/2026/09/17/tmt-newswire/mayor-nancy-expands-employment-opportunities-in-makati/2427182/amp</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16-09-2026 18:23 UTC</t>
+          <t>17-09-2026 03:34 UTC</t>
         </is>
       </c>
     </row>
@@ -679,238 +679,238 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inside FIND-CKD: Can Finerenone Pair With Immunosuppression in GN?</t>
+          <t>Interstitial Lung Disease Market Poised for Strong Growth Through 2036 with Breakthrough ILD Treatments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HCPLive</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.hcplive.com/view/inside-find-ckd-can-finerenone-pair-with-immunosuppression-in-gn-</t>
+          <t>https://www.openpr.com/news/4633962/interstitial-lung-disease-market-poised-for-strong-growth</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16-09-2026 19:06 UTC</t>
+          <t>17-09-2026 05:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Livestock Temperature Monitoring Tags Market To 2035: Disease Surveillance Drives Expansion - News and Statistics</t>
+          <t>Weapons plan principles to be announced in early October, Hikma spox says</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>964media</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/livestock-temperature-monitoring-tags-market-forecast-to-2035-growth-accelerates-on-disease-surveillance-demand/</t>
+          <t>https://en.964media.com/52693/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16-09-2026 20:51 UTC</t>
+          <t>17-09-2026 07:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vaccine Contract Manufacturing Market Poised for Steady Growth Through 2032 Amid Rising Immunization Demand – DelveInsight</t>
+          <t>DLCA Sues Eight Pharmaceutical Companies, Alleging Opioid Monitoring Failures and Misleading Marketing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Barchart.com</t>
+          <t>The Virgin Islands Consortium</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.barchart.com/press-releases/4646007/vaccine-contract-manufacturing-market-poised-for-steady-growth-through-2032-amid-rising-immunization-demand-delveinsight</t>
+          <t>https://viconsortium.com/vi-legal/virgin-islands-dlca-sues-eight-pharmaceutical-companies--alleging-opioid-monitoring-failures-and-misleading-marketing</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16-09-2026 23:30 UTC</t>
+          <t>17-09-2026 10:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CMU, Pitt, UPMC and Highmark showcase AI-powered convergence in life sciences</t>
+          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The Business Journals</t>
+          <t>thepharmaletter.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.bizjournals.com/pittsburgh/news/2026/09/16/pittsburgh-life-sciences-alliance-bio-health.html</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16-09-2026 18:47 UTC</t>
+          <t>17-09-2026 12:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oligomerix puts tau drug in new hands as trials begin</t>
+          <t>BMS, Ono sue to protect Opdivo from Amgen biosimilar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Longevity.Technology</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://longevity.technology/news/oligomerix-puts-tau-drug-in-new-hands-as-trials-begin/</t>
+          <t>https://firstwordpharma.com/story/7998630</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16-09-2026 17:26 UTC</t>
+          <t>16-09-2026 22:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3 Steps to Support Mental Health for Rural Youth</t>
+          <t>From the Financial Crisis to the 2022 Bear Market, How Does Amgen Demonstrate Resilience?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>The Miner Online</t>
+          <t>NAI500</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pendoreillerivervalley.com/article/6059,3-steps-to-support-mental-health-for-rural-youth</t>
+          <t>https://nai500.com/blog/2026/09/from-the-financial-crisis-to-the-2022-bear-market-how-does-amgen-demonstrate-resilience/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16-09-2026 13:00 UTC</t>
+          <t>17-09-2026 07:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Interstitial Lung Disease Market Poised for Strong Growth Through 2036 with Breakthrough ILD Treatments</t>
+          <t>Amgen hit with lawsuit over its proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Life Sciences IP Review</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4633962/interstitial-lung-disease-market-poised-for-strong-growth</t>
+          <t>https://www.lifesciencesipreview.com/biotech/amgen-hit-with-lawsuit-over-its-proposed-opdivo-biosimilar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17-09-2026 05:29 UTC</t>
+          <t>16-09-2026 21:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Weapons plan principles to be announced in early October, Hikma spox says</t>
+          <t>Amgen Confident In Cardiometabolic Pipeline After Novartis’s Negative Lp(a) Readout</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>964media</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://en.964media.com/52693/</t>
+          <t>https://insights.citeline.com/scrip/therapeutic-category/cardiovascular/amgen-confident-in-cardiometabolic-pipeline-after-novartiss-negative-lpa-readout-44IU5KUHR5GCVH5BZWKTKT6WXU/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17-09-2026 07:07 UTC</t>
+          <t>16-09-2026 22:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Iron Sucrose Market Set to Surpass USD 796.4 Million by 2033,</t>
+          <t>Bristol-Myers Looks To Block Amgen's Cancer Biosimilar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4632934/iron-sucrose-market-set-to-surpass-usd-796-4-million-by-2033</t>
+          <t>https://www.law360.com/ip/articles/2525837/bristol-myers-looks-to-block-amgen-s-cancer-biosimilar-</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16-09-2026 08:14 UTC</t>
+          <t>16-09-2026 19:44 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BMS, Ono take Amgen to task as FDA's Opdivo biosimilar decision looms</t>
+          <t>Amgen's Resilience Amid Economic Turbulence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Intellectia AI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/bms-ono-take-amgen-task-fdas-opdivo-biosimilar-decision-looms</t>
+          <t>https://intellectia.ai/news/stock/amgens-resilience-amid-economic-turbulence</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16-09-2026 15:08 UTC</t>
+          <t>16-09-2026 19:54 UTC</t>
         </is>
       </c>
     </row>
@@ -949,400 +949,400 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BMS, Ono sue to protect Opdivo from Amgen biosimilar</t>
+          <t>2027 Irish Opens Locked In as K Club and Dún Laoghaire Take Centre Stage</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FirstWord PHARMA</t>
+          <t>Sport for Business</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7998630</t>
+          <t>https://sportforbusiness.com/2027-irish-opens-locked-in-as-k-club-and-dun-laoghaire-take-centre-stage/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16-09-2026 22:04 UTC</t>
+          <t>17-09-2026 08:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amgen hit with lawsuit over its proposed Opdivo biosimilar</t>
+          <t>Amneal expands India operations after Kashiv buy, builds biosimilars portfolio</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Life Sciences IP Review</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.lifesciencesipreview.com/biotech/amgen-hit-with-lawsuit-over-its-proposed-opdivo-biosimilar</t>
+          <t>https://www.businesstoday.in/amp/latest/corporate/story/amneal-expands-india-operations-after-kashiv-buy-builds-biosimilars-portfolio-556089-2026-09-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16-09-2026 21:23 UTC</t>
+          <t>17-09-2026 07:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From the Financial Crisis to the 2022 Bear Market, How Does Amgen Demonstrate Resilience?</t>
+          <t>Organon Backs Women’s Health Efforts Across India</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NAI500</t>
+          <t>Pharmacy Business</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nai500.com/blog/2026/09/from-the-financial-crisis-to-the-2022-bear-market-how-does-amgen-demonstrate-resilience/</t>
+          <t>https://www.pharmacy.biz/organon-womens-health-support-india/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17-09-2026 07:11 UTC</t>
+          <t>17-09-2026 13:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amgen Confident In Cardiometabolic Pipeline After Novartis’s Negative Lp(a) Readout</t>
+          <t>Organon backs women’s health programmes in Bihar and Uttar Pradesh</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/scrip/therapeutic-category/cardiovascular/amgen-confident-in-cardiometabolic-pipeline-after-novartiss-negative-lpa-readout-44IU5KUHR5GCVH5BZWKTKT6WXU/</t>
+          <t>https://www.indianpharmapost.com/healthcare/organon-backs-womens-health-programmes-in-bihar-and-uttar-pradesh-21886</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16-09-2026 22:14 UTC</t>
+          <t>17-09-2026 04:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FDA cuts monitoring time for first two doses of Amgen’s IMDELLTRA</t>
+          <t>PhaseV Adds Klaus Beck and Avi Kulkarni to Scientific Advisory Board</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>citybiz</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/regulatory/fda-cuts-monitoring-time-for-first-two-doses-of-amgens-imdelltra-21872</t>
+          <t>https://www.citybiz.co/article/904492/phasev-adds-klaus-beck-and-avi-kulkarni-to-scientific-advisory-board/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16-09-2026 12:26 UTC</t>
+          <t>16-09-2026 20:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bristol Myers sues Amgen over proposed Opdivo biosimilar</t>
+          <t>Why Allison launched Allison Worldwide Health Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>PRWeek</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/bristol-myers-sues-amgen-over-proposed-opdivo-biosimilar/134282973</t>
+          <t>https://www.prweek.com/article/1970220/why-allison-launched-allison-worldwide-health-group</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16-09-2026 08:46 UTC</t>
+          <t>16-09-2026 20:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bristol-Myers Looks To Block Amgen's Cancer Biosimilar</t>
+          <t>Organon Announces Two Her Health Grants In India To Support Adolescent Girls' Health In Bihar And Women's Contraceptive Access In Uttar Pradesh</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>menafn.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.law360.com/ip/articles/2525837/bristol-myers-looks-to-block-amgen-s-cancer-biosimilar-</t>
+          <t>https://menafn.com/1111677524/Organon-Announces-Two-Her-Health-Grants-In-India-To-Support-Adolescent-Girls-Health-In-Bihar-And-Womens-Contraceptive-Access-In-Uttar-Pradesh</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16-09-2026 19:44 UTC</t>
+          <t>17-09-2026 06:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DP World Tour: BMW PGA Championship gets new date for 2027 due to Ryder Cup as significant schedule changes announced</t>
+          <t>Tyre Pyrolysis Plant Setup in India: Feasibility Report</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sky Sports</t>
+          <t>IMARC Group</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/golf/news/12176/13588539/dp-world-tour-bmw-pga-championship-gets-new-date-for-2027-due-to-ryder-cup-as-significant-schedule-changes-announced</t>
+          <t>https://www.imarcgroup.com/insight/tyre-pyrolysis-plant-setup-india</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16-09-2026 16:34 UTC</t>
+          <t>17-09-2026 07:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2027 Irish Open moved to July date at K Club</t>
+          <t>EnergyPathways &amp; Hycamite Hydrogen Graphite Plant UK</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RTE.ie</t>
+          <t>Fuel Cells Works</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.rte.ie/sport/golf/2026/0916/1591745-2027-irish-open-moved-to-july-date/</t>
+          <t>https://fuelcellsworks.com/2026/09/17/h2/energypathways-and-hycamite-to-advance-hydrogen-and-graphite-production-plant-in-uk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16-09-2026 09:37 UTC</t>
+          <t>17-09-2026 12:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DoP Secretary Manoj Joshi visits Amneal Pharmaceuticals</t>
+          <t>The Ghosts of Chernobyl</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Telos-eu.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/dop-secretary-manoj-joshi-visits-amneal-pharmaceuticals-21865</t>
+          <t>http://www.telos-eu.com/en/the-ghosts-of-chernobyl.html</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16-09-2026 10:23 UTC</t>
+          <t>17-09-2026 15:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Boryung and Korea Organon join to market Atozet for dyslipidemia in Korea - CHOSUNBIZ</t>
+          <t>Do Plant Proteins Increase Uric Acid? Expert Weighs In</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Onlymyhealth</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/16/XIBOSIHBPRGKPAZEWREFTCCMLQ/</t>
+          <t>https://www.onlymyhealth.com/can-plant-protein-increase-your-uric-acid-levels-expert-explains-12977850410</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16-09-2026 08:27 UTC</t>
+          <t>17-09-2026 13:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sandoz Appoints Ha Vo as General Manager, Vietnam</t>
+          <t>Dry Fungi Mycoproteins Market Size, Share &amp; Forecast 2036</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>Fact.MR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/sandoz-appoints-ha-vo-as-general-manager-vietnam/</t>
+          <t>https://www.factmr.com/report/dry-fungi-mycoproteins-market</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16-09-2026 12:54 UTC</t>
+          <t>17-09-2026 07:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PhaseV Appoints Biopharma Leaders Klaus Beck and Avi Kulkarni to Scientific Advisory Board to Guide Expansion of AI Conductor</t>
+          <t>Ghana’s Genser moves further downstream with natural gas liquids plant</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>africa-energy.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/il/news-releases/phasev-appoints-biopharma-leaders-klaus-beck-and-avi-kulkarni-to-scientific-advisory-board-to-guide-expansion-of-ai-conductor-302880241.html</t>
+          <t>https://www.africa-energy.com/news-centre/article/ghanas-genser-moves-further-downstream-natural-gas-liquids-plant</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16-09-2026 12:30 UTC</t>
+          <t>17-09-2026 10:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PhaseV Adds Klaus Beck and Avi Kulkarni to Scientific Advisory Board</t>
+          <t>Premier Energies to Form JV for 12 GWh BESS Facility</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>citybiz</t>
+          <t>Construction World</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.citybiz.co/article/904492/phasev-adds-klaus-beck-and-avi-kulkarni-to-scientific-advisory-board/</t>
+          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/premier-energies-to-form-jv-for-12-gwh-bess-facility/97510</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16-09-2026 20:04 UTC</t>
+          <t>17-09-2026 07:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Apotex Joins National "Hope Alliance" Campaign to Support Uninsured Patients</t>
+          <t>Foliar fertilization: Precision starts with application conditions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Hortidaily</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/apotex-joins-national-hope-alliance-campaign-to-support-uninsured-patients-302879290.html</t>
+          <t>https://www.hortidaily.com/article/9874133/foliar-fertilization-precision-starts-with-application-conditions/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>16-09-2026 13:00 UTC</t>
+          <t>17-09-2026 12:32 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Xanthate Flotation Collectors Market</t>
+          <t>"After seeing the excitement in Europe, we are thrilled to bring these hydrangeas to the U.S."</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>futuremarketinsights.com</t>
+          <t>FloralDaily</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.futuremarketinsights.com/reports/xanthate-flotation-collectors-market</t>
+          <t>https://www.floraldaily.com/article/9873937/after-seeing-the-excitement-in-europe-we-are-thrilled-to-bring-these-hydrangeas-to-the-u-s/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17-09-2026 06:37 UTC</t>
+          <t>17-09-2026 13:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dry Fungi Mycoproteins Market Size, Share &amp; Forecast 2036</t>
+          <t>21,000 living plants shape Ganesh idol with a green message in Andhra Pradesh</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fact.MR</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.factmr.com/report/dry-fungi-mycoproteins-market</t>
+          <t>https://www.indiatoday.in/india/story/21000-living-plants-turn-ganesh-idol-into-a-green-message-in-anakapalli-2996395-2026-09-17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17-09-2026 07:11 UTC</t>
+          <t>16-09-2026 20:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Premier Energies to Form JV for 12 GWh BESS Facility</t>
+          <t>This coal plant won Basin Electric’s reliability trophy, but it doesn’t plan to return it.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Construction World</t>
+          <t>power-eng.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/premier-energies-to-form-jv-for-12-gwh-bess-facility/97510</t>
+          <t>https://www.power-eng.com/coal/this-coal-plant-won-basin-electrics-reliability-trophy-but-it-doesnt-plan-to-return-it/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17-09-2026 07:33 UTC</t>
+          <t>17-09-2026 14:43 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pharmaceutical Manufacturing Plant Setup in India</t>
+          <t>Without bacteria or chemicals: How methanol and formaldehyde form abiotically in nature</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>imarcgroup.com</t>
+          <t>Phys.org</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.imarcgroup.com/insight/pharmaceutical-manufacturing-plant-setup-cost-india</t>
+          <t>https://phys.org/news/2026-09-bacteria-chemicals-methanol-formaldehyde-abiotically.html</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16-09-2026 15:19 UTC</t>
+          <t>16-09-2026 19:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21,000 living plants shape Ganesh idol with a green message in Andhra Pradesh</t>
+          <t>Xanthate Flotation Collectors Market</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Future Market Insights</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/21000-living-plants-turn-ganesh-idol-into-a-green-message-in-anakapalli-2996395-2026-09-17</t>
+          <t>https://www.futuremarketinsights.com/reports/xanthate-flotation-collectors-market</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16-09-2026 20:47 UTC</t>
+          <t>16-09-2026 18:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,967 +1489,967 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Without bacteria or chemicals: How methanol and formaldehyde form abiotically in nature</t>
+          <t>Microplastics in soil pose global threat by acting like ‘Trojan horse’ to deliver toxins</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phys.org</t>
+          <t>The Guardian</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://phys.org/news/2026-09-bacteria-chemicals-methanol-formaldehyde-abiotically.html</t>
+          <t>https://www.theguardian.com/environment/2026/sep/16/soil-microplastics-trojan-horse-toxins</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>16-09-2026 19:30 UTC</t>
+          <t>17-09-2026 01:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>In 2020, NASA put seeds from 11 crops aboard an experimental spaceplane; after months in orbit, scientists</t>
+          <t>Head and Neck Cancer Pipeline Gains Momentum: 80+ Companies Lead the Charge in Pioneering New Treatments | DelveInsight</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Barchart.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/international/us/in-2020-nasa-put-seeds-from-11-crops-aboard-an-experimental-spaceplane-after-months-in-orbit-scientists-brought-them-back-to-test-whether-they-could-still-grow/amp_articleshow/134296275.cms</t>
+          <t>https://www.barchart.com/press-releases/4646128/head-and-neck-cancer-pipeline-gains-momentum-80-companies-lead-the-charge-in-pioneering-new-treatments-delveinsight</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16-09-2026 20:18 UTC</t>
+          <t>16-09-2026 23:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What the Strait of Hormuz exposed about fertilizer security</t>
+          <t>Is Pfizer’s New Business Big Enough To Carry The Old One?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>World Fertilizer</t>
+          <t>Trefis</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.worldfertilizer.com/environment/16092026/what-the-strait-of-hormuz-exposed-about-fertilizer-security/amp/</t>
+          <t>https://www.trefis.com/stock/pfe/articles/615508/is-pfizers-new-business-big-enough-to-carry-the-old-one/2026-09-16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16-09-2026 15:36 UTC</t>
+          <t>16-09-2026 20:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nevada’s First Wastewater-to-Drinking-Water Plant Takes Shape in Reno</t>
+          <t>Bavarian Nordic names Tarja Stenvall as new CEO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Governing</t>
+          <t>Endpoints News</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.governing.com/infrastructure/nevadas-first-wastewater-to-drinking-water-plant-takes-shape-in-reno</t>
+          <t>https://endpoints.news/bavarian-nordic-names-tarja-stenvall-as-new-ceo/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>16-09-2026 21:21 UTC</t>
+          <t>17-09-2026 11:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The East African Community Seed and Plant Varieties Bill, 2025 must protect the Farmers and Seed Systems that feed the region</t>
+          <t>Pharma sector doubles down on AI to slash costs, timelines</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>greenpeace.org</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.greenpeace.org/africa/en/op-ed/61603/the-east-african-community-seed-and-plant-varieties-bill-2025-must-protect-the-farmers-and-seed-systems-that-feed-the-region/</t>
+          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/pharma-sector-doubles-down-ai-amid-hopes-slashing-costs-timelines-2026-09-16/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>16-09-2026 13:17 UTC</t>
+          <t>16-09-2026 20:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Can plant-based omega-3s really protect your heart?</t>
+          <t>Pfizer Raises 2026 Revenue Guidance to $62 Billion. Here’s What’s Behind the Beat</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Futura, le média qui explore le monde</t>
+          <t>TIKR.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.futura-sciences.com/en/doctors-stunned-these-2-omega-3-foods-could-dramatically-protect-your-arteries_900009/</t>
+          <t>https://www.tikr.com/blog/pfizer-raises-2026-revenue-guidance-to-62-billion-heres-whats-behind-the-beat</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>16-09-2026 12:12 UTC</t>
+          <t>16-09-2026 22:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fertilizer Production Plant Feasibility Study Report 2026: Setup Cost, ROI &amp; Business Plan</t>
+          <t>Fire Breaks Out At Pfizer Facility In Andover</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>industrytoday.co.uk</t>
+          <t>andovermanews.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://industrytoday.co.uk/manufacturing/fertilizer-production-plant-feasibility-study-report-2026-setup-cost-roi-business-plan</t>
+          <t>https://andovermanews.com/fire-breaks-out-at-pfizer-facility-in-andover/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16-09-2026 13:10 UTC</t>
+          <t>17-09-2026 13:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Trees Can Tell When They’re Crooked and Grow Special Wood to Straighten Themselves</t>
+          <t>What is Pfizer rStock | How RPFE Works, Use Cases and Values | MEXC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ZME Science</t>
+          <t>MEXC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.zmescience.com/science/biology/trees-correct-posture</t>
+          <t>https://www.mexc.co/en-PH/price/pfizer-rstock/info</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16-09-2026 13:08 UTC</t>
+          <t>17-09-2026 00:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bringing the art of Bonsai to Utah</t>
+          <t>Bavarian Nordic names new CEO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BYU Daily Universe</t>
+          <t>medwatch.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://universe.byu.edu/metro/bringing-the-art-of-bonsai-to-utah</t>
+          <t>https://medwatch.com/News/Pharma___Biotech/article19651697.ece</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16-09-2026 18:28 UTC</t>
+          <t>17-09-2026 08:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Head and Neck Cancer Pipeline Gains Momentum: 80+ Companies Lead the Charge in Pioneering New Treatments | DelveInsight</t>
+          <t>Alteogen Files Patent for Once-Monthly Obesity Drug Technology; Preclinical Results Due in November</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Barchart.com</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.barchart.com/press-releases/4646128/head-and-neck-cancer-pipeline-gains-momentum-80-companies-lead-the-charge-in-pioneering-new-treatments-delveinsight</t>
+          <t>https://finance.biggo.com/news/6b592b49-bff8-4b09-bd35-a65185b3eb83</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16-09-2026 23:46 UTC</t>
+          <t>17-09-2026 01:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Viatris-Mylan</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Gilead expands lenacapavir licensing to cover once-yearly HIV prevention</t>
+          <t>Covid Vaccines Delayed for Half of U.S. Children</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>StreetInsider</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.streetinsider.com/Corporate+News/Gilead+expands+lenacapavir+licensing+to+cover+once-yearly+HIV+prevention/27067898.html</t>
+          <t>https://www.nytimes.com/2026/09/16/well/covid-vaccines-vfc-program-delay.html</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16-09-2026 12:31 UTC</t>
+          <t>16-09-2026 22:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Is Pfizer’s New Business Big Enough To Carry The Old One?</t>
+          <t>Roche sees success in long-awaited confirmatory study of Lunsumio for follicular lymphoma</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Trefis</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.trefis.com/stock/pfe/articles/615508/is-pfizers-new-business-big-enough-to-carry-the-old-one/2026-09-16</t>
+          <t>https://firstwordpharma.com/story/8000583</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>16-09-2026 20:11 UTC</t>
+          <t>17-09-2026 13:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pharma sector doubles down on AI to slash costs, timelines</t>
+          <t>Japan approves subcutaneous formulation of LEQEMBI® for treatment of early Alzheimer’s Disease</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>BioSpectrum Asia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/pharma-sector-doubles-down-ai-amid-hopes-slashing-costs-timelines-2026-09-16/</t>
+          <t>https://www.biospectrumasia.com/news/30/28386/japan-approves-subcutaneous-formulation-of-leqembi-for-treatment-of-early-alzheimers-disease-.html</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>16-09-2026 20:42 UTC</t>
+          <t>17-09-2026 07:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pfizer Raises 2026 Revenue Guidance to $62 Billion. Here’s What’s Behind the Beat</t>
+          <t>Midlands TD Insists Skyclarys Must Be Made Available As Soon As Possible</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TIKR.com</t>
+          <t>Midlands 103</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.tikr.com/blog/pfizer-raises-2026-revenue-guidance-to-62-billion-heres-whats-behind-the-beat</t>
+          <t>https://www.midlands103.com/news/midlands-news/midlands-td-insists-skyclarys-must-be-made-available-as-soon-as-possible/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>16-09-2026 22:11 UTC</t>
+          <t>17-09-2026 07:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sourabh Pandey Appointed Senior Director, Commercial AI at Pfizer</t>
+          <t>BREAKING – Petition which could help FA sisters reaches 100,000 signatures</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>The Redditch Standard</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/sourabh-pandey-appointed-senior-director-commercial-ai-at-pfizer/</t>
+          <t>https://redditchstandard.co.uk/news/breaking-petition-which-could-help-fa-sisters-reaches-100000-signatures/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>16-09-2026 09:40 UTC</t>
+          <t>16-09-2026 23:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Zacks Analyst Blog Highlights Pfizer, Novartis, Candel and Janux</t>
+          <t>Dr Reddy's Enters Royalty-Free Agreement With Gilead For Annual Lenacapavir HIV Prevention</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>sahi.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/zacks-analyst-blog-highlights-pfizer-094700942.html</t>
+          <t>https://www.sahi.com/news/dr-reddy-s-enters-royalty-free-agreement-with-gilead-for-annual-lenacapavir-hiv-prevention</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>16-09-2026 09:47 UTC</t>
+          <t>17-09-2026 10:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pfizer follows AstraZeneca in pulling EU bladder cancer filing after CHMP concerns</t>
+          <t>Dr Reddy’s inks licensing deal with Gilead for once-yearly HIV lenacapavir</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AllSci</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://allsci.com/news/regulatory/zumrad-eu-application-pfizer-withdraws-zumrads/</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/dr-reddys-inks-licensing-deal-with-gilead-for-once-yearly-hiv-lenacapavir/articleshow/134313710.cms</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>16-09-2026 11:12 UTC</t>
+          <t>17-09-2026 13:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IP Group: NAV Reaches £1 Billion As Pfizer Obesity Royalty Value Rises To £152 Million</t>
+          <t>Dr Reddy's &amp; Gilead Pact for Once-Yearly HIV Prevention Drug</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pulse 2.0</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://pulse2.com/ip-group-nav-reaches-1-billion-as-pfizer-obesity-royalty-value-rises-to-152-million/</t>
+          <t>https://money.rediff.com/news/market/dr-reddy-s-gilead-pact-for-once-yearly-hiv-prevention-drug/54482920260917</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>16-09-2026 13:10 UTC</t>
+          <t>17-09-2026 08:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What is Pfizer rStock | How RPFE Works, Use Cases and Values | MEXC</t>
+          <t>Dr Reddy's signs royalty-free license with Gilead for lenacapavir</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MEXC</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.mexc.co/en-PH/price/pfizer-rstock/info</t>
+          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-enters-royalty-free-license-gilead-lenacapavir/51185185</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17-09-2026 00:00 UTC</t>
+          <t>17-09-2026 10:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Alteogen Files Patent for Once-Monthly Obesity Drug Technology; Preclinical Results Due in November</t>
+          <t>Dr. Reddy’s expands Gilead pact for HIV prevention drug</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/6b592b49-bff8-4b09-bd35-a65185b3eb83</t>
+          <t>https://www.thehindubusinessline.com/companies/dr-reddys-expands-pact-with-gilead-for-investigational-hiv-prevention-drug/article71475705.ece/amp/</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>17-09-2026 01:26 UTC</t>
+          <t>17-09-2026 07:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fake-drug racket suspect holed up in Azerbaijan, Karnataka mulls CBI probe</t>
+          <t>Dr. Nischal Shashidhar appointed AGM – Medical Affairs at Biological E.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/bangalore/bidadi-fake-drug-racket-karnataka-cbi-probe-azerbaijan-link-10880597/</t>
+          <t>https://www.indianpharmapost.com/biopharma/dr-nischal-shashidhar-appointed-agm-medical-affairs-at-biological-e-21890</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>16-09-2026 10:36 UTC</t>
+          <t>17-09-2026 11:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Japan approves subcutaneous formulation of LEQEMBI® for treatment of early Alzheimer’s Disease</t>
+          <t>Dr Reddy's Q1FY27 Results: Revenue falls 5.6%, margins hit by semaglutide</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/30/28386/japan-approves-subcutaneous-formulation-of-leqembi-for-treatment-of-early-alzheimers-disease-.html</t>
+          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-q1fy27-results-revenue-falls-5-6-margins-hit-semaglutide/51177311</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17-09-2026 07:26 UTC</t>
+          <t>17-09-2026 08:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Revealed: The largest corporate charitable contributors in the Bay State</t>
+          <t>Dr Reddy's inks pact with Gilead for once-yearly HIV prevention drug lenacapavir</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>The Business Journals</t>
+          <t>ET Manufacturing</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.bizjournals.com/boston/research/lists/2026/largest-corporate-charitable-contributors-2026.html</t>
+          <t>https://manufacturing.economictimes.indiatimes.com/amp/news/life-sciences/dr-reddys-inks-pact-with-gilead-for-once-yearly-hiv-prevention-drug-lenacapavir/134307526</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>16-09-2026 23:41 UTC</t>
+          <t>17-09-2026 09:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Midlands TD Insists Skyclarys Must Be Made Available As Soon As Possible</t>
+          <t>Dr. Reddy's faces fifth US securities probe after semaglutide hit</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>midlands103.com</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.midlands103.com/news/midlands-news/midlands-td-insists-skyclarys-must-be-made-available-as-soon-as-possible/</t>
+          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-under-probe-2-4bn-semaglutide-provision-hits-stock/48211614</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17-09-2026 07:23 UTC</t>
+          <t>17-09-2026 00:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BREAKING – Petition which could help FA sisters reaches 100,000 signatures</t>
+          <t>Top gainers and losers, September 17: HDFC LIC jumps 5%, TMPV rises 4%, ONGC falls 2%; check list</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>The Redditch Standard</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://redditchstandard.co.uk/news/breaking-petition-which-could-help-fa-sisters-reaches-100000-signatures/</t>
+          <t>https://upstox.com/news/market-news/stocks/top-gainers-and-losers-september-17-hdfc-lic-jumps-5-tmpv-rises-4-ongc-falls-2-check-list/article-200446/</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>16-09-2026 23:51 UTC</t>
+          <t>17-09-2026 10:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Eisai, Biogen announce Leqembi Pen has been approved in Japan</t>
+          <t>Top Gainers &amp; Losers, September 17, 2026 at 12:00 PM IST: HDFC Life Leads Gainers</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>HDFC Sky</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/the-fly/eisai-biogen-announce-leqembi-pen-has-been-approved-in-japan-thefly-news</t>
+          <t>https://hdfcsky.com/news/top-gainers-losers-september-17-2026-at-12-pm</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>16-09-2026 12:57 UTC</t>
+          <t>17-09-2026 07:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s expands Gilead pact for HIV prevention drug</t>
+          <t>Harsh Goenka, Kiran Mazumdar-Shaw criticise Fendi’s Rs 8.3 lakh ‘Navratri’ bag</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>The Indian Express</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/dr-reddys-expands-pact-with-gilead-for-investigational-hiv-prevention-drug/article71475705.ece</t>
+          <t>https://indianexpress.com/article/trending/trending-in-india/fendi-rs-8-3-lakh-bag-indian-craftsmanship-debate-kiran-mazumdar-shaw-harsh-goenka-10882436/lite/</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>17-09-2026 07:35 UTC</t>
+          <t>17-09-2026 12:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>US billionaire healthcare boss Prem Reddy sues nurses over 'track them down' campaign targeting him, daug</t>
+          <t>‘When will luxury brands stop colonising Indian crafts?’: H…</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>GujaratSamachar English</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/world/us/us-billionaire-healthcare-boss-prem-reddy-sues-nurses-over-track-them-down-campaign-targeting-him-daughter/articleshow/134289250.cms</t>
+          <t>https://english.gujaratsamachar.com/news/national/when-will-luxury-brands-stop-colonising-indian-crafts-harsh-goenka-kiran-mazumdar-shaw-slam-fendi-over-indian-rupee95-lakh-navratri-bag-63401233492</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>16-09-2026 14:17 UTC</t>
+          <t>17-09-2026 09:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Militant nurses accused of targeting billionaire health boss and daughter in disturbing campaign: ‘He can’t hide’</t>
+          <t>Kiran Mazumdar-Shaw Calls Out Fendi’s Rs 8.3 Lakh ‘Navratri’ Bag: ‘Undermines Our Authentic Talent’</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>pragativadi.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://nypost.com/2026/09/16/us-news/prime-healthcare-ceo-prem-reddy-accuses-california-nurses-association-of-targeting-family-homes/</t>
+          <t>https://pragativadi.com/kiran-mazumdar-shaw-calls-out-fendis-rs-8-3-lakh-navratri-bag-undermines-our-authentic-talent/</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>16-09-2026 12:00 UTC</t>
+          <t>16-09-2026 19:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gilead expands lenacapavir licensing to cover once-yearly HIV prevention</t>
+          <t>Viatris’ Wakix receives Japanese approval to treat OSAS and narcolepsy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>StreetInsider</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.streetinsider.com/Corporate+News/Gilead+expands+lenacapavir+licensing+to+cover+once-yearly+HIV+prevention/27067898.html</t>
+          <t>https://www.yahoo.com/news/science/articles/viatris-wakix-receives-japanese-approval-094045863.html</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>16-09-2026 12:31 UTC</t>
+          <t>17-09-2026 09:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MFs turn selective, pick Coal India, LIC among large-caps</t>
+          <t>FTSE rebalance: Meesho, Lenskart lead inflows; Biocon, Wipro out</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/mf/analysis/mfs-turn-selective-pick-coal-india-lic-among-large-caps/amp_articleshow/134298752.cms</t>
+          <t>https://www.businessupturn.com/finance/stock-market/ftse-september-rebalance-takes-effect-tomorrow-meesho-and-lenskart-lead-inflows-biocon-and-wipro-see-outflows/</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>17-09-2026 02:11 UTC</t>
+          <t>17-09-2026 10:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Remepy Welcomes Pharma R&amp;D Leader, Eran Harary, MD, as Chief Medical Officer, to Advance Hybrid Drug™ Pipeline</t>
+          <t>Cultural Appropriation or Collaboration? Fendi’s 'Navratri' Bag With Indian Roots Sparks Debate</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sg.finance.yahoo.com</t>
+          <t>Herzindagi</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/remepy-welcomes-pharma-r-d-113000258.html</t>
+          <t>https://www.herzindagi.com/fashion/cultural-appropriation-or-collaboration-fendi-navratri-bag-with-indian-roots-sparks-debate-article-1069221</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16-09-2026 11:30 UTC</t>
+          <t>17-09-2026 07:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>India clears 642-car import quota from UK under India-UK trade agreement</t>
+          <t>Fendi’s Rs 8 lakh ‘Gujarati mirror work bag’ sparks outrage - The Sentinel</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>The Sentinel - of this Land, for its People</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/auto/auto-news/india-clears-642-car-import-quota-from-uk-under-india-uk-trade-agreement/amp_articleshow/134283859.cms</t>
+          <t>https://www.sentinelassam.com/amp/story/more-news/entertainment/fendis-rs-8-lakh-gujarati-mirror-work-bag-sparks-outrage</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16-09-2026 09:49 UTC</t>
+          <t>17-09-2026 03:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw Calls Out Fendi’s Rs 8.3 Lakh ‘Navratri’ Bag: ‘Undermines Our Authentic Talent’</t>
+          <t>Prescription or not? At neighbourhood medical stores, consumers say rules are not always followed</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pragativadi</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/kiran-mazumdar-shaw-calls-out-fendis-rs-8-3-lakh-navratri-bag-undermines-our-authentic-talent/</t>
+          <t>https://www.thehindu.com/news/cities/Hyderabad/prescription-or-not-at-neighbourhood-medical-stores-consumers-say-rules-are-not-always-followed/article71476915.ece</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>16-09-2026 19:09 UTC</t>
+          <t>17-09-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cultural Appropriation or Collaboration? Fendi’s 'Navratri' Bag With Indian Roots Sparks Debate</t>
+          <t>Closing Bell: Market snaps 2-day fall; Sensex up 333 pts, Nifty above 23,200</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>herzindagi.com</t>
+          <t>IndiaIPO</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.herzindagi.com/fashion/cultural-appropriation-or-collaboration-fendi-navratri-bag-with-indian-roots-sparks-debate-article-1069221</t>
+          <t>https://www.indiaipo.in/news/detail/closing-bell-market-snaps-2-day-fall-sensex-up-333-pts-nifty-above-23200</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17-09-2026 07:39 UTC</t>
+          <t>17-09-2026 08:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fendi’s Rs 8 lakh ‘Gujarati mirror work bag’ sparks outrage - The Sentinel</t>
+          <t>Novo partners with Anthropic to speed up drug development with Claude</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>The Sentinel - of this Land, for its People</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/amp/story/more-news/entertainment/fendis-rs-8-lakh-gujarati-mirror-work-bag-sparks-outrage</t>
+          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/novo-partners-with-anthropic-to-speed-up-drug-development-with-claude/134297461</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>17-09-2026 03:19 UTC</t>
+          <t>17-09-2026 01:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2461,22 +2461,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma receives final USFDA approval for generic Beclomethasone inhalation Aerosol</t>
+          <t>Rakovina Therapeutics Announces Appointment of New Scientific Advisory Board Member</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/regulatory/aurobindo-pharma-receives-final-usfda-approval-for-generic-beclomethasone-inhalation-aerosol-21875</t>
+          <t>https://sg.finance.yahoo.com/news/rakovina-therapeutics-announces-appointment-scientific-083000136.html</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>16-09-2026 14:24 UTC</t>
+          <t>17-09-2026 08:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Remepy Welcomes Pharma R&amp;D Leader, Eran Harary, MD, as Chief Medical Officer, to Advance Hybrid Drug™ Pipeline</t>
+          <t>Sensex, Nifty trade in positive terrain; pharma shares snap 5-day losing streak</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sg.finance.yahoo.com</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/remepy-welcomes-pharma-r-d-113000258.html</t>
+          <t>https://www.business-standard.com/amp/markets/capital-market-news/sensex-nifty-trade-in-positive-terrain-pharma-shares-snap-5-day-losing-streak-126091700646_1.html</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>16-09-2026 11:30 UTC</t>
+          <t>17-09-2026 09:20 UTC</t>
         </is>
       </c>
     </row>
@@ -2515,22 +2515,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Closing Bell: Market snaps 2-day fall; Sensex up 332 pts, Nifty above 23,200</t>
+          <t>Longeveron explores strategic options after therapy fails mid-stage trial for infant heart condition</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IndiaIPO</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.indiaipo.in/news/detail/closing-bell-market-snaps-2-day-fall-sensex-up-332-pts-nifty-above-23200</t>
+          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/longeveron-explores-strategic-options-after-therapy-fails-mid-stage-trial-for-infant-heart-condition/134297463</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16-09-2026 11:27 UTC</t>
+          <t>17-09-2026 01:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2542,22 +2542,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Former Novartis Executive Ingrid Zhang Named Legend Biotech CEO, Succeeds Ying Huang</t>
+          <t>Novartis halts ALS drug development after mid-stage trial failure</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>medicaldialogues.in</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/former-novartis-executive-ingrid-zhang-named-legend-biotech-ceo-succeeds-ying-huang-179378</t>
+          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/novartis-halts-als-drug-development-after-mid-stage-trial-failure/134297430</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>16-09-2026 13:12 UTC</t>
+          <t>17-09-2026 01:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2569,22 +2569,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bristol Myers, Ono Sue Amgen to Block Proposed Opdivo Biosimilar in US</t>
+          <t>Sebi bars two entities over alleged cross-derivatives manipulation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>medicaldialogues.in</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/bristol-myers-ono-sue-amgen-to-block-proposed-opdivo-biosimilar-in-us-179377</t>
+          <t>https://m.economictimes.com/markets/stocks/news/indian-regulator-bars-two-entities-over-alleged-cross-derivatives-manipulation/articleshow/134291762.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>16-09-2026 13:05 UTC</t>
+          <t>16-09-2026 15:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,22 +2596,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sjögren's Syndrome Market to Witness Sustained Growth During the Forecast Period (2026-2036) Due to the Development of Targeted Immunotherapies, FcRn Inhibitors, TYK2 Inhibitors, and Cell Therapies | DelveInsight</t>
+          <t>Bank of India Mid Cap Fund Direct Growth Review 2026: NAV, Returns, Portfolio &amp; Should You Invest?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>prnewswire.co.uk</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.co.uk/news-releases/sjogrens-syndrome-market-to-witness-sustained-growth-during-the-forecast-period-20262036-due-to-the-development-of-targeted-immunotherapies-fcrn-inhibitors-tyk2-inhibitors-and-cell-therapies--delveinsight-302880061.html</t>
+          <t>https://univest.in/blogs/bank-of-india-mid-cap-fund-direct-growth-review-2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>16-09-2026 14:31 UTC</t>
+          <t>17-09-2026 04:46 UTC</t>
         </is>
       </c>
     </row>
@@ -2623,157 +2623,157 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Gilead Expands Lenacapavir Access With New PAHO Deal in Latin America</t>
+          <t>Amphetamine + Deaxmphetamine Market to Surpass USD 906.4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>sg.finance.yahoo.com</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/gilead-expands-lenacapavir-access-paho-142600311.html</t>
+          <t>https://www.openpr.com/news/4634064/amphetamine-deaxmphetamine-market-to-surpass-usd-906-4</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>16-09-2026 14:26 UTC</t>
+          <t>17-09-2026 06:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Market wrap: SBI, HDFC Life, TCS, Infosys top gainers and losers on Nifty and Sensex on Thursday</t>
+          <t>Charles River Launches Rapid Cell Banking Programs</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>contractpharma.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/market-wrap-sbi-hdfc-life-tcs-infosys-top-gainers-and-losers-on-nifty-and-sensex-on-thursday/articleshow/134286572.cms</t>
+          <t>https://www.contractpharma.com/breaking-news/charles-river-launches-rapid-cell-banking-programs/</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>16-09-2026 11:33 UTC</t>
+          <t>17-09-2026 14:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AI, algorithms and human judgement: The future of portfolio management</t>
+          <t>Thermo Fisher Launches SuperScript V Reverse Transcriptase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>contractpharma.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/ai-algorithms-and-human-judgement-the-future-of-portfolio-management/articleshow/134285324.cms</t>
+          <t>https://www.contractpharma.com/breaking-news/thermo-fisher-launches-superscript-v-reverse-transcriptase/</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>16-09-2026 10:42 UTC</t>
+          <t>16-09-2026 19:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sebi bars two entities over alleged cross-derivatives manipulation</t>
+          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/indian-regulator-bars-two-entities-over-alleged-cross-derivatives-manipulation/articleshow/134291762.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>16-09-2026 15:51 UTC</t>
+          <t>17-09-2026 12:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>India clears 642-car import quota from UK under India-UK trade agreement</t>
+          <t>Upperton Gains MHRA Approval for Nottingham Sterile Manufacturing Site</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>contractpharma.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/auto/auto-news/india-clears-642-car-import-quota-from-uk-under-india-uk-trade-agreement/amp_articleshow/134283859.cms</t>
+          <t>https://www.contractpharma.com/breaking-news/upperton-gains-mhra-approval-for-nottingham-sterile-manufacturing-site/</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>16-09-2026 09:49 UTC</t>
+          <t>17-09-2026 13:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cabinet raises PF wage ceiling to Rs 25,000 from Rs 15,000</t>
+          <t>SK Biopharma, 1STBIO Sign Parkinson’s Drug Deal</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>contractpharma.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/banking/finance/cabinet-raises-pf-wage-ceiling-to-rs-25000-ashwini-vaishnaw/amp_articleshow/134284053.cms</t>
+          <t>https://www.contractpharma.com/breaking-news/sk-biopharma-1stbio-sign-parkinsons-drug-deal/</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>16-09-2026 09:41 UTC</t>
+          <t>17-09-2026 12:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,22 +2785,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals, SPIMACO Bio Ink MENA Biosimilars Deal</t>
+          <t>Gilead Partners With Pan American Health Organization on Lenacapavir Access for Latin America, Caribbean</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>contractpharma.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/shilpa-biologicals-spimaco-bio-ink-mena-biosimilars-deal/</t>
+          <t>https://www.contractpharma.com/breaking-news/gilead-partners-with-pan-american-health-organization-on-lenacapavir-access-for-latin-america-caribbean/</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16-09-2026 13:24 UTC</t>
+          <t>16-09-2026 19:36 UTC</t>
         </is>
       </c>
     </row>
@@ -2812,157 +2812,157 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Shilpa Bio inks deal for PD-1 biosimilar for MENA market</t>
+          <t>Lilly TuneLab, Twist Bioscience Partner on Antibody Drug Discovery</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>contractpharma.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/shilpa-bio-inks-deal-for--1-biosimilar-for-mena-market</t>
+          <t>https://www.contractpharma.com/breaking-news/lilly-tunelab-twist-bioscience-partner-on-antibody-drug-discovery/</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16-09-2026 11:08 UTC</t>
+          <t>16-09-2026 16:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Piramal Pharma Plans Solar Power Plant in UK</t>
+          <t>Samsung Galaxy S26 gets first price hike in India, will start at Rs 99,999 from September 20th</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>91mobiles.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/piramal-pharma-plans-solar-power-plant-in-uk/</t>
+          <t>https://www.91mobiles.com/hub/samsung-galaxy-s26-first-price-hike-india-september-20th/</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>16-09-2026 14:56 UTC</t>
+          <t>17-09-2026 04:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Thermo Fisher Launches SuperScript V Reverse Transcriptase</t>
+          <t>Watch: Kinva Bio on What It Means to Be Among Samsung Solve for Tomorrow’s Top 20</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/thermo-fisher-launches-superscript-v-reverse-transcriptase/</t>
+          <t>https://news.samsung.com/in/watch-kinva-bio-on-what-it-means-to-be-among-samsung-solve-for-tomorrows-top-20</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>16-09-2026 19:11 UTC</t>
+          <t>17-09-2026 12:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Gilead Partners With Pan American Health Organization on Lenacapavir Access for Latin America, Caribbean</t>
+          <t>Galaxy A56 gets the second One UI 9 beta update</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/gilead-partners-with-pan-american-health-organization-on-lenacapavir-access-for-latin-america-caribbean/</t>
+          <t>https://www.sammobile.com/news/galaxy-a56-one-ui-9-beta-2-update/</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>16-09-2026 19:36 UTC</t>
+          <t>17-09-2026 09:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lilly TuneLab, Twist Bioscience Partner on Antibody Drug Discovery</t>
+          <t>Samsung Galaxy S26 Price in India Tipped to Increase by Rs 12,000: Check Details</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/lilly-tunelab-twist-bioscience-partner-on-antibody-drug-discovery/</t>
+          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s26-price-in-india-increase-by-rs-12000-12060021</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16-09-2026 16:02 UTC</t>
+          <t>17-09-2026 12:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hovione Doubles US Spray-Drying Capacity With Opening of New NJ Facility</t>
+          <t>Samsung Galaxy Z Fold 8 EMI drops under Forever plan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>t2ONLINE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/hovione-doubles-us-spray-drying-capacity-with-opening-of-new-nj-facility/</t>
+          <t>https://t2online.in/tech/tech-news/samsung-galaxy-z-fold-8-emi-drops-under-forever-plan/2008068</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>16-09-2026 14:51 UTC</t>
+          <t>17-09-2026 08:36 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,22 +2974,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Samsung Begins Official Rollout of One UI 9, Bringing the Latest Galaxy Experiences to More Devices</t>
+          <t>After 30 Years, Samsung Is Powering Innovation for India | Hindustan Times</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>hindustantimes.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/global/samsung-begins-official-rollout-of-one-ui-9-bringing-the-latest-galaxy-experiences-to-more-devices</t>
+          <t>https://www.hindustantimes.com/genesis/after-30-years-samsung-is-powering-innovation-for-india-101787854726831.html</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>16-09-2026 12:00 UTC</t>
+          <t>17-09-2026 14:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3001,22 +3001,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 Price To Hike By Rs 12,000 in India: Check New Prices</t>
+          <t>Samsung rolls out Galaxy Forever plan, brings new financing options for Galaxy Z Fold 8 Ultra, Fold 8 in India</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>My Mobile India</t>
+          <t>gadgetbridge.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.mymobileindia.com/samsung-galaxy-s26-price-to-hike-by-rs-12000-in-india-check-new-prices/</t>
+          <t>https://www.gadgetbridge.com/samsung-rolls-out-galaxy-forever-plan-brings-new-financing-options-for-galaxy-z-fold-8-ultra-fold-8-in-india/</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>17-09-2026 04:08 UTC</t>
+          <t>17-09-2026 14:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 gets first price hike in India, will start at Rs 99,999 from September 20th</t>
+          <t>Samsung could give the Galaxy S27 Ultra a major camera processing upgrade</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>91mobiles.com</t>
+          <t>Android Authority</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.91mobiles.com/hub/samsung-galaxy-s26-first-price-hike-india-september-20th/</t>
+          <t>https://www.androidauthority.com/samsung-galaxy-s27-ultra-camera-upgrades-leak-3712251/</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>17-09-2026 04:38 UTC</t>
+          <t>17-09-2026 07:52 UTC</t>
         </is>
       </c>
     </row>
@@ -3055,22 +3055,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Samsung Begins Official Rollout of One UI 9, Bringing the Latest Galaxy Experiences to More Devices</t>
+          <t>Samsung Galaxy S26 Price To Hike By Rs 12,000 in India: Check New Prices</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Samsung Mobile Press</t>
+          <t>My Mobile India</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.samsungmobilepress.com/articles/one-ui-9-official-rollout-latest-galaxy-experiences</t>
+          <t>https://www.mymobileindia.com/samsung-galaxy-s26-price-to-hike-by-rs-12000-in-india-check-new-prices/</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>16-09-2026 12:04 UTC</t>
+          <t>17-09-2026 04:08 UTC</t>
         </is>
       </c>
     </row>
@@ -3082,22 +3082,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Samsung One UI 9 Rollout Starts for Galaxy S26 Series: Check Eligible Galaxy Devices, New Features</t>
+          <t>Samsung’s Blue Tag Sale Makes Smarter Living More Accessible with AI-Powered Home Innovation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/news/samsung-one-ui-9-rollout-galaxy-s26-series-eligible-devices-features-12057853</t>
+          <t>https://news.samsung.com/za/samsungs-blue-tag-sale-makes-smarter-living-more-accessible-with-ai-powered-home-innovation</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>17-09-2026 06:17 UTC</t>
+          <t>17-09-2026 13:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3109,22 +3109,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Samsung India Sees Strong Festive Season Demand, Projects Double-Digit Growth</t>
+          <t>Samsung cuts Galaxy Z Fold8, Fold8 Ultra EMIs by 25 percent with Galaxy Forever</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Indian Retailer</t>
+          <t>91mobiles.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.indianretailer.com/news/samsung-india-sees-strong-festive-season-demand-projects-double-digit-growth</t>
+          <t>https://www.91mobiles.com/hub/samsung-galaxy-z-fold8-ultra-emis-galaxy-forever/</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>17-09-2026 06:22 UTC</t>
+          <t>17-09-2026 10:26 UTC</t>
         </is>
       </c>
     </row>
@@ -3136,22 +3136,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Samsung launches new AI fridge in India that recommends recipes; check Bespoke AI lineup and prices</t>
+          <t>Samsung phones get September 2026 Google Play System update</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/technology/samsung-launches-new-ai-fridge-in-india-that-recommends-recipes-check-bespoke-ai-lineup-and-prices-11789621850749.html</t>
+          <t>https://www.sammobile.com/news/samsung-phones-get-september-2026-google-play-system-update/</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>17-09-2026 05:56 UTC</t>
+          <t>17-09-2026 14:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,185 +3163,184 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Samsung India expects double-digit growth in H2 appliances on festive demand</t>
+          <t>Samsung Galaxy S27 Ultra Could Get New Image Processing for More Natural Photos: Leak</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>The Shillong Times</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://theshillongtimes.com/2026/09/17/samsung-india-expects-double-digit-growth-in-h2-appliances-on-festive-demand/</t>
+          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s27-ultra-rear-camera-video-specifications-leak-12060286</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>17-09-2026 00:44 UTC</t>
+          <t>17-09-2026 13:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Samsung just made its refrigerator smarter with Gemini; new AI appliances launched in India | Technology News
-(HT Tech)</t>
+          <t>Celltrion's Remsima Tops Japan's Infliximab Market, Surpassing Originator Drug</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hindustan Times</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/technology/samsung-just-made-its-refrigerator-smarter-with-gemini-new-ai-appliances-launched-in-india-101789624645164.html</t>
+          <t>https://finance.biggo.com/news/2ce8c00d-beb2-47a2-af48-bd21e57cd128</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>17-09-2026 06:14 UTC</t>
+          <t>17-09-2026 02:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Samsung Launches Stable One UI 9.0 for Galaxy S26 Series</t>
+          <t>Celltrion’s Remsima Takes No. 1 in Japan After 11 Years</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>India News Network</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.indianewsnetwork.com/en/samsung-launches-stable-one-ui-9-0-galaxy-s26-series-20260917</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277185</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>17-09-2026 04:40 UTC</t>
+          <t>17-09-2026 03:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Samsung One UI 9 stable update rolls out starting with Galaxy S26 series</t>
+          <t>Celltrion’s Remsima Takes No. 1 Spot in Japan’s Infliximab Market After 11 Years</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FoneArena.com</t>
+          <t>koreaittimes.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.fonearena.com/blog/492571/samsung-one-ui-9-stable-roll-out-galaxy-s26-series.html</t>
+          <t>https://www.koreaittimes.com/news/articleView.html?idxno=157265</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>17-09-2026 05:14 UTC</t>
+          <t>17-09-2026 01:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Samsung One UI 9.0 Stable Update Based on Android 17 Rolls Out for Galaxy S26 Series: Check New Features</t>
+          <t>Celltrion's autoimmune disease treatment "Ramsima" overtook the original drug 11 years after its lau..</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Gizbot</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.gizbot.com/mobile/news/samsung-one-ui-9-0-stable-update-android-17-rolls-out-galaxy-s26-series-new-features-128585.html</t>
+          <t>https://www.mk.co.kr/en/it/12155321</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>17-09-2026 06:00 UTC</t>
+          <t>17-09-2026 05:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Samsung begins rolling out One UI 9 with Android 17: Galaxy phones getting update and new features</t>
+          <t>Celltrion's Remsima Tops Japan Infliximab Market After 11 Years</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/technology/news/story/samsung-begins-rolling-out-one-ui-9-with-android-17-galaxy-phones-getting-update-and-new-features-556067-2026-09-17</t>
+          <t>https://en.sedaily.com/finance/2026/09/17/celltrions-remsima-tops-japan-infliximab-market-after-11</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>17-09-2026 06:02 UTC</t>
+          <t>17-09-2026 00:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Samsung launches Samsung Innovation Campus 2026 in Karnataka to Build an AI-ready Future, to Train 2000 Students</t>
+          <t>Celltrion captures Japan lead with Remsima biosimilar, eyes SC launch - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/in/samsung-launches-samsung-innovation-campus-2026-in-karnataka-to-build-an-ai-ready-future-to-train-2000-students</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/17/EBUUYC3ILVC6THC2NCM5WFOSQU/</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>17-09-2026 05:17 UTC</t>
+          <t>16-09-2026 23:56 UTC</t>
         </is>
       </c>
     </row>
@@ -3353,22 +3352,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Celltrion’s Remsima Takes No. 1 in Japan After 11 Years</t>
+          <t>Celltrion's Remsima Tops Japanese Infliximab Prescriptions After 11 Years Since Launch</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277185</t>
+          <t>https://www.asiae.co.kr/en/article/2026091707490713431</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>17-09-2026 03:56 UTC</t>
+          <t>16-09-2026 22:49 UTC</t>
         </is>
       </c>
     </row>
@@ -3380,265 +3379,265 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Celltrion's Remsima Tops Japan's Infliximab Market, Surpassing Originator Drug</t>
+          <t>Zymfentra, Xcopri Near $1 Billion Sales Mark</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/2ce8c00d-beb2-47a2-af48-bd21e57cd128</t>
+          <t>https://en.sedaily.com/finance/2026/09/17/zymfentra-xcopri-near-1-billion-sales-mark</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>17-09-2026 02:25 UTC</t>
+          <t>16-09-2026 22:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Celltrion’s Remsima Takes No. 1 Spot in Japan’s Infliximab Market After 11 Years</t>
+          <t>Prestige Biopharma IDC Obtains International Certification for Environmental and Occupational Health and Safety Standards</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Korea IT Times</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.koreaittimes.com/news/articleView.html?idxno=157265</t>
+          <t>https://www.asiae.co.kr/en/article/stock-etc/2026091709115812850</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>17-09-2026 01:37 UTC</t>
+          <t>17-09-2026 00:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Celltrion's autoimmune disease treatment "Ramsima" overtook the original drug 11 years after its lau..</t>
+          <t>About 20 Pusan National University Students Visit Bio and Logistics Sites... BJFEZ Holds 'Insight Trip'</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/en/it/12155321</t>
+          <t>https://www.asiae.co.kr/en/article/yeongnam/2026091715044359776</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>17-09-2026 05:12 UTC</t>
+          <t>17-09-2026 06:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Celltrion's Remsima Tops Japan Infliximab Market After 11 Years</t>
+          <t>Fortis moves Supreme Court against Delhi High Court order</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/17/celltrions-remsima-tops-japan-infliximab-market-after-11</t>
+          <t>https://timesofindia.indiatimes.com/business/india-business/fortis-moves-supreme-court-against-delhi-high-court-order/amp_articleshow/134309495.cms</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>17-09-2026 00:20 UTC</t>
+          <t>17-09-2026 10:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Celltrion's Ramcima tops Japan's infliximab market for first time, overtaking originator</t>
+          <t>AZ, Daiichi's Enhertu scores long-awaited NICE blessing in HER2-low breast cancer</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>헤럴드경제</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://mbiz.heraldcorp.com/article/10876273</t>
+          <t>https://www.fiercepharma.com/pharma/az-daiichis-enhertu-wins-long-awaited-nice-blessing</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>16-09-2026 23:04 UTC</t>
+          <t>16-09-2026 23:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Celltrion captures Japan lead with Remsima biosimilar, eyes SC launch - CHOSUNBIZ</t>
+          <t>AstraZeneca and Daiichi Sankyo secure NHS England access for Enhertu breast cancer drug</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Traders Union</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/17/EBUUYC3ILVC6THC2NCM5WFOSQU/</t>
+          <t>https://tradersunion.com/news/financial-news/show/3369162-enhertu-nhs-england-breast-cancer-access/</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>16-09-2026 23:56 UTC</t>
+          <t>17-09-2026 12:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Celltrion's Remsima Tops Japanese Infliximab Prescriptions After 11 Years Since Launch</t>
+          <t>Fortis Healthcare moves Supreme Court against Delhi HC forensic audit order</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Rediff</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/2026091707490713431</t>
+          <t>https://m.rediff.com/amp/business/report/fortis-healthcare-challenges-delhi-hc-forensic-audit-into-alleged-asset-erosion-by-former-promoters/20260917.htm</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>16-09-2026 22:49 UTC</t>
+          <t>17-09-2026 07:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Zymfentra, Xcopri Near $1 Billion Sales Mark</t>
+          <t>Special Report on Shareholding Daiichi Sankyo (7.39% → 7.97%) Blackrock Japan, et al.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/17/zymfentra-xcopri-near-1-billion-sales-mark</t>
+          <t>https://www.moomoo.com/news/post/76384289/special-report-on-shareholdings-daiichi-sankyo-7-39-7-97</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>16-09-2026 22:00 UTC</t>
+          <t>17-09-2026 07:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Prestige Biopharma IDC Obtains International Certification for Environmental and Occupational Health and Safety Standards</t>
+          <t>Fortis Healthcare moves Supreme Court against forensic audit order</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/stock-etc/2026091709115812850</t>
+          <t>https://www.thehindubusinessline.com/companies/fortis-healthcare-files-slp-against-forensic-audit-order-in-daiichi-sankyo-case/article71473603.ece</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>17-09-2026 00:11 UTC</t>
+          <t>16-09-2026 15:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>About 20 Pusan National University Students Visit Bio and Logistics Sites... BJFEZ Holds 'Insight Trip'</t>
+          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/yeongnam/2026091715044359776</t>
+          <t>https://www.marketscreener.com/news/astrazeneca-daiichi-breast-cancer-drug-cleared-for-nhs-use-in-england-ce785bd3dd88f124</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>17-09-2026 06:04 UTC</t>
+          <t>17-09-2026 11:39 UTC</t>
         </is>
       </c>
     </row>
@@ -3650,22 +3649,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Fortis Healthcare moves Supreme Court against forensic audit order</t>
+          <t>IHH Unit Fortis Files Supreme Court Petition Against Delhi High Court Order In Daiichi Proceedings</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>BusinessToday Malaysia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/fortis-healthcare-files-slp-against-forensic-audit-order-in-daiichi-sankyo-case/article71473603.ece</t>
+          <t>https://www.businesstoday.com.my/2026/09/17/ihh-unit-fortis-files-supreme-court-against-delhi-high-court-order-in-daiichi-proceedings/</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>16-09-2026 15:43 UTC</t>
+          <t>17-09-2026 10:19 UTC</t>
         </is>
       </c>
     </row>
@@ -3677,22 +3676,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AZ, Daiichi's Enhertu scores long-awaited NICE blessing in HER2-low breast cancer</t>
+          <t>NICE finally backs Enhertu for HER2-low breast cancer</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>pharmaphorum.com</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/az-daiichis-enhertu-wins-long-awaited-nice-blessing</t>
+          <t>https://pharmaphorum.com/news/nice-finally-backs-enhertu-her2-low-breast-cancer</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>16-09-2026 23:30 UTC</t>
+          <t>17-09-2026 09:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3704,22 +3703,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fortis moves SC against HC forensic audit order in company transactions</t>
+          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>islandpacket.com</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/companies/news/fortis-moves-sc-against-hc-forensic-audit-order-in-company-transactions-126091600888_1.html</t>
+          <t>https://www.islandpacket.com/living/article317278373.html</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>16-09-2026 11:51 UTC</t>
+          <t>17-09-2026 11:32 UTC</t>
         </is>
       </c>
     </row>
@@ -3731,22 +3730,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Daiichi and AstraZeneca cancer drugs secure further approvals in Japan</t>
+          <t>Fortis Healthcare Files SC Petition Against HC Order &amp; Signs Agreement for 400+ Bed Hospital</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>sahi.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/daiichi-and-astrazeneca-cancer-drugs-secure-further-approvals-in-japan-ce785bd2da8bff24</t>
+          <t>https://www.sahi.com/news/fortis-healthcare-files-special-leave-petition-before-supreme-court-against-delhi-hc-judgment</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>16-09-2026 08:47 UTC</t>
+          <t>16-09-2026 17:14 UTC</t>
         </is>
       </c>
     </row>
@@ -3758,22 +3757,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Fortis Healthcare moves Supreme Court against Delhi HC forensic audit order</t>
+          <t>A Life-Extending Breast Cancer Drug Finally Comes to England</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Rediff</t>
+          <t>Bloomberg.com</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://www.rediff.com/business/report/fortis-healthcare-challenges-delhi-hc-forensic-audit-into-alleged-asset-erosion-by-former-promoters/20260917.htm</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-16/a-life-extending-breast-cancer-drug-finally-comes-to-england</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>17-09-2026 07:03 UTC</t>
+          <t>16-09-2026 23:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3785,76 +3784,76 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Fortis moves SC against Delhi HC order in Daiichi Sankyo award case</t>
+          <t>‘Life-changing’ breast cancer drug now available on NHS in England</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Asianet Newsable</t>
+          <t>Financial Times</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://newsable.asianetnews.com/india/fortis-moves-sc-against-delhi-hc-order-in-daiichi-sankyo-award-case-articleshow-v6wnlq7</t>
+          <t>https://www.ft.com/content/e1f59abc-6ecf-4cef-80aa-75d201f731d0?syn-25a6b1a6=1</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>16-09-2026 11:00 UTC</t>
+          <t>16-09-2026 23:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Vishal Sikka's Hang Ten Systems Raises $53M Just Five Weeks After Seed Round</t>
+          <t>NICE Reverses Enhertu Rejection for HER2-Low Breast Cancer After Pricing &amp; Methods Changes</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BBN Times</t>
+          <t>NAVLIN DAILY</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://www.bbntimes.com/technology/vishal-sikka-s-hang-ten-systems-raises-53m-just-five-weeks-after-seed-round</t>
+          <t>https://www.navlindaily.com/article/31897/nice-reverses-enhertu-rejection-for-her2-low-breast-cancer-after-pricing-methods-changes</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>16-09-2026 18:44 UTC</t>
+          <t>17-09-2026 08:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Former Infosys chief’s AI startup nabs another $53M</t>
+          <t>Kura Oncology Q2FY26 Results: Comzifti revenue hits $9.1 million</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TechCrunch</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/former-infosys-chiefs-ai-startup-adds-50m-to-seed-weeks-after-initial-raise/</t>
+          <t>https://scanx.trade/stock-market-news/companies/kura-oncology-q2fy26-results-comzifti-revenue-hits-9-1-million/51187458</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>16-09-2026 13:00 UTC</t>
+          <t>17-09-2026 10:54 UTC</t>
         </is>
       </c>
     </row>
@@ -3866,22 +3865,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA : Barclays reaffirms its Buy rating</t>
+          <t>Savory Oral Nutrition Supplement Market</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Future Market Insights</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-barclays-reaffirms-its-buy-rating-ce785bd2dc88f726</t>
+          <t>https://www.futuremarketinsights.com/reports/savory-oral-nutrition-supplement-market</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>16-09-2026 12:09 UTC</t>
+          <t>17-09-2026 12:17 UTC</t>
         </is>
       </c>
     </row>
@@ -3893,76 +3892,76 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SK Hynix reportedly in talks with Intel to build memory chips in US</t>
+          <t>Hang Ten Systems Raises Another $53 Million in Seed Funding</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TechCrunch</t>
+          <t>Equitypandit</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/sk-hynix-reportedly-in-talks-with-intel-to-build-memory-chips-in-us/</t>
+          <t>https://www.equitypandit.com/hang-ten-systems-raises-another-53-million-in-seed-funding/</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>16-09-2026 13:23 UTC</t>
+          <t>17-09-2026 10:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Trialynx Wins DPHARM Idol Disrupt 2026</t>
+          <t>Fresenius SE &amp; Co. KGaA : Buy rating from UBS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/partner-content/trialynx-wins-dpharm-idol-disrupt-2026</t>
+          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-buy-rating-from-ubs-ce785bd3da81f421</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>16-09-2026 16:45 UTC</t>
+          <t>17-09-2026 11:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Alkermes Announces Appointment of Anne C. Whitaker to Board of Directors</t>
+          <t>Vishal Sikka's Hang Ten Systems Raises $53M Just Five Weeks After Seed Round</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>bbntimes.com</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/alkermes-announces-appointment-of-anne-c-whitaker-to-board-of-directors</t>
+          <t>https://www.bbntimes.com/technology/vishal-sikka-s-hang-ten-systems-raises-53m-just-five-weeks-after-seed-round</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>16-09-2026 14:12 UTC</t>
+          <t>16-09-2026 18:44 UTC</t>
         </is>
       </c>
     </row>
@@ -3974,130 +3973,130 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GSK Pharma Shareholders Approve Board and Managing Director Appointments via Postal Ballot</t>
+          <t>Bhavana Chivukula, Profiled By Influential Women, Advances Pharmaceutical Innovation Through Research And Manufacturing</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>EIN News</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/gsk-pharma-shareholders-approve-board-and-managing-director-appointments-via-postal-ballot</t>
+          <t>https://www.einnews.com/pr_news/943037449/bhavana-chivukula-profiled-by-influential-women-advances-pharmaceutical-innovation-through-research-and-manufacturing</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>16-09-2026 16:40 UTC</t>
+          <t>17-09-2026 13:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Alvotech Shares Rise After Double Upgrade From Barclays</t>
+          <t>GlycoEra hires Astria dealmaker as chief business officer</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/alvotech-shares-rise-after-double-upgrade-from-barclays-ce785bd2de81f42d</t>
+          <t>http://www.thepharmaletter.com/biotech-news/glycoera-hires-astria-dealmaker-as-chief-business-officer</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>16-09-2026 18:12 UTC</t>
+          <t>17-09-2026 08:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Alvotech upgraded to Overweight from Underweight at Barclays</t>
+          <t>Trialynx Wins DPHARM Idol Disrupt 2026</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/the-fly/alvotech-upgraded-to-overweight-from-underweight-at-barclays-thefly-news?mod=mw_quote_news</t>
+          <t>https://www.fiercepharma.com/partner-content/trialynx-wins-dpharm-idol-disrupt-2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>16-09-2026 12:43 UTC</t>
+          <t>16-09-2026 16:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>About Teva Pharmaceutical Industries Ltd. rStock</t>
+          <t>GSK Pharma Shareholders Approve Board and Managing Director Appointments via Postal Ballot</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/en-pt/price/teva-pharmaceutical-industries-ltd-rstock</t>
+          <t>https://www.tipranks.com/news/company-announcements/gsk-pharma-shareholders-approve-board-and-managing-director-appointments-via-postal-ballot</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>17-09-2026 00:57 UTC</t>
+          <t>16-09-2026 16:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Delhi HC orders tax dept to refund ₹783 cr to Teva Israel over Ranbaxy payment</t>
+          <t>Alvotech Shares Rise After Double Upgrade From Barclays</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>A2Z Taxcorp LLP</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://a2ztaxcorp.net/delhi-hc-orders-tax-dept-to-refund-%E2%82%B9783-cr-to-teva-israel-over-ranbaxy-payment/</t>
+          <t>https://www.marketscreener.com/news/alvotech-shares-rise-after-double-upgrade-from-barclays-ce785bd2de81f42d</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>16-09-2026 12:34 UTC</t>
+          <t>16-09-2026 18:12 UTC</t>
         </is>
       </c>
     </row>
@@ -4109,22 +4108,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Teva’s Lab-Made Antibody Shot for Celiac Shows Hopeful Results</t>
+          <t>About Teva Pharmaceutical Industries Ltd. rStock</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>allergicliving.com</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://www.allergicliving.com/2026/09/16/tevas-lab-made-antibody-shot-for-celiac-shows-hopeful-results/</t>
+          <t>https://www.coinbase.com/en-pt/price/teva-pharmaceutical-industries-ltd-rstock</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>16-09-2026 22:36 UTC</t>
+          <t>17-09-2026 00:57 UTC</t>
         </is>
       </c>
     </row>
@@ -4136,22 +4135,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mere Payment By Indian Resident To Non-Resident Not Income Accruing In India: Delhi High Court</t>
+          <t>Teva’s Lab-Made Antibody Shot for Celiac Shows Hopeful Results</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>livelawbiz.com</t>
+          <t>Allergic Living</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://www.livelawbiz.com/amp/income-tax/high-court/mere-payment-by-indian-resident-to-non-resident-not-income-accruing-in-india-delhi-high-court-550360</t>
+          <t>https://www.allergicliving.com/2026/09/16/tevas-lab-made-antibody-shot-for-celiac-shows-hopeful-results/</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>16-09-2026 14:11 UTC</t>
+          <t>16-09-2026 22:36 UTC</t>
         </is>
       </c>
     </row>
@@ -4163,22 +4162,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Teva launches educational website for HCPs to advance understanding of LAIs in schizophrenia care</t>
+          <t>Most Active Options Report: FPS, TEVA, AFL</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PharmaLive</t>
+          <t>Schaeffer's Investment Research</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://www.pharmalive.com/teva-launches-educational-website-for-hcps-to-advance-understanding-of-lais-in-schizophrenia-care/</t>
+          <t>https://www.schaeffersresearch.com/content/options/2026/09/16/most-active-options-report-fps-teva-afl</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>16-09-2026 13:44 UTC</t>
+          <t>16-09-2026 15:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4190,49 +4189,49 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Is the Teva Trailpeak as adventurous as its name suggests?</t>
+          <t>Teva Launches LongActingImpact.com to Advance Understanding of Earlier, Effective and Uninterrupted Schizophrenia Care</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>believeintherun.com</t>
+          <t>Indovizka.com</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://believeintherun.com/shoe-reviews/teva-trailpeak-review/</t>
+          <t>https://indovizka.com/news/detail/22813/teva-launches-longactingimpactcom-to-advance-understanding-of-earlier-effective-and-uninterrupted-schizophrenia-care</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>16-09-2026 13:39 UTC</t>
+          <t>17-09-2026 01:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Most Active Options Report: FPS, TEVA, AFL</t>
+          <t>Lantern Pharma to Present Open-Medicine AI — a Multi-Agentic Platform for End-to-End Therapeutic Development — Business Model, Roadmap, and Value Proposition on September 23</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Schaeffer's Investment Research</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://www.schaeffersresearch.com/content/options/2026/09/16/most-active-options-report-fps-teva-afl</t>
+          <t>https://sg.finance.yahoo.com/news/lantern-pharma-present-open-medicine-122000593.html</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>16-09-2026 15:53 UTC</t>
+          <t>17-09-2026 12:20 UTC</t>
         </is>
       </c>
     </row>
@@ -4244,22 +4243,22 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Shilpa Bio inks deal for PD-1 biosimilar for MENA market</t>
+          <t>WuXi XDC Out-Licenses WuXiTecan-2 Payload-Linker Technology Platform to Ona Therapeutics to Advance Novel ADC Research and Development</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/shilpa-bio-inks-deal-for--1-biosimilar-for-mena-market</t>
+          <t>https://sg.finance.yahoo.com/news/wuxi-xdc-licenses-wuxitecan-2-080900462.html</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>16-09-2026 11:08 UTC</t>
+          <t>17-09-2026 08:09 UTC</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4275,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>sg.finance.yahoo.com</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4303,7 +4302,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>sg.finance.yahoo.com</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4325,49 +4324,49 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>VivoSim Labs Unveils New NAMkind™ Drug Toxicity Data at EUROTOX 2026, Demonstrating Predictive Superiority in Liver and Gastrointestinal Safety Across Small Molecules and ADCs</t>
+          <t>Government of Canada invests up to $1.98 million to develop sustainable fertilizer technology to reduce emissions and microplastics</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>sg.finance.yahoo.com</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/vivosim-labs-unveils-namkind-drug-120500630.html</t>
+          <t>https://sg.finance.yahoo.com/news/government-canada-invests-1-98-163400092.html</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>16-09-2026 12:05 UTC</t>
+          <t>16-09-2026 16:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Government of Canada invests up to $1.98 million to develop sustainable fertilizer technology to reduce emissions and microplastics</t>
+          <t>Savory Oral Nutrition Supplement Market</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>sg.finance.yahoo.com</t>
+          <t>Future Market Insights</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/government-canada-invests-1-98-163400092.html</t>
+          <t>https://www.futuremarketinsights.com/reports/savory-oral-nutrition-supplement-market</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>16-09-2026 16:34 UTC</t>
+          <t>17-09-2026 12:17 UTC</t>
         </is>
       </c>
     </row>
@@ -4379,22 +4378,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Vishal Sikka's Hang Ten Systems Raises $53M Just Five Weeks After Seed Round</t>
+          <t>Hang Ten Systems Raises Another $53 Million in Seed Funding</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BBN Times</t>
+          <t>Equitypandit</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://www.bbntimes.com/technology/vishal-sikka-s-hang-ten-systems-raises-53m-just-five-weeks-after-seed-round</t>
+          <t>https://www.equitypandit.com/hang-ten-systems-raises-another-53-million-in-seed-funding/</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>16-09-2026 18:44 UTC</t>
+          <t>17-09-2026 10:58 UTC</t>
         </is>
       </c>
     </row>
@@ -4406,22 +4405,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Former Infosys chief’s AI startup nabs another $53M</t>
+          <t>Fresenius SE &amp; Co. KGaA : Buy rating from UBS</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TechCrunch</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/former-infosys-chiefs-ai-startup-adds-50m-to-seed-weeks-after-initial-raise/</t>
+          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-buy-rating-from-ubs-ce785bd3da81f421</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>16-09-2026 13:00 UTC</t>
+          <t>17-09-2026 11:13 UTC</t>
         </is>
       </c>
     </row>
@@ -4433,49 +4432,49 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA : Barclays reaffirms its Buy rating</t>
+          <t>Vishal Sikka's Hang Ten Systems Raises $53M Just Five Weeks After Seed Round</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>bbntimes.com</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-barclays-reaffirms-its-buy-rating-ce785bd2dc88f726</t>
+          <t>https://www.bbntimes.com/technology/vishal-sikka-s-hang-ten-systems-raises-53m-just-five-weeks-after-seed-round</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>16-09-2026 12:09 UTC</t>
+          <t>16-09-2026 18:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SK Hynix reportedly in talks with Intel to build memory chips in US</t>
+          <t>Upperton Gains MHRA Approval for Nottingham Sterile Manufacturing Site</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TechCrunch</t>
+          <t>contractpharma.com</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/sk-hynix-reportedly-in-talks-with-intel-to-build-memory-chips-in-us/</t>
+          <t>https://www.contractpharma.com/breaking-news/upperton-gains-mhra-approval-for-nottingham-sterile-manufacturing-site/</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>16-09-2026 13:23 UTC</t>
+          <t>17-09-2026 13:41 UTC</t>
         </is>
       </c>
     </row>
@@ -4514,22 +4513,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals, SPIMACO Bio Ink MENA Biosimilars Deal</t>
+          <t>South Korea shares rise as Fed rate hike eases uncertainty</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Business Recorder</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/shilpa-biologicals-spimaco-bio-ink-mena-biosimilars-deal/</t>
+          <t>https://www.brecorder.com/news/amp/40439930</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>16-09-2026 13:24 UTC</t>
+          <t>17-09-2026 06:44 UTC</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4545,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>디지털투데이</t>
+          <t>digitaltoday.co.kr</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4649,22 +4648,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Sanofi, UCB, Opella Join Clean Heat Program</t>
+          <t>[Opening Market] KOSPI Opens 0.9% Higher As Fed Uncertainty Eases</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/sanofi-ucb-opella-join-clean-heat-program/</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277168</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>16-09-2026 12:55 UTC</t>
+          <t>17-09-2026 02:19 UTC</t>
         </is>
       </c>
     </row>
@@ -4676,22 +4675,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Corrugated Vial Shipping Trays Market Forecast to 2035: Biologics Demand Drives Expansion - News and Statistics</t>
+          <t>Samsung Electronics, SK Hynix Rally Alongside U.S. Semiconductor Rebound</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/corrugated-vial-shipping-trays-market-to-accelerate-on-biologics-demand-reaching-2035-growth/</t>
+          <t>https://finance.biggo.com/news/3813f228-d1ad-486f-b0ad-7dd522d8db96</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>16-09-2026 13:31 UTC</t>
+          <t>17-09-2026 01:26 UTC</t>
         </is>
       </c>
     </row>
@@ -4703,22 +4702,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>[Opening Market] KOSPI Opens 0.9% Higher As Fed Uncertainty Eases</t>
+          <t>Won-dollar exchange rate fluctuates in upper 1,370s</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277168</t>
+          <t>https://mbiz.heraldcorp.com/article/10877041</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>17-09-2026 02:19 UTC</t>
+          <t>17-09-2026 04:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4729,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Won-dollar exchange rate fluctuates in upper 1,370s</t>
+          <t>US Federal Reserve raises benchmark interest rate by 0.25 percentage point</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4740,12 +4739,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://mbiz.heraldcorp.com/article/10877041</t>
+          <t>https://mbiz.heraldcorp.com/article/10876127</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>17-09-2026 04:01 UTC</t>
+          <t>16-09-2026 18:02 UTC</t>
         </is>
       </c>
     </row>
@@ -4757,22 +4756,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Samsung Electronics, SK Hynix Rally Alongside U.S. Semiconductor Rebound</t>
+          <t>Special prosecutor raids National Election Commission headquarters, 8 other sites</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/3813f228-d1ad-486f-b0ad-7dd522d8db96</t>
+          <t>https://mbiz.heraldcorp.com/article/10876510</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>17-09-2026 01:26 UTC</t>
+          <t>17-09-2026 00:33 UTC</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4783,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Special prosecutor raids National Election Commission headquarters, 8 other sites</t>
+          <t>Han River Bus marks first anniversary of service</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4794,12 +4793,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://mbiz.heraldcorp.com/article/10876510</t>
+          <t>https://mbiz.heraldcorp.com/article/10877045</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>17-09-2026 00:33 UTC</t>
+          <t>17-09-2026 04:01 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,157 +463,157 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
+          <t>Sandoz Gets Canada Approval for Generic Version of Ozempic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>thepharmaletter.com</t>
+          <t>WSJ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
+          <t>https://www.wsj.com/health/pharma/sandoz-gets-canada-approval-for-generic-version-of-ozempic-8f8dce3c</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17-09-2026 12:50 UTC</t>
+          <t>18-09-2026 05:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim launches PED Essentials, an online learning resource that gives patients a stronger voice</t>
+          <t>Sandoz approved for semaglutide sales in Canada</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>biospace.com</t>
+          <t>medwatch.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/boehringer-ingelheim-launches-ped-essentials-an-online-learning-resource-that-gives-patients-a-stronger-voice</t>
+          <t>https://medwatch.com/News/Pharma___Biotech/article19655814.ece</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17-09-2026 09:39 UTC</t>
+          <t>18-09-2026 07:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boehringer launches hub for patient experience data</t>
+          <t>Sandoz's Type-2 Diabetes Therapy Semaglutide Wins Approval in Canada</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pharmaphorum.com</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pharmaphorum.com/news/boehringer-launches-hub-patient-experience-data</t>
+          <t>https://www.marketscreener.com/news/sandoz-s-type-2-diabetes-therapy-semaglutide-wins-approval-in-canada-ce785adad98af026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17-09-2026 09:54 UTC</t>
+          <t>18-09-2026 05:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boehringer ends late-stage kidney disease study of Jardiance combo</t>
+          <t>Sandoz joins mAbxience to develop emicizumab biosimilar and expand haemophilia pipeline</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7998608</t>
+          <t>https://www.tipranks.com/news/company-announcements/sandoz-joins-mabxience-to-develop-emicizumab-biosimilar-and-expand-haemophilia-pipeline</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16-09-2026 22:04 UTC</t>
+          <t>18-09-2026 05:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boehringer halts Phase III kidney trial of vicadrostat/Jardiance combination</t>
+          <t>Sandoz Wins Canadian Approval for Generic Semaglutide, Targeting Growing GLP-1 Market</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>thepharmaletter.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/boehringer-halts-phase-iii-kidney-trial-of-vicadrostat-jardiance-combination</t>
+          <t>https://www.tipranks.com/news/company-announcements/sandoz-wins-canadian-approval-for-generic-semaglutide-targeting-growing-glp-1-market</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17-09-2026 08:57 UTC</t>
+          <t>18-09-2026 05:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Paper + Spark adds seven new clients as it’s named agency of the year at 2026 AMI Awards</t>
+          <t>Jensen Huang (Nvidia)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Campaign Brief</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://campaignbrief.com/paper-spark-adds-seven-new-clients-as-its-named-agency-of-the-year-at-2026-ami-awards/</t>
+          <t>https://en.ilsole24ore.com/art/jensen-huang-nvidia-AJuKjKGB</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17-09-2026 10:02 UTC</t>
+          <t>17-09-2026 18:27 UTC</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lilly backs Circle's latest fundraise as second cancer drug nears clinic</t>
+          <t>Boehringer Ingelheim launches PED Essentials for patient data collection</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7996747</t>
+          <t>https://www.clinicaltrialvanguard.com/news/boehringer-ingelheim-launches-ped-essentials-for-patient-data-collection/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16-09-2026 18:23 UTC</t>
+          <t>18-09-2026 06:42 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mayor Nancy expands employment opportunities in Makati</t>
+          <t>Siemens Healthineers, Boehringer team up on blood-based liver screening</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.manilatimes.net/2026/09/17/tmt-newswire/mayor-nancy-expands-employment-opportunities-in-makati/2427182/amp</t>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33245</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17-09-2026 03:34 UTC</t>
+          <t>18-09-2026 07:07 UTC</t>
         </is>
       </c>
     </row>
@@ -679,265 +679,265 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Interstitial Lung Disease Market Poised for Strong Growth Through 2036 with Breakthrough ILD Treatments</t>
+          <t>Boehringer Ingelheim launches PED Essentials, an online learning resource that gives patients a stronger voice</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4633962/interstitial-lung-disease-market-poised-for-strong-growth</t>
+          <t>https://www.biospace.com/press-releases/boehringer-ingelheim-launches-ped-essentials-an-online-learning-resource-that-gives-patients-a-stronger-voice</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17-09-2026 05:29 UTC</t>
+          <t>17-09-2026 09:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Weapons plan principles to be announced in early October, Hikma spox says</t>
+          <t>Boehringer launches hub for patient experience data</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>964media</t>
+          <t>pharmaphorum</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://en.964media.com/52693/</t>
+          <t>https://pharmaphorum.com/news/boehringer-launches-hub-patient-experience-data</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17-09-2026 07:07 UTC</t>
+          <t>17-09-2026 09:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DLCA Sues Eight Pharmaceutical Companies, Alleging Opioid Monitoring Failures and Misleading Marketing</t>
+          <t>Boehringer halts Phase III kidney trial of vicadrostat/Jardiance combination</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The Virgin Islands Consortium</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://viconsortium.com/vi-legal/virgin-islands-dlca-sues-eight-pharmaceutical-companies--alleging-opioid-monitoring-failures-and-misleading-marketing</t>
+          <t>https://www.thepharmaletter.com/pharma-news/boehringer-halts-phase-iii-kidney-trial-of-vicadrostat-jardiance-combination</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17-09-2026 10:34 UTC</t>
+          <t>17-09-2026 08:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
+          <t>Spot CKD: A Moment That Shouldn’t Be Missed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>thepharmaletter.com</t>
+          <t>CSRwire</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
+          <t>https://csrwire.com/press-release/spot-ckd-moment-shouldnt-be-missed/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17-09-2026 12:50 UTC</t>
+          <t>17-09-2026 20:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BMS, Ono sue to protect Opdivo from Amgen biosimilar</t>
+          <t>Certara Launches External Data Accelerator for CDISC Standards Compliance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7998630</t>
+          <t>https://www.clinicaltrialvanguard.com/news/certara-launches-external-data-accelerator-for-cdisc-standards-compliance/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16-09-2026 22:04 UTC</t>
+          <t>18-09-2026 06:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>From the Financial Crisis to the 2022 Bear Market, How Does Amgen Demonstrate Resilience?</t>
+          <t>Paper + Spark adds seven new clients as it’s named agency of the year at 2026 AMI Awards</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NAI500</t>
+          <t>Campaign Brief</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nai500.com/blog/2026/09/from-the-financial-crisis-to-the-2022-bear-market-how-does-amgen-demonstrate-resilience/</t>
+          <t>https://campaignbrief.com/paper-spark-adds-seven-new-clients-as-its-named-agency-of-the-year-at-2026-ami-awards/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17-09-2026 07:10 UTC</t>
+          <t>17-09-2026 10:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amgen hit with lawsuit over its proposed Opdivo biosimilar</t>
+          <t>SkinCure Analysis: Nonmelanoma Skin Cancer Cases 42% Higher Than Official Count</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Life Sciences IP Review</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.lifesciencesipreview.com/biotech/amgen-hit-with-lawsuit-over-its-proposed-opdivo-biosimilar</t>
+          <t>https://www.clinicaltrialvanguard.com/news/skincure-analysis-nonmelanoma-skin-cancer-cases-42-higher-than-official-count/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16-09-2026 21:23 UTC</t>
+          <t>18-09-2026 06:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amgen Confident In Cardiometabolic Pipeline After Novartis’s Negative Lp(a) Readout</t>
+          <t>Generic drugs get a legal boost from Supreme Court ruling, law firm analysis finds</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/scrip/therapeutic-category/cardiovascular/amgen-confident-in-cardiometabolic-pipeline-after-novartiss-negative-lpa-readout-44IU5KUHR5GCVH5BZWKTKT6WXU/</t>
+          <t>https://www.medicaleconomics.com/view/generic-drugs-get-a-legal-boost-from-supreme-court-ruling-law-firm-analysis-finds</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16-09-2026 22:14 UTC</t>
+          <t>17-09-2026 18:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bristol-Myers Looks To Block Amgen's Cancer Biosimilar</t>
+          <t>Senate Hearing Targets U.S. Generic Drug Manufacturing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>Legis1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.law360.com/ip/articles/2525837/bristol-myers-looks-to-block-amgen-s-cancer-biosimilar-</t>
+          <t>https://legis1.com/news/generic-drug-manufacturing-senate-panel-will</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16-09-2026 19:44 UTC</t>
+          <t>17-09-2026 18:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amgen's Resilience Amid Economic Turbulence</t>
+          <t>DLCA Sues Eight Pharmaceutical Companies, Alleging Opioid Monitoring Failures and Misleading Marketing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Intellectia AI</t>
+          <t>The Virgin Islands Consortium</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://intellectia.ai/news/stock/amgens-resilience-amid-economic-turbulence</t>
+          <t>https://viconsortium.com/vi-legal/virgin-islands-dlca-sues-eight-pharmaceutical-companies--alleging-opioid-monitoring-failures-and-misleading-marketing</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16-09-2026 19:54 UTC</t>
+          <t>17-09-2026 10:34 UTC</t>
         </is>
       </c>
     </row>
@@ -949,292 +949,292 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2027 Irish Opens Locked In as K Club and Dún Laoghaire Take Centre Stage</t>
+          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sport for Business</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://sportforbusiness.com/2027-irish-opens-locked-in-as-k-club-and-dun-laoghaire-take-centre-stage/</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17-09-2026 08:41 UTC</t>
+          <t>17-09-2026 12:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amneal expands India operations after Kashiv buy, builds biosimilars portfolio</t>
+          <t>Never Too Late (or Too Early) for Lipid Lowering: STAREE and REACT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Medscape</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/amp/latest/corporate/story/amneal-expands-india-operations-after-kashiv-buy-builds-biosimilars-portfolio-556089-2026-09-17</t>
+          <t>https://www.medscape.com/viewarticle/never-too-late-or-too-early-lipid-lowering-staree-and-react-2026a1000y8u</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17-09-2026 07:02 UTC</t>
+          <t>17-09-2026 18:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Organon Backs Women’s Health Efforts Across India</t>
+          <t>FDA-ordered studies of many drugs, devices on the market are not done</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pharmacy Business</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pharmacy.biz/organon-womens-health-support-india/</t>
+          <t>https://www.washingtonpost.com/health/2026/09/17/fda-ordered-studies-many-drugs-devices-market-are-not-done/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17-09-2026 13:36 UTC</t>
+          <t>17-09-2026 16:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Organon backs women’s health programmes in Bihar and Uttar Pradesh</t>
+          <t>FDA Reduces Monitoring Time for First Two Tarlatamab Doses</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Pharmacy Times</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/healthcare/organon-backs-womens-health-programmes-in-bihar-and-uttar-pradesh-21886</t>
+          <t>https://www.pharmacytimes.com/view/fda-reduces-monitoring-time-for-first-two-tarlatamab-doses</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17-09-2026 04:25 UTC</t>
+          <t>17-09-2026 17:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PhaseV Adds Klaus Beck and Avi Kulkarni to Scientific Advisory Board</t>
+          <t>The top life sciences firms in Mass. employ more people than last year</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>citybiz</t>
+          <t>The Business Journals</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.citybiz.co/article/904492/phasev-adds-klaus-beck-and-avi-kulkarni-to-scientific-advisory-board/</t>
+          <t>https://www.bizjournals.com/boston/research/lists/2026/largest-life-sciences-companies-in-massachusetts.html</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16-09-2026 20:04 UTC</t>
+          <t>17-09-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Why Allison launched Allison Worldwide Health Group</t>
+          <t>Ticket registration opens for Amgen Irish Open at K Club 2027</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PRWeek</t>
+          <t>Kildare Live</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.prweek.com/article/1970220/why-allison-launched-allison-worldwide-health-group</t>
+          <t>https://www.leinsterleader.ie/sport/ticket-registration-opens-for-amgen-irish-open-at-k-club-2027-9078090</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16-09-2026 20:18 UTC</t>
+          <t>17-09-2026 16:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Organon Announces Two Her Health Grants In India To Support Adolescent Girls' Health In Bihar And Women's Contraceptive Access In Uttar Pradesh</t>
+          <t>New taxes crucial to preserve EU budget, says Irish PM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>menafn.com</t>
+          <t>politico.eu</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://menafn.com/1111677524/Organon-Announces-Two-Her-Health-Grants-In-India-To-Support-Adolescent-Girls-Health-In-Bihar-And-Womens-Contraceptive-Access-In-Uttar-Pradesh</t>
+          <t>https://www.politico.eu/article/new-eu-taxes-crucial-to-preserve-budget-says-irish-pm-micheal-martin/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17-09-2026 06:25 UTC</t>
+          <t>17-09-2026 14:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tyre Pyrolysis Plant Setup in India: Feasibility Report</t>
+          <t>COMMENT: Shane Lowry's Amgen Irish Open win lifts all our hearts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IMARC Group</t>
+          <t>Offaly Live</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.imarcgroup.com/insight/tyre-pyrolysis-plant-setup-india</t>
+          <t>https://www.offalyexpress.ie/news/opinion/comment-shane-lowrys-amgen-irish-open-win-lifts-all-our-hearts-9074549</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17-09-2026 07:51 UTC</t>
+          <t>17-09-2026 20:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EnergyPathways &amp; Hycamite Hydrogen Graphite Plant UK</t>
+          <t>Organon Announces Two Her Health Grants in India to Support Adolescent Girls Health in Bihar and Womens Contraceptive Access in Uttar Pradesh</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fuel Cells Works</t>
+          <t>The Tribune</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://fuelcellsworks.com/2026/09/17/h2/energypathways-and-hycamite-to-advance-hydrogen-and-graphite-production-plant-in-uk</t>
+          <t>https://www.tribuneindia.com/news/business/organon-announces-two-her-health-grants-in-india-to-support-adolescent-girls-health-in-bihar-and-womens-contraceptive-access-in-uttar-pradesh/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17-09-2026 12:58 UTC</t>
+          <t>18-09-2026 07:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Ghosts of Chernobyl</t>
+          <t>Organon Backs Women’s Health Efforts Across India</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Telos-eu.</t>
+          <t>Pharmacy Business</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>http://www.telos-eu.com/en/the-ghosts-of-chernobyl.html</t>
+          <t>https://www.pharmacy.biz/organon-womens-health-support-india/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17-09-2026 15:01 UTC</t>
+          <t>17-09-2026 13:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Do Plant Proteins Increase Uric Acid? Expert Weighs In</t>
+          <t>Sandoz approved for semaglutide sales in Canada</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Onlymyhealth</t>
+          <t>medwatch.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.onlymyhealth.com/can-plant-protein-increase-your-uric-acid-levels-expert-explains-12977850410</t>
+          <t>https://medwatch.com/News/Pharma___Biotech/article19655814.ece</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17-09-2026 13:31 UTC</t>
+          <t>18-09-2026 07:05 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dry Fungi Mycoproteins Market Size, Share &amp; Forecast 2036</t>
+          <t>SK On, L&amp;F Form LFP Supply Alliance Against China</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fact.MR</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.factmr.com/report/dry-fungi-mycoproteins-market</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277288</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17-09-2026 07:11 UTC</t>
+          <t>18-09-2026 03:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ghana’s Genser moves further downstream with natural gas liquids plant</t>
+          <t>Holiday on September 18, 2026 — Bamboo Day: Interesting Facts About This Unusual Plant</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>africa-energy.com</t>
+          <t>UA.NEWS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.africa-energy.com/news-centre/article/ghanas-genser-moves-further-downstream-natural-gas-liquids-plant</t>
+          <t>https://ua.news/en/world/sviato-18-veresnia-den-bambuka-tsikavi-fakti-pro-nezvichainu-roslinu</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17-09-2026 10:54 UTC</t>
+          <t>18-09-2026 06:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Premier Energies to Form JV for 12 GWh BESS Facility</t>
+          <t>PhytoFoundry emerges from stealth with plant cell culture platform targeting high value bioactives</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Construction World</t>
+          <t>AgFunderNews</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/energy-infrastructure/power-and-renewable-energy/premier-energies-to-form-jv-for-12-gwh-bess-facility/97510</t>
+          <t>https://agfundernews.com/phytofoundry-targets-cosmetics-with-plant-cell-culture-platform-shaped-by-past-lessons</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17-09-2026 07:34 UTC</t>
+          <t>17-09-2026 16:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Foliar fertilization: Precision starts with application conditions</t>
+          <t>EnergyPathways &amp; Hycamite Hydrogen Graphite Plant UK</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hortidaily</t>
+          <t>Fuel Cells Works</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.hortidaily.com/article/9874133/foliar-fertilization-precision-starts-with-application-conditions/</t>
+          <t>https://fuelcellsworks.com/2026/09/17/h2/energypathways-and-hycamite-to-advance-hydrogen-and-graphite-production-plant-in-uk</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17-09-2026 12:32 UTC</t>
+          <t>17-09-2026 12:58 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>"After seeing the excitement in Europe, we are thrilled to bring these hydrangeas to the U.S."</t>
+          <t>The Ghosts of Chernobyl</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FloralDaily</t>
+          <t>Telos-eu.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.floraldaily.com/article/9873937/after-seeing-the-excitement-in-europe-we-are-thrilled-to-bring-these-hydrangeas-to-the-u-s/</t>
+          <t>http://www.telos-eu.com/en/the-ghosts-of-chernobyl.html</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17-09-2026 13:01 UTC</t>
+          <t>17-09-2026 15:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21,000 living plants shape Ganesh idol with a green message in Andhra Pradesh</t>
+          <t>Do Plant Proteins Increase Uric Acid? Expert Weighs In</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Onlymyhealth</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/21000-living-plants-turn-ganesh-idol-into-a-green-message-in-anakapalli-2996395-2026-09-17</t>
+          <t>https://www.onlymyhealth.com/can-plant-protein-increase-your-uric-acid-levels-expert-explains-12977850410</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16-09-2026 20:47 UTC</t>
+          <t>17-09-2026 13:31 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>This coal plant won Basin Electric’s reliability trophy, but it doesn’t plan to return it.</t>
+          <t>10 Flowering Bulbs to Plant in September—Before the Ground Gets Too Cold</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>power-eng.com</t>
+          <t>veranda.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.power-eng.com/coal/this-coal-plant-won-basin-electrics-reliability-trophy-but-it-doesnt-plan-to-return-it/</t>
+          <t>https://www.veranda.com/outdoor-garden/a73779126/bulbs-to-plant-september-before-ground-gets-too-cold/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17-09-2026 14:43 UTC</t>
+          <t>17-09-2026 21:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Without bacteria or chemicals: How methanol and formaldehyde form abiotically in nature</t>
+          <t>Tyre Pyrolysis Plant Setup in India: Feasibility Report</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phys.org</t>
+          <t>IMARC Group</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://phys.org/news/2026-09-bacteria-chemicals-methanol-formaldehyde-abiotically.html</t>
+          <t>https://www.imarcgroup.com/insight/tyre-pyrolysis-plant-setup-india</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16-09-2026 19:30 UTC</t>
+          <t>17-09-2026 07:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Xanthate Flotation Collectors Market</t>
+          <t>Wacker Chemie disappointed by US polysilicon policy, sets new goals</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Future Market Insights</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.futuremarketinsights.com/reports/xanthate-flotation-collectors-market</t>
+          <t>https://www.reuters.com/business/wacker-chemie-disappointed-by-us-polysilicon-policy-sets-new-goals-2026-09-17/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16-09-2026 18:30 UTC</t>
+          <t>17-09-2026 15:42 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,130 +1489,130 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Microplastics in soil pose global threat by acting like ‘Trojan horse’ to deliver toxins</t>
+          <t>FORM NO. 169 EDITABLE WORD FORMAT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>The Guardian</t>
+          <t>ctn press</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/environment/2026/sep/16/soil-microplastics-trojan-horse-toxins</t>
+          <t>https://cevnews.in/2026/09/income-tax-department-extends-important-deadlines-up-to-31-march-2027/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>17-09-2026 01:30 UTC</t>
+          <t>18-09-2026 04:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Head and Neck Cancer Pipeline Gains Momentum: 80+ Companies Lead the Charge in Pioneering New Treatments | DelveInsight</t>
+          <t>Planting Green Roofs for Biophilic Effects</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Barchart.com</t>
+          <t>Living Architecture Monitor</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.barchart.com/press-releases/4646128/head-and-neck-cancer-pipeline-gains-momentum-80-companies-lead-the-charge-in-pioneering-new-treatments-delveinsight</t>
+          <t>https://livingarchitecturemonitor.com/articles/planting-green-roofs-for-biophilic-effects</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16-09-2026 23:46 UTC</t>
+          <t>17-09-2026 09:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Is Pfizer’s New Business Big Enough To Carry The Old One?</t>
+          <t>Clove at first bite</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Trefis</t>
+          <t>Kirksville Daily Express</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.trefis.com/stock/pfe/articles/615508/is-pfizers-new-business-big-enough-to-carry-the-old-one/2026-09-16</t>
+          <t>http://www.kirksvilledailyexpress.com/stories/clove-at-first-bite,32741</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16-09-2026 20:11 UTC</t>
+          <t>17-09-2026 21:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bavarian Nordic names Tarja Stenvall as new CEO</t>
+          <t>McLaren Confirms First SUV, Second UK Factory and In-House Engines</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Endpoints News</t>
+          <t>Autocar Professional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://endpoints.news/bavarian-nordic-names-tarja-stenvall-as-new-ceo/</t>
+          <t>https://www.autocarpro.in/news/mclaren-confirms-first-suv-second-uk-factory-and-in-house-engines-134777</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17-09-2026 11:15 UTC</t>
+          <t>17-09-2026 13:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pharma sector doubles down on AI to slash costs, timelines</t>
+          <t>Plant Development Services to bring two new hydrangea brands to North American consumers in 2027</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>nurserymag.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/pharma-sector-doubles-down-ai-amid-hopes-slashing-costs-timelines-2026-09-16/</t>
+          <t>https://www.nurserymag.com/news/plant-development-services-two-new-hydrangea-brands-north-american-consumers-2027/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>16-09-2026 20:42 UTC</t>
+          <t>17-09-2026 15:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pfizer Raises 2026 Revenue Guidance to $62 Billion. Here’s What’s Behind the Beat</t>
+          <t>Behind the Science: Reprogramming Resistance to Prostate Cancer Treatment</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TIKR.com</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.tikr.com/blog/pfizer-raises-2026-revenue-guidance-to-62-billion-heres-whats-behind-the-beat</t>
+          <t>https://www.pfizer.com/news/articles/behind_the_science_reprogramming_resistance_to_prostate_cancer_treatment</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>16-09-2026 22:11 UTC</t>
+          <t>17-09-2026 16:35 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fire Breaks Out At Pfizer Facility In Andover</t>
+          <t>A year ago, President Trump pledged to lower Medicaid drug prices. Has that happened?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>andovermanews.com</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://andovermanews.com/fire-breaks-out-at-pfizer-facility-in-andover/</t>
+          <t>https://www.npr.org/2026/09/17/nx-s1-5971066/trump-rx-medicaid-generous-drug-prices-pfizer-favored-nation</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17-09-2026 13:50 UTC</t>
+          <t>17-09-2026 16:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1678,22 +1678,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What is Pfizer rStock | How RPFE Works, Use Cases and Values | MEXC</t>
+          <t>Pfizer, BioNTech Secure Health Canada Authorization for Omicron XFG-Adapted COVID-19 Vaccine</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MEXC</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.mexc.co/en-PH/price/pfizer-rstock/info</t>
+          <t>https://www.marketscreener.com/news/pfizer-biontech-secure-health-canada-authorization-for-omicron-xfg-adapted-covid-19-vaccine-ce785bd3de8cf62c</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>17-09-2026 00:00 UTC</t>
+          <t>17-09-2026 19:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1705,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bavarian Nordic names new CEO</t>
+          <t>Health Canada Authorizes Pfizer and BioNTech's Omicron XFG-Adapted COVID-19 Vaccine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>medwatch.com</t>
+          <t>PR Newswire Canada</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://medwatch.com/News/Pharma___Biotech/article19651697.ece</t>
+          <t>https://www.newswire.ca/news-releases/health-canada-authorizes-pfizer-and-biontech-s-omicron-xfg-adapted-covid-19-vaccine-854410179.html</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17-09-2026 08:59 UTC</t>
+          <t>17-09-2026 17:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1732,22 +1732,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alteogen Files Patent for Once-Monthly Obesity Drug Technology; Preclinical Results Due in November</t>
+          <t>Full Fed. Circ. Won't Rethink Pfizer's Paxlovid IP Win</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/6b592b49-bff8-4b09-bd35-a65185b3eb83</t>
+          <t>https://www.law360.com/articles/2526734/full-fed-circ-won-t-rethink-pfizer-s-paxlovid-ip-win</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>17-09-2026 01:26 UTC</t>
+          <t>17-09-2026 22:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1759,265 +1759,265 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Covid Vaccines Delayed for Half of U.S. Children</t>
+          <t>Health Canada Authorizes Pfizer and BioNTech's Omicron XFG-Adapted COVID-19 Vaccine</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>The Globe and Mail</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com/2026/09/16/well/covid-vaccines-vfc-program-delay.html</t>
+          <t>https://www.theglobeandmail.com/investing/markets/stocks/PFE-N/pressreleases/4664673/health-canada-authorizes-pfizer-and-biontech-s-omicron-xfg-adapted-covid-19-vaccine/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16-09-2026 22:51 UTC</t>
+          <t>17-09-2026 17:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Roche sees success in long-awaited confirmatory study of Lunsumio for follicular lymphoma</t>
+          <t>Novo partners with Orbis, deepening investment in oral peptide drugs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>BioPharma Dive</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/8000583</t>
+          <t>https://www.biopharmadive.com/news/novo-orbis-macrocyclic-peptides-oral-obesity-drugs/830645/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17-09-2026 13:39 UTC</t>
+          <t>17-09-2026 19:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Japan approves subcutaneous formulation of LEQEMBI® for treatment of early Alzheimer’s Disease</t>
+          <t>Bavarian Nordic names Tarja Stenvall as new CEO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia</t>
+          <t>Endpoints News</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/30/28386/japan-approves-subcutaneous-formulation-of-leqembi-for-treatment-of-early-alzheimers-disease-.html</t>
+          <t>https://endpoints.news/bavarian-nordic-names-tarja-stenvall-as-new-ceo/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>17-09-2026 07:21 UTC</t>
+          <t>17-09-2026 11:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Midlands TD Insists Skyclarys Must Be Made Available As Soon As Possible</t>
+          <t>Never Too Late (or Too Early) for Lipid Lowering: STAREE and REACT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Midlands 103</t>
+          <t>Medscape</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.midlands103.com/news/midlands-news/midlands-td-insists-skyclarys-must-be-made-available-as-soon-as-possible/</t>
+          <t>https://www.medscape.com/viewarticle/never-too-late-or-too-early-lipid-lowering-staree-and-react-2026a1000y8u?src=</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>17-09-2026 07:23 UTC</t>
+          <t>17-09-2026 18:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BREAKING – Petition which could help FA sisters reaches 100,000 signatures</t>
+          <t>Bavarian Nordic secures Sanofi, AZ vet to fill shoes of longtime CEO Paul Chaplin</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>The Redditch Standard</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://redditchstandard.co.uk/news/breaking-petition-which-could-help-fa-sisters-reaches-100000-signatures/</t>
+          <t>https://www.fiercepharma.com/pharma/bavarian-nordic-secures-sanofi-az-vet-fill-shoes-longtime-ceo-paul-chaplin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>16-09-2026 23:51 UTC</t>
+          <t>17-09-2026 15:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dr Reddy's Enters Royalty-Free Agreement With Gilead For Annual Lenacapavir HIV Prevention</t>
+          <t>Phase 3 Pediatric EMPAVELI Data Published in Clinical Journal of the American Society of Nephrology Show Reduction in Proteinuria and Stabilized Kidney Function in Adolescents with C3G or Primary IC-MPGN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sahi.com</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/dr-reddy-s-enters-royalty-free-agreement-with-gilead-for-annual-lenacapavir-hiv-prevention</t>
+          <t>https://investors.biogen.com/news-releases/news-release-details/phase-3-pediatric-empaveli-data-published-clinical-journal</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17-09-2026 10:22 UTC</t>
+          <t>17-09-2026 20:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dr Reddy’s inks licensing deal with Gilead for once-yearly HIV lenacapavir</t>
+          <t>BIIB Looks 11.6% Overvalued on GF Value™</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/dr-reddys-inks-licensing-deal-with-gilead-for-once-yearly-hiv-lenacapavir/articleshow/134313710.cms</t>
+          <t>https://www.gurufocus.com/news/9086835/biib-looks-116-overvalued-on-gf-value</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17-09-2026 13:34 UTC</t>
+          <t>17-09-2026 21:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dr Reddy's &amp; Gilead Pact for Once-Yearly HIV Prevention Drug</t>
+          <t>Roche's Lunsumio succeeds in long-awaited confirmatory follicular lymphoma study</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/dr-reddy-s-gilead-pact-for-once-yearly-hiv-prevention-drug/54482920260917</t>
+          <t>https://firstwordpharma.com/story/8000583</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>17-09-2026 08:25 UTC</t>
+          <t>17-09-2026 19:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dr Reddy's signs royalty-free license with Gilead for lenacapavir</t>
+          <t>The top life sciences firms in Mass. employ more people than last year</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>The Business Journals</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-enters-royalty-free-license-gilead-lenacapavir/51185185</t>
+          <t>https://www.bizjournals.com/boston/research/lists/2026/largest-life-sciences-companies-in-massachusetts.html</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17-09-2026 10:12 UTC</t>
+          <t>17-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s expands Gilead pact for HIV prevention drug</t>
+          <t>SK Biopharm takes 1st Bio’s LRRK2/c-Abl inhibitor in $315M deal</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>BioWorld News</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/dr-reddys-expands-pact-with-gilead-for-investigational-hiv-prevention-drug/article71475705.ece/amp/</t>
+          <t>https://www.bioworld.com/articles/734140-sk-biopharm-takes-1st-bios-lrrk2-c-abl-inhibitor-in-315m-deal</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>17-09-2026 07:35 UTC</t>
+          <t>17-09-2026 16:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,22 +2029,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dr. Nischal Shashidhar appointed AGM – Medical Affairs at Biological E.</t>
+          <t>Dr Reddy's signs India distribution deal for Takeda's Qdenga dengue vaccine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/biopharma/dr-nischal-shashidhar-appointed-agm-medical-affairs-at-biological-e-21890</t>
+          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/indias-dr-reddys-inks-distribution-agreement-with-takeda-dengue-vaccine-india-2026-09-18/</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17-09-2026 11:47 UTC</t>
+          <t>18-09-2026 03:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2056,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dr Reddy's Q1FY27 Results: Revenue falls 5.6%, margins hit by semaglutide</t>
+          <t>Dr Reddy’s to distribute Takeda’s QDENGA dengue vaccine in India</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Telangana Today</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-q1fy27-results-revenue-falls-5-6-margins-hit-semaglutide/51177311</t>
+          <t>https://telanganatoday.com/dr-reddys-to-distribute-takedas-qdenga-dengue-vaccine-in-india</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17-09-2026 08:18 UTC</t>
+          <t>18-09-2026 07:16 UTC</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dr Reddy's inks pact with Gilead for once-yearly HIV prevention drug lenacapavir</t>
+          <t>Dr. Reddy's Labs Agrees To Licensing Deal With Gilead For Once-Yearly Lenacapavir To Prevent HIV</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ET Manufacturing</t>
+          <t>Sahi</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://manufacturing.economictimes.indiatimes.com/amp/news/life-sciences/dr-reddys-inks-pact-with-gilead-for-once-yearly-hiv-prevention-drug-lenacapavir/134307526</t>
+          <t>https://www.sahi.com/news/dr-reddy-s-labs-agrees-to-licensing-deal-with-gilead-for-once-yearly-lenacapavir-to-prevent-hiv</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>17-09-2026 09:40 UTC</t>
+          <t>18-09-2026 03:38 UTC</t>
         </is>
       </c>
     </row>
@@ -2110,22 +2110,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dr. Reddy's faces fifth US securities probe after semaglutide hit</t>
+          <t>Dr Reddy's shares rise 2% after exclusive Qdenga distribution deal with Takeda</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-under-probe-2-4bn-semaglutide-provision-hits-stock/48211614</t>
+          <t>https://www.businesstoday.in/markets/stocks/story/dr-reddys-shares-rise-2-after-exclusive-qdenga-distribution-deal-with-takeda-556331-2026-09-18</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17-09-2026 00:23 UTC</t>
+          <t>18-09-2026 05:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2137,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Top gainers and losers, September 17: HDFC LIC jumps 5%, TMPV rises 4%, ONGC falls 2%; check list</t>
+          <t>Dr Reddy's, Takeda Partner for India's First Dengue Vaccine</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://upstox.com/news/market-news/stocks/top-gainers-and-losers-september-17-hdfc-lic-jumps-5-tmpv-rises-4-ongc-falls-2-check-list/article-200446/</t>
+          <t>https://money.rediff.com/news/market/dr-reddy-s-takeda-partner-for-india-s-first-dengue-vaccine/54548120260918</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>17-09-2026 10:55 UTC</t>
+          <t>18-09-2026 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2164,319 +2164,319 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Top Gainers &amp; Losers, September 17, 2026 at 12:00 PM IST: HDFC Life Leads Gainers</t>
+          <t>Takeda and Dr Reddy’s to distribute QDENGA dengue vaccine in India</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>The News Mill</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://hdfcsky.com/news/top-gainers-losers-september-17-2026-at-12-pm</t>
+          <t>https://thenewsmill.com/2026/09/takeda-and-dr-reddys-to-distribute-qdenga-dengue-vaccine-in-india/</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>17-09-2026 07:02 UTC</t>
+          <t>18-09-2026 07:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Harsh Goenka, Kiran Mazumdar-Shaw criticise Fendi’s Rs 8.3 lakh ‘Navratri’ bag</t>
+          <t>Dr Reddy’s Shares Rise on Takeda Dengue Vaccine Deal</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>Equitypandit</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/trending/trending-in-india/fendi-rs-8-3-lakh-bag-indian-craftsmanship-debate-kiran-mazumdar-shaw-harsh-goenka-10882436/lite/</t>
+          <t>https://www.equitypandit.com/dr-reddys-shares-rise-on-takeda-dengue-vaccine-deal/</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>17-09-2026 12:24 UTC</t>
+          <t>18-09-2026 06:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>‘When will luxury brands stop colonising Indian crafts?’: H…</t>
+          <t>Dr Reddy's signs India distribution deal for Takeda's Qdenga dengue vaccine, shares rise over 2%</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GujaratSamachar English</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://english.gujaratsamachar.com/news/national/when-will-luxury-brands-stop-colonising-indian-crafts-harsh-goenka-kiran-mazumdar-shaw-slam-fendi-over-indian-rupee95-lakh-navratri-bag-63401233492</t>
+          <t>https://www.moneycontrol.com/news/business/markets/dr-reddy-s-signs-india-distribution-deal-for-takeda-s-qdenga-dengue-vaccine-shares-rise-over-2-14032737.html</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17-09-2026 09:40 UTC</t>
+          <t>18-09-2026 04:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw Calls Out Fendi’s Rs 8.3 Lakh ‘Navratri’ Bag: ‘Undermines Our Authentic Talent’</t>
+          <t>India’s Dr Reddy’s inks distribution agreement with Takeda for dengue vaccine in India</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>pragativadi.com</t>
+          <t>The Mighty 790 KFGO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/kiran-mazumdar-shaw-calls-out-fendis-rs-8-3-lakh-navratri-bag-undermines-our-authentic-talent/</t>
+          <t>https://kfgo.com/2026/09/17/indias-dr-reddys-inks-distribution-agreement-with-takeda-for-dengue-vaccine-in-india/</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>16-09-2026 19:09 UTC</t>
+          <t>18-09-2026 04:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Viatris’ Wakix receives Japanese approval to treat OSAS and narcolepsy</t>
+          <t>Why Did Dr Reddy's Shares Rise Nearly 2% In Trade Today? Key Details Inside</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.yahoo.com/news/science/articles/viatris-wakix-receives-japanese-approval-094045863.html</t>
+          <t>https://www.ndtvprofit.com/markets/dr-reddys-share-price-today-exclusive-distribution-marketing-agreement-takeda-dengue-vaccine-qdenga-12062679</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>17-09-2026 09:40 UTC</t>
+          <t>18-09-2026 04:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FTSE rebalance: Meesho, Lenskart lead inflows; Biocon, Wipro out</t>
+          <t>Dr Reddy’s bags exclusive distribution rights of Takeda’s dengue vaccine QDENGA in India</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.businessupturn.com/finance/stock-market/ftse-september-rebalance-takes-effect-tomorrow-meesho-and-lenskart-lead-inflows-biocon-and-wipro-see-outflows/</t>
+          <t>https://www.thehindubusinessline.com/news/national/dr-reddys-bags-exclusive-distribution-rights-of-takedas-dengue-vaccine-qdenga-in-india/article71479463.ece</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>17-09-2026 10:45 UTC</t>
+          <t>18-09-2026 05:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cultural Appropriation or Collaboration? Fendi’s 'Navratri' Bag With Indian Roots Sparks Debate</t>
+          <t>Dr Reddy's shares gain 2% after Takeda dengue vaccine distribution deal</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Herzindagi</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.herzindagi.com/fashion/cultural-appropriation-or-collaboration-fendi-navratri-bag-with-indian-roots-sparks-debate-article-1069221</t>
+          <t>https://www.cnbctv18.com/market/dr-reddys-share-price-gains-takeda-qdenga-dengue-vaccine-distribution-deal-19993347.htm/amp</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>17-09-2026 07:39 UTC</t>
+          <t>18-09-2026 04:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fendi’s Rs 8 lakh ‘Gujarati mirror work bag’ sparks outrage - The Sentinel</t>
+          <t>BioTecNika Times Newsletter 17-09-2026- ICON plc Internship, ₹1.27 Lakh FSL Jobs, Freshers Openings at Intas &amp; More</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>The Sentinel - of this Land, for its People</t>
+          <t>BioTecNika</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.sentinelassam.com/amp/story/more-news/entertainment/fendis-rs-8-lakh-gujarati-mirror-work-bag-sparks-outrage</t>
+          <t>https://www.biotecnika.org/2026/09/biotecnika-times-newsletter-17-09-2026/</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>17-09-2026 03:19 UTC</t>
+          <t>17-09-2026 13:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Prescription or not? At neighbourhood medical stores, consumers say rules are not always followed</t>
+          <t>Justices Told Fed. Circ. Erred In Veterinary Software Feud</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/Hyderabad/prescription-or-not-at-neighbourhood-medical-stores-consumers-say-rules-are-not-always-followed/article71476915.ece</t>
+          <t>https://www.law360.com/healthcare-authority/digital-health-technology/articles/2526796/justices-told-fed-circ-erred-in-veterinary-software-feud</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>17-09-2026 14:00 UTC</t>
+          <t>18-09-2026 00:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Closing Bell: Market snaps 2-day fall; Sensex up 333 pts, Nifty above 23,200</t>
+          <t>Harsh Goenka, Kiran Mazumdar-Shaw criticise Fendi’s Rs 8.3 lakh ‘Navratri’ bag</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IndiaIPO</t>
+          <t>The Indian Express</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.indiaipo.in/news/detail/closing-bell-market-snaps-2-day-fall-sensex-up-333-pts-nifty-above-23200</t>
+          <t>https://indianexpress.com/article/trending/trending-in-india/fendi-rs-8-3-lakh-bag-indian-craftsmanship-debate-kiran-mazumdar-shaw-harsh-goenka-10882436/lite/</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17-09-2026 08:35 UTC</t>
+          <t>17-09-2026 12:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Novo partners with Anthropic to speed up drug development with Claude</t>
+          <t>‘When will luxury brands stop colonising Indian crafts?’: H…</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>GujaratSamachar English</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/novo-partners-with-anthropic-to-speed-up-drug-development-with-claude/134297461</t>
+          <t>https://english.gujaratsamachar.com/news/national/when-will-luxury-brands-stop-colonising-indian-crafts-harsh-goenka-kiran-mazumdar-shaw-slam-fendi-over-indian-rupee95-lakh-navratri-bag-63401233492</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>17-09-2026 01:48 UTC</t>
+          <t>17-09-2026 09:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Rakovina Therapeutics Announces Appointment of New Scientific Advisory Board Member</t>
+          <t>FTSE rebalance: Meesho, Lenskart lead inflows; Biocon, Wipro out</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/rakovina-therapeutics-announces-appointment-scientific-083000136.html</t>
+          <t>https://businessupturn.com/finance/stock-market/ftse-september-rebalance-takes-effect-tomorrow-meesho-and-lenskart-lead-inflows-biocon-and-wipro-see-outflows/</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>17-09-2026 08:30 UTC</t>
+          <t>17-09-2026 10:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sensex, Nifty trade in positive terrain; pharma shares snap 5-day losing streak</t>
+          <t>USFDA Inspection Ends With 1 Observation at Aurobindo Pharma's Apitoria API Facility</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/markets/capital-market-news/sensex-nifty-trade-in-positive-terrain-pharma-shares-snap-5-day-losing-streak-126091700646_1.html</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/usfda-inspection-ends-with-1-observation-at-aurobindo-pharmas-apitoria-api-facility-179458</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17-09-2026 09:20 UTC</t>
+          <t>17-09-2026 18:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2515,22 +2515,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longeveron explores strategic options after therapy fails mid-stage trial for infant heart condition</t>
+          <t>Aurobindo Pharma (NSE: AUROPHARMA) Receives USFDA Approval for First Inhalation Aerosol Product</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/longeveron-explores-strategic-options-after-therapy-fails-mid-stage-trial-for-infant-heart-condition/134297463</t>
+          <t>https://www.kalkine.co.in/article/healthcare/aurobindo-pharma-nse-auropharma-receives-usfda-approval-for-first-inhalation-aerosol-product</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17-09-2026 01:52 UTC</t>
+          <t>17-09-2026 09:29 UTC</t>
         </is>
       </c>
     </row>
@@ -2542,22 +2542,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Novartis halts ALS drug development after mid-stage trial failure</t>
+          <t>Closing Bell: Market snaps 2-day fall; Sensex up 333 pts, Nifty above 23,200</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>IndiaIPO</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/novartis-halts-als-drug-development-after-mid-stage-trial-failure/134297430</t>
+          <t>https://www.indiaipo.in/news/detail/closing-bell-market-snaps-2-day-fall-sensex-up-333-pts-nifty-above-23200</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17-09-2026 01:53 UTC</t>
+          <t>17-09-2026 08:35 UTC</t>
         </is>
       </c>
     </row>
@@ -2569,22 +2569,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sebi bars two entities over alleged cross-derivatives manipulation</t>
+          <t>Nifty Pharma Today: Up 1.66% to 26,579.25</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/indian-regulator-bars-two-entities-over-alleged-cross-derivatives-manipulation/articleshow/134291762.cms?UTM_Source=Google_Newsstand&amp;UTM_Campaign=RSS_Feed&amp;UTM_Medium=Referral</t>
+          <t>https://univest.in/blogs/nifty-pharma-today-closing-bell-2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>16-09-2026 15:51 UTC</t>
+          <t>17-09-2026 16:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,22 +2596,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bank of India Mid Cap Fund Direct Growth Review 2026: NAV, Returns, Portfolio &amp; Should You Invest?</t>
+          <t>Rakovina Therapeutics Announces Appointment of New Scientific Advisory Board Member</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>sg.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://univest.in/blogs/bank-of-india-mid-cap-fund-direct-growth-review-2026</t>
+          <t>https://sg.finance.yahoo.com/news/rakovina-therapeutics-announces-appointment-scientific-083000136.html</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>17-09-2026 04:46 UTC</t>
+          <t>17-09-2026 08:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2623,103 +2623,103 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Amphetamine + Deaxmphetamine Market to Surpass USD 906.4</t>
+          <t>Alembic Pharma's Vadodara Bioequivalence Facility Gets USFDA Inspection Closure, EIR Issued</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4634064/amphetamine-deaxmphetamine-market-to-surpass-usd-906-4</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/alembic-pharmas-vadodara-bioequivalence-facility-gets-usfda-inspection-closure-eir-issued-179459</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>17-09-2026 06:37 UTC</t>
+          <t>17-09-2026 18:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Charles River Launches Rapid Cell Banking Programs</t>
+          <t>Bulimia Nervosa Market: Steady Growth Amid Rising Diagnosis Rates and a Stagnant Pharmacological Pipeline Through 2036</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>contractpharma.com</t>
+          <t>Barchart.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/charles-river-launches-rapid-cell-banking-programs/</t>
+          <t>https://www.barchart.com/press-releases/4664223/bulimia-nervosa-market-steady-growth-amid-rising-diagnosis-rates-and-a-stagnant-pharmacological-pipeline-through-2036</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>17-09-2026 14:13 UTC</t>
+          <t>17-09-2026 17:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Thermo Fisher Launches SuperScript V Reverse Transcriptase</t>
+          <t>Novartis Drops Experimental Amyotrophic Lateral Sclerosis Drug After Mid-Stage Trial Failure</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>contractpharma.com</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/thermo-fisher-launches-superscript-v-reverse-transcriptase/</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/novartis-drops-experimental-amyotrophic-lateral-sclerosis-drug-after-mid-stage-trial-failure-179455</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>16-09-2026 19:11 UTC</t>
+          <t>17-09-2026 16:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
+          <t>Health Ministry Proposes Schedule K Exemption, Boxed Warnings for Levonorgestrel Pills</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/health-ministry-proposes-schedule-k-exemption-boxed-warnings-for-levonorgestrel-pills-179460</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17-09-2026 12:50 UTC</t>
+          <t>17-09-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -2731,22 +2731,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Upperton Gains MHRA Approval for Nottingham Sterile Manufacturing Site</t>
+          <t>Alkem launches NeuCeno for treatment of partial-onset seizures in adult patients</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>contractpharma.com</t>
+          <t>Express Pharma</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/upperton-gains-mhra-approval-for-nottingham-sterile-manufacturing-site/</t>
+          <t>https://www.expresspharma.in/amp/alkem-launches-neuceno-for-treatment-of-partial-onset-seizures-in-adult-patients/</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17-09-2026 13:41 UTC</t>
+          <t>17-09-2026 10:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2758,22 +2758,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SK Biopharma, 1STBIO Sign Parkinson’s Drug Deal</t>
+          <t>ProBio, Kun Tuo Partner to Accelerate Advancement of Innovative Therapies in China</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>contractpharma.com</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/sk-biopharma-1stbio-sign-parkinsons-drug-deal/</t>
+          <t>https://www.contractpharma.com/breaking-news/probio-kun-tuo-partner-to-accelerate-advancement-of-innovative-therapies-in-china/</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>17-09-2026 12:56 UTC</t>
+          <t>17-09-2026 19:10 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,22 +2785,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Gilead Partners With Pan American Health Organization on Lenacapavir Access for Latin America, Caribbean</t>
+          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>contractpharma.com</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/gilead-partners-with-pan-american-health-organization-on-lenacapavir-access-for-latin-america-caribbean/</t>
+          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16-09-2026 19:36 UTC</t>
+          <t>17-09-2026 12:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2812,157 +2812,157 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lilly TuneLab, Twist Bioscience Partner on Antibody Drug Discovery</t>
+          <t>Quotient Sciences Reports AI Clinical Trial Milestone</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>contractpharma.com</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/lilly-tunelab-twist-bioscience-partner-on-antibody-drug-discovery/</t>
+          <t>https://www.contractpharma.com/breaking-news/quotient-sciences-reports-ai-clinical-trial-milestone/</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16-09-2026 16:02 UTC</t>
+          <t>17-09-2026 19:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 gets first price hike in India, will start at Rs 99,999 from September 20th</t>
+          <t>Charles River Launches Rapid Cell Banking Programs</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>91mobiles.com</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.91mobiles.com/hub/samsung-galaxy-s26-first-price-hike-india-september-20th/</t>
+          <t>https://www.contractpharma.com/breaking-news/charles-river-launches-rapid-cell-banking-programs/</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>17-09-2026 04:38 UTC</t>
+          <t>17-09-2026 14:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Watch: Kinva Bio on What It Means to Be Among Samsung Solve for Tomorrow’s Top 20</t>
+          <t>Upperton Gains MHRA Approval for Nottingham Sterile Manufacturing Site</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/in/watch-kinva-bio-on-what-it-means-to-be-among-samsung-solve-for-tomorrows-top-20</t>
+          <t>https://www.contractpharma.com/breaking-news/upperton-gains-mhra-approval-for-nottingham-sterile-manufacturing-site/</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17-09-2026 12:30 UTC</t>
+          <t>17-09-2026 13:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Galaxy A56 gets the second One UI 9 beta update</t>
+          <t>WuXi XDC to Out-License Proprietary Payload-Linker Technology Platform to Ona Therapeutics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/galaxy-a56-one-ui-9-beta-2-update/</t>
+          <t>https://www.contractpharma.com/breaking-news/wuxi-xdc-to-out-license-proprietary-payload-linker-technology-platform-to-ona-therapeutics/</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>17-09-2026 09:55 UTC</t>
+          <t>17-09-2026 20:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 Price in India Tipped to Increase by Rs 12,000: Check Details</t>
+          <t>Kincell Bio, Cellipont Merge to Form Kincellis Advanced Therapies</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s26-price-in-india-increase-by-rs-12000-12060021</t>
+          <t>https://www.contractpharma.com/breaking-news/kincell-bio-cellipont-merge-to-form-kincellis-advanced-therapies/</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>17-09-2026 12:33 UTC</t>
+          <t>17-09-2026 18:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Z Fold 8 EMI drops under Forever plan</t>
+          <t>SK Biopharma, 1STBIO Sign Parkinson’s Drug Deal</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>t2ONLINE</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://t2online.in/tech/tech-news/samsung-galaxy-z-fold-8-emi-drops-under-forever-plan/2008068</t>
+          <t>https://www.contractpharma.com/breaking-news/sk-biopharma-1stbio-sign-parkinsons-drug-deal/</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>17-09-2026 08:36 UTC</t>
+          <t>17-09-2026 12:56 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,22 +2974,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>After 30 Years, Samsung Is Powering Innovation for India | Hindustan Times</t>
+          <t>iPhone 18 Pro Max vs. Samsung Galaxy S26 Ultra: Battle of the flagships</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>hindustantimes.com</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/genesis/after-30-years-samsung-is-powering-innovation-for-india-101787854726831.html</t>
+          <t>https://mashable.com/tech/iphone-18-pro-max-vs-galaxy-s26-ultra-price-specs</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>17-09-2026 14:03 UTC</t>
+          <t>18-09-2026 03:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3001,22 +3001,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Samsung rolls out Galaxy Forever plan, brings new financing options for Galaxy Z Fold 8 Ultra, Fold 8 in India</t>
+          <t>Watch: QuantHunt on Reimagining Cybersecurity for the Quantum Era</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>gadgetbridge.com</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.gadgetbridge.com/samsung-rolls-out-galaxy-forever-plan-brings-new-financing-options-for-galaxy-z-fold-8-ultra-fold-8-in-india/</t>
+          <t>https://news.samsung.com/in/watch-quanthunt-on-reimagining-cybersecurity-for-the-quantum-era</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>17-09-2026 14:48 UTC</t>
+          <t>18-09-2026 04:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Samsung could give the Galaxy S27 Ultra a major camera processing upgrade</t>
+          <t>Samsung Galaxy S26 series prices increased by Rs 20,000 in India, check new prices</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Android Authority</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.androidauthority.com/samsung-galaxy-s27-ultra-camera-upgrades-leak-3712251/</t>
+          <t>https://www.indiatoday.in/technology/story/samsung-galaxy-s26-price-hike-india-new-prices-all-variants-september-18-2997502-2026-09-18</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>17-09-2026 07:52 UTC</t>
+          <t>18-09-2026 07:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3055,22 +3055,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 Price To Hike By Rs 12,000 in India: Check New Prices</t>
+          <t>Samsung Galaxy A07s Has A 50 MP Camera, 5,000 mAh Battery</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>My Mobile India</t>
+          <t>Rediff</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.mymobileindia.com/samsung-galaxy-s26-price-to-hike-by-rs-12000-in-india-check-new-prices/</t>
+          <t>https://m.rediff.com/amp/getahead/report/samsung-galaxy-a07s-has-a-50-mp-camera-5000-mah-battery-gadgets-and-gaming-listicles/20260918.htm</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>17-09-2026 04:08 UTC</t>
+          <t>18-09-2026 04:24 UTC</t>
         </is>
       </c>
     </row>
@@ -3082,22 +3082,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Samsung’s Blue Tag Sale Makes Smarter Living More Accessible with AI-Powered Home Innovation</t>
+          <t>Samsung Galaxy S26 Series Could Become More Expensive By Rs. 20,000 Starting Today: Check New Prices</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/za/samsungs-blue-tag-sale-makes-smarter-living-more-accessible-with-ai-powered-home-innovation</t>
+          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s26-plus-ultra-price-hike-india-updated-prices-12062616</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>17-09-2026 13:51 UTC</t>
+          <t>18-09-2026 03:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3109,22 +3109,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Samsung cuts Galaxy Z Fold8, Fold8 Ultra EMIs by 25 percent with Galaxy Forever</t>
+          <t>Samsung phones get September 2026 Google Play System update</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>91mobiles.com</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.91mobiles.com/hub/samsung-galaxy-z-fold8-ultra-emis-galaxy-forever/</t>
+          <t>https://www.sammobile.com/news/samsung-phones-get-september-2026-google-play-system-update/</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>17-09-2026 10:26 UTC</t>
+          <t>17-09-2026 14:50 UTC</t>
         </is>
       </c>
     </row>
@@ -3136,22 +3136,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Samsung phones get September 2026 Google Play System update</t>
+          <t>Samsung Galaxy S26, S26 Ultra, Galaxy Z Fold 8 and Z Fold 8 Ultra price in India likely to be increased soon</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>gadgetbridge.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/samsung-phones-get-september-2026-google-play-system-update/</t>
+          <t>https://www.gadgetbridge.com/samsung-galaxy-s26-s26-ultra-galaxy-z-fold-8-and-z-fold-8-ultra-price-in-india-likely-to-be-increased-soon/</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>17-09-2026 14:50 UTC</t>
+          <t>18-09-2026 04:24 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,184 +3163,184 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S27 Ultra Could Get New Image Processing for More Natural Photos: Leak</t>
+          <t>Samsung Galaxy S26 Ultra, Galaxy S26 Price Hike of Rs 20,000</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>TelecomTalk</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s27-ultra-rear-camera-video-specifications-leak-12060286</t>
+          <t>https://telecomtalk.info/samsung-galaxy-s26-ultra-galaxy-s26-price/1011919/</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>17-09-2026 13:28 UTC</t>
+          <t>18-09-2026 05:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Celltrion's Remsima Tops Japan's Infliximab Market, Surpassing Originator Drug</t>
+          <t>Samsung cuts Galaxy Z Fold8, Fold8 Ultra EMIs by 25 percent with Galaxy Forever</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>91mobiles.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/2ce8c00d-beb2-47a2-af48-bd21e57cd128</t>
+          <t>https://www.91mobiles.com/hub/samsung-galaxy-z-fold8-ultra-emis-galaxy-forever/</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>17-09-2026 02:25 UTC</t>
+          <t>17-09-2026 10:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Celltrion’s Remsima Takes No. 1 in Japan After 11 Years</t>
+          <t>‘RAMageddon’ Strikes: Samsung Galaxy S26 Series Gets Massive Price Hike in India</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>Nokiamob</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277185</t>
+          <t>https://nokiamob.net/2026/09/18/ramageddon-strikes-samsung-galaxy-s26-series-gets-massive-price-hike-in-india/</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>17-09-2026 03:56 UTC</t>
+          <t>18-09-2026 05:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Celltrion’s Remsima Takes No. 1 Spot in Japan’s Infliximab Market After 11 Years</t>
+          <t>JOJO Ltd signs deal with Samsung to distribute channel on TV Plus</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>koreaittimes.com</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.koreaittimes.com/news/articleView.html?idxno=157265</t>
+          <t>https://scanx.trade/stock-market-news/companies/jojo-ltd-signs-deal-samsung-distribute-channel-tv-plus/51259068</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>17-09-2026 01:37 UTC</t>
+          <t>18-09-2026 05:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Celltrion's autoimmune disease treatment "Ramsima" overtook the original drug 11 years after its lau..</t>
+          <t>[Interview] The People Behind the Galaxy Z Series’ Camera Innovations ②: How Portrait Video Recreates the Look of Professional Camera Lenses</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/en/it/12155321</t>
+          <t>https://news.samsung.com/my/interview-the-people-behind-the-galaxy-z-series-camera-innovations-%E2%91%A1-how-portrait-video-recreates-the-look-of-professional-camera-lenses</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>17-09-2026 05:12 UTC</t>
+          <t>18-09-2026 02:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Celltrion's Remsima Tops Japan Infliximab Market After 11 Years</t>
+          <t>Apple Agrees to Samsung’s Higher Memory Prices for 2027: What It Could Mean for iPhone Prices</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>Gadgets 360</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/17/celltrions-remsima-tops-japan-infliximab-market-after-11</t>
+          <t>https://www.gadgets360.com/mobiles/news/apple-accepts-samsung-memory-price-hike-q1-2027-production-12063021</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>17-09-2026 00:20 UTC</t>
+          <t>18-09-2026 06:18 UTC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Celltrion captures Japan lead with Remsima biosimilar, eyes SC launch - CHOSUNBIZ</t>
+          <t>The new iPhone is here, but you can buy the Samsung Galaxy S26 FE and get a $200 gift card for free</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/09/17/EBUUYC3ILVC6THC2NCM5WFOSQU/</t>
+          <t>https://mashable.com/tech/sept-11-samsung-galaxy-gift-card-deal</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>16-09-2026 23:56 UTC</t>
+          <t>17-09-2026 23:39 UTC</t>
         </is>
       </c>
     </row>
@@ -3352,22 +3352,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Celltrion's Remsima Tops Japanese Infliximab Prescriptions After 11 Years Since Launch</t>
+          <t>Celltrion’s Remsima takes No. 1 spot in Japan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/2026091707490713431</t>
+          <t>https://pulse.mk.co.kr/news/english/12156269</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>16-09-2026 22:49 UTC</t>
+          <t>18-09-2026 01:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Zymfentra, Xcopri Near $1 Billion Sales Mark</t>
+          <t>Korea Cuts Prices of 80 Drugs, Saving 33.9 Billion Won</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/09/17/zymfentra-xcopri-near-1-billion-sales-mark</t>
+          <t>https://en.sedaily.com/technology/2026/09/18/korea-cuts-prices-of-80-drugs-saving-339-billion-won</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>16-09-2026 22:00 UTC</t>
+          <t>18-09-2026 01:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Prestige Biopharma IDC Obtains International Certification for Environmental and Occupational Health and Safety Standards</t>
+          <t>Prestige Biopharma Obtains Marketing Authorization for 'Tuzuneu' in Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3416,39 +3416,39 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/stock-etc/2026091709115812850</t>
+          <t>https://www.asiae.co.kr/en/article/2026091809382068983</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>17-09-2026 00:11 UTC</t>
+          <t>18-09-2026 00:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>About 20 Pusan National University Students Visit Bio and Logistics Sites... BJFEZ Holds 'Insight Trip'</t>
+          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/yeongnam/2026091715044359776</t>
+          <t>https://www.reuters.com/legal/litigation/astrazeneca-daiichi-breast-cancer-drug-cleared-nhs-use-england-2026-09-17/</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>17-09-2026 06:04 UTC</t>
+          <t>17-09-2026 15:07 UTC</t>
         </is>
       </c>
     </row>
@@ -3460,22 +3460,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Fortis moves Supreme Court against Delhi High Court order</t>
+          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Arab News</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/business/india-business/fortis-moves-supreme-court-against-delhi-high-court-order/amp_articleshow/134309495.cms</t>
+          <t>https://www.arabnews.com/world/astrazeneca-daiichi-breast-cancer-drug-cleared-for-nhs-use-in-england-3002134</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>17-09-2026 10:57 UTC</t>
+          <t>17-09-2026 16:46 UTC</t>
         </is>
       </c>
     </row>
@@ -3487,22 +3487,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AZ, Daiichi's Enhertu scores long-awaited NICE blessing in HER2-low breast cancer</t>
+          <t>AstraZeneca and Daiichi Sankyo secure NHS England access for Enhertu breast cancer drug</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Traders Union</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/az-daiichis-enhertu-wins-long-awaited-nice-blessing</t>
+          <t>https://tradersunion.com/news/financial-news/show/3369162-enhertu-nhs-england-breast-cancer-access/</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>16-09-2026 23:30 UTC</t>
+          <t>17-09-2026 12:13 UTC</t>
         </is>
       </c>
     </row>
@@ -3514,22 +3514,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AstraZeneca and Daiichi Sankyo secure NHS England access for Enhertu breast cancer drug</t>
+          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Traders Union</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://tradersunion.com/news/financial-news/show/3369162-enhertu-nhs-england-breast-cancer-access/</t>
+          <t>https://www.marketscreener.com/news/astrazeneca-daiichi-breast-cancer-drug-cleared-for-nhs-use-in-england-ce785bd3dd88f124</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>17-09-2026 12:13 UTC</t>
+          <t>17-09-2026 11:39 UTC</t>
         </is>
       </c>
     </row>
@@ -3541,22 +3541,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Fortis Healthcare moves Supreme Court against Delhi HC forensic audit order</t>
+          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Rediff</t>
+          <t>islandpacket.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://m.rediff.com/amp/business/report/fortis-healthcare-challenges-delhi-hc-forensic-audit-into-alleged-asset-erosion-by-former-promoters/20260917.htm</t>
+          <t>https://www.islandpacket.com/living/article317278373.html</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>17-09-2026 07:03 UTC</t>
+          <t>17-09-2026 11:32 UTC</t>
         </is>
       </c>
     </row>
@@ -3568,22 +3568,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Special Report on Shareholding Daiichi Sankyo (7.39% → 7.97%) Blackrock Japan, et al.</t>
+          <t>Fortis moves Supreme Court against Delhi High Court order</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Moomoo</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://www.moomoo.com/news/post/76384289/special-report-on-shareholdings-daiichi-sankyo-7-39-7-97</t>
+          <t>https://timesofindia.indiatimes.com/business/india-business/fortis-moves-supreme-court-against-delhi-high-court-order/articleshow/134309495.cms</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>17-09-2026 07:25 UTC</t>
+          <t>17-09-2026 10:57 UTC</t>
         </is>
       </c>
     </row>
@@ -3595,1210 +3595,805 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Fortis Healthcare moves Supreme Court against forensic audit order</t>
+          <t>IHH Unit Fortis Files Supreme Court Petition Against Delhi High Court Order In Daiichi Proceedings</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>BusinessToday Malaysia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/fortis-healthcare-files-slp-against-forensic-audit-order-in-daiichi-sankyo-case/article71473603.ece</t>
+          <t>https://www.businesstoday.com.my/2026/09/17/ihh-unit-fortis-files-supreme-court-against-delhi-high-court-order-in-daiichi-proceedings/</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>16-09-2026 15:43 UTC</t>
+          <t>17-09-2026 10:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
+          <t>Kura Oncology Q2FY26 Results: Comzifti revenue hits $9.1 million</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/astrazeneca-daiichi-breast-cancer-drug-cleared-for-nhs-use-in-england-ce785bd3dd88f124</t>
+          <t>https://scanx.trade/stock-market-news/companies/kura-oncology-q2fy26-results-comzifti-revenue-hits-9-1-million/51187458</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>17-09-2026 11:39 UTC</t>
+          <t>17-09-2026 10:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IHH Unit Fortis Files Supreme Court Petition Against Delhi High Court Order In Daiichi Proceedings</t>
+          <t>Meet the Montgomery County Companies Behind 10 Breakthrough Treatments</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BusinessToday Malaysia</t>
+          <t>MONTCO.Today</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.com.my/2026/09/17/ihh-unit-fortis-files-supreme-court-against-delhi-high-court-order-in-daiichi-proceedings/</t>
+          <t>https://montco.today/2026/09/montgomery-county-pharmaceutical-treatments/</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>17-09-2026 10:19 UTC</t>
+          <t>17-09-2026 16:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Mochida Pharmaceutical</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NICE finally backs Enhertu for HER2-low breast cancer</t>
+          <t>Major Depressive Disorder Clinical Trial Pipeline Boom as 75+ Companies are in the Race for Better Treatments | DelveInsight</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>pharmaphorum.com</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://pharmaphorum.com/news/nice-finally-backs-enhertu-her2-low-breast-cancer</t>
+          <t>https://businessupturn.com/brand-post/major-depressive-disorder-clinical-trial-pipeline-boom-as-75-companies-are-in-the-race-for-better-treatments-delveinsight/</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>17-09-2026 09:11 UTC</t>
+          <t>17-09-2026 18:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
+          <t>Hang Ten Systems Raises Another $53 Million in Seed Funding</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>islandpacket.com</t>
+          <t>Equitypandit</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.islandpacket.com/living/article317278373.html</t>
+          <t>https://www.equitypandit.com/hang-ten-systems-raises-another-53-million-in-seed-funding/</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>17-09-2026 11:32 UTC</t>
+          <t>17-09-2026 10:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Files SC Petition Against HC Order &amp; Signs Agreement for 400+ Bed Hospital</t>
+          <t>Fresenius SE &amp; Co. KGaA : Buy rating from UBS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>sahi.com</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/fortis-healthcare-files-special-leave-petition-before-supreme-court-against-delhi-hc-judgment</t>
+          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-buy-rating-from-ubs-ce785bd3da81f421</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>16-09-2026 17:14 UTC</t>
+          <t>17-09-2026 11:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>A Life-Extending Breast Cancer Drug Finally Comes to England</t>
+          <t>Otsuka ICU Medical LLC Issues Voluntary Nationwide Recall of 0.9% Sodium Chloride Injection, USP Due To a Product Mix-up with 10 mEq Potassium Chloride Injection</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bloomberg.com</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-09-16/a-life-extending-breast-cancer-drug-finally-comes-to-england</t>
+          <t>https://finance.yahoo.com/healthcare/articles/otsuka-icu-medical-llc-issues-210800118.html</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>16-09-2026 23:00 UTC</t>
+          <t>17-09-2026 21:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>‘Life-changing’ breast cancer drug now available on NHS in England</t>
+          <t>Ipsen appoints Mariette Finet to its Board of Directors</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Financial Times</t>
+          <t>GlobeNewswire</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://www.ft.com/content/e1f59abc-6ecf-4cef-80aa-75d201f731d0?syn-25a6b1a6=1</t>
+          <t>https://www.globenewswire.com/news-release/2026/09/18/3364489/0/en/ipsen-appoints-mariette-finet-to-its-board-of-directors.html</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>16-09-2026 23:00 UTC</t>
+          <t>18-09-2026 07:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NICE Reverses Enhertu Rejection for HER2-Low Breast Cancer After Pricing &amp; Methods Changes</t>
+          <t>FDA Clears Phase 1b/2 Trial of CAR T-Cell Therapy C-CAR168 for Refractory Progressive Multiple Sclerosis</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NAVLIN DAILY</t>
+          <t>NeurologyLive</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://www.navlindaily.com/article/31897/nice-reverses-enhertu-rejection-for-her2-low-breast-cancer-after-pricing-methods-changes</t>
+          <t>https://www.neurologylive.com/view/fda-clears-c-car168-trial-refractory-progressive-multiple-sclerosis</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>17-09-2026 08:51 UTC</t>
+          <t>17-09-2026 19:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Kura Oncology Q2FY26 Results: Comzifti revenue hits $9.1 million</t>
+          <t>Legend names Ingrid Zhang as CEO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/kura-oncology-q2fy26-results-comzifti-revenue-hits-9-1-million/51187458</t>
+          <t>https://www.thepharmaletter.com/biotech-news/legend-names-ingrid-zhang-as-ceo</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>17-09-2026 10:54 UTC</t>
+          <t>17-09-2026 18:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Savory Oral Nutrition Supplement Market</t>
+          <t>Bhavana Chivukula, Profiled By Influential Women, Advances Pharmaceutical Innovation Through Research And Manufacturing</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Future Market Insights</t>
+          <t>EIN News</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://www.futuremarketinsights.com/reports/savory-oral-nutrition-supplement-market</t>
+          <t>https://www.einnews.com/pr_news/943037449/bhavana-chivukula-profiled-by-influential-women-advances-pharmaceutical-innovation-through-research-and-manufacturing</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>17-09-2026 12:17 UTC</t>
+          <t>17-09-2026 13:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Hang Ten Systems Raises Another $53 Million in Seed Funding</t>
+          <t>GlycoEra hires Astria dealmaker as chief business officer</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Equitypandit</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://www.equitypandit.com/hang-ten-systems-raises-another-53-million-in-seed-funding/</t>
+          <t>http://www.thepharmaletter.com/biotech-news/glycoera-hires-astria-dealmaker-as-chief-business-officer</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>17-09-2026 10:58 UTC</t>
+          <t>17-09-2026 08:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA : Buy rating from UBS</t>
+          <t>Teva Seeks Ruling Against J&amp;J Bid to Block Simponi Biosimilars</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Bloomberg Law News</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-buy-rating-from-ubs-ce785bd3da81f421</t>
+          <t>https://news.bloomberglaw.com/health-law-and-business/teva-seeks-ruling-against-j-j-bid-to-block-simponi-biosimilars</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>17-09-2026 11:13 UTC</t>
+          <t>17-09-2026 15:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Vishal Sikka's Hang Ten Systems Raises $53M Just Five Weeks After Seed Round</t>
+          <t>Teva Seeks Ruling Against J&amp;J Bid to Block Simponi Biosimilars</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>bbntimes.com</t>
+          <t>Bloomberg Law News</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://www.bbntimes.com/technology/vishal-sikka-s-hang-ten-systems-raises-53m-just-five-weeks-after-seed-round</t>
+          <t>https://news.bloomberglaw.com/ip-law/teva-seeks-ruling-against-j-j-bid-to-block-simponi-biosimilars</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>16-09-2026 18:44 UTC</t>
+          <t>17-09-2026 15:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Bhavana Chivukula, Profiled By Influential Women, Advances Pharmaceutical Innovation Through Research And Manufacturing</t>
+          <t>The Evolving Law of Enablement: Federal Circuit Decisions in Wyeth and Teva Form a “Yin and Yang” Framework</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>EIN News</t>
+          <t>JD Supra</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.einnews.com/pr_news/943037449/bhavana-chivukula-profiled-by-influential-women-advances-pharmaceutical-innovation-through-research-and-manufacturing</t>
+          <t>https://www.jdsupra.com/legalnews/the-evolving-law-of-enablement-federal-5015742/</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>17-09-2026 13:22 UTC</t>
+          <t>17-09-2026 17:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GlycoEra hires Astria dealmaker as chief business officer</t>
+          <t>Fall Into Savings With Deals From Deuter, La Sportiva, Teva, and More</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>GearJunkie</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>http://www.thepharmaletter.com/biotech-news/glycoera-hires-astria-dealmaker-as-chief-business-officer</t>
+          <t>https://gearjunkie.com/deals/weekly-deals-9-17-26</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>17-09-2026 08:57 UTC</t>
+          <t>17-09-2026 19:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Trialynx Wins DPHARM Idol Disrupt 2026</t>
+          <t>Japan approves under-the-skin Keytruda made with Alteogen enzyme</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/partner-content/trialynx-wins-dpharm-idol-disrupt-2026</t>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33229</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>16-09-2026 16:45 UTC</t>
+          <t>18-09-2026 03:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GSK Pharma Shareholders Approve Board and Managing Director Appointments via Postal Ballot</t>
+          <t>A decade leading retinal care, Eylea 8mg now lasts even longer and better, expert says</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/gsk-pharma-shareholders-approve-board-and-managing-director-appointments-via-postal-ballot</t>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33231</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>16-09-2026 16:40 UTC</t>
+          <t>18-09-2026 03:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Alvotech Shares Rise After Double Upgrade From Barclays</t>
+          <t>Lantern Pharma to Present Open-Medicine AI — a Multi-Agentic Platform for End-to-End Therapeutic Development — Business Model, Roadmap, and Value Proposition on September 23</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>sg.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/alvotech-shares-rise-after-double-upgrade-from-barclays-ce785bd2de81f42d</t>
+          <t>https://sg.finance.yahoo.com/news/lantern-pharma-present-open-medicine-122000593.html</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>16-09-2026 18:12 UTC</t>
+          <t>17-09-2026 12:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>About Teva Pharmaceutical Industries Ltd. rStock</t>
+          <t>WuXi XDC Out-Licenses WuXiTecan-2 Payload-Linker Technology Platform to Ona Therapeutics to Advance Novel ADC Research and Development</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>sg.finance.yahoo.com</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/en-pt/price/teva-pharmaceutical-industries-ltd-rstock</t>
+          <t>https://sg.finance.yahoo.com/news/wuxi-xdc-licenses-wuxitecan-2-080900462.html</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>17-09-2026 00:57 UTC</t>
+          <t>17-09-2026 08:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Teva’s Lab-Made Antibody Shot for Celiac Shows Hopeful Results</t>
+          <t>Sandoz joins mAbxience to develop emicizumab biosimilar and expand haemophilia pipeline</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Allergic Living</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://www.allergicliving.com/2026/09/16/tevas-lab-made-antibody-shot-for-celiac-shows-hopeful-results/</t>
+          <t>https://www.tipranks.com/news/company-announcements/sandoz-joins-mabxience-to-develop-emicizumab-biosimilar-and-expand-haemophilia-pipeline</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>16-09-2026 22:36 UTC</t>
+          <t>18-09-2026 05:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Most Active Options Report: FPS, TEVA, AFL</t>
+          <t>Hang Ten Systems Raises Another $53 Million in Seed Funding</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Schaeffer's Investment Research</t>
+          <t>Equitypandit</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://www.schaeffersresearch.com/content/options/2026/09/16/most-active-options-report-fps-teva-afl</t>
+          <t>https://www.equitypandit.com/hang-ten-systems-raises-another-53-million-in-seed-funding/</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>16-09-2026 15:53 UTC</t>
+          <t>17-09-2026 10:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Teva Launches LongActingImpact.com to Advance Understanding of Earlier, Effective and Uninterrupted Schizophrenia Care</t>
+          <t>Fresenius SE &amp; Co. KGaA : Buy rating from UBS</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Indovizka.com</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://indovizka.com/news/detail/22813/teva-launches-longactingimpactcom-to-advance-understanding-of-earlier-effective-and-uninterrupted-schizophrenia-care</t>
+          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-buy-rating-from-ubs-ce785bd3da81f421</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>17-09-2026 01:34 UTC</t>
+          <t>17-09-2026 11:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Lantern Pharma to Present Open-Medicine AI — a Multi-Agentic Platform for End-to-End Therapeutic Development — Business Model, Roadmap, and Value Proposition on September 23</t>
+          <t>Otsuka ICU Medical LLC Issues Voluntary Nationwide Recall of 0.9% Sodium Chloride Injection, USP Due To a Product Mix-up with 10 mEq Potassium Chloride Injection</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/lantern-pharma-present-open-medicine-122000593.html</t>
+          <t>https://finance.yahoo.com/healthcare/articles/otsuka-icu-medical-llc-issues-210800118.html</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>17-09-2026 12:20 UTC</t>
+          <t>17-09-2026 21:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>WuXi XDC Out-Licenses WuXiTecan-2 Payload-Linker Technology Platform to Ona Therapeutics to Advance Novel ADC Research and Development</t>
+          <t>[Opening Market] KOSPI Surges Past 6,860 on Foreign, Institutional Buying</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/wuxi-xdc-licenses-wuxitecan-2-080900462.html</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277274</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>17-09-2026 08:09 UTC</t>
+          <t>18-09-2026 01:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Clarivate Reveals Citation Laureates 2026 Recognizing Transformative Scientific Breakthroughs</t>
+          <t>Upperton Gains MHRA Approval for Nottingham Sterile Manufacturing Site</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/clarivate-reveals-citation-laureates-2026-070500489.html</t>
+          <t>https://www.contractpharma.com/breaking-news/upperton-gains-mhra-approval-for-nottingham-sterile-manufacturing-site/</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>17-09-2026 07:05 UTC</t>
+          <t>17-09-2026 13:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Thirty Inspiring Middle School Scientists and Engineers Named Finalists in the 2026 Thermo Fisher Scientific Junior Innovators Challenge</t>
+          <t>Colorful iPhone 18 series hits shelves</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>mbiz.heraldcorp.com</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/thirty-inspiring-middle-school-scientists-160300649.html</t>
+          <t>https://mbiz.heraldcorp.com/article/10878448</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>16-09-2026 16:03 UTC</t>
+          <t>18-09-2026 03:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Government of Canada invests up to $1.98 million to develop sustainable fertilizer technology to reduce emissions and microplastics</t>
+          <t>Single-Use Bioprocess Connectors Market Forecast to 2035: Cell and Gene Therapy Demand Drives 12-16% CAGR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/government-canada-invests-1-98-163400092.html</t>
+          <t>https://www.indexbox.io/blog/single-use-bioprocess-connectors-market-forecast-to-2035-cell-and-gene-therapy-demand-drives-12-16-cagr/</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>16-09-2026 16:34 UTC</t>
+          <t>17-09-2026 13:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Savory Oral Nutrition Supplement Market</t>
+          <t>Personal data of 140 customers leaked from Kakao Games</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Future Market Insights</t>
+          <t>mbiz.heraldcorp.com</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://www.futuremarketinsights.com/reports/savory-oral-nutrition-supplement-market</t>
+          <t>https://mbiz.heraldcorp.com/article/10877550</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>17-09-2026 12:17 UTC</t>
+          <t>17-09-2026 08:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Hang Ten Systems Raises Another $53 Million in Seed Funding</t>
+          <t>Naver decides against acquiring stake in Baemin</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Equitypandit</t>
+          <t>mbiz.heraldcorp.com</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://www.equitypandit.com/hang-ten-systems-raises-another-53-million-in-seed-funding/</t>
+          <t>https://mbiz.heraldcorp.com/article/10877562</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>17-09-2026 10:58 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Fresenius SE &amp; Co. KGaA : Buy rating from UBS</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>marketscreener.com</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-buy-rating-from-ubs-ce785bd3da81f421</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>17-09-2026 11:13 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Vishal Sikka's Hang Ten Systems Raises $53M Just Five Weeks After Seed Round</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>bbntimes.com</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>https://www.bbntimes.com/technology/vishal-sikka-s-hang-ten-systems-raises-53m-just-five-weeks-after-seed-round</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>16-09-2026 18:44 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Upperton Gains MHRA Approval for Nottingham Sterile Manufacturing Site</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>contractpharma.com</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>https://www.contractpharma.com/breaking-news/upperton-gains-mhra-approval-for-nottingham-sterile-manufacturing-site/</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>17-09-2026 13:41 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>KOSPI Opens Higher, Shaking Off Hawkish FOMC Shock; AI and Falling Oil Prices Provide Lift</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>finance.biggo.com</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>https://finance.biggo.com/news/e6307ee5-9f5d-4361-aff0-d05874e91306</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>17-09-2026 02:06 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>South Korea shares rise as Fed rate hike eases uncertainty</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Business Recorder</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>https://www.brecorder.com/news/amp/40439930</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>17-09-2026 06:44 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>KOSPI ends near flat despite hawkish FOMC as foreigners net sell 2.3 trillion won</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>digitaltoday.co.kr</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>https://www.digitaltoday.co.kr/en/view/104900/kospi-ends-flat-despite-hawkish-fomc-as-foreigners-net-sell-2-3-trillion-won</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>17-09-2026 07:07 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>KOSPI, KOSDAQ Open Higher Despite Hawkish Fed Signals</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Seoul Economic Daily</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>https://en.sedaily.com/finance/2026/09/17/kospi-kosdaq-open-higher-despite-hawkish-fed-signals</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>17-09-2026 00:51 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>KOSPI Posts Early Gains Despite Fed Rate Hike...Individuals Lead Net Buying</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>아시아경제</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>https://www.asiae.co.kr/en/article/2026091710074710967</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>17-09-2026 01:07 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Despite the U.S. Federal Reserve's (Fed) rate hike last night, the KOSPI started higher on the 17th.</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>매일경제</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>https://www.mk.co.kr/en/stock/12155032</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>17-09-2026 00:20 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>[Opening Market] KOSPI Opens 0.9% Higher As Fed Uncertainty Eases</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Businesskorea</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277168</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>17-09-2026 02:19 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Samsung Electronics, SK Hynix Rally Alongside U.S. Semiconductor Rebound</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>finance.biggo.com</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>https://finance.biggo.com/news/3813f228-d1ad-486f-b0ad-7dd522d8db96</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>17-09-2026 01:26 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Won-dollar exchange rate fluctuates in upper 1,370s</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10877041</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>17-09-2026 04:01 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>US Federal Reserve raises benchmark interest rate by 0.25 percentage point</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10876127</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>16-09-2026 18:02 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Special prosecutor raids National Election Commission headquarters, 8 other sites</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10876510</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>17-09-2026 00:33 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Han River Bus marks first anniversary of service</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10877045</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>17-09-2026 04:01 UTC</t>
+          <t>17-09-2026 09:11 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E147"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz Gets Canada Approval for Generic Version of Ozempic</t>
+          <t>Sandoz announces collaboration with mAbxience to expand patient access to life-enhancing biosimilar medicines</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/health/pharma/sandoz-gets-canada-approval-for-generic-version-of-ozempic-8f8dce3c</t>
+          <t>https://www.sandoz.com/sandoz-announces-collaboration-mabxience-expand-patient-access-life-enhancing-biosimilar-medicines/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18-09-2026 05:45 UTC</t>
+          <t>18-09-2026 10:07 UTC</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sandoz approved for semaglutide sales in Canada</t>
+          <t>M&amp;A Roundup: Lisata Therapeutics Acquires Marea Therapeutics, mAbxience Enters Collaboration with Sandoz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>medwatch.com</t>
+          <t>pharmexec.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://medwatch.com/News/Pharma___Biotech/article19655814.ece</t>
+          <t>https://www.pharmexec.com/view/-lisata-therapeutics-acquires-marea-therapeutics-mabxience-collaboration-sandoz</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18-09-2026 07:05 UTC</t>
+          <t>18-09-2026 14:05 UTC</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sandoz's Type-2 Diabetes Therapy Semaglutide Wins Approval in Canada</t>
+          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/sandoz-s-type-2-diabetes-therapy-semaglutide-wins-approval-in-canada-ce785adad98af026</t>
+          <t>https://www.prnewswire.com/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883156.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18-09-2026 05:29 UTC</t>
+          <t>18-09-2026 10:16 UTC</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sandoz joins mAbxience to develop emicizumab biosimilar and expand haemophilia pipeline</t>
+          <t>Sandoz Canada receives Health Canada regulatory approval for (Pr)Sandoz® Semaglutide, a generic version of (Pr)Ozempic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/sandoz-joins-mabxience-to-develop-emicizumab-biosimilar-and-expand-haemophilia-pipeline</t>
+          <t>https://www.biospace.com/press-releases/sandoz-canada-receives-health-canada-regulatory-approval-for-prsandoz-semaglutide-a-generic-version-of-prozempic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18-09-2026 05:36 UTC</t>
+          <t>18-09-2026 12:57 UTC</t>
         </is>
       </c>
     </row>
@@ -571,211 +571,211 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sandoz Wins Canadian Approval for Generic Semaglutide, Targeting Growing GLP-1 Market</t>
+          <t>Priyaranjan Jha Appointed Global Head of GCCs and Country President, Sandoz India</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/sandoz-wins-canadian-approval-for-generic-semaglutide-targeting-growing-glp-1-market</t>
+          <t>https://hrtoday.in/priyaranjan-jha-appointed-global-head-of-gccs-and-country-president-sandoz-india/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18-09-2026 05:36 UTC</t>
+          <t>18-09-2026 11:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Stada</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jensen Huang (Nvidia)</t>
+          <t>Sandoz Adds First Hemophilia Biosimilar In Bio100 Expansion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://en.ilsole24ore.com/art/jensen-huang-nvidia-AJuKjKGB</t>
+          <t>https://insights.citeline.com/generics-bulletin/business/deals/sandoz-adds-first-hemophilia-biosimilar-in-bio100-expansion-VXPZZ54UQ5A6XNCWO7YM3W6AFQ/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17-09-2026 18:27 UTC</t>
+          <t>18-09-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim launches PED Essentials for patient data collection</t>
+          <t>mAbxience and Sandoz partner to develop and com...</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The Clinical Trial Vanguard</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.clinicaltrialvanguard.com/news/boehringer-ingelheim-launches-ped-essentials-for-patient-data-collection/</t>
+          <t>https://pluang.com/en/news-feed/mabxience-dan-sandoz-jalin-kerja-sama-percepat-akses-biosimilar-dunia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18-09-2026 06:42 UTC</t>
+          <t>18-09-2026 10:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Siemens Healthineers, Boehringer team up on blood-based liver screening</t>
+          <t>Sandoz Gets Canada Approval for Generic Version of Ozempic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>WSJ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33245</t>
+          <t>https://www.wsj.com/health/pharma/sandoz-gets-canada-approval-for-generic-version-of-ozempic-8f8dce3c</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18-09-2026 07:07 UTC</t>
+          <t>18-09-2026 05:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim launches PED Essentials, an online learning resource that gives patients a stronger voice</t>
+          <t>Sandoz receives regulatory approval for generic semaglutide in Canada, paving way to expand patient access to key GLP-1 medicine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/boehringer-ingelheim-launches-ped-essentials-an-online-learning-resource-that-gives-patients-a-stronger-voice</t>
+          <t>https://www.sandoz.com/sandoz-receives-regulatory-approval-generic-semaglutide-canada-paving-way-expand-patient-access-key/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17-09-2026 09:39 UTC</t>
+          <t>18-09-2026 05:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Boehringer launches hub for patient experience data</t>
+          <t>Sandoz Receives Canadian Approval for Generic Semaglutide</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pharmaphorum</t>
+          <t>Pharmacy Business</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pharmaphorum.com/news/boehringer-launches-hub-patient-experience-data</t>
+          <t>https://www.pharmacy.biz/sandoz-wins-canadian-generic-semaglutide-approval/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17-09-2026 09:54 UTC</t>
+          <t>18-09-2026 12:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Boehringer halts Phase III kidney trial of vicadrostat/Jardiance combination</t>
+          <t>Sandoz approved for semaglutide sales in Canada</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>medwatch.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/boehringer-halts-phase-iii-kidney-trial-of-vicadrostat-jardiance-combination</t>
+          <t>https://medwatch.com/News/Pharma___Biotech/article19655814.ece</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17-09-2026 08:57 UTC</t>
+          <t>18-09-2026 07:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spot CKD: A Moment That Shouldn’t Be Missed</t>
+          <t>Jensen Huang (Nvidia)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CSRwire</t>
+          <t>Il Sole 24 ORE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://csrwire.com/press-release/spot-ckd-moment-shouldnt-be-missed/</t>
+          <t>https://en.ilsole24ore.com/art/jensen-huang-nvidia-AJuKjKGB</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17-09-2026 20:05 UTC</t>
+          <t>17-09-2026 18:27 UTC</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Certara Launches External Data Accelerator for CDISC Standards Compliance</t>
+          <t>Boehringer Ingelheim launches PED Essentials for patient data collection</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.clinicaltrialvanguard.com/news/certara-launches-external-data-accelerator-for-cdisc-standards-compliance/</t>
+          <t>https://www.clinicaltrialvanguard.com/news/boehringer-ingelheim-launches-ped-essentials-for-patient-data-collection/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18-09-2026 06:52 UTC</t>
+          <t>18-09-2026 06:42 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Paper + Spark adds seven new clients as it’s named agency of the year at 2026 AMI Awards</t>
+          <t>Siemens Healthineers, Boehringer team up on blood-based liver screening</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Campaign Brief</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://campaignbrief.com/paper-spark-adds-seven-new-clients-as-its-named-agency-of-the-year-at-2026-ami-awards/</t>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33245</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17-09-2026 10:02 UTC</t>
+          <t>18-09-2026 07:07 UTC</t>
         </is>
       </c>
     </row>
@@ -841,238 +841,238 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SkinCure Analysis: Nonmelanoma Skin Cancer Cases 42% Higher Than Official Count</t>
+          <t>Boehringer discontinues Phase III EASi-KIDNEY trial of vicadrostat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>The Clinical Trial Vanguard</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.clinicaltrialvanguard.com/news/skincure-analysis-nonmelanoma-skin-cancer-cases-42-higher-than-official-count/</t>
+          <t>https://www.thepharmaletter.com/pharma-news/boehringer-halts-phase-iii-kidney-trial-of-vicadrostat-combination</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18-09-2026 06:42 UTC</t>
+          <t>18-09-2026 08:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Generic drugs get a legal boost from Supreme Court ruling, law firm analysis finds</t>
+          <t>Spot CKD: A Moment That Shouldn’t Be Missed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>CSRwire</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.medicaleconomics.com/view/generic-drugs-get-a-legal-boost-from-supreme-court-ruling-law-firm-analysis-finds</t>
+          <t>https://csrwire.com/press-release/spot-ckd-moment-shouldnt-be-missed/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17-09-2026 18:27 UTC</t>
+          <t>17-09-2026 20:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Senate Hearing Targets U.S. Generic Drug Manufacturing</t>
+          <t>Boehringer Ingelheim launches PED Essentials, an online learning resource that gives patients a stronger voice</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Legis1</t>
+          <t>indovizka.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://legis1.com/news/generic-drug-manufacturing-senate-panel-will</t>
+          <t>https://indovizka.com/news/detail/22834/boehringer-ingelheim-launches-ped-essentials-an-online-learning-resource-that-gives-patients-a-stronger-voice</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17-09-2026 18:03 UTC</t>
+          <t>18-09-2026 00:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DLCA Sues Eight Pharmaceutical Companies, Alleging Opioid Monitoring Failures and Misleading Marketing</t>
+          <t>Pyrantel Pamoate Suspension Market Forecast to 2035: Growth Driven by Expanding Livestock and Equine Populations</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The Virgin Islands Consortium</t>
+          <t>indexbox.io</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://viconsortium.com/vi-legal/virgin-islands-dlca-sues-eight-pharmaceutical-companies--alleging-opioid-monitoring-failures-and-misleading-marketing</t>
+          <t>https://www.indexbox.io/blog/pyrantel-pamoate-suspension-market-forecast-to-2035-growth-driven-by-expanding-livestock-and-equine-populations/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17-09-2026 10:34 UTC</t>
+          <t>18-09-2026 11:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
+          <t>Certara Launches External Data Accelerator for CDISC Standards Compliance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
+          <t>https://www.clinicaltrialvanguard.com/news/certara-launches-external-data-accelerator-for-cdisc-standards-compliance/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17-09-2026 12:54 UTC</t>
+          <t>18-09-2026 07:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Never Too Late (or Too Early) for Lipid Lowering: STAREE and REACT</t>
+          <t>SkinCure Analysis: Nonmelanoma Skin Cancer Cases 42% Higher Than Official Count</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.medscape.com/viewarticle/never-too-late-or-too-early-lipid-lowering-staree-and-react-2026a1000y8u</t>
+          <t>https://www.clinicaltrialvanguard.com/news/skincure-analysis-nonmelanoma-skin-cancer-cases-42-higher-than-official-count/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17-09-2026 18:21 UTC</t>
+          <t>18-09-2026 07:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FDA-ordered studies of many drugs, devices on the market are not done</t>
+          <t>New licensed treatment for equine insulin dysregulation launches in Great Britain</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>yourhorse.co.uk</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.washingtonpost.com/health/2026/09/17/fda-ordered-studies-many-drugs-devices-market-are-not-done/</t>
+          <t>https://www.yourhorse.co.uk/news/new-licensed-treatment-for-equine-insulin-dysregulation-launches-in-great-britain/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17-09-2026 16:00 UTC</t>
+          <t>18-09-2026 05:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FDA Reduces Monitoring Time for First Two Tarlatamab Doses</t>
+          <t>Generic drugs get a legal boost from Supreme Court ruling, law firm analysis finds</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pharmacy Times</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pharmacytimes.com/view/fda-reduces-monitoring-time-for-first-two-tarlatamab-doses</t>
+          <t>https://www.medicaleconomics.com/view/generic-drugs-get-a-legal-boost-from-supreme-court-ruling-law-firm-analysis-finds</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17-09-2026 17:34 UTC</t>
+          <t>17-09-2026 18:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The top life sciences firms in Mass. employ more people than last year</t>
+          <t>Senate Hearing Targets U.S. Generic Drug Manufacturing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The Business Journals</t>
+          <t>Legis1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.bizjournals.com/boston/research/lists/2026/largest-life-sciences-companies-in-massachusetts.html</t>
+          <t>https://legis1.com/news/generic-drug-manufacturing-senate-panel-will</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17-09-2026 14:00 UTC</t>
+          <t>17-09-2026 18:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ticket registration opens for Amgen Irish Open at K Club 2027</t>
+          <t>€176,000 raised for Make-A-Wish® Ireland at the Amgen Irish Open</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kildare Live</t>
+          <t>DP World Tour</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.leinsterleader.ie/sport/ticket-registration-opens-for-amgen-irish-open-at-k-club-2027-9078090</t>
+          <t>https://www.europeantour.com/dpworld-tour/news/articles/detail/176-000-raised-for-make-a-wish-ireland-at-the-amgen-irish-open/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17-09-2026 16:00 UTC</t>
+          <t>18-09-2026 10:14 UTC</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New taxes crucial to preserve EU budget, says Irish PM</t>
+          <t>Amgen Leads Strong Commercial Field into Irish Open Week at Doonbeg</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>politico.eu</t>
+          <t>Sport for Business</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.politico.eu/article/new-eu-taxes-crucial-to-preserve-budget-says-irish-pm-micheal-martin/</t>
+          <t>https://sportforbusiness.com/amgen-leads-strong-commercial-field-into-irish-open-week-at-doonbeg/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17-09-2026 14:42 UTC</t>
+          <t>18-09-2026 10:29 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,265 +1138,265 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COMMENT: Shane Lowry's Amgen Irish Open win lifts all our hearts</t>
+          <t>Never Too Late (or Too Early) for Lipid Lowering: STAREE and REACT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Offaly Live</t>
+          <t>Medscape</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.offalyexpress.ie/news/opinion/comment-shane-lowrys-amgen-irish-open-win-lifts-all-our-hearts-9074549</t>
+          <t>https://www.medscape.com/viewarticle/never-too-late-or-too-early-lipid-lowering-staree-and-react-2026a1000y8u</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17-09-2026 20:00 UTC</t>
+          <t>17-09-2026 18:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Organon Announces Two Her Health Grants in India to Support Adolescent Girls Health in Bihar and Womens Contraceptive Access in Uttar Pradesh</t>
+          <t>The Drugs and Devices Have Been on the Market for Years. But FDA-Ordered Studies Still Aren’t Done.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The Tribune</t>
+          <t>KFF Health News</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/organon-announces-two-her-health-grants-in-india-to-support-adolescent-girls-health-in-bihar-and-womens-contraceptive-access-in-uttar-pradesh/</t>
+          <t>https://kffhealthnews.org/health-industry/fda-approval-drugs-medical-devices-postmarket-studies-safety-delays-amgen-tavneos/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18-09-2026 07:12 UTC</t>
+          <t>18-09-2026 09:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Organon Backs Women’s Health Efforts Across India</t>
+          <t>Amgen releases roadmap for post-cardiac care</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pharmacy Business</t>
+          <t>Pharma in Focus</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pharmacy.biz/organon-womens-health-support-india/</t>
+          <t>https://pharmainfocus.com.au/article.php?newsid=25744</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17-09-2026 13:35 UTC</t>
+          <t>18-09-2026 00:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sandoz approved for semaglutide sales in Canada</t>
+          <t>Ticket registration opens for Amgen Irish Open at K Club 2027</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>medwatch.com</t>
+          <t>Kildare Live</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://medwatch.com/News/Pharma___Biotech/article19655814.ece</t>
+          <t>https://www.leinsterleader.ie/sport/ticket-registration-opens-for-amgen-irish-open-at-k-club-2027-9078090</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18-09-2026 07:05 UTC</t>
+          <t>17-09-2026 16:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SK On, L&amp;F Form LFP Supply Alliance Against China</t>
+          <t>COMMENT: Shane Lowry's Amgen Irish Open win lifts all our hearts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>Offaly Live</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277288</t>
+          <t>https://www.offalyexpress.ie/news/opinion/comment-shane-lowrys-amgen-irish-open-win-lifts-all-our-hearts-9074549</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18-09-2026 03:09 UTC</t>
+          <t>17-09-2026 20:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Holiday on September 18, 2026 — Bamboo Day: Interesting Facts About This Unusual Plant</t>
+          <t>FDA Reduces Monitoring Time for First Two Tarlatamab Doses</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UA.NEWS</t>
+          <t>Pharmacy Times</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://ua.news/en/world/sviato-18-veresnia-den-bambuka-tsikavi-fakti-pro-nezvichainu-roslinu</t>
+          <t>https://www.pharmacytimes.com/view/fda-reduces-monitoring-time-for-first-two-tarlatamab-doses</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18-09-2026 06:11 UTC</t>
+          <t>17-09-2026 17:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PhytoFoundry emerges from stealth with plant cell culture platform targeting high value bioactives</t>
+          <t>The Evolving Law of Enablement: Federal Circuit Decisions in Wyeth and Teva Form a “Yin and Yang” Framework</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AgFunderNews</t>
+          <t>JD Supra</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://agfundernews.com/phytofoundry-targets-cosmetics-with-plant-cell-culture-platform-shaped-by-past-lessons</t>
+          <t>https://www.jdsupra.com/legalnews/the-evolving-law-of-enablement-federal-5015742/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17-09-2026 16:27 UTC</t>
+          <t>17-09-2026 17:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EnergyPathways &amp; Hycamite Hydrogen Graphite Plant UK</t>
+          <t>Power rallies to make fast start in Asheville</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fuel Cells Works</t>
+          <t>RTE.ie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://fuelcellsworks.com/2026/09/17/h2/energypathways-and-hycamite-to-advance-hydrogen-and-graphite-production-plant-in-uk</t>
+          <t>https://www.rte.ie/sport/golf/2026/0917/1592004-power-rallies-to-make-fast-start-in-asheville/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17-09-2026 12:58 UTC</t>
+          <t>17-09-2026 22:02 UTC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Ghosts of Chernobyl</t>
+          <t>Organon Announces Two Her Health Grants in India to Support Adolescent Girls Health in Bihar and Womens Contraceptive Access in Uttar Pradesh</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Telos-eu.</t>
+          <t>The Tribune</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>http://www.telos-eu.com/en/the-ghosts-of-chernobyl.html</t>
+          <t>https://www.tribuneindia.com/news/business/organon-announces-two-her-health-grants-in-india-to-support-adolescent-girls-health-in-bihar-and-womens-contraceptive-access-in-uttar-pradesh/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17-09-2026 15:01 UTC</t>
+          <t>18-09-2026 07:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Do Plant Proteins Increase Uric Acid? Expert Weighs In</t>
+          <t>Sandoz approved for semaglutide sales in Canada</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Onlymyhealth</t>
+          <t>medwatch.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.onlymyhealth.com/can-plant-protein-increase-your-uric-acid-levels-expert-explains-12977850410</t>
+          <t>https://medwatch.com/News/Pharma___Biotech/article19655814.ece</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17-09-2026 13:31 UTC</t>
+          <t>18-09-2026 07:05 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10 Flowering Bulbs to Plant in September—Before the Ground Gets Too Cold</t>
+          <t>Tamil Nadu's Thoothukudi Port Floats Tender For Green Hydrogen Plant, Fuel Station</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>veranda.com</t>
+          <t>Swarajya</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.veranda.com/outdoor-garden/a73779126/bulbs-to-plant-september-before-ground-gets-too-cold/</t>
+          <t>https://swarajyamag.com/news-brief/tamil-nadus-thoothukudi-port-floats-tender-for-green-hydrogen-plant-fuel-station</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17-09-2026 21:52 UTC</t>
+          <t>18-09-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tyre Pyrolysis Plant Setup in India: Feasibility Report</t>
+          <t>Azerbaijan's 100 MW Gobustan Solar Plant Starts Operation - News and Statistics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IMARC Group</t>
+          <t>indexbox.io</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.imarcgroup.com/insight/tyre-pyrolysis-plant-setup-india</t>
+          <t>https://www.indexbox.io/blog/azerbaijans-first-auction-backed-100-mw-gobustan-solar-plant-begins-operation/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>17-09-2026 07:51 UTC</t>
+          <t>18-09-2026 11:34 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wacker Chemie disappointed by US polysilicon policy, sets new goals</t>
+          <t>A harvest for the wild: how responsible wild harvesting helps regeneration</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>discoverwildlife.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/wacker-chemie-disappointed-by-us-polysilicon-policy-sets-new-goals-2026-09-17/</t>
+          <t>https://www.discoverwildlife.com/environment/a-harvest-for-the-wild-how-responsible-plant-gathering-helps-protect-nature</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17-09-2026 15:42 UTC</t>
+          <t>18-09-2026 09:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FORM NO. 169 EDITABLE WORD FORMAT</t>
+          <t>Bio-Active Peptides Market</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ctn press</t>
+          <t>Future Market Insights</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://cevnews.in/2026/09/income-tax-department-extends-important-deadlines-up-to-31-march-2027/</t>
+          <t>https://www.futuremarketinsights.com/reports/bio-active-peptides-market</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18-09-2026 04:12 UTC</t>
+          <t>17-09-2026 18:30 UTC</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Planting Green Roofs for Biophilic Effects</t>
+          <t>SK On, L&amp;F Form LFP Supply Alliance Against China</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Living Architecture Monitor</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://livingarchitecturemonitor.com/articles/planting-green-roofs-for-biophilic-effects</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277288</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17-09-2026 09:01 UTC</t>
+          <t>18-09-2026 03:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Clove at first bite</t>
+          <t>How soybeans took over the American diet – without anyone noticing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kirksville Daily Express</t>
+          <t>Hot Springs Village Voice</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>http://www.kirksvilledailyexpress.com/stories/clove-at-first-bite,32741</t>
+          <t>http://www.hsvvoice.com/premium/theconversation/stories/how-soybeans-took-over-the-american-diet-without-anyonenoticing,156502</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17-09-2026 21:23 UTC</t>
+          <t>18-09-2026 11:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>McLaren Confirms First SUV, Second UK Factory and In-House Engines</t>
+          <t>Why Most Plants Are More Automated Than Autonomous</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Autocar Professional</t>
+          <t>ARC Advisory Group</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.autocarpro.in/news/mclaren-confirms-first-suv-second-uk-factory-and-in-house-engines-134777</t>
+          <t>https://www.arcweb.com/industry-best-practices/why-most-plants-more-automated-autonomous</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17-09-2026 13:12 UTC</t>
+          <t>17-09-2026 18:44 UTC</t>
         </is>
       </c>
     </row>
@@ -1597,184 +1597,184 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Plant Development Services to bring two new hydrangea brands to North American consumers in 2027</t>
+          <t>Holiday on September 18, 2026 — Bamboo Day: Interesting Facts About This Unusual Plant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>nurserymag.com</t>
+          <t>UA.NEWS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.nurserymag.com/news/plant-development-services-two-new-hydrangea-brands-north-american-consumers-2027/</t>
+          <t>https://ua.news/en/world/sviato-18-veresnia-den-bambuka-tsikavi-fakti-pro-nezvichainu-roslinu</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>17-09-2026 15:30 UTC</t>
+          <t>18-09-2026 06:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Behind the Science: Reprogramming Resistance to Prostate Cancer Treatment</t>
+          <t>PhytoFoundry emerges from stealth with plant cell culture platform targeting high value bioactives</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>AgFunderNews</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pfizer.com/news/articles/behind_the_science_reprogramming_resistance_to_prostate_cancer_treatment</t>
+          <t>https://agfundernews.com/phytofoundry-targets-cosmetics-with-plant-cell-culture-platform-shaped-by-past-lessons</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17-09-2026 16:35 UTC</t>
+          <t>17-09-2026 16:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A year ago, President Trump pledged to lower Medicaid drug prices. Has that happened?</t>
+          <t>10 Flowering Bulbs to Plant in September—Before the Ground Gets Too Cold</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>veranda.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.npr.org/2026/09/17/nx-s1-5971066/trump-rx-medicaid-generous-drug-prices-pfizer-favored-nation</t>
+          <t>https://www.veranda.com/outdoor-garden/a73779126/bulbs-to-plant-september-before-ground-gets-too-cold/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17-09-2026 16:45 UTC</t>
+          <t>17-09-2026 21:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pfizer, BioNTech Secure Health Canada Authorization for Omicron XFG-Adapted COVID-19 Vaccine</t>
+          <t>Keppel planning subsea cable to transmit solar energy from Indonesia to Jurong Island plant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>straitstimes.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/pfizer-biontech-secure-health-canada-authorization-for-omicron-xfg-adapted-covid-19-vaccine-ce785bd3de8cf62c</t>
+          <t>https://www.straitstimes.com/singapore/environment/keppel-planning-for-subsea-cable-to-transmit-solar-energy-from-indonesia-to-jurong-island-plant</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>17-09-2026 19:04 UTC</t>
+          <t>18-09-2026 11:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Health Canada Authorizes Pfizer and BioNTech's Omicron XFG-Adapted COVID-19 Vaccine</t>
+          <t>Wacker Chemie disappointed by US polysilicon policy, sets new goals</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PR Newswire Canada</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.newswire.ca/news-releases/health-canada-authorizes-pfizer-and-biontech-s-omicron-xfg-adapted-covid-19-vaccine-854410179.html</t>
+          <t>https://www.reuters.com/business/wacker-chemie-disappointed-by-us-polysilicon-policy-sets-new-goals-2026-09-17/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17-09-2026 17:30 UTC</t>
+          <t>17-09-2026 15:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Full Fed. Circ. Won't Rethink Pfizer's Paxlovid IP Win</t>
+          <t>This coal plant won Basin Electric’s reliability trophy, but it doesn’t plan to return it.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>power-eng.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.law360.com/articles/2526734/full-fed-circ-won-t-rethink-pfizer-s-paxlovid-ip-win</t>
+          <t>https://www.power-eng.com/coal/this-coal-plant-won-basin-electrics-reliability-trophy-but-it-doesnt-plan-to-return-it/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>17-09-2026 22:11 UTC</t>
+          <t>17-09-2026 19:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Health Canada Authorizes Pfizer and BioNTech's Omicron XFG-Adapted COVID-19 Vaccine</t>
+          <t>Invasive Species in Colombia: The Animals and Plants Threatening Native Biodiversity</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>The Globe and Mail</t>
+          <t>ColombiaOne.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.theglobeandmail.com/investing/markets/stocks/PFE-N/pressreleases/4664673/health-canada-authorizes-pfizer-and-biontech-s-omicron-xfg-adapted-covid-19-vaccine/</t>
+          <t>https://colombiaone.com/2026/09/17/invasive-species-colombia-animals-plants-threatening-native-biodiversity/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>17-09-2026 17:46 UTC</t>
+          <t>17-09-2026 19:19 UTC</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Novo partners with Orbis, deepening investment in oral peptide drugs</t>
+          <t>Novartis India acquires Pfizer’s Minipress brands for $150 million</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BioPharma Dive</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.biopharmadive.com/news/novo-orbis-macrocyclic-peptides-oral-obesity-drugs/830645/</t>
+          <t>https://www.thepharmaletter.com/pharma-news/novartis-india-acquiresp-fizer-s-minipress-brands-for-150-million</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17-09-2026 19:37 UTC</t>
+          <t>18-09-2026 10:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bavarian Nordic names Tarja Stenvall as new CEO</t>
+          <t>EPO revokes key Moderna patent for mRNA vaccines</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Endpoints News</t>
+          <t>JUVE Patent</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://endpoints.news/bavarian-nordic-names-tarja-stenvall-as-new-ceo/</t>
+          <t>https://www.juve-patent.com/people-and-business/epo-revokes-key-moderna-patent-for-mrna-vaccines/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>17-09-2026 11:15 UTC</t>
+          <t>18-09-2026 13:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Never Too Late (or Too Early) for Lipid Lowering: STAREE and REACT</t>
+          <t>Behind the Science: Reprogramming Resistance to Prostate Cancer Treatment</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>pfizer.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.medscape.com/viewarticle/never-too-late-or-too-early-lipid-lowering-staree-and-react-2026a1000y8u?src=</t>
+          <t>https://www.pfizer.com/news/articles/behind_the_science_reprogramming_resistance_to_prostate_cancer_treatment</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>17-09-2026 18:20 UTC</t>
+          <t>17-09-2026 16:35 UTC</t>
         </is>
       </c>
     </row>
@@ -1867,292 +1867,292 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bavarian Nordic secures Sanofi, AZ vet to fill shoes of longtime CEO Paul Chaplin</t>
+          <t>US plans Medicaid most-favored-nation pricing for some drugs in all states</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/bavarian-nordic-secures-sanofi-az-vet-fill-shoes-longtime-ceo-paul-chaplin</t>
+          <t>https://www.reuters.com/world/us-plans-medicaid-most-favored-nation-pricing-some-drugs-all-states-semafor-2026-09-18/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>17-09-2026 15:16 UTC</t>
+          <t>18-09-2026 14:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Phase 3 Pediatric EMPAVELI Data Published in Clinical Journal of the American Society of Nephrology Show Reduction in Proteinuria and Stabilized Kidney Function in Adolescents with C3G or Primary IC-MPGN</t>
+          <t>A year ago, President Trump pledged to lower Medicaid drug prices. Has that happened?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://investors.biogen.com/news-releases/news-release-details/phase-3-pediatric-empaveli-data-published-clinical-journal</t>
+          <t>https://www.npr.org/2026/09/17/nx-s1-5971066/trump-rx-medicaid-generous-drug-prices-pfizer-favored-nation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17-09-2026 20:16 UTC</t>
+          <t>17-09-2026 16:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BIIB Looks 11.6% Overvalued on GF Value™</t>
+          <t>Pfizer, BioNTech Secure Health Canada Authorization for Omicron XFG-Adapted COVID-19 Vaccine</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/9086835/biib-looks-116-overvalued-on-gf-value</t>
+          <t>https://www.marketscreener.com/news/pfizer-biontech-secure-health-canada-authorization-for-omicron-xfg-adapted-covid-19-vaccine-ce785bd3de8cf62c</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17-09-2026 21:14 UTC</t>
+          <t>17-09-2026 19:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Roche's Lunsumio succeeds in long-awaited confirmatory follicular lymphoma study</t>
+          <t>Full Fed. Circ. Won't Rethink Pfizer's Paxlovid IP Win</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/8000583</t>
+          <t>https://www.law360.com/articles/2526734/full-fed-circ-won-t-rethink-pfizer-s-paxlovid-ip-win</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>17-09-2026 19:31 UTC</t>
+          <t>17-09-2026 22:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The top life sciences firms in Mass. employ more people than last year</t>
+          <t>Health Canada Authorizes Pfizer and BioNTech's Omicron XFG-Adapted COVID-19 Vaccine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>The Business Journals</t>
+          <t>PR Newswire Canada</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.bizjournals.com/boston/research/lists/2026/largest-life-sciences-companies-in-massachusetts.html</t>
+          <t>https://www.newswire.ca/news-releases/health-canada-authorizes-pfizer-and-biontech-s-omicron-xfg-adapted-covid-19-vaccine-854410179.html</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17-09-2026 13:00 UTC</t>
+          <t>17-09-2026 17:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SK Biopharm takes 1st Bio’s LRRK2/c-Abl inhibitor in $315M deal</t>
+          <t>[Market Movers Analysis] MedicusPharma surges on September 17: Pfizer ADC collaboration and SkinJect</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BioWorld News</t>
+          <t>Bitget</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.bioworld.com/articles/734140-sk-biopharm-takes-1st-bios-lrrk2-c-abl-inhibitor-in-315m-deal</t>
+          <t>https://www.bitget.com/amp/news/detail/12560605843347</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>17-09-2026 16:00 UTC</t>
+          <t>17-09-2026 21:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dr Reddy's signs India distribution deal for Takeda's Qdenga dengue vaccine</t>
+          <t>Pfizer BioNTech XFG vaccine receives Health Canada authorization</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>grafa.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/indias-dr-reddys-inks-distribution-agreement-with-takeda-dengue-vaccine-india-2026-09-18/</t>
+          <t>https://grafa.com/en/news/united-states/pfizer-biontech-omicron-xfg-covid-vaccine-health-canada-authorization</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>18-09-2026 03:41 UTC</t>
+          <t>17-09-2026 20:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dr Reddy’s to distribute Takeda’s QDENGA dengue vaccine in India</t>
+          <t>PFE Looks 4.5% Overvalued on GF Value™ Amid New U.S.-China Bioph</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Telangana Today</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://telanganatoday.com/dr-reddys-to-distribute-takedas-qdenga-dengue-vaccine-in-india</t>
+          <t>https://www.gurufocus.com/news/9087891/pfe-looks-45-overvalued-on-gf-value-amid-new-uschina-biopharma-investment-rules</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>18-09-2026 07:16 UTC</t>
+          <t>18-09-2026 12:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Labs Agrees To Licensing Deal With Gilead For Once-Yearly Lenacapavir To Prevent HIV</t>
+          <t>Pfizer, BioNTech Secure Health Canada Authorization for Omicron XFG-Adapted COVID-19 Vaccine</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/dr-reddy-s-labs-agrees-to-licensing-deal-with-gilead-for-once-yearly-lenacapavir-to-prevent-hiv</t>
+          <t>https://www.moomoo.com/news/post/76417964/pfizer-biontech-secure-health-canada-authorization-for-omicron-xfg-adapted</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>18-09-2026 03:38 UTC</t>
+          <t>17-09-2026 19:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dr Reddy's shares rise 2% after exclusive Qdenga distribution deal with Takeda</t>
+          <t>Phase 3 Pediatric EMPAVELI Data Published in Clinical Journal of the American Society of Nephrology Show Reduction in Proteinuria and Stabilized Kidney Function in Adolescents with C3G or Primary IC-MPGN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/markets/stocks/story/dr-reddys-shares-rise-2-after-exclusive-qdenga-distribution-deal-with-takeda-556331-2026-09-18</t>
+          <t>https://investors.biogen.com/news-releases/news-release-details/phase-3-pediatric-empaveli-data-published-clinical-journal</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>18-09-2026 05:27 UTC</t>
+          <t>17-09-2026 20:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Dr Reddy's, Takeda Partner for India's First Dengue Vaccine</t>
+          <t>BIIB Looks 11.6% Overvalued on GF Value™</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/dr-reddy-s-takeda-partner-for-india-s-first-dengue-vaccine/54548120260918</t>
+          <t>https://www.gurufocus.com/news/9086835/biib-looks-116-overvalued-on-gf-value</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>18-09-2026 07:04 UTC</t>
+          <t>17-09-2026 21:14 UTC</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2164,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Takeda and Dr Reddy’s to distribute QDENGA dengue vaccine in India</t>
+          <t>Dr Reddy's signs India distribution deal for Takeda's Qdenga dengue vaccine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>The News Mill</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2026/09/takeda-and-dr-reddys-to-distribute-qdenga-dengue-vaccine-in-india/</t>
+          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/indias-dr-reddys-inks-distribution-agreement-with-takeda-dengue-vaccine-india-2026-09-18/</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>18-09-2026 07:12 UTC</t>
+          <t>18-09-2026 03:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Shares Rise on Takeda Dengue Vaccine Deal</t>
+          <t>Dr Reddy’s, Takeda join hands to bring QDENGA dengue vaccine to India</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Equitypandit</t>
+          <t>Telangana Today</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.equitypandit.com/dr-reddys-shares-rise-on-takeda-dengue-vaccine-deal/</t>
+          <t>https://telanganatoday.com/dr-reddys-takeda-join-hands-to-bring-qdenga-dengue-vaccine-to-india</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>18-09-2026 06:10 UTC</t>
+          <t>18-09-2026 12:19 UTC</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2218,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dr Reddy's signs India distribution deal for Takeda's Qdenga dengue vaccine, shares rise over 2%</t>
+          <t>Dr. Reddy's Partners With Gilead For HIV Prevention And Takeda For Dengue Vaccine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Sahi</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/business/markets/dr-reddy-s-signs-india-distribution-deal-for-takeda-s-qdenga-dengue-vaccine-shares-rise-over-2-14032737.html</t>
+          <t>https://www.sahi.com/news/dr-reddy-s-labs-agrees-to-licensing-deal-with-gilead-for-once-yearly-lenacapavir-to-prevent-hiv</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>18-09-2026 04:59 UTC</t>
+          <t>18-09-2026 09:29 UTC</t>
         </is>
       </c>
     </row>
@@ -2245,22 +2245,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>India’s Dr Reddy’s inks distribution agreement with Takeda for dengue vaccine in India</t>
+          <t>Japan's Takeda Pharma partners with Dr. Reddy’s Labs for dengue vaccine distribution in India</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>The Mighty 790 KFGO</t>
+          <t>BioSpectrum Asia</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://kfgo.com/2026/09/17/indias-dr-reddys-inks-distribution-agreement-with-takeda-for-dengue-vaccine-in-india/</t>
+          <t>https://www.biospectrumasia.com/news/49/28391/japans-takeda-pharma-partners-with-dr-reddys-labs-for-dengue-vaccine-distribution-in-india.html</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>18-09-2026 04:04 UTC</t>
+          <t>18-09-2026 07:55 UTC</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Why Did Dr Reddy's Shares Rise Nearly 2% In Trade Today? Key Details Inside</t>
+          <t>Dr. Reddy's Lab shares climb 3% on signing exclusive agreement to distribute dengue vaccine in India</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.ndtvprofit.com/markets/dr-reddys-share-price-today-exclusive-distribution-marketing-agreement-takeda-dengue-vaccine-qdenga-12062679</t>
+          <t>https://upstox.com/news/market-news/stocks/dr-reddy-s-lab-shares-climb-3-on-signing-exclusive-agreement-to-distribute-dengue-vaccine-in-india/article-200507/</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>18-09-2026 04:05 UTC</t>
+          <t>18-09-2026 08:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dr Reddy’s bags exclusive distribution rights of Takeda’s dengue vaccine QDENGA in India</t>
+          <t>Dr Reddy’s inks pact with Takeda for distribution of dengue vax Qdenga in India’s private market</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/news/national/dr-reddys-bags-exclusive-distribution-rights-of-takedas-dengue-vaccine-qdenga-in-india/article71479463.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/dr-reddys-inks-pact-with-takeda-for-distribution-of-dengue-vax-qdenga-in-indias-private-market/articleshow/134336216.cms</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>18-09-2026 05:30 UTC</t>
+          <t>18-09-2026 12:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2326,238 +2326,238 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dr Reddy's shares gain 2% after Takeda dengue vaccine distribution deal</t>
+          <t>India’s first dengue vaccine is coming: Dr Reddy’s ties up with Japan’s Takeda</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/market/dr-reddys-share-price-gains-takeda-qdenga-dengue-vaccine-distribution-deal-19993347.htm/amp</t>
+          <t>https://www.businesstoday.in/india/story/indias-first-dengue-vaccine-is-coming-dr-reddys-ties-up-with-japans-takeda-556473-2026-09-18</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>18-09-2026 04:56 UTC</t>
+          <t>18-09-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BioTecNika Times Newsletter 17-09-2026- ICON plc Internship, ₹1.27 Lakh FSL Jobs, Freshers Openings at Intas &amp; More</t>
+          <t>Dr Reddy’s shares jump 3% on deal with Takeda to distribute dengue vaccine Qdenga</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BioTecNika</t>
+          <t>Fortune India</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.biotecnika.org/2026/09/biotecnika-times-newsletter-17-09-2026/</t>
+          <t>https://www.fortuneindia.com/markets/dr-reddys-shares-jump-3-on-deal-with-takeda-to-distribute-dengue-vaccine-qdenga/159965</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>17-09-2026 13:18 UTC</t>
+          <t>18-09-2026 09:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Justices Told Fed. Circ. Erred In Veterinary Software Feud</t>
+          <t>Dr. Reddy’s to Roll Out Takeda’s Dengue Jab in India Next Year</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>Bloomberg.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.law360.com/healthcare-authority/digital-health-technology/articles/2526796/justices-told-fed-circ-erred-in-veterinary-software-feud</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-18/dr-reddy-s-to-roll-out-takeda-s-dengue-jab-in-india-next-year?srnd=prognosis</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>18-09-2026 00:21 UTC</t>
+          <t>18-09-2026 08:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Harsh Goenka, Kiran Mazumdar-Shaw criticise Fendi’s Rs 8.3 lakh ‘Navratri’ bag</t>
+          <t>India to Launch First Approved Dengue Vaccine Qdenga in 2027</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/trending/trending-in-india/fendi-rs-8-3-lakh-bag-indian-craftsmanship-debate-kiran-mazumdar-shaw-harsh-goenka-10882436/lite/</t>
+          <t>https://www.thehindu.com/business/india-to-launch-first-approved-dengue-vaccine-qdenga-in-2027/article71480215.ece</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17-09-2026 12:24 UTC</t>
+          <t>18-09-2026 11:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>‘When will luxury brands stop colonising Indian crafts?’: H…</t>
+          <t>Dr Reddy’s Shares Rise on Takeda Dengue Vaccine Deal</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GujaratSamachar English</t>
+          <t>equitypandit.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://english.gujaratsamachar.com/news/national/when-will-luxury-brands-stop-colonising-indian-crafts-harsh-goenka-kiran-mazumdar-shaw-slam-fendi-over-indian-rupee95-lakh-navratri-bag-63401233492</t>
+          <t>https://www.equitypandit.com/dr-reddys-shares-rise-on-takeda-dengue-vaccine-deal/</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>17-09-2026 09:40 UTC</t>
+          <t>18-09-2026 06:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FTSE rebalance: Meesho, Lenskart lead inflows; Biocon, Wipro out</t>
+          <t>Dr Reddy's, Takeda Partner for India's First Dengue Vaccine</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://businessupturn.com/finance/stock-market/ftse-september-rebalance-takes-effect-tomorrow-meesho-and-lenskart-lead-inflows-biocon-and-wipro-see-outflows/</t>
+          <t>https://money.rediff.com/news/market/dr-reddy-s-takeda-partner-for-india-s-first-dengue-vaccine/54548120260918</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>17-09-2026 10:50 UTC</t>
+          <t>18-09-2026 07:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>USFDA Inspection Ends With 1 Observation at Aurobindo Pharma's Apitoria API Facility</t>
+          <t>Dr Reddy’s to distribute Takeda’s dengue vaccine QDENGA in India’s private market from 2027</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Firstpost</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/usfda-inspection-ends-with-1-observation-at-aurobindo-pharmas-apitoria-api-facility-179458</t>
+          <t>https://www.firstpost.com/world/dr-reddys-to-distribute-takedas-dengue-vaccine-qdenga-in-indias-private-market-from-2027-14046897.html/amp</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17-09-2026 18:27 UTC</t>
+          <t>18-09-2026 12:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma (NSE: AUROPHARMA) Receives USFDA Approval for First Inhalation Aerosol Product</t>
+          <t>BioTecNika Times Newsletter 17-09-2026- ICON plc Internship, ₹1.27 Lakh FSL Jobs, Freshers Openings at Intas &amp; More</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>BioTecNika</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kalkine.co.in/article/healthcare/aurobindo-pharma-nse-auropharma-receives-usfda-approval-for-first-inhalation-aerosol-product</t>
+          <t>https://www.biotecnika.org/2026/09/biotecnika-times-newsletter-17-09-2026/</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17-09-2026 09:29 UTC</t>
+          <t>17-09-2026 21:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Closing Bell: Market snaps 2-day fall; Sensex up 333 pts, Nifty above 23,200</t>
+          <t>Justices Told Fed. Circ. Erred In Veterinary Software Feud</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IndiaIPO</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.indiaipo.in/news/detail/closing-bell-market-snaps-2-day-fall-sensex-up-333-pts-nifty-above-23200</t>
+          <t>https://www.law360.com/healthcare-authority/digital-health-technology/articles/2526796/justices-told-fed-circ-erred-in-veterinary-software-feud</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17-09-2026 08:35 UTC</t>
+          <t>18-09-2026 00:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2569,22 +2569,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nifty Pharma Today: Up 1.66% to 26,579.25</t>
+          <t>USFDA Inspection Ends With 1 Observation at Aurobindo Pharma's Apitoria API Facility</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://univest.in/blogs/nifty-pharma-today-closing-bell-2026</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/usfda-inspection-ends-with-1-observation-at-aurobindo-pharmas-apitoria-api-facility-179458</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>17-09-2026 16:26 UTC</t>
+          <t>17-09-2026 18:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,22 +2596,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rakovina Therapeutics Announces Appointment of New Scientific Advisory Board Member</t>
+          <t>Nifty Pharma Today: Up 1.66% to 26,579.25</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>sg.finance.yahoo.com</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/rakovina-therapeutics-announces-appointment-scientific-083000136.html</t>
+          <t>https://univest.in/blogs/nifty-pharma-today-closing-bell-2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>17-09-2026 08:30 UTC</t>
+          <t>17-09-2026 16:26 UTC</t>
         </is>
       </c>
     </row>
@@ -2623,22 +2623,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Alembic Pharma's Vadodara Bioequivalence Facility Gets USFDA Inspection Closure, EIR Issued</t>
+          <t>NIFTY50 gains for a third straight session on declining crude prices</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/alembic-pharmas-vadodara-bioequivalence-facility-gets-usfda-inspection-closure-eir-issued-179459</t>
+          <t>https://upstox.com/news/market-news/stocks/nifty-50-gains-for-a-third-straight-session-on-declining-crude-prices/article-200516/</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>17-09-2026 18:35 UTC</t>
+          <t>18-09-2026 10:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2650,22 +2650,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bulimia Nervosa Market: Steady Growth Amid Rising Diagnosis Rates and a Stagnant Pharmacological Pipeline Through 2036</t>
+          <t>Alembic Pharma's Vadodara Bioequivalence Facility Gets USFDA Inspection Closure, EIR Issued</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Barchart.com</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.barchart.com/press-releases/4664223/bulimia-nervosa-market-steady-growth-amid-rising-diagnosis-rates-and-a-stagnant-pharmacological-pipeline-through-2036</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/alembic-pharmas-vadodara-bioequivalence-facility-gets-usfda-inspection-closure-eir-issued-179459</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>17-09-2026 17:38 UTC</t>
+          <t>17-09-2026 18:35 UTC</t>
         </is>
       </c>
     </row>
@@ -2677,22 +2677,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Novartis Drops Experimental Amyotrophic Lateral Sclerosis Drug After Mid-Stage Trial Failure</t>
+          <t>Bulimia Nervosa Market: Steady Growth Amid Rising Diagnosis Rates and a Stagnant Pharmacological Pipeline Through 2036</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Barchart.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/novartis-drops-experimental-amyotrophic-lateral-sclerosis-drug-after-mid-stage-trial-failure-179455</t>
+          <t>https://www.barchart.com/press-releases/4664223/bulimia-nervosa-market-steady-growth-amid-rising-diagnosis-rates-and-a-stagnant-pharmacological-pipeline-through-2036</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17-09-2026 16:38 UTC</t>
+          <t>17-09-2026 17:38 UTC</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Health Ministry Proposes Schedule K Exemption, Boxed Warnings for Levonorgestrel Pills</t>
+          <t>Novartis Drops Experimental Amyotrophic Lateral Sclerosis Drug After Mid-Stage Trial Failure</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2714,66 +2714,66 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/health-ministry-proposes-schedule-k-exemption-boxed-warnings-for-levonorgestrel-pills-179460</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/novartis-drops-experimental-amyotrophic-lateral-sclerosis-drug-after-mid-stage-trial-failure-179455</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17-09-2026 14:00 UTC</t>
+          <t>17-09-2026 16:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Alkem launches NeuCeno for treatment of partial-onset seizures in adult patients</t>
+          <t>Indian patent office drafts new pharma guidelines to tighten scrutiny</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.expresspharma.in/amp/alkem-launches-neuceno-for-treatment-of-partial-onset-seizures-in-adult-patients/</t>
+          <t>https://www.thepharmaletter.com/pharma-news/indian-patent-office-drafts-new-pharma-guidelines-to-tighten-scrutiny</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17-09-2026 10:44 UTC</t>
+          <t>18-09-2026 13:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ProBio, Kun Tuo Partner to Accelerate Advancement of Innovative Therapies in China</t>
+          <t>BioTecNika Times-18-09-2026: Reliance Scholarships, BIRAC Young Professional Jobs, Freshers Jobs at Amneal &amp; Farelabs, &amp; More</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>BioTecNika</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/probio-kun-tuo-partner-to-accelerate-advancement-of-innovative-therapies-in-china/</t>
+          <t>https://www.biotecnika.org/2026/09/biotecnika-times-18-09-26/</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>17-09-2026 19:10 UTC</t>
+          <t>18-09-2026 13:52 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,22 +2785,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BMS and Ono sue Amgen to block proposed Opdivo biosimilar</t>
+          <t>Kincell Bio, Cellipont Merge to Form Kincellis Advanced Therapies</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biosimilars-news/bms-and-ono-sue-amgen-to-block-proposed-opdivo-biosimilar</t>
+          <t>https://www.contractpharma.com/breaking-news/kincell-bio-cellipont-merge-to-form-kincellis-advanced-therapies/</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>17-09-2026 12:54 UTC</t>
+          <t>17-09-2026 18:22 UTC</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Quotient Sciences Reports AI Clinical Trial Milestone</t>
+          <t>CND Life Sciences Opens Innovation Lab in Scottsdale</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/quotient-sciences-reports-ai-clinical-trial-milestone/</t>
+          <t>https://www.contractpharma.com/breaking-news/cnd-life-sciences-opens-innovation-lab-in-scottsdale/</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>17-09-2026 19:38 UTC</t>
+          <t>18-09-2026 12:58 UTC</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Charles River Launches Rapid Cell Banking Programs</t>
+          <t>ProBio, Kun Tuo Partner to Accelerate Advancement of Innovative Therapies in China</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/charles-river-launches-rapid-cell-banking-programs/</t>
+          <t>https://www.contractpharma.com/breaking-news/probio-kun-tuo-partner-to-accelerate-advancement-of-innovative-therapies-in-china/</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>17-09-2026 14:13 UTC</t>
+          <t>17-09-2026 19:10 UTC</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Upperton Gains MHRA Approval for Nottingham Sterile Manufacturing Site</t>
+          <t>Quotient Sciences Reports AI Clinical Trial Milestone</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/upperton-gains-mhra-approval-for-nottingham-sterile-manufacturing-site/</t>
+          <t>https://www.contractpharma.com/breaking-news/quotient-sciences-reports-ai-clinical-trial-milestone/</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17-09-2026 13:41 UTC</t>
+          <t>17-09-2026 19:38 UTC</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WuXi XDC to Out-License Proprietary Payload-Linker Technology Platform to Ona Therapeutics</t>
+          <t>Roche Genentech Innovation Center Boston Opens, Expanding Companies’ US Research Presence</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/wuxi-xdc-to-out-license-proprietary-payload-linker-technology-platform-to-ona-therapeutics/</t>
+          <t>https://www.contractpharma.com/breaking-news/roche-genentech-innovation-center-boston-opens-expanding-companies-us-research-presence/</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>17-09-2026 20:01 UTC</t>
+          <t>18-09-2026 14:42 UTC</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kincell Bio, Cellipont Merge to Form Kincellis Advanced Therapies</t>
+          <t>WuXi XDC to Out-License Proprietary Payload-Linker Technology Platform to Ona Therapeutics</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2930,39 +2930,39 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/kincell-bio-cellipont-merge-to-form-kincellis-advanced-therapies/</t>
+          <t>https://www.contractpharma.com/breaking-news/wuxi-xdc-to-out-license-proprietary-payload-linker-technology-platform-to-ona-therapeutics/</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>17-09-2026 18:22 UTC</t>
+          <t>17-09-2026 20:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SK Biopharma, 1STBIO Sign Parkinson’s Drug Deal</t>
+          <t>Samsung Galaxy S26 series prices increased by Rs 20,000 in India, check new prices</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/sk-biopharma-1stbio-sign-parkinsons-drug-deal/</t>
+          <t>https://www.indiatoday.in/technology/story/samsung-galaxy-s26-price-hike-india-new-prices-all-variants-september-18-2997502-2026-09-18</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>17-09-2026 12:56 UTC</t>
+          <t>18-09-2026 07:06 UTC</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Watch: QuantHunt on Reimagining Cybersecurity for the Quantum Era</t>
+          <t>Beyond the Factory Gates: How Samsung Chennai Plant Is Creating Opportunities for Small Businesses in Sriperumbudur</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/in/watch-quanthunt-on-reimagining-cybersecurity-for-the-quantum-era</t>
+          <t>https://news.samsung.com/in/beyond-the-factory-gates-how-samsung-chennai-plant-is-creating-opportunities-for-small-businesses-in-sriperumbudur</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>18-09-2026 04:03 UTC</t>
+          <t>18-09-2026 08:54 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 series prices increased by Rs 20,000 in India, check new prices</t>
+          <t>Why Choose the Duo When You Can Get Samsung’s Galaxy Z Flip 8 at a Lower Price</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>CNET</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/technology/story/samsung-galaxy-s26-price-hike-india-new-prices-all-variants-september-18-2997502-2026-09-18</t>
+          <t>https://www.cnet.com/deals/samsung-galaxy-z-flip-8-deals/</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>18-09-2026 07:06 UTC</t>
+          <t>18-09-2026 12:10 UTC</t>
         </is>
       </c>
     </row>
@@ -3055,22 +3055,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A07s Has A 50 MP Camera, 5,000 mAh Battery</t>
+          <t>Cooked: How Samsung Found A Kiwi Tim Cook To Fold Apple's Newest Launch</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rediff</t>
+          <t>BW Marketing World</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://m.rediff.com/amp/getahead/report/samsung-galaxy-a07s-has-a-50-mp-camera-5000-mah-battery-gadgets-and-gaming-listicles/20260918.htm</t>
+          <t>https://www.bwmarketingworld.com/article/samsung-trolls-apple-with-a-tim-cook-of-its-own-in-galaxy-z-fold-8-ad-624429</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>18-09-2026 04:24 UTC</t>
+          <t>18-09-2026 11:32 UTC</t>
         </is>
       </c>
     </row>
@@ -3082,22 +3082,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 Series Could Become More Expensive By Rs. 20,000 Starting Today: Check New Prices</t>
+          <t>Samsung Galaxy Z8 series ranked #1 in the foldable category: Consumer Reports</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>gadgetbridge.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/news/samsung-galaxy-s26-plus-ultra-price-hike-india-updated-prices-12062616</t>
+          <t>https://www.gadgetbridge.com/samsung-galaxy-z8-series-ranked-1-in-the-foldable-category-consumer-reports/</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>18-09-2026 03:45 UTC</t>
+          <t>18-09-2026 14:25 UTC</t>
         </is>
       </c>
     </row>
@@ -3109,22 +3109,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Samsung phones get September 2026 Google Play System update</t>
+          <t>Samsung Galaxy S26 Ultra, Galaxy S26 Price Hike of Rs 20,000</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>TelecomTalk</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/samsung-phones-get-september-2026-google-play-system-update/</t>
+          <t>https://telecomtalk.info/samsung-galaxy-s26-ultra-galaxy-s26-price/1011919/</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>17-09-2026 14:50 UTC</t>
+          <t>18-09-2026 05:30 UTC</t>
         </is>
       </c>
     </row>
@@ -3136,22 +3136,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26, S26 Ultra, Galaxy Z Fold 8 and Z Fold 8 Ultra price in India likely to be increased soon</t>
+          <t>Samsung Galaxy A18 4G: New Exynos 1610, Updates to 2032</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>gadgetbridge.com</t>
+          <t>Memeburn</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.gadgetbridge.com/samsung-galaxy-s26-s26-ultra-galaxy-z-fold-8-and-z-fold-8-ultra-price-in-india-likely-to-be-increased-soon/</t>
+          <t>https://memeburn.com/samsung-galaxy-a18-4g-specs-price-2/</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>18-09-2026 04:24 UTC</t>
+          <t>18-09-2026 09:34 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,22 +3163,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 Ultra, Galaxy S26 Price Hike of Rs 20,000</t>
+          <t>Samsung Fans Are Thoroughly Unimpressed by Apple’s Foldable Phone</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TelecomTalk</t>
+          <t>WSJ</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://telecomtalk.info/samsung-galaxy-s26-ultra-galaxy-s26-price/1011919/</t>
+          <t>https://www.wsj.com/tech/samsung-fans-are-thoroughly-unimpressed-by-apples-foldable-phone-0e6652fc</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>18-09-2026 05:30 UTC</t>
+          <t>18-09-2026 07:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3190,22 +3190,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Samsung cuts Galaxy Z Fold8, Fold8 Ultra EMIs by 25 percent with Galaxy Forever</t>
+          <t>How Samsung could drive up the cost of iPhones</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>91mobiles.com</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.91mobiles.com/hub/samsung-galaxy-z-fold8-ultra-emis-galaxy-forever/</t>
+          <t>https://www.sammobile.com/news/samsung-making-iphones-costlier-memory-chip-price-hikes/</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>17-09-2026 10:26 UTC</t>
+          <t>18-09-2026 10:38 UTC</t>
         </is>
       </c>
     </row>
@@ -3217,22 +3217,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>‘RAMageddon’ Strikes: Samsung Galaxy S26 Series Gets Massive Price Hike in India</t>
+          <t>Samsung Launches 2026 Bespoke AI Appliances in India With Gemini-Powered Family Hub Refrigerator</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Nokiamob</t>
+          <t>MySmartPrice</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://nokiamob.net/2026/09/18/ramageddon-strikes-samsung-galaxy-s26-series-gets-massive-price-hike-in-india/</t>
+          <t>https://www.mysmartprice.com/gear/appliances/appliances-news/samsung-launches-2026-bespoke-ai-appliances-in-india-with-gemini-powered-family-hub-refrigerator/</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>18-09-2026 05:54 UTC</t>
+          <t>18-09-2026 13:36 UTC</t>
         </is>
       </c>
     </row>
@@ -3244,22 +3244,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JOJO Ltd signs deal with Samsung to distribute channel on TV Plus</t>
+          <t>'Reheating our leftovers': Rivals use iPhone Duo buzz in advertising</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/jojo-ltd-signs-deal-samsung-distribute-channel-tv-plus/51259068</t>
+          <t>https://www.business-standard.com/technology/tech-news/apple-iphone-duo-samsung-motorola-foldable-advertising-rival-campaigns-126091801004_1.html</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>18-09-2026 05:47 UTC</t>
+          <t>18-09-2026 12:27 UTC</t>
         </is>
       </c>
     </row>
@@ -3271,22 +3271,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[Interview] The People Behind the Galaxy Z Series’ Camera Innovations ②: How Portrait Video Recreates the Look of Professional Camera Lenses</t>
+          <t>Best Samsung Galaxy phone deals: Save $250 at Amazon</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/my/interview-the-people-behind-the-galaxy-z-series-camera-innovations-%E2%91%A1-how-portrait-video-recreates-the-look-of-professional-camera-lenses</t>
+          <t>https://mashable.com/tech/sept-11-samsung-galaxy-phone-deals</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>18-09-2026 02:48 UTC</t>
+          <t>18-09-2026 09:10 UTC</t>
         </is>
       </c>
     </row>
@@ -3298,22 +3298,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Apple Agrees to Samsung’s Higher Memory Prices for 2027: What It Could Mean for iPhone Prices</t>
+          <t>Watch: QuantHunt on Reimagining Cybersecurity for the Quantum Era</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Gadgets 360</t>
+          <t>Samsung Global Newsroom</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.gadgets360.com/mobiles/news/apple-accepts-samsung-memory-price-hike-q1-2027-production-12063021</t>
+          <t>https://news.samsung.com/in/watch-quanthunt-on-reimagining-cybersecurity-for-the-quantum-era</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>18-09-2026 06:18 UTC</t>
+          <t>18-09-2026 04:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3325,22 +3325,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>The new iPhone is here, but you can buy the Samsung Galaxy S26 FE and get a $200 gift card for free</t>
+          <t>Samsung S26 Ultra price drops on Flipkart, available at the lowest</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://mashable.com/tech/sept-11-samsung-galaxy-gift-card-deal</t>
+          <t>https://www.indiatoday.in/visualstories/technology/samsung-s26-ultra-price-drops-on-flipkart-available-at-the-lowest-285836-18-09-2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>17-09-2026 23:39 UTC</t>
+          <t>18-09-2026 10:34 UTC</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://pulse.mk.co.kr/news/english/12156269</t>
+          <t>https://pulse.mk.co.kr/news/all/12156269</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3379,76 +3379,76 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Korea Cuts Prices of 80 Drugs, Saving 33.9 Billion Won</t>
+          <t>South Korea Cuts Prices on 80 Reimbursed Drugs by Average 4.6% Amid Prescription Surge, Saving ₩33.9 Billion</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/technology/2026/09/18/korea-cuts-prices-of-80-drugs-saving-339-billion-won</t>
+          <t>https://finance.biggo.com/news/77cf763b-c390-445d-9dca-6236ddd6902e</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>18-09-2026 01:53 UTC</t>
+          <t>18-09-2026 09:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Prestige Biopharma Obtains Marketing Authorization for 'Tuzuneu' in Trinidad and Tobago</t>
+          <t>Korea Cuts Prices of 80 Drugs, Saving 33.9 Billion Won</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/2026091809382068983</t>
+          <t>https://en.sedaily.com/technology/2026/09/18/korea-cuts-prices-of-80-drugs-saving-339-billion-won</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>18-09-2026 00:38 UTC</t>
+          <t>18-09-2026 01:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Prestige Biopharma</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
+          <t>Prestige Biopharma Obtains Marketing Authorization for 'Tuzuneu' in Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/litigation/astrazeneca-daiichi-breast-cancer-drug-cleared-nhs-use-england-2026-09-17/</t>
+          <t>https://www.asiae.co.kr/en/article/stock-disclosure/2026091809382068983</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>17-09-2026 15:07 UTC</t>
+          <t>18-09-2026 00:38 UTC</t>
         </is>
       </c>
     </row>
@@ -3460,22 +3460,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
+          <t>CHMP Recommends Post-Neoadjuvant Enhertu for HER2-Positive Early Breast Cancer</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Arab News</t>
+          <t>GenomeWeb</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.arabnews.com/world/astrazeneca-daiichi-breast-cancer-drug-cleared-for-nhs-use-in-england-3002134</t>
+          <t>https://www.genomeweb.com/precision-medicine/targeted-therapy/enhertu/gnw-chmp-breast-cancer-astrazeneca-daiichi-sankyo-20260918/</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>17-09-2026 16:46 UTC</t>
+          <t>18-09-2026 14:32 UTC</t>
         </is>
       </c>
     </row>
@@ -3487,22 +3487,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AstraZeneca and Daiichi Sankyo secure NHS England access for Enhertu breast cancer drug</t>
+          <t>AstraZeneca, Daiichi Sankyo's Enhertu Recommended for EU Approval for HER2 Positive Breast Cancer</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Traders Union</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://tradersunion.com/news/financial-news/show/3369162-enhertu-nhs-england-breast-cancer-access/</t>
+          <t>https://www.marketscreener.com/news/astrazeneca-daiichi-sankyo-s-enhertu-recommended-for-eu-approval-for-her2-positive-breast-cancer-ce785adada8ff527</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>17-09-2026 12:13 UTC</t>
+          <t>18-09-2026 12:38 UTC</t>
         </is>
       </c>
     </row>
@@ -3514,22 +3514,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
+          <t>Enhertu® Recommended for Approval in the EU by CHMP as Adjuvant Treatment for Patients with Residual Disease After Neoadjuvant Treatment for HER2 Positive Early Breast Cancer</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Investing News Network</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/astrazeneca-daiichi-breast-cancer-drug-cleared-for-nhs-use-in-england-ce785bd3dd88f124</t>
+          <t>https://investingnews.com/enhertu-r-recommended-for-approval-in-the-eu-by-chmp-as-adjuvant-treatment-for-patients-with-residual-disease-after-neoadjuvant-treatment-for-her2-positive-early-breast-cancer/</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>17-09-2026 11:39 UTC</t>
+          <t>18-09-2026 14:10 UTC</t>
         </is>
       </c>
     </row>
@@ -3546,17 +3546,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>islandpacket.com</t>
+          <t>Arab News</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.islandpacket.com/living/article317278373.html</t>
+          <t>https://www.arabnews.com/world/astrazeneca-daiichi-breast-cancer-drug-cleared-for-nhs-use-in-england-3002134</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>17-09-2026 11:32 UTC</t>
+          <t>17-09-2026 16:46 UTC</t>
         </is>
       </c>
     </row>
@@ -3568,22 +3568,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Fortis moves Supreme Court against Delhi High Court order</t>
+          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>WTVB</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/business/india-business/fortis-moves-supreme-court-against-delhi-high-court-order/articleshow/134309495.cms</t>
+          <t>https://wtvbam.com/2026/09/17/astrazeneca-daiichi-breast-cancer-drug-cleared-for-nhs-use-in-england/</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>17-09-2026 10:57 UTC</t>
+          <t>17-09-2026 15:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3595,22 +3595,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IHH Unit Fortis Files Supreme Court Petition Against Delhi High Court Order In Daiichi Proceedings</t>
+          <t>Enhertu receives EU recommendation for HER2-positive breast cancer</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BusinessToday Malaysia</t>
+          <t>grafa.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.com.my/2026/09/17/ihh-unit-fortis-files-supreme-court-against-delhi-high-court-order-in-daiichi-proceedings/</t>
+          <t>https://grafa.com/en/news/united-states/enhertu-eu-recommendation-her2-positive-breast-cancer</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>17-09-2026 10:19 UTC</t>
+          <t>18-09-2026 13:20 UTC</t>
         </is>
       </c>
     </row>
@@ -3622,22 +3622,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Kura Oncology Q2FY26 Results: Comzifti revenue hits $9.1 million</t>
+          <t>Grünenthal prices 850m euros of notes to refinance and fund expansion</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/kura-oncology-q2fy26-results-comzifti-revenue-hits-9-1-million/51187458</t>
+          <t>https://www.thepharmaletter.com/pharma-news/grunenthal-prices-850-million-euros-of-notes-to-refinance-and-fund-expansion</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>17-09-2026 10:54 UTC</t>
+          <t>18-09-2026 09:24 UTC</t>
         </is>
       </c>
     </row>
@@ -3703,22 +3703,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Hang Ten Systems Raises Another $53 Million in Seed Funding</t>
+          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Equitypandit</t>
+          <t>PR Newswire UK</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.equitypandit.com/hang-ten-systems-raises-another-53-million-in-seed-funding/</t>
+          <t>https://www.prnewswire.co.uk/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883167.html</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>17-09-2026 10:58 UTC</t>
+          <t>18-09-2026 10:28 UTC</t>
         </is>
       </c>
     </row>
@@ -3730,49 +3730,49 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA : Buy rating from UBS</t>
+          <t>Otsuka ICU Medical LLC Issues Voluntary Nationwide Recall of 0.9% Sodium Chloride Injection, USP Due To a Product Mix-up with 10 mEq Potassium Chloride Injection</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>finance.yahoo.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-buy-rating-from-ubs-ce785bd3da81f421</t>
+          <t>https://finance.yahoo.com/healthcare/articles/otsuka-icu-medical-llc-issues-210800118.html</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>17-09-2026 11:13 UTC</t>
+          <t>17-09-2026 21:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Otsuka ICU Medical LLC Issues Voluntary Nationwide Recall of 0.9% Sodium Chloride Injection, USP Due To a Product Mix-up with 10 mEq Potassium Chloride Injection</t>
+          <t>Panel Discussion: The new innovation economy: Building the ecosystem behind the molecule</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Express Pharma</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/otsuka-icu-medical-llc-issues-210800118.html</t>
+          <t>https://www.expresspharma.in/panel-discussion-the-new-innovation-economy-building-the-ecosystem-behind-the-molecule-25-aug-2026-blr/</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>17-09-2026 21:08 UTC</t>
+          <t>18-09-2026 07:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3811,22 +3811,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FDA Clears Phase 1b/2 Trial of CAR T-Cell Therapy C-CAR168 for Refractory Progressive Multiple Sclerosis</t>
+          <t>FDA approves first gene therapy for pediatric patients with Sanfilippo syndrome type A</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NeurologyLive</t>
+          <t>PharmaLive</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://www.neurologylive.com/view/fda-clears-c-car168-trial-refractory-progressive-multiple-sclerosis</t>
+          <t>https://www.pharmalive.com/fda-approves-first-gene-therapy-for-pediatric-patients-with-sanfilippo-syndrome-type-a/</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>17-09-2026 19:55 UTC</t>
+          <t>18-09-2026 13:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3838,22 +3838,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Legend names Ingrid Zhang as CEO</t>
+          <t>FDA Clears Phase 1b/2 Trial of CAR T-Cell Therapy C-CAR168 for Refractory Progressive Multiple Sclerosis</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>NeurologyLive</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biotech-news/legend-names-ingrid-zhang-as-ceo</t>
+          <t>https://www.neurologylive.com/view/fda-clears-c-car168-trial-refractory-progressive-multiple-sclerosis</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>17-09-2026 18:02 UTC</t>
+          <t>17-09-2026 19:55 UTC</t>
         </is>
       </c>
     </row>
@@ -3865,22 +3865,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bhavana Chivukula, Profiled By Influential Women, Advances Pharmaceutical Innovation Through Research And Manufacturing</t>
+          <t>Legend names Ingrid Zhang as CEO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EIN News</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://www.einnews.com/pr_news/943037449/bhavana-chivukula-profiled-by-influential-women-advances-pharmaceutical-innovation-through-research-and-manufacturing</t>
+          <t>https://www.thepharmaletter.com/biotech-news/legend-names-ingrid-zhang-as-ceo</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>17-09-2026 13:22 UTC</t>
+          <t>17-09-2026 18:02 UTC</t>
         </is>
       </c>
     </row>
@@ -3892,22 +3892,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GlycoEra hires Astria dealmaker as chief business officer</t>
+          <t>Livzon Proposes New Non-Executive Director With Strong Pet Pharma Credentials</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>http://www.thepharmaletter.com/biotech-news/glycoera-hires-astria-dealmaker-as-chief-business-officer</t>
+          <t>https://www.tipranks.com/news/company-announcements/livzon-proposes-new-non-executive-director-with-strong-pet-pharma-credentials</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>17-09-2026 08:57 UTC</t>
+          <t>18-09-2026 09:15 UTC</t>
         </is>
       </c>
     </row>
@@ -3919,29 +3919,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Teva Seeks Ruling Against J&amp;J Bid to Block Simponi Biosimilars</t>
+          <t>Sandoz Adds First Hemophilia Biosimilar In Bio100 Expansion</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bloomberg Law News</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.bloomberglaw.com/health-law-and-business/teva-seeks-ruling-against-j-j-bid-to-block-simponi-biosimilars</t>
+          <t>https://insights.citeline.com/generics-bulletin/business/deals/sandoz-adds-first-hemophilia-biosimilar-in-bio100-expansion-VXPZZ54UQ5A6XNCWO7YM3W6AFQ/</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>17-09-2026 15:20 UTC</t>
+          <t>18-09-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.bloomberglaw.com/ip-law/teva-seeks-ruling-against-j-j-bid-to-block-simponi-biosimilars</t>
+          <t>https://news.bloomberglaw.com/health-law-and-business/teva-seeks-ruling-against-j-j-bid-to-block-simponi-biosimilars</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3973,22 +3973,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>The Evolving Law of Enablement: Federal Circuit Decisions in Wyeth and Teva Form a “Yin and Yang” Framework</t>
+          <t>Delhi High Court says payments to overseas units aren't automatically taxable in India</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>JD Supra</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.jdsupra.com/legalnews/the-evolving-law-of-enablement-federal-5015742/</t>
+          <t>https://www.livemint.com/news/delhi-high-court-says-payments-to-overseas-units-arent-automatically-taxable-in-india-teva-ranbaxy-sun-11789705719136.html</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>17-09-2026 17:51 UTC</t>
+          <t>18-09-2026 09:25 UTC</t>
         </is>
       </c>
     </row>
@@ -4000,103 +4000,103 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Fall Into Savings With Deals From Deuter, La Sportiva, Teva, and More</t>
+          <t>The Evolving Law of Enablement: Federal Circuit Decisions in Wyeth and Teva Form a “Yin and Yang” Framework</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>GearJunkie</t>
+          <t>JD Supra</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://gearjunkie.com/deals/weekly-deals-9-17-26</t>
+          <t>https://www.jdsupra.com/legalnews/the-evolving-law-of-enablement-federal-5015742/</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>17-09-2026 19:50 UTC</t>
+          <t>17-09-2026 17:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Japan approves under-the-skin Keytruda made with Alteogen enzyme</t>
+          <t>Teva launches LongActingImpact.com to advance understanding of earlier, effective and uninterrupted Schizophrenia care</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Chain Drug Review</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33229</t>
+          <t>https://chaindrugreview.com/teva-launches-longactingimpact-com-to-advance-understanding-of-earlier-effective-and-uninterrupted-schizophrenia-care/</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>18-09-2026 03:33 UTC</t>
+          <t>17-09-2026 15:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>A decade leading retinal care, Eylea 8mg now lasts even longer and better, expert says</t>
+          <t>Teva Seeks Ruling Against J&amp;J Bid to Block Simponi Biosimilars</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Bloomberg Law News</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33231</t>
+          <t>https://news.bloomberglaw.com/ip-law/teva-seeks-ruling-against-j-j-bid-to-block-simponi-biosimilars</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>18-09-2026 03:47 UTC</t>
+          <t>17-09-2026 15:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Lantern Pharma to Present Open-Medicine AI — a Multi-Agentic Platform for End-to-End Therapeutic Development — Business Model, Roadmap, and Value Proposition on September 23</t>
+          <t>Fall Into Savings With Deals From Deuter, La Sportiva, Teva, and More</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>sg.finance.yahoo.com</t>
+          <t>GearJunkie</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/lantern-pharma-present-open-medicine-122000593.html</t>
+          <t>https://gearjunkie.com/deals/weekly-deals-9-17-26</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>17-09-2026 12:20 UTC</t>
+          <t>17-09-2026 19:50 UTC</t>
         </is>
       </c>
     </row>
@@ -4108,22 +4108,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>WuXi XDC Out-Licenses WuXiTecan-2 Payload-Linker Technology Platform to Ona Therapeutics to Advance Novel ADC Research and Development</t>
+          <t>Sandoz announces collaboration with mAbxience to expand patient access to life-enhancing biosimilar medicines</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>sg.finance.yahoo.com</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/wuxi-xdc-licenses-wuxitecan-2-080900462.html</t>
+          <t>https://www.sandoz.com/sandoz-announces-collaboration-mabxience-expand-patient-access-life-enhancing-biosimilar-medicines/</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>17-09-2026 08:09 UTC</t>
+          <t>18-09-2026 10:07 UTC</t>
         </is>
       </c>
     </row>
@@ -4135,184 +4135,184 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sandoz joins mAbxience to develop emicizumab biosimilar and expand haemophilia pipeline</t>
+          <t>Japan approves under-the-skin Keytruda made with Alteogen enzyme</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/sandoz-joins-mabxience-to-develop-emicizumab-biosimilar-and-expand-haemophilia-pipeline</t>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33229</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>18-09-2026 05:36 UTC</t>
+          <t>18-09-2026 03:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Hang Ten Systems Raises Another $53 Million in Seed Funding</t>
+          <t>A decade leading retinal care, Eylea 8mg now lasts even longer and better, expert says</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Equitypandit</t>
+          <t>Korea Biomedical Review</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://www.equitypandit.com/hang-ten-systems-raises-another-53-million-in-seed-funding/</t>
+          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33231</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>17-09-2026 10:58 UTC</t>
+          <t>18-09-2026 03:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA : Buy rating from UBS</t>
+          <t>Sandoz joins mAbxience to develop emicizumab biosimilar and expand haemophilia pipeline</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/fresenius-se-co-kgaa-buy-rating-from-ubs-ce785bd3da81f421</t>
+          <t>https://www.tipranks.com/news/company-announcements/sandoz-joins-mabxience-to-develop-emicizumab-biosimilar-and-expand-haemophilia-pipeline</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>17-09-2026 11:13 UTC</t>
+          <t>18-09-2026 05:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Polpharma Biologics</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Otsuka ICU Medical LLC Issues Voluntary Nationwide Recall of 0.9% Sodium Chloride Injection, USP Due To a Product Mix-up with 10 mEq Potassium Chloride Injection</t>
+          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>finance.yahoo.com</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/otsuka-icu-medical-llc-issues-210800118.html</t>
+          <t>https://finance.yahoo.com/healthcare/articles/mabxience-sandoz-sign-collaboration-agreement-101600978.html</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>17-09-2026 21:08 UTC</t>
+          <t>18-09-2026 10:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Polpharma Biologics</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[Opening Market] KOSPI Surges Past 6,860 on Foreign, Institutional Buying</t>
+          <t>CHMP recommends EU approval of Roche’s Ocrevus for children and adolescents with relapsing multiple sclerosis</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>finance.yahoo.com</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277274</t>
+          <t>https://finance.yahoo.com/healthcare/articles/chmp-recommends-eu-approval-roche-104500076.html</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>18-09-2026 01:47 UTC</t>
+          <t>18-09-2026 10:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Upperton Gains MHRA Approval for Nottingham Sterile Manufacturing Site</t>
+          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>PR Newswire UK</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/upperton-gains-mhra-approval-for-nottingham-sterile-manufacturing-site/</t>
+          <t>https://www.prnewswire.co.uk/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883167.html</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>17-09-2026 13:41 UTC</t>
+          <t>18-09-2026 10:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Samsung Biologics</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Colorful iPhone 18 series hits shelves</t>
+          <t>Otsuka ICU Medical LLC Issues Voluntary Nationwide Recall of 0.9% Sodium Chloride Injection, USP Due To a Product Mix-up with 10 mEq Potassium Chloride Injection</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>mbiz.heraldcorp.com</t>
+          <t>finance.yahoo.com</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://mbiz.heraldcorp.com/article/10878448</t>
+          <t>https://finance.yahoo.com/healthcare/articles/otsuka-icu-medical-llc-issues-210800118.html</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>18-09-2026 03:15 UTC</t>
+          <t>17-09-2026 21:08 UTC</t>
         </is>
       </c>
     </row>
@@ -4324,22 +4324,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Single-Use Bioprocess Connectors Market Forecast to 2035: Cell and Gene Therapy Demand Drives 12-16% CAGR</t>
+          <t>CDMOs/CMOs: The Key Moves in 2026</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>CHEManager</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/single-use-bioprocess-connectors-market-forecast-to-2035-cell-and-gene-therapy-demand-drives-12-16-cagr/</t>
+          <t>https://chemanager-online.com/en/news/cdmos-cmos-the-key-moves-in-2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>17-09-2026 13:06 UTC</t>
+          <t>18-09-2026 05:00 UTC</t>
         </is>
       </c>
     </row>
@@ -4351,22 +4351,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Personal data of 140 customers leaked from Kakao Games</t>
+          <t>[Closing Market] KOSPI Closes Up 2.66% As Foreigners Turn to Buy After 8 Sessions</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>mbiz.heraldcorp.com</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://mbiz.heraldcorp.com/article/10877550</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277339</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>17-09-2026 08:59 UTC</t>
+          <t>18-09-2026 09:19 UTC</t>
         </is>
       </c>
     </row>
@@ -4378,22 +4378,130 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Naver decides against acquiring stake in Baemin</t>
+          <t>KOSPI jumps 2.66% on semiconductor strength; Kosdaq also ends higher</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>mbiz.heraldcorp.com</t>
+          <t>디지털투데이</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://mbiz.heraldcorp.com/article/10877562</t>
+          <t>https://www.digitaltoday.co.kr/en/view/105507/kospi-jumps-2-66-percent-on-semiconductor-strength-kosdaq-also-ends-higher</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>17-09-2026 09:11 UTC</t>
+          <t>18-09-2026 06:58 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Foreigners Return as Net Buyers After 8 Sessions; Kospi Closes Up 2.66%</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>news.sbs.co.kr</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://news.sbs.co.kr/english/article.do?news_id=N1008760711</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>18-09-2026 08:03 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>[Opening Market] KOSPI Surges Past 6,860 on Foreign, Institutional Buying</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Businesskorea</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277274</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>18-09-2026 01:47 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Gallery Belvi hosts three-artist show 'Our Hour'</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>헤럴드경제</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://mbiz.heraldcorp.com/article/10876603</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>18-09-2026 01:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Samsung Biologics</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>President Lee's press conference delayed 30 minutes, to start at 10:30 a.m.</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>헤럴드경제</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://mbiz.heraldcorp.com/article/10877806</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>17-09-2026 23:25 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz announces collaboration with mAbxience to expand patient access to life-enhancing biosimilar medicines</t>
+          <t>mAbxience, Sandoz Partner on Emicizumab Biosimilar Deal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.sandoz.com/sandoz-announces-collaboration-mabxience-expand-patient-access-life-enhancing-biosimilar-medicines/</t>
+          <t>https://www.biopharminternational.com/view/mabxience-sandoz-emicizumab-biosimilar-deal</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18-09-2026 10:07 UTC</t>
+          <t>18-09-2026 15:56 UTC</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M&amp;A Roundup: Lisata Therapeutics Acquires Marea Therapeutics, mAbxience Enters Collaboration with Sandoz</t>
+          <t>mAbxience, Sandoz to Collaborate on Emicizumab Biosimilar Candidate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pharmexec.com</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pharmexec.com/view/-lisata-therapeutics-acquires-marea-therapeutics-mabxience-collaboration-sandoz</t>
+          <t>https://www.contractpharma.com/breaking-news/mabxience-sandoz-to-collaborate-on-emicizumab-biosimilar-candidate/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18-09-2026 14:05 UTC</t>
+          <t>18-09-2026 18:10 UTC</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
+          <t>M&amp;A Roundup: Lisata Therapeutics Acquires Marea Therapeutics, mAbxience Enters Collaboration with Sandoz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Pharmaceutical Executive</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883156.html</t>
+          <t>https://www.pharmexec.com/view/-lisata-therapeutics-acquires-marea-therapeutics-mabxience-collaboration-sandoz</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18-09-2026 10:16 UTC</t>
+          <t>18-09-2026 15:18 UTC</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sandoz Canada receives Health Canada regulatory approval for (Pr)Sandoz® Semaglutide, a generic version of (Pr)Ozempic</t>
+          <t>Sandoz Appoints Priyaranjan Jha As Global Head Of GCCs And Country President India</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>BW People</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/sandoz-canada-receives-health-canada-regulatory-approval-for-prsandoz-semaglutide-a-generic-version-of-prozempic</t>
+          <t>https://www.bwpeople.in/article/sandoz-appoints-priyaranjan-jha-as-global-head-of-gccs-and-country-president-india-624443</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18-09-2026 12:57 UTC</t>
+          <t>18-09-2026 12:07 UTC</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sandoz Adds First Hemophilia Biosimilar In Bio100 Expansion</t>
+          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/business/deals/sandoz-adds-first-hemophilia-biosimilar-in-bio100-expansion-VXPZZ54UQ5A6XNCWO7YM3W6AFQ/</t>
+          <t>https://www.prnewswire.com/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883156.html</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18-09-2026 10:30 UTC</t>
+          <t>18-09-2026 10:16 UTC</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mAbxience and Sandoz partner to develop and com...</t>
+          <t>Sandoz Canada receives Health Canada regulatory approval for (Pr)Sandoz® Semaglutide, a generic version of (Pr)Ozempic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/mabxience-dan-sandoz-jalin-kerja-sama-percepat-akses-biosimilar-dunia</t>
+          <t>https://www.biospace.com/press-releases/sandoz-canada-receives-health-canada-regulatory-approval-for-prsandoz-semaglutide-a-generic-version-of-prozempic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18-09-2026 10:38 UTC</t>
+          <t>18-09-2026 12:57 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sandoz Gets Canada Approval for Generic Version of Ozempic</t>
+          <t>Sandoz Adds First Hemophilia Biosimilar In Bio100 Expansion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/health/pharma/sandoz-gets-canada-approval-for-generic-version-of-ozempic-8f8dce3c</t>
+          <t>https://insights.citeline.com/generics-bulletin/business/deals/sandoz-adds-first-hemophilia-biosimilar-in-bio100-expansion-VXPZZ54UQ5A6XNCWO7YM3W6AFQ/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18-09-2026 05:44 UTC</t>
+          <t>18-09-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sandoz receives regulatory approval for generic semaglutide in Canada, paving way to expand patient access to key GLP-1 medicine</t>
+          <t>mAbxience and Sandoz partner to develop and com...</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>pluang.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.sandoz.com/sandoz-receives-regulatory-approval-generic-semaglutide-canada-paving-way-expand-patient-access-key/</t>
+          <t>https://pluang.com/en/news-feed/mabxience-dan-sandoz-jalin-kerja-sama-percepat-akses-biosimilar-dunia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18-09-2026 05:21 UTC</t>
+          <t>18-09-2026 10:38 UTC</t>
         </is>
       </c>
     </row>
@@ -728,135 +728,135 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandoz approved for semaglutide sales in Canada</t>
+          <t>CHMP's September meeting highlights</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>medwatch.com</t>
+          <t>AllSci</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://medwatch.com/News/Pharma___Biotech/article19655814.ece</t>
+          <t>https://allsci.com/news/tecvayli-chmp-opinion-recommends-johnson-johnsons/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18-09-2026 07:05 UTC</t>
+          <t>18-09-2026 16:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stada</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jensen Huang (Nvidia)</t>
+          <t>PMi Awards 2026 – the winners and highlights</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>PMLiVE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://en.ilsole24ore.com/art/jensen-huang-nvidia-AJuKjKGB</t>
+          <t>https://pmlive.com/blogs/pmi-awards-2026-the-winners-and-highlights/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17-09-2026 18:27 UTC</t>
+          <t>18-09-2026 15:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim launches PED Essentials for patient data collection</t>
+          <t>Trial Supports New Method for Easing IUD Insertion Pain</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>The Clinical Trial Vanguard</t>
+          <t>MedPage Today</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.clinicaltrialvanguard.com/news/boehringer-ingelheim-launches-ped-essentials-for-patient-data-collection/</t>
+          <t>https://www.medpagetoday.com/obgyn/generalobgyn/123073</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18-09-2026 06:42 UTC</t>
+          <t>18-09-2026 21:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Siemens Healthineers, Boehringer team up on blood-based liver screening</t>
+          <t>Poisons board moves to tighten controls on fake medical products</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>People Daily</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33245</t>
+          <t>https://peopledaily.digital/news/poisons-board-moves-to-tighten-controls-on-fake-medical-products</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18-09-2026 07:07 UTC</t>
+          <t>18-09-2026 15:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Boehringer discontinues Phase III EASi-KIDNEY trial of vicadrostat</t>
+          <t>Rheumatoid Arthritis Pipeline Insight 2026: 75+ Companies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/boehringer-halts-phase-iii-kidney-trial-of-vicadrostat-combination</t>
+          <t>https://www.openpr.com/news/4636200/rheumatoid-arthritis-pipeline-insight-2026-75-companies</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18-09-2026 08:33 UTC</t>
+          <t>18-09-2026 20:30 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spot CKD: A Moment That Shouldn’t Be Missed</t>
+          <t>Supporting udder health through every stage of the dairy lifecycle</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CSRwire</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://csrwire.com/press-release/spot-ckd-moment-shouldnt-be-missed/</t>
+          <t>https://www.boehringer-ingelheim.com/ie/animal-health/featured-stories/supporting-udder-health-dairy-herds</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17-09-2026 20:05 UTC</t>
+          <t>19-09-2026 00:11 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim launches PED Essentials, an online learning resource that gives patients a stronger voice</t>
+          <t>Lykke Hinsch Gylvin։ Patient Perspectives Deserve More Than a Place in the Conversation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>indovizka.com</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://indovizka.com/news/detail/22834/boehringer-ingelheim-launches-ped-essentials-an-online-learning-resource-that-gives-patients-a-stronger-voice</t>
+          <t>https://oncodaily.com/voices/lykke-hinsch-gylvin-588521</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18-09-2026 00:48 UTC</t>
+          <t>18-09-2026 15:37 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pyrantel Pamoate Suspension Market Forecast to 2035: Growth Driven by Expanding Livestock and Equine Populations</t>
+          <t>Boehringer discontinues Phase III EASi-KIDNEY trial of vicadrostat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>indexbox.io</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/pyrantel-pamoate-suspension-market-forecast-to-2035-growth-driven-by-expanding-livestock-and-equine-populations/</t>
+          <t>https://www.thepharmaletter.com/pharma-news/boehringer-halts-phase-iii-kidney-trial-of-vicadrostat-combination</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18-09-2026 11:06 UTC</t>
+          <t>18-09-2026 08:33 UTC</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Certara Launches External Data Accelerator for CDISC Standards Compliance</t>
+          <t>Praziquantel Antiparasitic Formulations Market To 2035: Livestock Intensification Drives Growth - News and Statistics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The Clinical Trial Vanguard</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.clinicaltrialvanguard.com/news/certara-launches-external-data-accelerator-for-cdisc-standards-compliance/</t>
+          <t>https://www.indexbox.io/blog/praziquantel-antiparasitic-formulations-market-forecast-to-2035-livestock-intensification-in-africa-and-asia-drives-4-6-cagr/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18-09-2026 07:32 UTC</t>
+          <t>18-09-2026 15:51 UTC</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SkinCure Analysis: Nonmelanoma Skin Cancer Cases 42% Higher Than Official Count</t>
+          <t>Dersimelagon NDA Accepted by FDA with Priority Review for EPP, XLP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>The Clinical Trial Vanguard</t>
+          <t>dermatologytimes.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.clinicaltrialvanguard.com/news/skincure-analysis-nonmelanoma-skin-cancer-cases-42-higher-than-official-count/</t>
+          <t>http://dermatologytimes.com/view/dersimelagon-nda-accepted-fda-priority-review-epp-xlp</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18-09-2026 07:32 UTC</t>
+          <t>18-09-2026 13:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New licensed treatment for equine insulin dysregulation launches in Great Britain</t>
+          <t>Kelli Lynch Appointed Vice President, Integrated Communications, Cardiovascular Portfolio &amp; Global Commercial Office at Medtronic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>yourhorse.co.uk</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.yourhorse.co.uk/news/new-licensed-treatment-for-equine-insulin-dysregulation-launches-in-great-britain/</t>
+          <t>https://hrtoday.in/kelli-lynch-appointed-vice-president-integrated-communications-cardiovascular-portfolio-global-commercial-office-at-medtronic/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18-09-2026 05:08 UTC</t>
+          <t>18-09-2026 11:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Generic drugs get a legal boost from Supreme Court ruling, law firm analysis finds</t>
+          <t>Lifebit to provide research platform for NIHR BioResource</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>digitalhealth.net</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.medicaleconomics.com/view/generic-drugs-get-a-legal-boost-from-supreme-court-ruling-law-firm-analysis-finds</t>
+          <t>https://www.digitalhealth.net/2026/09/lifebit-to-provide-research-platform-for-nihr-bioresource/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17-09-2026 18:27 UTC</t>
+          <t>18-09-2026 14:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Senate Hearing Targets U.S. Generic Drug Manufacturing</t>
+          <t>Trump: Most-Favored-Nation Drug Pricing Being Extended to State Medicaid Programs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Legis1</t>
+          <t>breitbart.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://legis1.com/news/generic-drug-manufacturing-senate-panel-will</t>
+          <t>https://www.breitbart.com/politics/2026/09/18/trump-most-favored-nation-drug-pricing-being-extended-to-state-medicaid-programs/amp/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17-09-2026 18:03 UTC</t>
+          <t>18-09-2026 23:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>€176,000 raised for Make-A-Wish® Ireland at the Amgen Irish Open</t>
+          <t>Iran Faces Influenza Vaccine Shortage as Procurement Stalls</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DP World Tour</t>
+          <t>NAVLIN DAILY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.europeantour.com/dpworld-tour/news/articles/detail/176-000-raised-for-make-a-wish-ireland-at-the-amgen-irish-open/</t>
+          <t>https://www.navlindaily.com/article/31915/iran-faces-influenza-vaccine-shortage-as-procurement-stalls</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18-09-2026 10:14 UTC</t>
+          <t>18-09-2026 09:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Amgen Leads Strong Commercial Field into Irish Open Week at Doonbeg</t>
+          <t>35th Abu Dhabi International Book Fair highlights shared values between UAE and China</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sport for Business</t>
+          <t>wam.ae</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://sportforbusiness.com/amgen-leads-strong-commercial-field-into-irish-open-week-at-doonbeg/</t>
+          <t>https://www.wam.ae/en/article/c2b4u2c-35th-abu-dhabi-international-book-fair-highlights</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18-09-2026 10:29 UTC</t>
+          <t>18-09-2026 13:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Never Too Late (or Too Early) for Lipid Lowering: STAREE and REACT</t>
+          <t>€176,000 raised for Make-A-Wish® Ireland at the Amgen Irish Open</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>europeantour.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.medscape.com/viewarticle/never-too-late-or-too-early-lipid-lowering-staree-and-react-2026a1000y8u</t>
+          <t>https://www.europeantour.com/dpworld-tour/news/articles/detail/176-000-raised-for-make-a-wish-ireland-at-the-amgen-irish-open/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17-09-2026 18:21 UTC</t>
+          <t>18-09-2026 10:14 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Drugs and Devices Have Been on the Market for Years. But FDA-Ordered Studies Still Aren’t Done.</t>
+          <t>Amgen Leads Strong Commercial Field into Irish Open Week at Doonbeg</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KFF Health News</t>
+          <t>sportforbusiness.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://kffhealthnews.org/health-industry/fda-approval-drugs-medical-devices-postmarket-studies-safety-delays-amgen-tavneos/</t>
+          <t>https://sportforbusiness.com/amgen-leads-strong-commercial-field-into-irish-open-week-at-doonbeg/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18-09-2026 09:03 UTC</t>
+          <t>18-09-2026 21:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Amgen releases roadmap for post-cardiac care</t>
+          <t>Litigation Trends to Watch: Sports Litigation Heats Up. Plus, Amgen's Data Security Troubles.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pharma in Focus</t>
+          <t>Law.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://pharmainfocus.com.au/article.php?newsid=25744</t>
+          <t>https://www.law.com/2026/09/18/litigation-trends-to-watch-sports-litigation-heats-up-plus-amgens-data-security-troubles/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18-09-2026 00:44 UTC</t>
+          <t>18-09-2026 18:25 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ticket registration opens for Amgen Irish Open at K Club 2027</t>
+          <t>Luke Thomas: What Do Children With Cancer Need Most?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kildare Live</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.leinsterleader.ie/sport/ticket-registration-opens-for-amgen-irish-open-at-k-club-2027-9078090</t>
+          <t>https://oncodaily.com/voices/luke-thomas-588680</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17-09-2026 16:00 UTC</t>
+          <t>18-09-2026 19:22 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>COMMENT: Shane Lowry's Amgen Irish Open win lifts all our hearts</t>
+          <t>RFK Jr. Eyes Wireless, RF Radiation; Cancer by the Month; AI for Cancer Symptoms</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Offaly Live</t>
+          <t>MedPage Today</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.offalyexpress.ie/news/opinion/comment-shane-lowrys-amgen-irish-open-win-lifts-all-our-hearts-9074549</t>
+          <t>https://www.medpagetoday.com/hematologyoncology/othercancers/123066</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17-09-2026 20:00 UTC</t>
+          <t>18-09-2026 22:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FDA Reduces Monitoring Time for First Two Tarlatamab Doses</t>
+          <t>The Drugs and Devices Have Been on the Market for Years. But FDA-Ordered Studies Still Aren’t Done.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pharmacy Times</t>
+          <t>KFF Health News</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pharmacytimes.com/view/fda-reduces-monitoring-time-for-first-two-tarlatamab-doses</t>
+          <t>https://kffhealthnews.org/health-industry/fda-approval-drugs-medical-devices-postmarket-studies-safety-delays-amgen-tavneos/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17-09-2026 17:34 UTC</t>
+          <t>18-09-2026 09:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,49 +1300,49 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Evolving Law of Enablement: Federal Circuit Decisions in Wyeth and Teva Form a “Yin and Yang” Framework</t>
+          <t>Trump says his son told him he will repay Russian oligarch for wedding parties</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JD Supra</t>
+          <t>The Detroit News</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.jdsupra.com/legalnews/the-evolving-law-of-enablement-federal-5015742/</t>
+          <t>https://www.detroitnews.com/story/news/nation/2026/09/18/trump-says-son-told-him-hell-pay-back-russian-oligarch-for-wedding/91832027007/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17-09-2026 17:51 UTC</t>
+          <t>18-09-2026 22:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Power rallies to make fast start in Asheville</t>
+          <t>Sun Pharma to acquire US-based Organon in nearly $11.75 billion deal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RTE.ie</t>
+          <t>DD News</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.rte.ie/sport/golf/2026/0917/1592004-power-rallies-to-make-fast-start-in-asheville/</t>
+          <t>https://ddnews.gov.in/en/sun-pharma-to-acquire-us-based-organon-in-nearly-11-75-billion-deal/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17-09-2026 22:02 UTC</t>
+          <t>18-09-2026 18:35 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,49 +1354,49 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Organon Announces Two Her Health Grants in India to Support Adolescent Girls Health in Bihar and Womens Contraceptive Access in Uttar Pradesh</t>
+          <t>Organon Announces Two Her Health Grants in India to Support Adolescent Girls' Health in Bihar and Women's Contraceptive Access in Uttar Pradesh</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The Tribune</t>
+          <t>indiasnews.net</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/organon-announces-two-her-health-grants-in-india-to-support-adolescent-girls-health-in-bihar-and-womens-contraceptive-access-in-uttar-pradesh/</t>
+          <t>https://www.indiasnews.net/news/279315499/organon-announces-two-her-health-grants-in-india-to-support-adolescent-girls-health-in-bihar-and-women-contraceptive-access-in-uttar-pradesh</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18-09-2026 07:12 UTC</t>
+          <t>18-09-2026 18:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sandoz approved for semaglutide sales in Canada</t>
+          <t>EnergyPathways, Hycamite Advance UK Hydrogen and Graphite Plant</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>medwatch.com</t>
+          <t>ChemAnalyst</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://medwatch.com/News/Pharma___Biotech/article19655814.ece</t>
+          <t>https://www.chemanalyst.com/NewsAndDeals/NewsDetails/energypathways-hycamite-advance-uk-hydrogen-44547</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>18-09-2026 07:05 UTC</t>
+          <t>18-09-2026 13:36 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tamil Nadu's Thoothukudi Port Floats Tender For Green Hydrogen Plant, Fuel Station</t>
+          <t>46th Chess Olympiad: Team India continues winning run; Gukesh, Nihal, Humpy show top form</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Swarajya</t>
+          <t>Public TV English</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://swarajyamag.com/news-brief/tamil-nadus-thoothukudi-port-floats-tender-for-green-hydrogen-plant-fuel-station</t>
+          <t>https://english.publictv.in/46th-chess-olympiad-team-india-continues-winning-run-gukesh-nihal-humpy-show-top-form/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>18-09-2026 12:00 UTC</t>
+          <t>19-09-2026 07:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Azerbaijan's 100 MW Gobustan Solar Plant Starts Operation - News and Statistics</t>
+          <t>Tamil Nadu's Thoothukudi Port Floats Tender For Green Hydrogen Plant, Fuel Station</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>indexbox.io</t>
+          <t>Swarajya</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/azerbaijans-first-auction-backed-100-mw-gobustan-solar-plant-begins-operation/</t>
+          <t>https://swarajyamag.com/amp/story/news-brief%2Ftamil-nadus-thoothukudi-port-floats-tender-for-green-hydrogen-plant-fuel-station</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>18-09-2026 11:34 UTC</t>
+          <t>18-09-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A harvest for the wild: how responsible wild harvesting helps regeneration</t>
+          <t>Nurturing soil microbes improves nitrogen efficiency</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>discoverwildlife.com</t>
+          <t>Brownfield Ag News</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.discoverwildlife.com/environment/a-harvest-for-the-wild-how-responsible-plant-gathering-helps-protect-nature</t>
+          <t>https://www.brownfieldagnews.com/news/nurturing-soil-microbes-improves-nitrogen-efficiency/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18-09-2026 09:00 UTC</t>
+          <t>18-09-2026 15:57 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bio-Active Peptides Market</t>
+          <t>Watering plants lowers blood pressure and anxiety in older adults</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Future Market Insights</t>
+          <t>PsyPost</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.futuremarketinsights.com/reports/bio-active-peptides-market</t>
+          <t>https://www.psypost.org/watering-plants-lowers-blood-pressure-and-anxiety-in-older-adults/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>17-09-2026 18:30 UTC</t>
+          <t>18-09-2026 20:17 UTC</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SK On, L&amp;F Form LFP Supply Alliance Against China</t>
+          <t>Are tea, coffee, red meat and alcohol giving you dangerous levels of iron?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>1News</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277288</t>
+          <t>https://www.1news.co.nz/2026/09/19/are-tea-coffee-red-meat-and-alcohol-giving-you-dangerous-levels-of-iron/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>18-09-2026 03:09 UTC</t>
+          <t>19-09-2026 06:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>How soybeans took over the American diet – without anyone noticing</t>
+          <t>Hyundai E&amp;C to lead gov’t push for 100-megawatt green hydrogen plants</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hot Springs Village Voice</t>
+          <t>Hydrogen Central</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>http://www.hsvvoice.com/premium/theconversation/stories/how-soybeans-took-over-the-american-diet-without-anyonenoticing,156502</t>
+          <t>https://hydrogen-central.com/hyundai-ec-to-lead-govt-push-for-100-megawatt-green-hydrogen-plants/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18-09-2026 11:54 UTC</t>
+          <t>18-09-2026 17:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1570,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Why Most Plants Are More Automated Than Autonomous</t>
+          <t>Jerky goes plant-based</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ARC Advisory Group</t>
+          <t>NBC 5 Dallas-Fort Worth</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.arcweb.com/industry-best-practices/why-most-plants-more-automated-autonomous</t>
+          <t>https://www.nbcdfw.com/video/texas-today/jerky-goes-plant-based/4079183/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17-09-2026 18:44 UTC</t>
+          <t>18-09-2026 17:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Holiday on September 18, 2026 — Bamboo Day: Interesting Facts About This Unusual Plant</t>
+          <t>A harvest for the wild: how responsible wild harvesting helps regeneration</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UA.NEWS</t>
+          <t>BBC Wildlife Magazine</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://ua.news/en/world/sviato-18-veresnia-den-bambuka-tsikavi-fakti-pro-nezvichainu-roslinu</t>
+          <t>https://www.discoverwildlife.com/environment/a-harvest-for-the-wild-how-responsible-plant-gathering-helps-protect-nature</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18-09-2026 06:11 UTC</t>
+          <t>18-09-2026 09:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PhytoFoundry emerges from stealth with plant cell culture platform targeting high value bioactives</t>
+          <t>Rare earth recovery from industrial waste</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AgFunderNews</t>
+          <t>RECYCLING magazin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://agfundernews.com/phytofoundry-targets-cosmetics-with-plant-cell-culture-platform-shaped-by-past-lessons</t>
+          <t>https://www.recycling-magazine.com/en/31243/rare-earth-recovery-from-industrial-waste</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17-09-2026 16:27 UTC</t>
+          <t>18-09-2026 08:31 UTC</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10 Flowering Bulbs to Plant in September—Before the Ground Gets Too Cold</t>
+          <t>11 Plants To Leave Alone In Fall—Pruning Them Now Could Cost You Flowers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>veranda.com</t>
+          <t>Southern Living</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.veranda.com/outdoor-garden/a73779126/bulbs-to-plant-september-before-ground-gets-too-cold/</t>
+          <t>https://www.southernliving.com/plants-never-prune-in-fall-12128485</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17-09-2026 21:52 UTC</t>
+          <t>18-09-2026 22:39 UTC</t>
         </is>
       </c>
     </row>
@@ -1678,22 +1678,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Keppel planning subsea cable to transmit solar energy from Indonesia to Jurong Island plant</t>
+          <t>Why is the USW so afraid of the rank and file at National Steel Car?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>straitstimes.com</t>
+          <t>World Socialist Web Site</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.straitstimes.com/singapore/environment/keppel-planning-for-subsea-cable-to-transmit-solar-energy-from-indonesia-to-jurong-island-plant</t>
+          <t>https://www.wsws.org/en/articles/2026/09/19/yhzw-s19.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18-09-2026 11:30 UTC</t>
+          <t>19-09-2026 00:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1705,76 +1705,76 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wacker Chemie disappointed by US polysilicon policy, sets new goals</t>
+          <t>How soybeans took over the American diet – without anyone noticing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Hot Springs Village Voice</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/wacker-chemie-disappointed-by-us-polysilicon-policy-sets-new-goals-2026-09-17/</t>
+          <t>http://www.hsvvoice.com/premium/theconversation/stories/how-soybeans-took-over-the-american-diet-without-anyonenoticing,156502</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17-09-2026 15:42 UTC</t>
+          <t>18-09-2026 11:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>This coal plant won Basin Electric’s reliability trophy, but it doesn’t plan to return it.</t>
+          <t>Novartis India buys Pfizer's Minipress (prazosin) brands for USD 150M</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>power-eng.com</t>
+          <t>Dealroom</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.power-eng.com/coal/this-coal-plant-won-basin-electrics-reliability-trophy-but-it-doesnt-plan-to-return-it/</t>
+          <t>https://app.dealroom.co/news/note/novartis-india-buys-pfizer-s-minipress-prazosin-brands-for-usd-150m</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>17-09-2026 19:42 UTC</t>
+          <t>19-09-2026 07:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Invasive Species in Colombia: The Animals and Plants Threatening Native Biodiversity</t>
+          <t>Novartis India acquires Pfizer’s Minipress brands for $150 million</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ColombiaOne.com</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://colombiaone.com/2026/09/17/invasive-species-colombia-animals-plants-threatening-native-biodiversity/</t>
+          <t>https://www.thepharmaletter.com/pharma-news/novartis-india-acquiresp-fizer-s-minipress-brands-for-150-million</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>17-09-2026 19:19 UTC</t>
+          <t>18-09-2026 13:40 UTC</t>
         </is>
       </c>
     </row>
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Novartis India acquires Pfizer’s Minipress brands for $150 million</t>
+          <t>From Padcev to PF-08634404: Pfizer's Oncology Growth Push</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>qz.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/novartis-india-acquiresp-fizer-s-minipress-brands-for-150-million</t>
+          <t>https://qz.com/from-padcev-to-pf-08634404-pfizer-s-oncology-growth-push</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>18-09-2026 10:04 UTC</t>
+          <t>18-09-2026 14:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EPO revokes key Moderna patent for mRNA vaccines</t>
+          <t>Pfizer NSE:PFIZER Senior Management Change September 2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JUVE Patent</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.juve-patent.com/people-and-business/epo-revokes-key-moderna-patent-for-mrna-vaccines/</t>
+          <t>https://www.kalkine.co.in/article/announcements/pfizer-nsepfizer-who-is-leaving-the-senior-management-team-in-september-2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>18-09-2026 13:37 UTC</t>
+          <t>18-09-2026 11:09 UTC</t>
         </is>
       </c>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Behind the Science: Reprogramming Resistance to Prostate Cancer Treatment</t>
+          <t>EPO revokes key Moderna patent for mRNA vaccines</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>pfizer.com</t>
+          <t>JUVE Patent</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pfizer.com/news/articles/behind_the_science_reprogramming_resistance_to_prostate_cancer_treatment</t>
+          <t>https://www.juve-patent.com/people-and-business/epo-revokes-key-moderna-patent-for-mrna-vaccines/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>17-09-2026 16:35 UTC</t>
+          <t>18-09-2026 13:37 UTC</t>
         </is>
       </c>
     </row>
@@ -1867,292 +1867,292 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>US plans Medicaid most-favored-nation pricing for some drugs in all states</t>
+          <t>Pfizer India’s Sharad Goswami resigns as Senior Director</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/us-plans-medicaid-most-favored-nation-pricing-some-drugs-all-states-semafor-2026-09-18/</t>
+          <t>https://scanx.trade/stock-market-news/companies/pfizer-indias-sharad-goswami-resigns-senior-director/51275248</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>18-09-2026 14:22 UTC</t>
+          <t>18-09-2026 11:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A year ago, President Trump pledged to lower Medicaid drug prices. Has that happened?</t>
+          <t>Japan approves LEQEMBI Pen for at-home treatment of early Alzheimer’s disease</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>BioSpectrum Asia</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.npr.org/2026/09/17/nx-s1-5971066/trump-rx-medicaid-generous-drug-prices-pfizer-favored-nation</t>
+          <t>https://www.biospectrumasia.com/news/26/28399/japan-approves-leqembi-pen-for-at-home-treatment-of-early-alzheimers-disease.html</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17-09-2026 16:45 UTC</t>
+          <t>18-09-2026 15:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pfizer, BioNTech Secure Health Canada Authorization for Omicron XFG-Adapted COVID-19 Vaccine</t>
+          <t>Weekly Buzz: RARE, BAYRY Win Approvals; SION Cuts Jobs, GSK Deals; AZN, RHHBY Lead</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>RTTNews</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/pfizer-biontech-secure-health-canada-authorization-for-omicron-xfg-adapted-covid-19-vaccine-ce785bd3de8cf62c</t>
+          <t>https://www.rttnews.com/amp/3692292/weekly-buzz-rare-bayry-win-approvals-sion-cuts-jobs-gsk-deals-azn-rhhby-lead.aspx</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17-09-2026 19:04 UTC</t>
+          <t>18-09-2026 14:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Full Fed. Circ. Won't Rethink Pfizer's Paxlovid IP Win</t>
+          <t>40% rider surge expected for 2026 Momentum Medical Scheme Cape Pioneer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>The Citizen</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.law360.com/articles/2526734/full-fed-circ-won-t-rethink-pfizer-s-paxlovid-ip-win</t>
+          <t>https://www.citizen.co.za/network-news/network-sport/2026/09/19/40-rider-surge-expected-for-2026-momentum-medical-scheme-cape-pioneer/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>17-09-2026 22:11 UTC</t>
+          <t>19-09-2026 00:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Health Canada Authorizes Pfizer and BioNTech's Omicron XFG-Adapted COVID-19 Vaccine</t>
+          <t>Dr Reddy’s, Takeda Partner To Distribute First Approved Dengue Vaccine In India</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PR Newswire Canada</t>
+          <t>BW Healthcare World</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.newswire.ca/news-releases/health-canada-authorizes-pfizer-and-biontech-s-omicron-xfg-adapted-covid-19-vaccine-854410179.html</t>
+          <t>https://www.bwhealthcareworld.com/article/dr-reddy-s-takeda-partner-to-distribute-first-approved-dengue-vaccine-in-india-624465</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17-09-2026 17:30 UTC</t>
+          <t>19-09-2026 03:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[Market Movers Analysis] MedicusPharma surges on September 17: Pfizer ADC collaboration and SkinJect</t>
+          <t>India First Dengue Vaccine Qdenga Launch Dr Reddy's &amp; Takeda Deal by 2027</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bitget</t>
+          <t>Sandesh</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.bitget.com/amp/news/detail/12560605843347</t>
+          <t>https://sandesh.com/india/news/india-first-dengue-vaccine-qdenga-launch-dr-reddys-and-takeda-deal-by-2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>17-09-2026 21:59 UTC</t>
+          <t>19-09-2026 05:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pfizer BioNTech XFG vaccine receives Health Canada authorization</t>
+          <t>Dr Reddy’s secures India rights of Takeda’s dengue vax; prepares H1 2027 rollout</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>grafa.com</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://grafa.com/en/news/united-states/pfizer-biontech-omicron-xfg-covid-vaccine-health-canada-authorization</t>
+          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/dr-reddys-secures-india-rights-of-takedas-dengue-vax-prepares-h1-2027-rollout/134339913</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17-09-2026 20:14 UTC</t>
+          <t>18-09-2026 16:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PFE Looks 4.5% Overvalued on GF Value™ Amid New U.S.-China Bioph</t>
+          <t>Dr. Reddy’s Laboratories Expands Gilead Collaboration for Once-Yearly Lenacapavir</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Chemical Industry Digest</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/9087891/pfe-looks-45-overvalued-on-gf-value-amid-new-uschina-biopharma-investment-rules</t>
+          <t>https://chemindigest.com/dr-reddys-laboratories-expands-gilead-collaboration-for-once-yearly-lenacapavir/</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>18-09-2026 12:04 UTC</t>
+          <t>19-09-2026 05:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pfizer, BioNTech Secure Health Canada Authorization for Omicron XFG-Adapted COVID-19 Vaccine</t>
+          <t>Dr. Reddy's, Takeda Pharma ink pact to distribute India's first dengue vaccine QDENGA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Moomoo</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.moomoo.com/news/post/76417964/pfizer-biontech-secure-health-canada-authorization-for-omicron-xfg-adapted</t>
+          <t>https://www.thehindu.com/business/Industry/dr-reddys-takeda-pharma-ink-pact-to-distribute-indias-first-dengue-vaccine-qdenga/article71479880.ece</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>17-09-2026 19:52 UTC</t>
+          <t>18-09-2026 09:22 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Phase 3 Pediatric EMPAVELI Data Published in Clinical Journal of the American Society of Nephrology Show Reduction in Proteinuria and Stabilized Kidney Function in Adolescents with C3G or Primary IC-MPGN</t>
+          <t>Dr Reddy's, Takeda Ink Deal to Launch Dengue Vaccine QDENGA in India's Private Market in 2027</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://investors.biogen.com/news-releases/news-release-details/phase-3-pediatric-empaveli-data-published-clinical-journal</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/dr-reddys-takeda-ink-deal-to-launch-dengue-vaccine-qdenga-in-indias-private-market-in-2027-179524</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17-09-2026 20:16 UTC</t>
+          <t>18-09-2026 16:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BIIB Looks 11.6% Overvalued on GF Value™</t>
+          <t>Dr Reddy's to sell Takeda's German-made dengue vaccine, Takeda-Biological E manufacturing pact targets national immunisation programmes</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Fortune India</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/9086835/biib-looks-116-overvalued-on-gf-value</t>
+          <t>https://www.fortuneindia.com/business-news/dr-reddys-to-sell-takedas-german-made-dengue-vaccine-takeda-biological-e-manufacturing-pact-targets-national-immunisation-programmes/160079</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>17-09-2026 21:14 UTC</t>
+          <t>18-09-2026 15:39 UTC</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2164,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dr Reddy's signs India distribution deal for Takeda's Qdenga dengue vaccine</t>
+          <t>Takeda partners Dr Reddy's to launch dengue vaccine Qdenga in India from 2027</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/healthcare-pharmaceuticals/indias-dr-reddys-inks-distribution-agreement-with-takeda-dengue-vaccine-india-2026-09-18/</t>
+          <t>https://m.economictimes.com/news/company/corporate-trends/takeda-partners-dr-reddys-to-launch-dengue-vaccine-qdenga-in-india-from-2027/articleshow/134342260.cms</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>18-09-2026 03:41 UTC</t>
+          <t>18-09-2026 18:31 UTC</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sahi</t>
+          <t>sahi.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2245,22 +2245,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Japan's Takeda Pharma partners with Dr. Reddy’s Labs for dengue vaccine distribution in India</t>
+          <t>Dr Reddy’s to distribute Qdenga, India’s first dengue vaccine | India News</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia</t>
+          <t>Hindustan Times</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/49/28391/japans-takeda-pharma-partners-with-dr-reddys-labs-for-dengue-vaccine-distribution-in-india.html</t>
+          <t>https://www.hindustantimes.com/india-news/dr-reddy-s-to-distribute-qdenga-india-s-first-dengue-vaccine-101789725890237.html</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>18-09-2026 07:55 UTC</t>
+          <t>18-09-2026 10:04 UTC</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Lab shares climb 3% on signing exclusive agreement to distribute dengue vaccine in India</t>
+          <t>Dr. Reddy’s to Roll Out Takeda’s Dengue Jab in India Next Year</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://upstox.com/news/market-news/stocks/dr-reddy-s-lab-shares-climb-3-on-signing-exclusive-agreement-to-distribute-dengue-vaccine-in-india/article-200507/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-18/dr-reddy-s-to-roll-out-takeda-s-dengue-jab-in-india-next-year</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>18-09-2026 08:48 UTC</t>
+          <t>18-09-2026 08:35 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dr Reddy’s inks pact with Takeda for distribution of dengue vax Qdenga in India’s private market</t>
+          <t>Takeda signs exclusive deal with Dr. Reddy’s to distribute QDENGA in India</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/dr-reddys-inks-pact-with-takeda-for-distribution-of-dengue-vax-qdenga-in-indias-private-market/articleshow/134336216.cms</t>
+          <t>https://www.indianpharmapost.com/biopharma/takeda-signs-exclusive-deal-with-dr-reddys-to-distribute-qdenga-in-india-21907</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>18-09-2026 12:59 UTC</t>
+          <t>18-09-2026 13:08 UTC</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>businesstoday.in</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2348,216 +2348,216 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dr Reddy’s shares jump 3% on deal with Takeda to distribute dengue vaccine Qdenga</t>
+          <t>Freshers Microbiology Jobs at Intas | Walk-In Drive</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fortune India</t>
+          <t>BioTecNika</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.fortuneindia.com/markets/dr-reddys-shares-jump-3-on-deal-with-takeda-to-distribute-dengue-vaccine-qdenga/159965</t>
+          <t>https://www.biotecnika.org/2026/09/intas-microbiology-fresher-job-walk-in-2026/</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>18-09-2026 09:16 UTC</t>
+          <t>18-09-2026 23:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s to Roll Out Takeda’s Dengue Jab in India Next Year</t>
+          <t>Mall, Gift Card Cos. Can Get Fees In Payment IP Suit</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bloomberg.com</t>
+          <t>law360.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-09-18/dr-reddy-s-to-roll-out-takeda-s-dengue-jab-in-india-next-year?srnd=prognosis</t>
+          <t>https://www.law360.com/healthcare-authority/other/articles/2526760/mall-gift-card-cos-can-get-fees-in-payment-ip-suit</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>18-09-2026 08:35 UTC</t>
+          <t>18-09-2026 21:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>India to Launch First Approved Dengue Vaccine Qdenga in 2027</t>
+          <t>Pharma leaders call for stronger R&amp;D, resilient supply chains and greater patient access</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/india-to-launch-first-approved-dengue-vaccine-qdenga-in-2027/article71480215.ece</t>
+          <t>https://www.indianpharmapost.com/news/pharma-leaders-call-for-stronger-rd-resilient-supply-chains-and-greater-patient-access-21915</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>18-09-2026 11:37 UTC</t>
+          <t>19-09-2026 03:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Shares Rise on Takeda Dengue Vaccine Deal</t>
+          <t>Aurobindo Pharma Gets US FDA Approval for Asthma Inhaler</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>equitypandit.com</t>
+          <t>The Indian Practitioner</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.equitypandit.com/dr-reddys-shares-rise-on-takeda-dengue-vaccine-deal/</t>
+          <t>https://theindianpractitioner.com/aurobindo-pharma-gets-us-fda-approval-for-asthma-inhaler/</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>18-09-2026 06:10 UTC</t>
+          <t>19-09-2026 07:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dr Reddy's, Takeda Partner for India's First Dengue Vaccine</t>
+          <t>US Pharmacy Giant Walgreens to Set Up GCC in Chennai, Plans 250+ Jobs in First Year</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://money.rediff.com/news/market/dr-reddy-s-takeda-partner-for-india-s-first-dengue-vaccine/54548120260918</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/us-pharmacy-giant-walgreens-to-set-up-gcc-in-chennai-plans-250-jobs-in-first-year-179526</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>18-09-2026 07:04 UTC</t>
+          <t>18-09-2026 17:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dr Reddy’s to distribute Takeda’s dengue vaccine QDENGA in India’s private market from 2027</t>
+          <t>Novo Nordisk, Orbis Ink Up to USD 1.4 Bn Deal to Develop Oral Cardiometabolic Therapies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Firstpost</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.firstpost.com/world/dr-reddys-to-distribute-takedas-dengue-vaccine-qdenga-in-indias-private-market-from-2027-14046897.html/amp</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/novo-nordisk-orbis-ink-up-to-usd-14-bn-deal-to-develop-oral-cardiometabolic-therapies-179521</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>18-09-2026 12:22 UTC</t>
+          <t>18-09-2026 16:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BioTecNika Times Newsletter 17-09-2026- ICON plc Internship, ₹1.27 Lakh FSL Jobs, Freshers Openings at Intas &amp; More</t>
+          <t>NIFTY50 gains for a third straight session on declining crude prices</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BioTecNika</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.biotecnika.org/2026/09/biotecnika-times-newsletter-17-09-2026/</t>
+          <t>https://upstox.com/news/market-news/stocks/nifty-50-gains-for-a-third-straight-session-on-declining-crude-prices/article-200516/</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17-09-2026 21:24 UTC</t>
+          <t>18-09-2026 10:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Justices Told Fed. Circ. Erred In Veterinary Software Feud</t>
+          <t>Dr Reddy's Confirms Gilead Licence Deal for Once-Yearly Lenacapavir for HIV Prevention</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.law360.com/healthcare-authority/digital-health-technology/articles/2526796/justices-told-fed-circ-erred-in-veterinary-software-feud</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/dr-reddys-confirms-gilead-licence-deal-for-once-yearly-lenacapavir-for-hiv-prevention-179525</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18-09-2026 00:21 UTC</t>
+          <t>18-09-2026 17:15 UTC</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>USFDA Inspection Ends With 1 Observation at Aurobindo Pharma's Apitoria API Facility</t>
+          <t>AstraZeneca, Daiichi Sankyo's Enhertu Gets NICE Nod for NHS Use in England for HER2-Low Breast Cancer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/usfda-inspection-ends-with-1-observation-at-aurobindo-pharmas-apitoria-api-facility-179458</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/astrazeneca-daiichi-sankyos-enhertu-gets-nice-nod-for-nhs-use-in-england-for-her2-low-breast-cancer-179522</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>17-09-2026 18:27 UTC</t>
+          <t>18-09-2026 16:40 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,184 +2596,184 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nifty Pharma Today: Up 1.66% to 26,579.25</t>
+          <t>Retired Tihar Jail Pharmacist Allegedly Duped of Rs 1.75 Cr, 1 Held</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://univest.in/blogs/nifty-pharma-today-closing-bell-2026</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/retired-tihar-jail-pharmacist-allegedly-duped-of-rs-175-cr-1-held-179523</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>17-09-2026 16:26 UTC</t>
+          <t>18-09-2026 16:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NIFTY50 gains for a third straight session on declining crude prices</t>
+          <t>Indian patent office drafts new pharma guidelines to tighten scrutiny</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://upstox.com/news/market-news/stocks/nifty-50-gains-for-a-third-straight-session-on-declining-crude-prices/article-200516/</t>
+          <t>https://www.thepharmaletter.com/pharma-news/indian-patent-office-drafts-new-pharma-guidelines-to-tighten-scrutiny</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>18-09-2026 10:21 UTC</t>
+          <t>18-09-2026 13:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Alembic Pharma's Vadodara Bioequivalence Facility Gets USFDA Inspection Closure, EIR Issued</t>
+          <t>BioTecNika Times-18-09-2026: Reliance Scholarships, BIRAC Young Professional Jobs, Freshers Jobs at Amneal &amp; Farelabs, &amp; More</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>BioTecNika</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/alembic-pharmas-vadodara-bioequivalence-facility-gets-usfda-inspection-closure-eir-issued-179459</t>
+          <t>https://www.biotecnika.org/2026/09/biotecnika-times-18-09-26/</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>17-09-2026 18:35 UTC</t>
+          <t>18-09-2026 13:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bulimia Nervosa Market: Steady Growth Amid Rising Diagnosis Rates and a Stagnant Pharmacological Pipeline Through 2036</t>
+          <t>Shilpa Medicare Unit VII inspection ends with one procedural observation</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Barchart.com</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.barchart.com/press-releases/4664223/bulimia-nervosa-market-steady-growth-amid-rising-diagnosis-rates-and-a-stagnant-pharmacological-pipeline-through-2036</t>
+          <t>https://www.business-standard.com/amp/markets/capital-market-news/shilpa-medicare-unit-vii-inspection-ends-with-one-procedural-observation-126091900148_1.html</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17-09-2026 17:38 UTC</t>
+          <t>19-09-2026 04:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Novartis Drops Experimental Amyotrophic Lateral Sclerosis Drug After Mid-Stage Trial Failure</t>
+          <t>Merck KGaA expands life science manufacturing hub in Bengaluru</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>BioProcess International</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/novartis-drops-experimental-amyotrophic-lateral-sclerosis-drug-after-mid-stage-trial-failure-179455</t>
+          <t>https://www.bioprocessintl.com/bioregions/merck-kgaa-expands-life-science-manufacturing-hub-in-bengaluru</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17-09-2026 16:38 UTC</t>
+          <t>18-09-2026 19:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Indian patent office drafts new pharma guidelines to tighten scrutiny</t>
+          <t>mAbxience, Sandoz to Collaborate on Emicizumab Biosimilar Candidate</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/indian-patent-office-drafts-new-pharma-guidelines-to-tighten-scrutiny</t>
+          <t>https://www.contractpharma.com/breaking-news/mabxience-sandoz-to-collaborate-on-emicizumab-biosimilar-candidate/</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>18-09-2026 13:55 UTC</t>
+          <t>18-09-2026 18:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BioTecNika Times-18-09-2026: Reliance Scholarships, BIRAC Young Professional Jobs, Freshers Jobs at Amneal &amp; Farelabs, &amp; More</t>
+          <t>Lisata Therapeutics to Acquire Marea, Agreeing to Concurrent $225M Private Placement</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BioTecNika</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.biotecnika.org/2026/09/biotecnika-times-18-09-26/</t>
+          <t>https://www.contractpharma.com/breaking-news/lisata-therapeutics-to-acquire-marea-agreeing-to-concurrent-225m-private-placement/</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>18-09-2026 13:52 UTC</t>
+          <t>18-09-2026 20:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Kincell Bio, Cellipont Merge to Form Kincellis Advanced Therapies</t>
+          <t>Roche Genentech Innovation Center Boston Opens, Expanding Companies’ US Research Presence</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/kincell-bio-cellipont-merge-to-form-kincellis-advanced-therapies/</t>
+          <t>https://www.contractpharma.com/breaking-news/roche-genentech-innovation-center-boston-opens-expanding-companies-us-research-presence/</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>17-09-2026 18:22 UTC</t>
+          <t>18-09-2026 14:42 UTC</t>
         </is>
       </c>
     </row>
@@ -2839,103 +2839,103 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ProBio, Kun Tuo Partner to Accelerate Advancement of Innovative Therapies in China</t>
+          <t>Shilpa Medicare: हैदराबाद यूनिट की USFDA जांच पूरी, मिला सिर्फ एक ऑब्जर्वेशन</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/probio-kun-tuo-partner-to-accelerate-advancement-of-innovative-therapies-in-china/</t>
+          <t>https://www.whalesbook.com/corporate-news/Hindi/healthcarebiotech/Shilpa-Medicare-Receives-Single-Procedural-Observation-Following-USFDA-Inspection-at-Hyderabad-Unit/6aad3c15f2017017ae6da429</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>17-09-2026 19:10 UTC</t>
+          <t>19-09-2026 02:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Quotient Sciences Reports AI Clinical Trial Milestone</t>
+          <t>Samsung Galaxy S27 Pro and S27 Ultra's battery capacities and charging specs revealed - GSMArena.com news</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/quotient-sciences-reports-ai-clinical-trial-milestone/</t>
+          <t>https://www.gsmarena.com/samsung_galaxy_s27_pro_and_s27_ultras_battery_capacities_and_charging_spec_revealed-news-74677.php</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17-09-2026 19:38 UTC</t>
+          <t>18-09-2026 16:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Roche Genentech Innovation Center Boston Opens, Expanding Companies’ US Research Presence</t>
+          <t>Android 17: Samsung rolls out One UI 9.0 to Galaxy S26, 26+, 26 Ultra</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Deccan Herald</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/roche-genentech-innovation-center-boston-opens-expanding-companies-us-research-presence/</t>
+          <t>https://www.deccanherald.com/technology/android-17-samsung-rolls-out-one-ui-90-to-galaxy-s26-26-26-ultra-4151808</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>18-09-2026 14:42 UTC</t>
+          <t>19-09-2026 07:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WuXi XDC to Out-License Proprietary Payload-Linker Technology Platform to Ona Therapeutics</t>
+          <t>Samsung smartphone shipments worldwide quarterly 2010-2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Statista</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/wuxi-xdc-to-out-license-proprietary-payload-linker-technology-platform-to-ona-therapeutics/</t>
+          <t>https://www.statista.com/statistics/299144/samsung-smartphone-shipments-worldwide/</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>17-09-2026 20:01 UTC</t>
+          <t>18-09-2026 15:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2947,22 +2947,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 series prices increased by Rs 20,000 in India, check new prices</t>
+          <t>Samsung Fans Are Thoroughly Unimpressed by Apple’s Foldable Phone</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>WSJ</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/technology/story/samsung-galaxy-s26-price-hike-india-new-prices-all-variants-september-18-2997502-2026-09-18</t>
+          <t>https://www.wsj.com/tech/samsung-fans-are-thoroughly-unimpressed-by-apples-foldable-phone-0e6652fc</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>18-09-2026 07:06 UTC</t>
+          <t>19-09-2026 01:28 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,22 +2974,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro Max vs. Samsung Galaxy S26 Ultra: Battle of the flagships</t>
+          <t>Samsung Electronics' union now only open to semiconductor workers</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>koreajoongangdaily.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://mashable.com/tech/iphone-18-pro-max-vs-galaxy-s26-ultra-price-specs</t>
+          <t>https://www.koreajoongangdaily.com/business/samsung-electronics-union-now-only-open-to-semiconductor-workers/12883234</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>18-09-2026 03:58 UTC</t>
+          <t>19-09-2026 07:08 UTC</t>
         </is>
       </c>
     </row>
@@ -3001,22 +3001,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Beyond the Factory Gates: How Samsung Chennai Plant Is Creating Opportunities for Small Businesses in Sriperumbudur</t>
+          <t>Samsung Galaxy Z Fold8 Ultra, Fold8 get 25% lower EMIs under Galaxy Forever plan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>businesstoday.in</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/in/beyond-the-factory-gates-how-samsung-chennai-plant-is-creating-opportunities-for-small-businesses-in-sriperumbudur</t>
+          <t>https://www.businesstoday.in/technology/news/story/samsung-galaxy-z-fold8-ultra-fold8-get-25-lower-emis-under-galaxy-forever-plan-556457-2026-09-19</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>18-09-2026 08:54 UTC</t>
+          <t>19-09-2026 07:30 UTC</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Why Choose the Duo When You Can Get Samsung’s Galaxy Z Flip 8 at a Lower Price</t>
+          <t>One UI 9 global release dates for some Galaxy devices revealed</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CNET</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.cnet.com/deals/samsung-galaxy-z-flip-8-deals/</t>
+          <t>https://www.sammobile.com/news/one-ui-9-global-release-dates-for-some-galaxy-devices-revealed/</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>18-09-2026 12:10 UTC</t>
+          <t>18-09-2026 19:42 UTC</t>
         </is>
       </c>
     </row>
@@ -3055,22 +3055,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cooked: How Samsung Found A Kiwi Tim Cook To Fold Apple's Newest Launch</t>
+          <t>Samsung Brings Gemini AI to Family Hub Fridge, Launches New Bespoke ACs in India</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BW Marketing World</t>
+          <t>analyticsinsight.net</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.bwmarketingworld.com/article/samsung-trolls-apple-with-a-tim-cook-of-its-own-in-galaxy-z-fold-8-ad-624429</t>
+          <t>https://www.analyticsinsight.net/news/samsung-brings-gemini-ai-to-family-hub-fridge-launches-new-bespoke-acs-in-india</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>18-09-2026 11:32 UTC</t>
+          <t>19-09-2026 05:58 UTC</t>
         </is>
       </c>
     </row>
@@ -3082,22 +3082,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Z8 series ranked #1 in the foldable category: Consumer Reports</t>
+          <t>Samsung’s battery upgrades for Galaxy S27 Ultra and Pro leak – is it enough?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>gadgetbridge.com</t>
+          <t>9to5Google</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.gadgetbridge.com/samsung-galaxy-z8-series-ranked-1-in-the-foldable-category-consumer-reports/</t>
+          <t>https://9to5google.com/2026/09/18/samsung-galaxy-s27-ultra-pro-battery-upgrades-leak/</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>18-09-2026 14:25 UTC</t>
+          <t>18-09-2026 20:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3109,22 +3109,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S26 Ultra, Galaxy S26 Price Hike of Rs 20,000</t>
+          <t>Cooked: How Samsung Found A Kiwi Tim Cook To Fold Apple's Newest Launch</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TelecomTalk</t>
+          <t>BW Marketing World</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://telecomtalk.info/samsung-galaxy-s26-ultra-galaxy-s26-price/1011919/</t>
+          <t>https://www.bwmarketingworld.com/article/samsung-trolls-apple-with-a-tim-cook-of-its-own-in-galaxy-z-fold-8-ad-624429</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>18-09-2026 05:30 UTC</t>
+          <t>18-09-2026 20:03 UTC</t>
         </is>
       </c>
     </row>
@@ -3136,22 +3136,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Samsung Galaxy A18 4G: New Exynos 1610, Updates to 2032</t>
+          <t>Samsung will finally give the Galaxy S27 Ultra something that users have been dying for</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Memeburn</t>
+          <t>PhoneArena</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://memeburn.com/samsung-galaxy-a18-4g-specs-price-2/</t>
+          <t>https://www.phonearena.com/news/big-change-coming-to-galaxy-s27-ultra_id183432</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>18-09-2026 09:34 UTC</t>
+          <t>18-09-2026 19:40 UTC</t>
         </is>
       </c>
     </row>
@@ -3163,22 +3163,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Samsung Fans Are Thoroughly Unimpressed by Apple’s Foldable Phone</t>
+          <t>The new iPhone is here, but you can buy the Samsung Galaxy S26 FE and get a $200 gift card for free</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/tech/samsung-fans-are-thoroughly-unimpressed-by-apples-foldable-phone-0e6652fc</t>
+          <t>https://mashable.com/tech/sept-11-samsung-galaxy-gift-card-deal</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>18-09-2026 07:58 UTC</t>
+          <t>18-09-2026 18:02 UTC</t>
         </is>
       </c>
     </row>
@@ -3190,22 +3190,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>How Samsung could drive up the cost of iPhones</t>
+          <t>Why the new Samsung Galaxy Z Fold8 Ultra is the ultimate smartphone</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Shreveport Times</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/samsung-making-iphones-costlier-memory-chip-price-hikes/</t>
+          <t>https://www.shreveporttimes.com/story/shopping/trending/drops/2026/09/18/shop-samsung-galaxy-z-fold8-ultra-smartphone-samsung-phones/91813711007/</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>18-09-2026 10:38 UTC</t>
+          <t>18-09-2026 18:12 UTC</t>
         </is>
       </c>
     </row>
@@ -3217,22 +3217,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Samsung Launches 2026 Bespoke AI Appliances in India With Gemini-Powered Family Hub Refrigerator</t>
+          <t>Samsung Phone Users Can Now Sync Photos and Video to Google</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MySmartPrice</t>
+          <t>CNET</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.mysmartprice.com/gear/appliances/appliances-news/samsung-launches-2026-bespoke-ai-appliances-in-india-with-gemini-powered-family-hub-refrigerator/</t>
+          <t>https://www.cnet.com/tech/mobile/samsung-phone-users-can-now-sync-photos-and-video-to-google/</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>18-09-2026 13:36 UTC</t>
+          <t>18-09-2026 21:28 UTC</t>
         </is>
       </c>
     </row>
@@ -3244,211 +3244,211 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>'Reheating our leftovers': Rivals use iPhone Duo buzz in advertising</t>
+          <t>The 3 Best RGB Mini LED TVs of 2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>RTINGS.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/technology/tech-news/apple-iphone-duo-samsung-motorola-foldable-advertising-rival-campaigns-126091801004_1.html</t>
+          <t>https://www.rtings.com/tv/reviews/best/rgb-mini-led</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>18-09-2026 12:27 UTC</t>
+          <t>19-09-2026 04:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Best Samsung Galaxy phone deals: Save $250 at Amazon</t>
+          <t>South Korea Cuts Prices on 80 Reimbursed Drugs by Average 4.6% Amid Prescription Surge, Saving ₩33.9 Billion</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>finance.biggo.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://mashable.com/tech/sept-11-samsung-galaxy-phone-deals</t>
+          <t>https://finance.biggo.com/news/77cf763b-c390-445d-9dca-6236ddd6902e</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>18-09-2026 09:10 UTC</t>
+          <t>18-09-2026 09:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Watch: QuantHunt on Reimagining Cybersecurity for the Quantum Era</t>
+          <t>AstraZeneca, Daiichi Sankyo's Enhertu Gets NICE Nod for NHS Use in England for HER2-Low Breast Cancer</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Samsung Global Newsroom</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/in/watch-quanthunt-on-reimagining-cybersecurity-for-the-quantum-era</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/astrazeneca-daiichi-sankyos-enhertu-gets-nice-nod-for-nhs-use-in-england-for-her2-low-breast-cancer-179522</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>18-09-2026 04:03 UTC</t>
+          <t>18-09-2026 16:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Samsung S26 Ultra price drops on Flipkart, available at the lowest</t>
+          <t>AstraZeneca, Daiichi Sankyo's Enhertu Recommended for EU Approval for HER2 Positive Breast Cancer</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/visualstories/technology/samsung-s26-ultra-price-drops-on-flipkart-available-at-the-lowest-285836-18-09-2026</t>
+          <t>https://www.marketscreener.com/news/astrazeneca-daiichi-sankyo-s-enhertu-recommended-for-eu-approval-for-her2-positive-breast-cancer-ce785adada8ff527</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>18-09-2026 10:34 UTC</t>
+          <t>18-09-2026 12:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Celltrion’s Remsima takes No. 1 spot in Japan</t>
+          <t>CHMP Recommends Post-Neoadjuvant Enhertu for HER2-Positive Early Breast Cancer</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>GenomeWeb</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://pulse.mk.co.kr/news/all/12156269</t>
+          <t>https://www.genomeweb.com/precision-medicine/targeted-therapy/enhertu/gnw-chmp-breast-cancer-astrazeneca-daiichi-sankyo-20260918/</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>18-09-2026 01:48 UTC</t>
+          <t>18-09-2026 14:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>South Korea Cuts Prices on 80 Reimbursed Drugs by Average 4.6% Amid Prescription Surge, Saving ₩33.9 Billion</t>
+          <t>Enhertu® Recommended for Approval in the EU by CHMP as Adjuvant Treatment for Patients with Residual Disease After Neoadjuvant Treatment for HER2 Positive Early Breast Cancer</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/77cf763b-c390-445d-9dca-6236ddd6902e</t>
+          <t>https://www.businesswire.com/news/home/20260917458618/en/Enhertu-Recommended-for-Approval-in-the-EU-by-CHMP-as-Adjuvant-Treatment-for-Patients-with-Residual-Disease-After-Neoadjuvant-Treatment-for-HER2-Positive-Early-Breast-Cancer</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>18-09-2026 09:35 UTC</t>
+          <t>18-09-2026 12:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Korea Cuts Prices of 80 Drugs, Saving 33.9 Billion Won</t>
+          <t>AstraZeneca, Daiichi celebrate another recommended approval of Enhertu</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>London South East</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/technology/2026/09/18/korea-cuts-prices-of-80-drugs-saving-339-billion-won</t>
+          <t>https://www.lse.co.uk/news/astrazeneca-daiichi-celebrate-another-recommended-approval-of-enhertu-97p4rciq062f79b.html</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>18-09-2026 01:53 UTC</t>
+          <t>18-09-2026 13:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Prestige Biopharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Prestige Biopharma Obtains Marketing Authorization for 'Tuzuneu' in Trinidad and Tobago</t>
+          <t>Fortis Healthcare (NSE:FORTIS) Hospital Expansion and Supreme Court Petition Update</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/stock-disclosure/2026091809382068983</t>
+          <t>https://www.kalkine.co.in/article/healthcare/fortis-healthcare-nsefortis-expands-hospital-network-while-pursuing-legal-relief-in-daiichi-sankyo-matter</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>18-09-2026 00:38 UTC</t>
+          <t>19-09-2026 06:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3460,508 +3460,508 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CHMP Recommends Post-Neoadjuvant Enhertu for HER2-Positive Early Breast Cancer</t>
+          <t>AstraZeneca, Daiichi Sankyo’s Enhertu recommended for approval in EU</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GenomeWeb</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.genomeweb.com/precision-medicine/targeted-therapy/enhertu/gnw-chmp-breast-cancer-astrazeneca-daiichi-sankyo-20260918/</t>
+          <t>https://www.tipranks.com/news/the-fly/astrazeneca-daiichi-sankyos-enhertu-recommended-for-approval-in-eu-thefly-news</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>18-09-2026 14:32 UTC</t>
+          <t>18-09-2026 13:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi Sankyo's Enhertu Recommended for EU Approval for HER2 Positive Breast Cancer</t>
+          <t>L-Lysine HCL Supplements Market Outlook to 2035</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/astrazeneca-daiichi-sankyo-s-enhertu-recommended-for-eu-approval-for-her2-positive-breast-cancer-ce785adada8ff527</t>
+          <t>https://www.indexbox.io/blog/l-lysine-hcl-supplements-market-outlook-to-2035/</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>18-09-2026 12:38 UTC</t>
+          <t>18-09-2026 23:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Enhertu® Recommended for Approval in the EU by CHMP as Adjuvant Treatment for Patients with Residual Disease After Neoadjuvant Treatment for HER2 Positive Early Breast Cancer</t>
+          <t>Grünenthal prices 850m euros of notes to refinance and fund expansion</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Investing News Network</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://investingnews.com/enhertu-r-recommended-for-approval-in-the-eu-by-chmp-as-adjuvant-treatment-for-patients-with-residual-disease-after-neoadjuvant-treatment-for-her2-positive-early-breast-cancer/</t>
+          <t>https://www.thepharmaletter.com/pharma-news/grunenthal-prices-850-million-euros-of-notes-to-refinance-and-fund-expansion</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>18-09-2026 14:10 UTC</t>
+          <t>18-09-2026 09:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
+          <t>Trump: Medicaid drug pricing deals reached for all 50 states</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Arab News</t>
+          <t>USA Today</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.arabnews.com/world/astrazeneca-daiichi-breast-cancer-drug-cleared-for-nhs-use-in-england-3002134</t>
+          <t>https://www.usatoday.com/story/money/personal-finance/healthcare/2026/09/18/trump-announced-medicaid-drug-pricing-deals-for-50-states/91829280007/</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>17-09-2026 16:46 UTC</t>
+          <t>18-09-2026 21:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AstraZeneca-Daiichi breast cancer drug cleared for NHS use in England</t>
+          <t>All 50 States Join Medicaid Drug Pricing Program: Trump</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>WTVB</t>
+          <t>NTD News</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://wtvbam.com/2026/09/17/astrazeneca-daiichi-breast-cancer-drug-cleared-for-nhs-use-in-england/</t>
+          <t>https://www.ntd.com/all-50-states-join-medicaid-drug-pricing-program-trump_1173670.html</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>17-09-2026 15:12 UTC</t>
+          <t>18-09-2026 21:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Enhertu receives EU recommendation for HER2-positive breast cancer</t>
+          <t>Trump: Most-Favored-Nation Drug Pricing Being Extended to State Medicaid Programs</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>grafa.com</t>
+          <t>breitbart.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://grafa.com/en/news/united-states/enhertu-eu-recommendation-her2-positive-breast-cancer</t>
+          <t>https://www.breitbart.com/politics/2026/09/18/trump-most-favored-nation-drug-pricing-being-extended-to-state-medicaid-programs/amp/</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>18-09-2026 13:20 UTC</t>
+          <t>18-09-2026 23:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Grünenthal prices 850m euros of notes to refinance and fund expansion</t>
+          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>PR Newswire UK</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/grunenthal-prices-850-million-euros-of-notes-to-refinance-and-fund-expansion</t>
+          <t>https://www.prnewswire.co.uk/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883167.html</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>18-09-2026 09:24 UTC</t>
+          <t>18-09-2026 10:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Meet the Montgomery County Companies Behind 10 Breakthrough Treatments</t>
+          <t>FDA approves first gene therapy for pediatric patients with Sanfilippo syndrome type A</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MONTCO.Today</t>
+          <t>PharmaLive</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://montco.today/2026/09/montgomery-county-pharmaceutical-treatments/</t>
+          <t>https://www.pharmalive.com/fda-approves-first-gene-therapy-for-pediatric-patients-with-sanfilippo-syndrome-type-a/</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>17-09-2026 16:00 UTC</t>
+          <t>18-09-2026 13:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Mochida Pharmaceutical</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Major Depressive Disorder Clinical Trial Pipeline Boom as 75+ Companies are in the Race for Better Treatments | DelveInsight</t>
+          <t>Ms. Rachel matches Macklemore's $1M Palestinian aid pledge, urges wealthy celebs to join</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>WPEC</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://businessupturn.com/brand-post/major-depressive-disorder-clinical-trial-pipeline-boom-as-75-companies-are-in-the-race-for-better-treatments-delveinsight/</t>
+          <t>https://cbs12.com/news/nation-world/childrens-entertainer-ms-rachel-accurso-matches-macklemores-1m-palestinian-aid-pledge-urges-wealthy-celebrities-to-join-ed-sheeran-tour-fallout-gillette-stadium-robert-kraft</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>17-09-2026 18:08 UTC</t>
+          <t>18-09-2026 12:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
+          <t>Livzon Proposes New Non-Executive Director With Strong Pet Pharma Credentials</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PR Newswire UK</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.co.uk/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883167.html</t>
+          <t>https://www.tipranks.com/news/company-announcements/livzon-proposes-new-non-executive-director-with-strong-pet-pharma-credentials</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>18-09-2026 10:28 UTC</t>
+          <t>18-09-2026 09:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Otsuka ICU Medical LLC Issues Voluntary Nationwide Recall of 0.9% Sodium Chloride Injection, USP Due To a Product Mix-up with 10 mEq Potassium Chloride Injection</t>
+          <t>Sandoz Adds First Hemophilia Biosimilar In Bio100 Expansion</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>finance.yahoo.com</t>
+          <t>insights.citeline.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/healthcare/articles/otsuka-icu-medical-llc-issues-210800118.html</t>
+          <t>https://insights.citeline.com/generics-bulletin/business/deals/sandoz-adds-first-hemophilia-biosimilar-in-bio100-expansion-VXPZZ54UQ5A6XNCWO7YM3W6AFQ/</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>17-09-2026 21:08 UTC</t>
+          <t>18-09-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Advanz Pharma</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Panel Discussion: The new innovation economy: Building the ecosystem behind the molecule</t>
+          <t>CHMP's September meeting highlights</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>AllSci</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://www.expresspharma.in/panel-discussion-the-new-innovation-economy-building-the-ecosystem-behind-the-molecule-25-aug-2026-blr/</t>
+          <t>https://allsci.com/news/tecvayli-chmp-opinion-recommends-johnson-johnsons/</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>18-09-2026 07:11 UTC</t>
+          <t>18-09-2026 16:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Advanz Pharma</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ipsen appoints Mariette Finet to its Board of Directors</t>
+          <t>Novartis AG : Deutsche Bank reaffirms its Neutral rating</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/09/18/3364489/0/en/ipsen-appoints-mariette-finet-to-its-board-of-directors.html</t>
+          <t>https://www.marketscreener.com/news/novartis-ag-deutsche-bank-reaffirms-its-neutral-rating-ce785adad88df62d</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>18-09-2026 07:26 UTC</t>
+          <t>18-09-2026 07:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FDA approves first gene therapy for pediatric patients with Sanfilippo syndrome type A</t>
+          <t>Israeli pharma giant Teva Israel wins tax battle before Delhi High Court against IT Department</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PharmaLive</t>
+          <t>Bar and Bench</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://www.pharmalive.com/fda-approves-first-gene-therapy-for-pediatric-patients-with-sanfilippo-syndrome-type-a/</t>
+          <t>https://www.barandbench.com/news/litigation/israel-pharma-giant-teva-israel-wins-tax-battle-before-delhi-high-court-against-it-department</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>18-09-2026 13:01 UTC</t>
+          <t>19-09-2026 06:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FDA Clears Phase 1b/2 Trial of CAR T-Cell Therapy C-CAR168 for Refractory Progressive Multiple Sclerosis</t>
+          <t>Teva Study: Providers Prioritize Tolerability Over Efficacy in Tardive Dyskinesia</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NeurologyLive</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://www.neurologylive.com/view/fda-clears-c-car168-trial-refractory-progressive-multiple-sclerosis</t>
+          <t>https://www.clinicaltrialvanguard.com/news/teva-study-providers-prioritize-tolerability-over-efficacy-in-tardive-dyskinesia/</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>17-09-2026 19:55 UTC</t>
+          <t>19-09-2026 06:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Legend names Ingrid Zhang as CEO</t>
+          <t>Teva Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Via Ritzau</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/biotech-news/legend-names-ingrid-zhang-as-ceo</t>
+          <t>https://via.ritzau.dk/pressemeddelelse/15171569/teva-pharmaceutical-industries-ltd?publisherId=90446&amp;lang=en</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>17-09-2026 18:02 UTC</t>
+          <t>18-09-2026 20:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Livzon Proposes New Non-Executive Director With Strong Pet Pharma Credentials</t>
+          <t>Teva Announces Positive Long-Term SOLARIS Data for Investigational Once-Monthly Olanzapine LAI TEV-'749 in Schizophrenia</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Quiver Quantitative</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/livzon-proposes-new-non-executive-director-with-strong-pet-pharma-credentials</t>
+          <t>https://www.quiverquant.com/news/Teva+Announces+Positive+Long-Term+SOLARIS+Data+for+Investigational+Once-Monthly+Olanzapine+LAI+TEV-%27749+in+Schizophrenia</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>18-09-2026 09:15 UTC</t>
+          <t>18-09-2026 20:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Sandoz Adds First Hemophilia Biosimilar In Bio100 Expansion</t>
+          <t>TEVA Looks 80.2% Overvalued on GF Value™</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/business/deals/sandoz-adds-first-hemophilia-biosimilar-in-bio100-expansion-VXPZZ54UQ5A6XNCWO7YM3W6AFQ/</t>
+          <t>https://www.gurufocus.com/news/9088606/teva-looks-802-overvalued-on-gf-value</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>18-09-2026 10:30 UTC</t>
+          <t>18-09-2026 21:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Teva Seeks Ruling Against J&amp;J Bid to Block Simponi Biosimilars</t>
+          <t>Teva shares Phase 3 data on once-monthly schizophrenia injection</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bloomberg Law News</t>
+          <t>StreetInsider</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.bloomberglaw.com/health-law-and-business/teva-seeks-ruling-against-j-j-bid-to-block-simponi-biosimilars</t>
+          <t>https://www.streetinsider.com/Corporate+News/Teva+shares+Phase+3+data+on+once-monthly+schizophrenia+injection/27080882.html</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>17-09-2026 15:20 UTC</t>
+          <t>18-09-2026 21:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3973,22 +3973,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Delhi High Court says payments to overseas units aren't automatically taxable in India</t>
+          <t>Is the Teva Trailpeak as adventurous as its name suggests?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Believe in the Run</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/delhi-high-court-says-payments-to-overseas-units-arent-automatically-taxable-in-india-teva-ranbaxy-sun-11789705719136.html</t>
+          <t>https://believeintherun.com/shoe-reviews/teva-trailpeak-review/</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>18-09-2026 09:25 UTC</t>
+          <t>18-09-2026 19:23 UTC</t>
         </is>
       </c>
     </row>
@@ -4000,22 +4000,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>The Evolving Law of Enablement: Federal Circuit Decisions in Wyeth and Teva Form a “Yin and Yang” Framework</t>
+          <t>Delhi High Court says payments to overseas units aren't automatically taxable in India</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>JD Supra</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://www.jdsupra.com/legalnews/the-evolving-law-of-enablement-federal-5015742/</t>
+          <t>https://www.livemint.com/news/delhi-high-court-says-payments-to-overseas-units-arent-automatically-taxable-in-india-teva-ranbaxy-sun-11789705719136.html</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>17-09-2026 17:51 UTC</t>
+          <t>18-09-2026 09:25 UTC</t>
         </is>
       </c>
     </row>
@@ -4027,481 +4027,184 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Teva launches LongActingImpact.com to advance understanding of earlier, effective and uninterrupted Schizophrenia care</t>
+          <t>Eurovision 2009 Andorra: Susanne Georgi - "La teva decisió (Get A Life)"</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chain Drug Review</t>
+          <t>eurovisionworld.com</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://chaindrugreview.com/teva-launches-longactingimpact-com-to-advance-understanding-of-earlier-effective-and-uninterrupted-schizophrenia-care/</t>
+          <t>https://eurovisionworld.com/eurovision/2009/andorra</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>17-09-2026 15:24 UTC</t>
+          <t>18-09-2026 09:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Teva Seeks Ruling Against J&amp;J Bid to Block Simponi Biosimilars</t>
+          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bloomberg Law News</t>
+          <t>PA Media</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.bloomberglaw.com/ip-law/teva-seeks-ruling-against-j-j-bid-to-block-simponi-biosimilars</t>
+          <t>https://pressreleasehub.pa.media/article/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-83709.html</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>17-09-2026 15:20 UTC</t>
+          <t>18-09-2026 10:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Polpharma Biologics</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Fall Into Savings With Deals From Deuter, La Sportiva, Teva, and More</t>
+          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>GearJunkie</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://gearjunkie.com/deals/weekly-deals-9-17-26</t>
+          <t>https://finance.yahoo.com/healthcare/articles/mabxience-sandoz-sign-collaboration-agreement-101600978.html</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>17-09-2026 19:50 UTC</t>
+          <t>18-09-2026 10:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Polpharma Biologics</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sandoz announces collaboration with mAbxience to expand patient access to life-enhancing biosimilar medicines</t>
+          <t>CHMP recommends EU approval of Roche’s Ocrevus for children and adolescents with relapsing multiple sclerosis</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://www.sandoz.com/sandoz-announces-collaboration-mabxience-expand-patient-access-life-enhancing-biosimilar-medicines/</t>
+          <t>https://finance.yahoo.com/healthcare/articles/chmp-recommends-eu-approval-roche-104500076.html</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>18-09-2026 10:07 UTC</t>
+          <t>18-09-2026 10:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Japan approves under-the-skin Keytruda made with Alteogen enzyme</t>
+          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>PR Newswire UK</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=33229</t>
+          <t>https://www.prnewswire.co.uk/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883167.html</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>18-09-2026 03:33 UTC</t>
+          <t>18-09-2026 10:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>A decade leading retinal care, Eylea 8mg now lasts even longer and better, expert says</t>
+          <t>[Closing Market] KOSPI Closes Up 2.66% As Foreigners Turn to Buy After 8 Sessions</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Korea Biomedical Review</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleView.html?idxno=33231</t>
+          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277339</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>18-09-2026 03:47 UTC</t>
+          <t>18-09-2026 09:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sandoz joins mAbxience to develop emicizumab biosimilar and expand haemophilia pipeline</t>
+          <t>Foreigners Return as Net Buyers After 8 Sessions; Kospi Closes Up 2.66%</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>news.sbs.co.kr</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/sandoz-joins-mabxience-to-develop-emicizumab-biosimilar-and-expand-haemophilia-pipeline</t>
+          <t>https://news.sbs.co.kr/english/article.do?news_id=N1008760711</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>18-09-2026 05:36 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Polpharma Biologics</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>finance.yahoo.com</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>https://finance.yahoo.com/healthcare/articles/mabxience-sandoz-sign-collaboration-agreement-101600978.html</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>18-09-2026 10:16 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Polpharma Biologics</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>CHMP recommends EU approval of Roche’s Ocrevus for children and adolescents with relapsing multiple sclerosis</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>finance.yahoo.com</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>https://finance.yahoo.com/healthcare/articles/chmp-recommends-eu-approval-roche-104500076.html</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>18-09-2026 10:45 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>PR Newswire UK</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>https://www.prnewswire.co.uk/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883167.html</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>18-09-2026 10:28 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Otsuka ICU Medical LLC Issues Voluntary Nationwide Recall of 0.9% Sodium Chloride Injection, USP Due To a Product Mix-up with 10 mEq Potassium Chloride Injection</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>finance.yahoo.com</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>https://finance.yahoo.com/healthcare/articles/otsuka-icu-medical-llc-issues-210800118.html</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>17-09-2026 21:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>CDMOs/CMOs: The Key Moves in 2026</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>CHEManager</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>https://chemanager-online.com/en/news/cdmos-cmos-the-key-moves-in-2026</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>18-09-2026 05:00 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>[Closing Market] KOSPI Closes Up 2.66% As Foreigners Turn to Buy After 8 Sessions</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Businesskorea</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277339</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>18-09-2026 09:19 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>KOSPI jumps 2.66% on semiconductor strength; Kosdaq also ends higher</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>디지털투데이</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>https://www.digitaltoday.co.kr/en/view/105507/kospi-jumps-2-66-percent-on-semiconductor-strength-kosdaq-also-ends-higher</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>18-09-2026 06:58 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Foreigners Return as Net Buyers After 8 Sessions; Kospi Closes Up 2.66%</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>news.sbs.co.kr</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>https://news.sbs.co.kr/english/article.do?news_id=N1008760711</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
           <t>18-09-2026 08:03 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>[Opening Market] KOSPI Surges Past 6,860 on Foreign, Institutional Buying</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Businesskorea</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277274</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>18-09-2026 01:47 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Gallery Belvi hosts three-artist show 'Our Hour'</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10876603</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>18-09-2026 01:00 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>President Lee's press conference delayed 30 minutes, to start at 10:30 a.m.</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10877806</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>17-09-2026 23:25 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mAbxience, Sandoz Partner on Emicizumab Biosimilar Deal</t>
+          <t>Sandoz Gets Canada Approval for Generic Version of Ozempic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BioPharm International</t>
+          <t>WSJ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.biopharminternational.com/view/mabxience-sandoz-emicizumab-biosimilar-deal</t>
+          <t>https://www.wsj.com/health/pharma/sandoz-gets-canada-approval-for-generic-version-of-ozempic-8f8dce3c</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18-09-2026 15:56 UTC</t>
+          <t>19-09-2026 13:24 UTC</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mAbxience, Sandoz to Collaborate on Emicizumab Biosimilar Candidate</t>
+          <t>Sandoz and mAbxience Sign Emicizumab Biosimilar Agreement</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Pharmacy Business</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/mabxience-sandoz-to-collaborate-on-emicizumab-biosimilar-candidate/</t>
+          <t>https://www.pharmacy.biz/sandoz-mabxience-emicizumab-biosimilar-agreement/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18-09-2026 18:10 UTC</t>
+          <t>19-09-2026 12:15 UTC</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M&amp;A Roundup: Lisata Therapeutics Acquires Marea Therapeutics, mAbxience Enters Collaboration with Sandoz</t>
+          <t>mAbxience, Sandoz to Collaborate on Emicizumab Biosimilar Candidate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pharmaceutical Executive</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pharmexec.com/view/-lisata-therapeutics-acquires-marea-therapeutics-mabxience-collaboration-sandoz</t>
+          <t>https://www.contractpharma.com/breaking-news/mabxience-sandoz-to-collaborate-on-emicizumab-biosimilar-candidate/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18-09-2026 15:18 UTC</t>
+          <t>18-09-2026 18:10 UTC</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sandoz Appoints Priyaranjan Jha As Global Head Of GCCs And Country President India</t>
+          <t>mAbxience, Sandoz Partner on Emicizumab Biosimilar Deal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BW People</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.bwpeople.in/article/sandoz-appoints-priyaranjan-jha-as-global-head-of-gccs-and-country-president-india-624443</t>
+          <t>https://www.biopharminternational.com/view/mabxience-sandoz-emicizumab-biosimilar-deal</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18-09-2026 12:07 UTC</t>
+          <t>18-09-2026 15:56 UTC</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Priyaranjan Jha Appointed Global Head of GCCs and Country President, Sandoz India</t>
+          <t>M&amp;A Roundup: Lisata Therapeutics Acquires Marea Therapeutics, mAbxience Enters Collaboration with Sandoz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>Pharmaceutical Executive</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/priyaranjan-jha-appointed-global-head-of-gccs-and-country-president-sandoz-india/</t>
+          <t>https://www.pharmexec.com/view/-lisata-therapeutics-acquires-marea-therapeutics-mabxience-collaboration-sandoz</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18-09-2026 11:07 UTC</t>
+          <t>18-09-2026 15:18 UTC</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
+          <t>Sandoz Canada gets Health Canada approval for generic semaglutide</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Voice of Healthcare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883156.html</t>
+          <t>https://vohnetwork.com/news/pharma/sandoz-canada-gets-health-canada-approval-for-generic-semaglutide</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18-09-2026 10:16 UTC</t>
+          <t>19-09-2026 05:40 UTC</t>
         </is>
       </c>
     </row>
@@ -625,103 +625,103 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sandoz Canada receives Health Canada regulatory approval for (Pr)Sandoz® Semaglutide, a generic version of (Pr)Ozempic</t>
+          <t>FDA Approves Fayuvi | PharmExec</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Pharmaceutical Executive</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/sandoz-canada-receives-health-canada-regulatory-approval-for-prsandoz-semaglutide-a-generic-version-of-prozempic</t>
+          <t>https://www.pharmexec.com/view/-daily-fda-approves-fayuvi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18-09-2026 12:57 UTC</t>
+          <t>18-09-2026 20:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sandoz Adds First Hemophilia Biosimilar In Bio100 Expansion</t>
+          <t>CHMP's September meeting highlights</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>AllSci</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/business/deals/sandoz-adds-first-hemophilia-biosimilar-in-bio100-expansion-VXPZZ54UQ5A6XNCWO7YM3W6AFQ/</t>
+          <t>https://allsci.com/news/tecvayli-chmp-opinion-recommends-johnson-johnsons/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18-09-2026 10:30 UTC</t>
+          <t>18-09-2026 16:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mAbxience and Sandoz partner to develop and com...</t>
+          <t>PMi Awards 2026 – the winners and highlights</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pluang.com</t>
+          <t>PMLiVE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/mabxience-dan-sandoz-jalin-kerja-sama-percepat-akses-biosimilar-dunia</t>
+          <t>https://pmlive.com/blogs/pmi-awards-2026-the-winners-and-highlights/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18-09-2026 10:38 UTC</t>
+          <t>18-09-2026 15:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandoz Receives Canadian Approval for Generic Semaglutide</t>
+          <t>Trial Supports New Method for Easing IUD Insertion Pain</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pharmacy Business</t>
+          <t>MedPage Today</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pharmacy.biz/sandoz-wins-canadian-generic-semaglutide-approval/</t>
+          <t>https://www.medpagetoday.com/obgyn/generalobgyn/123073</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18-09-2026 12:28 UTC</t>
+          <t>18-09-2026 21:01 UTC</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHMP's September meeting highlights</t>
+          <t>Poisons board moves to tighten controls on fake medical products</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AllSci</t>
+          <t>People Daily</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://allsci.com/news/tecvayli-chmp-opinion-recommends-johnson-johnsons/</t>
+          <t>https://peopledaily.digital/news/poisons-board-moves-to-tighten-controls-on-fake-medical-products</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18-09-2026 16:46 UTC</t>
+          <t>18-09-2026 15:44 UTC</t>
         </is>
       </c>
     </row>
@@ -760,103 +760,103 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PMi Awards 2026 – the winners and highlights</t>
+          <t>Rheumatoid Arthritis Pipeline Insight 2026: 75+ Companies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PMLiVE</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pmlive.com/blogs/pmi-awards-2026-the-winners-and-highlights/</t>
+          <t>https://www.openpr.com/news/4636200/rheumatoid-arthritis-pipeline-insight-2026-75-companies</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18-09-2026 15:14 UTC</t>
+          <t>18-09-2026 20:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trial Supports New Method for Easing IUD Insertion Pain</t>
+          <t>Supporting udder health through every stage of the dairy lifecycle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MedPage Today</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.medpagetoday.com/obgyn/generalobgyn/123073</t>
+          <t>https://www.boehringer-ingelheim.com/ie/animal-health/featured-stories/supporting-udder-health-dairy-herds</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18-09-2026 21:01 UTC</t>
+          <t>19-09-2026 00:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Poisons board moves to tighten controls on fake medical products</t>
+          <t>US Pharmacy Giant Walgreens to Set Up GCC in Chennai, Plans 250+ Jobs in First Year</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>People Daily</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://peopledaily.digital/news/poisons-board-moves-to-tighten-controls-on-fake-medical-products</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/us-pharmacy-giant-walgreens-to-set-up-gcc-in-chennai-plans-250-jobs-in-first-year-179526</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18-09-2026 15:44 UTC</t>
+          <t>18-09-2026 17:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rheumatoid Arthritis Pipeline Insight 2026: 75+ Companies</t>
+          <t>Lykke Hinsch Gylvin։ Patient Perspectives Deserve More Than a Place in the Conversation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4636200/rheumatoid-arthritis-pipeline-insight-2026-75-companies</t>
+          <t>https://oncodaily.com/voices/lykke-hinsch-gylvin-588521</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18-09-2026 20:30 UTC</t>
+          <t>18-09-2026 15:37 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Supporting udder health through every stage of the dairy lifecycle</t>
+          <t>Time to REACT Earlier: Is CVD Prevention Starting Too Late?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Medscape</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.boehringer-ingelheim.com/ie/animal-health/featured-stories/supporting-udder-health-dairy-herds</t>
+          <t>https://www.medscape.com/viewarticle/time-react-earlier-cvd-prevention-starting-too-late-2026a1000xws</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19-09-2026 00:11 UTC</t>
+          <t>18-09-2026 14:55 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lykke Hinsch Gylvin։ Patient Perspectives Deserve More Than a Place in the Conversation</t>
+          <t>Praziquantel Antiparasitic Formulations Market To 2035: Livestock Intensification Drives Growth - News and Statistics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oncodaily</t>
+          <t>indexbox.io</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://oncodaily.com/voices/lykke-hinsch-gylvin-588521</t>
+          <t>https://www.indexbox.io/blog/praziquantel-antiparasitic-formulations-market-forecast-to-2035-livestock-intensification-in-africa-and-asia-drives-4-6-cagr/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18-09-2026 15:37 UTC</t>
+          <t>18-09-2026 15:51 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Boehringer discontinues Phase III EASi-KIDNEY trial of vicadrostat</t>
+          <t>Ceva announces US companion animal focus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Vet Times</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/boehringer-halts-phase-iii-kidney-trial-of-vicadrostat-combination</t>
+          <t>https://www.vettimes.com/news/business/finance/ceva-announces-us-companion-animal-focus</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18-09-2026 08:33 UTC</t>
+          <t>18-09-2026 19:31 UTC</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Praziquantel Antiparasitic Formulations Market To 2035: Livestock Intensification Drives Growth - News and Statistics</t>
+          <t>All 50 States Join Medicaid Drug Pricing Program: Trump</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>NTD News</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/praziquantel-antiparasitic-formulations-market-forecast-to-2035-livestock-intensification-in-africa-and-asia-drives-4-6-cagr/</t>
+          <t>https://www.ntd.com/all-50-states-join-medicaid-drug-pricing-program-trump_1173670.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18-09-2026 15:51 UTC</t>
+          <t>18-09-2026 21:17 UTC</t>
         </is>
       </c>
     </row>
@@ -976,157 +976,157 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dersimelagon NDA Accepted by FDA with Priority Review for EPP, XLP</t>
+          <t>Trump: Most-Favored-Nation Drug Pricing Being Extended to State Medicaid Programs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dermatologytimes.com</t>
+          <t>breitbart.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>http://dermatologytimes.com/view/dersimelagon-nda-accepted-fda-priority-review-epp-xlp</t>
+          <t>https://www.breitbart.com/politics/2026/09/18/trump-most-favored-nation-drug-pricing-being-extended-to-state-medicaid-programs/amp/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18-09-2026 13:03 UTC</t>
+          <t>18-09-2026 23:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kelli Lynch Appointed Vice President, Integrated Communications, Cardiovascular Portfolio &amp; Global Commercial Office at Medtronic</t>
+          <t>Watch Amgen Irish Open (Final Round)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>Disney Plus</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/kelli-lynch-appointed-vice-president-integrated-communications-cardiovascular-portfolio-global-commercial-office-at-medtronic/</t>
+          <t>https://www.disneyplus.com/en-ai/browse/entity-31c39828-678b-47cd-a013-b0468014762e</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18-09-2026 11:24 UTC</t>
+          <t>19-09-2026 11:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lifebit to provide research platform for NIHR BioResource</t>
+          <t>AstraZeneca, Amgen TEZSPIRE meets Phase III EoE trial endpoints</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>digitalhealth.net</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.digitalhealth.net/2026/09/lifebit-to-provide-research-platform-for-nihr-bioresource/</t>
+          <t>https://scanx.trade/stock-market-news/companies/astrazeneca-amgen-tezspire-meets-phase-iii-eoe-trial-endpoints/49376112</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18-09-2026 14:17 UTC</t>
+          <t>19-09-2026 01:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trump: Most-Favored-Nation Drug Pricing Being Extended to State Medicaid Programs</t>
+          <t>Amgen Leads Strong Commercial Field into Irish Open Week at Doonbeg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>breitbart.com</t>
+          <t>Sport for Business</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.breitbart.com/politics/2026/09/18/trump-most-favored-nation-drug-pricing-being-extended-to-state-medicaid-programs/amp/</t>
+          <t>https://sportforbusiness.com/amgen-leads-strong-commercial-field-into-irish-open-week-at-doonbeg/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18-09-2026 23:46 UTC</t>
+          <t>19-09-2026 11:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Iran Faces Influenza Vaccine Shortage as Procurement Stalls</t>
+          <t>Litigation Trends to Watch: Sports Litigation Heats Up. Plus, Amgen's Data Security Troubles.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NAVLIN DAILY</t>
+          <t>Law.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.navlindaily.com/article/31915/iran-faces-influenza-vaccine-shortage-as-procurement-stalls</t>
+          <t>https://www.law.com/2026/09/18/litigation-trends-to-watch-sports-litigation-heats-up-plus-amgens-data-security-troubles/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18-09-2026 09:43 UTC</t>
+          <t>18-09-2026 18:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>35th Abu Dhabi International Book Fair highlights shared values between UAE and China</t>
+          <t>Luke Thomas: What Do Children With Cancer Need Most?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>wam.ae</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.wam.ae/en/article/c2b4u2c-35th-abu-dhabi-international-book-fair-highlights</t>
+          <t>https://oncodaily.com/voices/luke-thomas-588680</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18-09-2026 13:56 UTC</t>
+          <t>18-09-2026 19:22 UTC</t>
         </is>
       </c>
     </row>
@@ -1138,238 +1138,238 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>€176,000 raised for Make-A-Wish® Ireland at the Amgen Irish Open</t>
+          <t>RTÉ Extends Irish Open Deal and Secures Ryder Cup Highlights for 2027</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>europeantour.com</t>
+          <t>Sport for Business</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.europeantour.com/dpworld-tour/news/articles/detail/176-000-raised-for-make-a-wish-ireland-at-the-amgen-irish-open/</t>
+          <t>https://sportforbusiness.com/rte-extends-irish-open-deal-and-secures-ryder-cup-highlights-for-2027/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18-09-2026 10:14 UTC</t>
+          <t>19-09-2026 10:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Amgen Leads Strong Commercial Field into Irish Open Week at Doonbeg</t>
+          <t>Sun Pharma to acquire US-based Organon in nearly $11.75 billion deal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sportforbusiness.com</t>
+          <t>DD News</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://sportforbusiness.com/amgen-leads-strong-commercial-field-into-irish-open-week-at-doonbeg/</t>
+          <t>https://ddnews.gov.in/en/sun-pharma-to-acquire-us-based-organon-in-nearly-11-75-billion-deal/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18-09-2026 21:59 UTC</t>
+          <t>18-09-2026 18:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Litigation Trends to Watch: Sports Litigation Heats Up. Plus, Amgen's Data Security Troubles.</t>
+          <t>Organon Announces Two Her Health Grants in India to Support Adolescent Girls' Health in Bihar and Women's Contraceptive Access in Uttar Pradesh</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Law.com</t>
+          <t>indiasnews.net</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.law.com/2026/09/18/litigation-trends-to-watch-sports-litigation-heats-up-plus-amgens-data-security-troubles/</t>
+          <t>https://www.indiasnews.net/news/279315499/organon-announces-two-her-health-grants-in-india-to-support-adolescent-girls-health-in-bihar-and-women-contraceptive-access-in-uttar-pradesh</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18-09-2026 18:25 UTC</t>
+          <t>18-09-2026 18:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Luke Thomas: What Do Children With Cancer Need Most?</t>
+          <t>46th Chess Olympiad: Team India continues winning run; Gukesh, Nihal, Humpy show top form</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oncodaily</t>
+          <t>Public TV English</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://oncodaily.com/voices/luke-thomas-588680</t>
+          <t>https://english.publictv.in/46th-chess-olympiad-team-india-continues-winning-run-gukesh-nihal-humpy-show-top-form/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18-09-2026 19:22 UTC</t>
+          <t>19-09-2026 07:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RFK Jr. Eyes Wireless, RF Radiation; Cancer by the Month; AI for Cancer Symptoms</t>
+          <t>Looking for early signs of fall foliage? Check in these spots. | Lehigh Valley Nature Watch</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MedPage Today</t>
+          <t>lehighvalleylive.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.medpagetoday.com/hematologyoncology/othercancers/123066</t>
+          <t>https://www.lehighvalleylive.com/outdoors/2026/09/looking-for-early-signs-of-fall-foliage-check-in-these-spots-lehigh-valley-nature-watch.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18-09-2026 22:49 UTC</t>
+          <t>19-09-2026 11:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Drugs and Devices Have Been on the Market for Years. But FDA-Ordered Studies Still Aren’t Done.</t>
+          <t>Watering plants lowers blood pressure and anxiety in older adults</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KFF Health News</t>
+          <t>PsyPost</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://kffhealthnews.org/health-industry/fda-approval-drugs-medical-devices-postmarket-studies-safety-delays-amgen-tavneos/</t>
+          <t>https://www.psypost.org/watering-plants-lowers-blood-pressure-and-anxiety-in-older-adults/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18-09-2026 09:03 UTC</t>
+          <t>18-09-2026 20:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Trump says his son told him he will repay Russian oligarch for wedding parties</t>
+          <t>Are tea, coffee, red meat and alcohol giving you dangerous levels of iron?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>The Detroit News</t>
+          <t>1News</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.detroitnews.com/story/news/nation/2026/09/18/trump-says-son-told-him-hell-pay-back-russian-oligarch-for-wedding/91832027007/</t>
+          <t>https://www.1news.co.nz/2026/09/19/are-tea-coffee-red-meat-and-alcohol-giving-you-dangerous-levels-of-iron/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18-09-2026 22:24 UTC</t>
+          <t>19-09-2026 06:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sun Pharma to acquire US-based Organon in nearly $11.75 billion deal</t>
+          <t>Nurturing soil microbes improves nitrogen efficiency</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DD News</t>
+          <t>Brownfield Ag News</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/sun-pharma-to-acquire-us-based-organon-in-nearly-11-75-billion-deal/</t>
+          <t>https://www.brownfieldagnews.com/news/nurturing-soil-microbes-improves-nitrogen-efficiency/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18-09-2026 18:35 UTC</t>
+          <t>18-09-2026 15:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Organon Announces Two Her Health Grants in India to Support Adolescent Girls' Health in Bihar and Women's Contraceptive Access in Uttar Pradesh</t>
+          <t>Helen Chesnut's Garden Notes: What to make of this odd and challenging growing season?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>indiasnews.net</t>
+          <t>Times Colonist</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.indiasnews.net/news/279315499/organon-announces-two-her-health-grants-in-india-to-support-adolescent-girls-health-in-bihar-and-women-contraceptive-access-in-uttar-pradesh</t>
+          <t>https://www.timescolonist.com/homes/helen-chesnuts-garden-notes-what-to-make-of-this-odd-and-challenging-growing-season-12786467</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18-09-2026 18:59 UTC</t>
+          <t>19-09-2026 10:15 UTC</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1381,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EnergyPathways, Hycamite Advance UK Hydrogen and Graphite Plant</t>
+          <t>Table Mountain featured on 2026 UNESCO World Heritage coin</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ChemAnalyst</t>
+          <t>Cape Town ETC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.chemanalyst.com/NewsAndDeals/NewsDetails/energypathways-hycamite-advance-uk-hydrogen-44547</t>
+          <t>https://www.capetownetc.com/news/table-mountain-featured-on-2026-unesco-world-heritage-coin/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>18-09-2026 13:36 UTC</t>
+          <t>19-09-2026 10:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>46th Chess Olympiad: Team India continues winning run; Gukesh, Nihal, Humpy show top form</t>
+          <t>15 Plants that are banned or restricted in certain parts of the U.S.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Public TV English</t>
+          <t>Yahoo Creators</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/46th-chess-olympiad-team-india-continues-winning-run-gukesh-nihal-humpy-show-top-form/</t>
+          <t>https://creators.yahoo.com/lifestyle/story/15-plants-that-are-banned-or-restricted-in-certain-parts-of-the-us-082400445.html</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19-09-2026 07:15 UTC</t>
+          <t>19-09-2026 08:24 UTC</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tamil Nadu's Thoothukudi Port Floats Tender For Green Hydrogen Plant, Fuel Station</t>
+          <t>Hyundai E&amp;C to lead gov’t push for 100-megawatt green hydrogen plants</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Swarajya</t>
+          <t>Hydrogen Central</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://swarajyamag.com/amp/story/news-brief%2Ftamil-nadus-thoothukudi-port-floats-tender-for-green-hydrogen-plant-fuel-station</t>
+          <t>https://hydrogen-central.com/hyundai-ec-to-lead-govt-push-for-100-megawatt-green-hydrogen-plants/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>18-09-2026 12:00 UTC</t>
+          <t>18-09-2026 17:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nurturing soil microbes improves nitrogen efficiency</t>
+          <t>Third shift at Windsor Assembly Plant a sticking point as Unifor, Stellantis pause talks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brownfield Ag News</t>
+          <t>Windsor Star</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.brownfieldagnews.com/news/nurturing-soil-microbes-improves-nitrogen-efficiency/</t>
+          <t>https://windsorstar.com/news/third-shift-at-windsor-assembly-plant-a-sticking-point-as-unifor-stellantis-pause-talks/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18-09-2026 15:57 UTC</t>
+          <t>19-09-2026 13:05 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Watering plants lowers blood pressure and anxiety in older adults</t>
+          <t>Shell to pay $15M for air quality violations at Pa. petrochemical plant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PsyPost</t>
+          <t>PennLive.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.psypost.org/watering-plants-lowers-blood-pressure-and-anxiety-in-older-adults/</t>
+          <t>https://www.pennlive.com/news/2026/09/shell-to-pay-15m-for-air-quality-violations-at-pa-petrochemical-plant.html</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18-09-2026 20:17 UTC</t>
+          <t>19-09-2026 10:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Are tea, coffee, red meat and alcohol giving you dangerous levels of iron?</t>
+          <t>Jerky goes plant-based</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1News</t>
+          <t>NBC 5 Dallas-Fort Worth</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.1news.co.nz/2026/09/19/are-tea-coffee-red-meat-and-alcohol-giving-you-dangerous-levels-of-iron/</t>
+          <t>https://www.nbcdfw.com/video/texas-today/jerky-goes-plant-based/4079183/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19-09-2026 06:37 UTC</t>
+          <t>18-09-2026 17:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hyundai E&amp;C to lead gov’t push for 100-megawatt green hydrogen plants</t>
+          <t>11 Plants To Leave Alone In Fall—Pruning Them Now Could Cost You Flowers</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hydrogen Central</t>
+          <t>Southern Living</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://hydrogen-central.com/hyundai-ec-to-lead-govt-push-for-100-megawatt-green-hydrogen-plants/</t>
+          <t>https://www.southernliving.com/plants-never-prune-in-fall-12128485</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18-09-2026 17:27 UTC</t>
+          <t>18-09-2026 22:39 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,400 +1570,400 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jerky goes plant-based</t>
+          <t>Why is the USW so afraid of the rank and file at National Steel Car?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NBC 5 Dallas-Fort Worth</t>
+          <t>World Socialist Web Site</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.nbcdfw.com/video/texas-today/jerky-goes-plant-based/4079183/</t>
+          <t>https://www.wsws.org/en/articles/2026/09/19/yhzw-s19.html</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>18-09-2026 17:06 UTC</t>
+          <t>19-09-2026 00:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A harvest for the wild: how responsible wild harvesting helps regeneration</t>
+          <t>Novartis India buys Pfizer's Minipress (prazosin) brands for USD 150M</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BBC Wildlife Magazine</t>
+          <t>Dealroom</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.discoverwildlife.com/environment/a-harvest-for-the-wild-how-responsible-plant-gathering-helps-protect-nature</t>
+          <t>https://app.dealroom.co/news/note/novartis-india-buys-pfizer-s-minipress-prazosin-brands-for-usd-150m</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18-09-2026 09:00 UTC</t>
+          <t>19-09-2026 07:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rare earth recovery from industrial waste</t>
+          <t>Secret contracts reveal undisclosed terms in Trump’s drug-pricing deals</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RECYCLING magazin</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.recycling-magazine.com/en/31243/rare-earth-recovery-from-industrial-waste</t>
+          <t>https://www.washingtonpost.com/politics/2026/09/19/secret-contracts-reveal-undisclosed-terms-trumps-drug-pricing-deals/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>18-09-2026 08:31 UTC</t>
+          <t>19-09-2026 14:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11 Plants To Leave Alone In Fall—Pruning Them Now Could Cost You Flowers</t>
+          <t>All 50 states sign up for Trump's Medicaid most-favored-nation plan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Southern Living</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.southernliving.com/plants-never-prune-in-fall-12128485</t>
+          <t>https://www.reuters.com/world/us-plans-medicaid-most-favored-nation-pricing-some-drugs-all-states-semafor-2026-09-18/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18-09-2026 22:39 UTC</t>
+          <t>18-09-2026 20:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Why is the USW so afraid of the rank and file at National Steel Car?</t>
+          <t>ARDD 2026 brings global pharma, FDA leaders and longevity science pioneers to Harvard October 1–3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>World Socialist Web Site</t>
+          <t>EurekAlert!</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.wsws.org/en/articles/2026/09/19/yhzw-s19.html</t>
+          <t>https://www.eurekalert.org/news-releases/1144599</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19-09-2026 00:15 UTC</t>
+          <t>18-09-2026 17:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>How soybeans took over the American diet – without anyone noticing</t>
+          <t>Public Health Officers’ Strike Leaves Kenya Vulnerable to El Niño Disease Outbreaks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hot Springs Village Voice</t>
+          <t>Vellum Kenya</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>http://www.hsvvoice.com/premium/theconversation/stories/how-soybeans-took-over-the-american-diet-without-anyonenoticing,156502</t>
+          <t>https://vellum.co.ke/public-health-officers-strike-leaves-kenya-vulnerable-to-el-nino-disease-outbreaks/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>18-09-2026 11:54 UTC</t>
+          <t>19-09-2026 10:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Novartis India buys Pfizer's Minipress (prazosin) brands for USD 150M</t>
+          <t>Japan approves LEQEMBI Pen for at-home treatment of early Alzheimer’s disease</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dealroom</t>
+          <t>BioSpectrum Asia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://app.dealroom.co/news/note/novartis-india-buys-pfizer-s-minipress-prazosin-brands-for-usd-150m</t>
+          <t>https://www.biospectrumasia.com/news/26/28399/japan-approves-leqembi-pen-for-at-home-treatment-of-early-alzheimers-disease.html</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19-09-2026 07:37 UTC</t>
+          <t>18-09-2026 15:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Novartis India acquires Pfizer’s Minipress brands for $150 million</t>
+          <t>Weekly Buzz: RARE, BAYRY Win Approvals; SION Cuts Jobs, GSK Deals; AZN, RHHBY Lead</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>RTTNews</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/novartis-india-acquiresp-fizer-s-minipress-brands-for-150-million</t>
+          <t>https://www.rttnews.com/amp/3692292/weekly-buzz-rare-bayry-win-approvals-sion-cuts-jobs-gsk-deals-azn-rhhby-lead.aspx</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>18-09-2026 13:40 UTC</t>
+          <t>18-09-2026 14:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>From Padcev to PF-08634404: Pfizer's Oncology Growth Push</t>
+          <t>40% rider surge expected for 2026 Momentum Medical Scheme Cape Pioneer</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>qz.com</t>
+          <t>The Citizen</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://qz.com/from-padcev-to-pf-08634404-pfizer-s-oncology-growth-push</t>
+          <t>https://www.citizen.co.za/network-news/network-sport/2026/09/19/40-rider-surge-expected-for-2026-momentum-medical-scheme-cape-pioneer/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>18-09-2026 14:11 UTC</t>
+          <t>19-09-2026 06:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pfizer NSE:PFIZER Senior Management Change September 2026</t>
+          <t>Dr Reddy’s, Takeda Partner To Distribute First Approved Dengue Vaccine In India</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>bwhealthcareworld.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kalkine.co.in/article/announcements/pfizer-nsepfizer-who-is-leaving-the-senior-management-team-in-september-2026</t>
+          <t>https://www.bwhealthcareworld.com/article/dr-reddy-s-takeda-partner-to-distribute-first-approved-dengue-vaccine-in-india-624465</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>18-09-2026 11:09 UTC</t>
+          <t>19-09-2026 03:55 UTC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EPO revokes key Moderna patent for mRNA vaccines</t>
+          <t>Dr. Reddy’s Laboratories Expands Gilead Collaboration for Once-Yearly Lenacapavir</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JUVE Patent</t>
+          <t>Chemical Industry Digest</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.juve-patent.com/people-and-business/epo-revokes-key-moderna-patent-for-mrna-vaccines/</t>
+          <t>https://chemindigest.com/dr-reddys-laboratories-expands-gilead-collaboration-for-once-yearly-lenacapavir/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>18-09-2026 13:37 UTC</t>
+          <t>19-09-2026 05:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pfizer India’s Sharad Goswami resigns as Senior Director</t>
+          <t>India First Dengue Vaccine Qdenga Launch Dr Reddy's &amp; Takeda Deal by 2027</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Sandesh</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/pfizer-indias-sharad-goswami-resigns-senior-director/51275248</t>
+          <t>https://sandesh.com/india/news/india-first-dengue-vaccine-qdenga-launch-dr-reddys-and-takeda-deal-by-2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>18-09-2026 11:10 UTC</t>
+          <t>19-09-2026 05:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Japan approves LEQEMBI Pen for at-home treatment of early Alzheimer’s disease</t>
+          <t>Dr Reddy’s secures India rights of Takeda’s dengue vax; prepares H1 2027 rollout</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia</t>
+          <t>pharma.economictimes.indiatimes.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/26/28399/japan-approves-leqembi-pen-for-at-home-treatment-of-early-alzheimers-disease.html</t>
+          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/dr-reddys-secures-india-rights-of-takedas-dengue-vax-prepares-h1-2027-rollout/134339913</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>18-09-2026 15:50 UTC</t>
+          <t>18-09-2026 16:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Weekly Buzz: RARE, BAYRY Win Approvals; SION Cuts Jobs, GSK Deals; AZN, RHHBY Lead</t>
+          <t>Dr Reddy's, Takeda Ink Deal to Launch Dengue Vaccine QDENGA in India's Private Market in 2027</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RTTNews</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.rttnews.com/amp/3692292/weekly-buzz-rare-bayry-win-approvals-sion-cuts-jobs-gsk-deals-azn-rhhby-lead.aspx</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/dr-reddys-takeda-ink-deal-to-launch-dengue-vaccine-qdenga-in-indias-private-market-in-2027-179524</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>18-09-2026 14:44 UTC</t>
+          <t>18-09-2026 16:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>40% rider surge expected for 2026 Momentum Medical Scheme Cape Pioneer</t>
+          <t>Dr Reddy's to sell Takeda's German-made dengue vaccine, Takeda-Biological E manufacturing pact targets national immunisation programmes</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>The Citizen</t>
+          <t>Fortune India</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.citizen.co.za/network-news/network-sport/2026/09/19/40-rider-surge-expected-for-2026-momentum-medical-scheme-cape-pioneer/</t>
+          <t>https://www.fortuneindia.com/business-news/dr-reddys-to-sell-takedas-german-made-dengue-vaccine-takeda-biological-e-manufacturing-pact-targets-national-immunisation-programmes/160079</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19-09-2026 00:26 UTC</t>
+          <t>18-09-2026 15:39 UTC</t>
         </is>
       </c>
     </row>
@@ -1975,22 +1975,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dr Reddy’s, Takeda Partner To Distribute First Approved Dengue Vaccine In India</t>
+          <t>Takeda partners Dr Reddy's to launch dengue vaccine Qdenga in India from 2027</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BW Healthcare World</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.bwhealthcareworld.com/article/dr-reddy-s-takeda-partner-to-distribute-first-approved-dengue-vaccine-in-india-624465</t>
+          <t>https://m.economictimes.com/news/company/corporate-trends/takeda-partners-dr-reddys-to-launch-dengue-vaccine-qdenga-in-india-from-2027/articleshow/134342260.cms</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19-09-2026 03:10 UTC</t>
+          <t>18-09-2026 18:31 UTC</t>
         </is>
       </c>
     </row>
@@ -2002,22 +2002,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>India First Dengue Vaccine Qdenga Launch Dr Reddy's &amp; Takeda Deal by 2027</t>
+          <t>India’s first CDSCO-approved dengue vaccine coming in 2027: Dr Reddy’s to distribute QDENGA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sandesh</t>
+          <t>theweek.in</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://sandesh.com/india/news/india-first-dengue-vaccine-qdenga-launch-dr-reddys-and-takeda-deal-by-2027</t>
+          <t>https://www.theweek.in/news/health/2026/09/18/indias-first-cdsco-approved-dengue-vaccine-coming-in-2027-dr-reddys-to-distribute-qdenga.amp.html</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19-09-2026 05:17 UTC</t>
+          <t>18-09-2026 15:59 UTC</t>
         </is>
       </c>
     </row>
@@ -2029,22 +2029,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dr Reddy’s secures India rights of Takeda’s dengue vax; prepares H1 2027 rollout</t>
+          <t>Dr Reddy’s inks pact with Takeda for rollout of dengue vaccine in India</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/dr-reddys-secures-india-rights-of-takedas-dengue-vax-prepares-h1-2027-rollout/134339913</t>
+          <t>https://timesofindia.indiatimes.com/city/hyderabad/dr-reddys-inks-pact-with-takeda-for-rollout-of-dengue-vaccine-in-india/amp_articleshow/134336216.cms</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>18-09-2026 16:52 UTC</t>
+          <t>18-09-2026 17:41 UTC</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2056,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Laboratories Expands Gilead Collaboration for Once-Yearly Lenacapavir</t>
+          <t>Dr Reddy's Confirms Gilead Licence Deal for Once-Yearly Lenacapavir for HIV Prevention</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chemical Industry Digest</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://chemindigest.com/dr-reddys-laboratories-expands-gilead-collaboration-for-once-yearly-lenacapavir/</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/dr-reddys-confirms-gilead-licence-deal-for-once-yearly-lenacapavir-for-hiv-prevention-179525</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19-09-2026 05:30 UTC</t>
+          <t>18-09-2026 17:15 UTC</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2083,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dr. Reddy's, Takeda Pharma ink pact to distribute India's first dengue vaccine QDENGA</t>
+          <t>NewsBytes</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>The Tribune</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/business/Industry/dr-reddys-takeda-pharma-ink-pact-to-distribute-indias-first-dengue-vaccine-qdenga/article71479880.ece</t>
+          <t>https://www.tribuneindia.com/news/exam-mentor/newsbytes-370/amp</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>18-09-2026 09:22 UTC</t>
+          <t>18-09-2026 14:44 UTC</t>
         </is>
       </c>
     </row>
@@ -2110,751 +2110,751 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dr Reddy's, Takeda Ink Deal to Launch Dengue Vaccine QDENGA in India's Private Market in 2027</t>
+          <t>India’s first approved dengue vaccine QDENGA likely to hit private market in 2027</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>The South First</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/dr-reddys-takeda-ink-deal-to-launch-dengue-vaccine-qdenga-in-indias-private-market-in-2027-179524</t>
+          <t>https://thesouthfirst.com/health/indias-first-approved-dengue-vaccine-qdenga-likely-to-hit-private-market-in-2027/</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>18-09-2026 16:58 UTC</t>
+          <t>18-09-2026 15:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Dr Reddy's to sell Takeda's German-made dengue vaccine, Takeda-Biological E manufacturing pact targets national immunisation programmes</t>
+          <t>Freshers Microbiology Jobs at Intas | Walk-In Drive</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fortune India</t>
+          <t>BioTecNika</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.fortuneindia.com/business-news/dr-reddys-to-sell-takedas-german-made-dengue-vaccine-takeda-biological-e-manufacturing-pact-targets-national-immunisation-programmes/160079</t>
+          <t>https://www.biotecnika.org/2026/09/intas-microbiology-fresher-job-walk-in-2026/</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>18-09-2026 15:39 UTC</t>
+          <t>18-09-2026 23:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Takeda partners Dr Reddy's to launch dengue vaccine Qdenga in India from 2027</t>
+          <t>Mall, Gift Card Cos. Can Get Fees In Payment IP Suit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/company/corporate-trends/takeda-partners-dr-reddys-to-launch-dengue-vaccine-qdenga-in-india-from-2027/articleshow/134342260.cms</t>
+          <t>https://www.law360.com/healthcare-authority/other/articles/2526760/mall-gift-card-cos-can-get-fees-in-payment-ip-suit</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>18-09-2026 18:31 UTC</t>
+          <t>18-09-2026 21:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dr Reddy’s, Takeda join hands to bring QDENGA dengue vaccine to India</t>
+          <t>Leadership Is Not About Avoiding Hard Choices: Biocon's CHRO On Making The Layoff Call</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Telangana Today</t>
+          <t>BW People</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://telanganatoday.com/dr-reddys-takeda-join-hands-to-bring-qdenga-dengue-vaccine-to-india</t>
+          <t>https://www.bwpeople.in/article/leadership-is-not-about-avoiding-hard-choices-biocon-s-chro-on-making-the-layoff-call-624582</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>18-09-2026 12:19 UTC</t>
+          <t>19-09-2026 11:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Partners With Gilead For HIV Prevention And Takeda For Dengue Vaccine</t>
+          <t>Pharma leaders call for stronger R&amp;D, resilient supply chains and greater patient access</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>sahi.com</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.sahi.com/news/dr-reddy-s-labs-agrees-to-licensing-deal-with-gilead-for-once-yearly-lenacapavir-to-prevent-hiv</t>
+          <t>https://www.indianpharmapost.com/news/pharma-leaders-call-for-stronger-rd-resilient-supply-chains-and-greater-patient-access-21915</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>18-09-2026 09:29 UTC</t>
+          <t>19-09-2026 09:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dr Reddy’s to distribute Qdenga, India’s first dengue vaccine | India News</t>
+          <t>Aurobindo Pharma Gets US FDA Approval for Asthma Inhaler</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hindustan Times</t>
+          <t>The Indian Practitioner</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/dr-reddy-s-to-distribute-qdenga-india-s-first-dengue-vaccine-101789725890237.html</t>
+          <t>https://theindianpractitioner.com/aurobindo-pharma-gets-us-fda-approval-for-asthma-inhaler/</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>18-09-2026 10:04 UTC</t>
+          <t>19-09-2026 12:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s to Roll Out Takeda’s Dengue Jab in India Next Year</t>
+          <t>US Pharmacy Giant Walgreens to Set Up GCC in Chennai, Plans 250+ Jobs in First Year</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-09-18/dr-reddy-s-to-roll-out-takeda-s-dengue-jab-in-india-next-year</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/us-pharmacy-giant-walgreens-to-set-up-gcc-in-chennai-plans-250-jobs-in-first-year-179526</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>18-09-2026 08:35 UTC</t>
+          <t>18-09-2026 17:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Takeda signs exclusive deal with Dr. Reddy’s to distribute QDENGA in India</t>
+          <t>Novo Nordisk, Orbis Ink Up to USD 1.4 Bn Deal to Develop Oral Cardiometabolic Therapies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/biopharma/takeda-signs-exclusive-deal-with-dr-reddys-to-distribute-qdenga-in-india-21907</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/novo-nordisk-orbis-ink-up-to-usd-14-bn-deal-to-develop-oral-cardiometabolic-therapies-179521</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>18-09-2026 13:08 UTC</t>
+          <t>18-09-2026 16:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>India’s first dengue vaccine is coming: Dr Reddy’s ties up with Japan’s Takeda</t>
+          <t>Dr Reddy's Confirms Gilead Licence Deal for Once-Yearly Lenacapavir for HIV Prevention</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>businesstoday.in</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/india/story/indias-first-dengue-vaccine-is-coming-dr-reddys-ties-up-with-japans-takeda-556473-2026-09-18</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/dr-reddys-confirms-gilead-licence-deal-for-once-yearly-lenacapavir-for-hiv-prevention-179525</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>18-09-2026 11:00 UTC</t>
+          <t>18-09-2026 17:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Freshers Microbiology Jobs at Intas | Walk-In Drive</t>
+          <t>AstraZeneca, Daiichi Sankyo's Enhertu Gets NICE Nod for NHS Use in England for HER2-Low Breast Cancer</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BioTecNika</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.biotecnika.org/2026/09/intas-microbiology-fresher-job-walk-in-2026/</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/astrazeneca-daiichi-sankyos-enhertu-gets-nice-nod-for-nhs-use-in-england-for-her2-low-breast-cancer-179522</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>18-09-2026 23:38 UTC</t>
+          <t>18-09-2026 16:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mall, Gift Card Cos. Can Get Fees In Payment IP Suit</t>
+          <t>Retired Tihar Jail Pharmacist Allegedly Duped of Rs 1.75 Cr, 1 Held</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>law360.com</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.law360.com/healthcare-authority/other/articles/2526760/mall-gift-card-cos-can-get-fees-in-payment-ip-suit</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/retired-tihar-jail-pharmacist-allegedly-duped-of-rs-175-cr-1-held-179523</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>18-09-2026 21:27 UTC</t>
+          <t>18-09-2026 16:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pharma leaders call for stronger R&amp;D, resilient supply chains and greater patient access</t>
+          <t>Shilpa Medicare Unit VII inspection ends with one procedural observation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>business-standard.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/pharma-leaders-call-for-stronger-rd-resilient-supply-chains-and-greater-patient-access-21915</t>
+          <t>https://www.business-standard.com/amp/markets/capital-market-news/shilpa-medicare-unit-vii-inspection-ends-with-one-procedural-observation-126091900148_1.html</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19-09-2026 03:44 UTC</t>
+          <t>19-09-2026 04:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Gets US FDA Approval for Asthma Inhaler</t>
+          <t>Colorcon Showcases Digital Development Tools, Advanced Analytics and Customized Excipient Systems</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>The Indian Practitioner</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://theindianpractitioner.com/aurobindo-pharma-gets-us-fda-approval-for-asthma-inhaler/</t>
+          <t>https://www.contractpharma.com/live_from_shows/colorcon-showcases-digital-development-tools-advanced-analytics-and-customized-excipient-systems/</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19-09-2026 07:01 UTC</t>
+          <t>19-09-2026 08:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>US Pharmacy Giant Walgreens to Set Up GCC in Chennai, Plans 250+ Jobs in First Year</t>
+          <t>Merck KGaA expands life science manufacturing hub in Bengaluru</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>BioProcess International</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/us-pharmacy-giant-walgreens-to-set-up-gcc-in-chennai-plans-250-jobs-in-first-year-179526</t>
+          <t>https://www.bioprocessintl.com/bioregions/merck-kgaa-expands-life-science-manufacturing-hub-in-bengaluru</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>18-09-2026 17:27 UTC</t>
+          <t>18-09-2026 19:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Orbis Ink Up to USD 1.4 Bn Deal to Develop Oral Cardiometabolic Therapies</t>
+          <t>Sharp Expands Autoinjector and Pen Assembly Capacity in U.S. and EU</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/novo-nordisk-orbis-ink-up-to-usd-14-bn-deal-to-develop-oral-cardiometabolic-therapies-179521</t>
+          <t>https://www.contractpharma.com/live_from_shows/sharp-expands-autoinjector-and-pen-assembly-capacity-in-u-s-and-eu/</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>18-09-2026 16:05 UTC</t>
+          <t>19-09-2026 08:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NIFTY50 gains for a third straight session on declining crude prices</t>
+          <t>mAbxience, Sandoz to Collaborate on Emicizumab Biosimilar Candidate</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://upstox.com/news/market-news/stocks/nifty-50-gains-for-a-third-straight-session-on-declining-crude-prices/article-200516/</t>
+          <t>https://www.contractpharma.com/breaking-news/mabxience-sandoz-to-collaborate-on-emicizumab-biosimilar-candidate/</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>18-09-2026 10:21 UTC</t>
+          <t>18-09-2026 18:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dr Reddy's Confirms Gilead Licence Deal for Once-Yearly Lenacapavir for HIV Prevention</t>
+          <t>Lisata Therapeutics to Acquire Marea, Agreeing to Concurrent $225M Private Placement</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/dr-reddys-confirms-gilead-licence-deal-for-once-yearly-lenacapavir-for-hiv-prevention-179525</t>
+          <t>https://www.contractpharma.com/breaking-news/lisata-therapeutics-to-acquire-marea-agreeing-to-concurrent-225m-private-placement/</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18-09-2026 17:15 UTC</t>
+          <t>18-09-2026 20:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi Sankyo's Enhertu Gets NICE Nod for NHS Use in England for HER2-Low Breast Cancer</t>
+          <t>Roche Genentech Innovation Center Boston Opens, Expanding Companies’ US Research Presence</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/astrazeneca-daiichi-sankyos-enhertu-gets-nice-nod-for-nhs-use-in-england-for-her2-low-breast-cancer-179522</t>
+          <t>https://www.contractpharma.com/breaking-news/roche-genentech-innovation-center-boston-opens-expanding-companies-us-research-presence/</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>18-09-2026 16:40 UTC</t>
+          <t>18-09-2026 14:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Retired Tihar Jail Pharmacist Allegedly Duped of Rs 1.75 Cr, 1 Held</t>
+          <t>Shilpa Medicare: हैदराबाद यूनिट की USFDA जांच पूरी, मिला सिर्फ एक ऑब्जर्वेशन</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>whalesbook.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/retired-tihar-jail-pharmacist-allegedly-duped-of-rs-175-cr-1-held-179523</t>
+          <t>https://www.whalesbook.com/corporate-news/Hindi/healthcarebiotech/Shilpa-Medicare-Receives-Single-Procedural-Observation-Following-USFDA-Inspection-at-Hyderabad-Unit/6aad3c15f2017017ae6da429</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>18-09-2026 16:48 UTC</t>
+          <t>19-09-2026 02:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Indian patent office drafts new pharma guidelines to tighten scrutiny</t>
+          <t>Shilpa Medicare: அமெரிக்காவின் USFDA ஆய்வில் ஒரு அவதானிப்பு; கம்பெனி விளக்கம் என்ன?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>whalesbook.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/indian-patent-office-drafts-new-pharma-guidelines-to-tighten-scrutiny</t>
+          <t>https://www.whalesbook.com/corporate-news/Tamil/healthcarebiotech/Shilpa-Medicare-Receives-Single-Procedural-Observation-Following-USFDA-Inspection-at-Hyderabad-Unit/6aad3c15f2017017ae6da429</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>18-09-2026 13:55 UTC</t>
+          <t>18-09-2026 22:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BioTecNika Times-18-09-2026: Reliance Scholarships, BIRAC Young Professional Jobs, Freshers Jobs at Amneal &amp; Farelabs, &amp; More</t>
+          <t>Samsung One UI 9 Rollout Schedule: Galaxy S25, Foldables</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BioTecNika</t>
+          <t>samsung.gadgethacks.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.biotecnika.org/2026/09/biotecnika-times-18-09-26/</t>
+          <t>https://samsung.gadgethacks.com/news/samsung-one-ui-9-rollout-schedule-galaxy-s25-foldables/</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>18-09-2026 13:54 UTC</t>
+          <t>19-09-2026 12:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Unit VII inspection ends with one procedural observation</t>
+          <t>Five One UI 9 features you should try first</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>SamMobile</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/markets/capital-market-news/shilpa-medicare-unit-vii-inspection-ends-with-one-procedural-observation-126091900148_1.html</t>
+          <t>https://www.sammobile.com/news/five-one-ui-9-features-you-should-try-first/</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>19-09-2026 04:01 UTC</t>
+          <t>19-09-2026 10:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Merck KGaA expands life science manufacturing hub in Bengaluru</t>
+          <t>Karnataka To Get New Samsung Innovation Campus For AI Skills</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BioProcess International</t>
+          <t>rediff.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.bioprocessintl.com/bioregions/merck-kgaa-expands-life-science-manufacturing-hub-in-bengaluru</t>
+          <t>https://www.rediff.com/news/report/samsung-innovation-campus-launched-in-karnataka-for-ai-skills/20260919.htm</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>18-09-2026 19:42 UTC</t>
+          <t>19-09-2026 13:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>mAbxience, Sandoz to Collaborate on Emicizumab Biosimilar Candidate</t>
+          <t>Samsung Galaxy S27 Ultra Leaks: 7,000mAh Battery and 2nm Chip Could Be Its Biggest Upgrades</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>ascendants.in</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/mabxience-sandoz-to-collaborate-on-emicizumab-biosimilar-candidate/</t>
+          <t>https://ascendants.in/spotlight/samsung-galaxy-s27-ultra-price-in-india-launch-date-specifications-7000mah-battery-camera-leaks/</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>18-09-2026 18:10 UTC</t>
+          <t>19-09-2026 11:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lisata Therapeutics to Acquire Marea, Agreeing to Concurrent $225M Private Placement</t>
+          <t>Best Samsung Galaxy phone deals: Save $250 at Amazon</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/lisata-therapeutics-to-acquire-marea-agreeing-to-concurrent-225m-private-placement/</t>
+          <t>https://mashable.com/tech/sept-11-samsung-galaxy-phone-deals</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>18-09-2026 20:41 UTC</t>
+          <t>19-09-2026 10:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Roche Genentech Innovation Center Boston Opens, Expanding Companies’ US Research Presence</t>
+          <t>Android 17: Samsung rolls out One UI 9.0 to Galaxy S26, 26+, 26 Ultra</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Deccan Herald</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/roche-genentech-innovation-center-boston-opens-expanding-companies-us-research-presence/</t>
+          <t>https://www.deccanherald.com/technology/android-17-samsung-rolls-out-one-ui-90-to-galaxy-s26-26-26-ultra-4151808</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>18-09-2026 14:42 UTC</t>
+          <t>19-09-2026 07:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CND Life Sciences Opens Innovation Lab in Scottsdale</t>
+          <t>Samsung Electronics' union now only open to semiconductor workers</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Korea JoongAng Daily</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/cnd-life-sciences-opens-innovation-lab-in-scottsdale/</t>
+          <t>https://www.koreajoongangdaily.com/business/samsung-electronics-union-now-only-open-to-semiconductor-workers/12883234</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>18-09-2026 12:58 UTC</t>
+          <t>19-09-2026 07:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Shilpa Medicare: हैदराबाद यूनिट की USFDA जांच पूरी, मिला सिर्फ एक ऑब्जर्वेशन</t>
+          <t>Samsung Galaxy Z Fold8 Ultra, Fold8 get 25% lower EMIs under Galaxy Forever plan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/corporate-news/Hindi/healthcarebiotech/Shilpa-Medicare-Receives-Single-Procedural-Observation-Following-USFDA-Inspection-at-Hyderabad-Unit/6aad3c15f2017017ae6da429</t>
+          <t>https://www.businesstoday.in/technology/news/story/samsung-galaxy-z-fold8-ultra-fold8-get-25-lower-emis-under-galaxy-forever-plan-556457-2026-09-19</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19-09-2026 02:14 UTC</t>
+          <t>19-09-2026 07:30 UTC</t>
         </is>
       </c>
     </row>
@@ -2866,22 +2866,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S27 Pro and S27 Ultra's battery capacities and charging specs revealed - GSMArena.com news</t>
+          <t>Samsung Galaxy Watch Blood Sugar Monitoring: New Patent</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>Business Outreach Magazine</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.gsmarena.com/samsung_galaxy_s27_pro_and_s27_ultras_battery_capacities_and_charging_spec_revealed-news-74677.php</t>
+          <t>https://www.businessoutreach.in/samsung-galaxy-watch-blood-sugar-monitoring/</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>18-09-2026 16:33 UTC</t>
+          <t>19-09-2026 12:29 UTC</t>
         </is>
       </c>
     </row>
@@ -2893,22 +2893,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Android 17: Samsung rolls out One UI 9.0 to Galaxy S26, 26+, 26 Ultra</t>
+          <t>The Samsung Galaxy Watch9 Wants to Tell You Everything About Your Body</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Deccan Herald</t>
+          <t>WIRED</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/technology/android-17-samsung-rolls-out-one-ui-90-to-galaxy-s26-26-26-ultra-4151808</t>
+          <t>https://www.wired.com/review/samsung-galaxy-watch9/</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>19-09-2026 07:21 UTC</t>
+          <t>19-09-2026 10:08 UTC</t>
         </is>
       </c>
     </row>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Samsung smartphone shipments worldwide quarterly 2010-2026</t>
+          <t>Samsung Galaxy S27 Pro and S27 Ultra's battery capacities and charging specs revealed - GSMArena.com news</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Statista</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.statista.com/statistics/299144/samsung-smartphone-shipments-worldwide/</t>
+          <t>https://www.gsmarena.com/samsung_galaxy_s27_pro_and_s27_ultras_battery_capacities_and_charging_spec_revealed-news-74677.php</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>18-09-2026 15:23 UTC</t>
+          <t>18-09-2026 16:33 UTC</t>
         </is>
       </c>
     </row>
@@ -2947,22 +2947,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Samsung Fans Are Thoroughly Unimpressed by Apple’s Foldable Phone</t>
+          <t>Which Samsung Galaxy Z8 Foldable Should You Consider In Singapore? Local Media Shares More</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>news.samsung.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/tech/samsung-fans-are-thoroughly-unimpressed-by-apples-foldable-phone-0e6652fc</t>
+          <t>https://news.samsung.com/sg/which-samsung-galaxy-z8-foldable-should-you-consider-in-singapore-local-media-shares-more</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>19-09-2026 01:28 UTC</t>
+          <t>19-09-2026 10:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2974,22 +2974,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Samsung Electronics' union now only open to semiconductor workers</t>
+          <t>Samsung and Google should copy these 3 things from the iPhone Duo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>koreajoongangdaily.com</t>
+          <t>MakeUseOf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.koreajoongangdaily.com/business/samsung-electronics-union-now-only-open-to-semiconductor-workers/12883234</t>
+          <t>https://www.makeuseof.com/samsung-and-google-should-copy-these-3-things-from-the-iphone-duo/</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>19-09-2026 07:08 UTC</t>
+          <t>19-09-2026 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -3001,1210 +3001,967 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Z Fold8 Ultra, Fold8 get 25% lower EMIs under Galaxy Forever plan</t>
+          <t>Samsung smartphone shipments worldwide quarterly 2010-2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>businesstoday.in</t>
+          <t>Statista</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/technology/news/story/samsung-galaxy-z-fold8-ultra-fold8-get-25-lower-emis-under-galaxy-forever-plan-556457-2026-09-19</t>
+          <t>https://www.statista.com/statistics/299144/samsung-smartphone-shipments-worldwide/</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>19-09-2026 07:30 UTC</t>
+          <t>18-09-2026 15:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>One UI 9 global release dates for some Galaxy devices revealed</t>
+          <t>AstraZeneca, Daiichi Sankyo's Enhertu Gets NICE Nod for NHS Use in England for HER2-Low Breast Cancer</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/one-ui-9-global-release-dates-for-some-galaxy-devices-revealed/</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/astrazeneca-daiichi-sankyos-enhertu-gets-nice-nod-for-nhs-use-in-england-for-her2-low-breast-cancer-179522</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>18-09-2026 19:42 UTC</t>
+          <t>18-09-2026 16:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Samsung Brings Gemini AI to Family Hub Fridge, Launches New Bespoke ACs in India</t>
+          <t>Fortis Healthcare (NSE:FORTIS) Hospital Expansion and Supreme Court Petition Update</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>analyticsinsight.net</t>
+          <t>kalkine.co.in</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.analyticsinsight.net/news/samsung-brings-gemini-ai-to-family-hub-fridge-launches-new-bespoke-acs-in-india</t>
+          <t>https://www.kalkine.co.in/article/healthcare/fortis-healthcare-nsefortis-expands-hospital-network-while-pursuing-legal-relief-in-daiichi-sankyo-matter</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>19-09-2026 05:58 UTC</t>
+          <t>19-09-2026 06:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Samsung’s battery upgrades for Galaxy S27 Ultra and Pro leak – is it enough?</t>
+          <t>A court’s search for assets and the cost to corporate certainty</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>9to5Google</t>
+          <t>Bar and Bench</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://9to5google.com/2026/09/18/samsung-galaxy-s27-ultra-pro-battery-upgrades-leak/</t>
+          <t>https://www.barandbench.com/columns/a-courts-search-for-assets-and-the-cost-to-corporate-certainty</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>18-09-2026 20:00 UTC</t>
+          <t>19-09-2026 09:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cooked: How Samsung Found A Kiwi Tim Cook To Fold Apple's Newest Launch</t>
+          <t>Japan Approves T-DXd Combo and Dato-DXd for First-Line Metastatic Breast Cancer</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BW Marketing World</t>
+          <t>CancerNetwork</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.bwmarketingworld.com/article/samsung-trolls-apple-with-a-tim-cook-of-its-own-in-galaxy-z-fold-8-ad-624429</t>
+          <t>https://www.cancernetwork.com/view/japan-approves-t-dxd-combo-and-dato-dxd-for-first-line-metastatic-breast-cancer</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>18-09-2026 20:03 UTC</t>
+          <t>18-09-2026 19:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Samsung will finally give the Galaxy S27 Ultra something that users have been dying for</t>
+          <t>AstraZeneca halts one lung cancer trial after mixed Phase 3 results</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PhoneArena</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.phonearena.com/news/big-change-coming-to-galaxy-s27-ultra_id183432</t>
+          <t>https://scanx.trade/stock-market-news/companies/astrazeneca-halts-one-lung-cancer-trial-mixed-phase-3-results/48530243</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>18-09-2026 19:40 UTC</t>
+          <t>19-09-2026 02:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The new iPhone is here, but you can buy the Samsung Galaxy S26 FE and get a $200 gift card for free</t>
+          <t>Enhertu receives EU recommendation for HER2-positive breast cancer</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>grafa.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://mashable.com/tech/sept-11-samsung-galaxy-gift-card-deal</t>
+          <t>https://grafa.com/en/news/united-states/enhertu-eu-recommendation-her2-positive-breast-cancer</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>18-09-2026 18:02 UTC</t>
+          <t>18-09-2026 16:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Why the new Samsung Galaxy Z Fold8 Ultra is the ultimate smartphone</t>
+          <t>Articulate 2026 to bring biopharma leaders together around AI and scientific communication</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Shreveport Times</t>
+          <t>150sec</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.shreveporttimes.com/story/shopping/trending/drops/2026/09/18/shop-samsung-galaxy-z-fold8-ultra-smartphone-samsung-phones/91813711007/</t>
+          <t>https://150sec.com/articulate-2026-to-bring-biopharma-leaders-together-around-ai-and-scientific-communication/</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>18-09-2026 18:12 UTC</t>
+          <t>18-09-2026 19:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Samsung Phone Users Can Now Sync Photos and Video to Google</t>
+          <t>L-Lysine HCL Supplements Market Outlook to 2035</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CNET</t>
+          <t>indexbox.io</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.cnet.com/tech/mobile/samsung-phone-users-can-now-sync-photos-and-video-to-google/</t>
+          <t>https://www.indexbox.io/blog/l-lysine-hcl-supplements-market-outlook-to-2035/</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>18-09-2026 21:28 UTC</t>
+          <t>18-09-2026 23:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>The 3 Best RGB Mini LED TVs of 2026</t>
+          <t>Trump: Medicaid drug pricing deals reached for all 50 states</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>RTINGS.com</t>
+          <t>USA Today</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.rtings.com/tv/reviews/best/rgb-mini-led</t>
+          <t>https://www.usatoday.com/story/money/personal-finance/healthcare/2026/09/18/trump-announced-medicaid-drug-pricing-deals-for-50-states/91829280007/</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>19-09-2026 04:20 UTC</t>
+          <t>18-09-2026 21:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>South Korea Cuts Prices on 80 Reimbursed Drugs by Average 4.6% Amid Prescription Surge, Saving ₩33.9 Billion</t>
+          <t>All 50 States Join Medicaid Drug Pricing Program: Trump</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>finance.biggo.com</t>
+          <t>NTD News</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://finance.biggo.com/news/77cf763b-c390-445d-9dca-6236ddd6902e</t>
+          <t>https://www.ntd.com/all-50-states-join-medicaid-drug-pricing-program-trump_1173670.html</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>18-09-2026 09:35 UTC</t>
+          <t>18-09-2026 21:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi Sankyo's Enhertu Gets NICE Nod for NHS Use in England for HER2-Low Breast Cancer</t>
+          <t>Trump: Most-Favored-Nation Drug Pricing Being Extended to State Medicaid Programs</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>breitbart.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/astrazeneca-daiichi-sankyos-enhertu-gets-nice-nod-for-nhs-use-in-england-for-her2-low-breast-cancer-179522</t>
+          <t>https://www.breitbart.com/politics/2026/09/18/trump-most-favored-nation-drug-pricing-being-extended-to-state-medicaid-programs/amp/</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>18-09-2026 16:40 UTC</t>
+          <t>18-09-2026 23:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi Sankyo's Enhertu Recommended for EU Approval for HER2 Positive Breast Cancer</t>
+          <t>Colorcon Showcases Digital Development Tools, Advanced Analytics and Customized Excipient Systems</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/astrazeneca-daiichi-sankyo-s-enhertu-recommended-for-eu-approval-for-her2-positive-breast-cancer-ce785adada8ff527</t>
+          <t>https://www.contractpharma.com/live_from_shows/colorcon-showcases-digital-development-tools-advanced-analytics-and-customized-excipient-systems/</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>18-09-2026 12:38 UTC</t>
+          <t>19-09-2026 08:08 UTC</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CHMP Recommends Post-Neoadjuvant Enhertu for HER2-Positive Early Breast Cancer</t>
+          <t>Ocrevus for Paediatric MS Gets CHMP EU Backing</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GenomeWeb</t>
+          <t>Voice of Healthcare</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.genomeweb.com/precision-medicine/targeted-therapy/enhertu/gnw-chmp-breast-cancer-astrazeneca-daiichi-sankyo-20260918/</t>
+          <t>https://vohnetwork.com/news/pharma/chmp-backs-roche-s-ocrevus-for-paediatric-relapsing-multiple-sclerosis</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>18-09-2026 14:32 UTC</t>
+          <t>19-09-2026 06:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Advanz Pharma</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Enhertu® Recommended for Approval in the EU by CHMP as Adjuvant Treatment for Patients with Residual Disease After Neoadjuvant Treatment for HER2 Positive Early Breast Cancer</t>
+          <t>CHMP's September meeting highlights</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>AllSci</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260917458618/en/Enhertu-Recommended-for-Approval-in-the-EU-by-CHMP-as-Adjuvant-Treatment-for-Patients-with-Residual-Disease-After-Neoadjuvant-Treatment-for-HER2-Positive-Early-Breast-Cancer</t>
+          <t>https://allsci.com/news/tecvayli-chmp-opinion-recommends-johnson-johnsons/</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>18-09-2026 12:00 UTC</t>
+          <t>18-09-2026 16:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi celebrate another recommended approval of Enhertu</t>
+          <t>Teva Study: Providers Prioritize Tolerability Over Efficacy in Tardive Dyskinesia</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>London South East</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.lse.co.uk/news/astrazeneca-daiichi-celebrate-another-recommended-approval-of-enhertu-97p4rciq062f79b.html</t>
+          <t>https://www.clinicaltrialvanguard.com/news/teva-study-providers-prioritize-tolerability-over-efficacy-in-tardive-dyskinesia/</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>18-09-2026 13:04 UTC</t>
+          <t>19-09-2026 12:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Fortis Healthcare (NSE:FORTIS) Hospital Expansion and Supreme Court Petition Update</t>
+          <t>Israeli pharma giant Teva Israel wins tax battle before Delhi High Court against IT Department</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>Bar and Bench</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.kalkine.co.in/article/healthcare/fortis-healthcare-nsefortis-expands-hospital-network-while-pursuing-legal-relief-in-daiichi-sankyo-matter</t>
+          <t>https://www.barandbench.com/news/litigation/israel-pharma-giant-teva-israel-wins-tax-battle-before-delhi-high-court-against-it-department</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>19-09-2026 06:47 UTC</t>
+          <t>19-09-2026 06:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi Sankyo’s Enhertu recommended for approval in EU</t>
+          <t>Withholding A Refund For Over A Decade Is Arbitrary To The Point Of Being Confiscatory: Delhi High Court Orders Rs 783 Crore TDS Refund To Teva Israel</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>lawchakra.in</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/the-fly/astrazeneca-daiichi-sankyos-enhertu-recommended-for-approval-in-eu-thefly-news</t>
+          <t>https://lawchakra.in/high-court/delhi-high-court-teva-tds-refund-reassessment-quashed-protective-recovery-limitation/</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>18-09-2026 13:46 UTC</t>
+          <t>19-09-2026 08:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>L-Lysine HCL Supplements Market Outlook to 2035</t>
+          <t>Teva’s TEV-749 olanzapine LAI shows 80% stabilization rate in schizophrenia trial</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/l-lysine-hcl-supplements-market-outlook-to-2035/</t>
+          <t>https://www.clinicaltrialvanguard.com/news/tevas-tev-749-olanzapine-lai-shows-80-stabilization-rate-in-schizophrenia-trial/</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>18-09-2026 23:16 UTC</t>
+          <t>19-09-2026 06:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Grünenthal prices 850m euros of notes to refinance and fund expansion</t>
+          <t>Teva Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Via Ritzau</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/grunenthal-prices-850-million-euros-of-notes-to-refinance-and-fund-expansion</t>
+          <t>https://via.ritzau.dk/pressemeddelelse/15171569/teva-pharmaceutical-industries-ltd?publisherId=90446&amp;lang=en</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>18-09-2026 09:32 UTC</t>
+          <t>18-09-2026 20:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Trump: Medicaid drug pricing deals reached for all 50 states</t>
+          <t>Teva Announces Positive Long-Term SOLARIS Data for Investigational Once-Monthly Olanzapine LAI TEV-'749 in Schizophrenia</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA Today</t>
+          <t>Quiver Quantitative</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.usatoday.com/story/money/personal-finance/healthcare/2026/09/18/trump-announced-medicaid-drug-pricing-deals-for-50-states/91829280007/</t>
+          <t>https://www.quiverquant.com/news/Teva+Announces+Positive+Long-Term+SOLARIS+Data+for+Investigational+Once-Monthly+Olanzapine+LAI+TEV-%27749+in+Schizophrenia</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>18-09-2026 21:10 UTC</t>
+          <t>18-09-2026 20:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>All 50 States Join Medicaid Drug Pricing Program: Trump</t>
+          <t>TEVA Looks 80.2% Overvalued on GF Value™</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NTD News</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://www.ntd.com/all-50-states-join-medicaid-drug-pricing-program-trump_1173670.html</t>
+          <t>https://www.gurufocus.com/news/9088606/teva-looks-802-overvalued-on-gf-value</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>18-09-2026 21:17 UTC</t>
+          <t>18-09-2026 21:36 UTC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Trump: Most-Favored-Nation Drug Pricing Being Extended to State Medicaid Programs</t>
+          <t>Teva shares Phase 3 data on once-monthly schizophrenia injection</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>breitbart.com</t>
+          <t>StreetInsider</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.breitbart.com/politics/2026/09/18/trump-most-favored-nation-drug-pricing-being-extended-to-state-medicaid-programs/amp/</t>
+          <t>https://www.streetinsider.com/Corporate+News/Teva+shares+Phase+3+data+on+once-monthly+schizophrenia+injection/27080882.html</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>18-09-2026 23:46 UTC</t>
+          <t>18-09-2026 21:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
+          <t>Is the Teva Trailpeak as adventurous as its name suggests?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PR Newswire UK</t>
+          <t>Believe in the Run</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.co.uk/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883167.html</t>
+          <t>https://believeintherun.com/shoe-reviews/teva-trailpeak-review/</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>18-09-2026 10:28 UTC</t>
+          <t>18-09-2026 19:23 UTC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FDA approves first gene therapy for pediatric patients with Sanfilippo syndrome type A</t>
+          <t>Sandoz and mAbxience Sign Emicizumab Biosimilar Agreement</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PharmaLive</t>
+          <t>Pharmacy Business</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://www.pharmalive.com/fda-approves-first-gene-therapy-for-pediatric-patients-with-sanfilippo-syndrome-type-a/</t>
+          <t>https://www.pharmacy.biz/sandoz-mabxience-emicizumab-biosimilar-agreement/</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>18-09-2026 13:21 UTC</t>
+          <t>19-09-2026 12:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ms. Rachel matches Macklemore's $1M Palestinian aid pledge, urges wealthy celebs to join</t>
+          <t>Enhancing Quality And Environmental Monitoring Efficiency Through Paperless Sampling</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>WPEC</t>
+          <t>bioprocessonline.com</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://cbs12.com/news/nation-world/childrens-entertainer-ms-rachel-accurso-matches-macklemores-1m-palestinian-aid-pledge-urges-wealthy-celebrities-to-join-ed-sheeran-tour-fallout-gillette-stadium-robert-kraft</t>
+          <t>https://www.bioprocessonline.com/doc/enhancing-quality-and-environmental-monitoring-efficiency-through-paperless-sampling-0001</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>18-09-2026 12:33 UTC</t>
+          <t>19-09-2026 12:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Livzon Proposes New Non-Executive Director With Strong Pet Pharma Credentials</t>
+          <t>[Breaking] Flames, smoke reported near Riyadh airport: Reuters</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/livzon-proposes-new-non-executive-director-with-strong-pet-pharma-credentials</t>
+          <t>https://mbiz.heraldcorp.com/article/10879291</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>18-09-2026 09:15 UTC</t>
+          <t>19-09-2026 10:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sandoz Adds First Hemophilia Biosimilar In Bio100 Expansion</t>
+          <t>Addressing Barriers to Access for Today’s Cell and Gene Therapies</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>insights.citeline.com</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/business/deals/sandoz-adds-first-hemophilia-biosimilar-in-bio100-expansion-VXPZZ54UQ5A6XNCWO7YM3W6AFQ/</t>
+          <t>https://www.contractpharma.com/exclusives/addressing-barriers-to-access-for-todays-cell-and-gene-therapies/</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>18-09-2026 10:30 UTC</t>
+          <t>18-09-2026 15:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Advanz Pharma</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CHMP's September meeting highlights</t>
+          <t>Gang posed as wedding guests to pocket gift-money refunds and meal vouchers</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AllSci</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://allsci.com/news/tecvayli-chmp-opinion-recommends-johnson-johnsons/</t>
+          <t>https://mbiz.heraldcorp.com/article/10879088</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>18-09-2026 16:46 UTC</t>
+          <t>19-09-2026 02:17 UTC</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Advanz Pharma</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Novartis AG : Deutsche Bank reaffirms its Neutral rating</t>
+          <t>President Lee cheers on South Korean athletes at Asian Games opening</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/novartis-ag-deutsche-bank-reaffirms-its-neutral-rating-ce785adad88df62d</t>
+          <t>https://mbiz.heraldcorp.com/article/10879266</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>18-09-2026 07:59 UTC</t>
+          <t>19-09-2026 09:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Israeli pharma giant Teva Israel wins tax battle before Delhi High Court against IT Department</t>
+          <t>BTS, Blackpink earn additional nominations at 2026 MTV VMAs</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bar and Bench</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://www.barandbench.com/news/litigation/israel-pharma-giant-teva-israel-wins-tax-battle-before-delhi-high-court-against-it-department</t>
+          <t>https://mbiz.heraldcorp.com/article/10879104</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>19-09-2026 06:48 UTC</t>
+          <t>19-09-2026 02:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Teva Study: Providers Prioritize Tolerability Over Efficacy in Tardive Dyskinesia</t>
+          <t>Gyeongil University's RE:ON volunteer corps holds community recovery event in Uiseong-gun</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>The Clinical Trial Vanguard</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://www.clinicaltrialvanguard.com/news/teva-study-providers-prioritize-tolerability-over-efficacy-in-tardive-dyskinesia/</t>
+          <t>https://mbiz.heraldcorp.com/article/10879129</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>19-09-2026 06:42 UTC</t>
+          <t>19-09-2026 03:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Teva Pharmaceutical Industries Ltd</t>
+          <t>Cheong Wa Dae says it 'respects' justice minister nominee Kim Seung-won's decision to withdraw</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Via Ritzau</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://via.ritzau.dk/pressemeddelelse/15171569/teva-pharmaceutical-industries-ltd?publisherId=90446&amp;lang=en</t>
+          <t>https://mbiz.heraldcorp.com/article/10879113</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>18-09-2026 20:32 UTC</t>
+          <t>19-09-2026 02:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Teva Announces Positive Long-Term SOLARIS Data for Investigational Once-Monthly Olanzapine LAI TEV-'749 in Schizophrenia</t>
+          <t>US-Denmark Greenland deal falls short of Trump's annexation vision, WSJ says</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Quiver Quantitative</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://www.quiverquant.com/news/Teva+Announces+Positive+Long-Term+SOLARIS+Data+for+Investigational+Once-Monthly+Olanzapine+LAI+TEV-%27749+in+Schizophrenia</t>
+          <t>https://mbiz.heraldcorp.com/article/10879187</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>18-09-2026 20:40 UTC</t>
+          <t>19-09-2026 06:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TEVA Looks 80.2% Overvalued on GF Value™</t>
+          <t>Kim Seung-won to hold press conference at National Assembly amid mounting allegations</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/9088606/teva-looks-802-overvalued-on-gf-value</t>
+          <t>https://mbiz.heraldcorp.com/article/10879074</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>18-09-2026 21:36 UTC</t>
+          <t>19-09-2026 01:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Teva shares Phase 3 data on once-monthly schizophrenia injection</t>
+          <t>Antibody Contract Manufacturing Market to Reach USD 44.96 Billion by 2034, Growing at a CAGR of 9.96%</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>StreetInsider</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://www.streetinsider.com/Corporate+News/Teva+shares+Phase+3+data+on+once-monthly+schizophrenia+injection/27080882.html</t>
+          <t>https://www.openpr.com/news/4636095/antibody-contract-manufacturing-market-to-reach-usd-44-96</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>18-09-2026 21:00 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Is the Teva Trailpeak as adventurous as its name suggests?</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Believe in the Run</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>https://believeintherun.com/shoe-reviews/teva-trailpeak-review/</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>18-09-2026 19:23 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Delhi High Court says payments to overseas units aren't automatically taxable in India</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>https://www.livemint.com/news/delhi-high-court-says-payments-to-overseas-units-arent-automatically-taxable-in-india-teva-ranbaxy-sun-11789705719136.html</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>18-09-2026 09:25 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Eurovision 2009 Andorra: Susanne Georgi - "La teva decisió (Get A Life)"</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>eurovisionworld.com</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>https://eurovisionworld.com/eurovision/2009/andorra</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>18-09-2026 09:52 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>PA Media</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>https://pressreleasehub.pa.media/article/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-83709.html</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>18-09-2026 10:39 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Polpharma Biologics</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>https://finance.yahoo.com/healthcare/articles/mabxience-sandoz-sign-collaboration-agreement-101600978.html</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>18-09-2026 10:16 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Polpharma Biologics</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>CHMP recommends EU approval of Roche’s Ocrevus for children and adolescents with relapsing multiple sclerosis</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>https://finance.yahoo.com/healthcare/articles/chmp-recommends-eu-approval-roche-104500076.html</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>18-09-2026 10:45 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>mAbxience and Sandoz Sign a Collaboration Agreement to Advance Biosimilar Access Worldwide</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>PR Newswire UK</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>https://www.prnewswire.co.uk/news-releases/mabxience-and-sandoz-sign-a-collaboration-agreement-to-advance-biosimilar-access-worldwide-302883167.html</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>18-09-2026 10:28 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>[Closing Market] KOSPI Closes Up 2.66% As Foreigners Turn to Buy After 8 Sessions</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Businesskorea</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>https://www.businesskorea.co.kr/news/articleView.html?idxno=277339</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>18-09-2026 09:19 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Foreigners Return as Net Buyers After 8 Sessions; Kospi Closes Up 2.66%</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>news.sbs.co.kr</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>https://news.sbs.co.kr/english/article.do?news_id=N1008760711</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>18-09-2026 08:03 UTC</t>
+          <t>18-09-2026 17:18 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz Gets Canada Approval for Generic Version of Ozempic</t>
+          <t>Sandoz and mAbxience Sign Emicizumab Biosimilar Agreement</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>Pharmacy Business</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.wsj.com/health/pharma/sandoz-gets-canada-approval-for-generic-version-of-ozempic-8f8dce3c</t>
+          <t>https://www.pharmacy.biz/sandoz-mabxience-emicizumab-biosimilar-agreement/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19-09-2026 13:24 UTC</t>
+          <t>19-09-2026 12:13 UTC</t>
         </is>
       </c>
     </row>
@@ -490,3478 +490,2587 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sandoz and mAbxience Sign Emicizumab Biosimilar Agreement</t>
+          <t>Sandoz Wins Canadian Approval for Generic Semaglutide, Targeting Growing GLP-1 Market</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pharmacy Business</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pharmacy.biz/sandoz-mabxience-emicizumab-biosimilar-agreement/</t>
+          <t>https://www.tipranks.com/news/company-announcements/sandoz-wins-canadian-approval-for-generic-semaglutide-targeting-growing-glp-1-market</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19-09-2026 12:15 UTC</t>
+          <t>19-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mAbxience, Sandoz to Collaborate on Emicizumab Biosimilar Candidate</t>
+          <t>XLVets hails success of one health day event</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Vet Times</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/mabxience-sandoz-to-collaborate-on-emicizumab-biosimilar-candidate/</t>
+          <t>https://www.vettimes.com/news/business/practice-developments/xlvets-hails-success-of-one-health-day-event</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18-09-2026 18:10 UTC</t>
+          <t>19-09-2026 20:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mAbxience, Sandoz Partner on Emicizumab Biosimilar Deal</t>
+          <t>China’s economic expansion is reshaping Germany’s political landscape</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BioPharm International</t>
+          <t>Tomorrow's Affairs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.biopharminternational.com/view/mabxience-sandoz-emicizumab-biosimilar-deal</t>
+          <t>https://tomorrowsaffairs.com/chinas-economic-expansion-is-reshaping-germanys-political-landscape</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18-09-2026 15:56 UTC</t>
+          <t>19-09-2026 11:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M&amp;A Roundup: Lisata Therapeutics Acquires Marea Therapeutics, mAbxience Enters Collaboration with Sandoz</t>
+          <t>Watch Amgen Irish Open (Final Round)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pharmaceutical Executive</t>
+          <t>Disney Plus</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pharmexec.com/view/-lisata-therapeutics-acquires-marea-therapeutics-mabxience-collaboration-sandoz</t>
+          <t>https://www.disneyplus.com/en-ai/browse/entity-31c39828-678b-47cd-a013-b0468014762e</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18-09-2026 15:18 UTC</t>
+          <t>19-09-2026 11:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sandoz Canada gets Health Canada approval for generic semaglutide</t>
+          <t>Amgen Leads Strong Commercial Field into Irish Open Week at Doonbeg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Voice of Healthcare</t>
+          <t>Sport for Business</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://vohnetwork.com/news/pharma/sandoz-canada-gets-health-canada-approval-for-generic-semaglutide</t>
+          <t>https://sportforbusiness.com/amgen-leads-strong-commercial-field-into-irish-open-week-at-doonbeg/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19-09-2026 05:40 UTC</t>
+          <t>19-09-2026 21:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FDA Approves Fayuvi | PharmExec</t>
+          <t>This is Irish golf’s greatest era — next year’s Ryder Cup could cap it</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pharmaceutical Executive</t>
+          <t>The Times</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pharmexec.com/view/-daily-fda-approves-fayuvi</t>
+          <t>https://www.thetimes.com/sport/irish/article/this-is-irish-golfs-greatest-era-next-years-ryder-cup-could-cap-it-nqphfp995</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18-09-2026 20:45 UTC</t>
+          <t>19-09-2026 20:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHMP's September meeting highlights</t>
+          <t>RTÉ Extends Irish Open Deal and Secures Ryder Cup Highlights for 2027</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AllSci</t>
+          <t>Sport for Business</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://allsci.com/news/tecvayli-chmp-opinion-recommends-johnson-johnsons/</t>
+          <t>https://sportforbusiness.com/rte-extends-irish-open-deal-and-secures-ryder-cup-highlights-for-2027/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18-09-2026 16:46 UTC</t>
+          <t>19-09-2026 10:33 UTC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PMi Awards 2026 – the winners and highlights</t>
+          <t>‘You managed to hold onto the chain when there was clear jealousy that the one thing the President didn’t have was a chain’</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PMLiVE</t>
+          <t>Clare Echo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pmlive.com/blogs/pmi-awards-2026-the-winners-and-highlights/</t>
+          <t>https://www.clareecho.ie/you-managed-to-hold-onto-the-chain-when-there-was-clear-jealousy-that-the-one-thing-the-president-didnt-have-was-a-chain/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18-09-2026 15:14 UTC</t>
+          <t>19-09-2026 15:07 UTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trial Supports New Method for Easing IUD Insertion Pain</t>
+          <t>Conor McKeon: Donald Trump didn’t reduce us to the role of sycophantic gobshites — we did that ourselves</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MedPage Today</t>
+          <t>Irish Independent</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.medpagetoday.com/obgyn/generalobgyn/123073</t>
+          <t>https://www.independent.ie/sport/conor-mckeon-donald-trump-didnt-reduce-us-to-the-role-of-sycophantic-gobshites-we-did-that-ourselves/a/161572439.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18-09-2026 21:01 UTC</t>
+          <t>20-09-2026 05:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Poisons board moves to tighten controls on fake medical products</t>
+          <t>The Offaly Jesus Flag And Ireland's Love For Shane Lowry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>People Daily</t>
+          <t>Balls.ie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://peopledaily.digital/news/poisons-board-moves-to-tighten-controls-on-fake-medical-products</t>
+          <t>https://www.balls.ie/golf/the-offaly-jesus-flag-and-irelands-love-for-shane-lowry-663513</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18-09-2026 15:44 UTC</t>
+          <t>19-09-2026 22:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rheumatoid Arthritis Pipeline Insight 2026: 75+ Companies</t>
+          <t>‘Rory McIlroy Rule’ Claims Threaten Major Shake-Up as PGA Tour’s New Points System Faces Heat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>EssentiallySports</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.openpr.com/news/4636200/rheumatoid-arthritis-pipeline-insight-2026-75-companies</t>
+          <t>https://www.essentiallysports.com/golf-news-rory-mcilroy-rule-claims-threaten-major-shake-up-as-pga-tours-new-points-system-faces-heat/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18-09-2026 20:30 UTC</t>
+          <t>19-09-2026 19:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Supporting udder health through every stage of the dairy lifecycle</t>
+          <t>The secret pulse of plants</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>newindianexpress.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.boehringer-ingelheim.com/ie/animal-health/featured-stories/supporting-udder-health-dairy-herds</t>
+          <t>https://www.newindianexpress.com/lifestyle/books/2026/Sep/20/the-secret-pulse-of-plants</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19-09-2026 00:11 UTC</t>
+          <t>20-09-2026 00:37 UTC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>US Pharmacy Giant Walgreens to Set Up GCC in Chennai, Plans 250+ Jobs in First Year</t>
+          <t>He went to Rajasthan to make a film in 1994. Years later, filmmaker Pradip Krishen was restoring a 70-hect</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/us-pharmacy-giant-walgreens-to-set-up-gcc-in-chennai-plans-250-jobs-in-first-year-179526</t>
+          <t>https://m.economictimes.com/news/international/us/he-went-to-rajasthan-to-make-a-film-in-1994-years-later-filmmaker-pradip-krishen-was-restoring-a-70-hectare-desert-landscape-by-removing-an-invasive-tree-and-bringing-native-ecology-back/articleshow/134357272.cms</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18-09-2026 17:27 UTC</t>
+          <t>19-09-2026 18:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lykke Hinsch Gylvin։ Patient Perspectives Deserve More Than a Place in the Conversation</t>
+          <t>Can mycorrhizal fungi and rhizobacteria cut fertilizer use?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oncodaily</t>
+          <t>agronews.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://oncodaily.com/voices/lykke-hinsch-gylvin-588521</t>
+          <t>https://agronews.com/us/en/news/agricultural-blog/2026-09-19/103943</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18-09-2026 15:37 UTC</t>
+          <t>19-09-2026 17:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Time to REACT Earlier: Is CVD Prevention Starting Too Late?</t>
+          <t>Your Hydrangeas Might Not Bloom Next Year If You Do This in Fall, a Gardening Pro Warns</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>The Spruce</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.medscape.com/viewarticle/time-react-earlier-cvd-prevention-starting-too-late-2026a1000xws</t>
+          <t>https://www.thespruce.com/pruning-new-wood-on-hydrangeas-12113453</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18-09-2026 14:55 UTC</t>
+          <t>20-09-2026 02:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Praziquantel Antiparasitic Formulations Market To 2035: Livestock Intensification Drives Growth - News and Statistics</t>
+          <t>5 easy-to-grow hardy annuals to sow in September for early spring colour, including colourful cornflowers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>indexbox.io</t>
+          <t>Country Living Magazine</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.indexbox.io/blog/praziquantel-antiparasitic-formulations-market-forecast-to-2035-livestock-intensification-in-africa-and-asia-drives-4-6-cagr/</t>
+          <t>https://www.countryliving.com/uk/homes-interiors/gardens/a73788786/hardy-annuals-plant-september/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18-09-2026 15:51 UTC</t>
+          <t>20-09-2026 04:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ceva announces US companion animal focus</t>
+          <t>Are tea, coffee, red meat and alcohol giving you dangerous levels of iron?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vet Times</t>
+          <t>1news.co.nz</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.vettimes.com/news/business/finance/ceva-announces-us-companion-animal-focus</t>
+          <t>https://www.1news.co.nz/2026/09/19/are-tea-coffee-red-meat-and-alcohol-giving-you-dangerous-levels-of-iron/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18-09-2026 19:31 UTC</t>
+          <t>19-09-2026 19:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>All 50 States Join Medicaid Drug Pricing Program: Trump</t>
+          <t>You don’t need an acre to grow fresh fruit - these compact trees fit in almost any garden</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NTD News</t>
+          <t>The English Garden</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.ntd.com/all-50-states-join-medicaid-drug-pricing-program-trump_1173670.html</t>
+          <t>https://www.theenglishgarden.co.uk/gardens/small-gardens/best-fruit-trees-for-small-gardens/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18-09-2026 21:17 UTC</t>
+          <t>19-09-2026 10:49 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trump: Most-Favored-Nation Drug Pricing Being Extended to State Medicaid Programs</t>
+          <t>Conservation mentor uses practical science to form a soil health playbook</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>breitbart.com</t>
+          <t>The Norfolk Daily News</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.breitbart.com/politics/2026/09/18/trump-most-favored-nation-drug-pricing-being-extended-to-state-medicaid-programs/amp/</t>
+          <t>https://norfolkdailynews.com/agriculture/conservation-mentor-uses-practical-science-to-form-a-soil-health-playbook/article_03d08061-7a18-4278-8d35-859799367f5d.html</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18-09-2026 23:46 UTC</t>
+          <t>19-09-2026 17:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Watch Amgen Irish Open (Final Round)</t>
+          <t>Plant extract can make a lethal drug cocktail. Can it also treat opioid addiction?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Disney Plus</t>
+          <t>Texarkana Gazette</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.disneyplus.com/en-ai/browse/entity-31c39828-678b-47cd-a013-b0468014762e</t>
+          <t>https://www.texarkanagazette.com/news/2026/sep/19/plant-extract-can-make-a-lethal-drug-cocktail-can/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19-09-2026 11:56 UTC</t>
+          <t>19-09-2026 22:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AstraZeneca, Amgen TEZSPIRE meets Phase III EoE trial endpoints</t>
+          <t>Trump Announces Plans To Form Federal 'AI Force'</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Talk 650 KSTE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/astrazeneca-amgen-tezspire-meets-phase-iii-eoe-trial-endpoints/49376112</t>
+          <t>https://kste.iheart.com/content/2026-09-19-trump-announces-plans-to-form-federal-ai-force/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19-09-2026 01:34 UTC</t>
+          <t>20-09-2026 04:35 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amgen Leads Strong Commercial Field into Irish Open Week at Doonbeg</t>
+          <t>Moribund Benue Taraku Mills crosses 80% rehabilitation mark, production begins soon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sport for Business</t>
+          <t>vanguardngr.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://sportforbusiness.com/amgen-leads-strong-commercial-field-into-irish-open-week-at-doonbeg/</t>
+          <t>https://www.vanguardngr.com/2026/09/moribund-benue-taraku-mills-crosses-80-rehabilitation-mark-production-begins-soon/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19-09-2026 11:48 UTC</t>
+          <t>19-09-2026 22:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Litigation Trends to Watch: Sports Litigation Heats Up. Plus, Amgen's Data Security Troubles.</t>
+          <t>15 Plants that are banned or restricted in certain parts of the U.S.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Law.com</t>
+          <t>Yahoo Creators</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.law.com/2026/09/18/litigation-trends-to-watch-sports-litigation-heats-up-plus-amgens-data-security-troubles/</t>
+          <t>https://creators.yahoo.com/lifestyle/story/15-plants-that-are-banned-or-restricted-in-certain-parts-of-the-us-082400445.html</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18-09-2026 18:25 UTC</t>
+          <t>19-09-2026 08:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Luke Thomas: What Do Children With Cancer Need Most?</t>
+          <t>Helen Chesnut's Garden Notes: What to make of this odd and challenging growing season?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oncodaily</t>
+          <t>Times Colonist</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://oncodaily.com/voices/luke-thomas-588680</t>
+          <t>https://www.timescolonist.com/homes/helen-chesnuts-garden-notes-what-to-make-of-this-odd-and-challenging-growing-season-12786467</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18-09-2026 19:22 UTC</t>
+          <t>19-09-2026 10:15 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RTÉ Extends Irish Open Deal and Secures Ryder Cup Highlights for 2027</t>
+          <t>Third shift at Windsor Assembly Plant a sticking point as Unifor, Stellantis pause talks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sport for Business</t>
+          <t>Windsor Star</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://sportforbusiness.com/rte-extends-irish-open-deal-and-secures-ryder-cup-highlights-for-2027/</t>
+          <t>https://windsorstar.com/news/third-shift-at-windsor-assembly-plant-a-sticking-point-as-unifor-stellantis-pause-talks/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19-09-2026 10:33 UTC</t>
+          <t>19-09-2026 13:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sun Pharma to acquire US-based Organon in nearly $11.75 billion deal</t>
+          <t>Pfizer to share higher overseas drug revenue with US health agency</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DD News</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/sun-pharma-to-acquire-us-based-organon-in-nearly-11-75-billion-deal/</t>
+          <t>https://www.business-standard.com/world-news/pfizer-to-share-higher-overseas-drug-revenue-with-us-health-agency-126092000066_1.html</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18-09-2026 18:35 UTC</t>
+          <t>20-09-2026 02:34 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Organon Announces Two Her Health Grants in India to Support Adolescent Girls' Health in Bihar and Women's Contraceptive Access in Uttar Pradesh</t>
+          <t>Pfizer to Share Revenue With HHS in Deal on Overseas Drug Prices</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>indiasnews.net</t>
+          <t>Bloomberg.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.indiasnews.net/news/279315499/organon-announces-two-her-health-grants-in-india-to-support-adolescent-girls-health-in-bihar-and-women-contraceptive-access-in-uttar-pradesh</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-19/pfizer-to-share-revenue-with-hhs-in-deal-on-overseas-drug-prices</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18-09-2026 18:59 UTC</t>
+          <t>19-09-2026 21:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>46th Chess Olympiad: Team India continues winning run; Gukesh, Nihal, Humpy show top form</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Public TV English</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/46th-chess-olympiad-team-india-continues-winning-run-gukesh-nihal-humpy-show-top-form/</t>
+          <t>https://www.medicaleconomics.com/view/pfizer-s-lyme-disease-vaccine-shows-70-efficacy-texas-man-sentenced-to-12-5-years-in-61-5m-medicare-telemarketing-fraud-scheme-novo-nordisk-launches-wegovy-subscription-model-morning-medical-update</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19-09-2026 07:15 UTC</t>
+          <t>19-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Looking for early signs of fall foliage? Check in these spots. | Lehigh Valley Nature Watch</t>
+          <t>Secret contracts reveal undisclosed terms in Trump’s drug-pricing deals</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lehighvalleylive.com</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.lehighvalleylive.com/outdoors/2026/09/looking-for-early-signs-of-fall-foliage-check-in-these-spots-lehigh-valley-nature-watch.html</t>
+          <t>https://www.washingtonpost.com/politics/2026/09/19/secret-contracts-reveal-undisclosed-terms-trumps-drug-pricing-deals/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19-09-2026 11:00 UTC</t>
+          <t>19-09-2026 17:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Watering plants lowers blood pressure and anxiety in older adults</t>
+          <t>US renews West Asia travel alert, warns Iran conflict may escalate rapidly</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PsyPost</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.psypost.org/watering-plants-lowers-blood-pressure-and-anxiety-in-older-adults/</t>
+          <t>https://www.business-standard.com/world-news/us-renews-west-asia-travel-alert-warns-iran-conflict-may-escalate-rapidly-126092000072_1.html</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18-09-2026 20:17 UTC</t>
+          <t>20-09-2026 02:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Are tea, coffee, red meat and alcohol giving you dangerous levels of iron?</t>
+          <t>Nothing is Stopping Office-to-Resi Conversions in NYC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1News</t>
+          <t>The Real Deal</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.1news.co.nz/2026/09/19/are-tea-coffee-red-meat-and-alcohol-giving-you-dangerous-levels-of-iron/</t>
+          <t>https://therealdeal.com/new-york/2026/09/19/nothing-is-stopping-office-to-resi-conversions-in-nyc/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19-09-2026 06:37 UTC</t>
+          <t>19-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nurturing soil microbes improves nitrogen efficiency</t>
+          <t>Public Health Officers’ Strike Leaves Kenya Vulnerable to El Niño Disease Outbreaks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brownfield Ag News</t>
+          <t>Vellum Kenya</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.brownfieldagnews.com/news/nurturing-soil-microbes-improves-nitrogen-efficiency/</t>
+          <t>https://vellum.co.ke/public-health-officers-strike-leaves-kenya-vulnerable-to-el-nino-disease-outbreaks/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18-09-2026 15:57 UTC</t>
+          <t>19-09-2026 10:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Helen Chesnut's Garden Notes: What to make of this odd and challenging growing season?</t>
+          <t>Gerald Laubach Obituary (01/21/1926 - 08/31/2026) - New London, NH - The Day</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Times Colonist</t>
+          <t>Legacy obituary</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.timescolonist.com/homes/helen-chesnuts-garden-notes-what-to-make-of-this-odd-and-challenging-growing-season-12786467</t>
+          <t>https://www.legacy.com/us/obituaries/theday/name/gerald-laubach-obituary?id=62497124</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19-09-2026 10:15 UTC</t>
+          <t>20-09-2026 04:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Table Mountain featured on 2026 UNESCO World Heritage coin</t>
+          <t>Trump Administration Secret Drug Deals Reveal Undisclosed Terms</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cape Town ETC</t>
+          <t>SuaraGarut.ID</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.capetownetc.com/news/table-mountain-featured-on-2026-unesco-world-heritage-coin/</t>
+          <t>https://suaragarut.id/en/trump-admin-secret-drug-deals</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19-09-2026 10:00 UTC</t>
+          <t>19-09-2026 15:29 UTC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15 Plants that are banned or restricted in certain parts of the U.S.</t>
+          <t>Anthony Wallace Joins Sun Pharma as SVP &amp; Chief Commercial Officer, U.S. Innovative Medicines</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yahoo Creators</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://creators.yahoo.com/lifestyle/story/15-plants-that-are-banned-or-restricted-in-certain-parts-of-the-us-082400445.html</t>
+          <t>https://hrtoday.in/anthony-wallace-joins-sun-pharma-as-svp-chief-commercial-officer-u-s-innovative-medicines/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19-09-2026 08:24 UTC</t>
+          <t>19-09-2026 16:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hyundai E&amp;C to lead gov’t push for 100-megawatt green hydrogen plants</t>
+          <t>40% rider surge expected for 2026 Momentum Medical Scheme Cape Pioneer</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hydrogen Central</t>
+          <t>The Citizen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://hydrogen-central.com/hyundai-ec-to-lead-govt-push-for-100-megawatt-green-hydrogen-plants/</t>
+          <t>https://www.citizen.co.za/network-news/network-sport/2026/09/19/40-rider-surge-expected-for-2026-momentum-medical-scheme-cape-pioneer/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>18-09-2026 17:27 UTC</t>
+          <t>19-09-2026 12:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Third shift at Windsor Assembly Plant a sticking point as Unifor, Stellantis pause talks</t>
+          <t>AIOCD Opposes Mandatory CCTV At Pharmacies, Flags Rs 1 Lakh Cost Burden On Small Chemists</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Windsor Star</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://windsorstar.com/news/third-shift-at-windsor-assembly-plant-a-sticking-point-as-unifor-stellantis-pause-talks/</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/aiocd-opposes-mandatory-cctv-at-pharmacies-flags-rs-1-lakh-cost-burden-on-small-chemists-179588</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19-09-2026 13:05 UTC</t>
+          <t>19-09-2026 13:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Shell to pay $15M for air quality violations at Pa. petrochemical plant</t>
+          <t>Nifty Pharma Today: Up 0.57% in Early Trade</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PennLive.com</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pennlive.com/news/2026/09/shell-to-pay-15m-for-air-quality-violations-at-pa-petrochemical-plant.html</t>
+          <t>https://univest.in/blogs/nifty-pharma-today-opening-bell-2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19-09-2026 10:45 UTC</t>
+          <t>19-09-2026 10:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jerky goes plant-based</t>
+          <t>Manorama Industries completes postal ballot dispatch for independent director appointment</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NBC 5 Dallas-Fort Worth</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.nbcdfw.com/video/texas-today/jerky-goes-plant-based/4079183/</t>
+          <t>https://scanx.trade/stock-market-news/companies/manorama-industries-seeks-shareholder-nod-dr-rohini-tiwari-appointment/51273622</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>18-09-2026 17:06 UTC</t>
+          <t>19-09-2026 14:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11 Plants To Leave Alone In Fall—Pruning Them Now Could Cost You Flowers</t>
+          <t>Local doctor who delivers babies writes first novel</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Southern Living</t>
+          <t>Dayton Daily News</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.southernliving.com/plants-never-prune-in-fall-12128485</t>
+          <t>https://www.daytondailynews.com/community/community-gems/local-doctor-who-delivers-babies-writes-first-novel/article_48567f5b-3e57-5051-8bd7-3506a1e8b3e3.html</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18-09-2026 22:39 UTC</t>
+          <t>20-09-2026 06:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Why is the USW so afraid of the rank and file at National Steel Car?</t>
+          <t>Zealand Pharma's Zeydovio Gets Positive EU Opinion for Short Bowel Syndrome, 65.7% Achieve Reduced...</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>World Socialist Web Site</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.wsws.org/en/articles/2026/09/19/yhzw-s19.html</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/zealand-pharmas-zeydovio-gets-positive-eu-opinion-for-short-bowel-syndrome-657-achieve-reduced-parenteral-support-179581</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19-09-2026 00:15 UTC</t>
+          <t>19-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Novartis India buys Pfizer's Minipress (prazosin) brands for USD 150M</t>
+          <t>ENTOD Pharmaceuticals secures patent for its insulin eye drop</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dealroom</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://app.dealroom.co/news/note/novartis-india-buys-pfizer-s-minipress-prazosin-brands-for-usd-150m</t>
+          <t>https://economictimes.indiatimes.com/industry/healthcare/biotech/pharmaceuticals/entod-pharmaceuticals-secures-patent-for-its-insulin-eye-drop/articleshow/134359748.cms</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19-09-2026 07:37 UTC</t>
+          <t>19-09-2026 19:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Secret contracts reveal undisclosed terms in Trump’s drug-pricing deals</t>
+          <t>AI investment, government borrowing drive global cost of capital higher: Goldman Sachs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.washingtonpost.com/politics/2026/09/19/secret-contracts-reveal-undisclosed-terms-trumps-drug-pricing-deals/</t>
+          <t>https://m.economictimes.com/news/company/corporate-trends/ai-investment-government-borrowing-drive-global-cost-of-capital-higher-goldman-sachs/articleshow/134352343.cms</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19-09-2026 14:32 UTC</t>
+          <t>19-09-2026 10:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>All 50 states sign up for Trump's Medicaid most-favored-nation plan</t>
+          <t>Nestle in FSSAI Legal Net After Baby Food Sample Found Substandard, 3 Cases Filed</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/us-plans-medicaid-most-favored-nation-pricing-some-drugs-all-states-semafor-2026-09-18/</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/nestle-in-fssai-legal-net-after-baby-food-sample-found-substandard-3-cases-filed-179567</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18-09-2026 20:40 UTC</t>
+          <t>19-09-2026 11:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ARDD 2026 brings global pharma, FDA leaders and longevity science pioneers to Harvard October 1–3</t>
+          <t>Dengue cases rise across Tamil Nadu as monsoon intensifies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EurekAlert!</t>
+          <t>daijiworld.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.eurekalert.org/news-releases/1144599</t>
+          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1326161</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18-09-2026 17:31 UTC</t>
+          <t>19-09-2026 09:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Public Health Officers’ Strike Leaves Kenya Vulnerable to El Niño Disease Outbreaks</t>
+          <t>Freshers Microbiology Jobs at Intas | Walk-In Drive</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vellum Kenya</t>
+          <t>biotecnika.org</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://vellum.co.ke/public-health-officers-strike-leaves-kenya-vulnerable-to-el-nino-disease-outbreaks/</t>
+          <t>https://www.biotecnika.org/2026/09/intas-microbiology-fresher-job-walk-in-2026/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19-09-2026 10:30 UTC</t>
+          <t>19-09-2026 21:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Japan approves LEQEMBI Pen for at-home treatment of early Alzheimer’s disease</t>
+          <t>Kiran Mazumdar-Shaw Calls Out Fendi’s Rs 8.3 Lakh ‘Navratri’ Bag: ‘Undermines Our Authentic Talent’</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia</t>
+          <t>pragativadi.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/26/28399/japan-approves-leqembi-pen-for-at-home-treatment-of-early-alzheimers-disease.html</t>
+          <t>https://pragativadi.com/kiran-mazumdar-shaw-calls-out-fendis-rs-8-3-lakh-navratri-bag-undermines-our-authentic-talent/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>18-09-2026 15:50 UTC</t>
+          <t>20-09-2026 04:48 UTC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Weekly Buzz: RARE, BAYRY Win Approvals; SION Cuts Jobs, GSK Deals; AZN, RHHBY Lead</t>
+          <t>Pharma leaders call for stronger R&amp;D, resilient supply chains and greater patient access</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RTTNews</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.rttnews.com/amp/3692292/weekly-buzz-rare-bayry-win-approvals-sion-cuts-jobs-gsk-deals-azn-rhhby-lead.aspx</t>
+          <t>https://www.indianpharmapost.com/news/pharma-leaders-call-for-stronger-rd-resilient-supply-chains-and-greater-patient-access-21915</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>18-09-2026 14:44 UTC</t>
+          <t>19-09-2026 09:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>40% rider surge expected for 2026 Momentum Medical Scheme Cape Pioneer</t>
+          <t>Kotak Low Duration Fund(Ex) Standard-IDCW Weekly</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>The Citizen</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.citizen.co.za/network-news/network-sport/2026/09/19/40-rider-surge-expected-for-2026-momentum-medical-scheme-cape-pioneer/</t>
+          <t>https://m.economictimes.com/kotak-ultra-short-to-short-term-fund-standard-plan/mffactsheet/schemeid-7019.cms</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19-09-2026 06:21 UTC</t>
+          <t>19-09-2026 13:14 UTC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dr Reddy’s, Takeda Partner To Distribute First Approved Dengue Vaccine In India</t>
+          <t>Aurobindo Pharma Gets US FDA Approval for Asthma Inhaler</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>bwhealthcareworld.com</t>
+          <t>theindianpractitioner.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.bwhealthcareworld.com/article/dr-reddy-s-takeda-partner-to-distribute-first-approved-dengue-vaccine-in-india-624465</t>
+          <t>https://theindianpractitioner.com/aurobindo-pharma-gets-us-fda-approval-for-asthma-inhaler/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19-09-2026 03:55 UTC</t>
+          <t>19-09-2026 12:28 UTC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Laboratories Expands Gilead Collaboration for Once-Yearly Lenacapavir</t>
+          <t>Nifty Pharma Today: Up 0.57% in Early Trade</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chemical Industry Digest</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://chemindigest.com/dr-reddys-laboratories-expands-gilead-collaboration-for-once-yearly-lenacapavir/</t>
+          <t>https://univest.in/blogs/nifty-pharma-today-opening-bell-2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19-09-2026 05:30 UTC</t>
+          <t>19-09-2026 10:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>India First Dengue Vaccine Qdenga Launch Dr Reddy's &amp; Takeda Deal by 2027</t>
+          <t>Study Identifies Genetic Risk Factor for Lung Cancer in Never-Smokers</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sandesh</t>
+          <t>theindianpractitioner.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://sandesh.com/india/news/india-first-dengue-vaccine-qdenga-launch-dr-reddys-and-takeda-deal-by-2027</t>
+          <t>https://theindianpractitioner.com/study-identifies-genetic-risk-factor-for-lung-cancer-in-never-smokers/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>19-09-2026 05:17 UTC</t>
+          <t>19-09-2026 12:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dr Reddy’s secures India rights of Takeda’s dengue vax; prepares H1 2027 rollout</t>
+          <t>Quant Momentum Fund(G)-Direct Plan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>pharma.economictimes.indiatimes.com</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/dr-reddys-secures-india-rights-of-takedas-dengue-vax-prepares-h1-2027-rollout/134339913</t>
+          <t>https://univest.in/mutual-funds/quant-momentum-fund-g-direct-plan</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>18-09-2026 16:52 UTC</t>
+          <t>20-09-2026 00:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dr Reddy's, Takeda Ink Deal to Launch Dengue Vaccine QDENGA in India's Private Market in 2027</t>
+          <t>Quant Dynamic Asset Allocation Fund(G)-Direct Plan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/dr-reddys-takeda-ink-deal-to-launch-dengue-vaccine-qdenga-in-indias-private-market-in-2027-179524</t>
+          <t>https://univest.in/mutual-funds/quant-dynamic-asset-allocation-fund-g-direct-plan</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>18-09-2026 16:58 UTC</t>
+          <t>20-09-2026 01:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dr Reddy's to sell Takeda's German-made dengue vaccine, Takeda-Biological E manufacturing pact targets national immunisation programmes</t>
+          <t>Bank of India Mid Cap Fund(G)-Direct Plan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fortune India</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.fortuneindia.com/business-news/dr-reddys-to-sell-takedas-german-made-dengue-vaccine-takeda-biological-e-manufacturing-pact-targets-national-immunisation-programmes/160079</t>
+          <t>https://univest.in/mutual-funds/bank-of-india-mid-cap-fund-g-direct-plan</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>18-09-2026 15:39 UTC</t>
+          <t>19-09-2026 23:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Takeda partners Dr Reddy's to launch dengue vaccine Qdenga in India from 2027</t>
+          <t>Shilpa Medicare Hyderabad Unit Gets 1 Procedural Observation in USFDA Inspection</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/company/corporate-trends/takeda-partners-dr-reddys-to-launch-dengue-vaccine-qdenga-in-india-from-2027/articleshow/134342260.cms</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/shilpa-medicare-hyderabad-unit-gets-1-procedural-observation-in-usfda-inspection-179592</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>18-09-2026 18:31 UTC</t>
+          <t>19-09-2026 14:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>India’s first CDSCO-approved dengue vaccine coming in 2027: Dr Reddy’s to distribute QDENGA</t>
+          <t>Apple’s foldable debut gives Samsung Galaxy Z Fold8 a sales boost in Korea</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>theweek.in</t>
+          <t>Korea JoongAng Daily</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/health/2026/09/18/indias-first-cdsco-approved-dengue-vaccine-coming-in-2027-dr-reddys-to-distribute-qdenga.amp.html</t>
+          <t>https://www.koreajoongangdaily.com/business/apples-foldable-debut-gives-samsung-galaxy-z-fold8-a-sales-boost-in-korea/12883436</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>18-09-2026 15:59 UTC</t>
+          <t>20-09-2026 06:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dr Reddy’s inks pact with Takeda for rollout of dengue vaccine in India</t>
+          <t>The new iPhone is here, but you can buy the Samsung Galaxy S26 FE and get a $200 gift card for free</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/hyderabad/dr-reddys-inks-pact-with-takeda-for-rollout-of-dengue-vaccine-in-india/amp_articleshow/134336216.cms</t>
+          <t>https://mashable.com/tech/sept-11-samsung-galaxy-gift-card-deal</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>18-09-2026 17:41 UTC</t>
+          <t>20-09-2026 03:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dr Reddy's Confirms Gilead Licence Deal for Once-Yearly Lenacapavir for HIV Prevention</t>
+          <t>Samsung: India's AI Appliance Market Sees 9x Growth</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/dr-reddys-confirms-gilead-licence-deal-for-once-yearly-lenacapavir-for-hiv-prevention-179525</t>
+          <t>https://money.rediff.com/news/market/samsung-india-s-ai-appliance-market-sees-9x-growth/54660120260920</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>18-09-2026 17:15 UTC</t>
+          <t>20-09-2026 07:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NewsBytes</t>
+          <t>Samsung’s connected appliances in Southwest Asia jump nine-fold as India emerges as key AI market</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>The Tribune</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/exam-mentor/newsbytes-370/amp</t>
+          <t>https://www.moneycontrol.com/technology/samsung-s-connected-appliances-in-southwest-asia-jump-nine-fold-as-india-emerges-as-key-ai-market-article-14033788.html</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>18-09-2026 14:44 UTC</t>
+          <t>20-09-2026 07:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>India’s first approved dengue vaccine QDENGA likely to hit private market in 2027</t>
+          <t>Samsung, SK hynix near end of buybacks, leaving KOSPI without clear buyer</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>The South First</t>
+          <t>The Korea Times</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://thesouthfirst.com/health/indias-first-approved-dengue-vaccine-qdenga-likely-to-hit-private-market-in-2027/</t>
+          <t>https://www.koreatimes.co.kr/amp/economy/20260920/samsung-sk-hynix-near-end-of-buybacks-leaving-kospi-without-clear-buyer</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>18-09-2026 15:20 UTC</t>
+          <t>20-09-2026 06:01 UTC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Freshers Microbiology Jobs at Intas | Walk-In Drive</t>
+          <t>Samsung unveils AI and robotics strategy in the US — Korea Herald</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BioTecNika</t>
+          <t>UA.NEWS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.biotecnika.org/2026/09/intas-microbiology-fresher-job-walk-in-2026/</t>
+          <t>https://ua.news/en/technologies/samsung-predstavila-strategiiu-shi-ta-robototekhniki-v-ssha-korea-herald</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>18-09-2026 23:38 UTC</t>
+          <t>20-09-2026 06:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mall, Gift Card Cos. Can Get Fees In Payment IP Suit</t>
+          <t>Samsung Galaxy S27 Ultra Unveiled, 5700mAh Battery, 60W Charging</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>RS Web Solutions</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.law360.com/healthcare-authority/other/articles/2526760/mall-gift-card-cos-can-get-fees-in-payment-ip-suit</t>
+          <t>https://www.rswebsols.com/news/samsung-galaxy-s27-ultra-unveiled-5700mah-battery-60w-charging-and-additional-features/</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>18-09-2026 21:27 UTC</t>
+          <t>20-09-2026 07:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Leadership Is Not About Avoiding Hard Choices: Biocon's CHRO On Making The Layoff Call</t>
+          <t>Samsung Galaxy S27 Ultra Could Get the Upgrade Fans Have Been Waiting For to Beat the iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BW People</t>
+          <t>ascendants.in</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.bwpeople.in/article/leadership-is-not-about-avoiding-hard-choices-biocon-s-chro-on-making-the-layoff-call-624582</t>
+          <t>https://ascendants.in/industry_events/samsung-galaxy-s27-ultra-5700mah-battery-upgrade-iphone-18-pro-max/attachment/samsung-galaxy-s27-ultra/</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19-09-2026 11:07 UTC</t>
+          <t>20-09-2026 07:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pharma leaders call for stronger R&amp;D, resilient supply chains and greater patient access</t>
+          <t>Samsung Galaxy Tab S12+ and Tab S12 Ultra full specs leak with price and launch date</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Notebookcheck</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/pharma-leaders-call-for-stronger-rd-resilient-supply-chains-and-greater-patient-access-21915</t>
+          <t>https://www.notebookcheck.net/Samsung-Galaxy-Tab-S12-and-Tab-S12-Ultra-full-specs-leak-with-price-and-launch-date.1403188.0.html</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19-09-2026 09:39 UTC</t>
+          <t>19-09-2026 20:40 UTC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Gets US FDA Approval for Asthma Inhaler</t>
+          <t>India’s young consumers are giving Samsung’s AI appliance bet a big boost</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>The Indian Practitioner</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://theindianpractitioner.com/aurobindo-pharma-gets-us-fda-approval-for-asthma-inhaler/</t>
+          <t>https://m.economictimes.com/industry/cons-products/durables/indias-young-consumers-are-giving-samsungs-ai-appliance-bet-a-big-boost/amp_articleshow/134365163.cms</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19-09-2026 12:28 UTC</t>
+          <t>20-09-2026 08:05 UTC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>US Pharmacy Giant Walgreens to Set Up GCC in Chennai, Plans 250+ Jobs in First Year</t>
+          <t>Samsung could fast-track Galaxy Z TriFold 2 to compete with iPhone Duo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Mashable</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/us-pharmacy-giant-walgreens-to-set-up-gcc-in-chennai-plans-250-jobs-in-first-year-179526</t>
+          <t>https://mashable.com/tech/samsung-considering-trifold-2-to-compete-with-iphone-duo</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>18-09-2026 17:27 UTC</t>
+          <t>20-09-2026 02:42 UTC</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Orbis Ink Up to USD 1.4 Bn Deal to Develop Oral Cardiometabolic Therapies</t>
+          <t>Samsung Galaxy Z Fold8</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/novo-nordisk-orbis-ink-up-to-usd-14-bn-deal-to-develop-oral-cardiometabolic-therapies-179521</t>
+          <t>https://www.gsmarena.com/compare.php3?idPhone1=12074&amp;idPhone2=14673</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>18-09-2026 16:05 UTC</t>
+          <t>19-09-2026 21:06 UTC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dr Reddy's Confirms Gilead Licence Deal for Once-Yearly Lenacapavir for HIV Prevention</t>
+          <t>Compare Samsung Galaxy S25 vs. Apple iPhone 18 Pro Max</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>GSMArena.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/dr-reddys-confirms-gilead-licence-deal-for-once-yearly-lenacapavir-for-hiv-prevention-179525</t>
+          <t>https://www.gsmarena.com/compare.php3?idPhone1=13610&amp;idPhone2=14716</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>18-09-2026 17:15 UTC</t>
+          <t>19-09-2026 21:16 UTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi Sankyo's Enhertu Gets NICE Nod for NHS Use in England for HER2-Low Breast Cancer</t>
+          <t>KRX Healthcare shifts to large caps as Korea favors new-tech biomed - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/astrazeneca-daiichi-sankyos-enhertu-gets-nice-nod-for-nhs-use-in-england-for-her2-low-breast-cancer-179522</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/20/UYEIW47GOJA7XDOKS7M4MLXK6U/?outputType=amp</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>18-09-2026 16:40 UTC</t>
+          <t>19-09-2026 23:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Retired Tihar Jail Pharmacist Allegedly Duped of Rs 1.75 Cr, 1 Held</t>
+          <t>APAC Healthcare Weekly (Sept 20) –Sino Bio, Impact Therapeutics, Takeda, Daiichi Sankyo, SK Biopharm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Smartkarma</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/retired-tihar-jail-pharmacist-allegedly-duped-of-rs-175-cr-1-held-179523</t>
+          <t>https://www.smartkarma.com/insights/apac-healthcare-weekly-sept-20-sino-bio-impact-therapeutics-takeda-daiichi-sankyo-sk-biopharm</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>18-09-2026 16:48 UTC</t>
+          <t>20-09-2026 02:03 UTC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Unit VII inspection ends with one procedural observation</t>
+          <t>A court’s search for assets and the cost to corporate certainty</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>business-standard.com</t>
+          <t>Bar and Bench</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/markets/capital-market-news/shilpa-medicare-unit-vii-inspection-ends-with-one-procedural-observation-126091900148_1.html</t>
+          <t>https://www.barandbench.com/columns/a-courts-search-for-assets-and-the-cost-to-corporate-certainty</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19-09-2026 04:01 UTC</t>
+          <t>19-09-2026 09:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Colorcon Showcases Digital Development Tools, Advanced Analytics and Customized Excipient Systems</t>
+          <t>Zealand Pharma's Zeydovio Gets Positive EU Opinion for Short Bowel Syndrome, 65.7% Achieve Reduced...</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/live_from_shows/colorcon-showcases-digital-development-tools-advanced-analytics-and-customized-excipient-systems/</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/zealand-pharmas-zeydovio-gets-positive-eu-opinion-for-short-bowel-syndrome-657-achieve-reduced-parenteral-support-179581</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19-09-2026 08:08 UTC</t>
+          <t>19-09-2026 13:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Merck KGaA expands life science manufacturing hub in Bengaluru</t>
+          <t>Rachel A. Chiaverelli: A New Chapter in Oncology Translational Medicine at GSK</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BioProcess International</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.bioprocessintl.com/bioregions/merck-kgaa-expands-life-science-manufacturing-hub-in-bengaluru</t>
+          <t>https://oncodaily.com/career/rachel-a-chiaverelli-589517</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>18-09-2026 19:42 UTC</t>
+          <t>19-09-2026 19:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sharp Expands Autoinjector and Pen Assembly Capacity in U.S. and EU</t>
+          <t>AstraZeneca TAGRISSO cuts death risk 47% in early-stage lung cancer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/live_from_shows/sharp-expands-autoinjector-and-pen-assembly-capacity-in-u-s-and-eu/</t>
+          <t>https://scanx.trade/stock-market-news/companies/astrazeneca-tagrisso-cuts-death-risk-47-early-stage-lung-cancer-trial/50896313</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>19-09-2026 08:08 UTC</t>
+          <t>19-09-2026 11:32 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>mAbxience, Sandoz to Collaborate on Emicizumab Biosimilar Candidate</t>
+          <t>Nestle in FSSAI Legal Net After Baby Food Sample Found Substandard, 3 Cases Filed</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/mabxience-sandoz-to-collaborate-on-emicizumab-biosimilar-candidate/</t>
+          <t>https://medicaldialogues.in/amp/news/industry/pharma/nestle-in-fssai-legal-net-after-baby-food-sample-found-substandard-3-cases-filed-179567</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>18-09-2026 18:10 UTC</t>
+          <t>19-09-2026 11:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lisata Therapeutics to Acquire Marea, Agreeing to Concurrent $225M Private Placement</t>
+          <t>Teva Study: Providers Prioritize Tolerability Over Efficacy in Tardive Dyskinesia</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/lisata-therapeutics-to-acquire-marea-agreeing-to-concurrent-225m-private-placement/</t>
+          <t>https://www.clinicaltrialvanguard.com/news/teva-study-providers-prioritize-tolerability-over-efficacy-in-tardive-dyskinesia/</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18-09-2026 20:41 UTC</t>
+          <t>19-09-2026 12:31 UTC</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Roche Genentech Innovation Center Boston Opens, Expanding Companies’ US Research Presence</t>
+          <t>Withholding A Refund For Over A Decade Is Arbitrary To The Point Of Being Confiscatory: Delhi High Court Orders Rs 783 Crore TDS Refund To Teva Israel</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>LawChakra</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.contractpharma.com/breaking-news/roche-genentech-innovation-center-boston-opens-expanding-companies-us-research-presence/</t>
+          <t>https://lawchakra.in/high-court/delhi-high-court-teva-tds-refund-reassessment-quashed-protective-recovery-limitation/</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>18-09-2026 14:42 UTC</t>
+          <t>19-09-2026 08:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Shilpa Medicare: हैदराबाद यूनिट की USFDA जांच पूरी, मिला सिर्फ एक ऑब्जर्वेशन</t>
+          <t>Is the Teva Trailpeak as adventurous as its name suggests?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>whalesbook.com</t>
+          <t>Believe in the Run</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/corporate-news/Hindi/healthcarebiotech/Shilpa-Medicare-Receives-Single-Procedural-Observation-Following-USFDA-Inspection-at-Hyderabad-Unit/6aad3c15f2017017ae6da429</t>
+          <t>https://believeintherun.com/shoe-reviews/teva-trailpeak-review/</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>19-09-2026 02:14 UTC</t>
+          <t>19-09-2026 16:09 UTC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Shilpa Medicare: அமெரிக்காவின் USFDA ஆய்வில் ஒரு அவதானிப்பு; கம்பெனி விளக்கம் என்ன?</t>
+          <t>#Teva Announces New Olanzapine LAI (TEV-'749) Post Hoc Data Highlighting High Rates of Stabilization and Long-Term ...</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>whalesbook.com</t>
+          <t>Indovizka.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/corporate-news/Tamil/healthcarebiotech/Shilpa-Medicare-Receives-Single-Procedural-Observation-Following-USFDA-Inspection-at-Hyderabad-Unit/6aad3c15f2017017ae6da429</t>
+          <t>https://indovizka.com/news/detail/22862/teva-announces-new-olanzapine-lai-tev749-post-hoc-data-highlighting-high-rates-of-stabilization-and-longterm-</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>18-09-2026 22:48 UTC</t>
+          <t>20-09-2026 00:24 UTC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Samsung One UI 9 Rollout Schedule: Galaxy S25, Foldables</t>
+          <t>New Teva Study Identifies the Attributes that Healthcare Providers Prioritize when Selecting a Treatment for Tardive Dyskinesia in Older Patients</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>samsung.gadgethacks.com</t>
+          <t>riauone.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://samsung.gadgethacks.com/news/samsung-one-ui-9-rollout-schedule-galaxy-s25-foldables/</t>
+          <t>https://www.riauone.com/global/New-Teva-Study-Identifies-the-Attributes-that-Healthcare-Providers-Prioritize-when-Selecting-a-Treatment-for-Tardive-Dyskinesia-in-Older-Patients</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>19-09-2026 12:03 UTC</t>
+          <t>20-09-2026 01:11 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Five One UI 9 features you should try first</t>
+          <t>Sandoz and mAbxience Sign Emicizumab Biosimilar Agreement</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SamMobile</t>
+          <t>Pharmacy Business</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.sammobile.com/news/five-one-ui-9-features-you-should-try-first/</t>
+          <t>https://www.pharmacy.biz/sandoz-mabxience-emicizumab-biosimilar-agreement/</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>19-09-2026 10:48 UTC</t>
+          <t>19-09-2026 12:13 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Karnataka To Get New Samsung Innovation Campus For AI Skills</t>
+          <t>Enhancing Quality And Environmental Monitoring Efficiency Through Paperless Sampling</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>rediff.com</t>
+          <t>Bioprocess Online</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.rediff.com/news/report/samsung-innovation-campus-launched-in-karnataka-for-ai-skills/20260919.htm</t>
+          <t>https://www.bioprocessonline.com/doc/enhancing-quality-and-environmental-monitoring-efficiency-through-paperless-sampling-0001</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19-09-2026 13:43 UTC</t>
+          <t>20-09-2026 00:43 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S27 Ultra Leaks: 7,000mAh Battery and 2nm Chip Could Be Its Biggest Upgrades</t>
+          <t>Samsung Biologics labor talks seek fall deal as Korea mediator steps in - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ascendants.in</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://ascendants.in/spotlight/samsung-galaxy-s27-ultra-price-in-india-launch-date-specifications-7000mah-battery-camera-leaks/</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/20/ETB7FNLIN5CQNDK5CEXKTIF4MU/</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>19-09-2026 11:01 UTC</t>
+          <t>19-09-2026 23:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Best Samsung Galaxy phone deals: Save $250 at Amazon</t>
+          <t>[Breaking] Flames, smoke reported near Riyadh airport: Reuters</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mashable</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://mashable.com/tech/sept-11-samsung-galaxy-phone-deals</t>
+          <t>https://mbiz.heraldcorp.com/article/10879291</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>19-09-2026 10:09 UTC</t>
+          <t>19-09-2026 10:52 UTC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Android 17: Samsung rolls out One UI 9.0 to Galaxy S26, 26+, 26 Ultra</t>
+          <t>Kakao Says “Splitting Up Will Create More Value,” but Most Spin-Off Companies See Negative Growth</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Deccan Herald</t>
+          <t>IT조선</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/technology/android-17-samsung-rolls-out-one-ui-90-to-galaxy-s26-26-26-ultra-4151808</t>
+          <t>https://it.chosun.com/news/articleView.html?idxno=2023092170547</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19-09-2026 07:21 UTC</t>
+          <t>20-09-2026 05:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Samsung Electronics' union now only open to semiconductor workers</t>
+          <t>KRX Healthcare shifts to large caps as Korea favors new-tech biomed - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Korea JoongAng Daily</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.koreajoongangdaily.com/business/samsung-electronics-union-now-only-open-to-semiconductor-workers/12883234</t>
+          <t>https://biz.chosun.com/en/en-science/2026/09/20/UYEIW47GOJA7XDOKS7M4MLXK6U/?outputType=amp</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19-09-2026 07:08 UTC</t>
+          <t>19-09-2026 23:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Z Fold8 Ultra, Fold8 get 25% lower EMIs under Galaxy Forever plan</t>
+          <t>Gangwon Province links up with pet care facilities to ease chuseok travel for residents</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/technology/news/story/samsung-galaxy-z-fold8-ultra-fold8-get-25-lower-emis-under-galaxy-forever-plan-556457-2026-09-19</t>
+          <t>https://mbiz.heraldcorp.com/article/10879575</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19-09-2026 07:30 UTC</t>
+          <t>20-09-2026 04:44 UTC</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Samsung Galaxy Watch Blood Sugar Monitoring: New Patent</t>
+          <t>BREAKING: Cyclist Shin Ji-eun wins bronze, South Korea's first medal</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Business Outreach Magazine</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.businessoutreach.in/samsung-galaxy-watch-blood-sugar-monitoring/</t>
+          <t>https://mbiz.heraldcorp.com/article/10879489</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19-09-2026 12:29 UTC</t>
+          <t>20-09-2026 02:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The Samsung Galaxy Watch9 Wants to Tell You Everything About Your Body</t>
+          <t>Passenger who grabbed taxi driver's collar during political argument gets suspended sentence</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WIRED</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.wired.com/review/samsung-galaxy-watch9/</t>
+          <t>https://mbiz.heraldcorp.com/article/10879477</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>19-09-2026 10:08 UTC</t>
+          <t>20-09-2026 01:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S27 Pro and S27 Ultra's battery capacities and charging specs revealed - GSMArena.com news</t>
+          <t>(G)I-DLE's Soyeon addresses rumors of W1b monthly royalties</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GSMArena.com</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.gsmarena.com/samsung_galaxy_s27_pro_and_s27_ultras_battery_capacities_and_charging_spec_revealed-news-74677.php</t>
+          <t>https://mbiz.heraldcorp.com/article/10879404</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>18-09-2026 16:33 UTC</t>
+          <t>19-09-2026 23:39 UTC</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which Samsung Galaxy Z8 Foldable Should You Consider In Singapore? Local Media Shares More</t>
+          <t>Lotto draw No. 1242 winning numbers: 2, 4, 10, 16, 31, 41</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>news.samsung.com</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.samsung.com/sg/which-samsung-galaxy-z8-foldable-should-you-consider-in-singapore-local-media-shares-more</t>
+          <t>https://mbiz.heraldcorp.com/article/10879312</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>19-09-2026 10:27 UTC</t>
+          <t>19-09-2026 11:53 UTC</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Samsung and Google should copy these 3 things from the iPhone Duo</t>
+          <t>Korea Roller Sports Federation chief to serve as deputy chief of mission at 2026 Aichi-Nagoya Asian Games</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MakeUseOf</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.makeuseof.com/samsung-and-google-should-copy-these-3-things-from-the-iphone-duo/</t>
+          <t>https://mbiz.heraldcorp.com/article/10879305</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>19-09-2026 14:00 UTC</t>
+          <t>19-09-2026 11:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Samsung smartphone shipments worldwide quarterly 2010-2026</t>
+          <t>President Lee cheers on South Korean athletes at Asian Games opening</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Statista</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.statista.com/statistics/299144/samsung-smartphone-shipments-worldwide/</t>
+          <t>https://mbiz.heraldcorp.com/article/10879266</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>18-09-2026 15:23 UTC</t>
+          <t>19-09-2026 09:41 UTC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AstraZeneca, Daiichi Sankyo's Enhertu Gets NICE Nod for NHS Use in England for HER2-Low Breast Cancer</t>
+          <t>Gangnam District Mayor Kim Shares Chuseok Spirit, Making Songpyeon With Children</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/astrazeneca-daiichi-sankyos-enhertu-gets-nice-nod-for-nhs-use-in-england-for-her2-low-breast-cancer-179522</t>
+          <t>https://mbiz.heraldcorp.com/article/10879374</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>18-09-2026 16:40 UTC</t>
+          <t>19-09-2026 22:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Samsung Biologics</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Fortis Healthcare (NSE:FORTIS) Hospital Expansion and Supreme Court Petition Update</t>
+          <t>Jeju Air runs aviation safety classes for children at Seoul event</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>kalkine.co.in</t>
+          <t>헤럴드경제</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kalkine.co.in/article/healthcare/fortis-healthcare-nsefortis-expands-hospital-network-while-pursuing-legal-relief-in-daiichi-sankyo-matter</t>
+          <t>https://mbiz.heraldcorp.com/article/10879429</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>19-09-2026 06:47 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>A court’s search for assets and the cost to corporate certainty</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Bar and Bench</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>https://www.barandbench.com/columns/a-courts-search-for-assets-and-the-cost-to-corporate-certainty</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>19-09-2026 09:54 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Japan Approves T-DXd Combo and Dato-DXd for First-Line Metastatic Breast Cancer</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>CancerNetwork</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>https://www.cancernetwork.com/view/japan-approves-t-dxd-combo-and-dato-dxd-for-first-line-metastatic-breast-cancer</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>18-09-2026 19:11 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>AstraZeneca halts one lung cancer trial after mixed Phase 3 results</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>https://scanx.trade/stock-market-news/companies/astrazeneca-halts-one-lung-cancer-trial-mixed-phase-3-results/48530243</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>19-09-2026 02:26 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Enhertu receives EU recommendation for HER2-positive breast cancer</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>grafa.com</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>https://grafa.com/en/news/united-states/enhertu-eu-recommendation-her2-positive-breast-cancer</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>18-09-2026 16:50 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Articulate 2026 to bring biopharma leaders together around AI and scientific communication</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>150sec</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>https://150sec.com/articulate-2026-to-bring-biopharma-leaders-together-around-ai-and-scientific-communication/</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>18-09-2026 19:19 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>L-Lysine HCL Supplements Market Outlook to 2035</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>indexbox.io</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>https://www.indexbox.io/blog/l-lysine-hcl-supplements-market-outlook-to-2035/</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>18-09-2026 23:16 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Trump: Medicaid drug pricing deals reached for all 50 states</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>USA Today</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>https://www.usatoday.com/story/money/personal-finance/healthcare/2026/09/18/trump-announced-medicaid-drug-pricing-deals-for-50-states/91829280007/</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>18-09-2026 21:10 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>All 50 States Join Medicaid Drug Pricing Program: Trump</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>NTD News</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>https://www.ntd.com/all-50-states-join-medicaid-drug-pricing-program-trump_1173670.html</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>18-09-2026 21:17 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Trump: Most-Favored-Nation Drug Pricing Being Extended to State Medicaid Programs</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>breitbart.com</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>https://www.breitbart.com/politics/2026/09/18/trump-most-favored-nation-drug-pricing-being-extended-to-state-medicaid-programs/amp/</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>18-09-2026 23:46 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Colorcon Showcases Digital Development Tools, Advanced Analytics and Customized Excipient Systems</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Contract Pharma</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>https://www.contractpharma.com/live_from_shows/colorcon-showcases-digital-development-tools-advanced-analytics-and-customized-excipient-systems/</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>19-09-2026 08:08 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Ocrevus for Paediatric MS Gets CHMP EU Backing</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Voice of Healthcare</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>https://vohnetwork.com/news/pharma/chmp-backs-roche-s-ocrevus-for-paediatric-relapsing-multiple-sclerosis</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>19-09-2026 06:40 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Advanz Pharma</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>CHMP's September meeting highlights</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>AllSci</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>https://allsci.com/news/tecvayli-chmp-opinion-recommends-johnson-johnsons/</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>18-09-2026 16:46 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Teva Study: Providers Prioritize Tolerability Over Efficacy in Tardive Dyskinesia</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>The Clinical Trial Vanguard</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>https://www.clinicaltrialvanguard.com/news/teva-study-providers-prioritize-tolerability-over-efficacy-in-tardive-dyskinesia/</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>19-09-2026 12:31 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Israeli pharma giant Teva Israel wins tax battle before Delhi High Court against IT Department</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Bar and Bench</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>https://www.barandbench.com/news/litigation/israel-pharma-giant-teva-israel-wins-tax-battle-before-delhi-high-court-against-it-department</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>19-09-2026 06:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Withholding A Refund For Over A Decade Is Arbitrary To The Point Of Being Confiscatory: Delhi High Court Orders Rs 783 Crore TDS Refund To Teva Israel</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>lawchakra.in</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>https://lawchakra.in/high-court/delhi-high-court-teva-tds-refund-reassessment-quashed-protective-recovery-limitation/</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>19-09-2026 08:57 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Teva’s TEV-749 olanzapine LAI shows 80% stabilization rate in schizophrenia trial</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>The Clinical Trial Vanguard</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>https://www.clinicaltrialvanguard.com/news/tevas-tev-749-olanzapine-lai-shows-80-stabilization-rate-in-schizophrenia-trial/</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>19-09-2026 06:42 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Teva Pharmaceutical Industries Ltd</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Via Ritzau</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>https://via.ritzau.dk/pressemeddelelse/15171569/teva-pharmaceutical-industries-ltd?publisherId=90446&amp;lang=en</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>18-09-2026 20:32 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Teva Announces Positive Long-Term SOLARIS Data for Investigational Once-Monthly Olanzapine LAI TEV-'749 in Schizophrenia</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Quiver Quantitative</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>https://www.quiverquant.com/news/Teva+Announces+Positive+Long-Term+SOLARIS+Data+for+Investigational+Once-Monthly+Olanzapine+LAI+TEV-%27749+in+Schizophrenia</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>18-09-2026 20:40 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>TEVA Looks 80.2% Overvalued on GF Value™</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>GuruFocus</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>https://www.gurufocus.com/news/9088606/teva-looks-802-overvalued-on-gf-value</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>18-09-2026 21:36 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Teva shares Phase 3 data on once-monthly schizophrenia injection</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>StreetInsider</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>https://www.streetinsider.com/Corporate+News/Teva+shares+Phase+3+data+on+once-monthly+schizophrenia+injection/27080882.html</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>18-09-2026 21:00 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Is the Teva Trailpeak as adventurous as its name suggests?</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Believe in the Run</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>https://believeintherun.com/shoe-reviews/teva-trailpeak-review/</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>18-09-2026 19:23 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Sandoz and mAbxience Sign Emicizumab Biosimilar Agreement</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Pharmacy Business</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>https://www.pharmacy.biz/sandoz-mabxience-emicizumab-biosimilar-agreement/</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>19-09-2026 12:15 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Enhancing Quality And Environmental Monitoring Efficiency Through Paperless Sampling</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>bioprocessonline.com</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>https://www.bioprocessonline.com/doc/enhancing-quality-and-environmental-monitoring-efficiency-through-paperless-sampling-0001</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>19-09-2026 12:43 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>[Breaking] Flames, smoke reported near Riyadh airport: Reuters</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10879291</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>19-09-2026 10:52 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Addressing Barriers to Access for Today’s Cell and Gene Therapies</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Contract Pharma</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>https://www.contractpharma.com/exclusives/addressing-barriers-to-access-for-todays-cell-and-gene-therapies/</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>18-09-2026 15:17 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Gang posed as wedding guests to pocket gift-money refunds and meal vouchers</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10879088</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>19-09-2026 02:17 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>President Lee cheers on South Korean athletes at Asian Games opening</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10879266</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>19-09-2026 09:41 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>BTS, Blackpink earn additional nominations at 2026 MTV VMAs</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10879104</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>19-09-2026 02:34 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Gyeongil University's RE:ON volunteer corps holds community recovery event in Uiseong-gun</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10879129</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>19-09-2026 03:26 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Cheong Wa Dae says it 'respects' justice minister nominee Kim Seung-won's decision to withdraw</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10879113</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>19-09-2026 02:47 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>US-Denmark Greenland deal falls short of Trump's annexation vision, WSJ says</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10879187</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>19-09-2026 06:09 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Kim Seung-won to hold press conference at National Assembly amid mounting allegations</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>헤럴드경제</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>https://mbiz.heraldcorp.com/article/10879074</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>19-09-2026 01:49 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Samsung Biologics</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Antibody Contract Manufacturing Market to Reach USD 44.96 Billion by 2034, Growing at a CAGR of 9.96%</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>https://www.openpr.com/news/4636095/antibody-contract-manufacturing-market-to-reach-usd-44-96</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>18-09-2026 17:18 UTC</t>
+          <t>20-09-2026 00:11 UTC</t>
         </is>
       </c>
     </row>

--- a/news_results_raw.xlsx
+++ b/news_results_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,108 +458,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz and mAbxience Sign Emicizumab Biosimilar Agreement</t>
+          <t>Monensin Sodium Ionophore Market To 2035: Poultry Demand Drives 4.2% CAGR - News and Statistics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pharmacy Business</t>
+          <t>IndexBox</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pharmacy.biz/sandoz-mabxience-emicizumab-biosimilar-agreement/</t>
+          <t>https://www.indexbox.io/blog/monensin-sodium-ionophore-market-forecast-to-2035-poultry-coccidiostat-demand-drives-4-2-cagr/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19-09-2026 12:13 UTC</t>
+          <t>19-09-2026 15:56 UTC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sandoz Wins Canadian Approval for Generic Semaglutide, Targeting Growing GLP-1 Market</t>
+          <t>Pfizer to Share Revenue With HHS in Deal on Overseas Drug Prices</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/sandoz-wins-canadian-approval-for-generic-semaglutide-targeting-growing-glp-1-market</t>
+          <t>https://uk.finance.yahoo.com/news/pfizer-share-revenue-hhs-deal-211251182.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19-09-2026 13:00 UTC</t>
+          <t>19-09-2026 21:12 UTC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XLVets hails success of one health day event</t>
+          <t>Liver Injury FDA Warning for Tavneos Patients</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vet Times</t>
+          <t>Pharmacy Practice News</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.vettimes.com/news/business/practice-developments/xlvets-hails-success-of-one-health-day-event</t>
+          <t>https://www.pharmacypracticenews.com/Online-First/GI-Disorders/Article/09-26/Liver-Injury-FDA-Warning-for-Tavneos-Patients/81461</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19-09-2026 20:31 UTC</t>
+          <t>20-09-2026 06:47 UTC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>China’s economic expansion is reshaping Germany’s political landscape</t>
+          <t>Amgen Leads Strong Commercial Field into Irish Open Week at Doonbeg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tomorrow's Affairs</t>
+          <t>Sport for Business</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://tomorrowsaffairs.com/chinas-economic-expansion-is-reshaping-germanys-political-landscape</t>
+          <t>https://sportforbusiness.com/amgen-leads-strong-commercial-field-into-irish-open-week-at-doonbeg/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19-09-2026 11:42 UTC</t>
+          <t>19-09-2026 21:35 UTC</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Watch Amgen Irish Open (Final Round)</t>
+          <t>This is Irish golf’s greatest era — next year’s Ryder Cup could cap it</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Disney Plus</t>
+          <t>The Times</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.disneyplus.com/en-ai/browse/entity-31c39828-678b-47cd-a013-b0468014762e</t>
+          <t>https://www.thetimes.com/sport/irish/article/this-is-irish-golfs-greatest-era-next-years-ryder-cup-could-cap-it-nqphfp995</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19-09-2026 11:56 UTC</t>
+          <t>19-09-2026 20:58 UTC</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amgen Leads Strong Commercial Field into Irish Open Week at Doonbeg</t>
+          <t>‘You managed to hold onto the chain when there was clear jealousy that the one thing the President didn’t have was a chain’</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sport for Business</t>
+          <t>Clare Echo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://sportforbusiness.com/amgen-leads-strong-commercial-field-into-irish-open-week-at-doonbeg/</t>
+          <t>https://www.clareecho.ie/you-managed-to-hold-onto-the-chain-when-there-was-clear-jealousy-that-the-one-thing-the-president-didnt-have-was-a-chain/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19-09-2026 21:35 UTC</t>
+          <t>19-09-2026 15:07 UTC</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>This is Irish golf’s greatest era — next year’s Ryder Cup could cap it</t>
+          <t>Conor McKeon: Donald Trump didn’t reduce us to the role of sycophantic gobshites — we did that ourselves</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The Times</t>
+          <t>independent.ie</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.thetimes.com/sport/irish/article/this-is-irish-golfs-greatest-era-next-years-ryder-cup-could-cap-it-nqphfp995</t>
+          <t>https://www.independent.ie/sport/conor-mckeon-donald-trump-didnt-reduce-us-to-the-role-of-sycophantic-gobshites-we-did-that-ourselves/a/161572439.html</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19-09-2026 20:58 UTC</t>
+          <t>20-09-2026 05:30 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RTÉ Extends Irish Open Deal and Secures Ryder Cup Highlights for 2027</t>
+          <t>Irish Open &amp; Walker Cup success putts extra €20m into Clare economy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sport for Business</t>
+          <t>Clare Echo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://sportforbusiness.com/rte-extends-irish-open-deal-and-secures-ryder-cup-highlights-for-2027/</t>
+          <t>https://www.clareecho.ie/irish-open-walker-cup-success-putts-extra-e20m-into-clare-economy/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19-09-2026 10:33 UTC</t>
+          <t>20-09-2026 09:37 UTC</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>‘You managed to hold onto the chain when there was clear jealousy that the one thing the President didn’t have was a chain’</t>
+          <t>The Offaly Jesus Flag And Ireland's Love For Shane Lowry</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Clare Echo</t>
+          <t>Balls.ie</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.clareecho.ie/you-managed-to-hold-onto-the-chain-when-there-was-clear-jealousy-that-the-one-thing-the-president-didnt-have-was-a-chain/</t>
+          <t>https://www.balls.ie/golf/the-offaly-jesus-flag-and-irelands-love-for-shane-lowry-663513</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19-09-2026 15:07 UTC</t>
+          <t>19-09-2026 22:49 UTC</t>
         </is>
       </c>
     </row>
@@ -706,76 +706,76 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Conor McKeon: Donald Trump didn’t reduce us to the role of sycophantic gobshites — we did that ourselves</t>
+          <t>‘Rory McIlroy Rule’ Claims Threaten Major Shake-Up as PGA Tour’s New Points System Faces Heat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irish Independent</t>
+          <t>EssentiallySports</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.independent.ie/sport/conor-mckeon-donald-trump-didnt-reduce-us-to-the-role-of-sycophantic-gobshites-we-did-that-ourselves/a/161572439.html</t>
+          <t>https://www.essentiallysports.com/golf-news-rory-mcilroy-rule-claims-threaten-major-shake-up-as-pga-tours-new-points-system-faces-heat/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20-09-2026 05:30 UTC</t>
+          <t>19-09-2026 19:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Offaly Jesus Flag And Ireland's Love For Shane Lowry</t>
+          <t>Assam CM lays foundation stone for Adani Power’s Rs 48,000-crore thermal plant in Dhubri - India Tribune</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Balls.ie</t>
+          <t>India Tribune - Chicago</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.balls.ie/golf/the-offaly-jesus-flag-and-irelands-love-for-shane-lowry-663513</t>
+          <t>https://www.indiatribune.com/public/assam-cm-lays-foundation-stone-for-adani-powers-rs-48000-crore-thermal-plant-in-dhubri</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19-09-2026 22:49 UTC</t>
+          <t>20-09-2026 14:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>‘Rory McIlroy Rule’ Claims Threaten Major Shake-Up as PGA Tour’s New Points System Faces Heat</t>
+          <t>The secret pulse of plants</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EssentiallySports</t>
+          <t>newindianexpress.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.essentiallysports.com/golf-news-rory-mcilroy-rule-claims-threaten-major-shake-up-as-pga-tours-new-points-system-faces-heat/</t>
+          <t>https://www.newindianexpress.com/lifestyle/books/2026/Sep/20/the-secret-pulse-of-plants</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19-09-2026 19:54 UTC</t>
+          <t>20-09-2026 00:37 UTC</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The secret pulse of plants</t>
+          <t>5 hardy annuals to sow in September for early spring colour, including colourful cornflowers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>newindianexpress.com</t>
+          <t>countryliving.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/lifestyle/books/2026/Sep/20/the-secret-pulse-of-plants</t>
+          <t>https://www.countryliving.com/uk/homes-interiors/gardens/a73788786/hardy-annuals-plant-september/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20-09-2026 00:37 UTC</t>
+          <t>20-09-2026 05:37 UTC</t>
         </is>
       </c>
     </row>
@@ -814,22 +814,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>He went to Rajasthan to make a film in 1994. Years later, filmmaker Pradip Krishen was restoring a 70-hect</t>
+          <t>5 Plants that keep bugs out of your house</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>bona.co.za</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/international/us/he-went-to-rajasthan-to-make-a-film-in-1994-years-later-filmmaker-pradip-krishen-was-restoring-a-70-hectare-desert-landscape-by-removing-an-invasive-tree-and-bringing-native-ecology-back/articleshow/134357272.cms</t>
+          <t>https://www.bona.co.za/lifestyle/5-plants-that-keep-bugs-out-of-your-house/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19-09-2026 18:10 UTC</t>
+          <t>20-09-2026 11:11 UTC</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Can mycorrhizal fungi and rhizobacteria cut fertilizer use?</t>
+          <t>Kontomire Has Iron. But Is Your Body Getting It?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>agronews.com</t>
+          <t>Modern Ghana</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://agronews.com/us/en/news/agricultural-blog/2026-09-19/103943</t>
+          <t>https://www.modernghana.com/lifestyle/17480/kontomire-has-iron-but-is-your-body-getting.amp</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19-09-2026 17:06 UTC</t>
+          <t>20-09-2026 10:00 UTC</t>
         </is>
       </c>
     </row>
@@ -868,22 +868,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Your Hydrangeas Might Not Bloom Next Year If You Do This in Fall, a Gardening Pro Warns</t>
+          <t>He went to Rajasthan to make a film in 1994. Years later, filmmaker Pradip Krishen was restoring a 70-hect</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The Spruce</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.thespruce.com/pruning-new-wood-on-hydrangeas-12113453</t>
+          <t>https://m.economictimes.com/news/international/us/he-went-to-rajasthan-to-make-a-film-in-1994-years-later-filmmaker-pradip-krishen-was-restoring-a-70-hectare-desert-landscape-by-removing-an-invasive-tree-and-bringing-native-ecology-back/articleshow/134357272.cms</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20-09-2026 02:24 UTC</t>
+          <t>19-09-2026 18:10 UTC</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5 easy-to-grow hardy annuals to sow in September for early spring colour, including colourful cornflowers</t>
+          <t>Your Hydrangeas Might Not Bloom Next Year If You Do This in Fall, a Gardening Pro Warns</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Country Living Magazine</t>
+          <t>The Spruce</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.countryliving.com/uk/homes-interiors/gardens/a73788786/hardy-annuals-plant-september/</t>
+          <t>https://www.thespruce.com/pruning-new-wood-on-hydrangeas-12113453</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20-09-2026 04:43 UTC</t>
+          <t>20-09-2026 02:24 UTC</t>
         </is>
       </c>
     </row>
@@ -922,22 +922,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Are tea, coffee, red meat and alcohol giving you dangerous levels of iron?</t>
+          <t>Iron overload: how tea, coffee, red meat and alcohol can affect absorption</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1news.co.nz</t>
+          <t>Japan Today</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.1news.co.nz/2026/09/19/are-tea-coffee-red-meat-and-alcohol-giving-you-dangerous-levels-of-iron/</t>
+          <t>https://japantoday.com/category/features/health/Iron-overload-how-tea-coffee-red-meat-and-alcohol-can-affect-absorption</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19-09-2026 19:48 UTC</t>
+          <t>19-09-2026 19:10 UTC</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>You don’t need an acre to grow fresh fruit - these compact trees fit in almost any garden</t>
+          <t>Gabon bans all exports of iboga, with penalties to follow</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The English Garden</t>
+          <t>Benin Web TV</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.theenglishgarden.co.uk/gardens/small-gardens/best-fruit-trees-for-small-gardens/</t>
+          <t>https://beninwebtv.bj/en/gabon-bans-all-exports-of-iboga-with-penalties-to-follow/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19-09-2026 10:49 UTC</t>
+          <t>20-09-2026 13:56 UTC</t>
         </is>
       </c>
     </row>
@@ -976,22 +976,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Conservation mentor uses practical science to form a soil health playbook</t>
+          <t>Trump Announces Plans To Form Federal 'AI Force'</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>The Norfolk Daily News</t>
+          <t>KFBK News Radio</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://norfolkdailynews.com/agriculture/conservation-mentor-uses-practical-science-to-form-a-soil-health-playbook/article_03d08061-7a18-4278-8d35-859799367f5d.html</t>
+          <t>https://kfbk.iheart.com/content/2026-09-19-trump-announces-plans-to-form-federal-ai-force/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19-09-2026 17:06 UTC</t>
+          <t>20-09-2026 04:35 UTC</t>
         </is>
       </c>
     </row>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Trump Announces Plans To Form Federal 'AI Force'</t>
+          <t>Conservation mentor uses practical science to form a soil health playbook</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Talk 650 KSTE</t>
+          <t>The Norfolk Daily News</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://kste.iheart.com/content/2026-09-19-trump-announces-plans-to-form-federal-ai-force/</t>
+          <t>https://norfolkdailynews.com/agriculture/conservation-mentor-uses-practical-science-to-form-a-soil-health-playbook/article_03d08061-7a18-4278-8d35-859799367f5d.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20-09-2026 04:35 UTC</t>
+          <t>19-09-2026 17:06 UTC</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>vanguardngr.com</t>
+          <t>Vanguard News</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.vanguardngr.com/2026/09/moribund-benue-taraku-mills-crosses-80-rehabilitation-mark-production-begins-soon/</t>
+          <t>https://www.vanguardngr.com/2026/09/moribund-benue-taraku-mills-crosses-80-rehabilitation-mark-production-begins-soon/amp/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19-09-2026 22:06 UTC</t>
+          <t>19-09-2026 20:52 UTC</t>
         </is>
       </c>
     </row>
@@ -1084,76 +1084,76 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15 Plants that are banned or restricted in certain parts of the U.S.</t>
+          <t>Peugeot 308 could lose its hatchback shape as brand studies a 4.4 m fastback</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yahoo Creators</t>
+          <t>SpeedMe.ru</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://creators.yahoo.com/lifestyle/story/15-plants-that-are-banned-or-restricted-in-certain-parts-of-the-us-082400445.html</t>
+          <t>https://speedme.ru/en/ampposts/id79339-peugeot-308-could-lose-its-hatchback-shape-as-brand-studies-a-4-4-m-fastback</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>19-09-2026 08:24 UTC</t>
+          <t>20-09-2026 12:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Helen Chesnut's Garden Notes: What to make of this odd and challenging growing season?</t>
+          <t>Pfizer Quality Improvement Grant for System-Level Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Times Colonist</t>
+          <t>fundsforNGOs</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.timescolonist.com/homes/helen-chesnuts-garden-notes-what-to-make-of-this-odd-and-challenging-growing-season-12786467</t>
+          <t>https://www2.fundsforngos.org/research-2/pfizer-quality-improvement-grant-for-system-level-solutions/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19-09-2026 10:15 UTC</t>
+          <t>20-09-2026 11:04 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Third shift at Windsor Assembly Plant a sticking point as Unifor, Stellantis pause talks</t>
+          <t>Fake drugs: Karnataka cancels 16 licenses, suspends 8 including that of Pfizer depot</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Windsor Star</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://windsorstar.com/news/third-shift-at-windsor-assembly-plant-a-sticking-point-as-unifor-stellantis-pause-talks/</t>
+          <t>https://m.economictimes.com/news/india/fake-drugs-karnataka-cancels-16-licenses-suspends-8-including-that-of-pfizer-depot/articleshow/134369786.cms</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19-09-2026 13:05 UTC</t>
+          <t>20-09-2026 13:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pfizer to share higher overseas drug revenue with US health agency</t>
+          <t>From Padcev to PF-08634404: Pfizer's Oncology Growth Push</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>qz.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/world-news/pfizer-to-share-higher-overseas-drug-revenue-with-us-health-agency-126092000066_1.html</t>
+          <t>https://qz.com/from-padcev-to-pf-08634404-pfizer-s-oncology-growth-push</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20-09-2026 02:34 UTC</t>
+          <t>20-09-2026 09:08 UTC</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1219,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>Pfizer to share higher overseas drug revenue with US health agency</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.medicaleconomics.com/view/pfizer-s-lyme-disease-vaccine-shows-70-efficacy-texas-man-sentenced-to-12-5-years-in-61-5m-medicare-telemarketing-fraud-scheme-novo-nordisk-launches-wegovy-subscription-model-morning-medical-update</t>
+          <t>https://www.business-standard.com/world-news/pfizer-to-share-higher-overseas-drug-revenue-with-us-health-agency-126092000066_1.html</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19-09-2026 13:00 UTC</t>
+          <t>20-09-2026 02:34 UTC</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Secret contracts reveal undisclosed terms in Trump’s drug-pricing deals</t>
+          <t>Karnataka Fake Drug Racket: 16 Pharmacy Licences Cancelled, Action Against Pfizer C&amp;F Depot</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>News18</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.washingtonpost.com/politics/2026/09/19/secret-contracts-reveal-undisclosed-terms-trumps-drug-pricing-deals/</t>
+          <t>https://www.news18.com/amp/cities/bengaluru-news/karnataka-bidadis-fake-drug-racket-16-pharmacy-licences-cancelled-action-against-pfizer-cf-depot-ws-klt-10342692.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19-09-2026 17:00 UTC</t>
+          <t>20-09-2026 13:03 UTC</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>US renews West Asia travel alert, warns Iran conflict may escalate rapidly</t>
+          <t>Spurious Drug Racket Busted At Farmhouse In Karnataka's Bidadi, 24 Pharma Licences Face Action</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>ETV Bharat</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/world-news/us-renews-west-asia-travel-alert-warns-iran-conflict-may-escalate-rapidly-126092000072_1.html</t>
+          <t>https://www.etvbharat.com/en/state/spurious-drug-racket-busted-in-bidadi-enn26092004141</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20-09-2026 02:50 UTC</t>
+          <t>20-09-2026 13:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1300,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nothing is Stopping Office-to-Resi Conversions in NYC</t>
+          <t>Karnataka: 16 licences cancelled over suspected fake drug supply</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>The Real Deal</t>
+          <t>The Siasat Daily</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://therealdeal.com/new-york/2026/09/19/nothing-is-stopping-office-to-resi-conversions-in-nyc/</t>
+          <t>https://www.siasat.com/karnataka-16-licences-cancelled-over-suspected-fake-drug-supply-3545404/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19-09-2026 13:00 UTC</t>
+          <t>20-09-2026 14:36 UTC</t>
         </is>
       </c>
     </row>
@@ -1327,130 +1327,130 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Public Health Officers’ Strike Leaves Kenya Vulnerable to El Niño Disease Outbreaks</t>
+          <t>Secret contracts reveal undisclosed terms in Trump’s drug-pricing deals</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vellum Kenya</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://vellum.co.ke/public-health-officers-strike-leaves-kenya-vulnerable-to-el-nino-disease-outbreaks/</t>
+          <t>https://www.washingtonpost.com/politics/2026/09/19/secret-contracts-reveal-undisclosed-terms-trumps-drug-pricing-deals/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19-09-2026 10:47 UTC</t>
+          <t>19-09-2026 17:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gerald Laubach Obituary (01/21/1926 - 08/31/2026) - New London, NH - The Day</t>
+          <t>Anthony Wallace Joins Sun Pharma as SVP &amp; Chief Commercial Officer, U.S. Innovative Medicines</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Legacy obituary</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.legacy.com/us/obituaries/theday/name/gerald-laubach-obituary?id=62497124</t>
+          <t>https://hrtoday.in/anthony-wallace-joins-sun-pharma-as-svp-chief-commercial-officer-u-s-innovative-medicines/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20-09-2026 04:53 UTC</t>
+          <t>19-09-2026 16:10 UTC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Trump Administration Secret Drug Deals Reveal Undisclosed Terms</t>
+          <t>Takeda, Dr. Reddy’s sign agreement for QDENGA dengue vaccine in India</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SuaraGarut.ID</t>
+          <t>MediaBrief</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://suaragarut.id/en/trump-admin-secret-drug-deals</t>
+          <t>https://mediabrief.com/takeda-dr-reddys-deal/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19-09-2026 15:29 UTC</t>
+          <t>20-09-2026 09:57 UTC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Anthony Wallace Joins Sun Pharma as SVP &amp; Chief Commercial Officer, U.S. Innovative Medicines</t>
+          <t>Top 10 pharma firms sustain volume growth as smaller rivals struggle</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://hrtoday.in/anthony-wallace-joins-sun-pharma-as-svp-chief-commercial-officer-u-s-innovative-medicines/</t>
+          <t>https://www.business-standard.com/amp/industry/news/top-10-pharma-firms-sustain-volume-growth-as-smaller-rivals-struggle-126092000581_1.html</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19-09-2026 16:10 UTC</t>
+          <t>20-09-2026 12:50 UTC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>40% rider surge expected for 2026 Momentum Medical Scheme Cape Pioneer</t>
+          <t>Apollo Hospitals Founder, 93, On What Makes Him Show Up For Work Every Day</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>The Citizen</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.citizen.co.za/network-news/network-sport/2026/09/19/40-rider-surge-expected-for-2026-momentum-medical-scheme-cape-pioneer/</t>
+          <t>https://www.ndtv.com/health/apollo-hospitals-founder-93-on-what-makes-him-show-up-for-work-every-day-12071904</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19-09-2026 12:27 UTC</t>
+          <t>20-09-2026 09:39 UTC</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AIOCD Opposes Mandatory CCTV At Pharmacies, Flags Rs 1 Lakh Cost Burden On Small Chemists</t>
+          <t>Sensex, Nifty open lower amid rising crude oil prices, West Asia tensions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>DD News</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/aiocd-opposes-mandatory-cctv-at-pharmacies-flags-rs-1-lakh-cost-burden-on-small-chemists-179588</t>
+          <t>https://ddnews.gov.in/en/sensex-nifty-open-lower-amid-rising-crude-oil-prices-west-asia-tensions/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19-09-2026 13:53 UTC</t>
+          <t>20-09-2026 02:49 UTC</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nifty Pharma Today: Up 0.57% in Early Trade</t>
+          <t>ENTOD Pharmaceuticals secures patent for its insulin eye drop</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://univest.in/blogs/nifty-pharma-today-opening-bell-2026</t>
+          <t>https://economictimes.indiatimes.com/industry/healthcare/biotech/pharmaceuticals/entod-pharmaceuticals-secures-patent-for-its-insulin-eye-drop/articleshow/134359748.cms</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19-09-2026 10:57 UTC</t>
+          <t>19-09-2026 19:05 UTC</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Manorama Industries completes postal ballot dispatch for independent director appointment</t>
+          <t>Local doctor who delivers babies writes first novel</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Dayton Daily News</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/manorama-industries-seeks-shareholder-nod-dr-rohini-tiwari-appointment/51273622</t>
+          <t>https://www.daytondailynews.com/community/community-gems/local-doctor-who-delivers-babies-writes-first-novel/article_48567f5b-3e57-5051-8bd7-3506a1e8b3e3.html</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19-09-2026 14:14 UTC</t>
+          <t>20-09-2026 06:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Local doctor who delivers babies writes first novel</t>
+          <t>Dengue Vaccine Qdenga Coming To India: Doses, Efficacy And India Launch Timeline Explained</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dayton Daily News</t>
+          <t>ABP Live English</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.daytondailynews.com/community/community-gems/local-doctor-who-delivers-babies-writes-first-novel/article_48567f5b-3e57-5051-8bd7-3506a1e8b3e3.html</t>
+          <t>https://news.abplive.com/health/dengue-vaccine-qdenga-coming-to-india-doses-efficacy-and-india-launch-timeline-explained-1867545</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20-09-2026 06:00 UTC</t>
+          <t>20-09-2026 11:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1570,427 +1570,427 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zealand Pharma's Zeydovio Gets Positive EU Opinion for Short Bowel Syndrome, 65.7% Achieve Reduced...</t>
+          <t>After decades of waiting, India gets its first Dengue vaccine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Mathrubhumi English</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/amp/news/industry/pharma/zealand-pharmas-zeydovio-gets-positive-eu-opinion-for-short-bowel-syndrome-657-achieve-reduced-parenteral-support-179581</t>
+          <t>https://english.mathrubhumi.com/amp/lifestyle/health/qdenga-dengue-vaccine-india-2027-lm4j6xvx</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19-09-2026 13:00 UTC</t>
+          <t>20-09-2026 06:59 UTC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ENTOD Pharmaceuticals secures patent for its insulin eye drop</t>
+          <t>Top 10 pharma firms sustain volume growth as smaller rivals struggle</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://economictimes.indiatimes.com/industry/healthcare/biotech/pharmaceuticals/entod-pharmaceuticals-secures-patent-for-its-insulin-eye-drop/articleshow/134359748.cms</t>
+          <t>https://www.business-standard.com/amp/industry/news/top-10-pharma-firms-sustain-volume-growth-as-smaller-rivals-struggle-126092000581_1.html</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19-09-2026 19:05 UTC</t>
+          <t>